--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -120,7 +120,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
@@ -181,6 +181,13 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1015,7 +1022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G375"/>
+  <dimension ref="A1:G379"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col width="17.5703125" customWidth="1" style="2" min="1" max="1"/>
@@ -1111,12 +1118,14 @@
           <t>Fraction of Child and Adult Premature Mortality by Demographic Trait</t>
         </is>
       </c>
+      <c r="D3" s="7" t="n"/>
+      <c r="E3" s="7" t="n"/>
       <c r="F3" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G3" s="24" t="inlineStr">
         <is>
           <t>You wish to include premature mortality break-outs by sex, race, or ethnicity among your model outputs.</t>
         </is>
@@ -1138,12 +1147,14 @@
           <t>Fraction of Infant Premature Mortality by Demographic Trait</t>
         </is>
       </c>
+      <c r="D4" s="7" t="n"/>
+      <c r="E4" s="7" t="n"/>
       <c r="F4" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>You wish to include premature mortality break-outs by sex, race, or ethnicity among your model outputs.</t>
         </is>
@@ -1165,11 +1176,14 @@
           <t>Health Outcome Incidence per Ton Pollutant</t>
         </is>
       </c>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
       <c r="F5" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G5" s="26" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1187,11 +1201,14 @@
           <t>Number of Households</t>
         </is>
       </c>
+      <c r="D6" s="7" t="n"/>
+      <c r="E6" s="7" t="n"/>
       <c r="F6" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G6" s="26" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
       <c r="A7" s="2" t="inlineStr">
@@ -1209,12 +1226,14 @@
           <t>Quantization Size for Health Outcomes</t>
         </is>
       </c>
+      <c r="D7" s="7" t="n"/>
+      <c r="E7" s="7" t="n"/>
       <c r="F7" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="G7" s="24" t="inlineStr">
         <is>
           <t>Rounding error is visible in health outcome graphs when no policies are enabled.</t>
         </is>
@@ -1236,11 +1255,14 @@
           <t>Social Cost of Carbon</t>
         </is>
       </c>
+      <c r="D8" s="7" t="n"/>
+      <c r="E8" s="7" t="n"/>
       <c r="F8" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G8" s="26" t="n"/>
     </row>
     <row r="9" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="inlineStr">
@@ -1258,14 +1280,14 @@
           <t>Value of a Statistical Life</t>
         </is>
       </c>
-      <c r="D9" s="17" t="n"/>
-      <c r="E9" s="17" t="n"/>
+      <c r="D9" s="27" t="n"/>
+      <c r="E9" s="27" t="n"/>
       <c r="F9" s="18" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G9" s="17" t="n"/>
+      <c r="G9" s="28" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1283,11 +1305,14 @@
           <t>BAU Amount Spent on Building Components</t>
         </is>
       </c>
+      <c r="D10" s="7" t="n"/>
+      <c r="E10" s="7" t="n"/>
       <c r="F10" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G10" s="26" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -1305,11 +1330,14 @@
           <t>BAU Components Energy Use</t>
         </is>
       </c>
+      <c r="D11" s="7" t="n"/>
+      <c r="E11" s="7" t="n"/>
       <c r="F11" s="12" t="inlineStr">
         <is>
           <t>very high</t>
         </is>
       </c>
+      <c r="G11" s="26" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -1327,11 +1355,14 @@
           <t>BAU Data Center Load</t>
         </is>
       </c>
+      <c r="D12" s="7" t="n"/>
+      <c r="E12" s="7" t="n"/>
       <c r="F12" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G12" s="26" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -1349,11 +1380,14 @@
           <t>BAU Distributed Electricity Source Capacity</t>
         </is>
       </c>
+      <c r="D13" s="7" t="n"/>
+      <c r="E13" s="7" t="n"/>
       <c r="F13" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G13" s="26" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="A14" s="2" t="inlineStr">
@@ -1371,12 +1405,14 @@
           <t>BAU Fraction of Components Sold by Quality Level</t>
         </is>
       </c>
+      <c r="D14" s="7" t="n"/>
+      <c r="E14" s="7" t="n"/>
       <c r="F14" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="G14" s="24" t="inlineStr">
         <is>
           <t>You plan on using the building component rebate policy lever</t>
         </is>
@@ -1398,11 +1434,14 @@
           <t>BAU Perc Subsidy for Distributed Solar PV Capacity</t>
         </is>
       </c>
+      <c r="D15" s="7" t="n"/>
+      <c r="E15" s="7" t="n"/>
       <c r="F15" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G15" s="26" t="n"/>
     </row>
     <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="inlineStr">
@@ -1420,16 +1459,18 @@
           <t>Bldg Retrofitting E Savings and Costs</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D16" s="1" t="inlineStr">
         <is>
           <t>Percent Energy Savings from Retrofitting by Component, Retrofitting Cost per Unit Energy Saved</t>
         </is>
       </c>
+      <c r="E16" s="7" t="n"/>
       <c r="F16" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G16" s="26" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
       <c r="A17" s="2" t="inlineStr">
@@ -1447,12 +1488,14 @@
           <t>Change in Distributed Electricity Source Capacity This Year</t>
         </is>
       </c>
+      <c r="D17" s="7" t="n"/>
+      <c r="E17" s="7" t="n"/>
       <c r="F17" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G17" s="24" t="inlineStr">
         <is>
           <t>You plan on using a policy mandated change in distributed solar capacity additions</t>
         </is>
@@ -1474,11 +1517,14 @@
           <t>Component Lifetime</t>
         </is>
       </c>
+      <c r="D18" s="7" t="n"/>
+      <c r="E18" s="7" t="n"/>
       <c r="F18" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G18" s="26" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="A19" s="2" t="inlineStr">
@@ -1496,16 +1542,18 @@
           <t>Cost per Unit Distributed Solar Capacity</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D19" s="1" t="inlineStr">
         <is>
           <t>Cost per Unit Distributed Solar Capacity, Soft Costs per Unit Distributed Solar Capacity</t>
         </is>
       </c>
+      <c r="E19" s="7" t="n"/>
       <c r="F19" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G19" s="26" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1523,11 +1571,14 @@
           <t>Elasticity of Building Service Demand wrt Energy Cost</t>
         </is>
       </c>
+      <c r="D20" s="7" t="n"/>
+      <c r="E20" s="7" t="n"/>
       <c r="F20" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G20" s="26" t="n"/>
     </row>
     <row r="21" ht="30" customHeight="1">
       <c r="A21" s="2" t="inlineStr">
@@ -1545,11 +1596,14 @@
           <t>Elasticity of Component Energy Demand wrt Energy Cost</t>
         </is>
       </c>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
       <c r="F21" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G21" s="26" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1567,11 +1621,14 @@
           <t>Elasticity of Component Price wrt Energy Use</t>
         </is>
       </c>
+      <c r="D22" s="7" t="n"/>
+      <c r="E22" s="7" t="n"/>
       <c r="F22" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G22" s="26" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
       <c r="A23" s="2" t="inlineStr">
@@ -1589,11 +1646,14 @@
           <t>Elasticity of Distributed Solar Deployment wrt Subsidy Perc</t>
         </is>
       </c>
+      <c r="D23" s="7" t="n"/>
+      <c r="E23" s="7" t="n"/>
       <c r="F23" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G23" s="26" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1611,11 +1671,14 @@
           <t>Fraction of Buildings Owned by Entity</t>
         </is>
       </c>
+      <c r="D24" s="7" t="n"/>
+      <c r="E24" s="7" t="n"/>
       <c r="F24" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G24" s="26" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
       <c r="A25" s="2" t="inlineStr">
@@ -1633,11 +1696,14 @@
           <t>Incremental Cost per Unit Energy for Electrified Builidng Equipment</t>
         </is>
       </c>
+      <c r="D25" s="7" t="n"/>
+      <c r="E25" s="7" t="n"/>
       <c r="F25" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G25" s="26" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1655,11 +1721,14 @@
           <t>Max Distrib Solar Capacity</t>
         </is>
       </c>
+      <c r="D26" s="7" t="n"/>
+      <c r="E26" s="7" t="n"/>
       <c r="F26" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G26" s="26" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
       <c r="A27" s="2" t="inlineStr">
@@ -1677,12 +1746,14 @@
           <t>Market Share Changes due to Rebate Program by Quality Level</t>
         </is>
       </c>
+      <c r="D27" s="7" t="n"/>
+      <c r="E27" s="7" t="n"/>
       <c r="F27" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr">
+      <c r="G27" s="24" t="inlineStr">
         <is>
           <t>You plan on using the building component rebate policy lever</t>
         </is>
@@ -1704,11 +1775,14 @@
           <t>Percentage Components Fuel Use Reduction for Electricity</t>
         </is>
       </c>
+      <c r="D28" s="7" t="n"/>
+      <c r="E28" s="7" t="n"/>
       <c r="F28" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G28" s="26" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
       <c r="A29" s="2" t="inlineStr">
@@ -1726,12 +1800,14 @@
           <t>Perc E Use Difference from Std by Quality Level</t>
         </is>
       </c>
+      <c r="D29" s="7" t="n"/>
+      <c r="E29" s="7" t="n"/>
       <c r="F29" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr">
+      <c r="G29" s="24" t="inlineStr">
         <is>
           <t>You plan on using the building component rebate policy lever (otherwise set to zero)</t>
         </is>
@@ -1753,11 +1829,14 @@
           <t>Potential Percentage Eff Improvement due to Improved Contractor Edu and Training</t>
         </is>
       </c>
+      <c r="D30" s="7" t="n"/>
+      <c r="E30" s="7" t="n"/>
       <c r="F30" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G30" s="26" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
@@ -1775,11 +1854,14 @@
           <t>Potential Percentage Eff Improvement due to Improved Labeling</t>
         </is>
       </c>
+      <c r="D31" s="7" t="n"/>
+      <c r="E31" s="7" t="n"/>
       <c r="F31" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G31" s="26" t="n"/>
     </row>
     <row r="32" ht="45" customHeight="1">
       <c r="A32" s="2" t="inlineStr">
@@ -1797,12 +1879,14 @@
           <t>Recipient Buildings Fuel Fractions</t>
         </is>
       </c>
+      <c r="D32" s="7" t="n"/>
+      <c r="E32" s="7" t="n"/>
       <c r="F32" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr">
+      <c r="G32" s="24" t="inlineStr">
         <is>
           <t>You want this policy lever to be something other than a buildings electrification policy (e.g. shift to hydrogen, etc.)</t>
         </is>
@@ -1816,17 +1900,24 @@
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>RPfFBSCC</t>
+          <t>RPbBCT</t>
         </is>
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>Repayment Period for Financing Buildings Sector Capital Costs</t>
-        </is>
-      </c>
+          <t>Rebate Percentage by Building Component Type</t>
+        </is>
+      </c>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G33" s="26" t="inlineStr">
+        <is>
+          <t>You plan on using the building component rebate policy lever</t>
         </is>
       </c>
     </row>
@@ -1838,24 +1929,22 @@
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>RPbBCT</t>
+          <t>RPfFBSCC</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Rebate Percentage by Building Component Type</t>
-        </is>
-      </c>
+          <t>Repayment Period for Financing Buildings Sector Capital Costs</t>
+        </is>
+      </c>
+      <c r="D34" s="7" t="n"/>
+      <c r="E34" s="7" t="n"/>
       <c r="F34" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>You plan on using the building component rebate policy lever</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G34" s="24" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
       <c r="A35" s="2" t="inlineStr">
@@ -1873,11 +1962,14 @@
           <t>Share of Buildings Capital and Installation Costs by ISIC Code</t>
         </is>
       </c>
+      <c r="D35" s="7" t="n"/>
+      <c r="E35" s="7" t="n"/>
       <c r="F35" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G35" s="26" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1895,11 +1987,14 @@
           <t>Share of Building Retrofit Costs Borne by Government</t>
         </is>
       </c>
+      <c r="D36" s="7" t="n"/>
+      <c r="E36" s="7" t="n"/>
       <c r="F36" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G36" s="26" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1917,11 +2012,14 @@
           <t>Share of Components Energy Use that is New This Year</t>
         </is>
       </c>
+      <c r="D37" s="7" t="n"/>
+      <c r="E37" s="7" t="n"/>
       <c r="F37" s="14" t="inlineStr">
         <is>
           <t>to be determined via calibration</t>
         </is>
       </c>
+      <c r="G37" s="26" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -1939,11 +2037,14 @@
           <t>Share of Distriuted Solar Costs by Recipient ISIC Code</t>
         </is>
       </c>
+      <c r="D38" s="7" t="n"/>
+      <c r="E38" s="7" t="n"/>
       <c r="F38" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G38" s="26" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -1961,7 +2062,8 @@
           <t>Start Year Components Energy Use</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="D39" s="7" t="n"/>
+      <c r="E39" s="1" t="inlineStr">
         <is>
           <t>BCEU</t>
         </is>
@@ -1971,6 +2073,7 @@
           <t>very high</t>
         </is>
       </c>
+      <c r="G39" s="26" t="n"/>
     </row>
     <row r="40" ht="15.75" customHeight="1" thickBot="1">
       <c r="A40" s="17" t="inlineStr">
@@ -1988,8 +2091,8 @@
           <t>Start Year Distributed Electricity Capacity</t>
         </is>
       </c>
-      <c r="D40" s="17" t="n"/>
-      <c r="E40" s="17" t="inlineStr">
+      <c r="D40" s="27" t="n"/>
+      <c r="E40" s="27" t="inlineStr">
         <is>
           <t>BDEQ</t>
         </is>
@@ -1999,7 +2102,7 @@
           <t>high</t>
         </is>
       </c>
-      <c r="G40" s="17" t="n"/>
+      <c r="G40" s="28" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -2017,11 +2120,14 @@
           <t>BAU CCS Subsidy</t>
         </is>
       </c>
+      <c r="D41" s="7" t="n"/>
+      <c r="E41" s="7" t="n"/>
       <c r="F41" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G41" s="26" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
       <c r="A42" s="2" t="inlineStr">
@@ -2039,16 +2145,18 @@
           <t>BAU Fraction of CCS Potential Achieved by Industry</t>
         </is>
       </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="D42" s="1" t="inlineStr">
         <is>
           <t>BAU Fraction of CCS Potential Achieved by Industry Energy, BAU Fraction of CCS Potential Achieved by Industry Process</t>
         </is>
       </c>
+      <c r="E42" s="7" t="n"/>
       <c r="F42" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G42" s="26" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -2066,11 +2174,14 @@
           <t>Biomass with CCS Storage per MWh</t>
         </is>
       </c>
+      <c r="D43" s="7" t="n"/>
+      <c r="E43" s="7" t="n"/>
       <c r="F43" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G43" s="26" t="n"/>
     </row>
     <row r="44" ht="120" customHeight="1">
       <c r="A44" s="2" t="inlineStr">
@@ -2088,16 +2199,18 @@
           <t>CCS Calculations</t>
         </is>
       </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="D44" s="1" t="inlineStr">
         <is>
           <t>CC Capital Cost of Industrial Energy CCS Equipment, CC Capital Cost of Industrial Process CCS Equipment, CC Capital Cost of Industrial Hydrogen Sector CCS Equipment, CC CCS Total O&amp;M Cost per Ton Industrial Energy CO2 Sequestered, CC CCS Total O&amp;M Cost per Ton Industrial Process CO2 Sequestered, CC CCS Total O&amp;M Cost per Ton Hydrogen Sector CO2 Sequestered, CC Energy Use per Ton Industrial Energy CO2 Sequestered, CC Energy Use per Ton Industrial Process CO2 Sequestered, CC Energy Use per Ton Hydrogen Sector CO2 Sequestered</t>
         </is>
       </c>
+      <c r="E44" s="7" t="n"/>
       <c r="F44" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G44" s="26" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
       <c r="A45" s="2" t="inlineStr">
@@ -2115,16 +2228,18 @@
           <t>CO2 Capture Potentials</t>
         </is>
       </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="D45" s="1" t="inlineStr">
         <is>
           <t>CO2 Capture Potential by Electricity Source, CO2 Capture Potential by Industry,CO2 Capture Potential by Hydrogen Sector</t>
         </is>
       </c>
+      <c r="E45" s="7" t="n"/>
       <c r="F45" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G45" s="26" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -2142,11 +2257,14 @@
           <t>CCS Transportation and Storage Cost and Subsidies</t>
         </is>
       </c>
+      <c r="D46" s="7" t="n"/>
+      <c r="E46" s="7" t="n"/>
       <c r="F46" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G46" s="26" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -2164,11 +2282,14 @@
           <t>Cost Effective CCS Retrofit Capacity by Industry</t>
         </is>
       </c>
+      <c r="D47" s="7" t="n"/>
+      <c r="E47" s="7" t="n"/>
       <c r="F47" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G47" s="26" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -2186,11 +2307,14 @@
           <t>CCS Retrofit Deployment Time</t>
         </is>
       </c>
+      <c r="D48" s="7" t="n"/>
+      <c r="E48" s="7" t="n"/>
       <c r="F48" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G48" s="26" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -2208,12 +2332,14 @@
           <t>Non BAU Industry CCS Subsidy</t>
         </is>
       </c>
+      <c r="D49" s="7" t="n"/>
+      <c r="E49" s="7" t="n"/>
       <c r="F49" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr">
+      <c r="G49" s="24" t="inlineStr">
         <is>
           <t>You plan on using the non-BAU CCS subsidy boolean lever</t>
         </is>
@@ -2235,11 +2361,14 @@
           <t>Share of Cost Effective CCS Retrofit Construction Started in a Year</t>
         </is>
       </c>
+      <c r="D50" s="7" t="n"/>
+      <c r="E50" s="7" t="n"/>
       <c r="F50" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G50" s="26" t="n"/>
     </row>
     <row r="51" ht="30.75" customFormat="1" customHeight="1" s="17" thickBot="1">
       <c r="A51" s="17" t="inlineStr">
@@ -2257,11 +2386,14 @@
           <t>Share of CCS Transportation and Storage Costs by Recipient ISIC Code</t>
         </is>
       </c>
+      <c r="D51" s="7" t="n"/>
+      <c r="E51" s="7" t="n"/>
       <c r="F51" s="20" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G51" s="26" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -2279,11 +2411,14 @@
           <t>Discount Rate</t>
         </is>
       </c>
+      <c r="D52" s="7" t="n"/>
+      <c r="E52" s="7" t="n"/>
       <c r="F52" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G52" s="26" t="n"/>
     </row>
     <row r="53" ht="30.75" customHeight="1" thickBot="1">
       <c r="A53" s="17" t="inlineStr">
@@ -2301,14 +2436,14 @@
           <t>Quantization Size for Cash Flows</t>
         </is>
       </c>
-      <c r="D53" s="17" t="n"/>
-      <c r="E53" s="17" t="n"/>
+      <c r="D53" s="27" t="n"/>
+      <c r="E53" s="27" t="n"/>
       <c r="F53" s="22" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G53" s="17" t="inlineStr">
+      <c r="G53" s="28" t="inlineStr">
         <is>
           <t>Rounding error is visible in final web app output graphs in near-zero changes in cash flows</t>
         </is>
@@ -2330,14 +2465,14 @@
           <t>Quantization Size for Pollutants</t>
         </is>
       </c>
-      <c r="D54" s="17" t="n"/>
-      <c r="E54" s="17" t="n"/>
+      <c r="D54" s="27" t="n"/>
+      <c r="E54" s="27" t="n"/>
       <c r="F54" s="22" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G54" s="17" t="inlineStr">
+      <c r="G54" s="28" t="inlineStr">
         <is>
           <t>Rounding error is visible in final web app output graphs in near-zero changes in pollutants</t>
         </is>
@@ -2359,12 +2494,14 @@
           <t>Boolean Are Electricity Prices Affected by Changes in Production Costs</t>
         </is>
       </c>
+      <c r="D55" s="7" t="n"/>
+      <c r="E55" s="7" t="n"/>
       <c r="F55" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr">
+      <c r="G55" s="24" t="inlineStr">
         <is>
           <t>You are modeling a region where electricity prices are fixed, and electricity suppliers are expected to absorb any increases or decreases in cost without passing on these costs or savings to electricity buyers</t>
         </is>
@@ -2386,12 +2523,14 @@
           <t>Boolean Disable Carbon Tax Border Adjustment</t>
         </is>
       </c>
+      <c r="D56" s="7" t="n"/>
+      <c r="E56" s="7" t="n"/>
       <c r="F56" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr">
+      <c r="G56" s="24" t="inlineStr">
         <is>
           <t>You wish to disable carbon tax border adjustments</t>
         </is>
@@ -2413,12 +2552,14 @@
           <t>Boolean Disable Macroeconomic Feedback Loops</t>
         </is>
       </c>
+      <c r="D57" s="7" t="n"/>
+      <c r="E57" s="7" t="n"/>
       <c r="F57" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
+      <c r="G57" s="24" t="inlineStr">
         <is>
           <t>You wish to examine the model behavior while excluding indirect effects of the enabled policies on demand for energy-using services (mostly useful for isolating bugs, not intended to be used in production versions of the EPS)</t>
         </is>
@@ -2440,12 +2581,14 @@
           <t>Boolean Exempt Process Emissions from Carbon Tax</t>
         </is>
       </c>
+      <c r="D58" s="7" t="n"/>
+      <c r="E58" s="7" t="n"/>
       <c r="F58" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr">
+      <c r="G58" s="24" t="inlineStr">
         <is>
           <t>You want carbon pricing to only apply to energy-related emissions, exempting non-energy emissions associated with industrial, agricultural, and waste management operations</t>
         </is>
@@ -2467,12 +2610,14 @@
           <t>Boolean Elec Suppliers Have Foresight of Future RPS Values</t>
         </is>
       </c>
+      <c r="D59" s="7" t="n"/>
+      <c r="E59" s="7" t="n"/>
       <c r="F59" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr">
+      <c r="G59" s="24" t="inlineStr">
         <is>
           <t>You want electricity suppliers to have foresight of future RPS values in order to ramp up more quickly to a given target</t>
         </is>
@@ -2494,12 +2639,14 @@
           <t>Boolean Include Emissions from Exported Electricity</t>
         </is>
       </c>
+      <c r="D60" s="7" t="n"/>
+      <c r="E60" s="7" t="n"/>
       <c r="F60" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr">
+      <c r="G60" s="24" t="inlineStr">
         <is>
           <t>You wish to include the emissions associated with the generation of exported electricity (which occur inside the modeled region) from the modeled region's emissions outputs.  (The default is enabled.)</t>
         </is>
@@ -2521,12 +2668,14 @@
           <t>Boolean Include Emissions from Imported Electricity</t>
         </is>
       </c>
+      <c r="D61" s="7" t="n"/>
+      <c r="E61" s="7" t="n"/>
       <c r="F61" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr">
+      <c r="G61" s="24" t="inlineStr">
         <is>
           <t>You wish to include the emissions associated with the generation of imported electricity (which occur outside the modeled region) in the modeled region's emissions outputs  (The default is disabled.)</t>
         </is>
@@ -2548,12 +2697,14 @@
           <t>Boolean Rebate Carbon Tax on Exported Products</t>
         </is>
       </c>
+      <c r="D62" s="7" t="n"/>
+      <c r="E62" s="7" t="n"/>
       <c r="F62" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr">
+      <c r="G62" s="24" t="inlineStr">
         <is>
           <t>You wish for the government to rebate carbon taxes charged on exported products.  (This is only relevant when carbon tax border adjustments are enabled.  See ctrl-settings/BDCTBA)</t>
         </is>
@@ -2575,12 +2726,14 @@
           <t>Boolean Use Capacity Market for New Capacity Revenue</t>
         </is>
       </c>
+      <c r="D63" s="7" t="n"/>
+      <c r="E63" s="7" t="n"/>
       <c r="F63" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr">
+      <c r="G63" s="24" t="inlineStr">
         <is>
           <t>You wish the electricity sector to only collect capacity costs for new capacity and not pay them out to all resources in the market.</t>
         </is>
@@ -2602,12 +2755,14 @@
           <t>Boolean Use Twenty Year GWP Values</t>
         </is>
       </c>
+      <c r="D64" s="7" t="n"/>
+      <c r="E64" s="7" t="n"/>
       <c r="F64" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr">
+      <c r="G64" s="24" t="inlineStr">
         <is>
           <t>You wish to use 20-year GWP values instead of 100-year GWP values for GHGs (other than F-gases)</t>
         </is>
@@ -2629,12 +2784,14 @@
           <t>Data Center Load Growth Assumptions</t>
         </is>
       </c>
+      <c r="D65" s="7" t="n"/>
+      <c r="E65" s="7" t="n"/>
       <c r="F65" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr">
+      <c r="G65" s="24" t="inlineStr">
         <is>
           <t>You wish to use a low- or high-growth forecast for data centers in your region.</t>
         </is>
@@ -2656,12 +2813,14 @@
           <t>Exogenous GDP Growth Rate Adjustment, Boolean Use Exogenous GDP Growth Rate Adjustment</t>
         </is>
       </c>
+      <c r="D66" s="7" t="n"/>
+      <c r="E66" s="7" t="n"/>
       <c r="F66" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr">
+      <c r="G66" s="24" t="inlineStr">
         <is>
           <t>You need to adjust model-wide energy use due to events not accounted for in your energy use input data, such as a major recession that is too recent to yet be reflected in your energy use data.</t>
         </is>
@@ -2683,11 +2842,14 @@
           <t>Elasticity of Sectoral Energy Use with respect to GDP in Recession</t>
         </is>
       </c>
+      <c r="D67" s="7" t="n"/>
+      <c r="E67" s="7" t="n"/>
       <c r="F67" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G67" s="26" t="n"/>
     </row>
     <row r="68" ht="45" customHeight="1">
       <c r="A68" s="2" t="inlineStr">
@@ -2705,12 +2867,14 @@
           <t>First Year Impacted by Future Policies</t>
         </is>
       </c>
+      <c r="D68" s="7" t="n"/>
+      <c r="E68" s="7" t="n"/>
       <c r="F68" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr">
+      <c r="G68" s="24" t="inlineStr">
         <is>
           <t>2025 ends // or // you wish to model the impact of a policy package that will be passed in years after the present year (e.g., what if the next administration does XYZ)</t>
         </is>
@@ -2732,17 +2896,18 @@
           <t>Government Revenue Accounting</t>
         </is>
       </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="D69" s="1" t="inlineStr">
         <is>
           <t>GRA for Carbon Tax Revenue, GRA for CCS Subsidy, GRA for Fuel Tax Revenue, GRA for EV Subsidy, GRA for Vehicle Battery Subsidy, GRA for Electricity Generation Subsidies, GRA for Electricity Capacity Construction Subsidies, GRA for Distributed Solar Subsidy, GRA for Fuel Subsidies, GRA for National Debt Interest, GRA for Remaining Government Cash Flow Changes</t>
         </is>
       </c>
+      <c r="E69" s="7" t="n"/>
       <c r="F69" s="6" t="inlineStr">
         <is>
           <t>n/a (control lever)</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr">
+      <c r="G69" s="24" t="inlineStr">
         <is>
           <t>You wish to adjust the default mechanisms by which government accounts for increases or decreases to its cash flow.  This is only relevant for empty, newly-created scenarios made by model users.</t>
         </is>
@@ -2764,7 +2929,8 @@
           <t>Industry Category with Industry-wide Load Factor</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="D70" s="7" t="n"/>
+      <c r="E70" s="1" t="inlineStr">
         <is>
           <t>elec/SHELF</t>
         </is>
@@ -2774,7 +2940,7 @@
           <t>optional</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr">
+      <c r="G70" s="24" t="inlineStr">
         <is>
           <t>You wish to use industry-specific load factors for any industry categories. In the U.S. model, we use industry-specific load factors for ag/forestry and refining.</t>
         </is>
@@ -2796,11 +2962,14 @@
           <t>Model Run Vintage</t>
         </is>
       </c>
+      <c r="D71" s="7" t="n"/>
+      <c r="E71" s="7" t="n"/>
       <c r="F71" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G71" s="26" t="n"/>
     </row>
     <row r="72" ht="15.75" customHeight="1" thickBot="1">
       <c r="A72" s="17" t="inlineStr">
@@ -2818,14 +2987,14 @@
           <t>Modeled Vintage</t>
         </is>
       </c>
-      <c r="D72" s="17" t="n"/>
-      <c r="E72" s="17" t="n"/>
+      <c r="D72" s="27" t="n"/>
+      <c r="E72" s="27" t="n"/>
       <c r="F72" s="19" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="G72" s="17" t="n"/>
+      <c r="G72" s="28" t="n"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -2843,11 +3012,14 @@
           <t>BAU Fraction of Heat from CHP</t>
         </is>
       </c>
+      <c r="D73" s="7" t="n"/>
+      <c r="E73" s="7" t="n"/>
       <c r="F73" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G73" s="26" t="n"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -2865,11 +3037,14 @@
           <t>BAU Fraction of Heat Provided by Fuel</t>
         </is>
       </c>
+      <c r="D74" s="7" t="n"/>
+      <c r="E74" s="7" t="n"/>
       <c r="F74" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G74" s="26" t="n"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -2887,11 +3062,14 @@
           <t>CHP Equipment Cost per Unit Energy Shifted</t>
         </is>
       </c>
+      <c r="D75" s="7" t="n"/>
+      <c r="E75" s="7" t="n"/>
       <c r="F75" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G75" s="26" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -2909,11 +3087,14 @@
           <t>Efficiency of Conversion to Usable Heat</t>
         </is>
       </c>
+      <c r="D76" s="7" t="n"/>
+      <c r="E76" s="7" t="n"/>
       <c r="F76" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G76" s="26" t="n"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -2931,11 +3112,14 @@
           <t>Heat Distribution Losses</t>
         </is>
       </c>
+      <c r="D77" s="7" t="n"/>
+      <c r="E77" s="7" t="n"/>
       <c r="F77" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G77" s="26" t="n"/>
     </row>
     <row r="78" ht="30.75" customHeight="1" thickBot="1">
       <c r="A78" s="17" t="inlineStr">
@@ -2953,14 +3137,14 @@
           <t>Recipient Heat Fuel Fractions</t>
         </is>
       </c>
-      <c r="D78" s="17" t="n"/>
-      <c r="E78" s="17" t="n"/>
+      <c r="D78" s="27" t="n"/>
+      <c r="E78" s="27" t="n"/>
       <c r="F78" s="21" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G78" s="17" t="inlineStr">
+      <c r="G78" s="28" t="inlineStr">
         <is>
           <t>You want this policy lever to shift to a fuel other than hydrogen</t>
         </is>
@@ -2982,11 +3166,14 @@
           <t>BAU Ban New Power Plants This Year</t>
         </is>
       </c>
+      <c r="D79" s="7" t="n"/>
+      <c r="E79" s="7" t="n"/>
       <c r="F79" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G79" s="26" t="n"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -3004,11 +3191,14 @@
           <t>BAU Ban Power Plant Retrofits This Year</t>
         </is>
       </c>
+      <c r="D80" s="7" t="n"/>
+      <c r="E80" s="7" t="n"/>
       <c r="F80" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G80" s="26" t="n"/>
     </row>
     <row r="81" ht="45" customHeight="1">
       <c r="A81" s="2" t="inlineStr">
@@ -3026,16 +3216,18 @@
           <t>BAU Cost of Electricity Sector Capital</t>
         </is>
       </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="D81" s="1" t="inlineStr">
         <is>
           <t>BAU Cost of Electricity Sector Capital for Power Plants, BAU Cost of Electricity Sector Capital for Other Investments, BAU Cost of Electricity Sector Capital for Distributed Solar Investments</t>
         </is>
       </c>
+      <c r="E81" s="7" t="n"/>
       <c r="F81" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G81" s="26" t="n"/>
     </row>
     <row r="82" ht="30" customHeight="1">
       <c r="A82" s="2" t="inlineStr">
@@ -3053,16 +3245,18 @@
           <t>Battery Cost per Unit Capacity</t>
         </is>
       </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="D82" s="1" t="inlineStr">
         <is>
           <t>Battery Power Cost per Unit Capacity, Battery Energy Cost per Unit Capacity, Battery Balance of System Cost as Share of First Year Cost</t>
         </is>
       </c>
+      <c r="E82" s="7" t="n"/>
       <c r="F82" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G82" s="26" t="n"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -3080,11 +3274,14 @@
           <t>BAU Capacity Retirements before Quantization</t>
         </is>
       </c>
+      <c r="D83" s="7" t="n"/>
+      <c r="E83" s="7" t="n"/>
       <c r="F83" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G83" s="26" t="n"/>
     </row>
     <row r="84" ht="30" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -3102,11 +3299,14 @@
           <t>Boolean Does This Plant Type Use Maximum Capacity Factor</t>
         </is>
       </c>
+      <c r="D84" s="7" t="n"/>
+      <c r="E84" s="7" t="n"/>
       <c r="F84" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G84" s="26" t="n"/>
     </row>
     <row r="85" ht="45" customHeight="1">
       <c r="A85" s="2" t="inlineStr">
@@ -3124,16 +3324,18 @@
           <t>BAU EV Grid Balancing</t>
         </is>
       </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="D85" s="1" t="inlineStr">
         <is>
           <t>Fraction of EVs Used for Grid Balancing on Average Day, Fraction of EV Battery Capacity Used for Grid Balancing when EV is Used for Grid Balancing</t>
         </is>
       </c>
+      <c r="E85" s="7" t="n"/>
       <c r="F85" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G85" s="26" t="n"/>
     </row>
     <row r="86" ht="45" customHeight="1">
       <c r="A86" s="2" t="inlineStr">
@@ -3151,12 +3353,14 @@
           <t>BAU Guaranteed Dispatch Percentage by Electricity Source</t>
         </is>
       </c>
+      <c r="D86" s="7" t="n"/>
+      <c r="E86" s="7" t="n"/>
       <c r="F86" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr">
+      <c r="G86" s="24" t="inlineStr">
         <is>
           <t>You are modeling a region where power plants are dispatched based on non-market rules rather than by least marginal cost</t>
         </is>
@@ -3178,16 +3382,18 @@
           <t>BAU Heat Rates and Start Year Capacities</t>
         </is>
       </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="D87" s="1" t="inlineStr">
         <is>
           <t>BAU Heat Rates, BAU Start Year Capacities</t>
         </is>
       </c>
+      <c r="E87" s="7" t="n"/>
       <c r="F87" s="12" t="inlineStr">
         <is>
           <t>very high</t>
         </is>
       </c>
+      <c r="G87" s="26" t="n"/>
     </row>
     <row r="88">
       <c r="A88" s="2" t="inlineStr">
@@ -3205,11 +3411,14 @@
           <t>BAU Pumped Hydro Capacity</t>
         </is>
       </c>
+      <c r="D88" s="7" t="n"/>
+      <c r="E88" s="7" t="n"/>
       <c r="F88" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G88" s="26" t="n"/>
     </row>
     <row r="89" ht="75" customHeight="1">
       <c r="A89" s="2" t="inlineStr">
@@ -3227,12 +3436,14 @@
           <t>BAU Policy Mandated Capacity Construction Schedule</t>
         </is>
       </c>
+      <c r="D89" s="7" t="n"/>
+      <c r="E89" s="7" t="n"/>
       <c r="F89" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr">
+      <c r="G89" s="24" t="inlineStr">
         <is>
           <t>You know particular capacities of particular types of plants will come online in particular years (for example, they are already under construction), or you are modeling a region where power plant construction decisions are based on government mandates rather than being market-driven</t>
         </is>
@@ -3254,12 +3465,14 @@
           <t>BAU Policy Mandated Capacity Retrofit Schedule</t>
         </is>
       </c>
+      <c r="D90" s="7" t="n"/>
+      <c r="E90" s="7" t="n"/>
       <c r="F90" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr">
+      <c r="G90" s="24" t="inlineStr">
         <is>
           <t>You know particular capacities of particular types of plants will be retrofit with CCUS in particular years (for example, they are already under construction), or you are modeling a region where power plant retrofit decisions are based on government mandates rather than being market-driven</t>
         </is>
@@ -3281,11 +3494,14 @@
           <t>BAU Policy Mandated Grid Battery Storage Additions</t>
         </is>
       </c>
+      <c r="D91" s="7" t="n"/>
+      <c r="E91" s="7" t="n"/>
       <c r="F91" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G91" s="26" t="n"/>
     </row>
     <row r="92">
       <c r="A92" s="2" t="inlineStr">
@@ -3303,11 +3519,14 @@
           <t>BAU Pwr Plnt Elec Own Use Perc</t>
         </is>
       </c>
+      <c r="D92" s="7" t="n"/>
+      <c r="E92" s="7" t="n"/>
       <c r="F92" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G92" s="26" t="n"/>
     </row>
     <row r="93" ht="30" customHeight="1">
       <c r="A93" s="2" t="inlineStr">
@@ -3325,11 +3544,14 @@
           <t>BAU Percent Subsidy per Unit Grid Battery Capacity Deployed</t>
         </is>
       </c>
+      <c r="D93" s="7" t="n"/>
+      <c r="E93" s="7" t="n"/>
       <c r="F93" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G93" s="26" t="n"/>
     </row>
     <row r="94">
       <c r="A94" s="2" t="inlineStr">
@@ -3347,12 +3569,12 @@
           <t>BAU RPS Data by Subregion</t>
         </is>
       </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="D94" s="1" t="inlineStr">
         <is>
           <t>BAU RPS Percentages by Subregion, BAU Electricity Shares by Subregion</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E94" s="1" t="inlineStr">
         <is>
           <t>RQSD</t>
         </is>
@@ -3362,6 +3584,7 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G94" s="26" t="n"/>
     </row>
     <row r="95">
       <c r="A95" s="2" t="inlineStr">
@@ -3379,11 +3602,14 @@
           <t>BAU Subsidy for Grid Battery Production</t>
         </is>
       </c>
+      <c r="D95" s="7" t="n"/>
+      <c r="E95" s="7" t="n"/>
       <c r="F95" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G95" s="26" t="n"/>
     </row>
     <row r="96" ht="30" customHeight="1">
       <c r="A96" s="2" t="inlineStr">
@@ -3401,11 +3627,14 @@
           <t>BAU Subsidy per Unit Electricity Supplied to the Grid by Grid Batteries</t>
         </is>
       </c>
+      <c r="D96" s="7" t="n"/>
+      <c r="E96" s="7" t="n"/>
       <c r="F96" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G96" s="26" t="n"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -3423,11 +3652,14 @@
           <t>BAU Transmission and Distribution Loss Percentage</t>
         </is>
       </c>
+      <c r="D97" s="7" t="n"/>
+      <c r="E97" s="7" t="n"/>
       <c r="F97" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G97" s="26" t="n"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -3445,11 +3677,14 @@
           <t>BAU Zero Emis Credit for Nuc Plants</t>
         </is>
       </c>
+      <c r="D98" s="7" t="n"/>
+      <c r="E98" s="7" t="n"/>
       <c r="F98" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G98" s="26" t="n"/>
     </row>
     <row r="99" ht="75" customHeight="1">
       <c r="A99" s="2" t="inlineStr">
@@ -3467,16 +3702,18 @@
           <t>Capacity Construction and Maintenance Costs</t>
         </is>
       </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="D99" s="1" t="inlineStr">
         <is>
           <t>Annual CapEx per Unit Capacity, BAU Construction Cost per Unit Capacity, Annual Fixed O&amp;M Cost per Unit Capacity, Variable O&amp;M Cost per Unit Elec Output, BAU Soft Costs per Unit Capacity, Annual CapEx per Unit Capacity, Spur Line Construction Cost per Unit Capacity, BAU CCS Retrofit Costs per Unit Capacity</t>
         </is>
       </c>
+      <c r="E99" s="7" t="n"/>
       <c r="F99" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G99" s="26" t="n"/>
     </row>
     <row r="100" ht="30" customHeight="1">
       <c r="A100" s="2" t="inlineStr">
@@ -3494,11 +3731,14 @@
           <t>Clean Dispatchable Resource Demand for Reliability Curve Parameters</t>
         </is>
       </c>
+      <c r="D100" s="7" t="n"/>
+      <c r="E100" s="7" t="n"/>
       <c r="F100" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G100" s="26" t="n"/>
     </row>
     <row r="101" ht="75" customHeight="1">
       <c r="A101" s="2" t="inlineStr">
@@ -3516,12 +3756,14 @@
           <t>Capacity Retirements before Quantization</t>
         </is>
       </c>
+      <c r="D101" s="7" t="n"/>
+      <c r="E101" s="7" t="n"/>
       <c r="F101" s="6" t="inlineStr">
         <is>
           <t>n/a (policy lever)</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr">
+      <c r="G101" s="24" t="inlineStr">
         <is>
           <t>You wish to switch from the BAU plant retirement schedule to an alternative schedule you have specified in input data (rather than using the early retirement policy lever, which accelerates retirements and is additive to the BAU retirements)</t>
         </is>
@@ -3543,11 +3785,14 @@
           <t>Cap Ret per Unit Net Loss</t>
         </is>
       </c>
+      <c r="D102" s="7" t="n"/>
+      <c r="E102" s="7" t="n"/>
       <c r="F102" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G102" s="26" t="n"/>
     </row>
     <row r="103" ht="90" customHeight="1">
       <c r="A103" s="2" t="inlineStr">
@@ -3565,16 +3810,18 @@
           <t>Capacity Supply Curve</t>
         </is>
       </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="D103" s="1" t="inlineStr">
         <is>
           <t>Capacity Supply Curve Capacity Cost Multiplier vs Share of Exisiting Capacity Built This Year, Capacity Supply Curve Minimum Buildable Capacity for Plant Types with No Exisiting Capacity, Capacity Supply Curve Share of Cost Effective Capacity Built in a Single Year, Capacity Supply Curve Share of Cost Effective Hybrid Capacity Built in a Single Year</t>
         </is>
       </c>
+      <c r="E103" s="7" t="n"/>
       <c r="F103" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G103" s="26" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
       <c r="A104" s="2" t="inlineStr">
@@ -3592,11 +3839,14 @@
           <t>Distribution Construction Cost per Unit Increase in Peak Load</t>
         </is>
       </c>
+      <c r="D104" s="7" t="n"/>
+      <c r="E104" s="7" t="n"/>
       <c r="F104" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G104" s="26" t="n"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -3614,11 +3864,14 @@
           <t>Decommissioning Cost per Unit Capacity</t>
         </is>
       </c>
+      <c r="D105" s="7" t="n"/>
+      <c r="E105" s="7" t="n"/>
       <c r="F105" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G105" s="26" t="n"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -3636,11 +3889,14 @@
           <t>Dispatch Priority by Electricity Source</t>
         </is>
       </c>
+      <c r="D106" s="7" t="n"/>
+      <c r="E106" s="7" t="n"/>
       <c r="F106" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G106" s="26" t="n"/>
     </row>
     <row r="107" ht="30" customHeight="1">
       <c r="A107" s="2" t="inlineStr">
@@ -3658,16 +3914,18 @@
           <t>Demand Response Capacities</t>
         </is>
       </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="D107" s="1" t="inlineStr">
         <is>
           <t>BAU Demand Response Capacity, Potential Additional Demand Response Capacity, Average DR Hours per DR Event</t>
         </is>
       </c>
+      <c r="E107" s="7" t="n"/>
       <c r="F107" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G107" s="26" t="n"/>
     </row>
     <row r="108" ht="30" customHeight="1">
       <c r="A108" s="2" t="inlineStr">
@@ -3685,16 +3943,18 @@
           <t>Demand Response Costs</t>
         </is>
       </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="D108" s="1" t="inlineStr">
         <is>
           <t>Annual Cost per Unit Demand Response Capacity, Share of DR by Provider</t>
         </is>
       </c>
+      <c r="E108" s="7" t="n"/>
       <c r="F108" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G108" s="26" t="n"/>
     </row>
     <row r="109" ht="30" customHeight="1">
       <c r="A109" s="2" t="inlineStr">
@@ -3712,16 +3972,18 @@
           <t>Electricity Imports and Exports</t>
         </is>
       </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="D109" s="1" t="inlineStr">
         <is>
           <t>BAU Imported Electricity, BAU Exported Electricity, Imported Electricity Price, BAU Exported Electricity Price</t>
         </is>
       </c>
+      <c r="E109" s="7" t="n"/>
       <c r="F109" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G109" s="26" t="n"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -3739,16 +4001,18 @@
           <t>Electricity Storage Technology Round-Trip Efficiency</t>
         </is>
       </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="D110" s="1" t="inlineStr">
         <is>
           <t>Grid Battery Rount-Trip Efficiency, Pumped Hydro Round-Trip Efficiency</t>
         </is>
       </c>
+      <c r="E110" s="7" t="n"/>
       <c r="F110" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G110" s="26" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -3766,11 +4030,14 @@
           <t>Elec Sources Used for Rlbty and Lst Cst Dsptch</t>
         </is>
       </c>
+      <c r="D111" s="7" t="n"/>
+      <c r="E111" s="7" t="n"/>
       <c r="F111" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G111" s="26" t="n"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -3788,11 +4055,14 @@
           <t>Fraction of Grid Batteries Produced Domestically</t>
         </is>
       </c>
+      <c r="D112" s="7" t="n"/>
+      <c r="E112" s="7" t="n"/>
       <c r="F112" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G112" s="26" t="n"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -3810,11 +4080,14 @@
           <t>Grid Battery Capacity Growth per Unit Net Revenue</t>
         </is>
       </c>
+      <c r="D113" s="7" t="n"/>
+      <c r="E113" s="7" t="n"/>
       <c r="F113" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G113" s="26" t="n"/>
     </row>
     <row r="114" ht="30" customHeight="1">
       <c r="A114" s="2" t="inlineStr">
@@ -3832,16 +4105,18 @@
           <t>Grid Battery Storage Capacities</t>
         </is>
       </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="D114" s="1" t="inlineStr">
         <is>
           <t>Start Year Grid Battery Storage Capacity, Grid Battery Daily Storage Duration</t>
         </is>
       </c>
+      <c r="E114" s="7" t="n"/>
       <c r="F114" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G114" s="26" t="n"/>
     </row>
     <row r="115" ht="60" customHeight="1">
       <c r="A115" s="2" t="inlineStr">
@@ -3859,12 +4134,14 @@
           <t>Guaranteed Dispatch Percentage by Electricity Source</t>
         </is>
       </c>
+      <c r="D115" s="7" t="n"/>
+      <c r="E115" s="7" t="n"/>
       <c r="F115" s="6" t="inlineStr">
         <is>
           <t>n/a (policy lever)</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr">
+      <c r="G115" s="24" t="inlineStr">
         <is>
           <t>You are modeling a region where power plants are dispatched based on non-market rules rather than by least marginal cost, and you are setting this policy lever to alter the BAU percentages</t>
         </is>
@@ -3886,11 +4163,14 @@
           <t>Green Hydrogen Electricity Supply Logit Exponent</t>
         </is>
       </c>
+      <c r="D116" s="7" t="n"/>
+      <c r="E116" s="7" t="n"/>
       <c r="F116" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G116" s="26" t="n"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -3908,12 +4188,14 @@
           <t>Green Hydrogen Electricity Supply Shareweights</t>
         </is>
       </c>
+      <c r="D117" s="7" t="n"/>
+      <c r="E117" s="7" t="n"/>
       <c r="F117" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G117" s="26" t="inlineStr">
         <is>
           <t>Governs which sources can be built as dedicated off-grid supply for BOTH green hydrogen electrolysis AND industrial thermal battery charging (consolidated 2026-08-17; formerly a separate TBESS copy existed for thermal batteries).</t>
         </is>
@@ -3935,11 +4217,14 @@
           <t>Hybrid Electricity Source Battery Capacity per Unit Electricity Capacity</t>
         </is>
       </c>
+      <c r="D118" s="7" t="n"/>
+      <c r="E118" s="7" t="n"/>
       <c r="F118" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G118" s="26" t="n"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -3957,11 +4242,14 @@
           <t>Hydro Opportunity Cost</t>
         </is>
       </c>
+      <c r="D119" s="7" t="n"/>
+      <c r="E119" s="7" t="n"/>
       <c r="F119" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G119" s="26" t="n"/>
     </row>
     <row r="120" ht="30" customHeight="1">
       <c r="A120" s="2" t="inlineStr">
@@ -3979,11 +4267,14 @@
           <t>Increase in Capacity Factors for New Plants due to Technological Improvements</t>
         </is>
       </c>
+      <c r="D120" s="7" t="n"/>
+      <c r="E120" s="7" t="n"/>
       <c r="F120" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G120" s="26" t="n"/>
     </row>
     <row r="121">
       <c r="A121" s="2" t="inlineStr">
@@ -4001,11 +4292,14 @@
           <t>Load Factor Hourly Variance Multiplier</t>
         </is>
       </c>
+      <c r="D121" s="7" t="n"/>
+      <c r="E121" s="7" t="n"/>
       <c r="F121" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G121" s="26" t="n"/>
     </row>
     <row r="122">
       <c r="A122" s="2" t="inlineStr">
@@ -4023,11 +4317,14 @@
           <t>Max and Min Hourly Electriicty Imports and Exports</t>
         </is>
       </c>
+      <c r="D122" s="7" t="n"/>
+      <c r="E122" s="7" t="n"/>
       <c r="F122" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G122" s="26" t="n"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -4045,11 +4342,14 @@
           <t>Maximum Capacity Factor</t>
         </is>
       </c>
+      <c r="D123" s="7" t="n"/>
+      <c r="E123" s="7" t="n"/>
       <c r="F123" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G123" s="26" t="n"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -4067,11 +4367,14 @@
           <t>Min Life for Pwr Plnt Rtmnts</t>
         </is>
       </c>
+      <c r="D124" s="7" t="n"/>
+      <c r="E124" s="7" t="n"/>
       <c r="F124" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G124" s="26" t="n"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -4089,11 +4392,14 @@
           <t>Max Potential Capacity by Source</t>
         </is>
       </c>
+      <c r="D125" s="7" t="n"/>
+      <c r="E125" s="7" t="n"/>
       <c r="F125" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G125" s="26" t="n"/>
     </row>
     <row r="126">
       <c r="A126" s="2" t="inlineStr">
@@ -4111,11 +4417,14 @@
           <t>Minimum Power Plant Capacity</t>
         </is>
       </c>
+      <c r="D126" s="7" t="n"/>
+      <c r="E126" s="7" t="n"/>
       <c r="F126" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G126" s="26" t="n"/>
     </row>
     <row r="127">
       <c r="A127" s="2" t="inlineStr">
@@ -4133,11 +4442,14 @@
           <t>Normalized Standard Deviation of Dispatch Costs</t>
         </is>
       </c>
+      <c r="D127" s="7" t="n"/>
+      <c r="E127" s="7" t="n"/>
       <c r="F127" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G127" s="26" t="n"/>
     </row>
     <row r="128" ht="60" customHeight="1">
       <c r="A128" s="2" t="inlineStr">
@@ -4155,12 +4467,14 @@
           <t>Policy Mandated Capacity Construction Schedule</t>
         </is>
       </c>
+      <c r="D128" s="7" t="n"/>
+      <c r="E128" s="7" t="n"/>
       <c r="F128" s="6" t="inlineStr">
         <is>
           <t>n/a (policy lever)</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr">
+      <c r="G128" s="24" t="inlineStr">
         <is>
           <t>You are modeling a region where power plant construction decisions are based on government mandates rather than being market-driven, and you are setting this policy lever to alter the BAU mandates</t>
         </is>
@@ -4182,12 +4496,14 @@
           <t>Policy Mandated Capacity Retrofit Schedule</t>
         </is>
       </c>
+      <c r="D129" s="7" t="n"/>
+      <c r="E129" s="7" t="n"/>
       <c r="F129" s="6" t="inlineStr">
         <is>
           <t>n/a (policy lever)</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr">
+      <c r="G129" s="24" t="inlineStr">
         <is>
           <t>You are modeling a region where power plant CCUS retrofit decisions are based on government mandates rather than being market-driven, and you are setting this policy lever to alter the BAU mandates</t>
         </is>
@@ -4209,16 +4525,18 @@
           <t>RPS Alternative Compliance Payment</t>
         </is>
       </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="D130" s="1" t="inlineStr">
         <is>
           <t>BAU RPS Alternative Compliance Payment, RPS Alternative Compliance Payment</t>
         </is>
       </c>
+      <c r="E130" s="7" t="n"/>
       <c r="F130" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G130" s="26" t="n"/>
     </row>
     <row r="131" ht="45" customHeight="1">
       <c r="A131" s="2" t="inlineStr">
@@ -4236,16 +4554,18 @@
           <t>Regional Availability Factor</t>
         </is>
       </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="D131" s="1" t="inlineStr">
         <is>
           <t>Regional Availability Factor for Generation, Regional Availability Factor for Capacity, Regional Availability Factor for Demand-Altering Technologies</t>
         </is>
       </c>
+      <c r="E131" s="7" t="n"/>
       <c r="F131" s="14" t="inlineStr">
         <is>
           <t>to be determined via calibration</t>
         </is>
       </c>
+      <c r="G131" s="26" t="n"/>
     </row>
     <row r="132">
       <c r="A132" s="2" t="inlineStr">
@@ -4263,11 +4583,14 @@
           <t>Reserve Margin</t>
         </is>
       </c>
+      <c r="D132" s="7" t="n"/>
+      <c r="E132" s="7" t="n"/>
       <c r="F132" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G132" s="26" t="n"/>
     </row>
     <row r="133" ht="30" customHeight="1">
       <c r="A133" s="2" t="inlineStr">
@@ -4285,11 +4608,14 @@
           <t>Repayment Period for Financed Electricity Sector Capital Costs</t>
         </is>
       </c>
+      <c r="D133" s="7" t="n"/>
+      <c r="E133" s="7" t="n"/>
       <c r="F133" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G133" s="26" t="n"/>
     </row>
     <row r="134" ht="30" customHeight="1">
       <c r="A134" s="2" t="inlineStr">
@@ -4307,16 +4633,18 @@
           <t>RPS-Qualifying Source Definitions</t>
         </is>
       </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="D134" s="1" t="inlineStr">
         <is>
           <t>BAU RPS Qualifying Source Definitions, RPS Qualifying Source Definitions</t>
         </is>
       </c>
+      <c r="E134" s="7" t="n"/>
       <c r="F134" s="5" t="inlineStr">
         <is>
           <t>medium (n/a for RPS Qualifying Source Definitions, as it is a policy lever)</t>
         </is>
       </c>
+      <c r="G134" s="26" t="n"/>
     </row>
     <row r="135" ht="45" customHeight="1">
       <c r="A135" s="2" t="inlineStr">
@@ -4334,16 +4662,18 @@
           <t>Seasonal Electricity Storage</t>
         </is>
       </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="D135" s="1" t="inlineStr">
         <is>
           <t>Seasonal Electricity Storage Capacity, Seasonal Electricity Storage Annual Charge and Discharge Cycles, Seasonal Electricity Storage Round Trip Efficiency</t>
         </is>
       </c>
+      <c r="E135" s="7" t="n"/>
       <c r="F135" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G135" s="26" t="n"/>
     </row>
     <row r="136" ht="30" customHeight="1">
       <c r="A136" s="2" t="inlineStr">
@@ -4361,12 +4691,12 @@
           <t>Seasonal Hourly Equipment Load Factors</t>
         </is>
       </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="D136" s="1" t="inlineStr">
         <is>
           <t>Seasonal Hourly Equipment Load Factors, Days per Timeslice</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E136" s="1" t="inlineStr">
         <is>
           <t>ctrl-settings/ICwIwLF</t>
         </is>
@@ -4376,6 +4706,7 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G136" s="26" t="n"/>
     </row>
     <row r="137" ht="30" customHeight="1">
       <c r="A137" s="2" t="inlineStr">
@@ -4393,11 +4724,14 @@
           <t>Share of Costs that Must be Covered to be Deemed Profitable</t>
         </is>
       </c>
+      <c r="D137" s="7" t="n"/>
+      <c r="E137" s="7" t="n"/>
       <c r="F137" s="14" t="inlineStr">
         <is>
           <t>to be determined via calibration</t>
         </is>
       </c>
+      <c r="G137" s="26" t="n"/>
     </row>
     <row r="138" ht="45" customHeight="1">
       <c r="A138" s="2" t="inlineStr">
@@ -4415,16 +4749,18 @@
           <t>Share of Electricity Sector Capital and OM Costs by ISIC Code</t>
         </is>
       </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="D138" s="1" t="inlineStr">
         <is>
           <t>Share of Electricity Sector Capital Costs by ISIC Code, Share of Electricity Sector Fixed OM Costs by ISIC Code, Share of Electricity Sector Variable OM Costs by ISIC Code</t>
         </is>
       </c>
+      <c r="E138" s="7" t="n"/>
       <c r="F138" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G138" s="26" t="n"/>
     </row>
     <row r="139" ht="30" customHeight="1">
       <c r="A139" s="2" t="inlineStr">
@@ -4442,11 +4778,14 @@
           <t>Share of Forward Costs that Must be Covered to Prevent Retirement</t>
         </is>
       </c>
+      <c r="D139" s="7" t="n"/>
+      <c r="E139" s="7" t="n"/>
       <c r="F139" s="14" t="inlineStr">
         <is>
           <t>to be determined via calibration</t>
         </is>
       </c>
+      <c r="G139" s="26" t="n"/>
     </row>
     <row r="140" ht="30" customHeight="1">
       <c r="A140" s="2" t="inlineStr">
@@ -4464,11 +4803,14 @@
           <t>Share of Transmission and Distribution Capital Costs by ISIC Code</t>
         </is>
       </c>
+      <c r="D140" s="7" t="n"/>
+      <c r="E140" s="7" t="n"/>
       <c r="F140" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G140" s="26" t="n"/>
     </row>
     <row r="141" ht="30" customHeight="1">
       <c r="A141" s="2" t="inlineStr">
@@ -4486,11 +4828,14 @@
           <t>Share of Transmission and Distribution OM Costs by ISIC Code</t>
         </is>
       </c>
+      <c r="D141" s="7" t="n"/>
+      <c r="E141" s="7" t="n"/>
       <c r="F141" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G141" s="26" t="n"/>
     </row>
     <row r="142" ht="30" customHeight="1">
       <c r="A142" s="2" t="inlineStr">
@@ -4508,11 +4853,14 @@
           <t>Smoothing Time for Electricity Sector Capital Expenditures</t>
         </is>
       </c>
+      <c r="D142" s="7" t="n"/>
+      <c r="E142" s="7" t="n"/>
       <c r="F142" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G142" s="26" t="n"/>
     </row>
     <row r="143">
       <c r="A143" s="2" t="inlineStr">
@@ -4530,11 +4878,14 @@
           <t>Start Year Peak Electricity Load</t>
         </is>
       </c>
+      <c r="D143" s="7" t="n"/>
+      <c r="E143" s="7" t="n"/>
       <c r="F143" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G143" s="26" t="n"/>
     </row>
     <row r="144">
       <c r="A144" s="2" t="inlineStr">
@@ -4552,7 +4903,8 @@
           <t>Start Year Seasonal Expected Hourly Capacity Factors</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="D144" s="7" t="n"/>
+      <c r="E144" s="1" t="inlineStr">
         <is>
           <t>MCF</t>
         </is>
@@ -4562,6 +4914,7 @@
           <t>high</t>
         </is>
       </c>
+      <c r="G144" s="26" t="n"/>
     </row>
     <row r="145" ht="30" customHeight="1">
       <c r="A145" s="2" t="inlineStr">
@@ -4579,16 +4932,18 @@
           <t>Start Year Transmission and Distribution Costs</t>
         </is>
       </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="D145" s="1" t="inlineStr">
         <is>
           <t>Start Year Transmission Capital Costs, Start Year Distribution Capital Costs, Start Year Transmission OM Costs, Start Year Distribution OM Costs</t>
         </is>
       </c>
+      <c r="E145" s="7" t="n"/>
       <c r="F145" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G145" s="26" t="n"/>
     </row>
     <row r="146" ht="30" customHeight="1">
       <c r="A146" s="2" t="inlineStr">
@@ -4606,11 +4961,14 @@
           <t>Time Adjusted Capacity Factor Multiplier for Plants Built This Year</t>
         </is>
       </c>
+      <c r="D146" s="7" t="n"/>
+      <c r="E146" s="7" t="n"/>
       <c r="F146" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G146" s="26" t="n"/>
     </row>
     <row r="147" ht="30" customHeight="1">
       <c r="A147" t="inlineStr">
@@ -4628,12 +4986,14 @@
           <t>Thermal Battery Daily Charging Hours</t>
         </is>
       </c>
+      <c r="D147" s="7" t="n"/>
+      <c r="E147" s="7" t="n"/>
       <c r="F147" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G147" s="26" t="inlineStr">
         <is>
           <t>You wish to model grid-connected thermal battery charging; hours per day of charging (equipment design parameter coupled to TBCC). Which hours are cheapest is computed endogenously in Thermal Battery Charging Window.</t>
         </is>
@@ -4655,11 +5015,14 @@
           <t>Transmission Construction Cost per Unit New Electricity Capacity</t>
         </is>
       </c>
+      <c r="D148" s="7" t="n"/>
+      <c r="E148" s="7" t="n"/>
       <c r="F148" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G148" s="26" t="n"/>
     </row>
     <row r="149" ht="60.75" customHeight="1" thickBot="1">
       <c r="A149" s="2" t="inlineStr">
@@ -4677,11 +5040,14 @@
           <t>Usage Factor Discount for Grid Battery Storage</t>
         </is>
       </c>
+      <c r="D149" s="7" t="n"/>
+      <c r="E149" s="7" t="n"/>
       <c r="F149" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G149" s="26" t="n"/>
     </row>
     <row r="150" ht="30" customHeight="1">
       <c r="A150" s="17" t="inlineStr">
@@ -4699,18 +5065,18 @@
           <t>Water Use by Power Plant Type</t>
         </is>
       </c>
-      <c r="D150" s="17" t="inlineStr">
+      <c r="D150" s="27" t="inlineStr">
         <is>
           <t>Water Withdrawals by Power Plant Type, Water Consumption by Power Plant Type</t>
         </is>
       </c>
-      <c r="E150" s="17" t="n"/>
+      <c r="E150" s="27" t="n"/>
       <c r="F150" s="21" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G150" s="17" t="inlineStr">
+      <c r="G150" s="28" t="inlineStr">
         <is>
           <t>You want to estimate the amount of water withdrawn or consumed by power plants, and you believe power plants in the modeled region need different amounts of cooling water than the same types of power plants in the U.S.</t>
         </is>
@@ -4732,16 +5098,18 @@
           <t>BAU CO2 Sequestered Globally</t>
         </is>
       </c>
-      <c r="D151" s="2" t="inlineStr">
+      <c r="D151" s="1" t="inlineStr">
         <is>
           <t>BAU CO2 Sequestered Globally, Start Year BAU CO2 Sequestered Globally</t>
         </is>
       </c>
+      <c r="E151" s="7" t="n"/>
       <c r="F151" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G151" s="26" t="n"/>
     </row>
     <row r="152" ht="30" customHeight="1">
       <c r="A152" s="2" t="inlineStr">
@@ -4759,16 +5127,18 @@
           <t>BAU Global Battery Storage Capacity</t>
         </is>
       </c>
-      <c r="D152" s="2" t="inlineStr">
+      <c r="D152" s="1" t="inlineStr">
         <is>
           <t>BAU Global Battery Storage Capacity, Start Year Global Battery Storage Capacity</t>
         </is>
       </c>
+      <c r="E152" s="7" t="n"/>
       <c r="F152" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G152" s="26" t="n"/>
     </row>
     <row r="153" ht="30" customHeight="1">
       <c r="A153" s="2" t="inlineStr">
@@ -4786,11 +5156,14 @@
           <t>BAU Global Solar and Wind Capacities</t>
         </is>
       </c>
+      <c r="D153" s="7" t="n"/>
+      <c r="E153" s="7" t="n"/>
       <c r="F153" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G153" s="26" t="n"/>
     </row>
     <row r="154">
       <c r="A154" s="2" t="inlineStr">
@@ -4808,11 +5181,14 @@
           <t>Fraction of Technology Outside Modeled Region Affecting Endogenous Learning</t>
         </is>
       </c>
+      <c r="D154" s="7" t="n"/>
+      <c r="E154" s="7" t="n"/>
       <c r="F154" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G154" s="26" t="n"/>
     </row>
     <row r="155" ht="30" customHeight="1">
       <c r="A155" s="2" t="inlineStr">
@@ -4830,11 +5206,14 @@
           <t>Perc Decline in Battery Cost per Doubling of Capacity</t>
         </is>
       </c>
+      <c r="D155" s="7" t="n"/>
+      <c r="E155" s="7" t="n"/>
       <c r="F155" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G155" s="26" t="n"/>
     </row>
     <row r="156" ht="30.75" customHeight="1" thickBot="1">
       <c r="A156" s="2" t="inlineStr">
@@ -4852,11 +5231,14 @@
           <t>Perc Decline in Capacity Cost per Doubling of Capacity</t>
         </is>
       </c>
+      <c r="D156" s="7" t="n"/>
+      <c r="E156" s="7" t="n"/>
       <c r="F156" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G156" s="26" t="n"/>
     </row>
     <row r="157">
       <c r="A157" s="17" t="inlineStr">
@@ -4874,14 +5256,14 @@
           <t>Percent Decline in CCS Equipment Cost per Doubling of Capacity</t>
         </is>
       </c>
-      <c r="D157" s="17" t="n"/>
-      <c r="E157" s="17" t="n"/>
+      <c r="D157" s="27" t="n"/>
+      <c r="E157" s="27" t="n"/>
       <c r="F157" s="20" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="G157" s="17" t="n"/>
+      <c r="G157" s="28" t="n"/>
     </row>
     <row r="158" ht="30" customHeight="1">
       <c r="A158" s="2" t="inlineStr">
@@ -4899,11 +5281,14 @@
           <t>BAU Carbon Tax Rate</t>
         </is>
       </c>
+      <c r="D158" s="7" t="n"/>
+      <c r="E158" s="7" t="n"/>
       <c r="F158" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G158" s="26" t="n"/>
     </row>
     <row r="159" ht="30" customHeight="1">
       <c r="A159" s="2" t="inlineStr">
@@ -4921,11 +5306,14 @@
           <t>BAU Fraction of Industry Covered by Carbon Tax Border Adjustment</t>
         </is>
       </c>
+      <c r="D159" s="7" t="n"/>
+      <c r="E159" s="7" t="n"/>
       <c r="F159" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G159" s="26" t="n"/>
     </row>
     <row r="160" ht="30" customHeight="1">
       <c r="A160" s="2" t="inlineStr">
@@ -4943,11 +5331,14 @@
           <t>BAU Fraction of Industry Category Subject to Carbon Tax</t>
         </is>
       </c>
+      <c r="D160" s="7" t="n"/>
+      <c r="E160" s="7" t="n"/>
       <c r="F160" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G160" s="26" t="n"/>
     </row>
     <row r="161" ht="30" customHeight="1">
       <c r="A161" s="2" t="inlineStr">
@@ -4965,11 +5356,14 @@
           <t>BAU Fraction of Vehicle Types Subject to Carbon Tax</t>
         </is>
       </c>
+      <c r="D161" s="7" t="n"/>
+      <c r="E161" s="7" t="n"/>
       <c r="F161" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G161" s="26" t="n"/>
     </row>
     <row r="162">
       <c r="A162" s="2" t="inlineStr">
@@ -4987,16 +5381,18 @@
           <t>BAU Fuel Prices and Taxes</t>
         </is>
       </c>
-      <c r="D162" s="2" t="inlineStr">
+      <c r="D162" s="1" t="inlineStr">
         <is>
           <t>BAU Pretax Fuel Price by Sector, BAU Fuel Tax by Sector</t>
         </is>
       </c>
+      <c r="E162" s="7" t="n"/>
       <c r="F162" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G162" s="26" t="n"/>
     </row>
     <row r="163">
       <c r="A163" s="2" t="inlineStr">
@@ -5014,11 +5410,14 @@
           <t>BAU Fuel Production Imports and Exports</t>
         </is>
       </c>
+      <c r="D163" s="7" t="n"/>
+      <c r="E163" s="7" t="n"/>
       <c r="F163" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G163" s="26" t="n"/>
     </row>
     <row r="164" ht="45" customHeight="1">
       <c r="A164" s="2" t="inlineStr">
@@ -5036,11 +5435,14 @@
           <t>BAU Pollutants Taxed by Carbon Pricing</t>
         </is>
       </c>
+      <c r="D164" s="7" t="n"/>
+      <c r="E164" s="7" t="n"/>
       <c r="F164" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G164" s="26" t="n"/>
     </row>
     <row r="165">
       <c r="A165" s="2" t="inlineStr">
@@ -5058,16 +5460,18 @@
           <t>BAU Subsidies</t>
         </is>
       </c>
-      <c r="D165" s="2" t="inlineStr">
+      <c r="D165" s="1" t="inlineStr">
         <is>
           <t>BAU Subsidy for Thermal Fuels per Energy Unit Produced, BAU Subsidy per Unit Electricity Output, BAU Subsidy per Unit Electricity Capacity Built</t>
         </is>
       </c>
+      <c r="E165" s="7" t="n"/>
       <c r="F165" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G165" s="26" t="n"/>
     </row>
     <row r="166" ht="30" customHeight="1">
       <c r="A166" s="2" t="inlineStr">
@@ -5085,11 +5489,14 @@
           <t>Export Tax Rate by Fuel</t>
         </is>
       </c>
+      <c r="D166" s="7" t="n"/>
+      <c r="E166" s="7" t="n"/>
       <c r="F166" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G166" s="26" t="n"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -5107,11 +5514,14 @@
           <t>Fraction of Industry Covered by Carbon Tax Border Adjustment</t>
         </is>
       </c>
+      <c r="D167" s="7" t="n"/>
+      <c r="E167" s="7" t="n"/>
       <c r="F167" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G167" s="26" t="n"/>
     </row>
     <row r="168" ht="30" customHeight="1">
       <c r="A168" s="2" t="inlineStr">
@@ -5129,11 +5539,14 @@
           <t>Fraction of Industry Category Subject to Carbon Tax</t>
         </is>
       </c>
+      <c r="D168" s="7" t="n"/>
+      <c r="E168" s="7" t="n"/>
       <c r="F168" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G168" s="26" t="n"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -5151,7 +5564,8 @@
           <t>Fraction of Products That are Fuels by ISIC Code</t>
         </is>
       </c>
-      <c r="E169" s="2" t="inlineStr">
+      <c r="D169" s="7" t="n"/>
+      <c r="E169" s="1" t="inlineStr">
         <is>
           <t>BObIC, BFPaT</t>
         </is>
@@ -5161,6 +5575,7 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G169" s="26" t="n"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -5178,11 +5593,14 @@
           <t>Fraction of Vehicle Types Subject to Carbon Tax</t>
         </is>
       </c>
+      <c r="D170" s="7" t="n"/>
+      <c r="E170" s="7" t="n"/>
       <c r="F170" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G170" s="26" t="n"/>
     </row>
     <row r="171">
       <c r="A171" s="2" t="inlineStr">
@@ -5200,11 +5618,14 @@
           <t>Fuel Production Import Export Balancing Priorities</t>
         </is>
       </c>
+      <c r="D171" s="7" t="n"/>
+      <c r="E171" s="7" t="n"/>
       <c r="F171" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G171" s="26" t="n"/>
     </row>
     <row r="172" ht="30" customHeight="1">
       <c r="A172" s="2" t="inlineStr">
@@ -5222,11 +5643,14 @@
           <t>Fuel Surcharge Percentage by Power Plant Type</t>
         </is>
       </c>
+      <c r="D172" s="7" t="n"/>
+      <c r="E172" s="7" t="n"/>
       <c r="F172" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G172" s="26" t="n"/>
     </row>
     <row r="173">
       <c r="A173" s="2" t="inlineStr">
@@ -5244,12 +5668,14 @@
           <t>GWP by Pollutant by Timeframe</t>
         </is>
       </c>
+      <c r="D173" s="7" t="n"/>
+      <c r="E173" s="7" t="n"/>
       <c r="F173" s="6" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G173" s="2" t="inlineStr">
+      <c r="G173" s="24" t="inlineStr">
         <is>
           <t>You want to use a data source for GWP values other than IPCC AR5</t>
         </is>
@@ -5271,11 +5697,14 @@
           <t>International Market Fuel Price by Fuel Type</t>
         </is>
       </c>
+      <c r="D174" s="7" t="n"/>
+      <c r="E174" s="7" t="n"/>
       <c r="F174" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G174" s="26" t="n"/>
     </row>
     <row r="175" ht="30" customHeight="1">
       <c r="A175" s="2" t="inlineStr">
@@ -5293,12 +5722,14 @@
           <t>Maximum Percentage Increase in Fuel Exports</t>
         </is>
       </c>
+      <c r="D175" s="7" t="n"/>
+      <c r="E175" s="7" t="n"/>
       <c r="F175" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G175" s="2" t="inlineStr">
+      <c r="G175" s="24" t="inlineStr">
         <is>
           <t>You wish to cap the amount by which policies may increase the exports of one or more fuel types</t>
         </is>
@@ -5320,12 +5751,14 @@
           <t>Maximum Percentage Increase in Fuel Imports</t>
         </is>
       </c>
+      <c r="D176" s="7" t="n"/>
+      <c r="E176" s="7" t="n"/>
       <c r="F176" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G176" s="2" t="inlineStr">
+      <c r="G176" s="24" t="inlineStr">
         <is>
           <t>You wish to cap the amount by which policies may increase the imports of one or more fuel types</t>
         </is>
@@ -5347,12 +5780,14 @@
           <t>Maximum Percentage Increase in Fuel Production</t>
         </is>
       </c>
+      <c r="D177" s="7" t="n"/>
+      <c r="E177" s="7" t="n"/>
       <c r="F177" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G177" s="2" t="inlineStr">
+      <c r="G177" s="24" t="inlineStr">
         <is>
           <t>You wish to cap the amount by which policies may increase the production of one or more fuel types</t>
         </is>
@@ -5374,16 +5809,18 @@
           <t>Pollutant Emissions Intensities</t>
         </is>
       </c>
-      <c r="D178" s="2" t="inlineStr">
+      <c r="D178" s="1" t="inlineStr">
         <is>
           <t>Transportation Fuel Pollutant Emissions Intensities, Electricity Fuel Pollutant Emissions Intensities, Buildings Fuel Pollutant Emissions Intensities, Industrial Fuel Pollutant Emissions Intensities</t>
         </is>
       </c>
+      <c r="E178" s="7" t="n"/>
       <c r="F178" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G178" s="26" t="n"/>
     </row>
     <row r="179" ht="45" customHeight="1">
       <c r="A179" s="2" t="inlineStr">
@@ -5401,16 +5838,18 @@
           <t>Pollutant Emissions Intensity Improvement Rate</t>
         </is>
       </c>
-      <c r="D179" s="2" t="inlineStr">
+      <c r="D179" s="1" t="inlineStr">
         <is>
           <t>Transportation Fuel Pollutant Emissions Intensity Improvement Rate, Electricity Fuel Pollutant Emissions Intensity Improvement Rate, Buildings Fuel Pollutant Emissions Intensity Improvement Rate, Industrial Fuel Pollutant Emissions Intensity Improvement Rate</t>
         </is>
       </c>
+      <c r="E179" s="7" t="n"/>
       <c r="F179" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G179" s="26" t="n"/>
     </row>
     <row r="180" ht="30" customHeight="1">
       <c r="A180" s="2" t="inlineStr">
@@ -5428,11 +5867,14 @@
           <t>Percentage of Fuel Demand Change that Alters Exports</t>
         </is>
       </c>
+      <c r="D180" s="7" t="n"/>
+      <c r="E180" s="7" t="n"/>
       <c r="F180" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G180" s="26" t="n"/>
     </row>
     <row r="181" ht="45" customFormat="1" customHeight="1" s="17" thickBot="1">
       <c r="A181" s="2" t="inlineStr">
@@ -5450,12 +5892,14 @@
           <t>Pollutants Taxed by Carbon Pricing</t>
         </is>
       </c>
+      <c r="D181" s="7" t="n"/>
+      <c r="E181" s="7" t="n"/>
       <c r="F181" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G181" s="2" t="inlineStr">
+      <c r="G181" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">If there is a policy scenario with differing carbon pricing scheme than in the BAU. </t>
         </is>
@@ -5477,12 +5921,14 @@
           <t>Quantization Size for Energy</t>
         </is>
       </c>
+      <c r="D182" s="7" t="n"/>
+      <c r="E182" s="7" t="n"/>
       <c r="F182" s="22" t="inlineStr">
         <is>
           <t>n/a</t>
         </is>
       </c>
-      <c r="G182" s="17" t="inlineStr">
+      <c r="G182" s="28" t="inlineStr">
         <is>
           <t>Rounding error is visible in final web app output graphs in changes in fuel imports/exports with no policies enabled</t>
         </is>
@@ -5504,16 +5950,18 @@
           <t>Direct Air Capture Data</t>
         </is>
       </c>
-      <c r="D183" s="2" t="inlineStr">
+      <c r="D183" s="1" t="inlineStr">
         <is>
           <t>Direct Air Capture Potential, Direct Air Capture Energy Intensity, Direct Air Capture Amortized CapEx and OM</t>
         </is>
       </c>
+      <c r="E183" s="7" t="n"/>
       <c r="F183" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G183" s="26" t="n"/>
     </row>
     <row r="184" ht="30" customHeight="1">
       <c r="A184" s="17" t="inlineStr">
@@ -5531,16 +5979,18 @@
           <t>Enhanced Rock Weathering Data</t>
         </is>
       </c>
-      <c r="D184" s="17" t="inlineStr">
+      <c r="D184" s="27" t="inlineStr">
         <is>
           <t>Enhanced Rock Weathering Potential, Enhanced Rock Weathering Energy Intensity, Enhanced Rock Weathering Amortized CapEx and OM</t>
         </is>
       </c>
+      <c r="E184" s="7" t="n"/>
       <c r="F184" s="19" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G184" s="26" t="n"/>
     </row>
     <row r="185" ht="30" customHeight="1">
       <c r="A185" s="2" t="inlineStr">
@@ -5558,11 +6008,14 @@
           <t>BAU Cost of Hydrogen Sector Capital</t>
         </is>
       </c>
+      <c r="D185" s="7" t="n"/>
+      <c r="E185" s="7" t="n"/>
       <c r="F185" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G185" s="26" t="n"/>
     </row>
     <row r="186">
       <c r="A186" s="2" t="inlineStr">
@@ -5580,11 +6033,14 @@
           <t>BAU Subsidy for Hydrogen Production by Pathway</t>
         </is>
       </c>
+      <c r="D186" s="7" t="n"/>
+      <c r="E186" s="7" t="n"/>
       <c r="F186" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G186" s="26" t="n"/>
     </row>
     <row r="187">
       <c r="A187" s="2" t="inlineStr">
@@ -5602,11 +6058,14 @@
           <t>Electrolyzer Hydrogen Production per Unit Capacity</t>
         </is>
       </c>
+      <c r="D187" s="7" t="n"/>
+      <c r="E187" s="7" t="n"/>
       <c r="F187" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G187" s="26" t="n"/>
     </row>
     <row r="188">
       <c r="A188" s="2" t="inlineStr">
@@ -5624,11 +6083,14 @@
           <t>Fuel Intensity of Hydrogen Production</t>
         </is>
       </c>
+      <c r="D188" s="7" t="n"/>
+      <c r="E188" s="7" t="n"/>
       <c r="F188" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G188" s="26" t="n"/>
     </row>
     <row r="189" ht="30" customHeight="1">
       <c r="A189" s="2" t="inlineStr">
@@ -5646,11 +6108,14 @@
           <t>Fraction of Hydrogen Equipment Retiring by Age</t>
         </is>
       </c>
+      <c r="D189" s="7" t="n"/>
+      <c r="E189" s="7" t="n"/>
       <c r="F189" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G189" s="26" t="n"/>
     </row>
     <row r="190">
       <c r="A190" s="2" t="inlineStr">
@@ -5668,16 +6133,18 @@
           <t>Hydrogen Production Equipment Costs</t>
         </is>
       </c>
-      <c r="D190" s="2" t="inlineStr">
+      <c r="D190" s="1" t="inlineStr">
         <is>
           <t>Hydrogen Production Equipment CapEx, Hydrogen Production Equipment OpEx</t>
         </is>
       </c>
+      <c r="E190" s="7" t="n"/>
       <c r="F190" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G190" s="26" t="n"/>
     </row>
     <row r="191" ht="30" customHeight="1">
       <c r="A191" s="2" t="inlineStr">
@@ -5695,11 +6162,14 @@
           <t>Hydrogen Production Logit Coefficient</t>
         </is>
       </c>
+      <c r="D191" s="7" t="n"/>
+      <c r="E191" s="7" t="n"/>
       <c r="F191" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G191" s="26" t="n"/>
     </row>
     <row r="192">
       <c r="A192" s="2" t="inlineStr">
@@ -5717,11 +6187,14 @@
           <t>Hydrogen Production Percent Excess Capacity by Pathway</t>
         </is>
       </c>
+      <c r="D192" s="7" t="n"/>
+      <c r="E192" s="7" t="n"/>
       <c r="F192" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G192" s="26" t="n"/>
     </row>
     <row r="193" ht="30" customHeight="1">
       <c r="A193" s="2" t="inlineStr">
@@ -5739,11 +6212,14 @@
           <t>Hydrogen Production Shareweights</t>
         </is>
       </c>
+      <c r="D193" s="7" t="n"/>
+      <c r="E193" s="7" t="n"/>
       <c r="F193" s="14" t="inlineStr">
         <is>
           <t>to be determined via calibration</t>
         </is>
       </c>
+      <c r="G193" s="26" t="n"/>
     </row>
     <row r="194">
       <c r="A194" s="2" t="inlineStr">
@@ -5761,12 +6237,14 @@
           <t>Hydrogen Production Subsidy Duration</t>
         </is>
       </c>
+      <c r="D194" s="7" t="n"/>
+      <c r="E194" s="7" t="n"/>
       <c r="F194" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G194" s="2" t="inlineStr">
+      <c r="G194" s="24" t="inlineStr">
         <is>
           <t>If there is a hydrogen production subsidy in the region.</t>
         </is>
@@ -5788,11 +6266,14 @@
           <t>Preexisting Hydrogen Equipment Retirement Profiles</t>
         </is>
       </c>
+      <c r="D195" s="7" t="n"/>
+      <c r="E195" s="7" t="n"/>
       <c r="F195" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G195" s="26" t="n"/>
     </row>
     <row r="196" ht="30" customHeight="1">
       <c r="A196" s="2" t="inlineStr">
@@ -5810,11 +6291,14 @@
           <t>Repayment Period for Financed Hydrogen Sector Capital Costs</t>
         </is>
       </c>
+      <c r="D196" s="7" t="n"/>
+      <c r="E196" s="7" t="n"/>
       <c r="F196" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G196" s="26" t="n"/>
     </row>
     <row r="197" ht="30" customHeight="1">
       <c r="A197" s="2" t="inlineStr">
@@ -5832,11 +6316,14 @@
           <t>Start Year Hydrogen Demand That is Green and Low Carbon by Sector</t>
         </is>
       </c>
+      <c r="D197" s="7" t="n"/>
+      <c r="E197" s="7" t="n"/>
       <c r="F197" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G197" s="26" t="n"/>
     </row>
     <row r="198" ht="30" customHeight="1">
       <c r="A198" s="2" t="inlineStr">
@@ -5854,11 +6341,14 @@
           <t>Share of Hydrogen Production Capital Costs by Recipient ISIC Code</t>
         </is>
       </c>
+      <c r="D198" s="7" t="n"/>
+      <c r="E198" s="7" t="n"/>
       <c r="F198" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G198" s="26" t="n"/>
     </row>
     <row r="199" ht="30.75" customFormat="1" customHeight="1" s="17" thickBot="1">
       <c r="A199" s="2" t="inlineStr">
@@ -5876,11 +6366,14 @@
           <t>Start Year Annual Hydrogen Production Capacity</t>
         </is>
       </c>
+      <c r="D199" s="7" t="n"/>
+      <c r="E199" s="7" t="n"/>
       <c r="F199" s="12" t="inlineStr">
         <is>
           <t>very high</t>
         </is>
       </c>
+      <c r="G199" s="26" t="n"/>
     </row>
     <row r="200">
       <c r="A200" s="17" t="inlineStr">
@@ -5898,11 +6391,14 @@
           <t>Water Consumption of Hydrogen Production by Pathway</t>
         </is>
       </c>
+      <c r="D200" s="7" t="n"/>
+      <c r="E200" s="7" t="n"/>
       <c r="F200" s="20" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G200" s="26" t="n"/>
     </row>
     <row r="201" ht="30" customHeight="1">
       <c r="A201" t="inlineStr">
@@ -5920,11 +6416,14 @@
           <t>BAU Cement Demand</t>
         </is>
       </c>
+      <c r="D201" s="7" t="n"/>
+      <c r="E201" s="7" t="n"/>
       <c r="F201" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G201" s="26" t="n"/>
     </row>
     <row r="202">
       <c r="A202" s="2" t="inlineStr">
@@ -5934,24 +6433,22 @@
       </c>
       <c r="B202" s="2" t="inlineStr">
         <is>
-          <t>BCoISC</t>
+          <t>BCHPD</t>
         </is>
       </c>
       <c r="C202" s="2" t="inlineStr">
         <is>
-          <t>BAU Cost of Industry Sector Capital</t>
-        </is>
-      </c>
-      <c r="D202" s="2" t="inlineStr">
-        <is>
-          <t>Weighted Average Cost of Capital by Industry, Risk Premium for Equity</t>
-        </is>
-      </c>
+          <t>BAU Clean Heat PTC Duration</t>
+        </is>
+      </c>
+      <c r="D202" s="1" t="n"/>
+      <c r="E202" s="7" t="n"/>
       <c r="F202" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G202" s="26" t="n"/>
     </row>
     <row r="203" ht="45" customHeight="1">
       <c r="A203" s="2" t="inlineStr">
@@ -5961,17 +6458,24 @@
       </c>
       <c r="B203" s="2" t="inlineStr">
         <is>
-          <t>BCHPD</t>
+          <t>BCHSR</t>
         </is>
       </c>
       <c r="C203" s="2" t="inlineStr">
         <is>
-          <t>BAU Clean Heat PTC Duration</t>
-        </is>
-      </c>
+          <t>BAU Clean Heat Subsidy Rate</t>
+        </is>
+      </c>
+      <c r="D203" s="7" t="n"/>
+      <c r="E203" s="7" t="n"/>
       <c r="F203" s="16" t="inlineStr">
         <is>
           <t>optional</t>
+        </is>
+      </c>
+      <c r="G203" s="26" t="inlineStr">
+        <is>
+          <t xml:space="preserve">There is a clean-heat subsidy in your region. </t>
         </is>
       </c>
     </row>
@@ -5983,24 +6487,26 @@
       </c>
       <c r="B204" s="2" t="inlineStr">
         <is>
-          <t>BCHSR</t>
+          <t>BCoISC</t>
         </is>
       </c>
       <c r="C204" s="2" t="inlineStr">
         <is>
-          <t>BAU Clean Heat Subsidy Rate</t>
-        </is>
-      </c>
+          <t>BAU Cost of Industry Sector Capital</t>
+        </is>
+      </c>
+      <c r="D204" s="7" t="inlineStr">
+        <is>
+          <t>Weighted Average Cost of Capital by Industry, Risk Premium for Equity</t>
+        </is>
+      </c>
+      <c r="E204" s="7" t="n"/>
       <c r="F204" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G204" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">There is a clean-heat subsidy in your region. </t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G204" s="24" t="n"/>
     </row>
     <row r="205" ht="30" customHeight="1">
       <c r="A205" t="inlineStr">
@@ -6018,11 +6524,14 @@
           <t>BAU Clinker to Cement Ratio</t>
         </is>
       </c>
+      <c r="D205" s="7" t="n"/>
+      <c r="E205" s="7" t="n"/>
       <c r="F205" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G205" s="26" t="n"/>
     </row>
     <row r="206">
       <c r="A206" s="2" t="inlineStr">
@@ -6040,12 +6549,14 @@
           <t>Boolean Does Government Pay for Process Emissions Policies</t>
         </is>
       </c>
+      <c r="D206" s="7" t="n"/>
+      <c r="E206" s="7" t="n"/>
       <c r="F206" s="16" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G206" s="2" t="inlineStr">
+      <c r="G206" s="24" t="inlineStr">
         <is>
           <t xml:space="preserve">If you wish to implement process emissions policies that are paid for by government or change the U.S. assumptions. </t>
         </is>
@@ -6059,17 +6570,24 @@
       </c>
       <c r="B207" s="2" t="inlineStr">
         <is>
-          <t>BIEEI</t>
+          <t>BFoCDMbNI</t>
         </is>
       </c>
       <c r="C207" s="2" t="inlineStr">
         <is>
-          <t>BAU Industrial Equipment Efficiency Improvement</t>
-        </is>
-      </c>
+          <t>BAU Fraction of Clinker Demand Met by Net Imports</t>
+        </is>
+      </c>
+      <c r="D207" s="7" t="n"/>
+      <c r="E207" s="7" t="n"/>
       <c r="F207" s="3" t="inlineStr">
         <is>
           <t>high</t>
+        </is>
+      </c>
+      <c r="G207" s="26" t="inlineStr">
+        <is>
+          <t>Clinker-basis net-import share of cement consumption (negative for exporters); derive from national production, trade, and consumption statistics (USGS/UN Comtrade/association data). Closes the start-year balance on domestic clinker production.</t>
         </is>
       </c>
     </row>
@@ -6081,19 +6599,22 @@
       </c>
       <c r="B208" s="2" t="inlineStr">
         <is>
-          <t>BIEURfPEI</t>
+          <t>BIEEI</t>
         </is>
       </c>
       <c r="C208" s="2" t="inlineStr">
         <is>
-          <t>BAU Industrial Energy Use Reduction from Process Efficiency Improvements</t>
-        </is>
-      </c>
+          <t>BAU Industrial Equipment Efficiency Improvement</t>
+        </is>
+      </c>
+      <c r="D208" s="7" t="n"/>
+      <c r="E208" s="7" t="n"/>
       <c r="F208" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G208" s="26" t="n"/>
     </row>
     <row r="209" ht="30" customHeight="1">
       <c r="A209" s="2" t="inlineStr">
@@ -6103,24 +6624,22 @@
       </c>
       <c r="B209" s="2" t="inlineStr">
         <is>
-          <t>BIFU</t>
+          <t>BIEURfPEI</t>
         </is>
       </c>
       <c r="C209" s="2" t="inlineStr">
         <is>
-          <t>BAU Industrial Fuel Use</t>
-        </is>
-      </c>
-      <c r="D209" s="2" t="inlineStr">
-        <is>
-          <t>BAU Industrial Fuel Use for Energy, BAU Industrial Fuel Use as Feedstock</t>
-        </is>
-      </c>
+          <t>BAU Industrial Energy Use Reduction from Process Efficiency Improvements</t>
+        </is>
+      </c>
+      <c r="D209" s="1" t="n"/>
+      <c r="E209" s="7" t="n"/>
       <c r="F209" s="12" t="inlineStr">
         <is>
-          <t>very high</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G209" s="26" t="n"/>
     </row>
     <row r="210" ht="30" customHeight="1">
       <c r="A210" s="2" t="inlineStr">
@@ -6130,19 +6649,26 @@
       </c>
       <c r="B210" s="2" t="inlineStr">
         <is>
-          <t>BIISRP</t>
+          <t>BIFU</t>
         </is>
       </c>
       <c r="C210" s="2" t="inlineStr">
         <is>
-          <t>BAU Individual Industrial Site Retirement Profiles</t>
-        </is>
-      </c>
+          <t>BAU Industrial Fuel Use</t>
+        </is>
+      </c>
+      <c r="D210" s="7" t="inlineStr">
+        <is>
+          <t>BAU Industrial Fuel Use for Energy, BAU Industrial Fuel Use as Feedstock</t>
+        </is>
+      </c>
+      <c r="E210" s="7" t="n"/>
       <c r="F210" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>very high</t>
+        </is>
+      </c>
+      <c r="G210" s="26" t="n"/>
     </row>
     <row r="211" ht="30" customHeight="1">
       <c r="A211" s="2" t="inlineStr">
@@ -6152,24 +6678,22 @@
       </c>
       <c r="B211" s="2" t="inlineStr">
         <is>
-          <t>BPE</t>
+          <t>BIISRP</t>
         </is>
       </c>
       <c r="C211" s="2" t="inlineStr">
         <is>
-          <t>BAU Process Emissions</t>
-        </is>
-      </c>
-      <c r="D211" s="2" t="inlineStr">
-        <is>
-          <t>BAU Process Emissions, Share of Agriculture Process Emissions from Animals</t>
-        </is>
-      </c>
+          <t>BAU Individual Industrial Site Retirement Profiles</t>
+        </is>
+      </c>
+      <c r="D211" s="1" t="n"/>
+      <c r="E211" s="7" t="n"/>
       <c r="F211" s="14" t="inlineStr">
         <is>
-          <t>only adjust country selector (and non-country multipliers, if applicable)</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G211" s="26" t="n"/>
     </row>
     <row r="212" ht="30" customHeight="1">
       <c r="A212" s="2" t="inlineStr">
@@ -6179,24 +6703,26 @@
       </c>
       <c r="B212" s="2" t="inlineStr">
         <is>
-          <t>BPFUbIP</t>
+          <t>BPE</t>
         </is>
       </c>
       <c r="C212" s="2" t="inlineStr">
         <is>
-          <t>BAU Percentage Fuel Use by Industrial Process</t>
-        </is>
-      </c>
-      <c r="D212" s="2" t="inlineStr">
-        <is>
-          <t>BAU Percentage Fuel Use by Industrial Process for Thermal Fuels, BAU Percentage Fuel Use by Industrial Process for Electricity</t>
-        </is>
-      </c>
+          <t>BAU Process Emissions</t>
+        </is>
+      </c>
+      <c r="D212" s="1" t="inlineStr">
+        <is>
+          <t>BAU Process Emissions, Share of Agriculture Process Emissions from Animals</t>
+        </is>
+      </c>
+      <c r="E212" s="7" t="n"/>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>only adjust country selector (and non-country multipliers, if applicable)</t>
+        </is>
+      </c>
+      <c r="G212" s="26" t="n"/>
     </row>
     <row r="213" ht="30" customHeight="1">
       <c r="A213" s="2" t="inlineStr">
@@ -6206,19 +6732,26 @@
       </c>
       <c r="B213" s="2" t="inlineStr">
         <is>
-          <t>BSoAIGtAP</t>
+          <t>BPFUbIP</t>
         </is>
       </c>
       <c r="C213" s="2" t="inlineStr">
         <is>
-          <t>BAU Share of Agriculture Industry Going to Animal Products</t>
-        </is>
-      </c>
+          <t>BAU Percentage Fuel Use by Industrial Process</t>
+        </is>
+      </c>
+      <c r="D213" s="7" t="inlineStr">
+        <is>
+          <t>BAU Percentage Fuel Use by Industrial Process for Thermal Fuels, BAU Percentage Fuel Use by Industrial Process for Electricity</t>
+        </is>
+      </c>
+      <c r="E213" s="7" t="n"/>
       <c r="F213" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G213" s="26" t="n"/>
     </row>
     <row r="214" ht="30" customHeight="1">
       <c r="A214" t="inlineStr">
@@ -6228,24 +6761,22 @@
       </c>
       <c r="B214" t="inlineStr">
         <is>
-          <t>CCF</t>
+          <t>BSoAIGtAP</t>
         </is>
       </c>
       <c r="C214" t="inlineStr">
         <is>
-          <t>Calcination CO2 Factor by Pathway</t>
-        </is>
-      </c>
+          <t>BAU Share of Agriculture Industry Going to Animal Products</t>
+        </is>
+      </c>
+      <c r="D214" s="7" t="n"/>
+      <c r="E214" s="7" t="n"/>
       <c r="F214" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Chemistry constant (EPA GHGI calcination factor); same worldwide.</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G214" s="26" t="n"/>
     </row>
     <row r="215" ht="30" customHeight="1">
       <c r="A215" t="inlineStr">
@@ -6255,17 +6786,24 @@
       </c>
       <c r="B215" t="inlineStr">
         <is>
-          <t>CEIbPaF</t>
+          <t>CCF</t>
         </is>
       </c>
       <c r="C215" t="inlineStr">
         <is>
-          <t>Cement Energy Intensity by Pathway and Fuel</t>
-        </is>
-      </c>
+          <t>Calcination CO2 Factor by Pathway</t>
+        </is>
+      </c>
+      <c r="D215" s="7" t="n"/>
+      <c r="E215" s="7" t="n"/>
       <c r="F215" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G215" s="26" t="inlineStr">
+        <is>
+          <t>Chemistry constant (EPA GHGI calcination factor); same worldwide.</t>
         </is>
       </c>
     </row>
@@ -6277,24 +6815,22 @@
       </c>
       <c r="B216" t="inlineStr">
         <is>
-          <t>CNBEIR</t>
+          <t>CEIbPaF</t>
         </is>
       </c>
       <c r="C216" t="inlineStr">
         <is>
-          <t>Cement New Build Energy Intensity Ratio</t>
-        </is>
-      </c>
+          <t>Cement Energy Intensity by Pathway and Fuel</t>
+        </is>
+      </c>
+      <c r="D216" s="7" t="n"/>
+      <c r="E216" s="7" t="n"/>
       <c r="F216" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Engineering ratio (BAT over fleet-typical thermal intensity); update if the region fleet is far from the US 3.43 GJ/t basis.</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G216" s="26" t="n"/>
     </row>
     <row r="217" ht="30" customHeight="1">
       <c r="A217" t="inlineStr">
@@ -6304,17 +6840,24 @@
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>CPAL</t>
+          <t>CNBEIR</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
         <is>
-          <t>Cement Pathway Asset Life</t>
-        </is>
-      </c>
+          <t>Cement New Build Energy Intensity Ratio</t>
+        </is>
+      </c>
+      <c r="D217" s="7" t="n"/>
+      <c r="E217" s="7" t="n"/>
       <c r="F217" t="inlineStr">
         <is>
           <t>low</t>
+        </is>
+      </c>
+      <c r="G217" s="26" t="inlineStr">
+        <is>
+          <t>Engineering ratio (BAT over fleet-typical thermal intensity); update if the region fleet is far from the US 3.43 GJ/t basis.</t>
         </is>
       </c>
     </row>
@@ -6326,19 +6869,22 @@
       </c>
       <c r="B218" t="inlineStr">
         <is>
-          <t>CPCC</t>
+          <t>CPAL</t>
         </is>
       </c>
       <c r="C218" t="inlineStr">
         <is>
-          <t>Cement Pathway Capital Cost per Unit Annual Capacity</t>
-        </is>
-      </c>
+          <t>Cement Pathway Asset Life</t>
+        </is>
+      </c>
+      <c r="D218" s="7" t="n"/>
+      <c r="E218" s="7" t="n"/>
       <c r="F218" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G218" s="26" t="n"/>
     </row>
     <row r="219" ht="45" customHeight="1">
       <c r="A219" t="inlineStr">
@@ -6348,19 +6894,22 @@
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>CPPL</t>
+          <t>CPCC</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
         <is>
-          <t>Cement Pathway Campaign Length</t>
-        </is>
-      </c>
+          <t>Cement Pathway Capital Cost per Unit Annual Capacity</t>
+        </is>
+      </c>
+      <c r="D219" s="7" t="n"/>
+      <c r="E219" s="7" t="n"/>
       <c r="F219" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G219" s="26" t="n"/>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
@@ -6370,24 +6919,22 @@
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>CPRS</t>
+          <t>CPPL</t>
         </is>
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>Cement Preexisting Capacity Overhaul Decision Schedule</t>
-        </is>
-      </c>
+          <t>Cement Pathway Campaign Length</t>
+        </is>
+      </c>
+      <c r="D220" s="7" t="n"/>
+      <c r="E220" s="7" t="n"/>
       <c r="F220" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Build from the country kiln fleet age structure.</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G220" s="26" t="n"/>
     </row>
     <row r="221" ht="45" customHeight="1">
       <c r="A221" t="inlineStr">
@@ -6397,22 +6944,24 @@
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>CPSW</t>
+          <t>CPRS</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>Cement Pathway Shareweight</t>
-        </is>
-      </c>
+          <t>Cement Preexisting Capacity Overhaul Decision Schedule</t>
+        </is>
+      </c>
+      <c r="D221" s="7" t="n"/>
+      <c r="E221" s="7" t="n"/>
       <c r="F221" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Entry-gate years reflect the region-specific commercialization landscape for CCS, electric kilns, and alternative chemistries.</t>
+      <c r="G221" s="26" t="inlineStr">
+        <is>
+          <t>Build from the country kiln fleet age structure.</t>
         </is>
       </c>
     </row>
@@ -6424,17 +6973,24 @@
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>CRCC</t>
+          <t>CPSW</t>
         </is>
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>Cement Overhaul Capital Cost per Unit Annual Capacity</t>
-        </is>
-      </c>
+          <t>Cement Pathway Shareweight</t>
+        </is>
+      </c>
+      <c r="D222" s="7" t="n"/>
+      <c r="E222" s="7" t="n"/>
       <c r="F222" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G222" s="26" t="inlineStr">
+        <is>
+          <t>Entry-gate years reflect the region-specific commercialization landscape for CCS, electric kilns, and alternative chemistries.</t>
         </is>
       </c>
     </row>
@@ -6446,17 +7002,28 @@
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>CRSW</t>
+          <t>CRBW</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>Cement Overhaul Shareweight</t>
-        </is>
-      </c>
+          <t>Cement Replacement Blend Weight vs Tightness</t>
+        </is>
+      </c>
+      <c r="D223" s="7" t="inlineStr">
+        <is>
+          <t>CRBWvT.csv</t>
+        </is>
+      </c>
+      <c r="E223" s="7" t="n"/>
       <c r="F223" t="inlineStr">
         <is>
-          <t>to be determined via calibration</t>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G223" s="26" t="inlineStr">
+        <is>
+          <t>Re-solve the Hill-curve k from the region's start-year utilization and calibrated overhaul share (design memo section 4); shape parameter p is shared.</t>
         </is>
       </c>
     </row>
@@ -6468,14 +7035,22 @@
       </c>
       <c r="B224" t="inlineStr">
         <is>
-          <t>CSoIO</t>
+          <t>CRCC</t>
         </is>
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>Cement Share of Industry 239 Output</t>
-        </is>
-      </c>
+          <t>Cement Overhaul Capital Cost per Unit Annual Capacity</t>
+        </is>
+      </c>
+      <c r="D224" s="7" t="n"/>
+      <c r="E224" s="7" t="n"/>
+      <c r="F224" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G224" s="26" t="n"/>
     </row>
     <row r="225" ht="30" customHeight="1">
       <c r="A225" s="2" t="inlineStr">
@@ -6485,19 +7060,22 @@
       </c>
       <c r="B225" s="2" t="inlineStr">
         <is>
-          <t>EoDfIP</t>
+          <t>CRSW</t>
         </is>
       </c>
       <c r="C225" s="2" t="inlineStr">
         <is>
-          <t>Elasticities of Demand for Industrial Products</t>
-        </is>
-      </c>
+          <t>Cement Overhaul Shareweight</t>
+        </is>
+      </c>
+      <c r="D225" s="7" t="n"/>
+      <c r="E225" s="7" t="n"/>
       <c r="F225" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>to be determined via calibration</t>
+        </is>
+      </c>
+      <c r="G225" s="26" t="n"/>
     </row>
     <row r="226" ht="30" customHeight="1">
       <c r="A226" s="2" t="inlineStr">
@@ -6507,19 +7085,18 @@
       </c>
       <c r="B226" s="2" t="inlineStr">
         <is>
-          <t>EoIEECwEC</t>
+          <t>CSoIO</t>
         </is>
       </c>
       <c r="C226" s="2" t="inlineStr">
         <is>
-          <t>Elasticity of Industrial Equipment Energy Consumption with respect to Energy Cost</t>
-        </is>
-      </c>
-      <c r="F226" s="4" t="inlineStr">
-        <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>Cement Share of Industry 239 Output</t>
+        </is>
+      </c>
+      <c r="D226" s="7" t="n"/>
+      <c r="E226" s="7" t="n"/>
+      <c r="F226" s="4" t="n"/>
+      <c r="G226" s="26" t="n"/>
     </row>
     <row r="227" ht="30" customHeight="1">
       <c r="A227" s="2" t="inlineStr">
@@ -6529,17 +7106,28 @@
       </c>
       <c r="B227" s="2" t="inlineStr">
         <is>
-          <t>EoIEPwEEI</t>
+          <t>CTOA</t>
         </is>
       </c>
       <c r="C227" s="2" t="inlineStr">
         <is>
-          <t>Elasticity of Industrial Equipment Price with respect to Energy Efficiency Improvements</t>
-        </is>
-      </c>
+          <t>Cement Tightness Operating Adder vs Tightness</t>
+        </is>
+      </c>
+      <c r="D227" s="7" t="inlineStr">
+        <is>
+          <t>CTOAvT.csv</t>
+        </is>
+      </c>
+      <c r="E227" s="7" t="n"/>
       <c r="F227" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G227" s="26" t="inlineStr">
+        <is>
+          <t>Regional import-parity / congestion premium at full tightness; inert in the US build - zero is acceptable.</t>
         </is>
       </c>
     </row>
@@ -6551,22 +7139,24 @@
       </c>
       <c r="B228" s="2" t="inlineStr">
         <is>
-          <t>FLRbI</t>
+          <t>CULB</t>
         </is>
       </c>
       <c r="C228" s="2" t="inlineStr">
         <is>
-          <t>Foreign Leakage Rate by Industry</t>
-        </is>
-      </c>
+          <t>Cement Utilization Lower Bound</t>
+        </is>
+      </c>
+      <c r="D228" s="7" t="n"/>
+      <c r="E228" s="7" t="n"/>
       <c r="F228" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G228" s="2" t="inlineStr">
-        <is>
-          <t>You want to estimate induced foreign emissions</t>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G228" s="24" t="inlineStr">
+        <is>
+          <t>Regional historical clinker-utilization trough (envelope lower edge); staged values for 10 regions in the anchors package.</t>
         </is>
       </c>
     </row>
@@ -6578,17 +7168,24 @@
       </c>
       <c r="B229" s="2" t="inlineStr">
         <is>
-          <t>IECCpUAEU</t>
+          <t>CUUB</t>
         </is>
       </c>
       <c r="C229" s="2" t="inlineStr">
         <is>
-          <t>Industrial Equipment Capital Cost per Unit Annual Energy Use</t>
-        </is>
-      </c>
+          <t>Cement Utilization Upper Bound</t>
+        </is>
+      </c>
+      <c r="D229" s="7" t="n"/>
+      <c r="E229" s="7" t="n"/>
       <c r="F229" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G229" s="26" t="inlineStr">
+        <is>
+          <t>Regional historical clinker-utilization peak (envelope upper edge); staged values for 10 regions in the anchors package.</t>
         </is>
       </c>
     </row>
@@ -6600,19 +7197,22 @@
       </c>
       <c r="B230" s="2" t="inlineStr">
         <is>
-          <t>IELC</t>
+          <t>EoDfIP</t>
         </is>
       </c>
       <c r="C230" s="2" t="inlineStr">
         <is>
-          <t>Industrial Equipment Logit Coefficient</t>
-        </is>
-      </c>
+          <t>Elasticities of Demand for Industrial Products</t>
+        </is>
+      </c>
+      <c r="D230" s="7" t="n"/>
+      <c r="E230" s="7" t="n"/>
       <c r="F230" s="14" t="inlineStr">
         <is>
-          <t>to be determined via calibration</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G230" s="26" t="n"/>
     </row>
     <row r="231" ht="30" customHeight="1">
       <c r="A231" s="2" t="inlineStr">
@@ -6622,19 +7222,22 @@
       </c>
       <c r="B231" s="2" t="inlineStr">
         <is>
-          <t>IES</t>
+          <t>EoIEECwEC</t>
         </is>
       </c>
       <c r="C231" s="2" t="inlineStr">
         <is>
-          <t>Industrial Equipment Shareweights</t>
-        </is>
-      </c>
+          <t>Elasticity of Industrial Equipment Energy Consumption with respect to Energy Cost</t>
+        </is>
+      </c>
+      <c r="D231" s="7" t="n"/>
+      <c r="E231" s="7" t="n"/>
       <c r="F231" s="14" t="inlineStr">
         <is>
-          <t>to be determined via calibration</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G231" s="26" t="n"/>
     </row>
     <row r="232" ht="30" customHeight="1">
       <c r="A232" s="2" t="inlineStr">
@@ -6644,19 +7247,22 @@
       </c>
       <c r="B232" s="2" t="inlineStr">
         <is>
-          <t>IEMUEF</t>
+          <t>EoIEPwEEI</t>
         </is>
       </c>
       <c r="C232" s="2" t="inlineStr">
         <is>
-          <t>Industrial Equipment Minimum Unit Energy Factor</t>
-        </is>
-      </c>
+          <t>Elasticity of Industrial Equipment Price with respect to Energy Efficiency Improvements</t>
+        </is>
+      </c>
+      <c r="D232" s="7" t="n"/>
+      <c r="E232" s="7" t="n"/>
       <c r="F232" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G232" s="26" t="n"/>
     </row>
     <row r="233" ht="30" customHeight="1">
       <c r="A233" s="2" t="inlineStr">
@@ -6666,27 +7272,24 @@
       </c>
       <c r="B233" s="2" t="inlineStr">
         <is>
-          <t>IESD</t>
+          <t>FLRbI</t>
         </is>
       </c>
       <c r="C233" s="2" t="inlineStr">
         <is>
-          <t>Industrial Equipment Survival Data</t>
-        </is>
-      </c>
-      <c r="D233" s="2" t="inlineStr">
-        <is>
-          <t>Start Year Share of Industrial Equipment by Vintage, Retiring Fraction of Industrial Equipment Retiring by Age, Average Age at Which Equipment Retires</t>
-        </is>
-      </c>
+          <t>Foreign Leakage Rate by Industry</t>
+        </is>
+      </c>
+      <c r="D233" s="1" t="n"/>
+      <c r="E233" s="7" t="n"/>
       <c r="F233" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G233" s="2" t="inlineStr">
-        <is>
-          <t>"Start Year Share of Industrial Equipment by Vintage" must be updated if changing the first simulated year (Initial Time)</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G233" s="24" t="inlineStr">
+        <is>
+          <t>You want to estimate induced foreign emissions</t>
         </is>
       </c>
     </row>
@@ -6698,19 +7301,22 @@
       </c>
       <c r="B234" s="2" t="inlineStr">
         <is>
-          <t>IESE</t>
+          <t>IECCpUAEU</t>
         </is>
       </c>
       <c r="C234" s="2" t="inlineStr">
         <is>
-          <t>Import Export Substitution Elasticities</t>
-        </is>
-      </c>
+          <t>Industrial Equipment Capital Cost per Unit Annual Energy Use</t>
+        </is>
+      </c>
+      <c r="D234" s="7" t="n"/>
+      <c r="E234" s="7" t="n"/>
       <c r="F234" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G234" s="26" t="n"/>
     </row>
     <row r="235" ht="30" customHeight="1">
       <c r="A235" s="2" t="inlineStr">
@@ -6720,19 +7326,22 @@
       </c>
       <c r="B235" s="2" t="inlineStr">
         <is>
-          <t>IFSR</t>
+          <t>IELC</t>
         </is>
       </c>
       <c r="C235" s="2" t="inlineStr">
         <is>
-          <t>Industrial Fuel Shifting Ratio</t>
-        </is>
-      </c>
+          <t>Industrial Equipment Logit Coefficient</t>
+        </is>
+      </c>
+      <c r="D235" s="7" t="n"/>
+      <c r="E235" s="7" t="n"/>
       <c r="F235" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>to be determined via calibration</t>
+        </is>
+      </c>
+      <c r="G235" s="26" t="n"/>
     </row>
     <row r="236" ht="30" customHeight="1">
       <c r="A236" s="2" t="inlineStr">
@@ -6742,19 +7351,22 @@
       </c>
       <c r="B236" s="2" t="inlineStr">
         <is>
-          <t>IFSRF</t>
+          <t>IEMUEF</t>
         </is>
       </c>
       <c r="C236" s="2" t="inlineStr">
         <is>
-          <t>Industrial Feedstock Switching Recipient Fuel</t>
-        </is>
-      </c>
+          <t>Industrial Equipment Minimum Unit Energy Factor</t>
+        </is>
+      </c>
+      <c r="D236" s="7" t="n"/>
+      <c r="E236" s="7" t="n"/>
       <c r="F236" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G236" s="26" t="n"/>
     </row>
     <row r="237" ht="30" customHeight="1">
       <c r="A237" s="2" t="inlineStr">
@@ -6764,24 +7376,22 @@
       </c>
       <c r="B237" s="2" t="inlineStr">
         <is>
-          <t>IFStE</t>
+          <t>IES</t>
         </is>
       </c>
       <c r="C237" s="2" t="inlineStr">
         <is>
-          <t>Industrial Fuels Subject to Electrification</t>
-        </is>
-      </c>
+          <t>Industrial Equipment Shareweights</t>
+        </is>
+      </c>
+      <c r="D237" s="7" t="n"/>
+      <c r="E237" s="7" t="n"/>
       <c r="F237" s="6" t="inlineStr">
         <is>
-          <t>n/a (policy lever)</t>
-        </is>
-      </c>
-      <c r="G237" s="2" t="inlineStr">
-        <is>
-          <t>You wish for the industrial fuel shifting policy lever to affect a different set of source (BAU) fuel types than the default set (which consists of the fossil fuels).</t>
-        </is>
-      </c>
+          <t>to be determined via calibration</t>
+        </is>
+      </c>
+      <c r="G237" s="24" t="n"/>
     </row>
     <row r="238" ht="30" customHeight="1">
       <c r="A238" s="2" t="inlineStr">
@@ -6791,17 +7401,28 @@
       </c>
       <c r="B238" s="2" t="inlineStr">
         <is>
-          <t>IFTQfEERP</t>
+          <t>IESD</t>
         </is>
       </c>
       <c r="C238" s="2" t="inlineStr">
         <is>
-          <t>Industrial Fuel Types Qualifying for Early Equipment Retirement Policy</t>
-        </is>
-      </c>
+          <t>Industrial Equipment Survival Data</t>
+        </is>
+      </c>
+      <c r="D238" s="7" t="inlineStr">
+        <is>
+          <t>Start Year Share of Industrial Equipment by Vintage, Retiring Fraction of Industrial Equipment Retiring by Age, Average Age at Which Equipment Retires</t>
+        </is>
+      </c>
+      <c r="E238" s="7" t="n"/>
       <c r="F238" s="4" t="inlineStr">
         <is>
           <t>low</t>
+        </is>
+      </c>
+      <c r="G238" s="26" t="inlineStr">
+        <is>
+          <t>"Start Year Share of Industrial Equipment by Vintage" must be updated if changing the first simulated year (Initial Time)</t>
         </is>
       </c>
     </row>
@@ -6813,24 +7434,22 @@
       </c>
       <c r="B239" s="2" t="inlineStr">
         <is>
-          <t>IFTQfS</t>
+          <t>IESE</t>
         </is>
       </c>
       <c r="C239" s="2" t="inlineStr">
         <is>
-          <t>Industrial Fuels Qualifying for Support</t>
-        </is>
-      </c>
-      <c r="D239" s="2" t="inlineStr">
-        <is>
-          <t>Industrial Fuels Qualifying for PTC, Industrial Fuels Qualifying for ITC, Industrial Fuels Qualifying for Loans</t>
-        </is>
-      </c>
+          <t>Import Export Substitution Elasticities</t>
+        </is>
+      </c>
+      <c r="D239" s="1" t="n"/>
+      <c r="E239" s="7" t="n"/>
       <c r="F239" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G239" s="26" t="n"/>
     </row>
     <row r="240" ht="30" customHeight="1">
       <c r="A240" t="inlineStr">
@@ -6840,24 +7459,22 @@
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>MASCM</t>
+          <t>IFSR</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
         <is>
-          <t>Maximum Annual SCM Supply for Cement</t>
-        </is>
-      </c>
+          <t>Industrial Fuel Shifting Ratio</t>
+        </is>
+      </c>
+      <c r="D240" s="7" t="n"/>
+      <c r="E240" s="7" t="n"/>
       <c r="F240" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G240" t="inlineStr">
-        <is>
-          <t>Regional SCM supply (fly ash, slag, pozzolans) requires country-specific data from ash/slag associations or national statistics.</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G240" s="26" t="n"/>
     </row>
     <row r="241" ht="15.75" customHeight="1" thickBot="1">
       <c r="A241" s="2" t="inlineStr">
@@ -6867,19 +7484,22 @@
       </c>
       <c r="B241" s="2" t="inlineStr">
         <is>
-          <t>MHV</t>
+          <t>IFSRF</t>
         </is>
       </c>
       <c r="C241" s="2" t="inlineStr">
         <is>
-          <t>Methane Heating Value</t>
-        </is>
-      </c>
+          <t>Industrial Feedstock Switching Recipient Fuel</t>
+        </is>
+      </c>
+      <c r="D241" s="7" t="n"/>
+      <c r="E241" s="7" t="n"/>
       <c r="F241" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G241" s="26" t="n"/>
     </row>
     <row r="242">
       <c r="A242" s="2" t="inlineStr">
@@ -6889,22 +7509,24 @@
       </c>
       <c r="B242" s="2" t="inlineStr">
         <is>
-          <t>NIEAFSM</t>
+          <t>IFStE</t>
         </is>
       </c>
       <c r="C242" s="2" t="inlineStr">
         <is>
-          <t>New Industrial Equipment Alternative Fuel Shifting Matrix</t>
-        </is>
-      </c>
+          <t>Industrial Fuels Subject to Electrification</t>
+        </is>
+      </c>
+      <c r="D242" s="7" t="n"/>
+      <c r="E242" s="7" t="n"/>
       <c r="F242" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G242" s="2" t="inlineStr">
-        <is>
-          <t>If applying fuel shifting policies other than a shift to hydrogen combustion (e.g., coal-to-gas policies).</t>
+          <t>n/a (policy lever)</t>
+        </is>
+      </c>
+      <c r="G242" s="24" t="inlineStr">
+        <is>
+          <t>You wish for the industrial fuel shifting policy lever to affect a different set of source (BAU) fuel types than the default set (which consists of the fossil fuels).</t>
         </is>
       </c>
     </row>
@@ -6916,24 +7538,22 @@
       </c>
       <c r="B243" t="inlineStr">
         <is>
-          <t>PACS</t>
+          <t>IFTQfEERP</t>
         </is>
       </c>
       <c r="C243" t="inlineStr">
         <is>
-          <t>Potential Additional Clinker Substitution</t>
-        </is>
-      </c>
+          <t>Industrial Fuel Types Qualifying for Early Equipment Retirement Policy</t>
+        </is>
+      </c>
+      <c r="D243" s="7" t="n"/>
+      <c r="E243" s="7" t="n"/>
       <c r="F243" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G243" t="inlineStr">
-        <is>
-          <t>Achievable clinker-ratio reduction depends on regional cement standards, SCM markets, and the BAU ratio trajectory.</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G243" s="26" t="n"/>
     </row>
     <row r="244">
       <c r="A244" s="2" t="inlineStr">
@@ -6943,29 +7563,26 @@
       </c>
       <c r="B244" s="2" t="inlineStr">
         <is>
-          <t>PEAAC</t>
+          <t>IFTQfS</t>
         </is>
       </c>
       <c r="C244" s="2" t="inlineStr">
         <is>
-          <t>Process Emissions Additions and Costs</t>
-        </is>
-      </c>
-      <c r="D244" s="2" t="inlineStr">
-        <is>
-          <t>Process Emissions Additions and Costs, Marginal Cost Definitions</t>
-        </is>
-      </c>
+          <t>Industrial Fuels Qualifying for Support</t>
+        </is>
+      </c>
+      <c r="D244" s="1" t="inlineStr">
+        <is>
+          <t>Industrial Fuels Qualifying for PTC, Industrial Fuels Qualifying for ITC, Industrial Fuels Qualifying for Loans</t>
+        </is>
+      </c>
+      <c r="E244" s="7" t="n"/>
       <c r="F244" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G244" s="2" t="inlineStr">
-        <is>
-          <t>You want to test the addition rather than the reduction of process emissions for select industries</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G244" s="24" t="n"/>
     </row>
     <row r="245">
       <c r="A245" s="2" t="inlineStr">
@@ -6975,22 +7592,24 @@
       </c>
       <c r="B245" s="2" t="inlineStr">
         <is>
-          <t>PERAC</t>
+          <t>MACtCR</t>
         </is>
       </c>
       <c r="C245" s="2" t="inlineStr">
         <is>
-          <t>Process Emissions Reductions and Costs</t>
-        </is>
-      </c>
-      <c r="D245" s="2" t="inlineStr">
-        <is>
-          <t>Process Emissions Reductions and Costs, Marginal Cost Definitions</t>
-        </is>
-      </c>
+          <t>Minimum Achievable Clinker to Cement Ratio</t>
+        </is>
+      </c>
+      <c r="D245" s="1" t="n"/>
+      <c r="E245" s="7" t="n"/>
       <c r="F245" s="14" t="inlineStr">
         <is>
-          <t>only adjust country selector (and non-country multipliers, if applicable)</t>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G245" s="26" t="inlineStr">
+        <is>
+          <t>Achievable clinker-to-cement ratio at full SCM deployment depends on regional cement standards, SCM availability, and the BAU ratio (use the regional GCCA/association roadmap).</t>
         </is>
       </c>
     </row>
@@ -7002,19 +7621,22 @@
       </c>
       <c r="B246" s="2" t="inlineStr">
         <is>
-          <t>PIFURfE</t>
+          <t>MHV</t>
         </is>
       </c>
       <c r="C246" s="2" t="inlineStr">
         <is>
-          <t>Percentage Industry Fuel Use Reduction for Electricity</t>
-        </is>
-      </c>
+          <t>Methane Heating Value</t>
+        </is>
+      </c>
+      <c r="D246" s="7" t="n"/>
+      <c r="E246" s="7" t="n"/>
       <c r="F246" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G246" s="26" t="n"/>
     </row>
     <row r="247">
       <c r="A247" s="2" t="inlineStr">
@@ -7024,17 +7646,24 @@
       </c>
       <c r="B247" s="2" t="inlineStr">
         <is>
-          <t>PoONEUTiMEbIC</t>
+          <t>NIEAFSM</t>
         </is>
       </c>
       <c r="C247" s="2" t="inlineStr">
         <is>
-          <t>Percent of Other Nonprocess Energy Use That is Mobile Equipment by ISIC Code</t>
-        </is>
-      </c>
+          <t>New Industrial Equipment Alternative Fuel Shifting Matrix</t>
+        </is>
+      </c>
+      <c r="D247" s="7" t="n"/>
+      <c r="E247" s="7" t="n"/>
       <c r="F247" s="4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G247" s="26" t="inlineStr">
+        <is>
+          <t>If applying fuel shifting policies other than a shift to hydrogen combustion (e.g., coal-to-gas policies).</t>
         </is>
       </c>
     </row>
@@ -7046,17 +7675,28 @@
       </c>
       <c r="B248" s="2" t="inlineStr">
         <is>
-          <t>RoNEPtAPPpULA</t>
+          <t>PEAAC</t>
         </is>
       </c>
       <c r="C248" s="2" t="inlineStr">
         <is>
-          <t>Ratio of Nutritionally Equivalent Plant to Animal Products Produced per Unit Land Area</t>
-        </is>
-      </c>
+          <t>Process Emissions Additions and Costs</t>
+        </is>
+      </c>
+      <c r="D248" s="7" t="inlineStr">
+        <is>
+          <t>Process Emissions Additions and Costs, Marginal Cost Definitions</t>
+        </is>
+      </c>
+      <c r="E248" s="7" t="n"/>
       <c r="F248" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G248" s="26" t="inlineStr">
+        <is>
+          <t>You want to test the addition rather than the reduction of process emissions for select industries</t>
         </is>
       </c>
     </row>
@@ -7068,19 +7708,26 @@
       </c>
       <c r="B249" s="2" t="inlineStr">
         <is>
-          <t>RPfFISCC</t>
+          <t>PERAC</t>
         </is>
       </c>
       <c r="C249" s="2" t="inlineStr">
         <is>
-          <t>Repayment Period for Financed Industry Sector Capital Costs</t>
-        </is>
-      </c>
+          <t>Process Emissions Reductions and Costs</t>
+        </is>
+      </c>
+      <c r="D249" s="7" t="inlineStr">
+        <is>
+          <t>Process Emissions Reductions and Costs, Marginal Cost Definitions</t>
+        </is>
+      </c>
+      <c r="E249" s="7" t="n"/>
       <c r="F249" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>only adjust country selector (and non-country multipliers, if applicable)</t>
+        </is>
+      </c>
+      <c r="G249" s="26" t="n"/>
     </row>
     <row r="250">
       <c r="A250" t="inlineStr">
@@ -7090,24 +7737,22 @@
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>SCMEI</t>
+          <t>PIFURfE</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
         <is>
-          <t>SCM Production Energy per Ton of Substitution</t>
-        </is>
-      </c>
+          <t>Percentage Industry Fuel Use Reduction for Electricity</t>
+        </is>
+      </c>
+      <c r="D250" s="7" t="n"/>
+      <c r="E250" s="7" t="n"/>
       <c r="F250" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G250" t="inlineStr">
-        <is>
-          <t>Marginal-SCM mix (calcined clay share) is region-specific.</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G250" s="26" t="n"/>
     </row>
     <row r="251">
       <c r="A251" s="2" t="inlineStr">
@@ -7117,19 +7762,22 @@
       </c>
       <c r="B251" s="2" t="inlineStr">
         <is>
-          <t>SoCaOMSbRIC</t>
+          <t>PoONEUTiMEbIC</t>
         </is>
       </c>
       <c r="C251" s="2" t="inlineStr">
         <is>
-          <t>Share of Capital and OM Spending by Recipient ISIC Code</t>
-        </is>
-      </c>
+          <t>Percent of Other Nonprocess Energy Use That is Mobile Equipment by ISIC Code</t>
+        </is>
+      </c>
+      <c r="D251" s="7" t="n"/>
+      <c r="E251" s="7" t="n"/>
       <c r="F251" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G251" s="26" t="n"/>
     </row>
     <row r="252" ht="30" customHeight="1">
       <c r="A252" s="2" t="inlineStr">
@@ -7139,19 +7787,22 @@
       </c>
       <c r="B252" s="2" t="inlineStr">
         <is>
-          <t>SoCiIEPTtB</t>
+          <t>RoNEPtAPPpULA</t>
         </is>
       </c>
       <c r="C252" s="2" t="inlineStr">
         <is>
-          <t>Share of Change in Industry Expenses Passed Through to Buyers</t>
-        </is>
-      </c>
+          <t>Ratio of Nutritionally Equivalent Plant to Animal Products Produced per Unit Land Area</t>
+        </is>
+      </c>
+      <c r="D252" s="7" t="n"/>
+      <c r="E252" s="7" t="n"/>
       <c r="F252" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G252" s="26" t="n"/>
     </row>
     <row r="253" ht="30" customHeight="1">
       <c r="A253" s="2" t="inlineStr">
@@ -7161,19 +7812,22 @@
       </c>
       <c r="B253" s="2" t="inlineStr">
         <is>
-          <t>SoFCTiBoSFbI</t>
+          <t>RPfFISCC</t>
         </is>
       </c>
       <c r="C253" s="2" t="inlineStr">
         <is>
-          <t>Share of Fuel Consumption that is Byproduct or Secondary Fuel by Industry</t>
-        </is>
-      </c>
+          <t>Repayment Period for Financed Industry Sector Capital Costs</t>
+        </is>
+      </c>
+      <c r="D253" s="7" t="n"/>
+      <c r="E253" s="7" t="n"/>
       <c r="F253" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G253" s="26" t="n"/>
     </row>
     <row r="254">
       <c r="A254" s="2" t="inlineStr">
@@ -7183,17 +7837,24 @@
       </c>
       <c r="B254" s="2" t="inlineStr">
         <is>
-          <t>SoICETAF</t>
+          <t>SCMEI</t>
         </is>
       </c>
       <c r="C254" s="2" t="inlineStr">
         <is>
-          <t>Share of Industry Capital Expenditures That Are Financed</t>
-        </is>
-      </c>
+          <t>SCM Production Energy per Ton of Substitution</t>
+        </is>
+      </c>
+      <c r="D254" s="7" t="n"/>
+      <c r="E254" s="7" t="n"/>
       <c r="F254" s="5" t="inlineStr">
         <is>
           <t>medium</t>
+        </is>
+      </c>
+      <c r="G254" s="26" t="inlineStr">
+        <is>
+          <t>Marginal-SCM mix (calcined clay share) is region-specific.</t>
         </is>
       </c>
     </row>
@@ -7205,19 +7866,22 @@
       </c>
       <c r="B255" s="2" t="inlineStr">
         <is>
-          <t>SoPEASbRIC</t>
+          <t>SoCaOMSbRIC</t>
         </is>
       </c>
       <c r="C255" s="2" t="inlineStr">
         <is>
-          <t>Share of Process Emissions Abatement Spending by Recipient ISIC Code</t>
-        </is>
-      </c>
+          <t>Share of Capital and OM Spending by Recipient ISIC Code</t>
+        </is>
+      </c>
+      <c r="D255" s="7" t="n"/>
+      <c r="E255" s="7" t="n"/>
       <c r="F255" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G255" s="26" t="n"/>
     </row>
     <row r="256">
       <c r="A256" t="inlineStr">
@@ -7227,19 +7891,22 @@
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>SYCCU</t>
+          <t>SoCiIEPTtB</t>
         </is>
       </c>
       <c r="C256" t="inlineStr">
         <is>
-          <t>Start Year Cement Capacity Utilization</t>
-        </is>
-      </c>
+          <t>Share of Change in Industry Expenses Passed Through to Buyers</t>
+        </is>
+      </c>
+      <c r="D256" s="7" t="n"/>
+      <c r="E256" s="7" t="n"/>
       <c r="F256" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G256" s="26" t="n"/>
     </row>
     <row r="257">
       <c r="A257" t="inlineStr">
@@ -7249,19 +7916,22 @@
       </c>
       <c r="B257" t="inlineStr">
         <is>
-          <t>SYCPbP</t>
+          <t>SoFCTiBoSFbI</t>
         </is>
       </c>
       <c r="C257" t="inlineStr">
         <is>
-          <t>Start Year Clinker Production by Pathway</t>
-        </is>
-      </c>
+          <t>Share of Fuel Consumption that is Byproduct or Secondary Fuel by Industry</t>
+        </is>
+      </c>
+      <c r="D257" s="7" t="n"/>
+      <c r="E257" s="7" t="n"/>
       <c r="F257" t="inlineStr">
         <is>
-          <t>very high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G257" s="26" t="n"/>
     </row>
     <row r="258" ht="30" customHeight="1">
       <c r="A258" t="inlineStr">
@@ -7271,24 +7941,22 @@
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>TBCC</t>
+          <t>SoICETAF</t>
         </is>
       </c>
       <c r="C258" t="inlineStr">
         <is>
-          <t>Thermal Battery Capital Cost per Unit Annual Energy Served</t>
-        </is>
-      </c>
+          <t>Share of Industry Capital Expenditures That Are Financed</t>
+        </is>
+      </c>
+      <c r="D258" s="7" t="n"/>
+      <c r="E258" s="7" t="n"/>
       <c r="F258" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G258" t="inlineStr">
-        <is>
-          <t>You wish to include industrial thermal batteries as a heat technology option.</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G258" s="26" t="n"/>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
@@ -7298,24 +7966,22 @@
       </c>
       <c r="B259" t="inlineStr">
         <is>
-          <t>TBEM</t>
+          <t>SoPEASbRIC</t>
         </is>
       </c>
       <c r="C259" t="inlineStr">
         <is>
-          <t>Thermal Battery Eligibility Mask</t>
-        </is>
-      </c>
+          <t>Share of Process Emissions Abatement Spending by Recipient ISIC Code</t>
+        </is>
+      </c>
+      <c r="D259" s="7" t="n"/>
+      <c r="E259" s="7" t="n"/>
       <c r="F259" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>You wish to include industrial thermal batteries as a heat technology option.</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G259" s="26" t="n"/>
     </row>
     <row r="260">
       <c r="A260" t="inlineStr">
@@ -7325,24 +7991,22 @@
       </c>
       <c r="B260" t="inlineStr">
         <is>
-          <t>TBMLE</t>
+          <t>SYCCU</t>
         </is>
       </c>
       <c r="C260" t="inlineStr">
         <is>
-          <t>Thermal Battery Charging Mode Logit Exponent</t>
-        </is>
-      </c>
+          <t>Start Year Cement Capacity Utilization</t>
+        </is>
+      </c>
+      <c r="D260" s="7" t="n"/>
+      <c r="E260" s="7" t="n"/>
       <c r="F260" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G260" t="inlineStr">
-        <is>
-          <t>You wish to include industrial thermal batteries; sharpness of the grid vs off-grid charging mode competition.</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G260" s="26" t="n"/>
     </row>
     <row r="261" ht="30" customHeight="1">
       <c r="A261" t="inlineStr">
@@ -7352,24 +8016,22 @@
       </c>
       <c r="B261" t="inlineStr">
         <is>
-          <t>TBMS</t>
+          <t>SYCPbP</t>
         </is>
       </c>
       <c r="C261" t="inlineStr">
         <is>
-          <t>Thermal Battery Charging Mode Shareweights</t>
-        </is>
-      </c>
+          <t>Start Year Clinker Production by Pathway</t>
+        </is>
+      </c>
+      <c r="D261" s="7" t="n"/>
+      <c r="E261" s="7" t="n"/>
       <c r="F261" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G261" t="inlineStr">
-        <is>
-          <t>You wish to include industrial thermal batteries; set a mode to 0 to disable it (replaces the former SoTBCfG control setting).</t>
-        </is>
-      </c>
+          <t>very high</t>
+        </is>
+      </c>
+      <c r="G261" s="26" t="n"/>
     </row>
     <row r="262" ht="15.75" customHeight="1" thickBot="1">
       <c r="A262" t="inlineStr">
@@ -7379,24 +8041,22 @@
       </c>
       <c r="B262" t="inlineStr">
         <is>
-          <t>TBPD</t>
+          <t>SYIEUEFbIPaF</t>
         </is>
       </c>
       <c r="C262" t="inlineStr">
         <is>
-          <t>Thermal Battery PTC Duration</t>
-        </is>
-      </c>
+          <t>Start Year Industrial Equipment Unit Energy Factor by Industrial Process and Fuel</t>
+        </is>
+      </c>
+      <c r="D262" s="7" t="n"/>
+      <c r="E262" s="7" t="n"/>
       <c r="F262" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>You wish to include thermal battery production tax credits; years each vintage keeps its placed-in-service rate.</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G262" s="26" t="n"/>
     </row>
     <row r="263" ht="15.75" customHeight="1" thickBot="1">
       <c r="A263" t="inlineStr">
@@ -7406,20 +8066,22 @@
       </c>
       <c r="B263" t="inlineStr">
         <is>
-          <t>TBRTE</t>
+          <t>TBCC</t>
         </is>
       </c>
       <c r="C263" t="inlineStr">
         <is>
-          <t>Thermal Battery Round Trip Efficiency</t>
-        </is>
-      </c>
+          <t>Thermal Battery Capital Cost per Unit Annual Energy Served</t>
+        </is>
+      </c>
+      <c r="D263" s="7" t="n"/>
+      <c r="E263" s="7" t="n"/>
       <c r="F263" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G263" t="inlineStr">
+      <c r="G263" s="26" t="inlineStr">
         <is>
           <t>You wish to include industrial thermal batteries as a heat technology option.</t>
         </is>
@@ -7433,20 +8095,22 @@
       </c>
       <c r="B264" t="inlineStr">
         <is>
-          <t>TBS</t>
+          <t>TBEM</t>
         </is>
       </c>
       <c r="C264" t="inlineStr">
         <is>
-          <t>Thermal Battery Shareweight</t>
-        </is>
-      </c>
+          <t>Thermal Battery Eligibility Mask</t>
+        </is>
+      </c>
+      <c r="D264" s="7" t="n"/>
+      <c r="E264" s="7" t="n"/>
       <c r="F264" t="inlineStr">
         <is>
           <t>optional</t>
         </is>
       </c>
-      <c r="G264" t="inlineStr">
+      <c r="G264" s="26" t="inlineStr">
         <is>
           <t>You wish to include industrial thermal batteries as a heat technology option.</t>
         </is>
@@ -7460,17 +8124,24 @@
       </c>
       <c r="B265" s="2" t="inlineStr">
         <is>
-          <t>SYIEUEFbIPaF</t>
+          <t>TBMLE</t>
         </is>
       </c>
       <c r="C265" s="2" t="inlineStr">
         <is>
-          <t>Start Year Industrial Equipment Unit Energy Factor by Industrial Process and Fuel</t>
-        </is>
-      </c>
+          <t>Thermal Battery Charging Mode Logit Exponent</t>
+        </is>
+      </c>
+      <c r="D265" s="7" t="n"/>
+      <c r="E265" s="7" t="n"/>
       <c r="F265" s="3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G265" s="26" t="inlineStr">
+        <is>
+          <t>You wish to include industrial thermal batteries; sharpness of the grid vs off-grid charging mode competition.</t>
         </is>
       </c>
     </row>
@@ -7482,17 +8153,24 @@
       </c>
       <c r="B266" s="2" t="inlineStr">
         <is>
-          <t>WHRCC</t>
+          <t>TBMS</t>
         </is>
       </c>
       <c r="C266" s="2" t="inlineStr">
         <is>
-          <t>Waste Heat Recovery Capital Costs</t>
-        </is>
-      </c>
+          <t>Thermal Battery Charging Mode Shareweights</t>
+        </is>
+      </c>
+      <c r="D266" s="7" t="n"/>
+      <c r="E266" s="7" t="n"/>
       <c r="F266" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G266" s="26" t="inlineStr">
+        <is>
+          <t>You wish to include industrial thermal batteries; set a mode to 0 to disable it (replaces the former SoTBCfG control setting).</t>
         </is>
       </c>
     </row>
@@ -7504,120 +8182,134 @@
       </c>
       <c r="B267" s="17" t="inlineStr">
         <is>
-          <t>WHRPbI</t>
+          <t>TBPD</t>
         </is>
       </c>
       <c r="C267" s="17" t="inlineStr">
         <is>
-          <t>Waste Heat Recovery Potential by Industry</t>
-        </is>
-      </c>
-      <c r="D267" s="17" t="n"/>
-      <c r="E267" s="17" t="n"/>
+          <t>Thermal Battery PTC Duration</t>
+        </is>
+      </c>
+      <c r="D267" s="27" t="n"/>
+      <c r="E267" s="27" t="n"/>
       <c r="F267" s="18" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
-      <c r="G267" s="17" t="n"/>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G267" s="28" t="inlineStr">
+        <is>
+          <t>You wish to include thermal battery production tax credits; years each vintage keeps its placed-in-service rate.</t>
+        </is>
+      </c>
     </row>
     <row r="268">
       <c r="A268" s="2" t="inlineStr">
         <is>
-          <t>io-model</t>
+          <t>indst</t>
         </is>
       </c>
       <c r="B268" s="2" t="inlineStr">
         <is>
-          <t>ACTR</t>
+          <t>TBRTE</t>
         </is>
       </c>
       <c r="C268" s="2" t="inlineStr">
         <is>
-          <t>Avg Corp Tax Rate</t>
-        </is>
-      </c>
+          <t>Thermal Battery Round Trip Efficiency</t>
+        </is>
+      </c>
+      <c r="D268" s="7" t="n"/>
+      <c r="E268" s="7" t="n"/>
       <c r="F268" s="3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G268" s="26" t="inlineStr">
+        <is>
+          <t>You wish to include industrial thermal batteries as a heat technology option.</t>
         </is>
       </c>
     </row>
     <row r="269">
       <c r="A269" s="2" t="inlineStr">
         <is>
-          <t>io-model</t>
+          <t>indst</t>
         </is>
       </c>
       <c r="B269" s="2" t="inlineStr">
         <is>
-          <t>BDCSoCaESoPbIC</t>
+          <t>TBS</t>
         </is>
       </c>
       <c r="C269" s="2" t="inlineStr">
         <is>
-          <t>BAU Domestic Content Share of Consumption and Export Share of Production by ISIC Code</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
-        <is>
-          <t>BAU Domestic Content Share of Consumption, BAU Export Share of Production</t>
-        </is>
-      </c>
+          <t>Thermal Battery Shareweight</t>
+        </is>
+      </c>
+      <c r="D269" s="1" t="n"/>
+      <c r="E269" s="7" t="n"/>
       <c r="F269" s="3" t="inlineStr">
         <is>
-          <t>high</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G269" s="26" t="inlineStr">
+        <is>
+          <t>You wish to include industrial thermal batteries as a heat technology option.</t>
         </is>
       </c>
     </row>
     <row r="270" ht="30" customHeight="1">
       <c r="A270" s="2" t="inlineStr">
         <is>
-          <t>io-model</t>
+          <t>indst</t>
         </is>
       </c>
       <c r="B270" s="2" t="inlineStr">
         <is>
-          <t>BEaCP</t>
+          <t>WHRCC</t>
         </is>
       </c>
       <c r="C270" s="2" t="inlineStr">
         <is>
-          <t>BAU Employment and Compensation Projections</t>
-        </is>
-      </c>
-      <c r="D270" s="2" t="inlineStr">
-        <is>
-          <t>Employees, Employee Compensation</t>
-        </is>
-      </c>
+          <t>Waste Heat Recovery Capital Costs</t>
+        </is>
+      </c>
+      <c r="D270" s="1" t="n"/>
+      <c r="E270" s="7" t="n"/>
       <c r="F270" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G270" s="26" t="n"/>
     </row>
     <row r="271" ht="30" customHeight="1">
       <c r="A271" s="2" t="inlineStr">
         <is>
-          <t>io-model</t>
+          <t>indst</t>
         </is>
       </c>
       <c r="B271" s="2" t="inlineStr">
         <is>
-          <t>BEbIC</t>
+          <t>WHRPbI</t>
         </is>
       </c>
       <c r="C271" s="2" t="inlineStr">
         <is>
-          <t>BAU Employment by ISIC Code</t>
-        </is>
-      </c>
+          <t>Waste Heat Recovery Potential by Industry</t>
+        </is>
+      </c>
+      <c r="D271" s="7" t="n"/>
+      <c r="E271" s="7" t="n"/>
       <c r="F271" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G271" s="26" t="n"/>
     </row>
     <row r="272" ht="30.75" customHeight="1" thickBot="1">
       <c r="A272" s="2" t="inlineStr">
@@ -7627,19 +8319,22 @@
       </c>
       <c r="B272" s="2" t="inlineStr">
         <is>
-          <t>BECbIC</t>
+          <t>ACTR</t>
         </is>
       </c>
       <c r="C272" s="2" t="inlineStr">
         <is>
-          <t>BAU Employee Compensation by ISIC Code</t>
-        </is>
-      </c>
+          <t>Avg Corp Tax Rate</t>
+        </is>
+      </c>
+      <c r="D272" s="7" t="n"/>
+      <c r="E272" s="7" t="n"/>
       <c r="F272" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G272" s="26" t="n"/>
     </row>
     <row r="273" ht="30" customHeight="1">
       <c r="A273" s="2" t="inlineStr">
@@ -7649,19 +8344,26 @@
       </c>
       <c r="B273" s="2" t="inlineStr">
         <is>
-          <t>BGDP</t>
+          <t>BDCSoCaESoPbIC</t>
         </is>
       </c>
       <c r="C273" s="2" t="inlineStr">
         <is>
-          <t>BAU Gross Domestic Product</t>
-        </is>
-      </c>
+          <t>BAU Domestic Content Share of Consumption and Export Share of Production by ISIC Code</t>
+        </is>
+      </c>
+      <c r="D273" s="7" t="inlineStr">
+        <is>
+          <t>BAU Domestic Content Share of Consumption, BAU Export Share of Production</t>
+        </is>
+      </c>
+      <c r="E273" s="7" t="n"/>
       <c r="F273" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G273" s="26" t="n"/>
     </row>
     <row r="274" ht="30" customHeight="1">
       <c r="A274" s="2" t="inlineStr">
@@ -7671,19 +8373,26 @@
       </c>
       <c r="B274" s="2" t="inlineStr">
         <is>
-          <t>BObIC</t>
+          <t>BEaCP</t>
         </is>
       </c>
       <c r="C274" s="2" t="inlineStr">
         <is>
-          <t>BAU Output by ISIC Code</t>
-        </is>
-      </c>
+          <t>BAU Employment and Compensation Projections</t>
+        </is>
+      </c>
+      <c r="D274" s="7" t="inlineStr">
+        <is>
+          <t>Employees, Employee Compensation</t>
+        </is>
+      </c>
+      <c r="E274" s="7" t="n"/>
       <c r="F274" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G274" s="26" t="n"/>
     </row>
     <row r="275" ht="30" customHeight="1">
       <c r="A275" s="2" t="inlineStr">
@@ -7693,29 +8402,22 @@
       </c>
       <c r="B275" s="2" t="inlineStr">
         <is>
-          <t>BPCiOaDCSbIC</t>
+          <t>BEbIC</t>
         </is>
       </c>
       <c r="C275" s="2" t="inlineStr">
         <is>
-          <t>BAU Percent Change in Output and Domestic Content Share by ISIC Code</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
-        <is>
-          <t>BAU Percent Change in Output by ISIC Code, BAU Percent Change in Domestic Content Share by ISIC Code</t>
-        </is>
-      </c>
-      <c r="E275" s="2" t="inlineStr">
-        <is>
-          <t>BVAbIC</t>
-        </is>
-      </c>
+          <t>BAU Employment by ISIC Code</t>
+        </is>
+      </c>
+      <c r="D275" s="1" t="n"/>
+      <c r="E275" s="1" t="n"/>
       <c r="F275" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G275" s="26" t="n"/>
     </row>
     <row r="276" ht="30" customHeight="1">
       <c r="A276" s="2" t="inlineStr">
@@ -7725,19 +8427,22 @@
       </c>
       <c r="B276" s="2" t="inlineStr">
         <is>
-          <t>BVAbIC</t>
+          <t>BECbIC</t>
         </is>
       </c>
       <c r="C276" s="2" t="inlineStr">
         <is>
-          <t>BAU Value Added by ISIC Code</t>
-        </is>
-      </c>
+          <t>BAU Employee Compensation by ISIC Code</t>
+        </is>
+      </c>
+      <c r="D276" s="7" t="n"/>
+      <c r="E276" s="7" t="n"/>
       <c r="F276" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G276" s="26" t="n"/>
     </row>
     <row r="277" ht="15.75" customHeight="1" thickBot="1">
       <c r="A277" s="2" t="inlineStr">
@@ -7747,19 +8452,22 @@
       </c>
       <c r="B277" s="2" t="inlineStr">
         <is>
-          <t>DLIM</t>
+          <t>BGDP</t>
         </is>
       </c>
       <c r="C277" s="2" t="inlineStr">
         <is>
-          <t>Domestic Leontief Inverse Matrix</t>
-        </is>
-      </c>
+          <t>BAU Gross Domestic Product</t>
+        </is>
+      </c>
+      <c r="D277" s="7" t="n"/>
+      <c r="E277" s="7" t="n"/>
       <c r="F277" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G277" s="26" t="n"/>
     </row>
     <row r="278">
       <c r="A278" s="2" t="inlineStr">
@@ -7769,24 +8477,22 @@
       </c>
       <c r="B278" s="2" t="inlineStr">
         <is>
-          <t>DoEbIC</t>
+          <t>BObIC</t>
         </is>
       </c>
       <c r="C278" s="2" t="inlineStr">
         <is>
-          <t>Demographics of Employees by ISIC Code</t>
-        </is>
-      </c>
+          <t>BAU Output by ISIC Code</t>
+        </is>
+      </c>
+      <c r="D278" s="7" t="n"/>
+      <c r="E278" s="7" t="n"/>
       <c r="F278" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G278" s="2" t="inlineStr">
-        <is>
-          <t>You wish to include job break-outs by sex, race, ethnicity, or age bracket among your model outputs.</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G278" s="24" t="n"/>
     </row>
     <row r="279">
       <c r="A279" s="2" t="inlineStr">
@@ -7796,20 +8502,30 @@
       </c>
       <c r="B279" s="2" t="inlineStr">
         <is>
-          <t>FoGPbEaIC</t>
+          <t>BPCiOaDCSbIC</t>
         </is>
       </c>
       <c r="C279" s="2" t="inlineStr">
         <is>
-          <t>Fraction of Goods Purchased by Entity and ISIC Code</t>
-        </is>
-      </c>
-      <c r="D279" s="2" t="inlineStr">
-        <is>
-          <t>Fraction of Goods Purchased by Entity, Fraction of Goods Purchased by ISIC Code</t>
-        </is>
-      </c>
-      <c r="F279" s="3" t="n"/>
+          <t>BAU Percent Change in Output and Domestic Content Share by ISIC Code</t>
+        </is>
+      </c>
+      <c r="D279" s="1" t="inlineStr">
+        <is>
+          <t>BAU Percent Change in Output by ISIC Code, BAU Percent Change in Domestic Content Share by ISIC Code</t>
+        </is>
+      </c>
+      <c r="E279" s="7" t="inlineStr">
+        <is>
+          <t>BVAbIC</t>
+        </is>
+      </c>
+      <c r="F279" s="3" t="inlineStr">
+        <is>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G279" s="26" t="n"/>
     </row>
     <row r="280" ht="30" customHeight="1">
       <c r="A280" s="2" t="inlineStr">
@@ -7819,24 +8535,22 @@
       </c>
       <c r="B280" s="2" t="inlineStr">
         <is>
-          <t>FtPICM</t>
+          <t>BVAbIC</t>
         </is>
       </c>
       <c r="C280" s="2" t="inlineStr">
         <is>
-          <t>Fuel to Producing ISIC Code Map</t>
-        </is>
-      </c>
+          <t>BAU Value Added by ISIC Code</t>
+        </is>
+      </c>
+      <c r="D280" s="7" t="n"/>
+      <c r="E280" s="7" t="n"/>
       <c r="F280" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G280" s="2" t="inlineStr">
-        <is>
-          <t>This variable should not be altered.</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G280" s="24" t="n"/>
     </row>
     <row r="281" ht="30" customHeight="1">
       <c r="A281" s="2" t="inlineStr">
@@ -7846,24 +8560,22 @@
       </c>
       <c r="B281" s="2" t="inlineStr">
         <is>
-          <t>GaHEbIC</t>
+          <t>DLIM</t>
         </is>
       </c>
       <c r="C281" s="2" t="inlineStr">
         <is>
-          <t>Government and Household Expenditures by ISIC Code</t>
-        </is>
-      </c>
-      <c r="E281" s="2" t="inlineStr">
-        <is>
-          <t>DLIM</t>
-        </is>
-      </c>
+          <t>Domestic Leontief Inverse Matrix</t>
+        </is>
+      </c>
+      <c r="D281" s="7" t="n"/>
+      <c r="E281" s="1" t="n"/>
       <c r="F281" s="3" t="inlineStr">
         <is>
           <t>high</t>
         </is>
       </c>
+      <c r="G281" s="26" t="n"/>
     </row>
     <row r="282" ht="30" customHeight="1">
       <c r="A282" s="2" t="inlineStr">
@@ -7873,17 +8585,24 @@
       </c>
       <c r="B282" s="2" t="inlineStr">
         <is>
-          <t>HSR</t>
+          <t>DoEbIC</t>
         </is>
       </c>
       <c r="C282" s="2" t="inlineStr">
         <is>
-          <t>Household Savings Rate</t>
-        </is>
-      </c>
+          <t>Demographics of Employees by ISIC Code</t>
+        </is>
+      </c>
+      <c r="D282" s="7" t="n"/>
+      <c r="E282" s="7" t="n"/>
       <c r="F282" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G282" s="26" t="inlineStr">
+        <is>
+          <t>You wish to include job break-outs by sex, race, ethnicity, or age bracket among your model outputs.</t>
         </is>
       </c>
     </row>
@@ -7895,19 +8614,22 @@
       </c>
       <c r="B283" s="2" t="inlineStr">
         <is>
-          <t>IRoND</t>
+          <t>FoGPbEaIC</t>
         </is>
       </c>
       <c r="C283" s="2" t="inlineStr">
         <is>
-          <t>Interest Rate on National Debt</t>
-        </is>
-      </c>
-      <c r="F283" s="5" t="inlineStr">
-        <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>Fraction of Goods Purchased by Entity and ISIC Code</t>
+        </is>
+      </c>
+      <c r="D283" s="7" t="inlineStr">
+        <is>
+          <t>Fraction of Goods Purchased by Entity, Fraction of Goods Purchased by ISIC Code</t>
+        </is>
+      </c>
+      <c r="E283" s="7" t="n"/>
+      <c r="F283" s="5" t="n"/>
+      <c r="G283" s="26" t="n"/>
     </row>
     <row r="284" ht="30" customHeight="1">
       <c r="A284" s="2" t="inlineStr">
@@ -7917,17 +8639,24 @@
       </c>
       <c r="B284" s="2" t="inlineStr">
         <is>
-          <t>LPGRbIC</t>
+          <t>FtPICM</t>
         </is>
       </c>
       <c r="C284" s="2" t="inlineStr">
         <is>
-          <t>Labor Productivity Growth Rate by ISIC Code</t>
-        </is>
-      </c>
+          <t>Fuel to Producing ISIC Code Map</t>
+        </is>
+      </c>
+      <c r="D284" s="7" t="n"/>
+      <c r="E284" s="7" t="n"/>
       <c r="F284" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G284" s="26" t="inlineStr">
+        <is>
+          <t>This variable should not be altered.</t>
         </is>
       </c>
     </row>
@@ -7939,19 +8668,26 @@
       </c>
       <c r="B285" s="2" t="inlineStr">
         <is>
-          <t>PoNDHbE</t>
+          <t>GaHEbIC</t>
         </is>
       </c>
       <c r="C285" s="2" t="inlineStr">
         <is>
-          <t>Percent of National Debt Held by Entity</t>
+          <t>Government and Household Expenditures by ISIC Code</t>
+        </is>
+      </c>
+      <c r="D285" s="7" t="n"/>
+      <c r="E285" s="7" t="inlineStr">
+        <is>
+          <t>DLIM</t>
         </is>
       </c>
       <c r="F285" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G285" s="26" t="n"/>
     </row>
     <row r="286">
       <c r="A286" s="2" t="inlineStr">
@@ -7961,19 +8697,22 @@
       </c>
       <c r="B286" s="2" t="inlineStr">
         <is>
-          <t>TLIM</t>
+          <t>HSR</t>
         </is>
       </c>
       <c r="C286" s="2" t="inlineStr">
         <is>
-          <t>Total Leontief Inverse Matrix</t>
-        </is>
-      </c>
+          <t>Household Savings Rate</t>
+        </is>
+      </c>
+      <c r="D286" s="7" t="n"/>
+      <c r="E286" s="7" t="n"/>
       <c r="F286" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G286" s="26" t="n"/>
     </row>
     <row r="287">
       <c r="A287" s="2" t="inlineStr">
@@ -7983,24 +8722,22 @@
       </c>
       <c r="B287" s="2" t="inlineStr">
         <is>
-          <t>URPbIC</t>
+          <t>IRoND</t>
         </is>
       </c>
       <c r="C287" s="2" t="inlineStr">
         <is>
-          <t>Union Representation Percentage by ISIC Code</t>
-        </is>
-      </c>
+          <t>Interest Rate on National Debt</t>
+        </is>
+      </c>
+      <c r="D287" s="7" t="n"/>
+      <c r="E287" s="7" t="n"/>
       <c r="F287" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G287" s="2" t="inlineStr">
-        <is>
-          <t>You wish to include job break-outs by union status among your model outputs.</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G287" s="24" t="n"/>
     </row>
     <row r="288">
       <c r="A288" s="2" t="inlineStr">
@@ -8010,19 +8747,22 @@
       </c>
       <c r="B288" s="2" t="inlineStr">
         <is>
-          <t>VoSTR</t>
+          <t>LPGRbIC</t>
         </is>
       </c>
       <c r="C288" s="2" t="inlineStr">
         <is>
-          <t>VAT or Sales Tax Rate</t>
-        </is>
-      </c>
+          <t>Labor Productivity Growth Rate by ISIC Code</t>
+        </is>
+      </c>
+      <c r="D288" s="7" t="n"/>
+      <c r="E288" s="7" t="n"/>
       <c r="F288" s="19" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G288" s="26" t="n"/>
     </row>
     <row r="289">
       <c r="A289" s="17" t="inlineStr">
@@ -8032,120 +8772,126 @@
       </c>
       <c r="B289" s="17" t="inlineStr">
         <is>
-          <t>WMITR</t>
+          <t>PoNDHbE</t>
         </is>
       </c>
       <c r="C289" s="17" t="inlineStr">
         <is>
-          <t>Worker Marginal Income Tax Rate</t>
-        </is>
-      </c>
-      <c r="D289" s="17" t="n"/>
-      <c r="E289" s="17" t="n"/>
+          <t>Percent of National Debt Held by Entity</t>
+        </is>
+      </c>
+      <c r="D289" s="27" t="n"/>
+      <c r="E289" s="27" t="n"/>
       <c r="F289" s="19" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G289" s="17" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G289" s="28" t="n"/>
     </row>
     <row r="290" ht="30" customHeight="1">
       <c r="A290" s="2" t="inlineStr">
         <is>
-          <t>land</t>
+          <t>io-model</t>
         </is>
       </c>
       <c r="B290" s="2" t="inlineStr">
         <is>
-          <t>AOCoLUPpUA</t>
+          <t>TLIM</t>
         </is>
       </c>
       <c r="C290" s="2" t="inlineStr">
         <is>
-          <t>Annual Ongoing Cost of Land Use Policies per Unit Area</t>
-        </is>
-      </c>
+          <t>Total Leontief Inverse Matrix</t>
+        </is>
+      </c>
+      <c r="D290" s="7" t="n"/>
+      <c r="E290" s="7" t="n"/>
       <c r="F290" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G290" s="26" t="n"/>
     </row>
     <row r="291">
       <c r="A291" s="2" t="inlineStr">
         <is>
-          <t>land</t>
+          <t>io-model</t>
         </is>
       </c>
       <c r="B291" s="2" t="inlineStr">
         <is>
-          <t>BLAPE</t>
+          <t>URPbIC</t>
         </is>
       </c>
       <c r="C291" s="2" t="inlineStr">
         <is>
-          <t>BAU LULUCF Anthropogenic Pollutant Emissions</t>
-        </is>
-      </c>
-      <c r="E291" s="2" t="inlineStr">
-        <is>
-          <t>RPEpUACE</t>
-        </is>
-      </c>
+          <t>Union Representation Percentage by ISIC Code</t>
+        </is>
+      </c>
+      <c r="D291" s="7" t="n"/>
+      <c r="E291" s="1" t="n"/>
       <c r="F291" s="12" t="inlineStr">
         <is>
-          <t>very high</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G291" s="26" t="inlineStr">
+        <is>
+          <t>You wish to include job break-outs by union status among your model outputs.</t>
         </is>
       </c>
     </row>
     <row r="292">
       <c r="A292" s="2" t="inlineStr">
         <is>
-          <t>land</t>
+          <t>io-model</t>
         </is>
       </c>
       <c r="B292" s="2" t="inlineStr">
         <is>
-          <t>CApULAbIFM</t>
+          <t>VoSTR</t>
         </is>
       </c>
       <c r="C292" s="2" t="inlineStr">
         <is>
-          <t>CO2 Abated per Unit Land Area by Improved Forest Management</t>
-        </is>
-      </c>
+          <t>VAT or Sales Tax Rate</t>
+        </is>
+      </c>
+      <c r="D292" s="7" t="n"/>
+      <c r="E292" s="7" t="n"/>
       <c r="F292" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G292" s="26" t="n"/>
     </row>
     <row r="293" ht="30" customHeight="1">
       <c r="A293" s="2" t="inlineStr">
         <is>
-          <t>land</t>
+          <t>io-model</t>
         </is>
       </c>
       <c r="B293" s="2" t="inlineStr">
         <is>
-          <t>CiLVpUAAbP</t>
+          <t>WMITR</t>
         </is>
       </c>
       <c r="C293" s="2" t="inlineStr">
         <is>
-          <t>Change in Land Value per Unit Area Affected by Policy</t>
-        </is>
-      </c>
+          <t>Worker Marginal Income Tax Rate</t>
+        </is>
+      </c>
+      <c r="D293" s="7" t="n"/>
+      <c r="E293" s="7" t="n"/>
       <c r="F293" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G293" s="2" t="inlineStr">
-        <is>
-          <t>You want to estimate the change in land's financial value caused by LULUCF policies</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G293" s="24" t="n"/>
     </row>
     <row r="294">
       <c r="A294" s="2" t="inlineStr">
@@ -8155,19 +8901,22 @@
       </c>
       <c r="B294" s="2" t="inlineStr">
         <is>
-          <t>CSpULApYbP</t>
+          <t>AOCoLUPpUA</t>
         </is>
       </c>
       <c r="C294" s="2" t="inlineStr">
         <is>
-          <t>CO2 Sequestered per Unit Land Area per Year by Policy</t>
-        </is>
-      </c>
+          <t>Annual Ongoing Cost of Land Use Policies per Unit Area</t>
+        </is>
+      </c>
+      <c r="D294" s="7" t="n"/>
+      <c r="E294" s="7" t="n"/>
       <c r="F294" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G294" s="26" t="n"/>
     </row>
     <row r="295">
       <c r="A295" s="2" t="inlineStr">
@@ -8177,19 +8926,26 @@
       </c>
       <c r="B295" s="2" t="inlineStr">
         <is>
-          <t>FoFObE</t>
+          <t>BLAPE</t>
         </is>
       </c>
       <c r="C295" s="2" t="inlineStr">
         <is>
-          <t>Fraction of Forests Owned by Entity</t>
+          <t>BAU LULUCF Anthropogenic Pollutant Emissions</t>
+        </is>
+      </c>
+      <c r="D295" s="7" t="n"/>
+      <c r="E295" s="7" t="inlineStr">
+        <is>
+          <t>RPEpUACE</t>
         </is>
       </c>
       <c r="F295" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>very high</t>
+        </is>
+      </c>
+      <c r="G295" s="26" t="n"/>
     </row>
     <row r="296">
       <c r="A296" s="2" t="inlineStr">
@@ -8199,19 +8955,22 @@
       </c>
       <c r="B296" s="2" t="inlineStr">
         <is>
-          <t>ICoLUPpUA</t>
+          <t>CApULAbIFM</t>
         </is>
       </c>
       <c r="C296" s="2" t="inlineStr">
         <is>
-          <t>Implementation Cost of Land Use Policies per Unit Area</t>
-        </is>
-      </c>
+          <t>CO2 Abated per Unit Land Area by Improved Forest Management</t>
+        </is>
+      </c>
+      <c r="D296" s="7" t="n"/>
+      <c r="E296" s="7" t="n"/>
       <c r="F296" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G296" s="26" t="n"/>
     </row>
     <row r="297">
       <c r="A297" s="2" t="inlineStr">
@@ -8221,17 +8980,24 @@
       </c>
       <c r="B297" s="2" t="inlineStr">
         <is>
-          <t>PLANAbPiaSY</t>
+          <t>CiLVpUAAbP</t>
         </is>
       </c>
       <c r="C297" s="2" t="inlineStr">
         <is>
-          <t>Potential Land Area Newly Affected by Policy in a Single Year</t>
-        </is>
-      </c>
+          <t>Change in Land Value per Unit Area Affected by Policy</t>
+        </is>
+      </c>
+      <c r="D297" s="7" t="n"/>
+      <c r="E297" s="7" t="n"/>
       <c r="F297" s="12" t="inlineStr">
         <is>
-          <t>very high</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G297" s="26" t="inlineStr">
+        <is>
+          <t>You want to estimate the change in land's financial value caused by LULUCF policies</t>
         </is>
       </c>
     </row>
@@ -8243,130 +9009,122 @@
       </c>
       <c r="B298" s="17" t="inlineStr">
         <is>
-          <t>RPEpUACE</t>
+          <t>CSpULApYbP</t>
         </is>
       </c>
       <c r="C298" s="17" t="inlineStr">
         <is>
-          <t>Rebound Pollutant Emissions per Unit Avoided CO2 Emissions</t>
-        </is>
-      </c>
-      <c r="D298" s="17" t="n"/>
-      <c r="E298" s="17" t="n"/>
+          <t>CO2 Sequestered per Unit Land Area per Year by Policy</t>
+        </is>
+      </c>
+      <c r="D298" s="27" t="n"/>
+      <c r="E298" s="27" t="n"/>
       <c r="F298" s="20" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
-      <c r="G298" s="17" t="n"/>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G298" s="28" t="n"/>
     </row>
     <row r="299" ht="30" customHeight="1">
       <c r="A299" s="2" t="inlineStr">
         <is>
-          <t>plcy-schd</t>
+          <t>land</t>
         </is>
       </c>
       <c r="B299" s="2" t="inlineStr">
         <is>
-          <t>FoPITY</t>
+          <t>FoFObE</t>
         </is>
       </c>
       <c r="C299" s="2" t="inlineStr">
         <is>
-          <t>Fraction of Policy Implemented This Year</t>
-        </is>
-      </c>
+          <t>Fraction of Forests Owned by Entity</t>
+        </is>
+      </c>
+      <c r="D299" s="7" t="n"/>
+      <c r="E299" s="7" t="n"/>
       <c r="F299" s="6" t="inlineStr">
         <is>
-          <t>n/a (policy lever)</t>
-        </is>
-      </c>
-      <c r="G299" s="2" t="inlineStr">
-        <is>
-          <t>You are building a policy scenario that implements policies using a non-default schedule</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G299" s="24" t="n"/>
     </row>
     <row r="300">
       <c r="A300" s="2" t="inlineStr">
         <is>
-          <t>plcy-schd</t>
+          <t>land</t>
         </is>
       </c>
       <c r="B300" s="2" t="inlineStr">
         <is>
-          <t>FT</t>
+          <t>ICoLUPpUA</t>
         </is>
       </c>
       <c r="C300" s="2" t="inlineStr">
         <is>
-          <t>Final Time</t>
-        </is>
-      </c>
+          <t>Implementation Cost of Land Use Policies per Unit Area</t>
+        </is>
+      </c>
+      <c r="D300" s="7" t="n"/>
+      <c r="E300" s="7" t="n"/>
       <c r="F300" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G300" s="2" t="inlineStr">
-        <is>
-          <t>You want to alter the end year.  The EPS supports end year dates out to 2100.</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G300" s="24" t="n"/>
     </row>
     <row r="301">
       <c r="A301" s="2" t="inlineStr">
         <is>
-          <t>plcy-schd</t>
+          <t>land</t>
         </is>
       </c>
       <c r="B301" s="2" t="inlineStr">
         <is>
-          <t>FY</t>
+          <t>PLANAbPiaSY</t>
         </is>
       </c>
       <c r="C301" s="2" t="inlineStr">
         <is>
-          <t>Future Year</t>
-        </is>
-      </c>
+          <t>Potential Land Area Newly Affected by Policy in a Single Year</t>
+        </is>
+      </c>
+      <c r="D301" s="7" t="n"/>
+      <c r="E301" s="7" t="n"/>
       <c r="F301" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G301" s="2" t="inlineStr">
-        <is>
-          <t>If you change Initial Time, you need to update this file</t>
-        </is>
-      </c>
+          <t>very high</t>
+        </is>
+      </c>
+      <c r="G301" s="24" t="n"/>
     </row>
     <row r="302">
       <c r="A302" s="2" t="inlineStr">
         <is>
-          <t>plcy-schd</t>
+          <t>land</t>
         </is>
       </c>
       <c r="B302" s="2" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>RPEpUACE</t>
         </is>
       </c>
       <c r="C302" s="2" t="inlineStr">
         <is>
-          <t>Initial Time</t>
-        </is>
-      </c>
+          <t>Rebound Pollutant Emissions per Unit Avoided CO2 Emissions</t>
+        </is>
+      </c>
+      <c r="D302" s="7" t="n"/>
+      <c r="E302" s="7" t="n"/>
       <c r="F302" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G302" s="2" t="inlineStr">
-        <is>
-          <t>You have updated policy schedules (FoPITY) and start year input variables accordingly</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G302" s="24" t="n"/>
     </row>
     <row r="303">
       <c r="A303" s="17" t="inlineStr">
@@ -8376,110 +9134,138 @@
       </c>
       <c r="B303" s="17" t="inlineStr">
         <is>
-          <t>V</t>
+          <t>FoPITY</t>
         </is>
       </c>
       <c r="C303" s="17" t="inlineStr">
         <is>
-          <t>Vintage</t>
-        </is>
-      </c>
-      <c r="D303" s="17" t="n"/>
-      <c r="E303" s="17" t="n"/>
+          <t>Fraction of Policy Implemented This Year</t>
+        </is>
+      </c>
+      <c r="D303" s="27" t="n"/>
+      <c r="E303" s="27" t="n"/>
       <c r="F303" s="22" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G303" s="17" t="n"/>
+          <t>n/a (policy lever)</t>
+        </is>
+      </c>
+      <c r="G303" s="28" t="inlineStr">
+        <is>
+          <t>You are building a policy scenario that implements policies using a non-default schedule</t>
+        </is>
+      </c>
     </row>
     <row r="304">
       <c r="A304" s="2" t="inlineStr">
         <is>
-          <t>trans</t>
+          <t>plcy-schd</t>
         </is>
       </c>
       <c r="B304" s="2" t="inlineStr">
         <is>
-          <t>AIiBCbVT</t>
+          <t>FT</t>
         </is>
       </c>
       <c r="C304" s="2" t="inlineStr">
         <is>
-          <t>Ann Impvmt in Bat Cap by Veh Type</t>
-        </is>
-      </c>
+          <t>Final Time</t>
+        </is>
+      </c>
+      <c r="D304" s="7" t="n"/>
+      <c r="E304" s="7" t="n"/>
       <c r="F304" s="4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G304" s="26" t="inlineStr">
+        <is>
+          <t>You want to alter the end year.  The EPS supports end year dates out to 2100.</t>
         </is>
       </c>
     </row>
     <row r="305">
       <c r="A305" s="2" t="inlineStr">
         <is>
-          <t>trans</t>
+          <t>plcy-schd</t>
         </is>
       </c>
       <c r="B305" s="2" t="inlineStr">
         <is>
-          <t>ANVCV</t>
+          <t>FY</t>
         </is>
       </c>
       <c r="C305" s="2" t="inlineStr">
         <is>
-          <t>Additional New Vehicles Calibration Variable</t>
-        </is>
-      </c>
+          <t>Future Year</t>
+        </is>
+      </c>
+      <c r="D305" s="7" t="n"/>
+      <c r="E305" s="7" t="n"/>
       <c r="F305" s="14" t="inlineStr">
         <is>
-          <t>to be determined via calibration</t>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G305" s="26" t="inlineStr">
+        <is>
+          <t>If you change Initial Time, you need to update this file</t>
         </is>
       </c>
     </row>
     <row r="306" ht="60" customHeight="1">
       <c r="A306" s="2" t="inlineStr">
         <is>
-          <t>trans</t>
+          <t>plcy-schd</t>
         </is>
       </c>
       <c r="B306" s="2" t="inlineStr">
         <is>
-          <t>AVCC</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C306" s="2" t="inlineStr">
         <is>
-          <t>Avg Vehicle Charger Capacity</t>
-        </is>
-      </c>
+          <t>Initial Time</t>
+        </is>
+      </c>
+      <c r="D306" s="7" t="n"/>
+      <c r="E306" s="7" t="n"/>
       <c r="F306" s="4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G306" s="26" t="inlineStr">
+        <is>
+          <t>You have updated policy schedules (FoPITY) and start year input variables accordingly</t>
         </is>
       </c>
     </row>
     <row r="307">
       <c r="A307" s="2" t="inlineStr">
         <is>
-          <t>trans</t>
+          <t>plcy-schd</t>
         </is>
       </c>
       <c r="B307" s="2" t="inlineStr">
         <is>
-          <t>AVIC</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C307" s="2" t="inlineStr">
         <is>
-          <t>Annual Vehicle Insurance Cost</t>
-        </is>
-      </c>
+          <t>Vintage</t>
+        </is>
+      </c>
+      <c r="D307" s="7" t="n"/>
+      <c r="E307" s="7" t="n"/>
       <c r="F307" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G307" s="26" t="n"/>
     </row>
     <row r="308">
       <c r="A308" s="2" t="inlineStr">
@@ -8489,19 +9275,22 @@
       </c>
       <c r="B308" s="2" t="inlineStr">
         <is>
-          <t>AVL</t>
+          <t>AIiBCbVT</t>
         </is>
       </c>
       <c r="C308" s="2" t="inlineStr">
         <is>
-          <t>Avg Vehicle Lifetime</t>
-        </is>
-      </c>
+          <t>Ann Impvmt in Bat Cap by Veh Type</t>
+        </is>
+      </c>
+      <c r="D308" s="7" t="n"/>
+      <c r="E308" s="7" t="n"/>
       <c r="F308" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G308" s="26" t="n"/>
     </row>
     <row r="309">
       <c r="A309" s="2" t="inlineStr">
@@ -8511,19 +9300,22 @@
       </c>
       <c r="B309" s="2" t="inlineStr">
         <is>
-          <t>AVLo</t>
+          <t>ANVCV</t>
         </is>
       </c>
       <c r="C309" s="2" t="inlineStr">
         <is>
-          <t>Average Vehicle Loading</t>
-        </is>
-      </c>
+          <t>Additional New Vehicles Calibration Variable</t>
+        </is>
+      </c>
+      <c r="D309" s="7" t="n"/>
+      <c r="E309" s="7" t="n"/>
       <c r="F309" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>to be determined via calibration</t>
+        </is>
+      </c>
+      <c r="G309" s="26" t="n"/>
     </row>
     <row r="310">
       <c r="A310" s="2" t="inlineStr">
@@ -8533,19 +9325,22 @@
       </c>
       <c r="B310" s="2" t="inlineStr">
         <is>
-          <t>AVLRaPTC</t>
+          <t>AVCC</t>
         </is>
       </c>
       <c r="C310" s="2" t="inlineStr">
         <is>
-          <t>Annual Vehicle Licensing Registration and Property Tax Costs</t>
-        </is>
-      </c>
+          <t>Avg Vehicle Charger Capacity</t>
+        </is>
+      </c>
+      <c r="D310" s="7" t="n"/>
+      <c r="E310" s="7" t="n"/>
       <c r="F310" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G310" s="26" t="n"/>
     </row>
     <row r="311" ht="30" customHeight="1">
       <c r="A311" s="2" t="inlineStr">
@@ -8555,19 +9350,22 @@
       </c>
       <c r="B311" s="2" t="inlineStr">
         <is>
-          <t>AVMC</t>
+          <t>AVIC</t>
         </is>
       </c>
       <c r="C311" s="2" t="inlineStr">
         <is>
-          <t>Annual Vehicle Maintenance Cost</t>
-        </is>
-      </c>
+          <t>Annual Vehicle Insurance Cost</t>
+        </is>
+      </c>
+      <c r="D311" s="7" t="n"/>
+      <c r="E311" s="7" t="n"/>
       <c r="F311" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G311" s="26" t="n"/>
     </row>
     <row r="312">
       <c r="A312" s="2" t="inlineStr">
@@ -8577,19 +9375,22 @@
       </c>
       <c r="B312" s="2" t="inlineStr">
         <is>
-          <t>AVOP</t>
+          <t>AVL</t>
         </is>
       </c>
       <c r="C312" s="2" t="inlineStr">
         <is>
-          <t>Average Vehicle Ownership Period</t>
-        </is>
-      </c>
+          <t>Avg Vehicle Lifetime</t>
+        </is>
+      </c>
+      <c r="D312" s="7" t="n"/>
+      <c r="E312" s="7" t="n"/>
       <c r="F312" s="4" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
+      <c r="G312" s="26" t="n"/>
     </row>
     <row r="313">
       <c r="A313" s="2" t="inlineStr">
@@ -8599,19 +9400,22 @@
       </c>
       <c r="B313" s="2" t="inlineStr">
         <is>
-          <t>AVPC</t>
+          <t>AVLo</t>
         </is>
       </c>
       <c r="C313" s="2" t="inlineStr">
         <is>
-          <t>Annual Vehicle Parking Cost</t>
-        </is>
-      </c>
+          <t>Average Vehicle Loading</t>
+        </is>
+      </c>
+      <c r="D313" s="7" t="n"/>
+      <c r="E313" s="7" t="n"/>
       <c r="F313" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G313" s="26" t="n"/>
     </row>
     <row r="314" ht="30" customHeight="1">
       <c r="A314" s="2" t="inlineStr">
@@ -8621,19 +9425,22 @@
       </c>
       <c r="B314" s="2" t="inlineStr">
         <is>
-          <t>BAADTbVT</t>
+          <t>AVLRaPTC</t>
         </is>
       </c>
       <c r="C314" s="2" t="inlineStr">
         <is>
-          <t>BAU Average Annual Dist Traveled by Vehicle Type</t>
-        </is>
-      </c>
+          <t>Annual Vehicle Licensing Registration and Property Tax Costs</t>
+        </is>
+      </c>
+      <c r="D314" s="7" t="n"/>
+      <c r="E314" s="7" t="n"/>
       <c r="F314" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G314" s="26" t="n"/>
     </row>
     <row r="315" ht="60" customHeight="1">
       <c r="A315" s="2" t="inlineStr">
@@ -8643,19 +9450,22 @@
       </c>
       <c r="B315" s="2" t="inlineStr">
         <is>
-          <t>BCDTRtSY</t>
+          <t>AVMC</t>
         </is>
       </c>
       <c r="C315" s="2" t="inlineStr">
         <is>
-          <t>BAU Cargo Distance Transported Relative to Start Year</t>
-        </is>
-      </c>
+          <t>Annual Vehicle Maintenance Cost</t>
+        </is>
+      </c>
+      <c r="D315" s="7" t="n"/>
+      <c r="E315" s="7" t="n"/>
       <c r="F315" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G315" s="26" t="n"/>
     </row>
     <row r="316">
       <c r="A316" s="2" t="inlineStr">
@@ -8665,24 +9475,22 @@
       </c>
       <c r="B316" s="2" t="inlineStr">
         <is>
-          <t>BHNVFEAL</t>
+          <t>AVOP</t>
         </is>
       </c>
       <c r="C316" s="2" t="inlineStr">
         <is>
-          <t>BAU Historical New Vehicle Fuel Economy After Lifetime</t>
-        </is>
-      </c>
-      <c r="E316" s="2" t="inlineStr">
-        <is>
-          <t>BNVFE, AVLo, PTFURfE, AVL</t>
-        </is>
-      </c>
+          <t>Average Vehicle Ownership Period</t>
+        </is>
+      </c>
+      <c r="D316" s="7" t="n"/>
+      <c r="E316" s="1" t="n"/>
       <c r="F316" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G316" s="26" t="n"/>
     </row>
     <row r="317">
       <c r="A317" s="2" t="inlineStr">
@@ -8692,19 +9500,22 @@
       </c>
       <c r="B317" s="2" t="inlineStr">
         <is>
-          <t>BLP</t>
+          <t>AVPC</t>
         </is>
       </c>
       <c r="C317" s="2" t="inlineStr">
         <is>
-          <t>BAU LCFS Percentage</t>
-        </is>
-      </c>
+          <t>Annual Vehicle Parking Cost</t>
+        </is>
+      </c>
+      <c r="D317" s="7" t="n"/>
+      <c r="E317" s="7" t="n"/>
       <c r="F317" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G317" s="26" t="n"/>
     </row>
     <row r="318" ht="60" customHeight="1">
       <c r="A318" s="2" t="inlineStr">
@@ -8714,19 +9525,22 @@
       </c>
       <c r="B318" s="2" t="inlineStr">
         <is>
-          <t>BNoEVC</t>
+          <t>BAADTbVT</t>
         </is>
       </c>
       <c r="C318" s="2" t="inlineStr">
         <is>
-          <t>BAU Number of EV Chargers</t>
-        </is>
-      </c>
+          <t>BAU Average Annual Dist Traveled by Vehicle Type</t>
+        </is>
+      </c>
+      <c r="D318" s="7" t="n"/>
+      <c r="E318" s="7" t="n"/>
       <c r="F318" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G318" s="26" t="n"/>
     </row>
     <row r="319" ht="60" customHeight="1">
       <c r="A319" s="2" t="inlineStr">
@@ -8736,19 +9550,22 @@
       </c>
       <c r="B319" s="2" t="inlineStr">
         <is>
-          <t>BNoGP</t>
+          <t>BCDTRtSY</t>
         </is>
       </c>
       <c r="C319" s="2" t="inlineStr">
         <is>
-          <t>BAU Number of Gas Pumps</t>
-        </is>
-      </c>
+          <t>BAU Cargo Distance Transported Relative to Start Year</t>
+        </is>
+      </c>
+      <c r="D319" s="7" t="n"/>
+      <c r="E319" s="7" t="n"/>
       <c r="F319" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G319" s="26" t="n"/>
     </row>
     <row r="320" ht="60" customHeight="1">
       <c r="A320" s="2" t="inlineStr">
@@ -8758,12 +9575,18 @@
       </c>
       <c r="B320" s="2" t="inlineStr">
         <is>
-          <t>BNVFE</t>
+          <t>BHNVFEAL</t>
         </is>
       </c>
       <c r="C320" s="2" t="inlineStr">
         <is>
-          <t>BAU New Vehicle Fuel Economy</t>
+          <t>BAU Historical New Vehicle Fuel Economy After Lifetime</t>
+        </is>
+      </c>
+      <c r="D320" s="7" t="n"/>
+      <c r="E320" s="7" t="inlineStr">
+        <is>
+          <t>BNVFE, AVLo, PTFURfE, AVL</t>
         </is>
       </c>
       <c r="F320" s="5" t="inlineStr">
@@ -8771,6 +9594,7 @@
           <t>medium</t>
         </is>
       </c>
+      <c r="G320" s="26" t="n"/>
     </row>
     <row r="321">
       <c r="A321" s="2" t="inlineStr">
@@ -8780,19 +9604,22 @@
       </c>
       <c r="B321" s="2" t="inlineStr">
         <is>
-          <t>BPM</t>
+          <t>BLP</t>
         </is>
       </c>
       <c r="C321" s="2" t="inlineStr">
         <is>
-          <t>Battery Pack Markup</t>
-        </is>
-      </c>
+          <t>BAU LCFS Percentage</t>
+        </is>
+      </c>
+      <c r="D321" s="7" t="n"/>
+      <c r="E321" s="7" t="n"/>
       <c r="F321" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G321" s="26" t="n"/>
     </row>
     <row r="322" ht="30" customHeight="1">
       <c r="A322" s="2" t="inlineStr">
@@ -8802,19 +9629,22 @@
       </c>
       <c r="B322" s="2" t="inlineStr">
         <is>
-          <t>BPoEFUbVT</t>
+          <t>BNoEVC</t>
         </is>
       </c>
       <c r="C322" s="2" t="inlineStr">
         <is>
-          <t>BAU Perc of Each Fuel Used by Veh Technology</t>
-        </is>
-      </c>
+          <t>BAU Number of EV Chargers</t>
+        </is>
+      </c>
+      <c r="D322" s="7" t="n"/>
+      <c r="E322" s="7" t="n"/>
       <c r="F322" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G322" s="26" t="n"/>
     </row>
     <row r="323" ht="30" customHeight="1">
       <c r="A323" s="2" t="inlineStr">
@@ -8824,24 +9654,22 @@
       </c>
       <c r="B323" s="2" t="inlineStr">
         <is>
-          <t>BPP</t>
+          <t>BNoGP</t>
         </is>
       </c>
       <c r="C323" s="2" t="inlineStr">
         <is>
-          <t>Battery Pack Price</t>
-        </is>
-      </c>
-      <c r="D323" s="2" t="inlineStr">
-        <is>
-          <t>Battery Pack Price, Start Year Battery Pack Price</t>
-        </is>
-      </c>
+          <t>BAU Number of Gas Pumps</t>
+        </is>
+      </c>
+      <c r="D323" s="1" t="n"/>
+      <c r="E323" s="7" t="n"/>
       <c r="F323" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G323" s="26" t="n"/>
     </row>
     <row r="324">
       <c r="A324" s="2" t="inlineStr">
@@ -8851,19 +9679,22 @@
       </c>
       <c r="B324" s="2" t="inlineStr">
         <is>
-          <t>BPPM</t>
+          <t>BNVFE</t>
         </is>
       </c>
       <c r="C324" s="2" t="inlineStr">
         <is>
-          <t>Battery Pack Price Multiplier</t>
-        </is>
-      </c>
+          <t>BAU New Vehicle Fuel Economy</t>
+        </is>
+      </c>
+      <c r="D324" s="7" t="n"/>
+      <c r="E324" s="7" t="n"/>
       <c r="F324" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G324" s="26" t="n"/>
     </row>
     <row r="325" ht="60" customHeight="1">
       <c r="A325" s="2" t="inlineStr">
@@ -8873,19 +9704,22 @@
       </c>
       <c r="B325" s="2" t="inlineStr">
         <is>
-          <t>BRASC</t>
+          <t>BPM</t>
         </is>
       </c>
       <c r="C325" s="2" t="inlineStr">
         <is>
-          <t>BAU Range Anxiety Shadow Cost</t>
-        </is>
-      </c>
+          <t>Battery Pack Markup</t>
+        </is>
+      </c>
+      <c r="D325" s="7" t="n"/>
+      <c r="E325" s="7" t="n"/>
       <c r="F325" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G325" s="26" t="n"/>
     </row>
     <row r="326">
       <c r="A326" s="2" t="inlineStr">
@@ -8895,19 +9729,22 @@
       </c>
       <c r="B326" s="2" t="inlineStr">
         <is>
-          <t>BRZSPbMR</t>
+          <t>BPoEFUbVT</t>
         </is>
       </c>
       <c r="C326" s="2" t="inlineStr">
         <is>
-          <t>BAU Required ZEV Sales Perc by Model Region</t>
-        </is>
-      </c>
+          <t>BAU Perc of Each Fuel Used by Veh Technology</t>
+        </is>
+      </c>
+      <c r="D326" s="7" t="n"/>
+      <c r="E326" s="7" t="n"/>
       <c r="F326" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G326" s="26" t="n"/>
     </row>
     <row r="327" ht="60" customHeight="1">
       <c r="A327" s="2" t="inlineStr">
@@ -8917,19 +9754,26 @@
       </c>
       <c r="B327" s="2" t="inlineStr">
         <is>
-          <t>BRZSPbS</t>
+          <t>BPP</t>
         </is>
       </c>
       <c r="C327" s="2" t="inlineStr">
         <is>
-          <t>BAU Required ZEV Sales Perc by Subregion</t>
-        </is>
-      </c>
+          <t>Battery Pack Price</t>
+        </is>
+      </c>
+      <c r="D327" s="7" t="inlineStr">
+        <is>
+          <t>Battery Pack Price, Start Year Battery Pack Price</t>
+        </is>
+      </c>
+      <c r="E327" s="7" t="n"/>
       <c r="F327" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G327" s="26" t="n"/>
     </row>
     <row r="328" ht="45" customHeight="1">
       <c r="A328" s="2" t="inlineStr">
@@ -8939,19 +9783,22 @@
       </c>
       <c r="B328" s="2" t="inlineStr">
         <is>
-          <t>BSfVBP</t>
+          <t>BPPM</t>
         </is>
       </c>
       <c r="C328" s="2" t="inlineStr">
         <is>
-          <t>BAU Subsidy for Vehicle Battery Production</t>
-        </is>
-      </c>
+          <t>Battery Pack Price Multiplier</t>
+        </is>
+      </c>
+      <c r="D328" s="7" t="n"/>
+      <c r="E328" s="7" t="n"/>
       <c r="F328" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G328" s="26" t="n"/>
     </row>
     <row r="329" ht="60" customHeight="1">
       <c r="A329" s="2" t="inlineStr">
@@ -8961,19 +9808,22 @@
       </c>
       <c r="B329" s="2" t="inlineStr">
         <is>
-          <t>BVS</t>
+          <t>BRASC</t>
         </is>
       </c>
       <c r="C329" s="2" t="inlineStr">
         <is>
-          <t>BAU Vehicle Subsidy</t>
-        </is>
-      </c>
+          <t>BAU Range Anxiety Shadow Cost</t>
+        </is>
+      </c>
+      <c r="D329" s="7" t="n"/>
+      <c r="E329" s="7" t="n"/>
       <c r="F329" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G329" s="26" t="n"/>
     </row>
     <row r="330">
       <c r="A330" s="2" t="inlineStr">
@@ -8983,19 +9833,22 @@
       </c>
       <c r="B330" s="2" t="inlineStr">
         <is>
-          <t>BVTQaZ</t>
+          <t>BRZSPbMR</t>
         </is>
       </c>
       <c r="C330" s="2" t="inlineStr">
         <is>
-          <t>BAU Vehicle Technologies Qualifying as ZEVs</t>
-        </is>
-      </c>
+          <t>BAU Required ZEV Sales Perc by Model Region</t>
+        </is>
+      </c>
+      <c r="D330" s="7" t="n"/>
+      <c r="E330" s="7" t="n"/>
       <c r="F330" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G330" s="26" t="n"/>
     </row>
     <row r="331" ht="30" customHeight="1">
       <c r="A331" s="2" t="inlineStr">
@@ -9005,19 +9858,22 @@
       </c>
       <c r="B331" s="2" t="inlineStr">
         <is>
-          <t>BVTStL</t>
+          <t>BRZSPbS</t>
         </is>
       </c>
       <c r="C331" s="2" t="inlineStr">
         <is>
-          <t>Boolean Vehicle Types Subject to LCFS</t>
-        </is>
-      </c>
+          <t>BAU Required ZEV Sales Perc by Subregion</t>
+        </is>
+      </c>
+      <c r="D331" s="7" t="n"/>
+      <c r="E331" s="7" t="n"/>
       <c r="F331" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G331" s="26" t="n"/>
     </row>
     <row r="332" ht="30" customHeight="1">
       <c r="A332" s="2" t="inlineStr">
@@ -9027,24 +9883,22 @@
       </c>
       <c r="B332" s="2" t="inlineStr">
         <is>
-          <t>CIRbTF</t>
+          <t>BSfVBP</t>
         </is>
       </c>
       <c r="C332" s="2" t="inlineStr">
         <is>
-          <t>Carbon Intensity Ratios by Transportation Fuel</t>
-        </is>
-      </c>
+          <t>BAU Subsidy for Vehicle Battery Production</t>
+        </is>
+      </c>
+      <c r="D332" s="7" t="n"/>
+      <c r="E332" s="7" t="n"/>
       <c r="F332" s="6" t="inlineStr">
         <is>
-          <t>n/a (unless overriding model calcs)</t>
-        </is>
-      </c>
-      <c r="G332" s="2" t="inlineStr">
-        <is>
-          <t>You are modeling a low-carbon fuel standard (LCFS) that grants an amount of credit to certain fuels for contributing to the LCFS that is not in proportion to the actual CO2 emissions from those fuels.</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G332" s="24" t="n"/>
     </row>
     <row r="333">
       <c r="A333" s="2" t="inlineStr">
@@ -9054,19 +9908,22 @@
       </c>
       <c r="B333" s="2" t="inlineStr">
         <is>
-          <t>EoDfVUwFC</t>
+          <t>BVS</t>
         </is>
       </c>
       <c r="C333" s="2" t="inlineStr">
         <is>
-          <t>Elasticity of Demand for Vehicle Use wrt Fuel Cost</t>
-        </is>
-      </c>
+          <t>BAU Vehicle Subsidy</t>
+        </is>
+      </c>
+      <c r="D333" s="7" t="n"/>
+      <c r="E333" s="7" t="n"/>
       <c r="F333" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G333" s="26" t="n"/>
     </row>
     <row r="334" ht="60" customHeight="1">
       <c r="A334" s="2" t="inlineStr">
@@ -9076,19 +9933,22 @@
       </c>
       <c r="B334" s="2" t="inlineStr">
         <is>
-          <t>EoFoNVFE</t>
+          <t>BVTQaZ</t>
         </is>
       </c>
       <c r="C334" s="2" t="inlineStr">
         <is>
-          <t>Effect of Feebate on New Veh Fuel Economy</t>
-        </is>
-      </c>
+          <t>BAU Vehicle Technologies Qualifying as ZEVs</t>
+        </is>
+      </c>
+      <c r="D334" s="7" t="n"/>
+      <c r="E334" s="7" t="n"/>
       <c r="F334" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G334" s="26" t="n"/>
     </row>
     <row r="335">
       <c r="A335" s="2" t="inlineStr">
@@ -9098,19 +9958,22 @@
       </c>
       <c r="B335" s="2" t="inlineStr">
         <is>
-          <t>EoNVFEwFC</t>
+          <t>BVTStL</t>
         </is>
       </c>
       <c r="C335" s="2" t="inlineStr">
         <is>
-          <t>Elasticity of New Veh Fuel Economy wrt Fuel Cost</t>
-        </is>
-      </c>
+          <t>Boolean Vehicle Types Subject to LCFS</t>
+        </is>
+      </c>
+      <c r="D335" s="7" t="n"/>
+      <c r="E335" s="7" t="n"/>
       <c r="F335" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G335" s="26" t="n"/>
     </row>
     <row r="336">
       <c r="A336" s="2" t="inlineStr">
@@ -9120,17 +9983,24 @@
       </c>
       <c r="B336" s="2" t="inlineStr">
         <is>
-          <t>EoVPwFE</t>
+          <t>CIRbTF</t>
         </is>
       </c>
       <c r="C336" s="2" t="inlineStr">
         <is>
-          <t>Elasticity of Vehicle Price wrt Fuel Economy</t>
-        </is>
-      </c>
+          <t>Carbon Intensity Ratios by Transportation Fuel</t>
+        </is>
+      </c>
+      <c r="D336" s="7" t="n"/>
+      <c r="E336" s="7" t="n"/>
       <c r="F336" s="4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>n/a (unless overriding model calcs)</t>
+        </is>
+      </c>
+      <c r="G336" s="26" t="inlineStr">
+        <is>
+          <t>You are modeling a low-carbon fuel standard (LCFS) that grants an amount of credit to certain fuels for contributing to the LCFS that is not in proportion to the actual CO2 emissions from those fuels.</t>
         </is>
       </c>
     </row>
@@ -9142,24 +10012,22 @@
       </c>
       <c r="B337" s="2" t="inlineStr">
         <is>
-          <t>EVCAP</t>
+          <t>EoDfVUwFC</t>
         </is>
       </c>
       <c r="C337" s="2" t="inlineStr">
         <is>
-          <t>EV Charging Availability Parameters</t>
-        </is>
-      </c>
-      <c r="D337" s="2" t="inlineStr">
-        <is>
-          <t>EV Charging Availability Parameter A, EV Charging Availability Parameter B</t>
-        </is>
-      </c>
+          <t>Elasticity of Demand for Vehicle Use wrt Fuel Cost</t>
+        </is>
+      </c>
+      <c r="D337" s="1" t="n"/>
+      <c r="E337" s="7" t="n"/>
       <c r="F337" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G337" s="26" t="n"/>
     </row>
     <row r="338">
       <c r="A338" s="2" t="inlineStr">
@@ -9169,19 +10037,22 @@
       </c>
       <c r="B338" s="2" t="inlineStr">
         <is>
-          <t>EVCC</t>
+          <t>EoFoNVFE</t>
         </is>
       </c>
       <c r="C338" s="2" t="inlineStr">
         <is>
-          <t>EV Charger Cost</t>
-        </is>
-      </c>
+          <t>Effect of Feebate on New Veh Fuel Economy</t>
+        </is>
+      </c>
+      <c r="D338" s="7" t="n"/>
+      <c r="E338" s="7" t="n"/>
       <c r="F338" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G338" s="26" t="n"/>
     </row>
     <row r="339">
       <c r="A339" s="2" t="inlineStr">
@@ -9191,19 +10062,22 @@
       </c>
       <c r="B339" s="2" t="inlineStr">
         <is>
-          <t>EVCRSbRIC</t>
+          <t>EoNVFEwFC</t>
         </is>
       </c>
       <c r="C339" s="2" t="inlineStr">
         <is>
-          <t>EV Charger Revenue Share by Recipient ISIC Code</t>
-        </is>
-      </c>
+          <t>Elasticity of New Veh Fuel Economy wrt Fuel Cost</t>
+        </is>
+      </c>
+      <c r="D339" s="7" t="n"/>
+      <c r="E339" s="7" t="n"/>
       <c r="F339" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G339" s="26" t="n"/>
     </row>
     <row r="340" ht="45" customHeight="1">
       <c r="A340" s="2" t="inlineStr">
@@ -9213,19 +10087,22 @@
       </c>
       <c r="B340" s="2" t="inlineStr">
         <is>
-          <t>FoSfBPPTtC</t>
+          <t>EoVPwFE</t>
         </is>
       </c>
       <c r="C340" s="2" t="inlineStr">
         <is>
-          <t>Fraction of Subsidy for Battery Production Passed Through to Consumers</t>
-        </is>
-      </c>
+          <t>Elasticity of Vehicle Price wrt Fuel Economy</t>
+        </is>
+      </c>
+      <c r="D340" s="7" t="n"/>
+      <c r="E340" s="7" t="n"/>
       <c r="F340" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G340" s="26" t="n"/>
     </row>
     <row r="341" ht="45" customHeight="1">
       <c r="A341" s="2" t="inlineStr">
@@ -9235,19 +10112,26 @@
       </c>
       <c r="B341" s="2" t="inlineStr">
         <is>
-          <t>FoVBPD</t>
+          <t>EVCAP</t>
         </is>
       </c>
       <c r="C341" s="2" t="inlineStr">
         <is>
-          <t>Fraction of Vehicle Batteries Produced Domestically</t>
-        </is>
-      </c>
+          <t>EV Charging Availability Parameters</t>
+        </is>
+      </c>
+      <c r="D341" s="7" t="inlineStr">
+        <is>
+          <t>EV Charging Availability Parameter A, EV Charging Availability Parameter B</t>
+        </is>
+      </c>
+      <c r="E341" s="7" t="n"/>
       <c r="F341" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G341" s="26" t="n"/>
     </row>
     <row r="342" ht="30.75" customHeight="1" thickBot="1">
       <c r="A342" s="2" t="inlineStr">
@@ -9257,19 +10141,22 @@
       </c>
       <c r="B342" s="2" t="inlineStr">
         <is>
-          <t>FoVObE</t>
+          <t>EVCC</t>
         </is>
       </c>
       <c r="C342" s="2" t="inlineStr">
         <is>
-          <t>Fraction of Vehicles Owned by Entity</t>
-        </is>
-      </c>
+          <t>EV Charger Cost</t>
+        </is>
+      </c>
+      <c r="D342" s="7" t="n"/>
+      <c r="E342" s="7" t="n"/>
       <c r="F342" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G342" s="26" t="n"/>
     </row>
     <row r="343" ht="45" customHeight="1">
       <c r="A343" s="2" t="inlineStr">
@@ -9279,19 +10166,22 @@
       </c>
       <c r="B343" s="2" t="inlineStr">
         <is>
-          <t>FpUCD</t>
+          <t>EVCRSbRIC</t>
         </is>
       </c>
       <c r="C343" s="2" t="inlineStr">
         <is>
-          <t>Fares per Unit Cargo Distance</t>
-        </is>
-      </c>
+          <t>EV Charger Revenue Share by Recipient ISIC Code</t>
+        </is>
+      </c>
+      <c r="D343" s="7" t="n"/>
+      <c r="E343" s="7" t="n"/>
       <c r="F343" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G343" s="26" t="n"/>
     </row>
     <row r="344">
       <c r="A344" s="2" t="inlineStr">
@@ -9301,24 +10191,22 @@
       </c>
       <c r="B344" s="2" t="inlineStr">
         <is>
-          <t>GCApLC</t>
+          <t>FoSfBPPTtC</t>
         </is>
       </c>
       <c r="C344" s="2" t="inlineStr">
         <is>
-          <t>Grams CO2e Avoided per LCFS Credit</t>
-        </is>
-      </c>
+          <t>Fraction of Subsidy for Battery Production Passed Through to Consumers</t>
+        </is>
+      </c>
+      <c r="D344" s="7" t="n"/>
+      <c r="E344" s="7" t="n"/>
       <c r="F344" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G344" s="2" t="inlineStr">
-        <is>
-          <t>You are modeling a low-carbon fuel standard (LCFS) implemented via tradeable credits, and you want the EPS to estimate the number of LCFS credits generated and LCFS credit prices.</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G344" s="24" t="n"/>
     </row>
     <row r="345" ht="30" customHeight="1">
       <c r="A345" s="2" t="inlineStr">
@@ -9328,24 +10216,22 @@
       </c>
       <c r="B345" s="2" t="inlineStr">
         <is>
-          <t>ICtPSFfL</t>
+          <t>FoVBPD</t>
         </is>
       </c>
       <c r="C345" s="2" t="inlineStr">
         <is>
-          <t>Incremental Cost to Produce Substitute Fuel for LCFS</t>
-        </is>
-      </c>
+          <t>Fraction of Vehicle Batteries Produced Domestically</t>
+        </is>
+      </c>
+      <c r="D345" s="7" t="n"/>
+      <c r="E345" s="7" t="n"/>
       <c r="F345" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G345" s="2" t="inlineStr">
-        <is>
-          <t>You are modeling a low-carbon fuel standard (LCFS) implemented via tradeable credits, and you want the EPS to estimate the number of LCFS credits generated and LCFS credit prices.</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G345" s="24" t="n"/>
     </row>
     <row r="346" ht="30" customHeight="1">
       <c r="A346" s="2" t="inlineStr">
@@ -9355,24 +10241,22 @@
       </c>
       <c r="B346" s="2" t="inlineStr">
         <is>
-          <t>LCPC</t>
+          <t>FoVObE</t>
         </is>
       </c>
       <c r="C346" s="2" t="inlineStr">
         <is>
-          <t>LCFS Credit Price Cap</t>
-        </is>
-      </c>
+          <t>Fraction of Vehicles Owned by Entity</t>
+        </is>
+      </c>
+      <c r="D346" s="7" t="n"/>
+      <c r="E346" s="7" t="n"/>
       <c r="F346" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G346" s="2" t="inlineStr">
-        <is>
-          <t>You are modeling a low-carbon fuel standard (LCFS) implemented via tradeable credits, and you want the EPS to estimate the number of LCFS credits generated and LCFS credit prices.</t>
-        </is>
-      </c>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G346" s="24" t="n"/>
     </row>
     <row r="347">
       <c r="A347" s="2" t="inlineStr">
@@ -9382,24 +10266,22 @@
       </c>
       <c r="B347" s="2" t="inlineStr">
         <is>
-          <t>MPoEFUbVT</t>
+          <t>FpUCD</t>
         </is>
       </c>
       <c r="C347" s="2" t="inlineStr">
         <is>
-          <t>Max Perc of Each Fuel Usable by Vehicle Technology</t>
-        </is>
-      </c>
-      <c r="E347" s="2" t="inlineStr">
-        <is>
-          <t>BPoEFUbVT</t>
-        </is>
-      </c>
+          <t>Fares per Unit Cargo Distance</t>
+        </is>
+      </c>
+      <c r="D347" s="7" t="n"/>
+      <c r="E347" s="1" t="n"/>
       <c r="F347" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G347" s="26" t="n"/>
     </row>
     <row r="348">
       <c r="A348" s="2" t="inlineStr">
@@ -9409,17 +10291,24 @@
       </c>
       <c r="B348" s="2" t="inlineStr">
         <is>
-          <t>NBPoNVP</t>
+          <t>GCApLC</t>
         </is>
       </c>
       <c r="C348" s="2" t="inlineStr">
         <is>
-          <t>Non-Battery Portion of New Vehicle Prices</t>
-        </is>
-      </c>
+          <t>Grams CO2e Avoided per LCFS Credit</t>
+        </is>
+      </c>
+      <c r="D348" s="7" t="n"/>
+      <c r="E348" s="7" t="n"/>
       <c r="F348" s="5" t="inlineStr">
         <is>
-          <t>medium (LDVs, HDVs, motorbikes), low (non-road vehicle types)</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G348" s="26" t="inlineStr">
+        <is>
+          <t>You are modeling a low-carbon fuel standard (LCFS) implemented via tradeable credits, and you want the EPS to estimate the number of LCFS credits generated and LCFS credit prices.</t>
         </is>
       </c>
     </row>
@@ -9431,17 +10320,24 @@
       </c>
       <c r="B349" s="2" t="inlineStr">
         <is>
-          <t>PTFURfE</t>
+          <t>ICtPSFfL</t>
         </is>
       </c>
       <c r="C349" s="2" t="inlineStr">
         <is>
-          <t>Percentage Transportation Fuel Use Reduction for Electricity</t>
-        </is>
-      </c>
+          <t>Incremental Cost to Produce Substitute Fuel for LCFS</t>
+        </is>
+      </c>
+      <c r="D349" s="7" t="n"/>
+      <c r="E349" s="7" t="n"/>
       <c r="F349" s="4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G349" s="26" t="inlineStr">
+        <is>
+          <t>You are modeling a low-carbon fuel standard (LCFS) implemented via tradeable credits, and you want the EPS to estimate the number of LCFS credits generated and LCFS credit prices.</t>
         </is>
       </c>
     </row>
@@ -9453,17 +10349,24 @@
       </c>
       <c r="B350" s="2" t="inlineStr">
         <is>
-          <t>PVTStL</t>
+          <t>LCPC</t>
         </is>
       </c>
       <c r="C350" s="2" t="inlineStr">
         <is>
-          <t>Policy Vehicle Types Subject to LCFS</t>
-        </is>
-      </c>
+          <t>LCFS Credit Price Cap</t>
+        </is>
+      </c>
+      <c r="D350" s="7" t="n"/>
+      <c r="E350" s="7" t="n"/>
       <c r="F350" s="4" t="inlineStr">
         <is>
-          <t>low</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G350" s="26" t="inlineStr">
+        <is>
+          <t>You are modeling a low-carbon fuel standard (LCFS) implemented via tradeable credits, and you want the EPS to estimate the number of LCFS credits generated and LCFS credit prices.</t>
         </is>
       </c>
     </row>
@@ -9475,24 +10378,26 @@
       </c>
       <c r="B351" s="2" t="inlineStr">
         <is>
-          <t>QSfV</t>
+          <t>MPoEFUbVT</t>
         </is>
       </c>
       <c r="C351" s="2" t="inlineStr">
         <is>
-          <t>Quantization Size for Vehicles</t>
+          <t>Max Perc of Each Fuel Usable by Vehicle Technology</t>
+        </is>
+      </c>
+      <c r="D351" s="7" t="n"/>
+      <c r="E351" s="7" t="inlineStr">
+        <is>
+          <t>BPoEFUbVT</t>
         </is>
       </c>
       <c r="F351" s="6" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="G351" s="2" t="inlineStr">
-        <is>
-          <t>The fleet average fuel economy for certain vehicle types is being thrown off by rounding error, particularly when an erroneously introduced vehicle is the only vehicle of its type and technology in existence in a particular year</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G351" s="24" t="n"/>
     </row>
     <row r="352" ht="45" customHeight="1">
       <c r="A352" s="2" t="inlineStr">
@@ -9502,19 +10407,22 @@
       </c>
       <c r="B352" s="2" t="inlineStr">
         <is>
-          <t>RPEF</t>
+          <t>NBPoNVP</t>
         </is>
       </c>
       <c r="C352" s="2" t="inlineStr">
         <is>
-          <t>Retail Price Equivalent Factor</t>
-        </is>
-      </c>
+          <t>Non-Battery Portion of New Vehicle Prices</t>
+        </is>
+      </c>
+      <c r="D352" s="7" t="n"/>
+      <c r="E352" s="7" t="n"/>
       <c r="F352" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>medium (LDVs, HDVs, motorbikes), low (non-road vehicle types)</t>
+        </is>
+      </c>
+      <c r="G352" s="26" t="n"/>
     </row>
     <row r="353">
       <c r="A353" s="2" t="inlineStr">
@@ -9524,19 +10432,22 @@
       </c>
       <c r="B353" s="2" t="inlineStr">
         <is>
-          <t>RTMF</t>
+          <t>PTFURfE</t>
         </is>
       </c>
       <c r="C353" s="2" t="inlineStr">
         <is>
-          <t>Recipient Transportation Mode Fractions</t>
-        </is>
-      </c>
+          <t>Percentage Transportation Fuel Use Reduction for Electricity</t>
+        </is>
+      </c>
+      <c r="D353" s="7" t="n"/>
+      <c r="E353" s="7" t="n"/>
       <c r="F353" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G353" s="26" t="n"/>
     </row>
     <row r="354" ht="30" customHeight="1">
       <c r="A354" s="2" t="inlineStr">
@@ -9546,24 +10457,22 @@
       </c>
       <c r="B354" s="2" t="inlineStr">
         <is>
-          <t>RZSPbS</t>
+          <t>PVTStL</t>
         </is>
       </c>
       <c r="C354" s="2" t="inlineStr">
         <is>
-          <t>Required ZEV Sales Percentage by Subregion</t>
-        </is>
-      </c>
+          <t>Policy Vehicle Types Subject to LCFS</t>
+        </is>
+      </c>
+      <c r="D354" s="7" t="n"/>
+      <c r="E354" s="7" t="n"/>
       <c r="F354" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G354" s="2" t="inlineStr">
-        <is>
-          <t>You are modeling non-BAU subregional ZEV sales requirements (as opposed to a national ZEV sales standard)</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G354" s="24" t="n"/>
     </row>
     <row r="355" ht="30" customHeight="1">
       <c r="A355" s="2" t="inlineStr">
@@ -9573,17 +10482,24 @@
       </c>
       <c r="B355" s="2" t="inlineStr">
         <is>
-          <t>SoCDTtiNTY</t>
+          <t>QSfV</t>
         </is>
       </c>
       <c r="C355" s="2" t="inlineStr">
         <is>
-          <t>Share of Cargo Dist Transported that is New This Year</t>
-        </is>
-      </c>
+          <t>Quantization Size for Vehicles</t>
+        </is>
+      </c>
+      <c r="D355" s="7" t="n"/>
+      <c r="E355" s="7" t="n"/>
       <c r="F355" s="14" t="inlineStr">
         <is>
-          <t>to be determined via calibration</t>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="G355" s="26" t="inlineStr">
+        <is>
+          <t>The fleet average fuel economy for certain vehicle types is being thrown off by rounding error, particularly when an erroneously introduced vehicle is the only vehicle of its type and technology in existence in a particular year</t>
         </is>
       </c>
     </row>
@@ -9595,19 +10511,22 @@
       </c>
       <c r="B356" s="2" t="inlineStr">
         <is>
-          <t>SRPbVT</t>
+          <t>RPEF</t>
         </is>
       </c>
       <c r="C356" s="2" t="inlineStr">
         <is>
-          <t>Separately Regulated Pollutants by Vehicle Type</t>
-        </is>
-      </c>
+          <t>Retail Price Equivalent Factor</t>
+        </is>
+      </c>
+      <c r="D356" s="7" t="n"/>
+      <c r="E356" s="7" t="n"/>
       <c r="F356" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G356" s="26" t="n"/>
     </row>
     <row r="357">
       <c r="A357" s="2" t="inlineStr">
@@ -9617,19 +10536,22 @@
       </c>
       <c r="B357" s="2" t="inlineStr">
         <is>
-          <t>SYBCbVT</t>
+          <t>RTMF</t>
         </is>
       </c>
       <c r="C357" s="2" t="inlineStr">
         <is>
-          <t>Start Year Battery Cap by Veh Type</t>
-        </is>
-      </c>
+          <t>Recipient Transportation Mode Fractions</t>
+        </is>
+      </c>
+      <c r="D357" s="7" t="n"/>
+      <c r="E357" s="7" t="n"/>
       <c r="F357" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G357" s="26" t="n"/>
     </row>
     <row r="358" ht="30" customHeight="1">
       <c r="A358" s="2" t="inlineStr">
@@ -9639,17 +10561,24 @@
       </c>
       <c r="B358" s="2" t="inlineStr">
         <is>
-          <t>SYFAFE</t>
+          <t>RZSPbS</t>
         </is>
       </c>
       <c r="C358" s="2" t="inlineStr">
         <is>
-          <t>Start Year Fleet Avg Fuel Economy</t>
-        </is>
-      </c>
+          <t>Required ZEV Sales Percentage by Subregion</t>
+        </is>
+      </c>
+      <c r="D358" s="7" t="n"/>
+      <c r="E358" s="7" t="n"/>
       <c r="F358" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G358" s="26" t="inlineStr">
+        <is>
+          <t>You are modeling non-BAU subregional ZEV sales requirements (as opposed to a national ZEV sales standard)</t>
         </is>
       </c>
     </row>
@@ -9661,19 +10590,22 @@
       </c>
       <c r="B359" s="2" t="inlineStr">
         <is>
-          <t>SYNoEVC</t>
+          <t>SoCDTtiNTY</t>
         </is>
       </c>
       <c r="C359" s="2" t="inlineStr">
         <is>
-          <t>Start Year Number of EV Chargers</t>
-        </is>
-      </c>
+          <t>Share of Cargo Dist Transported that is New This Year</t>
+        </is>
+      </c>
+      <c r="D359" s="7" t="n"/>
+      <c r="E359" s="7" t="n"/>
       <c r="F359" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>to be determined via calibration</t>
+        </is>
+      </c>
+      <c r="G359" s="26" t="n"/>
     </row>
     <row r="360">
       <c r="A360" s="2" t="inlineStr">
@@ -9683,22 +10615,47 @@
       </c>
       <c r="B360" s="2" t="inlineStr">
         <is>
-          <t>SYVbT</t>
+          <t>SRPbVT</t>
         </is>
       </c>
       <c r="C360" s="2" t="inlineStr">
         <is>
-          <t>Start Year Vehicles by Technology</t>
-        </is>
-      </c>
+          <t>Separately Regulated Pollutants by Vehicle Type</t>
+        </is>
+      </c>
+      <c r="D360" s="7" t="n"/>
+      <c r="E360" s="7" t="n"/>
       <c r="F360" s="12" t="inlineStr">
         <is>
-          <t>very high</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G360" s="26" t="n"/>
     </row>
     <row r="361">
-      <c r="F361" s="12" t="n"/>
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>trans</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>SYBCbVT</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>Start Year Battery Cap by Veh Type</t>
+        </is>
+      </c>
+      <c r="D361" s="7" t="n"/>
+      <c r="E361" s="7" t="n"/>
+      <c r="F361" s="12" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G361" s="26" t="n"/>
     </row>
     <row r="362">
       <c r="A362" s="2" t="inlineStr">
@@ -9708,19 +10665,22 @@
       </c>
       <c r="B362" s="2" t="inlineStr">
         <is>
-          <t>TTLE</t>
+          <t>SYFAFE</t>
         </is>
       </c>
       <c r="C362" s="2" t="inlineStr">
         <is>
-          <t>Transportation Technology Logit Exponents</t>
-        </is>
-      </c>
+          <t>Start Year Fleet Avg Fuel Economy</t>
+        </is>
+      </c>
+      <c r="D362" s="7" t="n"/>
+      <c r="E362" s="7" t="n"/>
       <c r="F362" s="14" t="inlineStr">
         <is>
-          <t>to be determined via calibration</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G362" s="26" t="n"/>
     </row>
     <row r="363">
       <c r="A363" s="2" t="inlineStr">
@@ -9730,24 +10690,22 @@
       </c>
       <c r="B363" s="2" t="inlineStr">
         <is>
-          <t>TTS</t>
+          <t>SYNoEVC</t>
         </is>
       </c>
       <c r="C363" s="2" t="inlineStr">
         <is>
-          <t>Transportation Technology Shareweights</t>
-        </is>
-      </c>
-      <c r="E363" s="2" t="inlineStr">
-        <is>
-          <t>SYVbT</t>
-        </is>
-      </c>
+          <t>Start Year Number of EV Chargers</t>
+        </is>
+      </c>
+      <c r="D363" s="7" t="n"/>
+      <c r="E363" s="1" t="n"/>
       <c r="F363" s="5" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
+      <c r="G363" s="26" t="n"/>
     </row>
     <row r="364">
       <c r="A364" s="2" t="inlineStr">
@@ -9757,19 +10715,22 @@
       </c>
       <c r="B364" s="2" t="inlineStr">
         <is>
-          <t>VBDR</t>
+          <t>SYVbT</t>
         </is>
       </c>
       <c r="C364" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Buyer Discount Rate</t>
-        </is>
-      </c>
+          <t>Start Year Vehicles by Technology</t>
+        </is>
+      </c>
+      <c r="D364" s="7" t="n"/>
+      <c r="E364" s="7" t="n"/>
       <c r="F364" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>very high</t>
+        </is>
+      </c>
+      <c r="G364" s="26" t="n"/>
     </row>
     <row r="365">
       <c r="A365" s="2" t="inlineStr">
@@ -9779,19 +10740,22 @@
       </c>
       <c r="B365" s="2" t="inlineStr">
         <is>
-          <t>VRSbRIC</t>
+          <t>TTLE</t>
         </is>
       </c>
       <c r="C365" s="2" t="inlineStr">
         <is>
-          <t>Veh Revenue Share by Recipient ISIC Code</t>
-        </is>
-      </c>
+          <t>Transportation Technology Logit Exponents</t>
+        </is>
+      </c>
+      <c r="D365" s="7" t="n"/>
+      <c r="E365" s="7" t="n"/>
       <c r="F365" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>to be determined via calibration</t>
+        </is>
+      </c>
+      <c r="G365" s="26" t="n"/>
     </row>
     <row r="366">
       <c r="A366" s="2" t="inlineStr">
@@ -9801,24 +10765,26 @@
       </c>
       <c r="B366" s="2" t="inlineStr">
         <is>
-          <t>VSbS</t>
+          <t>TTS</t>
         </is>
       </c>
       <c r="C366" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Shares by Subregion</t>
+          <t>Transportation Technology Shareweights</t>
+        </is>
+      </c>
+      <c r="D366" s="7" t="n"/>
+      <c r="E366" s="7" t="inlineStr">
+        <is>
+          <t>SYVbT</t>
         </is>
       </c>
       <c r="F366" s="3" t="inlineStr">
         <is>
-          <t>high</t>
-        </is>
-      </c>
-      <c r="G366" s="2" t="inlineStr">
-        <is>
-          <t>If you don't wish to consider sub-regional ZEV mandates, you do not need a data source for this variable.  See the "About" tab of this variable for details.</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G366" s="24" t="n"/>
     </row>
     <row r="367">
       <c r="A367" s="2" t="inlineStr">
@@ -9828,24 +10794,22 @@
       </c>
       <c r="B367" s="2" t="inlineStr">
         <is>
-          <t>VTQaZ</t>
+          <t>VBDR</t>
         </is>
       </c>
       <c r="C367" s="2" t="inlineStr">
         <is>
-          <t>Vehicle Technologies Qualifying as ZEVs</t>
-        </is>
-      </c>
+          <t>Vehicle Buyer Discount Rate</t>
+        </is>
+      </c>
+      <c r="D367" s="7" t="n"/>
+      <c r="E367" s="7" t="n"/>
       <c r="F367" s="16" t="inlineStr">
         <is>
-          <t>optional</t>
-        </is>
-      </c>
-      <c r="G367" s="2" t="inlineStr">
-        <is>
-          <t>You wish to use a policy lever to test the effects of switching from one (potentially time-varying) set of ZEV-qualifying vehicle definitions to a different such set.</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G367" s="24" t="n"/>
     </row>
     <row r="368">
       <c r="A368" s="17" t="inlineStr">
@@ -9855,103 +10819,105 @@
       </c>
       <c r="B368" s="17" t="inlineStr">
         <is>
-          <t>VTStFES</t>
+          <t>VRSbRIC</t>
         </is>
       </c>
       <c r="C368" s="17" t="inlineStr">
         <is>
-          <t>Vehicle Technologies Subject to Fuel Economy Standards</t>
-        </is>
-      </c>
-      <c r="D368" s="17" t="n"/>
-      <c r="E368" s="17" t="n"/>
+          <t>Veh Revenue Share by Recipient ISIC Code</t>
+        </is>
+      </c>
+      <c r="D368" s="27" t="n"/>
+      <c r="E368" s="27" t="n"/>
       <c r="F368" s="20" t="inlineStr">
         <is>
           <t>low</t>
         </is>
       </c>
-      <c r="G368" s="17" t="n"/>
+      <c r="G368" s="28" t="n"/>
     </row>
     <row r="369">
       <c r="A369" s="2" t="inlineStr">
         <is>
-          <t>web-app</t>
+          <t>trans</t>
         </is>
       </c>
       <c r="B369" s="2" t="inlineStr">
         <is>
-          <t>BCF</t>
+          <t>VSbS</t>
         </is>
       </c>
       <c r="C369" s="2" t="inlineStr">
         <is>
-          <t>BTU Conversion Factors</t>
-        </is>
-      </c>
-      <c r="D369" s="2" t="inlineStr">
-        <is>
-          <t>BTU per Large Fuel Output Unit, BTU per Small Fuel Output Unit, Vehicle Fuel Economy Unit Conversion Factors, BTU per Energy Import Export Output Unit</t>
-        </is>
-      </c>
+          <t>Vehicle Shares by Subregion</t>
+        </is>
+      </c>
+      <c r="D369" s="1" t="n"/>
+      <c r="E369" s="7" t="n"/>
       <c r="F369" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>high</t>
+        </is>
+      </c>
+      <c r="G369" s="26" t="inlineStr">
+        <is>
+          <t>If you don't wish to consider sub-regional ZEV mandates, you do not need a data source for this variable.  See the "About" tab of this variable for details.</t>
         </is>
       </c>
     </row>
     <row r="370">
       <c r="A370" s="2" t="inlineStr">
         <is>
-          <t>web-app</t>
+          <t>trans</t>
         </is>
       </c>
       <c r="B370" s="2" t="inlineStr">
         <is>
-          <t>BpTPEU</t>
+          <t>VTQaZ</t>
         </is>
       </c>
       <c r="C370" s="2" t="inlineStr">
         <is>
-          <t>BTU per Total Primary Energy Unit</t>
-        </is>
-      </c>
-      <c r="D370" s="2" t="inlineStr">
-        <is>
-          <t>BTU per Large Primary Energy Unit, BTU per Small Primary Energy Unit</t>
-        </is>
-      </c>
+          <t>Vehicle Technologies Qualifying as ZEVs</t>
+        </is>
+      </c>
+      <c r="D370" s="1" t="n"/>
+      <c r="E370" s="7" t="n"/>
       <c r="F370" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>optional</t>
+        </is>
+      </c>
+      <c r="G370" s="26" t="inlineStr">
+        <is>
+          <t>You wish to use a policy lever to test the effects of switching from one (potentially time-varying) set of ZEV-qualifying vehicle definitions to a different such set.</t>
         </is>
       </c>
     </row>
     <row r="371">
       <c r="A371" s="2" t="inlineStr">
         <is>
-          <t>web-app</t>
+          <t>trans</t>
         </is>
       </c>
       <c r="B371" s="2" t="inlineStr">
         <is>
-          <t>CDCF</t>
+          <t>VTStFES</t>
         </is>
       </c>
       <c r="C371" s="2" t="inlineStr">
         <is>
-          <t>Cargo Distance Conversion Factors</t>
-        </is>
-      </c>
-      <c r="D371" s="2" t="inlineStr">
-        <is>
-          <t>Passenger Miles per Passenger Distance Output Unit, Freight Ton Miles per Freight Distance Output Unit</t>
-        </is>
-      </c>
+          <t>Vehicle Technologies Subject to Fuel Economy Standards</t>
+        </is>
+      </c>
+      <c r="D371" s="1" t="n"/>
+      <c r="E371" s="7" t="n"/>
       <c r="F371" s="5" t="inlineStr">
         <is>
-          <t>medium</t>
-        </is>
-      </c>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G371" s="26" t="n"/>
     </row>
     <row r="372">
       <c r="A372" s="2" t="inlineStr">
@@ -9961,19 +10927,26 @@
       </c>
       <c r="B372" s="2" t="inlineStr">
         <is>
-          <t>CID</t>
+          <t>BCF</t>
         </is>
       </c>
       <c r="C372" s="2" t="inlineStr">
         <is>
-          <t>Check Input Data</t>
-        </is>
-      </c>
+          <t>BTU Conversion Factors</t>
+        </is>
+      </c>
+      <c r="D372" s="7" t="inlineStr">
+        <is>
+          <t>BTU per Large Fuel Output Unit, BTU per Small Fuel Output Unit, Vehicle Fuel Economy Unit Conversion Factors, BTU per Energy Import Export Output Unit</t>
+        </is>
+      </c>
+      <c r="E372" s="7" t="n"/>
       <c r="F372" s="25" t="inlineStr">
         <is>
-          <t>do not edit - QC file to automatically check specified files</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G372" s="26" t="n"/>
     </row>
     <row r="373">
       <c r="A373" s="2" t="inlineStr">
@@ -9983,19 +10956,26 @@
       </c>
       <c r="B373" s="2" t="inlineStr">
         <is>
-          <t>LpWOU</t>
+          <t>BpTPEU</t>
         </is>
       </c>
       <c r="C373" s="2" t="inlineStr">
         <is>
-          <t>Liters per Water Output Unit</t>
-        </is>
-      </c>
+          <t>BTU per Total Primary Energy Unit</t>
+        </is>
+      </c>
+      <c r="D373" s="7" t="inlineStr">
+        <is>
+          <t>BTU per Large Primary Energy Unit, BTU per Small Primary Energy Unit</t>
+        </is>
+      </c>
+      <c r="E373" s="7" t="n"/>
       <c r="F373" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G373" s="26" t="n"/>
     </row>
     <row r="374">
       <c r="A374" s="2" t="inlineStr">
@@ -10005,24 +10985,26 @@
       </c>
       <c r="B374" s="2" t="inlineStr">
         <is>
-          <t>MOU</t>
+          <t>CDCF</t>
         </is>
       </c>
       <c r="C374" s="2" t="inlineStr">
         <is>
-          <t>Mass Output Unit</t>
-        </is>
-      </c>
-      <c r="D374" s="2" t="inlineStr">
-        <is>
-          <t>Large Mass Output Unit, Small Mass Output Unit</t>
-        </is>
-      </c>
+          <t>Cargo Distance Conversion Factors</t>
+        </is>
+      </c>
+      <c r="D374" s="1" t="inlineStr">
+        <is>
+          <t>Passenger Miles per Passenger Distance Output Unit, Freight Ton Miles per Freight Distance Output Unit</t>
+        </is>
+      </c>
+      <c r="E374" s="7" t="n"/>
       <c r="F374" s="4" t="inlineStr">
         <is>
-          <t>low</t>
-        </is>
-      </c>
+          <t>medium</t>
+        </is>
+      </c>
+      <c r="G374" s="26" t="n"/>
     </row>
     <row r="375">
       <c r="A375" s="17" t="inlineStr">
@@ -10032,26 +11014,110 @@
       </c>
       <c r="B375" s="17" t="inlineStr">
         <is>
+          <t>CID</t>
+        </is>
+      </c>
+      <c r="C375" s="17" t="inlineStr">
+        <is>
+          <t>Check Input Data</t>
+        </is>
+      </c>
+      <c r="D375" s="27" t="n"/>
+      <c r="E375" s="27" t="n"/>
+      <c r="F375" s="18" t="inlineStr">
+        <is>
+          <t>do not edit - QC file to automatically check specified files</t>
+        </is>
+      </c>
+      <c r="G375" s="28" t="n"/>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>web-app</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>LpWOU</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>Liters per Water Output Unit</t>
+        </is>
+      </c>
+      <c r="D376" s="7" t="n"/>
+      <c r="E376" s="7" t="n"/>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G376" s="26" t="n"/>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>web-app</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>MOU</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>Mass Output Unit</t>
+        </is>
+      </c>
+      <c r="D377" s="7" t="inlineStr">
+        <is>
+          <t>Large Mass Output Unit, Small Mass Output Unit</t>
+        </is>
+      </c>
+      <c r="E377" s="7" t="n"/>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>low</t>
+        </is>
+      </c>
+      <c r="G377" s="26" t="n"/>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>web-app</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
           <t>OCCF</t>
         </is>
       </c>
-      <c r="C375" s="17" t="inlineStr">
+      <c r="C378" t="inlineStr">
         <is>
           <t>Output Currency Conversion Factors</t>
         </is>
       </c>
-      <c r="D375" s="17" t="inlineStr">
+      <c r="D378" s="7" t="inlineStr">
         <is>
           <t>Dollars per Large Output Currency Unit, Dollars per Medium Output Currency Unit, Dollars per Small Output Currency Unit</t>
         </is>
       </c>
-      <c r="E375" s="17" t="n"/>
-      <c r="F375" s="18" t="inlineStr">
+      <c r="E378" s="7" t="n"/>
+      <c r="F378" t="inlineStr">
         <is>
           <t>medium</t>
         </is>
       </c>
-      <c r="G375" s="17" t="n"/>
+      <c r="G378" s="26" t="n"/>
+    </row>
+    <row r="379">
+      <c r="D379" s="7" t="n"/>
+      <c r="E379" s="7" t="n"/>
+      <c r="G379" s="26" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3542397F-0E05-40D4-818F-1A79AF3E7822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6F2122-6EFC-4C98-9904-0C82F363627D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31095" yWindow="2295" windowWidth="21600" windowHeight="12585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1766" uniqueCount="1009">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1015">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -3049,6 +3049,24 @@
   </si>
   <si>
     <t>Clinker Substitution Potential Available by Year</t>
+  </si>
+  <si>
+    <t>CKFSR</t>
+  </si>
+  <si>
+    <t>Cement Kiln Fuel Shift Recipient Fractions</t>
+  </si>
+  <si>
+    <t>Where each fossil kiln fuel's shifted energy goes under the kiln fuel shift policy. The US file sends every fossil fuel to alternative fuels; edit the rows for regions whose kiln-fuel policy converts kilns to gas or co-fires hydrogen.</t>
+  </si>
+  <si>
+    <t>BCPCS</t>
+  </si>
+  <si>
+    <t>BAU Cement Pathway Capital Subsidy</t>
+  </si>
+  <si>
+    <t>Grants or investment tax credits the region already gives new low-carbon clinker capacity, as a share of pathway capital cost by year; zero where none exist (US). Convert capture-equipment-only credits using the capture share of the CCS pathway's capital cost.</t>
   </si>
 </sst>
 </file>
@@ -3532,82 +3550,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>10</v>
       </c>
@@ -3615,32 +3633,32 @@
         <v>940</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
         <v>37</v>
       </c>
@@ -3648,17 +3666,17 @@
         <v>946</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>947</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>20</v>
       </c>
@@ -3666,42 +3684,42 @@
         <v>949</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>29</v>
       </c>
@@ -3709,84 +3727,84 @@
         <v>957</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>25</v>
       </c>
@@ -3794,62 +3812,62 @@
         <v>972</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>973</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>974</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>975</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>976</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>977</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>978</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>979</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>980</v>
       </c>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>981</v>
       </c>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>982</v>
       </c>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>983</v>
       </c>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>984</v>
       </c>
@@ -3862,21 +3880,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G378"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G380"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.453125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="51.26953125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="67" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.81640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.54296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="54" style="2" customWidth="1"/>
-    <col min="8" max="9" width="8.81640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.81640625" style="2"/>
+    <col min="8" max="9" width="8.85546875" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -3899,7 +3917,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -3918,7 +3936,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -3937,7 +3955,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3956,7 +3974,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -3973,7 +3991,7 @@
       </c>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -3990,7 +4008,7 @@
       </c>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -4009,7 +4027,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -4026,7 +4044,7 @@
       </c>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>7</v>
       </c>
@@ -4043,7 +4061,7 @@
       </c>
       <c r="G9" s="28"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -4060,7 +4078,7 @@
       </c>
       <c r="G10" s="26"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -4077,7 +4095,7 @@
       </c>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -4094,7 +4112,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
@@ -4111,7 +4129,7 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -4130,7 +4148,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -4147,7 +4165,7 @@
       </c>
       <c r="G15" s="26"/>
     </row>
-    <row r="16" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -4166,7 +4184,7 @@
       </c>
       <c r="G16" s="26"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -4185,7 +4203,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -4202,7 +4220,7 @@
       </c>
       <c r="G18" s="26"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>32</v>
       </c>
@@ -4221,7 +4239,7 @@
       </c>
       <c r="G19" s="26"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
@@ -4238,7 +4256,7 @@
       </c>
       <c r="G20" s="26"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
@@ -4255,7 +4273,7 @@
       </c>
       <c r="G21" s="26"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
@@ -4272,7 +4290,7 @@
       </c>
       <c r="G22" s="26"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>32</v>
       </c>
@@ -4289,7 +4307,7 @@
       </c>
       <c r="G23" s="26"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -4306,7 +4324,7 @@
       </c>
       <c r="G24" s="26"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>32</v>
       </c>
@@ -4323,7 +4341,7 @@
       </c>
       <c r="G25" s="26"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>32</v>
       </c>
@@ -4340,7 +4358,7 @@
       </c>
       <c r="G26" s="26"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -4359,7 +4377,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
@@ -4376,7 +4394,7 @@
       </c>
       <c r="G28" s="26"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
@@ -4395,7 +4413,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -4412,7 +4430,7 @@
       </c>
       <c r="G30" s="26"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>32</v>
       </c>
@@ -4429,7 +4447,7 @@
       </c>
       <c r="G31" s="26"/>
     </row>
-    <row r="32" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -4448,7 +4466,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
@@ -4467,7 +4485,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -4484,7 +4502,7 @@
       </c>
       <c r="G34" s="24"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>32</v>
       </c>
@@ -4501,7 +4519,7 @@
       </c>
       <c r="G35" s="26"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -4518,7 +4536,7 @@
       </c>
       <c r="G36" s="26"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>32</v>
       </c>
@@ -4535,7 +4553,7 @@
       </c>
       <c r="G37" s="26"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>32</v>
       </c>
@@ -4552,7 +4570,7 @@
       </c>
       <c r="G38" s="26"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>32</v>
       </c>
@@ -4571,7 +4589,7 @@
       </c>
       <c r="G39" s="26"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
         <v>32</v>
       </c>
@@ -4590,7 +4608,7 @@
       </c>
       <c r="G40" s="28"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>104</v>
       </c>
@@ -4607,7 +4625,7 @@
       </c>
       <c r="G41" s="26"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>104</v>
       </c>
@@ -4626,7 +4644,7 @@
       </c>
       <c r="G42" s="26"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>104</v>
       </c>
@@ -4643,7 +4661,7 @@
       </c>
       <c r="G43" s="26"/>
     </row>
-    <row r="44" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>104</v>
       </c>
@@ -4662,7 +4680,7 @@
       </c>
       <c r="G44" s="26"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>104</v>
       </c>
@@ -4681,7 +4699,7 @@
       </c>
       <c r="G45" s="26"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>104</v>
       </c>
@@ -4698,7 +4716,7 @@
       </c>
       <c r="G46" s="26"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>104</v>
       </c>
@@ -4715,7 +4733,7 @@
       </c>
       <c r="G47" s="26"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>104</v>
       </c>
@@ -4732,7 +4750,7 @@
       </c>
       <c r="G48" s="26"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>104</v>
       </c>
@@ -4751,7 +4769,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>104</v>
       </c>
@@ -4768,7 +4786,7 @@
       </c>
       <c r="G50" s="26"/>
     </row>
-    <row r="51" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
         <v>104</v>
       </c>
@@ -4785,7 +4803,7 @@
       </c>
       <c r="G51" s="26"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>131</v>
       </c>
@@ -4802,7 +4820,7 @@
       </c>
       <c r="G52" s="26"/>
     </row>
-    <row r="53" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
         <v>131</v>
       </c>
@@ -4821,7 +4839,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
         <v>137</v>
       </c>
@@ -4840,7 +4858,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>141</v>
       </c>
@@ -4859,7 +4877,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>141</v>
       </c>
@@ -4878,7 +4896,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>141</v>
       </c>
@@ -4897,7 +4915,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>141</v>
       </c>
@@ -4916,7 +4934,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>141</v>
       </c>
@@ -4935,7 +4953,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>141</v>
       </c>
@@ -4954,7 +4972,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>141</v>
       </c>
@@ -4973,7 +4991,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>141</v>
       </c>
@@ -4992,7 +5010,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>141</v>
       </c>
@@ -5011,7 +5029,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>141</v>
       </c>
@@ -5030,7 +5048,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>141</v>
       </c>
@@ -5049,7 +5067,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>141</v>
       </c>
@@ -5068,7 +5086,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>141</v>
       </c>
@@ -5085,7 +5103,7 @@
       </c>
       <c r="G67" s="26"/>
     </row>
-    <row r="68" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>141</v>
       </c>
@@ -5104,7 +5122,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>141</v>
       </c>
@@ -5125,7 +5143,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>141</v>
       </c>
@@ -5146,7 +5164,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>141</v>
       </c>
@@ -5163,7 +5181,7 @@
       </c>
       <c r="G71" s="26"/>
     </row>
-    <row r="72" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
         <v>141</v>
       </c>
@@ -5180,7 +5198,7 @@
       </c>
       <c r="G72" s="28"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>196</v>
       </c>
@@ -5197,7 +5215,7 @@
       </c>
       <c r="G73" s="26"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>196</v>
       </c>
@@ -5214,7 +5232,7 @@
       </c>
       <c r="G74" s="26"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>196</v>
       </c>
@@ -5231,7 +5249,7 @@
       </c>
       <c r="G75" s="26"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>196</v>
       </c>
@@ -5248,7 +5266,7 @@
       </c>
       <c r="G76" s="26"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>196</v>
       </c>
@@ -5265,7 +5283,7 @@
       </c>
       <c r="G77" s="26"/>
     </row>
-    <row r="78" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="17" t="s">
         <v>196</v>
       </c>
@@ -5284,7 +5302,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>210</v>
       </c>
@@ -5301,7 +5319,7 @@
       </c>
       <c r="G79" s="26"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>210</v>
       </c>
@@ -5318,7 +5336,7 @@
       </c>
       <c r="G80" s="26"/>
     </row>
-    <row r="81" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>210</v>
       </c>
@@ -5337,7 +5355,7 @@
       </c>
       <c r="G81" s="26"/>
     </row>
-    <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>210</v>
       </c>
@@ -5356,7 +5374,7 @@
       </c>
       <c r="G82" s="26"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>210</v>
       </c>
@@ -5373,7 +5391,7 @@
       </c>
       <c r="G83" s="26"/>
     </row>
-    <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>210</v>
       </c>
@@ -5390,7 +5408,7 @@
       </c>
       <c r="G84" s="26"/>
     </row>
-    <row r="85" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>210</v>
       </c>
@@ -5409,7 +5427,7 @@
       </c>
       <c r="G85" s="26"/>
     </row>
-    <row r="86" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>210</v>
       </c>
@@ -5428,7 +5446,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
@@ -5447,7 +5465,7 @@
       </c>
       <c r="G87" s="26"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>210</v>
       </c>
@@ -5464,7 +5482,7 @@
       </c>
       <c r="G88" s="26"/>
     </row>
-    <row r="89" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>210</v>
       </c>
@@ -5483,7 +5501,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>210</v>
       </c>
@@ -5502,7 +5520,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>210</v>
       </c>
@@ -5519,7 +5537,7 @@
       </c>
       <c r="G91" s="26"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>210</v>
       </c>
@@ -5536,7 +5554,7 @@
       </c>
       <c r="G92" s="26"/>
     </row>
-    <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>210</v>
       </c>
@@ -5553,7 +5571,7 @@
       </c>
       <c r="G93" s="26"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>210</v>
       </c>
@@ -5574,7 +5592,7 @@
       </c>
       <c r="G94" s="26"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>210</v>
       </c>
@@ -5591,7 +5609,7 @@
       </c>
       <c r="G95" s="26"/>
     </row>
-    <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>210</v>
       </c>
@@ -5608,7 +5626,7 @@
       </c>
       <c r="G96" s="26"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>210</v>
       </c>
@@ -5625,7 +5643,7 @@
       </c>
       <c r="G97" s="26"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>210</v>
       </c>
@@ -5642,7 +5660,7 @@
       </c>
       <c r="G98" s="26"/>
     </row>
-    <row r="99" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>210</v>
       </c>
@@ -5661,7 +5679,7 @@
       </c>
       <c r="G99" s="26"/>
     </row>
-    <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>210</v>
       </c>
@@ -5678,7 +5696,7 @@
       </c>
       <c r="G100" s="26"/>
     </row>
-    <row r="101" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>210</v>
       </c>
@@ -5697,7 +5715,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>210</v>
       </c>
@@ -5714,7 +5732,7 @@
       </c>
       <c r="G102" s="26"/>
     </row>
-    <row r="103" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>210</v>
       </c>
@@ -5733,7 +5751,7 @@
       </c>
       <c r="G103" s="26"/>
     </row>
-    <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>210</v>
       </c>
@@ -5750,7 +5768,7 @@
       </c>
       <c r="G104" s="26"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>210</v>
       </c>
@@ -5767,7 +5785,7 @@
       </c>
       <c r="G105" s="26"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>210</v>
       </c>
@@ -5784,7 +5802,7 @@
       </c>
       <c r="G106" s="26"/>
     </row>
-    <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>210</v>
       </c>
@@ -5803,7 +5821,7 @@
       </c>
       <c r="G107" s="26"/>
     </row>
-    <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>210</v>
       </c>
@@ -5822,7 +5840,7 @@
       </c>
       <c r="G108" s="26"/>
     </row>
-    <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>210</v>
       </c>
@@ -5841,7 +5859,7 @@
       </c>
       <c r="G109" s="26"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>210</v>
       </c>
@@ -5860,7 +5878,7 @@
       </c>
       <c r="G110" s="26"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>210</v>
       </c>
@@ -5877,7 +5895,7 @@
       </c>
       <c r="G111" s="26"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>210</v>
       </c>
@@ -5894,7 +5912,7 @@
       </c>
       <c r="G112" s="26"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>210</v>
       </c>
@@ -5911,7 +5929,7 @@
       </c>
       <c r="G113" s="26"/>
     </row>
-    <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>210</v>
       </c>
@@ -5930,7 +5948,7 @@
       </c>
       <c r="G114" s="26"/>
     </row>
-    <row r="115" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>210</v>
       </c>
@@ -5949,7 +5967,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>210</v>
       </c>
@@ -5966,7 +5984,7 @@
       </c>
       <c r="G116" s="26"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>210</v>
       </c>
@@ -5985,7 +6003,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>210</v>
       </c>
@@ -6002,7 +6020,7 @@
       </c>
       <c r="G118" s="26"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>210</v>
       </c>
@@ -6019,7 +6037,7 @@
       </c>
       <c r="G119" s="26"/>
     </row>
-    <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>210</v>
       </c>
@@ -6036,7 +6054,7 @@
       </c>
       <c r="G120" s="26"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>210</v>
       </c>
@@ -6053,7 +6071,7 @@
       </c>
       <c r="G121" s="26"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>210</v>
       </c>
@@ -6070,7 +6088,7 @@
       </c>
       <c r="G122" s="26"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>210</v>
       </c>
@@ -6087,7 +6105,7 @@
       </c>
       <c r="G123" s="26"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>210</v>
       </c>
@@ -6104,7 +6122,7 @@
       </c>
       <c r="G124" s="26"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>210</v>
       </c>
@@ -6121,7 +6139,7 @@
       </c>
       <c r="G125" s="26"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>210</v>
       </c>
@@ -6138,7 +6156,7 @@
       </c>
       <c r="G126" s="26"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>210</v>
       </c>
@@ -6155,7 +6173,7 @@
       </c>
       <c r="G127" s="26"/>
     </row>
-    <row r="128" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>210</v>
       </c>
@@ -6174,7 +6192,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>210</v>
       </c>
@@ -6193,7 +6211,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>210</v>
       </c>
@@ -6212,7 +6230,7 @@
       </c>
       <c r="G130" s="26"/>
     </row>
-    <row r="131" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>210</v>
       </c>
@@ -6231,7 +6249,7 @@
       </c>
       <c r="G131" s="26"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>210</v>
       </c>
@@ -6248,7 +6266,7 @@
       </c>
       <c r="G132" s="26"/>
     </row>
-    <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>210</v>
       </c>
@@ -6265,7 +6283,7 @@
       </c>
       <c r="G133" s="26"/>
     </row>
-    <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>210</v>
       </c>
@@ -6284,7 +6302,7 @@
       </c>
       <c r="G134" s="26"/>
     </row>
-    <row r="135" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>210</v>
       </c>
@@ -6303,7 +6321,7 @@
       </c>
       <c r="G135" s="26"/>
     </row>
-    <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>210</v>
       </c>
@@ -6324,7 +6342,7 @@
       </c>
       <c r="G136" s="26"/>
     </row>
-    <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>210</v>
       </c>
@@ -6341,7 +6359,7 @@
       </c>
       <c r="G137" s="26"/>
     </row>
-    <row r="138" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>210</v>
       </c>
@@ -6360,7 +6378,7 @@
       </c>
       <c r="G138" s="26"/>
     </row>
-    <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>210</v>
       </c>
@@ -6377,7 +6395,7 @@
       </c>
       <c r="G139" s="26"/>
     </row>
-    <row r="140" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>210</v>
       </c>
@@ -6394,7 +6412,7 @@
       </c>
       <c r="G140" s="26"/>
     </row>
-    <row r="141" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>210</v>
       </c>
@@ -6411,7 +6429,7 @@
       </c>
       <c r="G141" s="26"/>
     </row>
-    <row r="142" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>210</v>
       </c>
@@ -6428,7 +6446,7 @@
       </c>
       <c r="G142" s="26"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>210</v>
       </c>
@@ -6445,7 +6463,7 @@
       </c>
       <c r="G143" s="26"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>210</v>
       </c>
@@ -6464,7 +6482,7 @@
       </c>
       <c r="G144" s="26"/>
     </row>
-    <row r="145" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>210</v>
       </c>
@@ -6483,7 +6501,7 @@
       </c>
       <c r="G145" s="26"/>
     </row>
-    <row r="146" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>210</v>
       </c>
@@ -6500,7 +6518,7 @@
       </c>
       <c r="G146" s="26"/>
     </row>
-    <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>210</v>
       </c>
@@ -6519,7 +6537,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>210</v>
       </c>
@@ -6536,7 +6554,7 @@
       </c>
       <c r="G148" s="26"/>
     </row>
-    <row r="149" spans="1:7" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:7" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>210</v>
       </c>
@@ -6553,7 +6571,7 @@
       </c>
       <c r="G149" s="26"/>
     </row>
-    <row r="150" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="17" t="s">
         <v>210</v>
       </c>
@@ -6574,7 +6592,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>388</v>
       </c>
@@ -6593,7 +6611,7 @@
       </c>
       <c r="G151" s="26"/>
     </row>
-    <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>388</v>
       </c>
@@ -6612,7 +6630,7 @@
       </c>
       <c r="G152" s="26"/>
     </row>
-    <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>388</v>
       </c>
@@ -6629,7 +6647,7 @@
       </c>
       <c r="G153" s="26"/>
     </row>
-    <row r="154" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>388</v>
       </c>
@@ -6646,7 +6664,7 @@
       </c>
       <c r="G154" s="26"/>
     </row>
-    <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>388</v>
       </c>
@@ -6663,7 +6681,7 @@
       </c>
       <c r="G155" s="26"/>
     </row>
-    <row r="156" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>388</v>
       </c>
@@ -6680,7 +6698,7 @@
       </c>
       <c r="G156" s="26"/>
     </row>
-    <row r="157" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
         <v>388</v>
       </c>
@@ -6697,7 +6715,7 @@
       </c>
       <c r="G157" s="28"/>
     </row>
-    <row r="158" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>405</v>
       </c>
@@ -6714,7 +6732,7 @@
       </c>
       <c r="G158" s="26"/>
     </row>
-    <row r="159" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>405</v>
       </c>
@@ -6731,7 +6749,7 @@
       </c>
       <c r="G159" s="26"/>
     </row>
-    <row r="160" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>405</v>
       </c>
@@ -6748,7 +6766,7 @@
       </c>
       <c r="G160" s="26"/>
     </row>
-    <row r="161" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>405</v>
       </c>
@@ -6765,7 +6783,7 @@
       </c>
       <c r="G161" s="26"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>405</v>
       </c>
@@ -6784,7 +6802,7 @@
       </c>
       <c r="G162" s="26"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>405</v>
       </c>
@@ -6801,7 +6819,7 @@
       </c>
       <c r="G163" s="26"/>
     </row>
-    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>405</v>
       </c>
@@ -6818,7 +6836,7 @@
       </c>
       <c r="G164" s="26"/>
     </row>
-    <row r="165" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>405</v>
       </c>
@@ -6837,7 +6855,7 @@
       </c>
       <c r="G165" s="26"/>
     </row>
-    <row r="166" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>405</v>
       </c>
@@ -6854,7 +6872,7 @@
       </c>
       <c r="G166" s="26"/>
     </row>
-    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>405</v>
       </c>
@@ -6871,7 +6889,7 @@
       </c>
       <c r="G167" s="26"/>
     </row>
-    <row r="168" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>405</v>
       </c>
@@ -6888,7 +6906,7 @@
       </c>
       <c r="G168" s="26"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>405</v>
       </c>
@@ -6907,7 +6925,7 @@
       </c>
       <c r="G169" s="26"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>405</v>
       </c>
@@ -6924,7 +6942,7 @@
       </c>
       <c r="G170" s="26"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>405</v>
       </c>
@@ -6941,7 +6959,7 @@
       </c>
       <c r="G171" s="26"/>
     </row>
-    <row r="172" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>405</v>
       </c>
@@ -6958,7 +6976,7 @@
       </c>
       <c r="G172" s="26"/>
     </row>
-    <row r="173" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>405</v>
       </c>
@@ -6977,7 +6995,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>405</v>
       </c>
@@ -6994,7 +7012,7 @@
       </c>
       <c r="G174" s="26"/>
     </row>
-    <row r="175" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>405</v>
       </c>
@@ -7013,7 +7031,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>405</v>
       </c>
@@ -7032,7 +7050,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>405</v>
       </c>
@@ -7051,7 +7069,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>405</v>
       </c>
@@ -7070,7 +7088,7 @@
       </c>
       <c r="G178" s="26"/>
     </row>
-    <row r="179" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>405</v>
       </c>
@@ -7089,7 +7107,7 @@
       </c>
       <c r="G179" s="26"/>
     </row>
-    <row r="180" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>405</v>
       </c>
@@ -7106,7 +7124,7 @@
       </c>
       <c r="G180" s="26"/>
     </row>
-    <row r="181" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>405</v>
       </c>
@@ -7125,7 +7143,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="17" t="s">
         <v>405</v>
       </c>
@@ -7144,7 +7162,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="183" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>467</v>
       </c>
@@ -7163,7 +7181,7 @@
       </c>
       <c r="G183" s="26"/>
     </row>
-    <row r="184" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="17" t="s">
         <v>471</v>
       </c>
@@ -7182,7 +7200,7 @@
       </c>
       <c r="G184" s="26"/>
     </row>
-    <row r="185" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>475</v>
       </c>
@@ -7199,7 +7217,7 @@
       </c>
       <c r="G185" s="26"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>475</v>
       </c>
@@ -7216,7 +7234,7 @@
       </c>
       <c r="G186" s="26"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>475</v>
       </c>
@@ -7233,7 +7251,7 @@
       </c>
       <c r="G187" s="26"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>475</v>
       </c>
@@ -7250,7 +7268,7 @@
       </c>
       <c r="G188" s="26"/>
     </row>
-    <row r="189" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>475</v>
       </c>
@@ -7267,7 +7285,7 @@
       </c>
       <c r="G189" s="26"/>
     </row>
-    <row r="190" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>475</v>
       </c>
@@ -7286,7 +7304,7 @@
       </c>
       <c r="G190" s="26"/>
     </row>
-    <row r="191" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>475</v>
       </c>
@@ -7303,7 +7321,7 @@
       </c>
       <c r="G191" s="26"/>
     </row>
-    <row r="192" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>475</v>
       </c>
@@ -7320,7 +7338,7 @@
       </c>
       <c r="G192" s="26"/>
     </row>
-    <row r="193" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>475</v>
       </c>
@@ -7337,7 +7355,7 @@
       </c>
       <c r="G193" s="26"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>475</v>
       </c>
@@ -7356,7 +7374,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>475</v>
       </c>
@@ -7373,7 +7391,7 @@
       </c>
       <c r="G195" s="26"/>
     </row>
-    <row r="196" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>475</v>
       </c>
@@ -7390,7 +7408,7 @@
       </c>
       <c r="G196" s="26"/>
     </row>
-    <row r="197" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>475</v>
       </c>
@@ -7407,7 +7425,7 @@
       </c>
       <c r="G197" s="26"/>
     </row>
-    <row r="198" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>475</v>
       </c>
@@ -7424,7 +7442,7 @@
       </c>
       <c r="G198" s="26"/>
     </row>
-    <row r="199" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>475</v>
       </c>
@@ -7441,7 +7459,7 @@
       </c>
       <c r="G199" s="26"/>
     </row>
-    <row r="200" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A200" s="17" t="s">
         <v>475</v>
       </c>
@@ -7458,7 +7476,7 @@
       </c>
       <c r="G200" s="26"/>
     </row>
-    <row r="201" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>510</v>
       </c>
@@ -7475,7 +7493,7 @@
       </c>
       <c r="G201" s="26"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>510</v>
       </c>
@@ -7492,7 +7510,7 @@
       </c>
       <c r="G202" s="26"/>
     </row>
-    <row r="203" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>510</v>
       </c>
@@ -7511,7 +7529,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>510</v>
       </c>
@@ -7530,286 +7548,288 @@
       </c>
       <c r="G204" s="24"/>
     </row>
-    <row r="205" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>510</v>
       </c>
       <c r="B205" t="s">
-        <v>521</v>
+        <v>1012</v>
       </c>
       <c r="C205" t="s">
-        <v>522</v>
+        <v>1013</v>
       </c>
       <c r="D205" s="7"/>
       <c r="E205" s="7"/>
       <c r="F205" t="s">
-        <v>10</v>
-      </c>
-      <c r="G205" s="26"/>
-    </row>
-    <row r="206" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A206" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G205" s="26" t="s">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
         <v>510</v>
       </c>
-      <c r="B206" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C206" s="2" t="s">
-        <v>524</v>
+      <c r="B206" t="s">
+        <v>521</v>
+      </c>
+      <c r="C206" t="s">
+        <v>522</v>
       </c>
       <c r="D206" s="7"/>
       <c r="E206" s="7"/>
-      <c r="F206" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G206" s="24" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F206" t="s">
+        <v>10</v>
+      </c>
+      <c r="G206" s="26"/>
+    </row>
+    <row r="207" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B207" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C207" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D207" s="7"/>
       <c r="E207" s="7"/>
-      <c r="F207" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G207" s="26" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F207" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G207" s="24" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D208" s="7"/>
       <c r="E208" s="7"/>
       <c r="F208" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G208" s="26"/>
-    </row>
-    <row r="209" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G208" s="26" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="D209" s="1"/>
+        <v>530</v>
+      </c>
+      <c r="D209" s="7"/>
       <c r="E209" s="7"/>
-      <c r="F209" s="12" t="s">
+      <c r="F209" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G209" s="26"/>
     </row>
-    <row r="210" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="D210" s="7" t="s">
-        <v>535</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="D210" s="1"/>
       <c r="E210" s="7"/>
-      <c r="F210" s="3" t="s">
-        <v>37</v>
+      <c r="F210" s="12" t="s">
+        <v>10</v>
       </c>
       <c r="G210" s="26"/>
     </row>
-    <row r="211" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="D211" s="1"/>
+        <v>534</v>
+      </c>
+      <c r="D211" s="7" t="s">
+        <v>535</v>
+      </c>
       <c r="E211" s="7"/>
-      <c r="F211" s="14" t="s">
-        <v>10</v>
+      <c r="F211" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="G211" s="26"/>
     </row>
-    <row r="212" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D212" s="1" t="s">
-        <v>540</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="D212" s="1"/>
       <c r="E212" s="7"/>
-      <c r="F212" s="4" t="s">
-        <v>541</v>
+      <c r="F212" s="14" t="s">
+        <v>10</v>
       </c>
       <c r="G212" s="26"/>
     </row>
-    <row r="213" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B213" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C213" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D213" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E213" s="7"/>
+      <c r="F213" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="G213" s="26"/>
+    </row>
+    <row r="214" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B214" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C213" s="2" t="s">
+      <c r="C214" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D213" s="7" t="s">
+      <c r="D214" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="E213" s="7"/>
-      <c r="F213" s="5" t="s">
+      <c r="E214" s="7"/>
+      <c r="F214" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G213" s="26"/>
-    </row>
-    <row r="214" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A214" t="s">
-        <v>510</v>
-      </c>
-      <c r="B214" t="s">
-        <v>545</v>
-      </c>
-      <c r="C214" t="s">
-        <v>546</v>
-      </c>
-      <c r="D214" s="7"/>
-      <c r="E214" s="7"/>
-      <c r="F214" t="s">
-        <v>20</v>
-      </c>
       <c r="G214" s="26"/>
     </row>
-    <row r="215" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>510</v>
       </c>
       <c r="B215" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C215" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D215" s="7"/>
       <c r="E215" s="7"/>
       <c r="F215" t="s">
-        <v>29</v>
-      </c>
-      <c r="G215" s="26" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="G215" s="26"/>
+    </row>
+    <row r="216" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>510</v>
       </c>
       <c r="B216" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="C216" t="s">
-        <v>551</v>
+        <v>548</v>
       </c>
       <c r="D216" s="7"/>
       <c r="E216" s="7"/>
       <c r="F216" t="s">
-        <v>20</v>
-      </c>
-      <c r="G216" s="26"/>
-    </row>
-    <row r="217" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="G216" s="26" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>510</v>
       </c>
       <c r="B217" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="C217" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="D217" s="7"/>
       <c r="E217" s="7"/>
       <c r="F217" t="s">
-        <v>29</v>
-      </c>
-      <c r="G217" s="26" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="G217" s="26"/>
+    </row>
+    <row r="218" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>510</v>
       </c>
       <c r="B218" t="s">
-        <v>555</v>
+        <v>1009</v>
       </c>
       <c r="C218" t="s">
-        <v>556</v>
+        <v>1010</v>
       </c>
       <c r="D218" s="7"/>
       <c r="E218" s="7"/>
       <c r="F218" t="s">
         <v>29</v>
       </c>
-      <c r="G218" s="26"/>
-    </row>
-    <row r="219" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G218" s="26" t="s">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>510</v>
       </c>
       <c r="B219" t="s">
-        <v>1004</v>
+        <v>552</v>
       </c>
       <c r="C219" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D219" s="7" t="s">
-        <v>1006</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="D219" s="7"/>
       <c r="E219" s="7"/>
       <c r="F219" t="s">
-        <v>20</v>
-      </c>
-      <c r="G219" s="26"/>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="G219" s="26" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>510</v>
       </c>
       <c r="B220" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C220" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D220" s="7"/>
       <c r="E220" s="7"/>
@@ -7818,725 +7838,727 @@
       </c>
       <c r="G220" s="26"/>
     </row>
-    <row r="221" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>510</v>
       </c>
       <c r="B221" t="s">
-        <v>559</v>
+        <v>1004</v>
       </c>
       <c r="C221" t="s">
-        <v>560</v>
-      </c>
-      <c r="D221" s="7"/>
+        <v>1005</v>
+      </c>
+      <c r="D221" s="7" t="s">
+        <v>1006</v>
+      </c>
       <c r="E221" s="7"/>
       <c r="F221" t="s">
-        <v>10</v>
-      </c>
-      <c r="G221" s="26" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="G221" s="26"/>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>510</v>
       </c>
       <c r="B222" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C222" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="D222" s="7"/>
       <c r="E222" s="7"/>
       <c r="F222" t="s">
-        <v>10</v>
-      </c>
-      <c r="G222" s="26" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="G222" s="26"/>
+    </row>
+    <row r="223" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>510</v>
       </c>
       <c r="B223" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C223" t="s">
-        <v>566</v>
-      </c>
-      <c r="D223" s="7" t="s">
-        <v>567</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="D223" s="7"/>
       <c r="E223" s="7"/>
       <c r="F223" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G223" s="26" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A224" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A224" t="s">
         <v>510</v>
       </c>
-      <c r="B224" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C224" s="2" t="s">
-        <v>570</v>
+      <c r="B224" t="s">
+        <v>562</v>
+      </c>
+      <c r="C224" t="s">
+        <v>563</v>
       </c>
       <c r="D224" s="7"/>
       <c r="E224" s="7"/>
-      <c r="F224" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G224" s="26"/>
-    </row>
-    <row r="225" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A225" s="2" t="s">
+      <c r="F224" t="s">
+        <v>10</v>
+      </c>
+      <c r="G224" s="26" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A225" t="s">
         <v>510</v>
       </c>
-      <c r="B225" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="C225" s="2" t="s">
-        <v>572</v>
-      </c>
-      <c r="D225" s="7"/>
+      <c r="B225" t="s">
+        <v>565</v>
+      </c>
+      <c r="C225" t="s">
+        <v>566</v>
+      </c>
+      <c r="D225" s="7" t="s">
+        <v>567</v>
+      </c>
       <c r="E225" s="7"/>
-      <c r="F225" s="4"/>
-      <c r="G225" s="26"/>
-    </row>
-    <row r="226" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F225" t="s">
+        <v>20</v>
+      </c>
+      <c r="G225" s="26" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B226" s="2" t="s">
-        <v>1007</v>
+        <v>569</v>
       </c>
       <c r="C226" s="2" t="s">
-        <v>1008</v>
+        <v>570</v>
       </c>
       <c r="D226" s="7"/>
       <c r="E226" s="7"/>
-      <c r="F226" s="4"/>
+      <c r="F226" s="5" t="s">
+        <v>96</v>
+      </c>
       <c r="G226" s="26"/>
     </row>
-    <row r="227" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B227" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C227" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D227" s="7"/>
       <c r="E227" s="7"/>
-      <c r="F227" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G227" s="24" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="228" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F227" s="4"/>
+      <c r="G227" s="26"/>
+    </row>
+    <row r="228" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>576</v>
+        <v>1007</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>577</v>
+        <v>1008</v>
       </c>
       <c r="D228" s="7"/>
       <c r="E228" s="7"/>
-      <c r="F228" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G228" s="26" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F228" s="4"/>
+      <c r="G228" s="26"/>
+    </row>
+    <row r="229" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B229" s="2" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="C229" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="D229" s="7"/>
       <c r="E229" s="7"/>
-      <c r="F229" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G229" s="26"/>
-    </row>
-    <row r="230" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F229" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G229" s="24" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B230" s="2" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C230" s="2" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D230" s="7"/>
       <c r="E230" s="7"/>
-      <c r="F230" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G230" s="26"/>
-    </row>
-    <row r="231" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F230" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G230" s="26" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D231" s="7"/>
       <c r="E231" s="7"/>
-      <c r="F231" s="4" t="s">
+      <c r="F231" s="14" t="s">
         <v>20</v>
       </c>
       <c r="G231" s="26"/>
     </row>
-    <row r="232" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="D232" s="1"/>
+        <v>582</v>
+      </c>
+      <c r="D232" s="7"/>
       <c r="E232" s="7"/>
-      <c r="F232" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G232" s="24" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F232" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G232" s="26"/>
+    </row>
+    <row r="233" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="D233" s="7"/>
       <c r="E233" s="7"/>
-      <c r="F233" s="5" t="s">
+      <c r="F233" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G233" s="26"/>
     </row>
-    <row r="234" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="D234" s="7"/>
+        <v>586</v>
+      </c>
+      <c r="D234" s="1"/>
       <c r="E234" s="7"/>
       <c r="F234" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G234" s="26"/>
-    </row>
-    <row r="235" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="G234" s="24" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>592</v>
+        <v>588</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>593</v>
+        <v>589</v>
       </c>
       <c r="D235" s="7"/>
       <c r="E235" s="7"/>
-      <c r="F235" s="4" t="s">
-        <v>29</v>
+      <c r="F235" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G235" s="26"/>
     </row>
-    <row r="236" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>594</v>
+        <v>590</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>595</v>
+        <v>591</v>
       </c>
       <c r="D236" s="7"/>
       <c r="E236" s="7"/>
-      <c r="F236" s="6" t="s">
+      <c r="F236" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G236" s="24"/>
-    </row>
-    <row r="237" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G236" s="26"/>
+    </row>
+    <row r="237" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>596</v>
+        <v>592</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D237" s="7" t="s">
-        <v>598</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="D237" s="7"/>
       <c r="E237" s="7"/>
       <c r="F237" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G237" s="26" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G237" s="26"/>
+    </row>
+    <row r="238" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D238" s="1"/>
+        <v>595</v>
+      </c>
+      <c r="D238" s="7"/>
       <c r="E238" s="7"/>
-      <c r="F238" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G238" s="26"/>
-    </row>
-    <row r="239" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A239" t="s">
+      <c r="F238" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G238" s="24"/>
+    </row>
+    <row r="239" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A239" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B239" t="s">
-        <v>602</v>
-      </c>
-      <c r="C239" t="s">
-        <v>603</v>
-      </c>
-      <c r="D239" s="7"/>
+      <c r="B239" s="2" t="s">
+        <v>596</v>
+      </c>
+      <c r="C239" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="D239" s="7" t="s">
+        <v>598</v>
+      </c>
       <c r="E239" s="7"/>
-      <c r="F239" t="s">
+      <c r="F239" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G239" s="26"/>
-    </row>
-    <row r="240" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G239" s="26" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="240" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>604</v>
+        <v>600</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D240" s="7"/>
+        <v>601</v>
+      </c>
+      <c r="D240" s="1"/>
       <c r="E240" s="7"/>
       <c r="F240" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G240" s="26"/>
     </row>
-    <row r="241" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A241" s="2" t="s">
+    <row r="241" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A241" t="s">
         <v>510</v>
       </c>
-      <c r="B241" s="2" t="s">
-        <v>606</v>
-      </c>
-      <c r="C241" s="2" t="s">
-        <v>607</v>
+      <c r="B241" t="s">
+        <v>602</v>
+      </c>
+      <c r="C241" t="s">
+        <v>603</v>
       </c>
       <c r="D241" s="7"/>
       <c r="E241" s="7"/>
-      <c r="F241" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="G241" s="24" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A242" t="s">
+      <c r="F241" t="s">
+        <v>29</v>
+      </c>
+      <c r="G241" s="26"/>
+    </row>
+    <row r="242" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A242" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B242" t="s">
-        <v>609</v>
-      </c>
-      <c r="C242" t="s">
-        <v>610</v>
+      <c r="B242" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="C242" s="2" t="s">
+        <v>605</v>
       </c>
       <c r="D242" s="7"/>
       <c r="E242" s="7"/>
-      <c r="F242" t="s">
+      <c r="F242" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G242" s="26"/>
     </row>
-    <row r="243" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>611</v>
+        <v>606</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D243" s="1" t="s">
-        <v>613</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="D243" s="7"/>
       <c r="E243" s="7"/>
       <c r="F243" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="G243" s="24" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="244" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A244" t="s">
+        <v>510</v>
+      </c>
+      <c r="B244" t="s">
+        <v>609</v>
+      </c>
+      <c r="C244" t="s">
+        <v>610</v>
+      </c>
+      <c r="D244" s="7"/>
+      <c r="E244" s="7"/>
+      <c r="F244" t="s">
         <v>29</v>
       </c>
-      <c r="G243" s="24"/>
-    </row>
-    <row r="244" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A244" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B244" s="2" t="s">
-        <v>614</v>
-      </c>
-      <c r="C244" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D244" s="1"/>
-      <c r="E244" s="7"/>
-      <c r="F244" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G244" s="26" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="245" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G244" s="26"/>
+    </row>
+    <row r="245" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D245" s="7"/>
+        <v>612</v>
+      </c>
+      <c r="D245" s="1" t="s">
+        <v>613</v>
+      </c>
       <c r="E245" s="7"/>
-      <c r="F245" s="4" t="s">
+      <c r="F245" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G245" s="26"/>
-    </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G245" s="24"/>
+    </row>
+    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>619</v>
+        <v>614</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="D246" s="7"/>
+        <v>615</v>
+      </c>
+      <c r="D246" s="1"/>
       <c r="E246" s="7"/>
-      <c r="F246" s="4" t="s">
-        <v>14</v>
+      <c r="F246" s="14" t="s">
+        <v>10</v>
       </c>
       <c r="G246" s="26" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>622</v>
+        <v>617</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="D247" s="7" t="s">
-        <v>624</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="D247" s="7"/>
       <c r="E247" s="7"/>
-      <c r="F247" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G247" s="26" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="248" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F247" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G247" s="26"/>
+    </row>
+    <row r="248" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>626</v>
+        <v>619</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="D248" s="7" t="s">
-        <v>628</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="D248" s="7"/>
       <c r="E248" s="7"/>
-      <c r="F248" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="G248" s="26"/>
-    </row>
-    <row r="249" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A249" t="s">
+      <c r="F248" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G248" s="26" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="249" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A249" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B249" t="s">
-        <v>629</v>
-      </c>
-      <c r="C249" t="s">
-        <v>630</v>
-      </c>
-      <c r="D249" s="7"/>
+      <c r="B249" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C249" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D249" s="7" t="s">
+        <v>624</v>
+      </c>
       <c r="E249" s="7"/>
-      <c r="F249" t="s">
-        <v>29</v>
-      </c>
-      <c r="G249" s="26"/>
-    </row>
-    <row r="250" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="F249" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G249" s="26" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="250" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>631</v>
+        <v>626</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="D250" s="7"/>
+        <v>627</v>
+      </c>
+      <c r="D250" s="7" t="s">
+        <v>628</v>
+      </c>
       <c r="E250" s="7"/>
-      <c r="F250" s="4" t="s">
-        <v>29</v>
+      <c r="F250" s="5" t="s">
+        <v>541</v>
       </c>
       <c r="G250" s="26"/>
     </row>
-    <row r="251" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A251" s="2" t="s">
+    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A251" t="s">
         <v>510</v>
       </c>
-      <c r="B251" s="2" t="s">
-        <v>633</v>
-      </c>
-      <c r="C251" s="2" t="s">
-        <v>634</v>
+      <c r="B251" t="s">
+        <v>629</v>
+      </c>
+      <c r="C251" t="s">
+        <v>630</v>
       </c>
       <c r="D251" s="7"/>
       <c r="E251" s="7"/>
-      <c r="F251" s="4" t="s">
-        <v>20</v>
+      <c r="F251" t="s">
+        <v>29</v>
       </c>
       <c r="G251" s="26"/>
     </row>
-    <row r="252" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>635</v>
+        <v>631</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>636</v>
+        <v>632</v>
       </c>
       <c r="D252" s="7"/>
       <c r="E252" s="7"/>
-      <c r="F252" s="5" t="s">
-        <v>20</v>
+      <c r="F252" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G252" s="26"/>
     </row>
-    <row r="253" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>637</v>
+        <v>633</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>638</v>
+        <v>634</v>
       </c>
       <c r="D253" s="7"/>
       <c r="E253" s="7"/>
-      <c r="F253" s="5" t="s">
+      <c r="F253" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G253" s="26" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G253" s="26"/>
+    </row>
+    <row r="254" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>640</v>
+        <v>635</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>641</v>
+        <v>636</v>
       </c>
       <c r="D254" s="7"/>
       <c r="E254" s="7"/>
-      <c r="F254" s="4" t="s">
-        <v>29</v>
+      <c r="F254" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G254" s="26"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A255" t="s">
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A255" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B255" t="s">
-        <v>642</v>
-      </c>
-      <c r="C255" t="s">
-        <v>643</v>
+      <c r="B255" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C255" s="2" t="s">
+        <v>638</v>
       </c>
       <c r="D255" s="7"/>
       <c r="E255" s="7"/>
-      <c r="F255" t="s">
-        <v>29</v>
-      </c>
-      <c r="G255" s="26"/>
-    </row>
-    <row r="256" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A256" t="s">
+      <c r="F255" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G255" s="26" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B256" t="s">
-        <v>644</v>
-      </c>
-      <c r="C256" t="s">
-        <v>645</v>
+      <c r="B256" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>641</v>
       </c>
       <c r="D256" s="7"/>
       <c r="E256" s="7"/>
-      <c r="F256" t="s">
-        <v>20</v>
+      <c r="F256" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G256" s="26"/>
     </row>
-    <row r="257" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" t="s">
         <v>510</v>
       </c>
       <c r="B257" t="s">
-        <v>646</v>
+        <v>642</v>
       </c>
       <c r="C257" t="s">
-        <v>647</v>
+        <v>643</v>
       </c>
       <c r="D257" s="7"/>
       <c r="E257" s="7"/>
       <c r="F257" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G257" s="26"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A258" t="s">
         <v>510</v>
       </c>
       <c r="B258" t="s">
-        <v>648</v>
+        <v>644</v>
       </c>
       <c r="C258" t="s">
-        <v>649</v>
+        <v>645</v>
       </c>
       <c r="D258" s="7"/>
       <c r="E258" s="7"/>
       <c r="F258" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G258" s="26"/>
     </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" t="s">
         <v>510</v>
       </c>
       <c r="B259" t="s">
-        <v>650</v>
+        <v>646</v>
       </c>
       <c r="C259" t="s">
-        <v>651</v>
+        <v>647</v>
       </c>
       <c r="D259" s="7"/>
       <c r="E259" s="7"/>
       <c r="F259" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G259" s="26"/>
     </row>
-    <row r="260" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>510</v>
       </c>
       <c r="B260" t="s">
-        <v>652</v>
+        <v>648</v>
       </c>
       <c r="C260" t="s">
-        <v>653</v>
+        <v>649</v>
       </c>
       <c r="D260" s="7"/>
       <c r="E260" s="7"/>
       <c r="F260" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G260" s="26"/>
     </row>
-    <row r="261" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" t="s">
         <v>510</v>
       </c>
       <c r="B261" t="s">
-        <v>654</v>
+        <v>650</v>
       </c>
       <c r="C261" t="s">
-        <v>655</v>
+        <v>651</v>
       </c>
       <c r="D261" s="7"/>
       <c r="E261" s="7"/>
@@ -8545,538 +8567,536 @@
       </c>
       <c r="G261" s="26"/>
     </row>
-    <row r="262" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" t="s">
         <v>510</v>
       </c>
       <c r="B262" t="s">
-        <v>656</v>
+        <v>652</v>
       </c>
       <c r="C262" t="s">
-        <v>657</v>
+        <v>653</v>
       </c>
       <c r="D262" s="7"/>
       <c r="E262" s="7"/>
       <c r="F262" t="s">
-        <v>14</v>
-      </c>
-      <c r="G262" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" x14ac:dyDescent="0.35">
+        <v>37</v>
+      </c>
+      <c r="G262" s="26"/>
+    </row>
+    <row r="263" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>510</v>
       </c>
       <c r="B263" t="s">
-        <v>659</v>
+        <v>654</v>
       </c>
       <c r="C263" t="s">
-        <v>660</v>
+        <v>655</v>
       </c>
       <c r="D263" s="7"/>
       <c r="E263" s="7"/>
       <c r="F263" t="s">
-        <v>14</v>
-      </c>
-      <c r="G263" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A264" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G263" s="26"/>
+    </row>
+    <row r="264" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A264" t="s">
         <v>510</v>
       </c>
-      <c r="B264" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C264" s="2" t="s">
-        <v>662</v>
+      <c r="B264" t="s">
+        <v>656</v>
+      </c>
+      <c r="C264" t="s">
+        <v>657</v>
       </c>
       <c r="D264" s="7"/>
       <c r="E264" s="7"/>
-      <c r="F264" s="3" t="s">
+      <c r="F264" t="s">
         <v>14</v>
       </c>
       <c r="G264" s="26" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A265" s="2" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A265" t="s">
         <v>510</v>
       </c>
-      <c r="B265" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>665</v>
+      <c r="B265" t="s">
+        <v>659</v>
+      </c>
+      <c r="C265" t="s">
+        <v>660</v>
       </c>
       <c r="D265" s="7"/>
       <c r="E265" s="7"/>
-      <c r="F265" s="5" t="s">
+      <c r="F265" t="s">
         <v>14</v>
       </c>
       <c r="G265" s="26" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A266" s="17" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B266" s="17" t="s">
-        <v>667</v>
-      </c>
-      <c r="C266" s="17" t="s">
-        <v>668</v>
-      </c>
-      <c r="D266" s="27"/>
-      <c r="E266" s="27"/>
-      <c r="F266" s="18" t="s">
+      <c r="B266" s="2" t="s">
+        <v>661</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="D266" s="7"/>
+      <c r="E266" s="7"/>
+      <c r="F266" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="G266" s="28" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G266" s="26" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>671</v>
+        <v>665</v>
       </c>
       <c r="D267" s="7"/>
       <c r="E267" s="7"/>
-      <c r="F267" s="3" t="s">
+      <c r="F267" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G267" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A268" s="2" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A268" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="B268" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="C268" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="D268" s="1"/>
-      <c r="E268" s="7"/>
-      <c r="F268" s="3" t="s">
+      <c r="B268" s="17" t="s">
+        <v>667</v>
+      </c>
+      <c r="C268" s="17" t="s">
+        <v>668</v>
+      </c>
+      <c r="D268" s="27"/>
+      <c r="E268" s="27"/>
+      <c r="F268" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G268" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G268" s="28" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>674</v>
+        <v>670</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="D269" s="1"/>
+        <v>671</v>
+      </c>
+      <c r="D269" s="7"/>
       <c r="E269" s="7"/>
       <c r="F269" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G269" s="26"/>
-    </row>
-    <row r="270" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="G269" s="26" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B270" s="2" t="s">
-        <v>676</v>
+        <v>672</v>
       </c>
       <c r="C270" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="D270" s="7"/>
+        <v>673</v>
+      </c>
+      <c r="D270" s="1"/>
       <c r="E270" s="7"/>
       <c r="F270" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G270" s="26"/>
-    </row>
-    <row r="271" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+      <c r="G270" s="26" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="2" t="s">
-        <v>678</v>
+        <v>510</v>
       </c>
       <c r="B271" s="2" t="s">
-        <v>679</v>
+        <v>674</v>
       </c>
       <c r="C271" s="2" t="s">
-        <v>680</v>
-      </c>
-      <c r="D271" s="7"/>
+        <v>675</v>
+      </c>
+      <c r="D271" s="1"/>
       <c r="E271" s="7"/>
       <c r="F271" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G271" s="26"/>
     </row>
-    <row r="272" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="2" t="s">
-        <v>678</v>
+        <v>510</v>
       </c>
       <c r="B272" s="2" t="s">
-        <v>681</v>
+        <v>676</v>
       </c>
       <c r="C272" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="D272" s="7" t="s">
-        <v>683</v>
-      </c>
+        <v>677</v>
+      </c>
+      <c r="D272" s="7"/>
       <c r="E272" s="7"/>
       <c r="F272" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G272" s="26"/>
     </row>
-    <row r="273" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B273" s="2" t="s">
-        <v>684</v>
+        <v>679</v>
       </c>
       <c r="C273" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="D273" s="7" t="s">
-        <v>686</v>
-      </c>
+        <v>680</v>
+      </c>
+      <c r="D273" s="7"/>
       <c r="E273" s="7"/>
       <c r="F273" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G273" s="26"/>
     </row>
-    <row r="274" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B274" s="2" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="C274" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="D274" s="1"/>
-      <c r="E274" s="1"/>
+        <v>682</v>
+      </c>
+      <c r="D274" s="7" t="s">
+        <v>683</v>
+      </c>
+      <c r="E274" s="7"/>
       <c r="F274" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G274" s="26"/>
     </row>
-    <row r="275" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>689</v>
+        <v>684</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="D275" s="7"/>
+        <v>685</v>
+      </c>
+      <c r="D275" s="7" t="s">
+        <v>686</v>
+      </c>
       <c r="E275" s="7"/>
       <c r="F275" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G275" s="26"/>
     </row>
-    <row r="276" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>691</v>
+        <v>687</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>692</v>
-      </c>
-      <c r="D276" s="7"/>
-      <c r="E276" s="7"/>
+        <v>688</v>
+      </c>
+      <c r="D276" s="1"/>
+      <c r="E276" s="1"/>
       <c r="F276" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G276" s="26"/>
     </row>
-    <row r="277" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B277" s="2" t="s">
-        <v>693</v>
+        <v>689</v>
       </c>
       <c r="C277" s="2" t="s">
-        <v>694</v>
+        <v>690</v>
       </c>
       <c r="D277" s="7"/>
       <c r="E277" s="7"/>
-      <c r="F277" s="16" t="s">
+      <c r="F277" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G277" s="24"/>
-    </row>
-    <row r="278" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G277" s="26"/>
+    </row>
+    <row r="278" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A278" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>695</v>
+        <v>691</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="D278" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="E278" s="7" t="s">
-        <v>698</v>
-      </c>
+        <v>692</v>
+      </c>
+      <c r="D278" s="7"/>
+      <c r="E278" s="7"/>
       <c r="F278" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G278" s="26"/>
     </row>
-    <row r="279" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>698</v>
+        <v>693</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>699</v>
+        <v>694</v>
       </c>
       <c r="D279" s="7"/>
       <c r="E279" s="7"/>
-      <c r="F279" s="6" t="s">
+      <c r="F279" s="16" t="s">
         <v>10</v>
       </c>
       <c r="G279" s="24"/>
     </row>
-    <row r="280" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>700</v>
+        <v>695</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>701</v>
-      </c>
-      <c r="D280" s="7"/>
-      <c r="E280" s="1"/>
+        <v>696</v>
+      </c>
+      <c r="D280" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="E280" s="7" t="s">
+        <v>698</v>
+      </c>
       <c r="F280" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G280" s="26"/>
     </row>
-    <row r="281" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>703</v>
+        <v>699</v>
       </c>
       <c r="D281" s="7"/>
       <c r="E281" s="7"/>
-      <c r="F281" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G281" s="26" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F281" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G281" s="24"/>
+    </row>
+    <row r="282" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>705</v>
+        <v>700</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="D282" s="7" t="s">
-        <v>707</v>
-      </c>
-      <c r="E282" s="7"/>
-      <c r="F282" s="5"/>
+        <v>701</v>
+      </c>
+      <c r="D282" s="7"/>
+      <c r="E282" s="1"/>
+      <c r="F282" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G282" s="26"/>
     </row>
-    <row r="283" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="D283" s="7"/>
       <c r="E283" s="7"/>
       <c r="F283" s="5" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="G283" s="26" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="D284" s="7"/>
-      <c r="E284" s="7" t="s">
-        <v>700</v>
-      </c>
-      <c r="F284" s="5" t="s">
-        <v>10</v>
-      </c>
+        <v>706</v>
+      </c>
+      <c r="D284" s="7" t="s">
+        <v>707</v>
+      </c>
+      <c r="E284" s="7"/>
+      <c r="F284" s="5"/>
       <c r="G284" s="26"/>
     </row>
-    <row r="285" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>713</v>
+        <v>708</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>714</v>
+        <v>709</v>
       </c>
       <c r="D285" s="7"/>
       <c r="E285" s="7"/>
-      <c r="F285" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G285" s="26"/>
-    </row>
-    <row r="286" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F285" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G285" s="26" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>715</v>
+        <v>711</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>716</v>
+        <v>712</v>
       </c>
       <c r="D286" s="7"/>
-      <c r="E286" s="7"/>
-      <c r="F286" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G286" s="24"/>
-    </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E286" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="F286" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G286" s="26"/>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>717</v>
+        <v>713</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>718</v>
+        <v>714</v>
       </c>
       <c r="D287" s="7"/>
       <c r="E287" s="7"/>
-      <c r="F287" s="19" t="s">
+      <c r="F287" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G287" s="26"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A288" s="17" t="s">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A288" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="B288" s="17" t="s">
-        <v>719</v>
-      </c>
-      <c r="C288" s="17" t="s">
-        <v>720</v>
-      </c>
-      <c r="D288" s="27"/>
-      <c r="E288" s="27"/>
-      <c r="F288" s="19" t="s">
+      <c r="B288" s="2" t="s">
+        <v>715</v>
+      </c>
+      <c r="C288" s="2" t="s">
+        <v>716</v>
+      </c>
+      <c r="D288" s="7"/>
+      <c r="E288" s="7"/>
+      <c r="F288" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G288" s="28"/>
-    </row>
-    <row r="289" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G288" s="24"/>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>721</v>
+        <v>717</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>722</v>
+        <v>718</v>
       </c>
       <c r="D289" s="7"/>
       <c r="E289" s="7"/>
-      <c r="F289" s="5" t="s">
-        <v>10</v>
+      <c r="F289" s="19" t="s">
+        <v>20</v>
       </c>
       <c r="G289" s="26"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A290" s="2" t="s">
+    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A290" s="17" t="s">
         <v>678</v>
       </c>
-      <c r="B290" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="D290" s="7"/>
-      <c r="E290" s="1"/>
-      <c r="F290" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G290" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="291" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B290" s="17" t="s">
+        <v>719</v>
+      </c>
+      <c r="C290" s="17" t="s">
+        <v>720</v>
+      </c>
+      <c r="D290" s="27"/>
+      <c r="E290" s="27"/>
+      <c r="F290" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G290" s="28"/>
+    </row>
+    <row r="291" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>726</v>
+        <v>721</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>727</v>
+        <v>722</v>
       </c>
       <c r="D291" s="7"/>
       <c r="E291" s="7"/>
@@ -9085,246 +9105,244 @@
       </c>
       <c r="G291" s="26"/>
     </row>
-    <row r="292" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>728</v>
+        <v>723</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>729</v>
+        <v>724</v>
       </c>
       <c r="D292" s="7"/>
-      <c r="E292" s="7"/>
-      <c r="F292" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G292" s="24"/>
-    </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E292" s="1"/>
+      <c r="F292" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G292" s="26" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>731</v>
+        <v>726</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>732</v>
+        <v>727</v>
       </c>
       <c r="D293" s="7"/>
       <c r="E293" s="7"/>
       <c r="F293" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G293" s="26"/>
     </row>
-    <row r="294" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>733</v>
+        <v>728</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>734</v>
+        <v>729</v>
       </c>
       <c r="D294" s="7"/>
-      <c r="E294" s="7" t="s">
-        <v>735</v>
-      </c>
-      <c r="F294" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G294" s="26"/>
-    </row>
-    <row r="295" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="E294" s="7"/>
+      <c r="F294" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G294" s="24"/>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>730</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>737</v>
+        <v>732</v>
       </c>
       <c r="D295" s="7"/>
       <c r="E295" s="7"/>
-      <c r="F295" s="3" t="s">
+      <c r="F295" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G295" s="26"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>730</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>739</v>
+        <v>734</v>
       </c>
       <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
-      <c r="F296" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G296" s="26" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A297" s="17" t="s">
+      <c r="E296" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="F296" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G296" s="26"/>
+    </row>
+    <row r="297" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A297" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="B297" s="17" t="s">
-        <v>741</v>
-      </c>
-      <c r="C297" s="17" t="s">
-        <v>742</v>
-      </c>
-      <c r="D297" s="27"/>
-      <c r="E297" s="27"/>
-      <c r="F297" s="20" t="s">
+      <c r="B297" s="2" t="s">
+        <v>736</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>737</v>
+      </c>
+      <c r="D297" s="7"/>
+      <c r="E297" s="7"/>
+      <c r="F297" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G297" s="28"/>
-    </row>
-    <row r="298" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G297" s="26"/>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>730</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>743</v>
+        <v>738</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>744</v>
+        <v>739</v>
       </c>
       <c r="D298" s="7"/>
       <c r="E298" s="7"/>
-      <c r="F298" s="6" t="s">
+      <c r="F298" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G298" s="26" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A299" s="17" t="s">
+        <v>730</v>
+      </c>
+      <c r="B299" s="17" t="s">
+        <v>741</v>
+      </c>
+      <c r="C299" s="17" t="s">
+        <v>742</v>
+      </c>
+      <c r="D299" s="27"/>
+      <c r="E299" s="27"/>
+      <c r="F299" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G298" s="24"/>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A299" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>746</v>
-      </c>
-      <c r="D299" s="7"/>
-      <c r="E299" s="7"/>
-      <c r="F299" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G299" s="24"/>
-    </row>
-    <row r="300" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G299" s="28"/>
+    </row>
+    <row r="300" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
         <v>730</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>747</v>
+        <v>743</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>748</v>
+        <v>744</v>
       </c>
       <c r="D300" s="7"/>
       <c r="E300" s="7"/>
       <c r="F300" s="6" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G300" s="24"/>
     </row>
-    <row r="301" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>730</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>735</v>
+        <v>745</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D301" s="7"/>
       <c r="E301" s="7"/>
       <c r="F301" s="6" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G301" s="24"/>
     </row>
-    <row r="302" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A302" s="17" t="s">
-        <v>750</v>
-      </c>
-      <c r="B302" s="17" t="s">
-        <v>751</v>
-      </c>
-      <c r="C302" s="17" t="s">
-        <v>752</v>
-      </c>
-      <c r="D302" s="27"/>
-      <c r="E302" s="27"/>
-      <c r="F302" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="G302" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A302" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B302" s="2" t="s">
+        <v>747</v>
+      </c>
+      <c r="C302" s="2" t="s">
+        <v>748</v>
+      </c>
+      <c r="D302" s="7"/>
+      <c r="E302" s="7"/>
+      <c r="F302" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G302" s="24"/>
+    </row>
+    <row r="303" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>754</v>
+        <v>735</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="D303" s="7"/>
       <c r="E303" s="7"/>
-      <c r="F303" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G303" s="26" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A304" s="2" t="s">
+      <c r="F303" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G303" s="24"/>
+    </row>
+    <row r="304" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A304" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="B304" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="C304" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="D304" s="7"/>
-      <c r="E304" s="7"/>
-      <c r="F304" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G304" s="26" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B304" s="17" t="s">
+        <v>751</v>
+      </c>
+      <c r="C304" s="17" t="s">
+        <v>752</v>
+      </c>
+      <c r="D304" s="27"/>
+      <c r="E304" s="27"/>
+      <c r="F304" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="G304" s="28" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>750</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="D305" s="7"/>
       <c r="E305" s="7"/>
@@ -9332,258 +9350,260 @@
         <v>25</v>
       </c>
       <c r="G305" s="26" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>750</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="D306" s="7"/>
       <c r="E306" s="7"/>
-      <c r="F306" s="5" t="s">
+      <c r="F306" s="14" t="s">
         <v>25</v>
       </c>
-      <c r="G306" s="26"/>
-    </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G306" s="26" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="307" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="D307" s="7"/>
       <c r="E307" s="7"/>
       <c r="F307" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G307" s="26"/>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="G307" s="26" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>768</v>
+        <v>763</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>769</v>
+        <v>764</v>
       </c>
       <c r="D308" s="7"/>
       <c r="E308" s="7"/>
       <c r="F308" s="5" t="s">
-        <v>96</v>
+        <v>25</v>
       </c>
       <c r="G308" s="26"/>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>770</v>
+        <v>766</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>771</v>
+        <v>767</v>
       </c>
       <c r="D309" s="7"/>
       <c r="E309" s="7"/>
-      <c r="F309" s="5" t="s">
+      <c r="F309" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G309" s="26"/>
     </row>
-    <row r="310" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>772</v>
+        <v>768</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="D310" s="7"/>
       <c r="E310" s="7"/>
-      <c r="F310" s="4" t="s">
-        <v>20</v>
+      <c r="F310" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="G310" s="26"/>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>774</v>
+        <v>770</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>775</v>
+        <v>771</v>
       </c>
       <c r="D311" s="7"/>
       <c r="E311" s="7"/>
-      <c r="F311" s="4" t="s">
+      <c r="F311" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G311" s="26"/>
     </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>776</v>
+        <v>772</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>777</v>
+        <v>773</v>
       </c>
       <c r="D312" s="7"/>
       <c r="E312" s="7"/>
-      <c r="F312" s="5" t="s">
+      <c r="F312" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G312" s="26"/>
     </row>
-    <row r="313" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>778</v>
+        <v>774</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="D313" s="7"/>
       <c r="E313" s="7"/>
-      <c r="F313" s="3" t="s">
-        <v>20</v>
+      <c r="F313" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G313" s="26"/>
     </row>
-    <row r="314" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>780</v>
+        <v>776</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>781</v>
+        <v>777</v>
       </c>
       <c r="D314" s="7"/>
       <c r="E314" s="7"/>
-      <c r="F314" s="3" t="s">
-        <v>29</v>
+      <c r="F314" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G314" s="26"/>
     </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>782</v>
+        <v>778</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>783</v>
+        <v>779</v>
       </c>
       <c r="D315" s="7"/>
-      <c r="E315" s="1"/>
-      <c r="F315" s="5" t="s">
-        <v>29</v>
+      <c r="E315" s="7"/>
+      <c r="F315" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G315" s="26"/>
     </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>784</v>
+        <v>780</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="D316" s="7"/>
       <c r="E316" s="7"/>
       <c r="F316" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G316" s="26"/>
     </row>
-    <row r="317" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="D317" s="7"/>
-      <c r="E317" s="7"/>
+      <c r="E317" s="1"/>
       <c r="F317" s="5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G317" s="26"/>
     </row>
-    <row r="318" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>789</v>
+        <v>785</v>
       </c>
       <c r="D318" s="7"/>
       <c r="E318" s="7"/>
-      <c r="F318" s="5" t="s">
-        <v>10</v>
+      <c r="F318" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G318" s="26"/>
     </row>
-    <row r="319" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>790</v>
+        <v>786</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>791</v>
+        <v>787</v>
       </c>
       <c r="D319" s="7"/>
-      <c r="E319" s="7" t="s">
-        <v>792</v>
-      </c>
+      <c r="E319" s="7"/>
       <c r="F319" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G319" s="26"/>
     </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>793</v>
+        <v>788</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>794</v>
+        <v>789</v>
       </c>
       <c r="D320" s="7"/>
       <c r="E320" s="7"/>
@@ -9592,49 +9612,51 @@
       </c>
       <c r="G320" s="26"/>
     </row>
-    <row r="321" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>795</v>
+        <v>790</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="D321" s="7"/>
-      <c r="E321" s="7"/>
+      <c r="E321" s="7" t="s">
+        <v>792</v>
+      </c>
       <c r="F321" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G321" s="26"/>
     </row>
-    <row r="322" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>797</v>
+        <v>793</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="D322" s="1"/>
+        <v>794</v>
+      </c>
+      <c r="D322" s="7"/>
       <c r="E322" s="7"/>
       <c r="F322" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G322" s="26"/>
     </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>799</v>
+        <v>795</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>800</v>
+        <v>796</v>
       </c>
       <c r="D323" s="7"/>
       <c r="E323" s="7"/>
@@ -9643,68 +9665,66 @@
       </c>
       <c r="G323" s="26"/>
     </row>
-    <row r="324" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>801</v>
+        <v>797</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="D324" s="7"/>
+        <v>798</v>
+      </c>
+      <c r="D324" s="1"/>
       <c r="E324" s="7"/>
       <c r="F324" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G324" s="26"/>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>803</v>
+        <v>799</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>804</v>
+        <v>800</v>
       </c>
       <c r="D325" s="7"/>
       <c r="E325" s="7"/>
-      <c r="F325" s="3" t="s">
+      <c r="F325" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G325" s="26"/>
     </row>
-    <row r="326" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>805</v>
+        <v>801</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="D326" s="7" t="s">
-        <v>807</v>
-      </c>
+        <v>802</v>
+      </c>
+      <c r="D326" s="7"/>
       <c r="E326" s="7"/>
-      <c r="F326" s="3" t="s">
+      <c r="F326" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G326" s="26"/>
     </row>
-    <row r="327" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>808</v>
+        <v>803</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>809</v>
+        <v>804</v>
       </c>
       <c r="D327" s="7"/>
       <c r="E327" s="7"/>
@@ -9713,892 +9733,928 @@
       </c>
       <c r="G327" s="26"/>
     </row>
-    <row r="328" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>810</v>
+        <v>805</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>811</v>
-      </c>
-      <c r="D328" s="7"/>
+        <v>806</v>
+      </c>
+      <c r="D328" s="7" t="s">
+        <v>807</v>
+      </c>
       <c r="E328" s="7"/>
       <c r="F328" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G328" s="26"/>
     </row>
-    <row r="329" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>812</v>
+        <v>808</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>813</v>
+        <v>809</v>
       </c>
       <c r="D329" s="7"/>
       <c r="E329" s="7"/>
-      <c r="F329" s="4" t="s">
-        <v>10</v>
+      <c r="F329" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G329" s="26"/>
     </row>
-    <row r="330" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>814</v>
+        <v>810</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>815</v>
+        <v>811</v>
       </c>
       <c r="D330" s="7"/>
       <c r="E330" s="7"/>
-      <c r="F330" s="4" t="s">
-        <v>10</v>
+      <c r="F330" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G330" s="26"/>
     </row>
-    <row r="331" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>816</v>
+        <v>812</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>817</v>
+        <v>813</v>
       </c>
       <c r="D331" s="7"/>
       <c r="E331" s="7"/>
-      <c r="F331" s="6" t="s">
+      <c r="F331" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G331" s="24"/>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G331" s="26"/>
+    </row>
+    <row r="332" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>818</v>
+        <v>814</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>819</v>
+        <v>815</v>
       </c>
       <c r="D332" s="7"/>
       <c r="E332" s="7"/>
-      <c r="F332" s="5" t="s">
+      <c r="F332" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G332" s="26"/>
     </row>
-    <row r="333" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>820</v>
+        <v>816</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="D333" s="7"/>
       <c r="E333" s="7"/>
-      <c r="F333" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G333" s="26"/>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F333" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G333" s="24"/>
+    </row>
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>823</v>
+        <v>819</v>
       </c>
       <c r="D334" s="7"/>
       <c r="E334" s="7"/>
       <c r="F334" s="5" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G334" s="26"/>
     </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D335" s="7"/>
       <c r="E335" s="7"/>
-      <c r="F335" s="4" t="s">
-        <v>826</v>
-      </c>
-      <c r="G335" s="26" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="336" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F335" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G335" s="26"/>
+    </row>
+    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="D336" s="1"/>
+        <v>823</v>
+      </c>
+      <c r="D336" s="7"/>
       <c r="E336" s="7"/>
       <c r="F336" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G336" s="26"/>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="D337" s="7"/>
       <c r="E337" s="7"/>
       <c r="F337" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G337" s="26"/>
-    </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.35">
+        <v>826</v>
+      </c>
+      <c r="G337" s="26" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>832</v>
+        <v>828</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="D338" s="7"/>
+        <v>829</v>
+      </c>
+      <c r="D338" s="1"/>
       <c r="E338" s="7"/>
-      <c r="F338" s="4" t="s">
+      <c r="F338" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G338" s="26"/>
     </row>
-    <row r="339" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>834</v>
+        <v>830</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>835</v>
+        <v>831</v>
       </c>
       <c r="D339" s="7"/>
       <c r="E339" s="7"/>
-      <c r="F339" s="5" t="s">
-        <v>29</v>
+      <c r="F339" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G339" s="26"/>
     </row>
-    <row r="340" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>836</v>
+        <v>832</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="D340" s="7" t="s">
-        <v>838</v>
-      </c>
+        <v>833</v>
+      </c>
+      <c r="D340" s="7"/>
       <c r="E340" s="7"/>
-      <c r="F340" s="3" t="s">
+      <c r="F340" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G340" s="26"/>
     </row>
-    <row r="341" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="341" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>839</v>
+        <v>834</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>840</v>
+        <v>835</v>
       </c>
       <c r="D341" s="7"/>
       <c r="E341" s="7"/>
-      <c r="F341" s="3" t="s">
+      <c r="F341" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G341" s="26"/>
     </row>
-    <row r="342" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>841</v>
+        <v>836</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>842</v>
-      </c>
-      <c r="D342" s="7"/>
+        <v>837</v>
+      </c>
+      <c r="D342" s="7" t="s">
+        <v>838</v>
+      </c>
       <c r="E342" s="7"/>
-      <c r="F342" s="5" t="s">
-        <v>29</v>
+      <c r="F342" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G342" s="26"/>
     </row>
-    <row r="343" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A343" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>843</v>
+        <v>839</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>844</v>
+        <v>840</v>
       </c>
       <c r="D343" s="7"/>
       <c r="E343" s="7"/>
-      <c r="F343" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G343" s="24"/>
-    </row>
-    <row r="344" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F343" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G343" s="26"/>
+    </row>
+    <row r="344" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>845</v>
+        <v>841</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>846</v>
+        <v>842</v>
       </c>
       <c r="D344" s="7"/>
       <c r="E344" s="7"/>
-      <c r="F344" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G344" s="24"/>
-    </row>
-    <row r="345" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F344" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G344" s="26"/>
+    </row>
+    <row r="345" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>847</v>
+        <v>843</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="D345" s="7"/>
       <c r="E345" s="7"/>
       <c r="F345" s="16" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G345" s="24"/>
     </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="D346" s="7"/>
-      <c r="E346" s="1"/>
-      <c r="F346" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G346" s="26"/>
-    </row>
-    <row r="347" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E346" s="7"/>
+      <c r="F346" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G346" s="24"/>
+    </row>
+    <row r="347" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="D347" s="7"/>
       <c r="E347" s="7"/>
-      <c r="F347" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G347" s="26" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="348" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F347" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G347" s="24"/>
+    </row>
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="D348" s="7"/>
-      <c r="E348" s="7"/>
+      <c r="E348" s="1"/>
       <c r="F348" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G348" s="26" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="349" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="G348" s="26"/>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>857</v>
+        <v>852</v>
       </c>
       <c r="D349" s="7"/>
       <c r="E349" s="7"/>
-      <c r="F349" s="4" t="s">
+      <c r="F349" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G349" s="26" t="s">
         <v>853</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>858</v>
+        <v>854</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>859</v>
+        <v>855</v>
       </c>
       <c r="D350" s="7"/>
-      <c r="E350" s="7" t="s">
-        <v>803</v>
-      </c>
-      <c r="F350" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G350" s="24"/>
-    </row>
-    <row r="351" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E350" s="7"/>
+      <c r="F350" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G350" s="26" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="D351" s="7"/>
       <c r="E351" s="7"/>
-      <c r="F351" s="5" t="s">
-        <v>862</v>
-      </c>
-      <c r="G351" s="26"/>
-    </row>
-    <row r="352" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="F351" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G351" s="26" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="352" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="D352" s="7"/>
-      <c r="E352" s="7"/>
-      <c r="F352" s="5" t="s">
+      <c r="E352" s="7" t="s">
+        <v>803</v>
+      </c>
+      <c r="F352" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G352" s="26"/>
-    </row>
-    <row r="353" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G352" s="24"/>
+    </row>
+    <row r="353" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="D353" s="7"/>
       <c r="E353" s="7"/>
-      <c r="F353" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G353" s="24"/>
-    </row>
-    <row r="354" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F353" s="5" t="s">
+        <v>862</v>
+      </c>
+      <c r="G353" s="26"/>
+    </row>
+    <row r="354" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D354" s="7"/>
       <c r="E354" s="7"/>
-      <c r="F354" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G354" s="26" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F354" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G354" s="26"/>
+    </row>
+    <row r="355" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="D355" s="7"/>
       <c r="E355" s="7"/>
-      <c r="F355" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G355" s="26"/>
-    </row>
-    <row r="356" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F355" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G355" s="24"/>
+    </row>
+    <row r="356" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="D356" s="7"/>
       <c r="E356" s="7"/>
-      <c r="F356" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G356" s="26"/>
-    </row>
-    <row r="357" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F356" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G356" s="26" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D357" s="7"/>
       <c r="E357" s="7"/>
       <c r="F357" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G357" s="26" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="G357" s="26"/>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>877</v>
+        <v>872</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>878</v>
+        <v>873</v>
       </c>
       <c r="D358" s="7"/>
       <c r="E358" s="7"/>
-      <c r="F358" s="5" t="s">
-        <v>96</v>
+      <c r="F358" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G358" s="26"/>
     </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="D359" s="7"/>
       <c r="E359" s="7"/>
-      <c r="F359" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G359" s="26"/>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A360" t="s">
+      <c r="F359" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G359" s="26" t="s">
+        <v>876</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A360" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B360" t="s">
-        <v>881</v>
-      </c>
-      <c r="C360" t="s">
-        <v>882</v>
+      <c r="B360" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>878</v>
       </c>
       <c r="D360" s="7"/>
       <c r="E360" s="7"/>
-      <c r="F360" s="12" t="s">
-        <v>29</v>
+      <c r="F360" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="G360" s="26"/>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>884</v>
+        <v>880</v>
       </c>
       <c r="D361" s="7"/>
       <c r="E361" s="7"/>
-      <c r="F361" s="14" t="s">
+      <c r="F361" s="12" t="s">
         <v>20</v>
       </c>
       <c r="G361" s="26"/>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A362" s="2" t="s">
+    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A362" t="s">
         <v>765</v>
       </c>
-      <c r="B362" s="2" t="s">
-        <v>885</v>
-      </c>
-      <c r="C362" s="2" t="s">
-        <v>886</v>
+      <c r="B362" t="s">
+        <v>881</v>
+      </c>
+      <c r="C362" t="s">
+        <v>882</v>
       </c>
       <c r="D362" s="7"/>
-      <c r="E362" s="1"/>
-      <c r="F362" s="5" t="s">
-        <v>20</v>
+      <c r="E362" s="7"/>
+      <c r="F362" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="G362" s="26"/>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>887</v>
+        <v>883</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>888</v>
+        <v>884</v>
       </c>
       <c r="D363" s="7"/>
       <c r="E363" s="7"/>
-      <c r="F363" s="5" t="s">
-        <v>37</v>
+      <c r="F363" s="14" t="s">
+        <v>20</v>
       </c>
       <c r="G363" s="26"/>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>889</v>
+        <v>885</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>890</v>
+        <v>886</v>
       </c>
       <c r="D364" s="7"/>
-      <c r="E364" s="7"/>
-      <c r="F364" s="4" t="s">
-        <v>96</v>
+      <c r="E364" s="1"/>
+      <c r="F364" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G364" s="26"/>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>891</v>
+        <v>887</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>892</v>
+        <v>888</v>
       </c>
       <c r="D365" s="7"/>
-      <c r="E365" s="7" t="s">
-        <v>887</v>
-      </c>
-      <c r="F365" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G365" s="24"/>
-    </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E365" s="7"/>
+      <c r="F365" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G365" s="26"/>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>893</v>
+        <v>889</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>894</v>
+        <v>890</v>
       </c>
       <c r="D366" s="7"/>
       <c r="E366" s="7"/>
-      <c r="F366" s="16" t="s">
+      <c r="F366" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G366" s="26"/>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A367" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B367" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="D367" s="7"/>
+      <c r="E367" s="7" t="s">
+        <v>887</v>
+      </c>
+      <c r="F367" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G366" s="24"/>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A367" s="17" t="s">
-        <v>765</v>
-      </c>
-      <c r="B367" s="17" t="s">
-        <v>895</v>
-      </c>
-      <c r="C367" s="17" t="s">
-        <v>896</v>
-      </c>
-      <c r="D367" s="27"/>
-      <c r="E367" s="27"/>
-      <c r="F367" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G367" s="28"/>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G367" s="24"/>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>898</v>
-      </c>
-      <c r="D368" s="1"/>
+        <v>894</v>
+      </c>
+      <c r="D368" s="7"/>
       <c r="E368" s="7"/>
-      <c r="F368" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G368" s="26" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A369" s="2" t="s">
+      <c r="F368" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G368" s="24"/>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A369" s="17" t="s">
         <v>765</v>
       </c>
-      <c r="B369" s="2" t="s">
-        <v>900</v>
-      </c>
-      <c r="C369" s="2" t="s">
-        <v>901</v>
-      </c>
-      <c r="D369" s="1"/>
-      <c r="E369" s="7"/>
-      <c r="F369" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G369" s="26" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B369" s="17" t="s">
+        <v>895</v>
+      </c>
+      <c r="C369" s="17" t="s">
+        <v>896</v>
+      </c>
+      <c r="D369" s="27"/>
+      <c r="E369" s="27"/>
+      <c r="F369" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G369" s="28"/>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
       <c r="D370" s="1"/>
       <c r="E370" s="7"/>
       <c r="F370" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G370" s="26" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A371" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B371" s="2" t="s">
+        <v>900</v>
+      </c>
+      <c r="C371" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="D371" s="1"/>
+      <c r="E371" s="7"/>
+      <c r="F371" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G371" s="26" t="s">
+        <v>902</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A372" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B372" s="2" t="s">
+        <v>903</v>
+      </c>
+      <c r="C372" s="2" t="s">
+        <v>904</v>
+      </c>
+      <c r="D372" s="1"/>
+      <c r="E372" s="7"/>
+      <c r="F372" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G370" s="26"/>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A371" s="2" t="s">
-        <v>905</v>
-      </c>
-      <c r="B371" s="2" t="s">
-        <v>906</v>
-      </c>
-      <c r="C371" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="D371" s="7" t="s">
-        <v>908</v>
-      </c>
-      <c r="E371" s="7"/>
-      <c r="F371" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G371" s="26"/>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A372" s="2" t="s">
-        <v>905</v>
-      </c>
-      <c r="B372" s="2" t="s">
-        <v>909</v>
-      </c>
-      <c r="C372" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="D372" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="E372" s="7"/>
-      <c r="F372" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="G372" s="26"/>
     </row>
-    <row r="373" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>905</v>
       </c>
       <c r="B373" s="2" t="s">
+        <v>906</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>907</v>
+      </c>
+      <c r="D373" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="E373" s="7"/>
+      <c r="F373" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G373" s="26"/>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A374" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>909</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>910</v>
+      </c>
+      <c r="D374" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="E374" s="7"/>
+      <c r="F374" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G374" s="26"/>
+    </row>
+    <row r="375" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A375" s="2" t="s">
+        <v>905</v>
+      </c>
+      <c r="B375" s="2" t="s">
         <v>912</v>
       </c>
-      <c r="C373" s="2" t="s">
+      <c r="C375" s="2" t="s">
         <v>913</v>
       </c>
-      <c r="D373" s="1" t="s">
+      <c r="D375" s="1" t="s">
         <v>914</v>
       </c>
-      <c r="E373" s="7"/>
-      <c r="F373" s="4" t="s">
+      <c r="E375" s="7"/>
+      <c r="F375" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G373" s="26"/>
-    </row>
-    <row r="374" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A374" s="17" t="s">
+      <c r="G375" s="26"/>
+    </row>
+    <row r="376" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A376" s="17" t="s">
         <v>905</v>
       </c>
-      <c r="B374" s="17" t="s">
+      <c r="B376" s="17" t="s">
         <v>915</v>
       </c>
-      <c r="C374" s="17" t="s">
+      <c r="C376" s="17" t="s">
         <v>916</v>
       </c>
-      <c r="D374" s="27"/>
-      <c r="E374" s="27"/>
-      <c r="F374" s="18" t="s">
+      <c r="D376" s="27"/>
+      <c r="E376" s="27"/>
+      <c r="F376" s="18" t="s">
         <v>917</v>
       </c>
-      <c r="G374" s="28"/>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A375" t="s">
-        <v>905</v>
-      </c>
-      <c r="B375" t="s">
-        <v>918</v>
-      </c>
-      <c r="C375" t="s">
-        <v>919</v>
-      </c>
-      <c r="D375" s="7"/>
-      <c r="E375" s="7"/>
-      <c r="F375" t="s">
-        <v>29</v>
-      </c>
-      <c r="G375" s="26"/>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A376" t="s">
-        <v>905</v>
-      </c>
-      <c r="B376" t="s">
-        <v>920</v>
-      </c>
-      <c r="C376" t="s">
-        <v>921</v>
-      </c>
-      <c r="D376" s="7" t="s">
-        <v>922</v>
-      </c>
-      <c r="E376" s="7"/>
-      <c r="F376" t="s">
-        <v>29</v>
-      </c>
-      <c r="G376" s="26"/>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G376" s="28"/>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" t="s">
         <v>905</v>
       </c>
       <c r="B377" t="s">
-        <v>923</v>
+        <v>918</v>
       </c>
       <c r="C377" t="s">
-        <v>924</v>
-      </c>
-      <c r="D377" s="7" t="s">
-        <v>925</v>
-      </c>
+        <v>919</v>
+      </c>
+      <c r="D377" s="7"/>
       <c r="E377" s="7"/>
       <c r="F377" t="s">
+        <v>29</v>
+      </c>
+      <c r="G377" s="26"/>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A378" t="s">
+        <v>905</v>
+      </c>
+      <c r="B378" t="s">
+        <v>920</v>
+      </c>
+      <c r="C378" t="s">
+        <v>921</v>
+      </c>
+      <c r="D378" s="7" t="s">
+        <v>922</v>
+      </c>
+      <c r="E378" s="7"/>
+      <c r="F378" t="s">
+        <v>29</v>
+      </c>
+      <c r="G378" s="26"/>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>905</v>
+      </c>
+      <c r="B379" t="s">
+        <v>923</v>
+      </c>
+      <c r="C379" t="s">
+        <v>924</v>
+      </c>
+      <c r="D379" s="7" t="s">
+        <v>925</v>
+      </c>
+      <c r="E379" s="7"/>
+      <c r="F379" t="s">
         <v>20</v>
       </c>
-      <c r="G377" s="26"/>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="D378" s="7"/>
-      <c r="E378" s="7"/>
-      <c r="G378" s="26"/>
+      <c r="G379" s="26"/>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D380" s="7"/>
+      <c r="E380" s="7"/>
+      <c r="G380" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10609,13 +10665,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" customWidth="1"/>
-    <col min="2" max="2" width="52.26953125" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="52.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10623,7 +10679,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -10631,7 +10687,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -10639,7 +10695,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -10647,7 +10703,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>131</v>
       </c>
@@ -10655,7 +10711,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>141</v>
       </c>
@@ -10663,7 +10719,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>137</v>
       </c>
@@ -10671,7 +10727,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>196</v>
       </c>
@@ -10679,7 +10735,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>210</v>
       </c>
@@ -10687,7 +10743,7 @@
         <v>993</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>388</v>
       </c>
@@ -10695,7 +10751,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>405</v>
       </c>
@@ -10703,7 +10759,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>467</v>
       </c>
@@ -10711,7 +10767,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>475</v>
       </c>
@@ -10719,7 +10775,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>510</v>
       </c>
@@ -10727,7 +10783,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>678</v>
       </c>
@@ -10735,7 +10791,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>730</v>
       </c>
@@ -10743,7 +10799,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>750</v>
       </c>
@@ -10751,7 +10807,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>765</v>
       </c>
@@ -10759,7 +10815,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>905</v>
       </c>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-develop\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D6F2122-6EFC-4C98-9904-0C82F363627D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAB845F-F13E-4CF2-A244-FC7B5E47D5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="31095" yWindow="2295" windowWidth="21600" windowHeight="12585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2340" yWindow="2340" windowWidth="43200" windowHeight="17085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1015">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="1017">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -2328,12 +2328,6 @@
     <t>Ann Impvmt in Bat Cap by Veh Type</t>
   </si>
   <si>
-    <t>ANVCV</t>
-  </si>
-  <si>
-    <t>Additional New Vehicles Calibration Variable</t>
-  </si>
-  <si>
     <t>AVCC</t>
   </si>
   <si>
@@ -2394,15 +2388,6 @@
     <t>BAU Cargo Distance Transported Relative to Start Year</t>
   </si>
   <si>
-    <t>BHNVFEAL</t>
-  </si>
-  <si>
-    <t>BAU Historical New Vehicle Fuel Economy After Lifetime</t>
-  </si>
-  <si>
-    <t>BNVFE, AVLo, PTFURfE, AVL</t>
-  </si>
-  <si>
     <t>BLP</t>
   </si>
   <si>
@@ -2421,12 +2406,6 @@
     <t>BAU Number of Gas Pumps</t>
   </si>
   <si>
-    <t>BNVFE</t>
-  </si>
-  <si>
-    <t>BAU New Vehicle Fuel Economy</t>
-  </si>
-  <si>
     <t>BPM</t>
   </si>
   <si>
@@ -2655,12 +2634,6 @@
     <t>You are modeling non-BAU subregional ZEV sales requirements (as opposed to a national ZEV sales standard)</t>
   </si>
   <si>
-    <t>SoCDTtiNTY</t>
-  </si>
-  <si>
-    <t>Share of Cargo Dist Transported that is New This Year</t>
-  </si>
-  <si>
     <t>SRPbVT</t>
   </si>
   <si>
@@ -2673,12 +2646,6 @@
     <t>Start Year Battery Cap by Veh Type</t>
   </si>
   <si>
-    <t>SYFAFE</t>
-  </si>
-  <si>
-    <t>Start Year Fleet Avg Fuel Economy</t>
-  </si>
-  <si>
     <t>SYNoEVC</t>
   </si>
   <si>
@@ -3067,13 +3034,52 @@
   </si>
   <si>
     <t>Grants or investment tax credits the region already gives new low-carbon clinker capacity, as a share of pathway capital cost by year; zero where none exist (US). Convert capture-equipment-only credits using the capture share of the CCS pathway's capital cost.</t>
+  </si>
+  <si>
+    <t>APDiVMwA</t>
+  </si>
+  <si>
+    <t>Annual Percent Decline in Vehicle Mileage with Age</t>
+  </si>
+  <si>
+    <t>NVFEbV</t>
+  </si>
+  <si>
+    <t>New Vehicle Fuel Economy by Vintage</t>
+  </si>
+  <si>
+    <t>SYVSbV</t>
+  </si>
+  <si>
+    <t>Start Year Vehicle Share by Vintage</t>
+  </si>
+  <si>
+    <t>VWLbV, VWSbV, VWSPbV</t>
+  </si>
+  <si>
+    <t>VWLbV</t>
+  </si>
+  <si>
+    <t>Vehicle Weibull Location by Vintage</t>
+  </si>
+  <si>
+    <t>VWSbV</t>
+  </si>
+  <si>
+    <t>Vehicle Weibull Scale by Vintage</t>
+  </si>
+  <si>
+    <t>VWSPbV</t>
+  </si>
+  <si>
+    <t>Vehicle Weibull Shape Parameter by Vintage</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3550,326 +3556,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1">
       <c r="A1" s="7" t="s">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3" t="s">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5" t="s">
+        <v>918</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6" t="s">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8" t="s">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1">
+      <c r="A9" t="s">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1">
+      <c r="A10" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1">
+      <c r="A11" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1">
+      <c r="A12" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1">
+      <c r="A13" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="15" spans="1:1">
+      <c r="A15" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
+    <row r="16" spans="1:1">
+      <c r="A16" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
+    <row r="17" spans="1:3">
+      <c r="A17" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3">
       <c r="A19" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B19" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3">
       <c r="B20" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3">
       <c r="B21" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3">
       <c r="B22" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3">
       <c r="B23" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="24" spans="1:3">
       <c r="B24" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3">
       <c r="B26" s="13" t="s">
         <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3">
       <c r="C27" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3">
       <c r="C28" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3">
       <c r="A30" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B30" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3">
       <c r="B31" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3">
       <c r="B32" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3">
       <c r="B33" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3">
       <c r="B34" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3">
       <c r="B35" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3">
       <c r="B36" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3">
       <c r="B37" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3">
       <c r="A39" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B39" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3">
       <c r="B40" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3">
       <c r="B41" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3">
       <c r="B42" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3">
       <c r="B43" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="44" spans="1:3">
       <c r="B44" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3">
       <c r="B45" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="46" spans="1:3">
       <c r="B46" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="48" spans="1:3">
       <c r="A48" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:2">
       <c r="B49" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
       <c r="B50" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
       <c r="B51" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
       <c r="B52" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
       <c r="B53" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
       <c r="B54" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
       <c r="B55" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
       <c r="A57" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B57" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="B58" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="B59" t="s">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="B60" t="s">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62" s="7" t="s">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64" t="s">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="65" spans="1:1">
+      <c r="A65" t="s">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="66" spans="1:1">
+      <c r="A66" t="s">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="67" spans="1:1">
+      <c r="A67" t="s">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="68" spans="1:1">
+      <c r="A68" t="s">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="69" spans="1:1">
+      <c r="A69" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B58" t="s">
+    <row r="70" spans="1:1">
+      <c r="A70" t="s">
         <v>973</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B59" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="B60" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A62" s="7" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A63" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A66" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A69" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A70" t="s">
-        <v>984</v>
       </c>
     </row>
   </sheetData>
@@ -3880,8 +3886,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G380"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:G381"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" style="2" customWidth="1"/>
@@ -3894,7 +3900,7 @@
     <col min="10" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -3917,7 +3923,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" ht="45" customHeight="1">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -3936,7 +3942,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" ht="30" customHeight="1">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -3955,7 +3961,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" ht="30" customHeight="1">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3974,7 +3980,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -3991,7 +3997,7 @@
       </c>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -4008,7 +4014,7 @@
       </c>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" ht="30" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -4027,7 +4033,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -4044,7 +4050,7 @@
       </c>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A9" s="17" t="s">
         <v>7</v>
       </c>
@@ -4061,7 +4067,7 @@
       </c>
       <c r="G9" s="28"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -4078,7 +4084,7 @@
       </c>
       <c r="G10" s="26"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -4095,7 +4101,7 @@
       </c>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -4112,7 +4118,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7">
       <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
@@ -4129,7 +4135,7 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:7" ht="30" customHeight="1">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -4148,7 +4154,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:7">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -4165,7 +4171,7 @@
       </c>
       <c r="G15" s="26"/>
     </row>
-    <row r="16" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:7" ht="45" customHeight="1">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -4184,7 +4190,7 @@
       </c>
       <c r="G16" s="26"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:7" ht="30" customHeight="1">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -4203,7 +4209,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:7">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -4220,7 +4226,7 @@
       </c>
       <c r="G18" s="26"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:7" ht="30" customHeight="1">
       <c r="A19" s="2" t="s">
         <v>32</v>
       </c>
@@ -4239,7 +4245,7 @@
       </c>
       <c r="G19" s="26"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:7">
       <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
@@ -4256,7 +4262,7 @@
       </c>
       <c r="G20" s="26"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:7" ht="30" customHeight="1">
       <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
@@ -4273,7 +4279,7 @@
       </c>
       <c r="G21" s="26"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:7">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
@@ -4290,7 +4296,7 @@
       </c>
       <c r="G22" s="26"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:7" ht="30" customHeight="1">
       <c r="A23" s="2" t="s">
         <v>32</v>
       </c>
@@ -4307,7 +4313,7 @@
       </c>
       <c r="G23" s="26"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -4324,7 +4330,7 @@
       </c>
       <c r="G24" s="26"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:7" ht="30" customHeight="1">
       <c r="A25" s="2" t="s">
         <v>32</v>
       </c>
@@ -4341,7 +4347,7 @@
       </c>
       <c r="G25" s="26"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:7">
       <c r="A26" s="2" t="s">
         <v>32</v>
       </c>
@@ -4358,7 +4364,7 @@
       </c>
       <c r="G26" s="26"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:7" ht="30" customHeight="1">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -4377,7 +4383,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:7" ht="30" customHeight="1">
       <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
@@ -4394,7 +4400,7 @@
       </c>
       <c r="G28" s="26"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:7" ht="30" customHeight="1">
       <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
@@ -4413,7 +4419,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:7" ht="30" customHeight="1">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -4430,7 +4436,7 @@
       </c>
       <c r="G30" s="26"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:7" ht="30" customHeight="1">
       <c r="A31" s="2" t="s">
         <v>32</v>
       </c>
@@ -4447,7 +4453,7 @@
       </c>
       <c r="G31" s="26"/>
     </row>
-    <row r="32" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:7" ht="45" customHeight="1">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -4466,7 +4472,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:7" ht="30" customHeight="1">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
@@ -4485,7 +4491,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:7" ht="30" customHeight="1">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -4502,7 +4508,7 @@
       </c>
       <c r="G34" s="24"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:7" ht="30" customHeight="1">
       <c r="A35" s="2" t="s">
         <v>32</v>
       </c>
@@ -4519,7 +4525,7 @@
       </c>
       <c r="G35" s="26"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:7">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -4536,7 +4542,7 @@
       </c>
       <c r="G36" s="26"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:7">
       <c r="A37" s="2" t="s">
         <v>32</v>
       </c>
@@ -4553,7 +4559,7 @@
       </c>
       <c r="G37" s="26"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:7">
       <c r="A38" s="2" t="s">
         <v>32</v>
       </c>
@@ -4570,7 +4576,7 @@
       </c>
       <c r="G38" s="26"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:7">
       <c r="A39" s="2" t="s">
         <v>32</v>
       </c>
@@ -4589,7 +4595,7 @@
       </c>
       <c r="G39" s="26"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A40" s="17" t="s">
         <v>32</v>
       </c>
@@ -4608,7 +4614,7 @@
       </c>
       <c r="G40" s="28"/>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:7">
       <c r="A41" s="2" t="s">
         <v>104</v>
       </c>
@@ -4625,7 +4631,7 @@
       </c>
       <c r="G41" s="26"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:7" ht="30" customHeight="1">
       <c r="A42" s="2" t="s">
         <v>104</v>
       </c>
@@ -4644,7 +4650,7 @@
       </c>
       <c r="G42" s="26"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7">
       <c r="A43" s="2" t="s">
         <v>104</v>
       </c>
@@ -4661,7 +4667,7 @@
       </c>
       <c r="G43" s="26"/>
     </row>
-    <row r="44" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" ht="120" customHeight="1">
       <c r="A44" s="2" t="s">
         <v>104</v>
       </c>
@@ -4680,7 +4686,7 @@
       </c>
       <c r="G44" s="26"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="30" customHeight="1">
       <c r="A45" s="2" t="s">
         <v>104</v>
       </c>
@@ -4699,7 +4705,7 @@
       </c>
       <c r="G45" s="26"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7">
       <c r="A46" s="2" t="s">
         <v>104</v>
       </c>
@@ -4716,7 +4722,7 @@
       </c>
       <c r="G46" s="26"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:7">
       <c r="A47" s="2" t="s">
         <v>104</v>
       </c>
@@ -4733,7 +4739,7 @@
       </c>
       <c r="G47" s="26"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:7">
       <c r="A48" s="2" t="s">
         <v>104</v>
       </c>
@@ -4750,7 +4756,7 @@
       </c>
       <c r="G48" s="26"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:7">
       <c r="A49" s="2" t="s">
         <v>104</v>
       </c>
@@ -4769,7 +4775,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:7" ht="30" customHeight="1">
       <c r="A50" s="2" t="s">
         <v>104</v>
       </c>
@@ -4786,7 +4792,7 @@
       </c>
       <c r="G50" s="26"/>
     </row>
-    <row r="51" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
       <c r="A51" s="17" t="s">
         <v>104</v>
       </c>
@@ -4803,7 +4809,7 @@
       </c>
       <c r="G51" s="26"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:7">
       <c r="A52" s="2" t="s">
         <v>131</v>
       </c>
@@ -4820,7 +4826,7 @@
       </c>
       <c r="G52" s="26"/>
     </row>
-    <row r="53" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
       <c r="A53" s="17" t="s">
         <v>131</v>
       </c>
@@ -4839,7 +4845,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
       <c r="A54" s="17" t="s">
         <v>137</v>
       </c>
@@ -4858,7 +4864,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:7" ht="60" customHeight="1">
       <c r="A55" s="2" t="s">
         <v>141</v>
       </c>
@@ -4877,7 +4883,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7">
       <c r="A56" s="2" t="s">
         <v>141</v>
       </c>
@@ -4896,7 +4902,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:7" ht="60" customHeight="1">
       <c r="A57" s="2" t="s">
         <v>141</v>
       </c>
@@ -4915,7 +4921,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:7" ht="60" customHeight="1">
       <c r="A58" s="2" t="s">
         <v>141</v>
       </c>
@@ -4934,7 +4940,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:7" ht="45" customHeight="1">
       <c r="A59" s="2" t="s">
         <v>141</v>
       </c>
@@ -4953,7 +4959,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:7" ht="60" customHeight="1">
       <c r="A60" s="2" t="s">
         <v>141</v>
       </c>
@@ -4972,7 +4978,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:7" ht="60" customHeight="1">
       <c r="A61" s="2" t="s">
         <v>141</v>
       </c>
@@ -4991,7 +4997,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:7" ht="60" customHeight="1">
       <c r="A62" s="2" t="s">
         <v>141</v>
       </c>
@@ -5010,7 +5016,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:7" ht="45" customHeight="1">
       <c r="A63" s="2" t="s">
         <v>141</v>
       </c>
@@ -5029,7 +5035,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:7" ht="30" customHeight="1">
       <c r="A64" s="2" t="s">
         <v>141</v>
       </c>
@@ -5048,7 +5054,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:7" ht="30" customHeight="1">
       <c r="A65" s="2" t="s">
         <v>141</v>
       </c>
@@ -5067,7 +5073,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:7" ht="60" customHeight="1">
       <c r="A66" s="2" t="s">
         <v>141</v>
       </c>
@@ -5086,7 +5092,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:7" ht="30" customHeight="1">
       <c r="A67" s="2" t="s">
         <v>141</v>
       </c>
@@ -5103,7 +5109,7 @@
       </c>
       <c r="G67" s="26"/>
     </row>
-    <row r="68" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:7" ht="45" customHeight="1">
       <c r="A68" s="2" t="s">
         <v>141</v>
       </c>
@@ -5122,7 +5128,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:7" ht="90" customHeight="1">
       <c r="A69" s="2" t="s">
         <v>141</v>
       </c>
@@ -5143,7 +5149,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:7" ht="45" customHeight="1">
       <c r="A70" s="2" t="s">
         <v>141</v>
       </c>
@@ -5164,7 +5170,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:7">
       <c r="A71" s="2" t="s">
         <v>141</v>
       </c>
@@ -5181,7 +5187,7 @@
       </c>
       <c r="G71" s="26"/>
     </row>
-    <row r="72" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A72" s="17" t="s">
         <v>141</v>
       </c>
@@ -5198,7 +5204,7 @@
       </c>
       <c r="G72" s="28"/>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:7">
       <c r="A73" s="2" t="s">
         <v>196</v>
       </c>
@@ -5215,7 +5221,7 @@
       </c>
       <c r="G73" s="26"/>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:7">
       <c r="A74" s="2" t="s">
         <v>196</v>
       </c>
@@ -5232,7 +5238,7 @@
       </c>
       <c r="G74" s="26"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:7">
       <c r="A75" s="2" t="s">
         <v>196</v>
       </c>
@@ -5249,7 +5255,7 @@
       </c>
       <c r="G75" s="26"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:7">
       <c r="A76" s="2" t="s">
         <v>196</v>
       </c>
@@ -5266,7 +5272,7 @@
       </c>
       <c r="G76" s="26"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:7">
       <c r="A77" s="2" t="s">
         <v>196</v>
       </c>
@@ -5283,7 +5289,7 @@
       </c>
       <c r="G77" s="26"/>
     </row>
-    <row r="78" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
       <c r="A78" s="17" t="s">
         <v>196</v>
       </c>
@@ -5302,7 +5308,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:7">
       <c r="A79" s="2" t="s">
         <v>210</v>
       </c>
@@ -5319,7 +5325,7 @@
       </c>
       <c r="G79" s="26"/>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:7">
       <c r="A80" s="2" t="s">
         <v>210</v>
       </c>
@@ -5336,7 +5342,7 @@
       </c>
       <c r="G80" s="26"/>
     </row>
-    <row r="81" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" ht="45" customHeight="1">
       <c r="A81" s="2" t="s">
         <v>210</v>
       </c>
@@ -5355,7 +5361,7 @@
       </c>
       <c r="G81" s="26"/>
     </row>
-    <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="30" customHeight="1">
       <c r="A82" s="2" t="s">
         <v>210</v>
       </c>
@@ -5374,7 +5380,7 @@
       </c>
       <c r="G82" s="26"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7">
       <c r="A83" s="2" t="s">
         <v>210</v>
       </c>
@@ -5391,7 +5397,7 @@
       </c>
       <c r="G83" s="26"/>
     </row>
-    <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" ht="30" customHeight="1">
       <c r="A84" s="2" t="s">
         <v>210</v>
       </c>
@@ -5408,7 +5414,7 @@
       </c>
       <c r="G84" s="26"/>
     </row>
-    <row r="85" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="45" customHeight="1">
       <c r="A85" s="2" t="s">
         <v>210</v>
       </c>
@@ -5427,7 +5433,7 @@
       </c>
       <c r="G85" s="26"/>
     </row>
-    <row r="86" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:7" ht="45" customHeight="1">
       <c r="A86" s="2" t="s">
         <v>210</v>
       </c>
@@ -5446,7 +5452,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:7">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
@@ -5465,7 +5471,7 @@
       </c>
       <c r="G87" s="26"/>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:7">
       <c r="A88" s="2" t="s">
         <v>210</v>
       </c>
@@ -5482,7 +5488,7 @@
       </c>
       <c r="G88" s="26"/>
     </row>
-    <row r="89" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" ht="75" customHeight="1">
       <c r="A89" s="2" t="s">
         <v>210</v>
       </c>
@@ -5501,7 +5507,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:7" ht="75" customHeight="1">
       <c r="A90" s="2" t="s">
         <v>210</v>
       </c>
@@ -5520,7 +5526,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:7">
       <c r="A91" s="2" t="s">
         <v>210</v>
       </c>
@@ -5537,7 +5543,7 @@
       </c>
       <c r="G91" s="26"/>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:7">
       <c r="A92" s="2" t="s">
         <v>210</v>
       </c>
@@ -5554,7 +5560,7 @@
       </c>
       <c r="G92" s="26"/>
     </row>
-    <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" ht="30" customHeight="1">
       <c r="A93" s="2" t="s">
         <v>210</v>
       </c>
@@ -5571,7 +5577,7 @@
       </c>
       <c r="G93" s="26"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7">
       <c r="A94" s="2" t="s">
         <v>210</v>
       </c>
@@ -5592,7 +5598,7 @@
       </c>
       <c r="G94" s="26"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:7">
       <c r="A95" s="2" t="s">
         <v>210</v>
       </c>
@@ -5609,7 +5615,7 @@
       </c>
       <c r="G95" s="26"/>
     </row>
-    <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" ht="30" customHeight="1">
       <c r="A96" s="2" t="s">
         <v>210</v>
       </c>
@@ -5626,7 +5632,7 @@
       </c>
       <c r="G96" s="26"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7">
       <c r="A97" s="2" t="s">
         <v>210</v>
       </c>
@@ -5643,7 +5649,7 @@
       </c>
       <c r="G97" s="26"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7">
       <c r="A98" s="2" t="s">
         <v>210</v>
       </c>
@@ -5660,7 +5666,7 @@
       </c>
       <c r="G98" s="26"/>
     </row>
-    <row r="99" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" ht="75" customHeight="1">
       <c r="A99" s="2" t="s">
         <v>210</v>
       </c>
@@ -5679,7 +5685,7 @@
       </c>
       <c r="G99" s="26"/>
     </row>
-    <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="30" customHeight="1">
       <c r="A100" s="2" t="s">
         <v>210</v>
       </c>
@@ -5696,7 +5702,7 @@
       </c>
       <c r="G100" s="26"/>
     </row>
-    <row r="101" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="75" customHeight="1">
       <c r="A101" s="2" t="s">
         <v>210</v>
       </c>
@@ -5715,7 +5721,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7">
       <c r="A102" s="2" t="s">
         <v>210</v>
       </c>
@@ -5732,7 +5738,7 @@
       </c>
       <c r="G102" s="26"/>
     </row>
-    <row r="103" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" ht="90" customHeight="1">
       <c r="A103" s="2" t="s">
         <v>210</v>
       </c>
@@ -5751,7 +5757,7 @@
       </c>
       <c r="G103" s="26"/>
     </row>
-    <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="30" customHeight="1">
       <c r="A104" s="2" t="s">
         <v>210</v>
       </c>
@@ -5768,7 +5774,7 @@
       </c>
       <c r="G104" s="26"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7">
       <c r="A105" s="2" t="s">
         <v>210</v>
       </c>
@@ -5785,7 +5791,7 @@
       </c>
       <c r="G105" s="26"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7">
       <c r="A106" s="2" t="s">
         <v>210</v>
       </c>
@@ -5802,7 +5808,7 @@
       </c>
       <c r="G106" s="26"/>
     </row>
-    <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" ht="30" customHeight="1">
       <c r="A107" s="2" t="s">
         <v>210</v>
       </c>
@@ -5821,7 +5827,7 @@
       </c>
       <c r="G107" s="26"/>
     </row>
-    <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" ht="30" customHeight="1">
       <c r="A108" s="2" t="s">
         <v>210</v>
       </c>
@@ -5840,7 +5846,7 @@
       </c>
       <c r="G108" s="26"/>
     </row>
-    <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" ht="30" customHeight="1">
       <c r="A109" s="2" t="s">
         <v>210</v>
       </c>
@@ -5859,7 +5865,7 @@
       </c>
       <c r="G109" s="26"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7">
       <c r="A110" s="2" t="s">
         <v>210</v>
       </c>
@@ -5878,7 +5884,7 @@
       </c>
       <c r="G110" s="26"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7">
       <c r="A111" s="2" t="s">
         <v>210</v>
       </c>
@@ -5895,7 +5901,7 @@
       </c>
       <c r="G111" s="26"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7">
       <c r="A112" s="2" t="s">
         <v>210</v>
       </c>
@@ -5912,7 +5918,7 @@
       </c>
       <c r="G112" s="26"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:7">
       <c r="A113" s="2" t="s">
         <v>210</v>
       </c>
@@ -5929,7 +5935,7 @@
       </c>
       <c r="G113" s="26"/>
     </row>
-    <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" ht="30" customHeight="1">
       <c r="A114" s="2" t="s">
         <v>210</v>
       </c>
@@ -5948,7 +5954,7 @@
       </c>
       <c r="G114" s="26"/>
     </row>
-    <row r="115" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="60" customHeight="1">
       <c r="A115" s="2" t="s">
         <v>210</v>
       </c>
@@ -5967,7 +5973,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:7">
       <c r="A116" s="2" t="s">
         <v>210</v>
       </c>
@@ -5984,7 +5990,7 @@
       </c>
       <c r="G116" s="26"/>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:7">
       <c r="A117" s="2" t="s">
         <v>210</v>
       </c>
@@ -6003,7 +6009,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:7" ht="30" customHeight="1">
       <c r="A118" s="2" t="s">
         <v>210</v>
       </c>
@@ -6020,7 +6026,7 @@
       </c>
       <c r="G118" s="26"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:7">
       <c r="A119" s="2" t="s">
         <v>210</v>
       </c>
@@ -6037,7 +6043,7 @@
       </c>
       <c r="G119" s="26"/>
     </row>
-    <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" ht="30" customHeight="1">
       <c r="A120" s="2" t="s">
         <v>210</v>
       </c>
@@ -6054,7 +6060,7 @@
       </c>
       <c r="G120" s="26"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7">
       <c r="A121" s="2" t="s">
         <v>210</v>
       </c>
@@ -6071,7 +6077,7 @@
       </c>
       <c r="G121" s="26"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:7">
       <c r="A122" s="2" t="s">
         <v>210</v>
       </c>
@@ -6088,7 +6094,7 @@
       </c>
       <c r="G122" s="26"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:7">
       <c r="A123" s="2" t="s">
         <v>210</v>
       </c>
@@ -6105,7 +6111,7 @@
       </c>
       <c r="G123" s="26"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:7">
       <c r="A124" s="2" t="s">
         <v>210</v>
       </c>
@@ -6122,7 +6128,7 @@
       </c>
       <c r="G124" s="26"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:7">
       <c r="A125" s="2" t="s">
         <v>210</v>
       </c>
@@ -6139,7 +6145,7 @@
       </c>
       <c r="G125" s="26"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:7">
       <c r="A126" s="2" t="s">
         <v>210</v>
       </c>
@@ -6156,7 +6162,7 @@
       </c>
       <c r="G126" s="26"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:7">
       <c r="A127" s="2" t="s">
         <v>210</v>
       </c>
@@ -6173,7 +6179,7 @@
       </c>
       <c r="G127" s="26"/>
     </row>
-    <row r="128" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" ht="60" customHeight="1">
       <c r="A128" s="2" t="s">
         <v>210</v>
       </c>
@@ -6192,7 +6198,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:7" ht="60" customHeight="1">
       <c r="A129" s="2" t="s">
         <v>210</v>
       </c>
@@ -6211,7 +6217,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:7" ht="30" customHeight="1">
       <c r="A130" s="2" t="s">
         <v>210</v>
       </c>
@@ -6230,7 +6236,7 @@
       </c>
       <c r="G130" s="26"/>
     </row>
-    <row r="131" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:7" ht="45" customHeight="1">
       <c r="A131" s="2" t="s">
         <v>210</v>
       </c>
@@ -6249,7 +6255,7 @@
       </c>
       <c r="G131" s="26"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7">
       <c r="A132" s="2" t="s">
         <v>210</v>
       </c>
@@ -6266,7 +6272,7 @@
       </c>
       <c r="G132" s="26"/>
     </row>
-    <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" ht="30" customHeight="1">
       <c r="A133" s="2" t="s">
         <v>210</v>
       </c>
@@ -6283,7 +6289,7 @@
       </c>
       <c r="G133" s="26"/>
     </row>
-    <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:7" ht="30" customHeight="1">
       <c r="A134" s="2" t="s">
         <v>210</v>
       </c>
@@ -6302,7 +6308,7 @@
       </c>
       <c r="G134" s="26"/>
     </row>
-    <row r="135" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="45" customHeight="1">
       <c r="A135" s="2" t="s">
         <v>210</v>
       </c>
@@ -6321,7 +6327,7 @@
       </c>
       <c r="G135" s="26"/>
     </row>
-    <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="30" customHeight="1">
       <c r="A136" s="2" t="s">
         <v>210</v>
       </c>
@@ -6342,7 +6348,7 @@
       </c>
       <c r="G136" s="26"/>
     </row>
-    <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:7" ht="30" customHeight="1">
       <c r="A137" s="2" t="s">
         <v>210</v>
       </c>
@@ -6359,7 +6365,7 @@
       </c>
       <c r="G137" s="26"/>
     </row>
-    <row r="138" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="45" customHeight="1">
       <c r="A138" s="2" t="s">
         <v>210</v>
       </c>
@@ -6378,7 +6384,7 @@
       </c>
       <c r="G138" s="26"/>
     </row>
-    <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="30" customHeight="1">
       <c r="A139" s="2" t="s">
         <v>210</v>
       </c>
@@ -6395,7 +6401,7 @@
       </c>
       <c r="G139" s="26"/>
     </row>
-    <row r="140" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:7" ht="30" customHeight="1">
       <c r="A140" s="2" t="s">
         <v>210</v>
       </c>
@@ -6412,7 +6418,7 @@
       </c>
       <c r="G140" s="26"/>
     </row>
-    <row r="141" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:7" ht="30" customHeight="1">
       <c r="A141" s="2" t="s">
         <v>210</v>
       </c>
@@ -6429,7 +6435,7 @@
       </c>
       <c r="G141" s="26"/>
     </row>
-    <row r="142" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:7" ht="30" customHeight="1">
       <c r="A142" s="2" t="s">
         <v>210</v>
       </c>
@@ -6446,7 +6452,7 @@
       </c>
       <c r="G142" s="26"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7">
       <c r="A143" s="2" t="s">
         <v>210</v>
       </c>
@@ -6463,7 +6469,7 @@
       </c>
       <c r="G143" s="26"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:7">
       <c r="A144" s="2" t="s">
         <v>210</v>
       </c>
@@ -6482,7 +6488,7 @@
       </c>
       <c r="G144" s="26"/>
     </row>
-    <row r="145" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" ht="30" customHeight="1">
       <c r="A145" s="2" t="s">
         <v>210</v>
       </c>
@@ -6501,7 +6507,7 @@
       </c>
       <c r="G145" s="26"/>
     </row>
-    <row r="146" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:7" ht="30" customHeight="1">
       <c r="A146" s="2" t="s">
         <v>210</v>
       </c>
@@ -6518,7 +6524,7 @@
       </c>
       <c r="G146" s="26"/>
     </row>
-    <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:7" ht="30" customHeight="1">
       <c r="A147" t="s">
         <v>210</v>
       </c>
@@ -6537,7 +6543,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:7" ht="30">
       <c r="A148" s="2" t="s">
         <v>210</v>
       </c>
@@ -6554,7 +6560,7 @@
       </c>
       <c r="G148" s="26"/>
     </row>
-    <row r="149" spans="1:7" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:7" ht="60.75" customHeight="1" thickBot="1">
       <c r="A149" s="2" t="s">
         <v>210</v>
       </c>
@@ -6571,7 +6577,7 @@
       </c>
       <c r="G149" s="26"/>
     </row>
-    <row r="150" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:7" ht="30" customHeight="1">
       <c r="A150" s="17" t="s">
         <v>210</v>
       </c>
@@ -6592,7 +6598,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:7" ht="30" customHeight="1">
       <c r="A151" s="2" t="s">
         <v>388</v>
       </c>
@@ -6611,7 +6617,7 @@
       </c>
       <c r="G151" s="26"/>
     </row>
-    <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:7" ht="30" customHeight="1">
       <c r="A152" s="2" t="s">
         <v>388</v>
       </c>
@@ -6630,7 +6636,7 @@
       </c>
       <c r="G152" s="26"/>
     </row>
-    <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:7" ht="30" customHeight="1">
       <c r="A153" s="2" t="s">
         <v>388</v>
       </c>
@@ -6647,7 +6653,7 @@
       </c>
       <c r="G153" s="26"/>
     </row>
-    <row r="154" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="30">
       <c r="A154" s="2" t="s">
         <v>388</v>
       </c>
@@ -6664,7 +6670,7 @@
       </c>
       <c r="G154" s="26"/>
     </row>
-    <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="30" customHeight="1">
       <c r="A155" s="2" t="s">
         <v>388</v>
       </c>
@@ -6681,7 +6687,7 @@
       </c>
       <c r="G155" s="26"/>
     </row>
-    <row r="156" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
       <c r="A156" s="2" t="s">
         <v>388</v>
       </c>
@@ -6698,7 +6704,7 @@
       </c>
       <c r="G156" s="26"/>
     </row>
-    <row r="157" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:7" ht="30">
       <c r="A157" s="17" t="s">
         <v>388</v>
       </c>
@@ -6715,7 +6721,7 @@
       </c>
       <c r="G157" s="28"/>
     </row>
-    <row r="158" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:7" ht="30" customHeight="1">
       <c r="A158" s="2" t="s">
         <v>405</v>
       </c>
@@ -6732,7 +6738,7 @@
       </c>
       <c r="G158" s="26"/>
     </row>
-    <row r="159" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:7" ht="30" customHeight="1">
       <c r="A159" s="2" t="s">
         <v>405</v>
       </c>
@@ -6749,7 +6755,7 @@
       </c>
       <c r="G159" s="26"/>
     </row>
-    <row r="160" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:7" ht="30" customHeight="1">
       <c r="A160" s="2" t="s">
         <v>405</v>
       </c>
@@ -6766,7 +6772,7 @@
       </c>
       <c r="G160" s="26"/>
     </row>
-    <row r="161" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:7" ht="30" customHeight="1">
       <c r="A161" s="2" t="s">
         <v>405</v>
       </c>
@@ -6783,7 +6789,7 @@
       </c>
       <c r="G161" s="26"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7">
       <c r="A162" s="2" t="s">
         <v>405</v>
       </c>
@@ -6802,7 +6808,7 @@
       </c>
       <c r="G162" s="26"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:7">
       <c r="A163" s="2" t="s">
         <v>405</v>
       </c>
@@ -6819,7 +6825,7 @@
       </c>
       <c r="G163" s="26"/>
     </row>
-    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" ht="45" customHeight="1">
       <c r="A164" s="2" t="s">
         <v>405</v>
       </c>
@@ -6836,7 +6842,7 @@
       </c>
       <c r="G164" s="26"/>
     </row>
-    <row r="165" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="45">
       <c r="A165" s="2" t="s">
         <v>405</v>
       </c>
@@ -6855,7 +6861,7 @@
       </c>
       <c r="G165" s="26"/>
     </row>
-    <row r="166" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="30" customHeight="1">
       <c r="A166" s="2" t="s">
         <v>405</v>
       </c>
@@ -6872,7 +6878,7 @@
       </c>
       <c r="G166" s="26"/>
     </row>
-    <row r="167" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="30">
       <c r="A167" s="2" t="s">
         <v>405</v>
       </c>
@@ -6889,7 +6895,7 @@
       </c>
       <c r="G167" s="26"/>
     </row>
-    <row r="168" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="30" customHeight="1">
       <c r="A168" s="2" t="s">
         <v>405</v>
       </c>
@@ -6906,7 +6912,7 @@
       </c>
       <c r="G168" s="26"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7">
       <c r="A169" s="2" t="s">
         <v>405</v>
       </c>
@@ -6925,7 +6931,7 @@
       </c>
       <c r="G169" s="26"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:7">
       <c r="A170" s="2" t="s">
         <v>405</v>
       </c>
@@ -6942,7 +6948,7 @@
       </c>
       <c r="G170" s="26"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:7">
       <c r="A171" s="2" t="s">
         <v>405</v>
       </c>
@@ -6959,7 +6965,7 @@
       </c>
       <c r="G171" s="26"/>
     </row>
-    <row r="172" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" ht="30" customHeight="1">
       <c r="A172" s="2" t="s">
         <v>405</v>
       </c>
@@ -6976,7 +6982,7 @@
       </c>
       <c r="G172" s="26"/>
     </row>
-    <row r="173" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="30">
       <c r="A173" s="2" t="s">
         <v>405</v>
       </c>
@@ -6995,7 +7001,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:7" ht="30" customHeight="1">
       <c r="A174" s="2" t="s">
         <v>405</v>
       </c>
@@ -7012,7 +7018,7 @@
       </c>
       <c r="G174" s="26"/>
     </row>
-    <row r="175" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:7" ht="30" customHeight="1">
       <c r="A175" s="2" t="s">
         <v>405</v>
       </c>
@@ -7031,7 +7037,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:7" ht="30" customHeight="1">
       <c r="A176" s="2" t="s">
         <v>405</v>
       </c>
@@ -7050,7 +7056,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" ht="45" customHeight="1">
       <c r="A177" s="2" t="s">
         <v>405</v>
       </c>
@@ -7069,7 +7075,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" ht="60" customHeight="1">
       <c r="A178" s="2" t="s">
         <v>405</v>
       </c>
@@ -7088,7 +7094,7 @@
       </c>
       <c r="G178" s="26"/>
     </row>
-    <row r="179" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" ht="45" customHeight="1">
       <c r="A179" s="2" t="s">
         <v>405</v>
       </c>
@@ -7107,7 +7113,7 @@
       </c>
       <c r="G179" s="26"/>
     </row>
-    <row r="180" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="30" customHeight="1">
       <c r="A180" s="2" t="s">
         <v>405</v>
       </c>
@@ -7124,7 +7130,7 @@
       </c>
       <c r="G180" s="26"/>
     </row>
-    <row r="181" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1">
       <c r="A181" s="2" t="s">
         <v>405</v>
       </c>
@@ -7143,7 +7149,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" ht="30" customHeight="1">
       <c r="A182" s="17" t="s">
         <v>405</v>
       </c>
@@ -7162,7 +7168,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="183" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
       <c r="A183" s="2" t="s">
         <v>467</v>
       </c>
@@ -7181,7 +7187,7 @@
       </c>
       <c r="G183" s="26"/>
     </row>
-    <row r="184" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" ht="30" customHeight="1">
       <c r="A184" s="17" t="s">
         <v>471</v>
       </c>
@@ -7200,7 +7206,7 @@
       </c>
       <c r="G184" s="26"/>
     </row>
-    <row r="185" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" ht="30" customHeight="1">
       <c r="A185" s="2" t="s">
         <v>475</v>
       </c>
@@ -7217,7 +7223,7 @@
       </c>
       <c r="G185" s="26"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7">
       <c r="A186" s="2" t="s">
         <v>475</v>
       </c>
@@ -7234,7 +7240,7 @@
       </c>
       <c r="G186" s="26"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7">
       <c r="A187" s="2" t="s">
         <v>475</v>
       </c>
@@ -7251,7 +7257,7 @@
       </c>
       <c r="G187" s="26"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7">
       <c r="A188" s="2" t="s">
         <v>475</v>
       </c>
@@ -7268,7 +7274,7 @@
       </c>
       <c r="G188" s="26"/>
     </row>
-    <row r="189" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" ht="30" customHeight="1">
       <c r="A189" s="2" t="s">
         <v>475</v>
       </c>
@@ -7285,7 +7291,7 @@
       </c>
       <c r="G189" s="26"/>
     </row>
-    <row r="190" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" ht="30">
       <c r="A190" s="2" t="s">
         <v>475</v>
       </c>
@@ -7304,7 +7310,7 @@
       </c>
       <c r="G190" s="26"/>
     </row>
-    <row r="191" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" ht="30" customHeight="1">
       <c r="A191" s="2" t="s">
         <v>475</v>
       </c>
@@ -7321,7 +7327,7 @@
       </c>
       <c r="G191" s="26"/>
     </row>
-    <row r="192" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="30">
       <c r="A192" s="2" t="s">
         <v>475</v>
       </c>
@@ -7338,7 +7344,7 @@
       </c>
       <c r="G192" s="26"/>
     </row>
-    <row r="193" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" ht="30" customHeight="1">
       <c r="A193" s="2" t="s">
         <v>475</v>
       </c>
@@ -7355,7 +7361,7 @@
       </c>
       <c r="G193" s="26"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7">
       <c r="A194" s="2" t="s">
         <v>475</v>
       </c>
@@ -7374,7 +7380,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:7" ht="30" customHeight="1">
       <c r="A195" s="2" t="s">
         <v>475</v>
       </c>
@@ -7391,7 +7397,7 @@
       </c>
       <c r="G195" s="26"/>
     </row>
-    <row r="196" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:7" ht="30" customHeight="1">
       <c r="A196" s="2" t="s">
         <v>475</v>
       </c>
@@ -7408,7 +7414,7 @@
       </c>
       <c r="G196" s="26"/>
     </row>
-    <row r="197" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:7" ht="30" customHeight="1">
       <c r="A197" s="2" t="s">
         <v>475</v>
       </c>
@@ -7425,7 +7431,7 @@
       </c>
       <c r="G197" s="26"/>
     </row>
-    <row r="198" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:7" ht="30" customHeight="1">
       <c r="A198" s="2" t="s">
         <v>475</v>
       </c>
@@ -7442,7 +7448,7 @@
       </c>
       <c r="G198" s="26"/>
     </row>
-    <row r="199" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
       <c r="A199" s="2" t="s">
         <v>475</v>
       </c>
@@ -7459,7 +7465,7 @@
       </c>
       <c r="G199" s="26"/>
     </row>
-    <row r="200" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:7" ht="30">
       <c r="A200" s="17" t="s">
         <v>475</v>
       </c>
@@ -7476,7 +7482,7 @@
       </c>
       <c r="G200" s="26"/>
     </row>
-    <row r="201" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:7" ht="30" customHeight="1">
       <c r="A201" t="s">
         <v>510</v>
       </c>
@@ -7493,7 +7499,7 @@
       </c>
       <c r="G201" s="26"/>
     </row>
-    <row r="202" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:7">
       <c r="A202" s="2" t="s">
         <v>510</v>
       </c>
@@ -7510,7 +7516,7 @@
       </c>
       <c r="G202" s="26"/>
     </row>
-    <row r="203" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:7" ht="45" customHeight="1">
       <c r="A203" s="2" t="s">
         <v>510</v>
       </c>
@@ -7529,7 +7535,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7">
       <c r="A204" s="2" t="s">
         <v>510</v>
       </c>
@@ -7548,15 +7554,15 @@
       </c>
       <c r="G204" s="24"/>
     </row>
-    <row r="205" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:7" ht="30" customHeight="1">
       <c r="A205" t="s">
         <v>510</v>
       </c>
       <c r="B205" t="s">
-        <v>1012</v>
+        <v>1001</v>
       </c>
       <c r="C205" t="s">
-        <v>1013</v>
+        <v>1002</v>
       </c>
       <c r="D205" s="7"/>
       <c r="E205" s="7"/>
@@ -7564,10 +7570,10 @@
         <v>20</v>
       </c>
       <c r="G205" s="26" t="s">
-        <v>1014</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" ht="30" customHeight="1">
       <c r="A206" t="s">
         <v>510</v>
       </c>
@@ -7584,7 +7590,7 @@
       </c>
       <c r="G206" s="26"/>
     </row>
-    <row r="207" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:7" ht="45">
       <c r="A207" s="2" t="s">
         <v>510</v>
       </c>
@@ -7603,7 +7609,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="208" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:7" ht="30" customHeight="1">
       <c r="A208" s="2" t="s">
         <v>510</v>
       </c>
@@ -7622,7 +7628,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" ht="30" customHeight="1">
       <c r="A209" s="2" t="s">
         <v>510</v>
       </c>
@@ -7639,7 +7645,7 @@
       </c>
       <c r="G209" s="26"/>
     </row>
-    <row r="210" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" ht="30" customHeight="1">
       <c r="A210" s="2" t="s">
         <v>510</v>
       </c>
@@ -7656,7 +7662,7 @@
       </c>
       <c r="G210" s="26"/>
     </row>
-    <row r="211" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" ht="30" customHeight="1">
       <c r="A211" s="2" t="s">
         <v>510</v>
       </c>
@@ -7675,7 +7681,7 @@
       </c>
       <c r="G211" s="26"/>
     </row>
-    <row r="212" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" ht="30" customHeight="1">
       <c r="A212" s="2" t="s">
         <v>510</v>
       </c>
@@ -7692,7 +7698,7 @@
       </c>
       <c r="G212" s="26"/>
     </row>
-    <row r="213" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" ht="30" customHeight="1">
       <c r="A213" s="2" t="s">
         <v>510</v>
       </c>
@@ -7711,7 +7717,7 @@
       </c>
       <c r="G213" s="26"/>
     </row>
-    <row r="214" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" ht="30" customHeight="1">
       <c r="A214" s="2" t="s">
         <v>510</v>
       </c>
@@ -7730,7 +7736,7 @@
       </c>
       <c r="G214" s="26"/>
     </row>
-    <row r="215" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" ht="30" customHeight="1">
       <c r="A215" t="s">
         <v>510</v>
       </c>
@@ -7747,7 +7753,7 @@
       </c>
       <c r="G215" s="26"/>
     </row>
-    <row r="216" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" ht="30" customHeight="1">
       <c r="A216" t="s">
         <v>510</v>
       </c>
@@ -7766,7 +7772,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7">
       <c r="A217" t="s">
         <v>510</v>
       </c>
@@ -7783,15 +7789,15 @@
       </c>
       <c r="G217" s="26"/>
     </row>
-    <row r="218" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" ht="30" customHeight="1">
       <c r="A218" t="s">
         <v>510</v>
       </c>
       <c r="B218" t="s">
-        <v>1009</v>
+        <v>998</v>
       </c>
       <c r="C218" t="s">
-        <v>1010</v>
+        <v>999</v>
       </c>
       <c r="D218" s="7"/>
       <c r="E218" s="7"/>
@@ -7799,10 +7805,10 @@
         <v>29</v>
       </c>
       <c r="G218" s="26" t="s">
-        <v>1011</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="30" customHeight="1">
       <c r="A219" t="s">
         <v>510</v>
       </c>
@@ -7821,7 +7827,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:7">
       <c r="A220" t="s">
         <v>510</v>
       </c>
@@ -7838,18 +7844,18 @@
       </c>
       <c r="G220" s="26"/>
     </row>
-    <row r="221" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:7" ht="45" customHeight="1">
       <c r="A221" t="s">
         <v>510</v>
       </c>
       <c r="B221" t="s">
-        <v>1004</v>
+        <v>993</v>
       </c>
       <c r="C221" t="s">
-        <v>1005</v>
+        <v>994</v>
       </c>
       <c r="D221" s="7" t="s">
-        <v>1006</v>
+        <v>995</v>
       </c>
       <c r="E221" s="7"/>
       <c r="F221" t="s">
@@ -7857,7 +7863,7 @@
       </c>
       <c r="G221" s="26"/>
     </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:7">
       <c r="A222" t="s">
         <v>510</v>
       </c>
@@ -7874,7 +7880,7 @@
       </c>
       <c r="G222" s="26"/>
     </row>
-    <row r="223" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:7" ht="45" customHeight="1">
       <c r="A223" t="s">
         <v>510</v>
       </c>
@@ -7893,7 +7899,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:7">
       <c r="A224" t="s">
         <v>510</v>
       </c>
@@ -7912,7 +7918,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="225" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:7" ht="45" customHeight="1">
       <c r="A225" t="s">
         <v>510</v>
       </c>
@@ -7933,7 +7939,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="226" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:7" ht="30" customHeight="1">
       <c r="A226" s="2" t="s">
         <v>510</v>
       </c>
@@ -7950,7 +7956,7 @@
       </c>
       <c r="G226" s="26"/>
     </row>
-    <row r="227" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" ht="30" customHeight="1">
       <c r="A227" s="2" t="s">
         <v>510</v>
       </c>
@@ -7965,22 +7971,22 @@
       <c r="F227" s="4"/>
       <c r="G227" s="26"/>
     </row>
-    <row r="228" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" ht="30" customHeight="1">
       <c r="A228" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B228" s="2" t="s">
-        <v>1007</v>
+        <v>996</v>
       </c>
       <c r="C228" s="2" t="s">
-        <v>1008</v>
+        <v>997</v>
       </c>
       <c r="D228" s="7"/>
       <c r="E228" s="7"/>
       <c r="F228" s="4"/>
       <c r="G228" s="26"/>
     </row>
-    <row r="229" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:7" ht="30" customHeight="1">
       <c r="A229" s="2" t="s">
         <v>510</v>
       </c>
@@ -7999,7 +8005,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:7" ht="30" customHeight="1">
       <c r="A230" s="2" t="s">
         <v>510</v>
       </c>
@@ -8018,7 +8024,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:7" ht="30" customHeight="1">
       <c r="A231" s="2" t="s">
         <v>510</v>
       </c>
@@ -8035,7 +8041,7 @@
       </c>
       <c r="G231" s="26"/>
     </row>
-    <row r="232" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:7" ht="30" customHeight="1">
       <c r="A232" s="2" t="s">
         <v>510</v>
       </c>
@@ -8052,7 +8058,7 @@
       </c>
       <c r="G232" s="26"/>
     </row>
-    <row r="233" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:7" ht="30" customHeight="1">
       <c r="A233" s="2" t="s">
         <v>510</v>
       </c>
@@ -8069,7 +8075,7 @@
       </c>
       <c r="G233" s="26"/>
     </row>
-    <row r="234" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:7" ht="30" customHeight="1">
       <c r="A234" s="2" t="s">
         <v>510</v>
       </c>
@@ -8088,7 +8094,7 @@
         <v>587</v>
       </c>
     </row>
-    <row r="235" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:7" ht="30" customHeight="1">
       <c r="A235" s="2" t="s">
         <v>510</v>
       </c>
@@ -8105,7 +8111,7 @@
       </c>
       <c r="G235" s="26"/>
     </row>
-    <row r="236" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:7" ht="30" customHeight="1">
       <c r="A236" s="2" t="s">
         <v>510</v>
       </c>
@@ -8122,7 +8128,7 @@
       </c>
       <c r="G236" s="26"/>
     </row>
-    <row r="237" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:7" ht="30" customHeight="1">
       <c r="A237" s="2" t="s">
         <v>510</v>
       </c>
@@ -8139,7 +8145,7 @@
       </c>
       <c r="G237" s="26"/>
     </row>
-    <row r="238" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:7" ht="30" customHeight="1">
       <c r="A238" s="2" t="s">
         <v>510</v>
       </c>
@@ -8156,7 +8162,7 @@
       </c>
       <c r="G238" s="24"/>
     </row>
-    <row r="239" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:7" ht="30" customHeight="1">
       <c r="A239" s="2" t="s">
         <v>510</v>
       </c>
@@ -8177,7 +8183,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="240" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:7" ht="30" customHeight="1">
       <c r="A240" s="2" t="s">
         <v>510</v>
       </c>
@@ -8194,7 +8200,7 @@
       </c>
       <c r="G240" s="26"/>
     </row>
-    <row r="241" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:7" ht="30" customHeight="1">
       <c r="A241" t="s">
         <v>510</v>
       </c>
@@ -8211,7 +8217,7 @@
       </c>
       <c r="G241" s="26"/>
     </row>
-    <row r="242" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A242" s="2" t="s">
         <v>510</v>
       </c>
@@ -8228,7 +8234,7 @@
       </c>
       <c r="G242" s="26"/>
     </row>
-    <row r="243" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:7" ht="45">
       <c r="A243" s="2" t="s">
         <v>510</v>
       </c>
@@ -8247,7 +8253,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="244" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:7" ht="30" customHeight="1">
       <c r="A244" t="s">
         <v>510</v>
       </c>
@@ -8264,7 +8270,7 @@
       </c>
       <c r="G244" s="26"/>
     </row>
-    <row r="245" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:7" ht="30">
       <c r="A245" s="2" t="s">
         <v>510</v>
       </c>
@@ -8283,7 +8289,7 @@
       </c>
       <c r="G245" s="24"/>
     </row>
-    <row r="246" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:7">
       <c r="A246" s="2" t="s">
         <v>510</v>
       </c>
@@ -8302,7 +8308,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="247" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:7">
       <c r="A247" s="2" t="s">
         <v>510</v>
       </c>
@@ -8319,7 +8325,7 @@
       </c>
       <c r="G247" s="26"/>
     </row>
-    <row r="248" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:7" ht="30">
       <c r="A248" s="2" t="s">
         <v>510</v>
       </c>
@@ -8338,7 +8344,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="249" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:7" ht="30" customHeight="1">
       <c r="A249" s="2" t="s">
         <v>510</v>
       </c>
@@ -8359,7 +8365,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="250" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" ht="30" customHeight="1">
       <c r="A250" s="2" t="s">
         <v>510</v>
       </c>
@@ -8378,7 +8384,7 @@
       </c>
       <c r="G250" s="26"/>
     </row>
-    <row r="251" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="251" spans="1:7">
       <c r="A251" t="s">
         <v>510</v>
       </c>
@@ -8395,7 +8401,7 @@
       </c>
       <c r="G251" s="26"/>
     </row>
-    <row r="252" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="252" spans="1:7" ht="30">
       <c r="A252" s="2" t="s">
         <v>510</v>
       </c>
@@ -8412,7 +8418,7 @@
       </c>
       <c r="G252" s="26"/>
     </row>
-    <row r="253" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="253" spans="1:7" ht="30" customHeight="1">
       <c r="A253" s="2" t="s">
         <v>510</v>
       </c>
@@ -8429,7 +8435,7 @@
       </c>
       <c r="G253" s="26"/>
     </row>
-    <row r="254" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="254" spans="1:7" ht="30" customHeight="1">
       <c r="A254" s="2" t="s">
         <v>510</v>
       </c>
@@ -8446,7 +8452,7 @@
       </c>
       <c r="G254" s="26"/>
     </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="255" spans="1:7">
       <c r="A255" s="2" t="s">
         <v>510</v>
       </c>
@@ -8465,7 +8471,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="256" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="256" spans="1:7" ht="30">
       <c r="A256" s="2" t="s">
         <v>510</v>
       </c>
@@ -8482,7 +8488,7 @@
       </c>
       <c r="G256" s="26"/>
     </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="257" spans="1:7">
       <c r="A257" t="s">
         <v>510</v>
       </c>
@@ -8499,7 +8505,7 @@
       </c>
       <c r="G257" s="26"/>
     </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="258" spans="1:7">
       <c r="A258" t="s">
         <v>510</v>
       </c>
@@ -8516,7 +8522,7 @@
       </c>
       <c r="G258" s="26"/>
     </row>
-    <row r="259" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="259" spans="1:7" ht="30" customHeight="1">
       <c r="A259" t="s">
         <v>510</v>
       </c>
@@ -8533,7 +8539,7 @@
       </c>
       <c r="G259" s="26"/>
     </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="260" spans="1:7">
       <c r="A260" t="s">
         <v>510</v>
       </c>
@@ -8550,7 +8556,7 @@
       </c>
       <c r="G260" s="26"/>
     </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="261" spans="1:7">
       <c r="A261" t="s">
         <v>510</v>
       </c>
@@ -8567,7 +8573,7 @@
       </c>
       <c r="G261" s="26"/>
     </row>
-    <row r="262" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" ht="30" customHeight="1">
       <c r="A262" t="s">
         <v>510</v>
       </c>
@@ -8584,7 +8590,7 @@
       </c>
       <c r="G262" s="26"/>
     </row>
-    <row r="263" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A263" t="s">
         <v>510</v>
       </c>
@@ -8601,7 +8607,7 @@
       </c>
       <c r="G263" s="26"/>
     </row>
-    <row r="264" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A264" t="s">
         <v>510</v>
       </c>
@@ -8620,7 +8626,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="265" spans="1:7">
       <c r="A265" t="s">
         <v>510</v>
       </c>
@@ -8639,7 +8645,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="266" spans="1:7">
       <c r="A266" s="2" t="s">
         <v>510</v>
       </c>
@@ -8658,7 +8664,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="267" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="267" spans="1:7" ht="30" customHeight="1">
       <c r="A267" s="2" t="s">
         <v>510</v>
       </c>
@@ -8677,7 +8683,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="268" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" ht="30" customHeight="1">
       <c r="A268" s="17" t="s">
         <v>510</v>
       </c>
@@ -8696,7 +8702,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7">
       <c r="A269" s="2" t="s">
         <v>510</v>
       </c>
@@ -8715,7 +8721,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="270" spans="1:7">
       <c r="A270" s="2" t="s">
         <v>510</v>
       </c>
@@ -8734,7 +8740,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="271" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" ht="30" customHeight="1">
       <c r="A271" s="2" t="s">
         <v>510</v>
       </c>
@@ -8751,7 +8757,7 @@
       </c>
       <c r="G271" s="26"/>
     </row>
-    <row r="272" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="272" spans="1:7" ht="30" customHeight="1">
       <c r="A272" s="2" t="s">
         <v>510</v>
       </c>
@@ -8768,7 +8774,7 @@
       </c>
       <c r="G272" s="26"/>
     </row>
-    <row r="273" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
       <c r="A273" s="2" t="s">
         <v>678</v>
       </c>
@@ -8785,7 +8791,7 @@
       </c>
       <c r="G273" s="26"/>
     </row>
-    <row r="274" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="274" spans="1:7" ht="30" customHeight="1">
       <c r="A274" s="2" t="s">
         <v>678</v>
       </c>
@@ -8804,7 +8810,7 @@
       </c>
       <c r="G274" s="26"/>
     </row>
-    <row r="275" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="275" spans="1:7" ht="30" customHeight="1">
       <c r="A275" s="2" t="s">
         <v>678</v>
       </c>
@@ -8823,7 +8829,7 @@
       </c>
       <c r="G275" s="26"/>
     </row>
-    <row r="276" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="276" spans="1:7" ht="30" customHeight="1">
       <c r="A276" s="2" t="s">
         <v>678</v>
       </c>
@@ -8840,7 +8846,7 @@
       </c>
       <c r="G276" s="26"/>
     </row>
-    <row r="277" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="277" spans="1:7" ht="30" customHeight="1">
       <c r="A277" s="2" t="s">
         <v>678</v>
       </c>
@@ -8857,7 +8863,7 @@
       </c>
       <c r="G277" s="26"/>
     </row>
-    <row r="278" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
       <c r="A278" s="2" t="s">
         <v>678</v>
       </c>
@@ -8874,7 +8880,7 @@
       </c>
       <c r="G278" s="26"/>
     </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="279" spans="1:7">
       <c r="A279" s="2" t="s">
         <v>678</v>
       </c>
@@ -8891,7 +8897,7 @@
       </c>
       <c r="G279" s="24"/>
     </row>
-    <row r="280" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" ht="30">
       <c r="A280" s="2" t="s">
         <v>678</v>
       </c>
@@ -8912,7 +8918,7 @@
       </c>
       <c r="G280" s="26"/>
     </row>
-    <row r="281" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="281" spans="1:7" ht="30" customHeight="1">
       <c r="A281" s="2" t="s">
         <v>678</v>
       </c>
@@ -8929,7 +8935,7 @@
       </c>
       <c r="G281" s="24"/>
     </row>
-    <row r="282" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="282" spans="1:7" ht="30" customHeight="1">
       <c r="A282" s="2" t="s">
         <v>678</v>
       </c>
@@ -8946,7 +8952,7 @@
       </c>
       <c r="G282" s="26"/>
     </row>
-    <row r="283" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" ht="30" customHeight="1">
       <c r="A283" s="2" t="s">
         <v>678</v>
       </c>
@@ -8965,7 +8971,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="284" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="284" spans="1:7" ht="30" customHeight="1">
       <c r="A284" s="2" t="s">
         <v>678</v>
       </c>
@@ -8982,7 +8988,7 @@
       <c r="F284" s="5"/>
       <c r="G284" s="26"/>
     </row>
-    <row r="285" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="285" spans="1:7" ht="30" customHeight="1">
       <c r="A285" s="2" t="s">
         <v>678</v>
       </c>
@@ -9001,7 +9007,7 @@
         <v>710</v>
       </c>
     </row>
-    <row r="286" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="286" spans="1:7" ht="30" customHeight="1">
       <c r="A286" s="2" t="s">
         <v>678</v>
       </c>
@@ -9020,7 +9026,7 @@
       </c>
       <c r="G286" s="26"/>
     </row>
-    <row r="287" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="287" spans="1:7">
       <c r="A287" s="2" t="s">
         <v>678</v>
       </c>
@@ -9037,7 +9043,7 @@
       </c>
       <c r="G287" s="26"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7">
       <c r="A288" s="2" t="s">
         <v>678</v>
       </c>
@@ -9054,7 +9060,7 @@
       </c>
       <c r="G288" s="24"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="289" spans="1:7">
       <c r="A289" s="2" t="s">
         <v>678</v>
       </c>
@@ -9071,7 +9077,7 @@
       </c>
       <c r="G289" s="26"/>
     </row>
-    <row r="290" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="290" spans="1:7">
       <c r="A290" s="17" t="s">
         <v>678</v>
       </c>
@@ -9088,7 +9094,7 @@
       </c>
       <c r="G290" s="28"/>
     </row>
-    <row r="291" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="291" spans="1:7" ht="30" customHeight="1">
       <c r="A291" s="2" t="s">
         <v>678</v>
       </c>
@@ -9105,7 +9111,7 @@
       </c>
       <c r="G291" s="26"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="292" spans="1:7">
       <c r="A292" s="2" t="s">
         <v>678</v>
       </c>
@@ -9124,7 +9130,7 @@
         <v>725</v>
       </c>
     </row>
-    <row r="293" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="293" spans="1:7">
       <c r="A293" s="2" t="s">
         <v>678</v>
       </c>
@@ -9141,7 +9147,7 @@
       </c>
       <c r="G293" s="26"/>
     </row>
-    <row r="294" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="294" spans="1:7" ht="30" customHeight="1">
       <c r="A294" s="2" t="s">
         <v>678</v>
       </c>
@@ -9158,7 +9164,7 @@
       </c>
       <c r="G294" s="24"/>
     </row>
-    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="295" spans="1:7">
       <c r="A295" s="2" t="s">
         <v>730</v>
       </c>
@@ -9175,7 +9181,7 @@
       </c>
       <c r="G295" s="26"/>
     </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="296" spans="1:7">
       <c r="A296" s="2" t="s">
         <v>730</v>
       </c>
@@ -9194,7 +9200,7 @@
       </c>
       <c r="G296" s="26"/>
     </row>
-    <row r="297" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="297" spans="1:7" ht="30">
       <c r="A297" s="2" t="s">
         <v>730</v>
       </c>
@@ -9211,7 +9217,7 @@
       </c>
       <c r="G297" s="26"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="298" spans="1:7">
       <c r="A298" s="2" t="s">
         <v>730</v>
       </c>
@@ -9230,7 +9236,7 @@
         <v>740</v>
       </c>
     </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="299" spans="1:7">
       <c r="A299" s="17" t="s">
         <v>730</v>
       </c>
@@ -9247,7 +9253,7 @@
       </c>
       <c r="G299" s="28"/>
     </row>
-    <row r="300" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="300" spans="1:7" ht="30" customHeight="1">
       <c r="A300" s="2" t="s">
         <v>730</v>
       </c>
@@ -9264,7 +9270,7 @@
       </c>
       <c r="G300" s="24"/>
     </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="301" spans="1:7">
       <c r="A301" s="2" t="s">
         <v>730</v>
       </c>
@@ -9281,7 +9287,7 @@
       </c>
       <c r="G301" s="24"/>
     </row>
-    <row r="302" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="302" spans="1:7" ht="30">
       <c r="A302" s="2" t="s">
         <v>730</v>
       </c>
@@ -9298,7 +9304,7 @@
       </c>
       <c r="G302" s="24"/>
     </row>
-    <row r="303" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="303" spans="1:7" ht="30">
       <c r="A303" s="2" t="s">
         <v>730</v>
       </c>
@@ -9315,7 +9321,7 @@
       </c>
       <c r="G303" s="24"/>
     </row>
-    <row r="304" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="304" spans="1:7" ht="30">
       <c r="A304" s="17" t="s">
         <v>750</v>
       </c>
@@ -9334,7 +9340,7 @@
         <v>753</v>
       </c>
     </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="305" spans="1:7">
       <c r="A305" s="2" t="s">
         <v>750</v>
       </c>
@@ -9353,7 +9359,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7">
       <c r="A306" s="2" t="s">
         <v>750</v>
       </c>
@@ -9372,7 +9378,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="307" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" ht="60" customHeight="1">
       <c r="A307" s="2" t="s">
         <v>750</v>
       </c>
@@ -9391,7 +9397,7 @@
         <v>762</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="308" spans="1:7">
       <c r="A308" s="2" t="s">
         <v>750</v>
       </c>
@@ -9408,7 +9414,7 @@
       </c>
       <c r="G308" s="26"/>
     </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="309" spans="1:7">
       <c r="A309" s="2" t="s">
         <v>765</v>
       </c>
@@ -9425,32 +9431,32 @@
       </c>
       <c r="G309" s="26"/>
     </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="310" spans="1:7">
       <c r="A310" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>768</v>
+        <v>1004</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>769</v>
+        <v>1005</v>
       </c>
       <c r="D310" s="7"/>
       <c r="E310" s="7"/>
-      <c r="F310" s="5" t="s">
-        <v>96</v>
+      <c r="F310" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G310" s="26"/>
     </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7">
       <c r="A311" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D311" s="7"/>
       <c r="E311" s="7"/>
@@ -9459,15 +9465,15 @@
       </c>
       <c r="G311" s="26"/>
     </row>
-    <row r="312" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="312" spans="1:7" ht="30" customHeight="1">
       <c r="A312" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D312" s="7"/>
       <c r="E312" s="7"/>
@@ -9476,15 +9482,15 @@
       </c>
       <c r="G312" s="26"/>
     </row>
-    <row r="313" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="313" spans="1:7">
       <c r="A313" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D313" s="7"/>
       <c r="E313" s="7"/>
@@ -9493,15 +9499,15 @@
       </c>
       <c r="G313" s="26"/>
     </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="314" spans="1:7">
       <c r="A314" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D314" s="7"/>
       <c r="E314" s="7"/>
@@ -9510,15 +9516,15 @@
       </c>
       <c r="G314" s="26"/>
     </row>
-    <row r="315" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="315" spans="1:7" ht="30" customHeight="1">
       <c r="A315" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D315" s="7"/>
       <c r="E315" s="7"/>
@@ -9527,15 +9533,15 @@
       </c>
       <c r="G315" s="26"/>
     </row>
-    <row r="316" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="316" spans="1:7" ht="60" customHeight="1">
       <c r="A316" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D316" s="7"/>
       <c r="E316" s="7"/>
@@ -9544,15 +9550,15 @@
       </c>
       <c r="G316" s="26"/>
     </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="317" spans="1:7">
       <c r="A317" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D317" s="7"/>
       <c r="E317" s="1"/>
@@ -9561,15 +9567,15 @@
       </c>
       <c r="G317" s="26"/>
     </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="318" spans="1:7">
       <c r="A318" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D318" s="7"/>
       <c r="E318" s="7"/>
@@ -9578,15 +9584,15 @@
       </c>
       <c r="G318" s="26"/>
     </row>
-    <row r="319" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="319" spans="1:7" ht="60" customHeight="1">
       <c r="A319" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D319" s="7"/>
       <c r="E319" s="7"/>
@@ -9595,15 +9601,15 @@
       </c>
       <c r="G319" s="26"/>
     </row>
-    <row r="320" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="320" spans="1:7" ht="60" customHeight="1">
       <c r="A320" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D320" s="7"/>
       <c r="E320" s="7"/>
@@ -9612,119 +9618,119 @@
       </c>
       <c r="G320" s="26"/>
     </row>
-    <row r="321" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7">
       <c r="A321" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D321" s="7"/>
-      <c r="E321" s="7" t="s">
-        <v>792</v>
-      </c>
+      <c r="E321" s="7"/>
       <c r="F321" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G321" s="26"/>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" ht="30" customHeight="1">
       <c r="A322" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="D322" s="7"/>
       <c r="E322" s="7"/>
       <c r="F322" s="5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G322" s="26"/>
     </row>
-    <row r="323" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="323" spans="1:7" ht="30" customHeight="1">
       <c r="A323" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="D323" s="7"/>
+        <v>793</v>
+      </c>
+      <c r="D323" s="1"/>
       <c r="E323" s="7"/>
       <c r="F323" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G323" s="26"/>
     </row>
-    <row r="324" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" ht="60" customHeight="1">
       <c r="A324" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>798</v>
-      </c>
-      <c r="D324" s="1"/>
+        <v>795</v>
+      </c>
+      <c r="D324" s="7"/>
       <c r="E324" s="7"/>
       <c r="F324" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G324" s="26"/>
     </row>
-    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7">
       <c r="A325" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="D325" s="7"/>
       <c r="E325" s="7"/>
-      <c r="F325" s="5" t="s">
+      <c r="F325" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G325" s="26"/>
     </row>
-    <row r="326" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" ht="60" customHeight="1">
       <c r="A326" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="D326" s="7"/>
+        <v>799</v>
+      </c>
+      <c r="D326" s="7" t="s">
+        <v>800</v>
+      </c>
       <c r="E326" s="7"/>
-      <c r="F326" s="5" t="s">
+      <c r="F326" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G326" s="26"/>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="327" spans="1:7" ht="45" customHeight="1">
       <c r="A327" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D327" s="7"/>
       <c r="E327" s="7"/>
@@ -9733,845 +9739,845 @@
       </c>
       <c r="G327" s="26"/>
     </row>
-    <row r="328" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" ht="60" customHeight="1">
       <c r="A328" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>806</v>
-      </c>
-      <c r="D328" s="7" t="s">
-        <v>807</v>
-      </c>
+        <v>804</v>
+      </c>
+      <c r="D328" s="7"/>
       <c r="E328" s="7"/>
       <c r="F328" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G328" s="26"/>
     </row>
-    <row r="329" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="329" spans="1:7">
       <c r="A329" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D329" s="7"/>
       <c r="E329" s="7"/>
-      <c r="F329" s="3" t="s">
-        <v>20</v>
+      <c r="F329" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G329" s="26"/>
     </row>
-    <row r="330" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" ht="30" customHeight="1">
       <c r="A330" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="D330" s="7"/>
       <c r="E330" s="7"/>
-      <c r="F330" s="3" t="s">
-        <v>20</v>
+      <c r="F330" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G330" s="26"/>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" ht="30" customHeight="1">
       <c r="A331" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D331" s="7"/>
       <c r="E331" s="7"/>
-      <c r="F331" s="4" t="s">
+      <c r="F331" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G331" s="26"/>
-    </row>
-    <row r="332" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G331" s="24"/>
+    </row>
+    <row r="332" spans="1:7">
       <c r="A332" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="D332" s="7"/>
       <c r="E332" s="7"/>
-      <c r="F332" s="4" t="s">
+      <c r="F332" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G332" s="26"/>
     </row>
-    <row r="333" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" ht="60" customHeight="1">
       <c r="A333" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D333" s="7"/>
       <c r="E333" s="7"/>
-      <c r="F333" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G333" s="24"/>
-    </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F333" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G333" s="26"/>
+    </row>
+    <row r="334" spans="1:7">
       <c r="A334" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="D334" s="7"/>
       <c r="E334" s="7"/>
       <c r="F334" s="5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G334" s="26"/>
     </row>
-    <row r="335" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7">
       <c r="A335" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D335" s="7"/>
       <c r="E335" s="7"/>
-      <c r="F335" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G335" s="26"/>
-    </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F335" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="G335" s="26" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="336" spans="1:7" ht="45" customHeight="1">
       <c r="A336" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B336" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="C336" s="2" t="s">
         <v>822</v>
       </c>
-      <c r="C336" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="D336" s="7"/>
+      <c r="D336" s="1"/>
       <c r="E336" s="7"/>
       <c r="F336" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G336" s="26"/>
     </row>
-    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7">
       <c r="A337" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B337" s="2" t="s">
+        <v>823</v>
+      </c>
+      <c r="C337" s="2" t="s">
         <v>824</v>
-      </c>
-      <c r="C337" s="2" t="s">
-        <v>825</v>
       </c>
       <c r="D337" s="7"/>
       <c r="E337" s="7"/>
       <c r="F337" s="4" t="s">
-        <v>826</v>
-      </c>
-      <c r="G337" s="26" t="s">
-        <v>827</v>
-      </c>
-    </row>
-    <row r="338" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>20</v>
+      </c>
+      <c r="G337" s="26"/>
+    </row>
+    <row r="338" spans="1:7">
       <c r="A338" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>829</v>
-      </c>
-      <c r="D338" s="1"/>
+        <v>826</v>
+      </c>
+      <c r="D338" s="7"/>
       <c r="E338" s="7"/>
-      <c r="F338" s="5" t="s">
+      <c r="F338" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G338" s="26"/>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" ht="45" customHeight="1">
       <c r="A339" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="D339" s="7"/>
       <c r="E339" s="7"/>
-      <c r="F339" s="4" t="s">
-        <v>20</v>
+      <c r="F339" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G339" s="26"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="340" spans="1:7" ht="45" customHeight="1">
       <c r="A340" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="D340" s="7"/>
+        <v>830</v>
+      </c>
+      <c r="D340" s="7" t="s">
+        <v>831</v>
+      </c>
       <c r="E340" s="7"/>
-      <c r="F340" s="4" t="s">
+      <c r="F340" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G340" s="26"/>
     </row>
-    <row r="341" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="341" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
       <c r="A341" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D341" s="7"/>
       <c r="E341" s="7"/>
-      <c r="F341" s="5" t="s">
+      <c r="F341" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G341" s="26"/>
     </row>
-    <row r="342" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="342" spans="1:7" ht="45" customHeight="1">
       <c r="A342" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>837</v>
-      </c>
-      <c r="D342" s="7" t="s">
-        <v>838</v>
-      </c>
+        <v>835</v>
+      </c>
+      <c r="D342" s="7"/>
       <c r="E342" s="7"/>
-      <c r="F342" s="3" t="s">
-        <v>20</v>
+      <c r="F342" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G342" s="26"/>
     </row>
-    <row r="343" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:7" ht="30">
       <c r="A343" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="D343" s="7"/>
       <c r="E343" s="7"/>
-      <c r="F343" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G343" s="26"/>
-    </row>
-    <row r="344" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F343" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G343" s="24"/>
+    </row>
+    <row r="344" spans="1:7" ht="30" customHeight="1">
       <c r="A344" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="D344" s="7"/>
       <c r="E344" s="7"/>
-      <c r="F344" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G344" s="26"/>
-    </row>
-    <row r="345" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="F344" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G344" s="24"/>
+    </row>
+    <row r="345" spans="1:7" ht="30" customHeight="1">
       <c r="A345" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="D345" s="7"/>
       <c r="E345" s="7"/>
       <c r="F345" s="16" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G345" s="24"/>
     </row>
-    <row r="346" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="346" spans="1:7">
       <c r="A346" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="D346" s="7"/>
-      <c r="E346" s="7"/>
-      <c r="F346" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G346" s="24"/>
-    </row>
-    <row r="347" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E346" s="1"/>
+      <c r="F346" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G346" s="26"/>
+    </row>
+    <row r="347" spans="1:7">
       <c r="A347" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D347" s="7"/>
       <c r="E347" s="7"/>
-      <c r="F347" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G347" s="24"/>
-    </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F347" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G347" s="26" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="348" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
       <c r="A348" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D348" s="7"/>
-      <c r="E348" s="1"/>
+      <c r="E348" s="7"/>
       <c r="F348" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G348" s="26"/>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G348" s="26" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" ht="45" customHeight="1">
       <c r="A349" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D349" s="7"/>
       <c r="E349" s="7"/>
-      <c r="F349" s="5" t="s">
+      <c r="F349" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G349" s="26" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="350" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" ht="30" customHeight="1">
       <c r="A350" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="D350" s="7"/>
-      <c r="E350" s="7"/>
-      <c r="F350" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G350" s="26" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="351" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E350" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="F350" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G350" s="24"/>
+    </row>
+    <row r="351" spans="1:7" ht="45" customHeight="1">
       <c r="A351" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D351" s="7"/>
       <c r="E351" s="7"/>
-      <c r="F351" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G351" s="26" t="s">
-        <v>853</v>
-      </c>
-    </row>
-    <row r="352" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F351" s="5" t="s">
+        <v>855</v>
+      </c>
+      <c r="G351" s="26"/>
+    </row>
+    <row r="352" spans="1:7" ht="45" customHeight="1">
       <c r="A352" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>858</v>
+        <v>1006</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>859</v>
+        <v>1007</v>
       </c>
       <c r="D352" s="7"/>
-      <c r="E352" s="7" t="s">
-        <v>803</v>
-      </c>
-      <c r="F352" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G352" s="24"/>
-    </row>
-    <row r="353" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E352" s="7"/>
+      <c r="F352" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G352" s="26"/>
+    </row>
+    <row r="353" spans="1:7" ht="30">
       <c r="A353" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="D353" s="7"/>
       <c r="E353" s="7"/>
       <c r="F353" s="5" t="s">
-        <v>862</v>
+        <v>29</v>
       </c>
       <c r="G353" s="26"/>
     </row>
-    <row r="354" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="354" spans="1:7" ht="30" customHeight="1">
       <c r="A354" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="D354" s="7"/>
       <c r="E354" s="7"/>
-      <c r="F354" s="5" t="s">
+      <c r="F354" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G354" s="26"/>
-    </row>
-    <row r="355" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G354" s="24"/>
+    </row>
+    <row r="355" spans="1:7" ht="30" customHeight="1">
       <c r="A355" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="D355" s="7"/>
       <c r="E355" s="7"/>
-      <c r="F355" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G355" s="24"/>
-    </row>
-    <row r="356" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F355" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G355" s="26" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7">
       <c r="A356" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D356" s="7"/>
       <c r="E356" s="7"/>
-      <c r="F356" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G356" s="26" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F356" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G356" s="26"/>
+    </row>
+    <row r="357" spans="1:7">
       <c r="A357" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="D357" s="7"/>
       <c r="E357" s="7"/>
-      <c r="F357" s="5" t="s">
+      <c r="F357" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G357" s="26"/>
     </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" ht="30" customHeight="1">
       <c r="A358" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>872</v>
+        <v>867</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>873</v>
+        <v>868</v>
       </c>
       <c r="D358" s="7"/>
       <c r="E358" s="7"/>
-      <c r="F358" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G358" s="26"/>
-    </row>
-    <row r="359" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F358" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G358" s="26" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7">
       <c r="A359" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D359" s="7"/>
       <c r="E359" s="7"/>
-      <c r="F359" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G359" s="26" t="s">
-        <v>876</v>
-      </c>
-    </row>
-    <row r="360" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A360" s="2" t="s">
+      <c r="F359" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G359" s="26"/>
+    </row>
+    <row r="360" spans="1:7">
+      <c r="A360" t="s">
         <v>765</v>
       </c>
-      <c r="B360" s="2" t="s">
-        <v>877</v>
-      </c>
-      <c r="C360" s="2" t="s">
-        <v>878</v>
+      <c r="B360" t="s">
+        <v>872</v>
+      </c>
+      <c r="C360" t="s">
+        <v>873</v>
       </c>
       <c r="D360" s="7"/>
       <c r="E360" s="7"/>
-      <c r="F360" s="5" t="s">
-        <v>96</v>
+      <c r="F360" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="G360" s="26"/>
     </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="361" spans="1:7">
       <c r="A361" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>879</v>
+        <v>874</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>880</v>
+        <v>875</v>
       </c>
       <c r="D361" s="7"/>
-      <c r="E361" s="7"/>
-      <c r="F361" s="12" t="s">
+      <c r="E361" s="1"/>
+      <c r="F361" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G361" s="26"/>
     </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A362" t="s">
+    <row r="362" spans="1:7">
+      <c r="A362" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B362" t="s">
-        <v>881</v>
-      </c>
-      <c r="C362" t="s">
-        <v>882</v>
+      <c r="B362" s="2" t="s">
+        <v>876</v>
+      </c>
+      <c r="C362" s="2" t="s">
+        <v>877</v>
       </c>
       <c r="D362" s="7"/>
       <c r="E362" s="7"/>
-      <c r="F362" s="12" t="s">
-        <v>29</v>
+      <c r="F362" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G362" s="26"/>
     </row>
-    <row r="363" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7">
       <c r="A363" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>883</v>
+        <v>1008</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>884</v>
+        <v>1009</v>
       </c>
       <c r="D363" s="7"/>
-      <c r="E363" s="7"/>
-      <c r="F363" s="14" t="s">
+      <c r="E363" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F363" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G363" s="26"/>
     </row>
-    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="364" spans="1:7">
       <c r="A364" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>885</v>
+        <v>878</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>886</v>
+        <v>879</v>
       </c>
       <c r="D364" s="7"/>
-      <c r="E364" s="1"/>
-      <c r="F364" s="5" t="s">
-        <v>20</v>
+      <c r="E364" s="7"/>
+      <c r="F364" s="4" t="s">
+        <v>96</v>
       </c>
       <c r="G364" s="26"/>
     </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="365" spans="1:7">
       <c r="A365" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>887</v>
+        <v>880</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>888</v>
+        <v>881</v>
       </c>
       <c r="D365" s="7"/>
-      <c r="E365" s="7"/>
-      <c r="F365" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="G365" s="26"/>
-    </row>
-    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="E365" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="F365" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G365" s="24"/>
+    </row>
+    <row r="366" spans="1:7">
       <c r="A366" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>889</v>
+        <v>882</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>890</v>
+        <v>883</v>
       </c>
       <c r="D366" s="7"/>
       <c r="E366" s="7"/>
-      <c r="F366" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G366" s="26"/>
-    </row>
-    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A367" s="2" t="s">
+      <c r="F366" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G366" s="24"/>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" s="17" t="s">
         <v>765</v>
       </c>
-      <c r="B367" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="C367" s="2" t="s">
-        <v>892</v>
-      </c>
-      <c r="D367" s="7"/>
-      <c r="E367" s="7" t="s">
-        <v>887</v>
-      </c>
-      <c r="F367" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G367" s="24"/>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B367" s="17" t="s">
+        <v>884</v>
+      </c>
+      <c r="C367" s="17" t="s">
+        <v>885</v>
+      </c>
+      <c r="D367" s="27"/>
+      <c r="E367" s="27"/>
+      <c r="F367" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G367" s="28"/>
+    </row>
+    <row r="368" spans="1:7">
       <c r="A368" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>893</v>
+        <v>886</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>894</v>
-      </c>
-      <c r="D368" s="7"/>
+        <v>887</v>
+      </c>
+      <c r="D368" s="1"/>
       <c r="E368" s="7"/>
-      <c r="F368" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G368" s="24"/>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A369" s="17" t="s">
+      <c r="F368" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G368" s="26" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7">
+      <c r="A369" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B369" s="17" t="s">
-        <v>895</v>
-      </c>
-      <c r="C369" s="17" t="s">
-        <v>896</v>
-      </c>
-      <c r="D369" s="27"/>
-      <c r="E369" s="27"/>
-      <c r="F369" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G369" s="28"/>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B369" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="D369" s="1"/>
+      <c r="E369" s="7"/>
+      <c r="F369" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G369" s="26" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" ht="30">
       <c r="A370" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>897</v>
+        <v>892</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>898</v>
+        <v>893</v>
       </c>
       <c r="D370" s="1"/>
       <c r="E370" s="7"/>
       <c r="F370" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G370" s="26" t="s">
-        <v>899</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="G370" s="26"/>
+    </row>
+    <row r="371" spans="1:7">
       <c r="A371" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>900</v>
+        <v>1011</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>901</v>
+        <v>1012</v>
       </c>
       <c r="D371" s="1"/>
       <c r="E371" s="7"/>
       <c r="F371" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G371" s="26" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="372" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="G371" s="26"/>
+    </row>
+    <row r="372" spans="1:7">
       <c r="A372" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>903</v>
+        <v>1013</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>904</v>
+        <v>1014</v>
       </c>
       <c r="D372" s="1"/>
-      <c r="E372" s="7"/>
+      <c r="E372" s="7" t="s">
+        <v>772</v>
+      </c>
       <c r="F372" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G372" s="26"/>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="373" spans="1:7">
       <c r="A373" s="2" t="s">
-        <v>905</v>
+        <v>765</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>906</v>
+        <v>1015</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>907</v>
-      </c>
-      <c r="D373" s="7" t="s">
-        <v>908</v>
-      </c>
+        <v>1016</v>
+      </c>
+      <c r="D373" s="1"/>
       <c r="E373" s="7"/>
-      <c r="F373" s="25" t="s">
+      <c r="F373" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G373" s="26"/>
+    </row>
+    <row r="374" spans="1:7">
+      <c r="A374" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="D374" s="7" t="s">
+        <v>897</v>
+      </c>
+      <c r="E374" s="7"/>
+      <c r="F374" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G373" s="26"/>
-    </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A374" s="2" t="s">
-        <v>905</v>
-      </c>
-      <c r="B374" s="2" t="s">
-        <v>909</v>
-      </c>
-      <c r="C374" s="2" t="s">
-        <v>910</v>
-      </c>
-      <c r="D374" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="E374" s="7"/>
-      <c r="F374" s="4" t="s">
-        <v>20</v>
-      </c>
       <c r="G374" s="26"/>
     </row>
-    <row r="375" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="375" spans="1:7">
       <c r="A375" s="2" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>912</v>
+        <v>898</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>913</v>
-      </c>
-      <c r="D375" s="1" t="s">
-        <v>914</v>
+        <v>899</v>
+      </c>
+      <c r="D375" s="7" t="s">
+        <v>900</v>
       </c>
       <c r="E375" s="7"/>
       <c r="F375" s="4" t="s">
@@ -10579,82 +10585,101 @@
       </c>
       <c r="G375" s="26"/>
     </row>
-    <row r="376" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A376" s="17" t="s">
+    <row r="376" spans="1:7" ht="30">
+      <c r="A376" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D376" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="E376" s="7"/>
+      <c r="F376" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G376" s="26"/>
+    </row>
+    <row r="377" spans="1:7" ht="30">
+      <c r="A377" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="B377" s="17" t="s">
+        <v>904</v>
+      </c>
+      <c r="C377" s="17" t="s">
         <v>905</v>
       </c>
-      <c r="B376" s="17" t="s">
-        <v>915</v>
-      </c>
-      <c r="C376" s="17" t="s">
-        <v>916</v>
-      </c>
-      <c r="D376" s="27"/>
-      <c r="E376" s="27"/>
-      <c r="F376" s="18" t="s">
-        <v>917</v>
-      </c>
-      <c r="G376" s="28"/>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A377" t="s">
-        <v>905</v>
-      </c>
-      <c r="B377" t="s">
-        <v>918</v>
-      </c>
-      <c r="C377" t="s">
-        <v>919</v>
-      </c>
-      <c r="D377" s="7"/>
-      <c r="E377" s="7"/>
-      <c r="F377" t="s">
-        <v>29</v>
-      </c>
-      <c r="G377" s="26"/>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D377" s="27"/>
+      <c r="E377" s="27"/>
+      <c r="F377" s="18" t="s">
+        <v>906</v>
+      </c>
+      <c r="G377" s="28"/>
+    </row>
+    <row r="378" spans="1:7">
       <c r="A378" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="B378" t="s">
-        <v>920</v>
+        <v>907</v>
       </c>
       <c r="C378" t="s">
-        <v>921</v>
-      </c>
-      <c r="D378" s="7" t="s">
-        <v>922</v>
-      </c>
+        <v>908</v>
+      </c>
+      <c r="D378" s="7"/>
       <c r="E378" s="7"/>
       <c r="F378" t="s">
         <v>29</v>
       </c>
       <c r="G378" s="26"/>
     </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="379" spans="1:7">
       <c r="A379" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="B379" t="s">
-        <v>923</v>
+        <v>909</v>
       </c>
       <c r="C379" t="s">
-        <v>924</v>
+        <v>910</v>
       </c>
       <c r="D379" s="7" t="s">
-        <v>925</v>
+        <v>911</v>
       </c>
       <c r="E379" s="7"/>
       <c r="F379" t="s">
+        <v>29</v>
+      </c>
+      <c r="G379" s="26"/>
+    </row>
+    <row r="380" spans="1:7">
+      <c r="A380" t="s">
+        <v>894</v>
+      </c>
+      <c r="B380" t="s">
+        <v>912</v>
+      </c>
+      <c r="C380" t="s">
+        <v>913</v>
+      </c>
+      <c r="D380" s="7" t="s">
+        <v>914</v>
+      </c>
+      <c r="E380" s="7"/>
+      <c r="F380" t="s">
         <v>20</v>
       </c>
-      <c r="G379" s="26"/>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D380" s="7"/>
-      <c r="E380" s="7"/>
       <c r="G380" s="26"/>
+    </row>
+    <row r="381" spans="1:7">
+      <c r="D381" s="7"/>
+      <c r="E381" s="7"/>
+      <c r="G381" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10665,162 +10690,162 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
     <col min="2" max="2" width="52.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
       <c r="A3" t="s">
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
       <c r="A4" t="s">
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
       <c r="A5" t="s">
         <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
       <c r="A6" t="s">
         <v>141</v>
       </c>
       <c r="B6" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
       <c r="A7" t="s">
         <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
       <c r="A8" t="s">
         <v>196</v>
       </c>
       <c r="B8" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
       <c r="A9" t="s">
         <v>210</v>
       </c>
       <c r="B9" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
       <c r="A10" t="s">
         <v>388</v>
       </c>
       <c r="B10" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
       <c r="A11" t="s">
         <v>405</v>
       </c>
       <c r="B11" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
       <c r="A12" t="s">
         <v>467</v>
       </c>
       <c r="B12" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
       <c r="A13" t="s">
         <v>475</v>
       </c>
       <c r="B13" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
       <c r="A14" t="s">
         <v>510</v>
       </c>
       <c r="B14" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
       <c r="A15" t="s">
         <v>678</v>
       </c>
       <c r="B15" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
       <c r="A16" t="s">
         <v>730</v>
       </c>
       <c r="B16" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+        <v>989</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
       <c r="A17" t="s">
         <v>750</v>
       </c>
       <c r="B17" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
       <c r="A18" t="s">
         <v>765</v>
       </c>
       <c r="B18" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
       <c r="A19" t="s">
-        <v>905</v>
+        <v>894</v>
       </c>
       <c r="B19" t="s">
-        <v>1003</v>
+        <v>992</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-develop\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\US\Models\eps-us\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAB845F-F13E-4CF2-A244-FC7B5E47D5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A58A88B2-63BC-4970-A761-4029CB82A961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="43200" windowHeight="17085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4680" yWindow="4680" windowWidth="43200" windowHeight="17145" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="1021">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -3073,6 +3073,18 @@
   </si>
   <si>
     <t>Vehicle Weibull Shape Parameter by Vintage</t>
+  </si>
+  <si>
+    <t>EoFSwTD</t>
+  </si>
+  <si>
+    <t>Elasticity of Fleet Size wrt Travel Demand</t>
+  </si>
+  <si>
+    <t>Your country has data on vehicle occupancy or load factors, or on how car ownership responds to transit and demand-management policies</t>
+  </si>
+  <si>
+    <t>EoFSwTD Elasticity of Fleet Size wrt Travel Demand, EoFSwMS Elasticity of Fleet Size wrt Mode Shifting, SYVUR Start Year Vehicle Utilization Rate, RUoMV Relative Use of Marginal Vehicles, VAUL Vehicle Absorbed Use as Loading</t>
   </si>
 </sst>
 </file>
@@ -3886,7 +3898,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G381"/>
+  <dimension ref="A1:G382"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
@@ -9916,32 +9928,36 @@
         <v>765</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>825</v>
+        <v>1017</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="D338" s="7"/>
+        <v>1018</v>
+      </c>
+      <c r="D338" s="7" t="s">
+        <v>1020</v>
+      </c>
       <c r="E338" s="7"/>
       <c r="F338" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G338" s="26"/>
-    </row>
-    <row r="339" spans="1:7" ht="45" customHeight="1">
+        <v>29</v>
+      </c>
+      <c r="G338" s="26" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="339" spans="1:7">
       <c r="A339" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D339" s="7"/>
       <c r="E339" s="7"/>
-      <c r="F339" s="5" t="s">
-        <v>29</v>
+      <c r="F339" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G339" s="26"/>
     </row>
@@ -9950,85 +9966,85 @@
         <v>765</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="D340" s="7" t="s">
-        <v>831</v>
-      </c>
+        <v>828</v>
+      </c>
+      <c r="D340" s="7"/>
       <c r="E340" s="7"/>
-      <c r="F340" s="3" t="s">
-        <v>20</v>
+      <c r="F340" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G340" s="26"/>
     </row>
-    <row r="341" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="341" spans="1:7" ht="45" customHeight="1">
       <c r="A341" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="D341" s="7"/>
+        <v>830</v>
+      </c>
+      <c r="D341" s="7" t="s">
+        <v>831</v>
+      </c>
       <c r="E341" s="7"/>
       <c r="F341" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G341" s="26"/>
     </row>
-    <row r="342" spans="1:7" ht="45" customHeight="1">
+    <row r="342" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
       <c r="A342" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D342" s="7"/>
       <c r="E342" s="7"/>
-      <c r="F342" s="5" t="s">
+      <c r="F342" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G342" s="26"/>
     </row>
-    <row r="343" spans="1:7" ht="30">
+    <row r="343" spans="1:7" ht="45" customHeight="1">
       <c r="A343" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D343" s="7"/>
       <c r="E343" s="7"/>
-      <c r="F343" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G343" s="24"/>
-    </row>
-    <row r="344" spans="1:7" ht="30" customHeight="1">
+      <c r="F343" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G343" s="26"/>
+    </row>
+    <row r="344" spans="1:7" ht="30">
       <c r="A344" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D344" s="7"/>
       <c r="E344" s="7"/>
       <c r="F344" s="16" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G344" s="24"/>
     </row>
@@ -10037,10 +10053,10 @@
         <v>765</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="D345" s="7"/>
       <c r="E345" s="7"/>
@@ -10049,70 +10065,68 @@
       </c>
       <c r="G345" s="24"/>
     </row>
-    <row r="346" spans="1:7">
+    <row r="346" spans="1:7" ht="30" customHeight="1">
       <c r="A346" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D346" s="7"/>
-      <c r="E346" s="1"/>
-      <c r="F346" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G346" s="26"/>
+      <c r="E346" s="7"/>
+      <c r="F346" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G346" s="24"/>
     </row>
     <row r="347" spans="1:7">
       <c r="A347" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D347" s="7"/>
-      <c r="E347" s="7"/>
-      <c r="F347" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G347" s="26" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="348" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+      <c r="E347" s="1"/>
+      <c r="F347" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G347" s="26"/>
+    </row>
+    <row r="348" spans="1:7">
       <c r="A348" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D348" s="7"/>
       <c r="E348" s="7"/>
-      <c r="F348" s="4" t="s">
+      <c r="F348" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G348" s="26" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="349" spans="1:7" ht="45" customHeight="1">
+    <row r="349" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
       <c r="A349" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D349" s="7"/>
       <c r="E349" s="7"/>
@@ -10123,213 +10137,215 @@
         <v>846</v>
       </c>
     </row>
-    <row r="350" spans="1:7" ht="30" customHeight="1">
+    <row r="350" spans="1:7" ht="45" customHeight="1">
       <c r="A350" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D350" s="7"/>
-      <c r="E350" s="7" t="s">
-        <v>796</v>
-      </c>
-      <c r="F350" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G350" s="24"/>
-    </row>
-    <row r="351" spans="1:7" ht="45" customHeight="1">
+      <c r="E350" s="7"/>
+      <c r="F350" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G350" s="26" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="351" spans="1:7" ht="30" customHeight="1">
       <c r="A351" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D351" s="7"/>
-      <c r="E351" s="7"/>
-      <c r="F351" s="5" t="s">
-        <v>855</v>
-      </c>
-      <c r="G351" s="26"/>
+      <c r="E351" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="F351" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G351" s="24"/>
     </row>
     <row r="352" spans="1:7" ht="45" customHeight="1">
       <c r="A352" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>1006</v>
+        <v>853</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>1007</v>
+        <v>854</v>
       </c>
       <c r="D352" s="7"/>
       <c r="E352" s="7"/>
       <c r="F352" s="5" t="s">
-        <v>20</v>
+        <v>855</v>
       </c>
       <c r="G352" s="26"/>
     </row>
-    <row r="353" spans="1:7" ht="30">
+    <row r="353" spans="1:7" ht="45" customHeight="1">
       <c r="A353" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>856</v>
+        <v>1006</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>857</v>
+        <v>1007</v>
       </c>
       <c r="D353" s="7"/>
       <c r="E353" s="7"/>
       <c r="F353" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G353" s="26"/>
     </row>
-    <row r="354" spans="1:7" ht="30" customHeight="1">
+    <row r="354" spans="1:7" ht="30">
       <c r="A354" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D354" s="7"/>
       <c r="E354" s="7"/>
-      <c r="F354" s="16" t="s">
+      <c r="F354" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G354" s="24"/>
+      <c r="G354" s="26"/>
     </row>
     <row r="355" spans="1:7" ht="30" customHeight="1">
       <c r="A355" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="D355" s="7"/>
       <c r="E355" s="7"/>
-      <c r="F355" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G355" s="26" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="356" spans="1:7">
+      <c r="F355" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G355" s="24"/>
+    </row>
+    <row r="356" spans="1:7" ht="30" customHeight="1">
       <c r="A356" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="D356" s="7"/>
       <c r="E356" s="7"/>
-      <c r="F356" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G356" s="26"/>
+      <c r="F356" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G356" s="26" t="s">
+        <v>862</v>
+      </c>
     </row>
     <row r="357" spans="1:7">
       <c r="A357" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="D357" s="7"/>
       <c r="E357" s="7"/>
-      <c r="F357" s="4" t="s">
+      <c r="F357" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G357" s="26"/>
     </row>
-    <row r="358" spans="1:7" ht="30" customHeight="1">
+    <row r="358" spans="1:7">
       <c r="A358" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="D358" s="7"/>
       <c r="E358" s="7"/>
-      <c r="F358" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G358" s="26" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7">
+      <c r="F358" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G358" s="26"/>
+    </row>
+    <row r="359" spans="1:7" ht="30" customHeight="1">
       <c r="A359" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="D359" s="7"/>
       <c r="E359" s="7"/>
-      <c r="F359" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G359" s="26"/>
+      <c r="F359" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G359" s="26" t="s">
+        <v>869</v>
+      </c>
     </row>
     <row r="360" spans="1:7">
-      <c r="A360" t="s">
+      <c r="A360" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B360" t="s">
-        <v>872</v>
-      </c>
-      <c r="C360" t="s">
-        <v>873</v>
+      <c r="B360" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>871</v>
       </c>
       <c r="D360" s="7"/>
       <c r="E360" s="7"/>
       <c r="F360" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G360" s="26"/>
+    </row>
+    <row r="361" spans="1:7">
+      <c r="A361" t="s">
+        <v>765</v>
+      </c>
+      <c r="B361" t="s">
+        <v>872</v>
+      </c>
+      <c r="C361" t="s">
+        <v>873</v>
+      </c>
+      <c r="D361" s="7"/>
+      <c r="E361" s="7"/>
+      <c r="F361" s="12" t="s">
         <v>29</v>
-      </c>
-      <c r="G360" s="26"/>
-    </row>
-    <row r="361" spans="1:7">
-      <c r="A361" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="B361" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="C361" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="D361" s="7"/>
-      <c r="E361" s="1"/>
-      <c r="F361" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="G361" s="26"/>
     </row>
@@ -10338,15 +10354,15 @@
         <v>765</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D362" s="7"/>
-      <c r="E362" s="7"/>
+      <c r="E362" s="1"/>
       <c r="F362" s="5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G362" s="26"/>
     </row>
@@ -10355,17 +10371,15 @@
         <v>765</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>1008</v>
+        <v>876</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>1009</v>
+        <v>877</v>
       </c>
       <c r="D363" s="7"/>
-      <c r="E363" s="7" t="s">
-        <v>1010</v>
-      </c>
+      <c r="E363" s="7"/>
       <c r="F363" s="5" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G363" s="26"/>
     </row>
@@ -10374,15 +10388,17 @@
         <v>765</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>878</v>
+        <v>1008</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>879</v>
+        <v>1009</v>
       </c>
       <c r="D364" s="7"/>
-      <c r="E364" s="7"/>
-      <c r="F364" s="4" t="s">
-        <v>96</v>
+      <c r="E364" s="7" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F364" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G364" s="26"/>
     </row>
@@ -10391,118 +10407,118 @@
         <v>765</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D365" s="7"/>
-      <c r="E365" s="7" t="s">
-        <v>876</v>
-      </c>
-      <c r="F365" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G365" s="24"/>
+      <c r="E365" s="7"/>
+      <c r="F365" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G365" s="26"/>
     </row>
     <row r="366" spans="1:7">
       <c r="A366" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B366" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C366" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="D366" s="7"/>
+      <c r="E366" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="F366" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G366" s="24"/>
+    </row>
+    <row r="367" spans="1:7">
+      <c r="A367" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B367" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="C366" s="2" t="s">
+      <c r="C367" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="D366" s="7"/>
-      <c r="E366" s="7"/>
-      <c r="F366" s="16" t="s">
+      <c r="D367" s="7"/>
+      <c r="E367" s="7"/>
+      <c r="F367" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G366" s="24"/>
-    </row>
-    <row r="367" spans="1:7">
-      <c r="A367" s="17" t="s">
+      <c r="G367" s="24"/>
+    </row>
+    <row r="368" spans="1:7">
+      <c r="A368" s="17" t="s">
         <v>765</v>
       </c>
-      <c r="B367" s="17" t="s">
+      <c r="B368" s="17" t="s">
         <v>884</v>
       </c>
-      <c r="C367" s="17" t="s">
+      <c r="C368" s="17" t="s">
         <v>885</v>
       </c>
-      <c r="D367" s="27"/>
-      <c r="E367" s="27"/>
-      <c r="F367" s="20" t="s">
+      <c r="D368" s="27"/>
+      <c r="E368" s="27"/>
+      <c r="F368" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G367" s="28"/>
-    </row>
-    <row r="368" spans="1:7">
-      <c r="A368" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="B368" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="C368" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="D368" s="1"/>
-      <c r="E368" s="7"/>
-      <c r="F368" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G368" s="26" t="s">
-        <v>888</v>
-      </c>
+      <c r="G368" s="28"/>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="D369" s="1"/>
       <c r="E369" s="7"/>
       <c r="F369" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G369" s="26" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7" ht="30">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7">
       <c r="A370" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D370" s="1"/>
       <c r="E370" s="7"/>
       <c r="F370" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G370" s="26"/>
-    </row>
-    <row r="371" spans="1:7">
+        <v>14</v>
+      </c>
+      <c r="G370" s="26" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" ht="30">
       <c r="A371" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>1011</v>
+        <v>892</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1012</v>
+        <v>893</v>
       </c>
       <c r="D371" s="1"/>
       <c r="E371" s="7"/>
@@ -10516,15 +10532,13 @@
         <v>765</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="D372" s="1"/>
-      <c r="E372" s="7" t="s">
-        <v>772</v>
-      </c>
+      <c r="E372" s="7"/>
       <c r="F372" s="5" t="s">
         <v>29</v>
       </c>
@@ -10535,13 +10549,15 @@
         <v>765</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D373" s="1"/>
-      <c r="E373" s="7"/>
+      <c r="E373" s="7" t="s">
+        <v>772</v>
+      </c>
       <c r="F373" s="5" t="s">
         <v>29</v>
       </c>
@@ -10549,20 +10565,18 @@
     </row>
     <row r="374" spans="1:7">
       <c r="A374" s="2" t="s">
-        <v>894</v>
+        <v>765</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>895</v>
+        <v>1015</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="D374" s="7" t="s">
-        <v>897</v>
-      </c>
+        <v>1016</v>
+      </c>
+      <c r="D374" s="1"/>
       <c r="E374" s="7"/>
-      <c r="F374" s="25" t="s">
-        <v>20</v>
+      <c r="F374" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G374" s="26"/>
     </row>
@@ -10571,32 +10585,32 @@
         <v>894</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D375" s="7" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="E375" s="7"/>
-      <c r="F375" s="4" t="s">
+      <c r="F375" s="25" t="s">
         <v>20</v>
       </c>
       <c r="G375" s="26"/>
     </row>
-    <row r="376" spans="1:7" ht="30">
+    <row r="376" spans="1:7">
       <c r="A376" s="2" t="s">
         <v>894</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="D376" s="1" t="s">
-        <v>903</v>
+        <v>899</v>
+      </c>
+      <c r="D376" s="7" t="s">
+        <v>900</v>
       </c>
       <c r="E376" s="7"/>
       <c r="F376" s="4" t="s">
@@ -10605,52 +10619,52 @@
       <c r="G376" s="26"/>
     </row>
     <row r="377" spans="1:7" ht="30">
-      <c r="A377" s="17" t="s">
+      <c r="A377" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="B377" s="17" t="s">
+      <c r="B377" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D377" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="E377" s="7"/>
+      <c r="F377" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G377" s="26"/>
+    </row>
+    <row r="378" spans="1:7" ht="30">
+      <c r="A378" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="B378" s="17" t="s">
         <v>904</v>
       </c>
-      <c r="C377" s="17" t="s">
+      <c r="C378" s="17" t="s">
         <v>905</v>
       </c>
-      <c r="D377" s="27"/>
-      <c r="E377" s="27"/>
-      <c r="F377" s="18" t="s">
+      <c r="D378" s="27"/>
+      <c r="E378" s="27"/>
+      <c r="F378" s="18" t="s">
         <v>906</v>
       </c>
-      <c r="G377" s="28"/>
-    </row>
-    <row r="378" spans="1:7">
-      <c r="A378" t="s">
-        <v>894</v>
-      </c>
-      <c r="B378" t="s">
-        <v>907</v>
-      </c>
-      <c r="C378" t="s">
-        <v>908</v>
-      </c>
-      <c r="D378" s="7"/>
-      <c r="E378" s="7"/>
-      <c r="F378" t="s">
-        <v>29</v>
-      </c>
-      <c r="G378" s="26"/>
+      <c r="G378" s="28"/>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" t="s">
         <v>894</v>
       </c>
       <c r="B379" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C379" t="s">
-        <v>910</v>
-      </c>
-      <c r="D379" s="7" t="s">
-        <v>911</v>
-      </c>
+        <v>908</v>
+      </c>
+      <c r="D379" s="7"/>
       <c r="E379" s="7"/>
       <c r="F379" t="s">
         <v>29</v>
@@ -10662,24 +10676,43 @@
         <v>894</v>
       </c>
       <c r="B380" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C380" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D380" s="7" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="E380" s="7"/>
       <c r="F380" t="s">
+        <v>29</v>
+      </c>
+      <c r="G380" s="26"/>
+    </row>
+    <row r="381" spans="1:7">
+      <c r="A381" t="s">
+        <v>894</v>
+      </c>
+      <c r="B381" t="s">
+        <v>912</v>
+      </c>
+      <c r="C381" t="s">
+        <v>913</v>
+      </c>
+      <c r="D381" s="7" t="s">
+        <v>914</v>
+      </c>
+      <c r="E381" s="7"/>
+      <c r="F381" t="s">
         <v>20</v>
       </c>
-      <c r="G380" s="26"/>
-    </row>
-    <row r="381" spans="1:7">
-      <c r="D381" s="7"/>
-      <c r="E381" s="7"/>
       <c r="G381" s="26"/>
+    </row>
+    <row r="382" spans="1:7">
+      <c r="D382" s="7"/>
+      <c r="E382" s="7"/>
+      <c r="G382" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-develop\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\.claude\worktrees\cement-onto-robbie\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCAB845F-F13E-4CF2-A244-FC7B5E47D5C0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9437FD38-AFFB-4F98-B00B-B033C273205A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2340" yWindow="2340" windowWidth="43200" windowHeight="17085" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1781" uniqueCount="1017">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="1044">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -3024,9 +3024,6 @@
     <t>Cement Kiln Fuel Shift Recipient Fractions</t>
   </si>
   <si>
-    <t>Where each fossil kiln fuel's shifted energy goes under the kiln fuel shift policy. The US file sends every fossil fuel to alternative fuels; edit the rows for regions whose kiln-fuel policy converts kilns to gas or co-fires hydrogen.</t>
-  </si>
-  <si>
     <t>BCPCS</t>
   </si>
   <si>
@@ -3073,13 +3070,97 @@
   </si>
   <si>
     <t>Vehicle Weibull Shape Parameter by Vintage</t>
+  </si>
+  <si>
+    <t>Which fuel replaces each fossil kiln fuel under the kiln fuel shift lever (a fuel-to-fuel matrix over the industrial fuel list; US: every fossil fuel to biomass, which carries alternative fuels). Change the rows for coal-to-gas or hydrogen kiln programs.</t>
+  </si>
+  <si>
+    <t>BCAF</t>
+  </si>
+  <si>
+    <t>BAU Cement Carbon Price Allocation Fraction</t>
+  </si>
+  <si>
+    <t>Share of the cement carbon-price bill already handed back against output under policies in place (free allocation in an ETS). Zero for the US; enter the regional free-allocation share and its phase-down.</t>
+  </si>
+  <si>
+    <t>CABI</t>
+  </si>
+  <si>
+    <t>Cement Allocation Benchmark Intensity</t>
+  </si>
+  <si>
+    <t>Benchmark clinker CO2 intensity for output-based allocation: the official ETS benchmark where one exists (EU 0.656 from 2026), otherwise the regional median plant intensity (US: EPA 2019 median 0.838).</t>
+  </si>
+  <si>
+    <t>CCTS</t>
+  </si>
+  <si>
+    <t>Cement CCfD Two Sided Share</t>
+  </si>
+  <si>
+    <t>Share of cement carbon contracts for difference that pay back the excess when the carbon price passes the strike (1 = German two-sided design, 0 = Dutch one-sided). Only matters when the contract lever is used.</t>
+  </si>
+  <si>
+    <t>CDSC</t>
+  </si>
+  <si>
+    <t>Cement Direct Separation Capture Inputs</t>
+  </si>
+  <si>
+    <t>Capture capital, operating cost and electricity for the electric kiln with CCS (purification and compression of a nearly pure CO2 stream). Only matters once that pathway is built.</t>
+  </si>
+  <si>
+    <t>CIBP</t>
+  </si>
+  <si>
+    <t>Cement Import Border Fee Parameters</t>
+  </si>
+  <si>
+    <t>Import CO2 intensity, delivered import price and Armington elasticity for the cement border fee lever. Replace with regional trade data (USGS-type import statistics, JRC or GCCA intensities); the elasticity can stay.</t>
+  </si>
+  <si>
+    <t>CSBS</t>
+  </si>
+  <si>
+    <t>Cement Share of Start Year Capacity Below Standard</t>
+  </si>
+  <si>
+    <t>Share of start-year kiln capacity below a precalciner-grade energy standard, by pathway (US 0.09 from kiln-type shares; China about 0.16). Only matters when the kiln performance standard lever is used.</t>
+  </si>
+  <si>
+    <t>CSCC</t>
+  </si>
+  <si>
+    <t>Cement Calcined Clay Capital Inputs</t>
+  </si>
+  <si>
+    <t>Calcined clay plant capital per tonne of annual capacity and the calcined clay share of clinker substitution. Only matters when a policy raises clinker substitution.</t>
+  </si>
+  <si>
+    <t>LCCT</t>
+  </si>
+  <si>
+    <t>Low Carbon Cement Credit Threshold as Share of Fleet CO2 Intensity</t>
+  </si>
+  <si>
+    <t>Share of last year's fleet-average CO2 intensity at or below which cement earns the production tax credit lever (US: 40 percent below the benchmark, 0.6). Only matters when that lever is used.</t>
+  </si>
+  <si>
+    <t>LCPT</t>
+  </si>
+  <si>
+    <t>Low Carbon Procurement Threshold as Share of Fleet CO2 Intensity</t>
+  </si>
+  <si>
+    <t>Share of last year's fleet-average CO2 intensity at or below which cement counts as low-carbon for the procurement lever (US: GSA best-20-percent limit over the PCA industry-average declaration, 0.817). Only matters when that lever is used.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3556,82 +3637,82 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="16" spans="1:1">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="17" spans="1:3">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>928</v>
       </c>
     </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>10</v>
       </c>
@@ -3639,32 +3720,32 @@
         <v>929</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B20" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B21" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="23" spans="1:3">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B23" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="24" spans="1:3">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B24" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
         <v>37</v>
       </c>
@@ -3672,17 +3753,17 @@
         <v>935</v>
       </c>
     </row>
-    <row r="27" spans="1:3">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="28" spans="1:3">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="30" spans="1:3">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>20</v>
       </c>
@@ -3690,42 +3771,42 @@
         <v>938</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B32" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B34" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="36" spans="1:3">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="37" spans="1:3">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>29</v>
       </c>
@@ -3733,84 +3814,84 @@
         <v>946</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B40" t="s">
         <v>947</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B41" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B42" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B43" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B44" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="45" spans="1:3">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B45" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="46" spans="1:3">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B46" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B50" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B51" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B52" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B53" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="54" spans="1:2">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B54" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="55" spans="1:2">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B55" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>25</v>
       </c>
@@ -3818,62 +3899,62 @@
         <v>961</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B58" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B59" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B60" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" s="7" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>970</v>
       </c>
     </row>
-    <row r="68" spans="1:1">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>971</v>
       </c>
     </row>
-    <row r="69" spans="1:1">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>972</v>
       </c>
     </row>
-    <row r="70" spans="1:1">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>973</v>
       </c>
@@ -3886,8 +3967,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G381"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <dimension ref="A1:G390"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" style="2" customWidth="1"/>
@@ -3900,7 +3981,7 @@
     <col min="10" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -3923,7 +4004,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1">
+    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -3942,7 +4023,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -3961,7 +4042,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -3980,7 +4061,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -3997,7 +4078,7 @@
       </c>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -4014,7 +4095,7 @@
       </c>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -4033,7 +4114,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -4050,7 +4131,7 @@
       </c>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>7</v>
       </c>
@@ -4067,7 +4148,7 @@
       </c>
       <c r="G9" s="28"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -4084,7 +4165,7 @@
       </c>
       <c r="G10" s="26"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -4101,7 +4182,7 @@
       </c>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -4118,7 +4199,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
@@ -4135,7 +4216,7 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -4154,7 +4235,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -4171,7 +4252,7 @@
       </c>
       <c r="G15" s="26"/>
     </row>
-    <row r="16" spans="1:7" ht="45" customHeight="1">
+    <row r="16" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -4190,7 +4271,7 @@
       </c>
       <c r="G16" s="26"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -4209,7 +4290,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -4226,7 +4307,7 @@
       </c>
       <c r="G18" s="26"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>32</v>
       </c>
@@ -4245,7 +4326,7 @@
       </c>
       <c r="G19" s="26"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
@@ -4262,7 +4343,7 @@
       </c>
       <c r="G20" s="26"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
@@ -4279,7 +4360,7 @@
       </c>
       <c r="G21" s="26"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
@@ -4296,7 +4377,7 @@
       </c>
       <c r="G22" s="26"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>32</v>
       </c>
@@ -4313,7 +4394,7 @@
       </c>
       <c r="G23" s="26"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -4330,7 +4411,7 @@
       </c>
       <c r="G24" s="26"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>32</v>
       </c>
@@ -4347,7 +4428,7 @@
       </c>
       <c r="G25" s="26"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>32</v>
       </c>
@@ -4364,7 +4445,7 @@
       </c>
       <c r="G26" s="26"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -4383,7 +4464,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
@@ -4400,7 +4481,7 @@
       </c>
       <c r="G28" s="26"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
@@ -4419,7 +4500,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -4436,7 +4517,7 @@
       </c>
       <c r="G30" s="26"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>32</v>
       </c>
@@ -4453,7 +4534,7 @@
       </c>
       <c r="G31" s="26"/>
     </row>
-    <row r="32" spans="1:7" ht="45" customHeight="1">
+    <row r="32" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -4472,7 +4553,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
@@ -4491,7 +4572,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -4508,7 +4589,7 @@
       </c>
       <c r="G34" s="24"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>32</v>
       </c>
@@ -4525,7 +4606,7 @@
       </c>
       <c r="G35" s="26"/>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -4542,7 +4623,7 @@
       </c>
       <c r="G36" s="26"/>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>32</v>
       </c>
@@ -4559,7 +4640,7 @@
       </c>
       <c r="G37" s="26"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>32</v>
       </c>
@@ -4576,7 +4657,7 @@
       </c>
       <c r="G38" s="26"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>32</v>
       </c>
@@ -4595,7 +4676,7 @@
       </c>
       <c r="G39" s="26"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
         <v>32</v>
       </c>
@@ -4614,7 +4695,7 @@
       </c>
       <c r="G40" s="28"/>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>104</v>
       </c>
@@ -4631,7 +4712,7 @@
       </c>
       <c r="G41" s="26"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>104</v>
       </c>
@@ -4650,7 +4731,7 @@
       </c>
       <c r="G42" s="26"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>104</v>
       </c>
@@ -4667,7 +4748,7 @@
       </c>
       <c r="G43" s="26"/>
     </row>
-    <row r="44" spans="1:7" ht="120" customHeight="1">
+    <row r="44" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>104</v>
       </c>
@@ -4686,7 +4767,7 @@
       </c>
       <c r="G44" s="26"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>104</v>
       </c>
@@ -4705,7 +4786,7 @@
       </c>
       <c r="G45" s="26"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>104</v>
       </c>
@@ -4722,7 +4803,7 @@
       </c>
       <c r="G46" s="26"/>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>104</v>
       </c>
@@ -4739,7 +4820,7 @@
       </c>
       <c r="G47" s="26"/>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>104</v>
       </c>
@@ -4756,7 +4837,7 @@
       </c>
       <c r="G48" s="26"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>104</v>
       </c>
@@ -4775,7 +4856,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>104</v>
       </c>
@@ -4792,7 +4873,7 @@
       </c>
       <c r="G50" s="26"/>
     </row>
-    <row r="51" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
+    <row r="51" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
         <v>104</v>
       </c>
@@ -4809,7 +4890,7 @@
       </c>
       <c r="G51" s="26"/>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>131</v>
       </c>
@@ -4826,7 +4907,7 @@
       </c>
       <c r="G52" s="26"/>
     </row>
-    <row r="53" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="53" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
         <v>131</v>
       </c>
@@ -4845,7 +4926,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="54" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
         <v>137</v>
       </c>
@@ -4864,7 +4945,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="60" customHeight="1">
+    <row r="55" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>141</v>
       </c>
@@ -4883,7 +4964,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>141</v>
       </c>
@@ -4902,7 +4983,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="60" customHeight="1">
+    <row r="57" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>141</v>
       </c>
@@ -4921,7 +5002,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="60" customHeight="1">
+    <row r="58" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>141</v>
       </c>
@@ -4940,7 +5021,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="45" customHeight="1">
+    <row r="59" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>141</v>
       </c>
@@ -4959,7 +5040,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="60" customHeight="1">
+    <row r="60" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>141</v>
       </c>
@@ -4978,7 +5059,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="60" customHeight="1">
+    <row r="61" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>141</v>
       </c>
@@ -4997,7 +5078,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="60" customHeight="1">
+    <row r="62" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>141</v>
       </c>
@@ -5016,7 +5097,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="45" customHeight="1">
+    <row r="63" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>141</v>
       </c>
@@ -5035,7 +5116,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="30" customHeight="1">
+    <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>141</v>
       </c>
@@ -5054,7 +5135,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="30" customHeight="1">
+    <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>141</v>
       </c>
@@ -5073,7 +5154,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="60" customHeight="1">
+    <row r="66" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>141</v>
       </c>
@@ -5092,7 +5173,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="30" customHeight="1">
+    <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>141</v>
       </c>
@@ -5109,7 +5190,7 @@
       </c>
       <c r="G67" s="26"/>
     </row>
-    <row r="68" spans="1:7" ht="45" customHeight="1">
+    <row r="68" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>141</v>
       </c>
@@ -5128,7 +5209,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="90" customHeight="1">
+    <row r="69" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>141</v>
       </c>
@@ -5149,7 +5230,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="45" customHeight="1">
+    <row r="70" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>141</v>
       </c>
@@ -5170,7 +5251,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>141</v>
       </c>
@@ -5187,7 +5268,7 @@
       </c>
       <c r="G71" s="26"/>
     </row>
-    <row r="72" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="72" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
         <v>141</v>
       </c>
@@ -5204,7 +5285,7 @@
       </c>
       <c r="G72" s="28"/>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>196</v>
       </c>
@@ -5221,7 +5302,7 @@
       </c>
       <c r="G73" s="26"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>196</v>
       </c>
@@ -5238,7 +5319,7 @@
       </c>
       <c r="G74" s="26"/>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>196</v>
       </c>
@@ -5255,7 +5336,7 @@
       </c>
       <c r="G75" s="26"/>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>196</v>
       </c>
@@ -5272,7 +5353,7 @@
       </c>
       <c r="G76" s="26"/>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>196</v>
       </c>
@@ -5289,7 +5370,7 @@
       </c>
       <c r="G77" s="26"/>
     </row>
-    <row r="78" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="78" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="17" t="s">
         <v>196</v>
       </c>
@@ -5308,7 +5389,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>210</v>
       </c>
@@ -5325,7 +5406,7 @@
       </c>
       <c r="G79" s="26"/>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>210</v>
       </c>
@@ -5342,7 +5423,7 @@
       </c>
       <c r="G80" s="26"/>
     </row>
-    <row r="81" spans="1:7" ht="45" customHeight="1">
+    <row r="81" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>210</v>
       </c>
@@ -5361,7 +5442,7 @@
       </c>
       <c r="G81" s="26"/>
     </row>
-    <row r="82" spans="1:7" ht="30" customHeight="1">
+    <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>210</v>
       </c>
@@ -5380,7 +5461,7 @@
       </c>
       <c r="G82" s="26"/>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>210</v>
       </c>
@@ -5397,7 +5478,7 @@
       </c>
       <c r="G83" s="26"/>
     </row>
-    <row r="84" spans="1:7" ht="30" customHeight="1">
+    <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>210</v>
       </c>
@@ -5414,7 +5495,7 @@
       </c>
       <c r="G84" s="26"/>
     </row>
-    <row r="85" spans="1:7" ht="45" customHeight="1">
+    <row r="85" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>210</v>
       </c>
@@ -5433,7 +5514,7 @@
       </c>
       <c r="G85" s="26"/>
     </row>
-    <row r="86" spans="1:7" ht="45" customHeight="1">
+    <row r="86" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>210</v>
       </c>
@@ -5452,7 +5533,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
@@ -5471,7 +5552,7 @@
       </c>
       <c r="G87" s="26"/>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>210</v>
       </c>
@@ -5488,7 +5569,7 @@
       </c>
       <c r="G88" s="26"/>
     </row>
-    <row r="89" spans="1:7" ht="75" customHeight="1">
+    <row r="89" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>210</v>
       </c>
@@ -5507,7 +5588,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="75" customHeight="1">
+    <row r="90" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>210</v>
       </c>
@@ -5526,7 +5607,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>210</v>
       </c>
@@ -5543,7 +5624,7 @@
       </c>
       <c r="G91" s="26"/>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>210</v>
       </c>
@@ -5560,7 +5641,7 @@
       </c>
       <c r="G92" s="26"/>
     </row>
-    <row r="93" spans="1:7" ht="30" customHeight="1">
+    <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>210</v>
       </c>
@@ -5577,7 +5658,7 @@
       </c>
       <c r="G93" s="26"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>210</v>
       </c>
@@ -5598,7 +5679,7 @@
       </c>
       <c r="G94" s="26"/>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>210</v>
       </c>
@@ -5615,7 +5696,7 @@
       </c>
       <c r="G95" s="26"/>
     </row>
-    <row r="96" spans="1:7" ht="30" customHeight="1">
+    <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>210</v>
       </c>
@@ -5632,7 +5713,7 @@
       </c>
       <c r="G96" s="26"/>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>210</v>
       </c>
@@ -5649,7 +5730,7 @@
       </c>
       <c r="G97" s="26"/>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>210</v>
       </c>
@@ -5666,7 +5747,7 @@
       </c>
       <c r="G98" s="26"/>
     </row>
-    <row r="99" spans="1:7" ht="75" customHeight="1">
+    <row r="99" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>210</v>
       </c>
@@ -5685,7 +5766,7 @@
       </c>
       <c r="G99" s="26"/>
     </row>
-    <row r="100" spans="1:7" ht="30" customHeight="1">
+    <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>210</v>
       </c>
@@ -5702,7 +5783,7 @@
       </c>
       <c r="G100" s="26"/>
     </row>
-    <row r="101" spans="1:7" ht="75" customHeight="1">
+    <row r="101" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>210</v>
       </c>
@@ -5721,7 +5802,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>210</v>
       </c>
@@ -5738,7 +5819,7 @@
       </c>
       <c r="G102" s="26"/>
     </row>
-    <row r="103" spans="1:7" ht="90" customHeight="1">
+    <row r="103" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>210</v>
       </c>
@@ -5757,7 +5838,7 @@
       </c>
       <c r="G103" s="26"/>
     </row>
-    <row r="104" spans="1:7" ht="30" customHeight="1">
+    <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>210</v>
       </c>
@@ -5774,7 +5855,7 @@
       </c>
       <c r="G104" s="26"/>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>210</v>
       </c>
@@ -5791,7 +5872,7 @@
       </c>
       <c r="G105" s="26"/>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>210</v>
       </c>
@@ -5808,7 +5889,7 @@
       </c>
       <c r="G106" s="26"/>
     </row>
-    <row r="107" spans="1:7" ht="30" customHeight="1">
+    <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>210</v>
       </c>
@@ -5827,7 +5908,7 @@
       </c>
       <c r="G107" s="26"/>
     </row>
-    <row r="108" spans="1:7" ht="30" customHeight="1">
+    <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>210</v>
       </c>
@@ -5846,7 +5927,7 @@
       </c>
       <c r="G108" s="26"/>
     </row>
-    <row r="109" spans="1:7" ht="30" customHeight="1">
+    <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>210</v>
       </c>
@@ -5865,7 +5946,7 @@
       </c>
       <c r="G109" s="26"/>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>210</v>
       </c>
@@ -5884,7 +5965,7 @@
       </c>
       <c r="G110" s="26"/>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>210</v>
       </c>
@@ -5901,7 +5982,7 @@
       </c>
       <c r="G111" s="26"/>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>210</v>
       </c>
@@ -5918,7 +5999,7 @@
       </c>
       <c r="G112" s="26"/>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>210</v>
       </c>
@@ -5935,7 +6016,7 @@
       </c>
       <c r="G113" s="26"/>
     </row>
-    <row r="114" spans="1:7" ht="30" customHeight="1">
+    <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>210</v>
       </c>
@@ -5954,7 +6035,7 @@
       </c>
       <c r="G114" s="26"/>
     </row>
-    <row r="115" spans="1:7" ht="60" customHeight="1">
+    <row r="115" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>210</v>
       </c>
@@ -5973,7 +6054,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>210</v>
       </c>
@@ -5990,7 +6071,7 @@
       </c>
       <c r="G116" s="26"/>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>210</v>
       </c>
@@ -6009,7 +6090,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="30" customHeight="1">
+    <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>210</v>
       </c>
@@ -6026,7 +6107,7 @@
       </c>
       <c r="G118" s="26"/>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>210</v>
       </c>
@@ -6043,7 +6124,7 @@
       </c>
       <c r="G119" s="26"/>
     </row>
-    <row r="120" spans="1:7" ht="30" customHeight="1">
+    <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>210</v>
       </c>
@@ -6060,7 +6141,7 @@
       </c>
       <c r="G120" s="26"/>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>210</v>
       </c>
@@ -6077,7 +6158,7 @@
       </c>
       <c r="G121" s="26"/>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>210</v>
       </c>
@@ -6094,7 +6175,7 @@
       </c>
       <c r="G122" s="26"/>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>210</v>
       </c>
@@ -6111,7 +6192,7 @@
       </c>
       <c r="G123" s="26"/>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>210</v>
       </c>
@@ -6128,7 +6209,7 @@
       </c>
       <c r="G124" s="26"/>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>210</v>
       </c>
@@ -6145,7 +6226,7 @@
       </c>
       <c r="G125" s="26"/>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>210</v>
       </c>
@@ -6162,7 +6243,7 @@
       </c>
       <c r="G126" s="26"/>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>210</v>
       </c>
@@ -6179,7 +6260,7 @@
       </c>
       <c r="G127" s="26"/>
     </row>
-    <row r="128" spans="1:7" ht="60" customHeight="1">
+    <row r="128" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>210</v>
       </c>
@@ -6198,7 +6279,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="60" customHeight="1">
+    <row r="129" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>210</v>
       </c>
@@ -6217,7 +6298,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="30" customHeight="1">
+    <row r="130" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>210</v>
       </c>
@@ -6236,7 +6317,7 @@
       </c>
       <c r="G130" s="26"/>
     </row>
-    <row r="131" spans="1:7" ht="45" customHeight="1">
+    <row r="131" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>210</v>
       </c>
@@ -6255,7 +6336,7 @@
       </c>
       <c r="G131" s="26"/>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>210</v>
       </c>
@@ -6272,7 +6353,7 @@
       </c>
       <c r="G132" s="26"/>
     </row>
-    <row r="133" spans="1:7" ht="30" customHeight="1">
+    <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>210</v>
       </c>
@@ -6289,7 +6370,7 @@
       </c>
       <c r="G133" s="26"/>
     </row>
-    <row r="134" spans="1:7" ht="30" customHeight="1">
+    <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>210</v>
       </c>
@@ -6308,7 +6389,7 @@
       </c>
       <c r="G134" s="26"/>
     </row>
-    <row r="135" spans="1:7" ht="45" customHeight="1">
+    <row r="135" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>210</v>
       </c>
@@ -6327,7 +6408,7 @@
       </c>
       <c r="G135" s="26"/>
     </row>
-    <row r="136" spans="1:7" ht="30" customHeight="1">
+    <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>210</v>
       </c>
@@ -6348,7 +6429,7 @@
       </c>
       <c r="G136" s="26"/>
     </row>
-    <row r="137" spans="1:7" ht="30" customHeight="1">
+    <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>210</v>
       </c>
@@ -6365,7 +6446,7 @@
       </c>
       <c r="G137" s="26"/>
     </row>
-    <row r="138" spans="1:7" ht="45" customHeight="1">
+    <row r="138" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>210</v>
       </c>
@@ -6384,7 +6465,7 @@
       </c>
       <c r="G138" s="26"/>
     </row>
-    <row r="139" spans="1:7" ht="30" customHeight="1">
+    <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>210</v>
       </c>
@@ -6401,7 +6482,7 @@
       </c>
       <c r="G139" s="26"/>
     </row>
-    <row r="140" spans="1:7" ht="30" customHeight="1">
+    <row r="140" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>210</v>
       </c>
@@ -6418,7 +6499,7 @@
       </c>
       <c r="G140" s="26"/>
     </row>
-    <row r="141" spans="1:7" ht="30" customHeight="1">
+    <row r="141" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>210</v>
       </c>
@@ -6435,7 +6516,7 @@
       </c>
       <c r="G141" s="26"/>
     </row>
-    <row r="142" spans="1:7" ht="30" customHeight="1">
+    <row r="142" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>210</v>
       </c>
@@ -6452,7 +6533,7 @@
       </c>
       <c r="G142" s="26"/>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>210</v>
       </c>
@@ -6469,7 +6550,7 @@
       </c>
       <c r="G143" s="26"/>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>210</v>
       </c>
@@ -6488,7 +6569,7 @@
       </c>
       <c r="G144" s="26"/>
     </row>
-    <row r="145" spans="1:7" ht="30" customHeight="1">
+    <row r="145" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>210</v>
       </c>
@@ -6507,7 +6588,7 @@
       </c>
       <c r="G145" s="26"/>
     </row>
-    <row r="146" spans="1:7" ht="30" customHeight="1">
+    <row r="146" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>210</v>
       </c>
@@ -6524,7 +6605,7 @@
       </c>
       <c r="G146" s="26"/>
     </row>
-    <row r="147" spans="1:7" ht="30" customHeight="1">
+    <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>210</v>
       </c>
@@ -6543,7 +6624,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="30">
+    <row r="148" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>210</v>
       </c>
@@ -6560,7 +6641,7 @@
       </c>
       <c r="G148" s="26"/>
     </row>
-    <row r="149" spans="1:7" ht="60.75" customHeight="1" thickBot="1">
+    <row r="149" spans="1:7" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>210</v>
       </c>
@@ -6577,7 +6658,7 @@
       </c>
       <c r="G149" s="26"/>
     </row>
-    <row r="150" spans="1:7" ht="30" customHeight="1">
+    <row r="150" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="17" t="s">
         <v>210</v>
       </c>
@@ -6598,7 +6679,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="30" customHeight="1">
+    <row r="151" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>388</v>
       </c>
@@ -6617,7 +6698,7 @@
       </c>
       <c r="G151" s="26"/>
     </row>
-    <row r="152" spans="1:7" ht="30" customHeight="1">
+    <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>388</v>
       </c>
@@ -6636,7 +6717,7 @@
       </c>
       <c r="G152" s="26"/>
     </row>
-    <row r="153" spans="1:7" ht="30" customHeight="1">
+    <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>388</v>
       </c>
@@ -6653,7 +6734,7 @@
       </c>
       <c r="G153" s="26"/>
     </row>
-    <row r="154" spans="1:7" ht="30">
+    <row r="154" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>388</v>
       </c>
@@ -6670,7 +6751,7 @@
       </c>
       <c r="G154" s="26"/>
     </row>
-    <row r="155" spans="1:7" ht="30" customHeight="1">
+    <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>388</v>
       </c>
@@ -6687,7 +6768,7 @@
       </c>
       <c r="G155" s="26"/>
     </row>
-    <row r="156" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="156" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>388</v>
       </c>
@@ -6704,7 +6785,7 @@
       </c>
       <c r="G156" s="26"/>
     </row>
-    <row r="157" spans="1:7" ht="30">
+    <row r="157" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
         <v>388</v>
       </c>
@@ -6721,7 +6802,7 @@
       </c>
       <c r="G157" s="28"/>
     </row>
-    <row r="158" spans="1:7" ht="30" customHeight="1">
+    <row r="158" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>405</v>
       </c>
@@ -6738,7 +6819,7 @@
       </c>
       <c r="G158" s="26"/>
     </row>
-    <row r="159" spans="1:7" ht="30" customHeight="1">
+    <row r="159" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>405</v>
       </c>
@@ -6755,7 +6836,7 @@
       </c>
       <c r="G159" s="26"/>
     </row>
-    <row r="160" spans="1:7" ht="30" customHeight="1">
+    <row r="160" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>405</v>
       </c>
@@ -6772,7 +6853,7 @@
       </c>
       <c r="G160" s="26"/>
     </row>
-    <row r="161" spans="1:7" ht="30" customHeight="1">
+    <row r="161" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>405</v>
       </c>
@@ -6789,7 +6870,7 @@
       </c>
       <c r="G161" s="26"/>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>405</v>
       </c>
@@ -6808,7 +6889,7 @@
       </c>
       <c r="G162" s="26"/>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>405</v>
       </c>
@@ -6825,7 +6906,7 @@
       </c>
       <c r="G163" s="26"/>
     </row>
-    <row r="164" spans="1:7" ht="45" customHeight="1">
+    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>405</v>
       </c>
@@ -6842,7 +6923,7 @@
       </c>
       <c r="G164" s="26"/>
     </row>
-    <row r="165" spans="1:7" ht="45">
+    <row r="165" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>405</v>
       </c>
@@ -6861,7 +6942,7 @@
       </c>
       <c r="G165" s="26"/>
     </row>
-    <row r="166" spans="1:7" ht="30" customHeight="1">
+    <row r="166" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>405</v>
       </c>
@@ -6878,7 +6959,7 @@
       </c>
       <c r="G166" s="26"/>
     </row>
-    <row r="167" spans="1:7" ht="30">
+    <row r="167" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>405</v>
       </c>
@@ -6895,7 +6976,7 @@
       </c>
       <c r="G167" s="26"/>
     </row>
-    <row r="168" spans="1:7" ht="30" customHeight="1">
+    <row r="168" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>405</v>
       </c>
@@ -6912,7 +6993,7 @@
       </c>
       <c r="G168" s="26"/>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>405</v>
       </c>
@@ -6931,7 +7012,7 @@
       </c>
       <c r="G169" s="26"/>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>405</v>
       </c>
@@ -6948,7 +7029,7 @@
       </c>
       <c r="G170" s="26"/>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>405</v>
       </c>
@@ -6965,7 +7046,7 @@
       </c>
       <c r="G171" s="26"/>
     </row>
-    <row r="172" spans="1:7" ht="30" customHeight="1">
+    <row r="172" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>405</v>
       </c>
@@ -6982,7 +7063,7 @@
       </c>
       <c r="G172" s="26"/>
     </row>
-    <row r="173" spans="1:7" ht="30">
+    <row r="173" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>405</v>
       </c>
@@ -7001,7 +7082,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="30" customHeight="1">
+    <row r="174" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>405</v>
       </c>
@@ -7018,7 +7099,7 @@
       </c>
       <c r="G174" s="26"/>
     </row>
-    <row r="175" spans="1:7" ht="30" customHeight="1">
+    <row r="175" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>405</v>
       </c>
@@ -7037,7 +7118,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="30" customHeight="1">
+    <row r="176" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>405</v>
       </c>
@@ -7056,7 +7137,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="45" customHeight="1">
+    <row r="177" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>405</v>
       </c>
@@ -7075,7 +7156,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="60" customHeight="1">
+    <row r="178" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>405</v>
       </c>
@@ -7094,7 +7175,7 @@
       </c>
       <c r="G178" s="26"/>
     </row>
-    <row r="179" spans="1:7" ht="45" customHeight="1">
+    <row r="179" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>405</v>
       </c>
@@ -7113,7 +7194,7 @@
       </c>
       <c r="G179" s="26"/>
     </row>
-    <row r="180" spans="1:7" ht="30" customHeight="1">
+    <row r="180" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>405</v>
       </c>
@@ -7130,7 +7211,7 @@
       </c>
       <c r="G180" s="26"/>
     </row>
-    <row r="181" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1">
+    <row r="181" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>405</v>
       </c>
@@ -7149,7 +7230,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="30" customHeight="1">
+    <row r="182" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="17" t="s">
         <v>405</v>
       </c>
@@ -7168,7 +7249,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="183" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
+    <row r="183" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>467</v>
       </c>
@@ -7187,7 +7268,7 @@
       </c>
       <c r="G183" s="26"/>
     </row>
-    <row r="184" spans="1:7" ht="30" customHeight="1">
+    <row r="184" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="17" t="s">
         <v>471</v>
       </c>
@@ -7206,7 +7287,7 @@
       </c>
       <c r="G184" s="26"/>
     </row>
-    <row r="185" spans="1:7" ht="30" customHeight="1">
+    <row r="185" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>475</v>
       </c>
@@ -7223,7 +7304,7 @@
       </c>
       <c r="G185" s="26"/>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>475</v>
       </c>
@@ -7240,7 +7321,7 @@
       </c>
       <c r="G186" s="26"/>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>475</v>
       </c>
@@ -7257,7 +7338,7 @@
       </c>
       <c r="G187" s="26"/>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>475</v>
       </c>
@@ -7274,7 +7355,7 @@
       </c>
       <c r="G188" s="26"/>
     </row>
-    <row r="189" spans="1:7" ht="30" customHeight="1">
+    <row r="189" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>475</v>
       </c>
@@ -7291,7 +7372,7 @@
       </c>
       <c r="G189" s="26"/>
     </row>
-    <row r="190" spans="1:7" ht="30">
+    <row r="190" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>475</v>
       </c>
@@ -7310,7 +7391,7 @@
       </c>
       <c r="G190" s="26"/>
     </row>
-    <row r="191" spans="1:7" ht="30" customHeight="1">
+    <row r="191" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>475</v>
       </c>
@@ -7327,7 +7408,7 @@
       </c>
       <c r="G191" s="26"/>
     </row>
-    <row r="192" spans="1:7" ht="30">
+    <row r="192" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>475</v>
       </c>
@@ -7344,7 +7425,7 @@
       </c>
       <c r="G192" s="26"/>
     </row>
-    <row r="193" spans="1:7" ht="30" customHeight="1">
+    <row r="193" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>475</v>
       </c>
@@ -7361,7 +7442,7 @@
       </c>
       <c r="G193" s="26"/>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>475</v>
       </c>
@@ -7380,7 +7461,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="30" customHeight="1">
+    <row r="195" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>475</v>
       </c>
@@ -7397,7 +7478,7 @@
       </c>
       <c r="G195" s="26"/>
     </row>
-    <row r="196" spans="1:7" ht="30" customHeight="1">
+    <row r="196" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>475</v>
       </c>
@@ -7414,7 +7495,7 @@
       </c>
       <c r="G196" s="26"/>
     </row>
-    <row r="197" spans="1:7" ht="30" customHeight="1">
+    <row r="197" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>475</v>
       </c>
@@ -7431,7 +7512,7 @@
       </c>
       <c r="G197" s="26"/>
     </row>
-    <row r="198" spans="1:7" ht="30" customHeight="1">
+    <row r="198" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>475</v>
       </c>
@@ -7448,7 +7529,7 @@
       </c>
       <c r="G198" s="26"/>
     </row>
-    <row r="199" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
+    <row r="199" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>475</v>
       </c>
@@ -7465,7 +7546,7 @@
       </c>
       <c r="G199" s="26"/>
     </row>
-    <row r="200" spans="1:7" ht="30">
+    <row r="200" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="17" t="s">
         <v>475</v>
       </c>
@@ -7482,322 +7563,324 @@
       </c>
       <c r="G200" s="26"/>
     </row>
-    <row r="201" spans="1:7" ht="30" customHeight="1">
+    <row r="201" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>510</v>
       </c>
       <c r="B201" t="s">
-        <v>511</v>
+        <v>1017</v>
       </c>
       <c r="C201" t="s">
-        <v>512</v>
+        <v>1018</v>
       </c>
       <c r="D201" s="7"/>
       <c r="E201" s="7"/>
       <c r="F201" t="s">
+        <v>20</v>
+      </c>
+      <c r="G201" s="26" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A202" t="s">
+        <v>510</v>
+      </c>
+      <c r="B202" t="s">
+        <v>511</v>
+      </c>
+      <c r="C202" t="s">
+        <v>512</v>
+      </c>
+      <c r="D202" s="7"/>
+      <c r="E202" s="7"/>
+      <c r="F202" t="s">
         <v>10</v>
       </c>
-      <c r="G201" s="26"/>
-    </row>
-    <row r="202" spans="1:7">
-      <c r="A202" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B202" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C202" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="D202" s="1"/>
-      <c r="E202" s="7"/>
-      <c r="F202" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G202" s="26"/>
     </row>
-    <row r="203" spans="1:7" ht="45" customHeight="1">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B203" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C203" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="D203" s="7"/>
+        <v>514</v>
+      </c>
+      <c r="D203" s="1"/>
       <c r="E203" s="7"/>
-      <c r="F203" s="16" t="s">
+      <c r="F203" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G203" s="26" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7">
+      <c r="G203" s="26"/>
+    </row>
+    <row r="204" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D204" s="7" t="s">
-        <v>520</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="D204" s="7"/>
       <c r="E204" s="7"/>
       <c r="F204" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G204" s="26" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A205" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B205" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C205" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D205" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="E205" s="7"/>
+      <c r="F205" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G204" s="24"/>
-    </row>
-    <row r="205" spans="1:7" ht="30" customHeight="1">
-      <c r="A205" t="s">
-        <v>510</v>
-      </c>
-      <c r="B205" t="s">
-        <v>1001</v>
-      </c>
-      <c r="C205" t="s">
-        <v>1002</v>
-      </c>
-      <c r="D205" s="7"/>
-      <c r="E205" s="7"/>
-      <c r="F205" t="s">
-        <v>20</v>
-      </c>
-      <c r="G205" s="26" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" ht="30" customHeight="1">
+      <c r="G205" s="24"/>
+    </row>
+    <row r="206" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>510</v>
       </c>
       <c r="B206" t="s">
-        <v>521</v>
+        <v>1000</v>
       </c>
       <c r="C206" t="s">
-        <v>522</v>
+        <v>1001</v>
       </c>
       <c r="D206" s="7"/>
       <c r="E206" s="7"/>
       <c r="F206" t="s">
-        <v>10</v>
-      </c>
-      <c r="G206" s="26"/>
-    </row>
-    <row r="207" spans="1:7" ht="45">
-      <c r="A207" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G206" s="26" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
         <v>510</v>
       </c>
-      <c r="B207" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C207" s="2" t="s">
-        <v>524</v>
+      <c r="B207" t="s">
+        <v>521</v>
+      </c>
+      <c r="C207" t="s">
+        <v>522</v>
       </c>
       <c r="D207" s="7"/>
       <c r="E207" s="7"/>
-      <c r="F207" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G207" s="24" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="208" spans="1:7" ht="30" customHeight="1">
+      <c r="F207" t="s">
+        <v>10</v>
+      </c>
+      <c r="G207" s="26"/>
+    </row>
+    <row r="208" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B208" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C208" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D208" s="7"/>
       <c r="E208" s="7"/>
-      <c r="F208" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G208" s="26" t="s">
-        <v>528</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" ht="30" customHeight="1">
+      <c r="F208" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G208" s="24" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D209" s="7"/>
       <c r="E209" s="7"/>
       <c r="F209" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G209" s="26"/>
-    </row>
-    <row r="210" spans="1:7" ht="30" customHeight="1">
+      <c r="G209" s="26" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="210" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="D210" s="1"/>
+        <v>530</v>
+      </c>
+      <c r="D210" s="7"/>
       <c r="E210" s="7"/>
-      <c r="F210" s="12" t="s">
+      <c r="F210" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G210" s="26"/>
     </row>
-    <row r="211" spans="1:7" ht="30" customHeight="1">
+    <row r="211" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="D211" s="7" t="s">
-        <v>535</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="D211" s="1"/>
       <c r="E211" s="7"/>
-      <c r="F211" s="3" t="s">
-        <v>37</v>
+      <c r="F211" s="12" t="s">
+        <v>10</v>
       </c>
       <c r="G211" s="26"/>
     </row>
-    <row r="212" spans="1:7" ht="30" customHeight="1">
+    <row r="212" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="D212" s="1"/>
+        <v>534</v>
+      </c>
+      <c r="D212" s="7" t="s">
+        <v>535</v>
+      </c>
       <c r="E212" s="7"/>
-      <c r="F212" s="14" t="s">
-        <v>10</v>
+      <c r="F212" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="G212" s="26"/>
     </row>
-    <row r="213" spans="1:7" ht="30" customHeight="1">
+    <row r="213" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D213" s="1" t="s">
-        <v>540</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="D213" s="1"/>
       <c r="E213" s="7"/>
-      <c r="F213" s="4" t="s">
-        <v>541</v>
+      <c r="F213" s="14" t="s">
+        <v>10</v>
       </c>
       <c r="G213" s="26"/>
     </row>
-    <row r="214" spans="1:7" ht="30" customHeight="1">
+    <row r="214" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B214" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C214" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D214" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E214" s="7"/>
+      <c r="F214" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="G214" s="26"/>
+    </row>
+    <row r="215" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B215" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C214" s="2" t="s">
+      <c r="C215" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D214" s="7" t="s">
+      <c r="D215" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="E214" s="7"/>
-      <c r="F214" s="5" t="s">
+      <c r="E215" s="7"/>
+      <c r="F215" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G214" s="26"/>
-    </row>
-    <row r="215" spans="1:7" ht="30" customHeight="1">
-      <c r="A215" t="s">
-        <v>510</v>
-      </c>
-      <c r="B215" t="s">
-        <v>545</v>
-      </c>
-      <c r="C215" t="s">
-        <v>546</v>
-      </c>
-      <c r="D215" s="7"/>
-      <c r="E215" s="7"/>
-      <c r="F215" t="s">
-        <v>20</v>
-      </c>
       <c r="G215" s="26"/>
     </row>
-    <row r="216" spans="1:7" ht="30" customHeight="1">
+    <row r="216" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>510</v>
       </c>
       <c r="B216" t="s">
-        <v>547</v>
+        <v>545</v>
       </c>
       <c r="C216" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="D216" s="7"/>
       <c r="E216" s="7"/>
       <c r="F216" t="s">
-        <v>29</v>
-      </c>
-      <c r="G216" s="26" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="217" spans="1:7">
+        <v>20</v>
+      </c>
+      <c r="G216" s="26"/>
+    </row>
+    <row r="217" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>510</v>
       </c>
       <c r="B217" t="s">
-        <v>550</v>
+        <v>1020</v>
       </c>
       <c r="C217" t="s">
-        <v>551</v>
+        <v>1021</v>
       </c>
       <c r="D217" s="7"/>
       <c r="E217" s="7"/>
       <c r="F217" t="s">
         <v>20</v>
       </c>
-      <c r="G217" s="26"/>
-    </row>
-    <row r="218" spans="1:7" ht="30" customHeight="1">
+      <c r="G217" s="26" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>510</v>
       </c>
       <c r="B218" t="s">
-        <v>998</v>
+        <v>547</v>
       </c>
       <c r="C218" t="s">
-        <v>999</v>
+        <v>548</v>
       </c>
       <c r="D218" s="7"/>
       <c r="E218" s="7"/>
@@ -7805,18 +7888,18 @@
         <v>29</v>
       </c>
       <c r="G218" s="26" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" ht="30" customHeight="1">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>510</v>
       </c>
       <c r="B219" t="s">
-        <v>552</v>
+        <v>1023</v>
       </c>
       <c r="C219" t="s">
-        <v>553</v>
+        <v>1024</v>
       </c>
       <c r="D219" s="7"/>
       <c r="E219" s="7"/>
@@ -7824,575 +7907,575 @@
         <v>29</v>
       </c>
       <c r="G219" s="26" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>510</v>
       </c>
       <c r="B220" t="s">
-        <v>555</v>
+        <v>1026</v>
       </c>
       <c r="C220" t="s">
-        <v>556</v>
+        <v>1027</v>
       </c>
       <c r="D220" s="7"/>
       <c r="E220" s="7"/>
       <c r="F220" t="s">
         <v>29</v>
       </c>
-      <c r="G220" s="26"/>
-    </row>
-    <row r="221" spans="1:7" ht="45" customHeight="1">
+      <c r="G220" s="26" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>510</v>
       </c>
       <c r="B221" t="s">
-        <v>993</v>
+        <v>550</v>
       </c>
       <c r="C221" t="s">
-        <v>994</v>
-      </c>
-      <c r="D221" s="7" t="s">
-        <v>995</v>
-      </c>
+        <v>551</v>
+      </c>
+      <c r="D221" s="7"/>
       <c r="E221" s="7"/>
       <c r="F221" t="s">
         <v>20</v>
       </c>
       <c r="G221" s="26"/>
     </row>
-    <row r="222" spans="1:7">
+    <row r="222" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>510</v>
       </c>
       <c r="B222" t="s">
-        <v>557</v>
+        <v>1029</v>
       </c>
       <c r="C222" t="s">
-        <v>558</v>
+        <v>1030</v>
       </c>
       <c r="D222" s="7"/>
       <c r="E222" s="7"/>
       <c r="F222" t="s">
-        <v>29</v>
-      </c>
-      <c r="G222" s="26"/>
-    </row>
-    <row r="223" spans="1:7" ht="45" customHeight="1">
+        <v>20</v>
+      </c>
+      <c r="G222" s="26" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>510</v>
       </c>
       <c r="B223" t="s">
-        <v>559</v>
+        <v>998</v>
       </c>
       <c r="C223" t="s">
-        <v>560</v>
+        <v>999</v>
       </c>
       <c r="D223" s="7"/>
       <c r="E223" s="7"/>
       <c r="F223" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G223" s="26" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>510</v>
       </c>
       <c r="B224" t="s">
-        <v>562</v>
+        <v>552</v>
       </c>
       <c r="C224" t="s">
-        <v>563</v>
+        <v>553</v>
       </c>
       <c r="D224" s="7"/>
       <c r="E224" s="7"/>
       <c r="F224" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G224" s="26" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" ht="45" customHeight="1">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>510</v>
       </c>
       <c r="B225" t="s">
-        <v>565</v>
+        <v>555</v>
       </c>
       <c r="C225" t="s">
-        <v>566</v>
-      </c>
-      <c r="D225" s="7" t="s">
-        <v>567</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="D225" s="7"/>
       <c r="E225" s="7"/>
       <c r="F225" t="s">
+        <v>29</v>
+      </c>
+      <c r="G225" s="26"/>
+    </row>
+    <row r="226" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A226" t="s">
+        <v>510</v>
+      </c>
+      <c r="B226" t="s">
+        <v>993</v>
+      </c>
+      <c r="C226" t="s">
+        <v>994</v>
+      </c>
+      <c r="D226" s="7" t="s">
+        <v>995</v>
+      </c>
+      <c r="E226" s="7"/>
+      <c r="F226" t="s">
         <v>20</v>
       </c>
-      <c r="G225" s="26" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="30" customHeight="1">
-      <c r="A226" s="2" t="s">
+      <c r="G226" s="26"/>
+    </row>
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A227" t="s">
         <v>510</v>
       </c>
-      <c r="B226" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C226" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="D226" s="7"/>
-      <c r="E226" s="7"/>
-      <c r="F226" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G226" s="26"/>
-    </row>
-    <row r="227" spans="1:7" ht="30" customHeight="1">
-      <c r="A227" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B227" s="2" t="s">
-        <v>571</v>
-      </c>
-      <c r="C227" s="2" t="s">
-        <v>572</v>
+      <c r="B227" t="s">
+        <v>557</v>
+      </c>
+      <c r="C227" t="s">
+        <v>558</v>
       </c>
       <c r="D227" s="7"/>
       <c r="E227" s="7"/>
-      <c r="F227" s="4"/>
+      <c r="F227" t="s">
+        <v>29</v>
+      </c>
       <c r="G227" s="26"/>
     </row>
-    <row r="228" spans="1:7" ht="30" customHeight="1">
-      <c r="A228" s="2" t="s">
+    <row r="228" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A228" t="s">
         <v>510</v>
       </c>
-      <c r="B228" s="2" t="s">
-        <v>996</v>
-      </c>
-      <c r="C228" s="2" t="s">
-        <v>997</v>
+      <c r="B228" t="s">
+        <v>559</v>
+      </c>
+      <c r="C228" t="s">
+        <v>560</v>
       </c>
       <c r="D228" s="7"/>
       <c r="E228" s="7"/>
-      <c r="F228" s="4"/>
-      <c r="G228" s="26"/>
-    </row>
-    <row r="229" spans="1:7" ht="30" customHeight="1">
-      <c r="A229" s="2" t="s">
+      <c r="F228" t="s">
+        <v>10</v>
+      </c>
+      <c r="G228" s="26" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A229" t="s">
         <v>510</v>
       </c>
-      <c r="B229" s="2" t="s">
-        <v>573</v>
-      </c>
-      <c r="C229" s="2" t="s">
-        <v>574</v>
+      <c r="B229" t="s">
+        <v>562</v>
+      </c>
+      <c r="C229" t="s">
+        <v>563</v>
       </c>
       <c r="D229" s="7"/>
       <c r="E229" s="7"/>
-      <c r="F229" s="16" t="s">
+      <c r="F229" t="s">
         <v>10</v>
       </c>
-      <c r="G229" s="24" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="30" customHeight="1">
-      <c r="A230" s="2" t="s">
+      <c r="G229" s="26" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A230" t="s">
         <v>510</v>
       </c>
-      <c r="B230" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="C230" s="2" t="s">
-        <v>577</v>
-      </c>
-      <c r="D230" s="7"/>
+      <c r="B230" t="s">
+        <v>565</v>
+      </c>
+      <c r="C230" t="s">
+        <v>566</v>
+      </c>
+      <c r="D230" s="7" t="s">
+        <v>567</v>
+      </c>
       <c r="E230" s="7"/>
-      <c r="F230" s="5" t="s">
-        <v>10</v>
+      <c r="F230" t="s">
+        <v>20</v>
       </c>
       <c r="G230" s="26" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="231" spans="1:7" ht="30" customHeight="1">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B231" s="2" t="s">
-        <v>579</v>
+        <v>569</v>
       </c>
       <c r="C231" s="2" t="s">
-        <v>580</v>
+        <v>570</v>
       </c>
       <c r="D231" s="7"/>
       <c r="E231" s="7"/>
-      <c r="F231" s="14" t="s">
-        <v>20</v>
+      <c r="F231" s="5" t="s">
+        <v>96</v>
       </c>
       <c r="G231" s="26"/>
     </row>
-    <row r="232" spans="1:7" ht="30" customHeight="1">
+    <row r="232" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>581</v>
+        <v>1032</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>582</v>
+        <v>1033</v>
       </c>
       <c r="D232" s="7"/>
       <c r="E232" s="7"/>
-      <c r="F232" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G232" s="26"/>
-    </row>
-    <row r="233" spans="1:7" ht="30" customHeight="1">
+      <c r="F232" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G232" s="26" t="s">
+        <v>1034</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>583</v>
+        <v>1035</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>584</v>
+        <v>1036</v>
       </c>
       <c r="D233" s="7"/>
       <c r="E233" s="7"/>
       <c r="F233" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G233" s="26"/>
-    </row>
-    <row r="234" spans="1:7" ht="30" customHeight="1">
+        <v>29</v>
+      </c>
+      <c r="G233" s="26" t="s">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>585</v>
+        <v>571</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="D234" s="1"/>
+        <v>572</v>
+      </c>
+      <c r="D234" s="7"/>
       <c r="E234" s="7"/>
-      <c r="F234" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G234" s="24" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="235" spans="1:7" ht="30" customHeight="1">
+      <c r="F234" s="4"/>
+      <c r="G234" s="26"/>
+    </row>
+    <row r="235" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>588</v>
+        <v>996</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>589</v>
+        <v>997</v>
       </c>
       <c r="D235" s="7"/>
       <c r="E235" s="7"/>
-      <c r="F235" s="5" t="s">
-        <v>20</v>
-      </c>
+      <c r="F235" s="4"/>
       <c r="G235" s="26"/>
     </row>
-    <row r="236" spans="1:7" ht="30" customHeight="1">
+    <row r="236" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>590</v>
+        <v>573</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>591</v>
+        <v>574</v>
       </c>
       <c r="D236" s="7"/>
       <c r="E236" s="7"/>
-      <c r="F236" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G236" s="26"/>
-    </row>
-    <row r="237" spans="1:7" ht="30" customHeight="1">
+      <c r="F236" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G236" s="24" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>592</v>
+        <v>576</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>593</v>
+        <v>577</v>
       </c>
       <c r="D237" s="7"/>
       <c r="E237" s="7"/>
-      <c r="F237" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G237" s="26"/>
-    </row>
-    <row r="238" spans="1:7" ht="30" customHeight="1">
+      <c r="F237" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G237" s="26" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>594</v>
+        <v>579</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>595</v>
+        <v>580</v>
       </c>
       <c r="D238" s="7"/>
       <c r="E238" s="7"/>
-      <c r="F238" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G238" s="24"/>
-    </row>
-    <row r="239" spans="1:7" ht="30" customHeight="1">
+      <c r="F238" s="14" t="s">
+        <v>20</v>
+      </c>
+      <c r="G238" s="26"/>
+    </row>
+    <row r="239" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>596</v>
+        <v>581</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D239" s="7" t="s">
-        <v>598</v>
-      </c>
+        <v>582</v>
+      </c>
+      <c r="D239" s="7"/>
       <c r="E239" s="7"/>
-      <c r="F239" s="4" t="s">
+      <c r="F239" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G239" s="26" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="240" spans="1:7" ht="30" customHeight="1">
+      <c r="G239" s="26"/>
+    </row>
+    <row r="240" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>600</v>
+        <v>583</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D240" s="1"/>
+        <v>584</v>
+      </c>
+      <c r="D240" s="7"/>
       <c r="E240" s="7"/>
       <c r="F240" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G240" s="26"/>
     </row>
-    <row r="241" spans="1:7" ht="30" customHeight="1">
-      <c r="A241" t="s">
+    <row r="241" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A241" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B241" t="s">
-        <v>602</v>
-      </c>
-      <c r="C241" t="s">
-        <v>603</v>
-      </c>
-      <c r="D241" s="7"/>
+      <c r="B241" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="C241" s="2" t="s">
+        <v>586</v>
+      </c>
+      <c r="D241" s="1"/>
       <c r="E241" s="7"/>
-      <c r="F241" t="s">
-        <v>29</v>
-      </c>
-      <c r="G241" s="26"/>
-    </row>
-    <row r="242" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+      <c r="F241" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G241" s="24" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="242" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>604</v>
+        <v>588</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>605</v>
+        <v>589</v>
       </c>
       <c r="D242" s="7"/>
       <c r="E242" s="7"/>
-      <c r="F242" s="4" t="s">
-        <v>29</v>
+      <c r="F242" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G242" s="26"/>
     </row>
-    <row r="243" spans="1:7" ht="45">
+    <row r="243" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>606</v>
+        <v>590</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="D243" s="7"/>
       <c r="E243" s="7"/>
-      <c r="F243" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="G243" s="24" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="244" spans="1:7" ht="30" customHeight="1">
-      <c r="A244" t="s">
+      <c r="F243" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G243" s="26"/>
+    </row>
+    <row r="244" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A244" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B244" t="s">
-        <v>609</v>
-      </c>
-      <c r="C244" t="s">
-        <v>610</v>
+      <c r="B244" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="C244" s="2" t="s">
+        <v>593</v>
       </c>
       <c r="D244" s="7"/>
       <c r="E244" s="7"/>
-      <c r="F244" t="s">
+      <c r="F244" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G244" s="26"/>
     </row>
-    <row r="245" spans="1:7" ht="30">
+    <row r="245" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>611</v>
+        <v>594</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D245" s="1" t="s">
-        <v>613</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="D245" s="7"/>
       <c r="E245" s="7"/>
-      <c r="F245" s="16" t="s">
-        <v>29</v>
+      <c r="F245" s="6" t="s">
+        <v>96</v>
       </c>
       <c r="G245" s="24"/>
     </row>
-    <row r="246" spans="1:7">
+    <row r="246" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>614</v>
+        <v>596</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D246" s="1"/>
+        <v>597</v>
+      </c>
+      <c r="D246" s="7" t="s">
+        <v>598</v>
+      </c>
       <c r="E246" s="7"/>
-      <c r="F246" s="14" t="s">
-        <v>10</v>
+      <c r="F246" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G246" s="26" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="247" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>617</v>
+        <v>600</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D247" s="7"/>
+        <v>601</v>
+      </c>
+      <c r="D247" s="1"/>
       <c r="E247" s="7"/>
       <c r="F247" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G247" s="26"/>
     </row>
-    <row r="248" spans="1:7" ht="30">
-      <c r="A248" s="2" t="s">
+    <row r="248" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A248" t="s">
         <v>510</v>
       </c>
-      <c r="B248" s="2" t="s">
-        <v>619</v>
-      </c>
-      <c r="C248" s="2" t="s">
-        <v>620</v>
+      <c r="B248" t="s">
+        <v>602</v>
+      </c>
+      <c r="C248" t="s">
+        <v>603</v>
       </c>
       <c r="D248" s="7"/>
       <c r="E248" s="7"/>
-      <c r="F248" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G248" s="26" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="249" spans="1:7" ht="30" customHeight="1">
+      <c r="F248" t="s">
+        <v>29</v>
+      </c>
+      <c r="G248" s="26"/>
+    </row>
+    <row r="249" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A249" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>622</v>
+        <v>604</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="D249" s="7" t="s">
-        <v>624</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="D249" s="7"/>
       <c r="E249" s="7"/>
-      <c r="F249" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G249" s="26" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="250" spans="1:7" ht="30" customHeight="1">
+      <c r="F249" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G249" s="26"/>
+    </row>
+    <row r="250" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>626</v>
+        <v>606</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="D250" s="7" t="s">
-        <v>628</v>
-      </c>
+        <v>607</v>
+      </c>
+      <c r="D250" s="7"/>
       <c r="E250" s="7"/>
-      <c r="F250" s="5" t="s">
-        <v>541</v>
-      </c>
-      <c r="G250" s="26"/>
-    </row>
-    <row r="251" spans="1:7">
+      <c r="F250" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="G250" s="24" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="251" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" t="s">
         <v>510</v>
       </c>
       <c r="B251" t="s">
-        <v>629</v>
+        <v>609</v>
       </c>
       <c r="C251" t="s">
-        <v>630</v>
+        <v>610</v>
       </c>
       <c r="D251" s="7"/>
       <c r="E251" s="7"/>
@@ -8401,85 +8484,91 @@
       </c>
       <c r="G251" s="26"/>
     </row>
-    <row r="252" spans="1:7" ht="30">
+    <row r="252" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>631</v>
+        <v>611</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="D252" s="7"/>
+        <v>612</v>
+      </c>
+      <c r="D252" s="1" t="s">
+        <v>613</v>
+      </c>
       <c r="E252" s="7"/>
-      <c r="F252" s="4" t="s">
+      <c r="F252" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G252" s="26"/>
-    </row>
-    <row r="253" spans="1:7" ht="30" customHeight="1">
+      <c r="G252" s="24"/>
+    </row>
+    <row r="253" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>633</v>
+        <v>1038</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="D253" s="7"/>
+        <v>1039</v>
+      </c>
+      <c r="D253" s="1"/>
       <c r="E253" s="7"/>
-      <c r="F253" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G253" s="26"/>
-    </row>
-    <row r="254" spans="1:7" ht="30" customHeight="1">
+      <c r="F253" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G253" s="26" t="s">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="254" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>635</v>
+        <v>1041</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>636</v>
-      </c>
-      <c r="D254" s="7"/>
+        <v>1042</v>
+      </c>
+      <c r="D254" s="1"/>
       <c r="E254" s="7"/>
-      <c r="F254" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G254" s="26"/>
-    </row>
-    <row r="255" spans="1:7">
+      <c r="F254" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G254" s="26" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>637</v>
+        <v>614</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>638</v>
-      </c>
-      <c r="D255" s="7"/>
+        <v>615</v>
+      </c>
+      <c r="D255" s="1"/>
       <c r="E255" s="7"/>
-      <c r="F255" s="5" t="s">
-        <v>20</v>
+      <c r="F255" s="14" t="s">
+        <v>10</v>
       </c>
       <c r="G255" s="26" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" ht="30">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>640</v>
+        <v>617</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>641</v>
+        <v>618</v>
       </c>
       <c r="D256" s="7"/>
       <c r="E256" s="7"/>
@@ -8488,66 +8577,74 @@
       </c>
       <c r="G256" s="26"/>
     </row>
-    <row r="257" spans="1:7">
-      <c r="A257" t="s">
+    <row r="257" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A257" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B257" t="s">
-        <v>642</v>
-      </c>
-      <c r="C257" t="s">
-        <v>643</v>
+      <c r="B257" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C257" s="2" t="s">
+        <v>620</v>
       </c>
       <c r="D257" s="7"/>
       <c r="E257" s="7"/>
-      <c r="F257" t="s">
-        <v>29</v>
-      </c>
-      <c r="G257" s="26"/>
-    </row>
-    <row r="258" spans="1:7">
-      <c r="A258" t="s">
+      <c r="F257" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G257" s="26" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="258" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A258" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B258" t="s">
-        <v>644</v>
-      </c>
-      <c r="C258" t="s">
-        <v>645</v>
-      </c>
-      <c r="D258" s="7"/>
+      <c r="B258" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C258" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D258" s="7" t="s">
+        <v>624</v>
+      </c>
       <c r="E258" s="7"/>
-      <c r="F258" t="s">
-        <v>20</v>
-      </c>
-      <c r="G258" s="26"/>
-    </row>
-    <row r="259" spans="1:7" ht="30" customHeight="1">
-      <c r="A259" t="s">
+      <c r="F258" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G258" s="26" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A259" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B259" t="s">
-        <v>646</v>
-      </c>
-      <c r="C259" t="s">
-        <v>647</v>
-      </c>
-      <c r="D259" s="7"/>
+      <c r="B259" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C259" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D259" s="7" t="s">
+        <v>628</v>
+      </c>
       <c r="E259" s="7"/>
-      <c r="F259" t="s">
-        <v>20</v>
+      <c r="F259" s="5" t="s">
+        <v>541</v>
       </c>
       <c r="G259" s="26"/>
     </row>
-    <row r="260" spans="1:7">
+    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A260" t="s">
         <v>510</v>
       </c>
       <c r="B260" t="s">
-        <v>648</v>
+        <v>629</v>
       </c>
       <c r="C260" t="s">
-        <v>649</v>
+        <v>630</v>
       </c>
       <c r="D260" s="7"/>
       <c r="E260" s="7"/>
@@ -8556,1181 +8653,1181 @@
       </c>
       <c r="G260" s="26"/>
     </row>
-    <row r="261" spans="1:7">
-      <c r="A261" t="s">
+    <row r="261" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A261" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B261" t="s">
-        <v>650</v>
-      </c>
-      <c r="C261" t="s">
-        <v>651</v>
+      <c r="B261" s="2" t="s">
+        <v>631</v>
+      </c>
+      <c r="C261" s="2" t="s">
+        <v>632</v>
       </c>
       <c r="D261" s="7"/>
       <c r="E261" s="7"/>
-      <c r="F261" t="s">
-        <v>10</v>
+      <c r="F261" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G261" s="26"/>
     </row>
-    <row r="262" spans="1:7" ht="30" customHeight="1">
-      <c r="A262" t="s">
+    <row r="262" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B262" t="s">
-        <v>652</v>
-      </c>
-      <c r="C262" t="s">
-        <v>653</v>
+      <c r="B262" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>634</v>
       </c>
       <c r="D262" s="7"/>
       <c r="E262" s="7"/>
-      <c r="F262" t="s">
-        <v>37</v>
+      <c r="F262" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G262" s="26"/>
     </row>
-    <row r="263" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A263" t="s">
+    <row r="263" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A263" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B263" t="s">
-        <v>654</v>
-      </c>
-      <c r="C263" t="s">
-        <v>655</v>
+      <c r="B263" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C263" s="2" t="s">
+        <v>636</v>
       </c>
       <c r="D263" s="7"/>
       <c r="E263" s="7"/>
-      <c r="F263" t="s">
-        <v>10</v>
+      <c r="F263" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G263" s="26"/>
     </row>
-    <row r="264" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A264" t="s">
+    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A264" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B264" t="s">
-        <v>656</v>
-      </c>
-      <c r="C264" t="s">
-        <v>657</v>
+      <c r="B264" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C264" s="2" t="s">
+        <v>638</v>
       </c>
       <c r="D264" s="7"/>
       <c r="E264" s="7"/>
-      <c r="F264" t="s">
-        <v>14</v>
+      <c r="F264" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G264" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7">
-      <c r="A265" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B265" t="s">
-        <v>659</v>
-      </c>
-      <c r="C265" t="s">
-        <v>660</v>
+      <c r="B265" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>641</v>
       </c>
       <c r="D265" s="7"/>
       <c r="E265" s="7"/>
-      <c r="F265" t="s">
-        <v>14</v>
-      </c>
-      <c r="G265" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="266" spans="1:7">
-      <c r="A266" s="2" t="s">
+      <c r="F265" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G265" s="26"/>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
         <v>510</v>
       </c>
-      <c r="B266" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>662</v>
+      <c r="B266" t="s">
+        <v>642</v>
+      </c>
+      <c r="C266" t="s">
+        <v>643</v>
       </c>
       <c r="D266" s="7"/>
       <c r="E266" s="7"/>
-      <c r="F266" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G266" s="26" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="267" spans="1:7" ht="30" customHeight="1">
-      <c r="A267" s="2" t="s">
+      <c r="F266" t="s">
+        <v>29</v>
+      </c>
+      <c r="G266" s="26"/>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A267" t="s">
         <v>510</v>
       </c>
-      <c r="B267" s="2" t="s">
-        <v>664</v>
-      </c>
-      <c r="C267" s="2" t="s">
-        <v>665</v>
+      <c r="B267" t="s">
+        <v>644</v>
+      </c>
+      <c r="C267" t="s">
+        <v>645</v>
       </c>
       <c r="D267" s="7"/>
       <c r="E267" s="7"/>
-      <c r="F267" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G267" s="26" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="268" spans="1:7" ht="30" customHeight="1">
-      <c r="A268" s="17" t="s">
+      <c r="F267" t="s">
+        <v>20</v>
+      </c>
+      <c r="G267" s="26"/>
+    </row>
+    <row r="268" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A268" t="s">
         <v>510</v>
       </c>
-      <c r="B268" s="17" t="s">
-        <v>667</v>
-      </c>
-      <c r="C268" s="17" t="s">
-        <v>668</v>
-      </c>
-      <c r="D268" s="27"/>
-      <c r="E268" s="27"/>
-      <c r="F268" s="18" t="s">
-        <v>14</v>
-      </c>
-      <c r="G268" s="28" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="269" spans="1:7">
-      <c r="A269" s="2" t="s">
+      <c r="B268" t="s">
+        <v>646</v>
+      </c>
+      <c r="C268" t="s">
+        <v>647</v>
+      </c>
+      <c r="D268" s="7"/>
+      <c r="E268" s="7"/>
+      <c r="F268" t="s">
+        <v>20</v>
+      </c>
+      <c r="G268" s="26"/>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A269" t="s">
         <v>510</v>
       </c>
-      <c r="B269" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="C269" s="2" t="s">
-        <v>671</v>
+      <c r="B269" t="s">
+        <v>648</v>
+      </c>
+      <c r="C269" t="s">
+        <v>649</v>
       </c>
       <c r="D269" s="7"/>
       <c r="E269" s="7"/>
-      <c r="F269" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G269" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="270" spans="1:7">
-      <c r="A270" s="2" t="s">
+      <c r="F269" t="s">
+        <v>29</v>
+      </c>
+      <c r="G269" s="26"/>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A270" t="s">
         <v>510</v>
       </c>
-      <c r="B270" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="C270" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="D270" s="1"/>
+      <c r="B270" t="s">
+        <v>650</v>
+      </c>
+      <c r="C270" t="s">
+        <v>651</v>
+      </c>
+      <c r="D270" s="7"/>
       <c r="E270" s="7"/>
-      <c r="F270" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G270" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="271" spans="1:7" ht="30" customHeight="1">
-      <c r="A271" s="2" t="s">
+      <c r="F270" t="s">
+        <v>10</v>
+      </c>
+      <c r="G270" s="26"/>
+    </row>
+    <row r="271" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A271" t="s">
         <v>510</v>
       </c>
-      <c r="B271" s="2" t="s">
-        <v>674</v>
-      </c>
-      <c r="C271" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="D271" s="1"/>
+      <c r="B271" t="s">
+        <v>652</v>
+      </c>
+      <c r="C271" t="s">
+        <v>653</v>
+      </c>
+      <c r="D271" s="7"/>
       <c r="E271" s="7"/>
-      <c r="F271" s="3" t="s">
-        <v>20</v>
+      <c r="F271" t="s">
+        <v>37</v>
       </c>
       <c r="G271" s="26"/>
     </row>
-    <row r="272" spans="1:7" ht="30" customHeight="1">
-      <c r="A272" s="2" t="s">
+    <row r="272" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A272" t="s">
         <v>510</v>
       </c>
-      <c r="B272" s="2" t="s">
-        <v>676</v>
-      </c>
-      <c r="C272" s="2" t="s">
-        <v>677</v>
+      <c r="B272" t="s">
+        <v>654</v>
+      </c>
+      <c r="C272" t="s">
+        <v>655</v>
       </c>
       <c r="D272" s="7"/>
       <c r="E272" s="7"/>
-      <c r="F272" s="3" t="s">
-        <v>20</v>
+      <c r="F272" t="s">
+        <v>10</v>
       </c>
       <c r="G272" s="26"/>
     </row>
-    <row r="273" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
-      <c r="A273" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="B273" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="C273" s="2" t="s">
-        <v>680</v>
+    <row r="273" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A273" t="s">
+        <v>510</v>
+      </c>
+      <c r="B273" t="s">
+        <v>656</v>
+      </c>
+      <c r="C273" t="s">
+        <v>657</v>
       </c>
       <c r="D273" s="7"/>
       <c r="E273" s="7"/>
-      <c r="F273" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G273" s="26"/>
-    </row>
-    <row r="274" spans="1:7" ht="30" customHeight="1">
-      <c r="A274" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="B274" s="2" t="s">
-        <v>681</v>
-      </c>
-      <c r="C274" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="D274" s="7" t="s">
-        <v>683</v>
-      </c>
+      <c r="F273" t="s">
+        <v>14</v>
+      </c>
+      <c r="G273" s="26" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A274" t="s">
+        <v>510</v>
+      </c>
+      <c r="B274" t="s">
+        <v>659</v>
+      </c>
+      <c r="C274" t="s">
+        <v>660</v>
+      </c>
+      <c r="D274" s="7"/>
       <c r="E274" s="7"/>
-      <c r="F274" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G274" s="26"/>
-    </row>
-    <row r="275" spans="1:7" ht="30" customHeight="1">
+      <c r="F274" t="s">
+        <v>14</v>
+      </c>
+      <c r="G274" s="26" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
-        <v>678</v>
+        <v>510</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>684</v>
+        <v>661</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="D275" s="7" t="s">
-        <v>686</v>
-      </c>
+        <v>662</v>
+      </c>
+      <c r="D275" s="7"/>
       <c r="E275" s="7"/>
       <c r="F275" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G275" s="26"/>
-    </row>
-    <row r="276" spans="1:7" ht="30" customHeight="1">
+        <v>14</v>
+      </c>
+      <c r="G275" s="26" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
-        <v>678</v>
+        <v>510</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>687</v>
+        <v>664</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="D276" s="1"/>
-      <c r="E276" s="1"/>
-      <c r="F276" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G276" s="26"/>
-    </row>
-    <row r="277" spans="1:7" ht="30" customHeight="1">
-      <c r="A277" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="B277" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="D277" s="7"/>
-      <c r="E277" s="7"/>
-      <c r="F277" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G277" s="26"/>
-    </row>
-    <row r="278" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+        <v>665</v>
+      </c>
+      <c r="D276" s="7"/>
+      <c r="E276" s="7"/>
+      <c r="F276" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G276" s="26" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="17" t="s">
+        <v>510</v>
+      </c>
+      <c r="B277" s="17" t="s">
+        <v>667</v>
+      </c>
+      <c r="C277" s="17" t="s">
+        <v>668</v>
+      </c>
+      <c r="D277" s="27"/>
+      <c r="E277" s="27"/>
+      <c r="F277" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G277" s="28" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
-        <v>678</v>
+        <v>510</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>691</v>
+        <v>670</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>692</v>
+        <v>671</v>
       </c>
       <c r="D278" s="7"/>
       <c r="E278" s="7"/>
       <c r="F278" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G278" s="26"/>
-    </row>
-    <row r="279" spans="1:7">
+        <v>14</v>
+      </c>
+      <c r="G278" s="26" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
-        <v>678</v>
+        <v>510</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>693</v>
+        <v>672</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>694</v>
-      </c>
-      <c r="D279" s="7"/>
+        <v>673</v>
+      </c>
+      <c r="D279" s="1"/>
       <c r="E279" s="7"/>
-      <c r="F279" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G279" s="24"/>
-    </row>
-    <row r="280" spans="1:7" ht="30">
+      <c r="F279" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="G279" s="26" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
-        <v>678</v>
+        <v>510</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>695</v>
+        <v>674</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="D280" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="E280" s="7" t="s">
-        <v>698</v>
-      </c>
+        <v>675</v>
+      </c>
+      <c r="D280" s="1"/>
+      <c r="E280" s="7"/>
       <c r="F280" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G280" s="26"/>
     </row>
-    <row r="281" spans="1:7" ht="30" customHeight="1">
+    <row r="281" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
-        <v>678</v>
+        <v>510</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>698</v>
+        <v>676</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>699</v>
+        <v>677</v>
       </c>
       <c r="D281" s="7"/>
       <c r="E281" s="7"/>
-      <c r="F281" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G281" s="24"/>
-    </row>
-    <row r="282" spans="1:7" ht="30" customHeight="1">
+      <c r="F281" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G281" s="26"/>
+    </row>
+    <row r="282" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>700</v>
+        <v>679</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>701</v>
+        <v>680</v>
       </c>
       <c r="D282" s="7"/>
-      <c r="E282" s="1"/>
+      <c r="E282" s="7"/>
       <c r="F282" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G282" s="26"/>
     </row>
-    <row r="283" spans="1:7" ht="30" customHeight="1">
+    <row r="283" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>702</v>
+        <v>681</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="D283" s="7"/>
+        <v>682</v>
+      </c>
+      <c r="D283" s="7" t="s">
+        <v>683</v>
+      </c>
       <c r="E283" s="7"/>
-      <c r="F283" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G283" s="26" t="s">
-        <v>704</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" ht="30" customHeight="1">
+      <c r="F283" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G283" s="26"/>
+    </row>
+    <row r="284" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>705</v>
+        <v>684</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>706</v>
+        <v>685</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>707</v>
+        <v>686</v>
       </c>
       <c r="E284" s="7"/>
-      <c r="F284" s="5"/>
+      <c r="F284" s="3" t="s">
+        <v>10</v>
+      </c>
       <c r="G284" s="26"/>
     </row>
-    <row r="285" spans="1:7" ht="30" customHeight="1">
+    <row r="285" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>708</v>
+        <v>687</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="D285" s="7"/>
-      <c r="E285" s="7"/>
-      <c r="F285" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G285" s="26" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="286" spans="1:7" ht="30" customHeight="1">
+        <v>688</v>
+      </c>
+      <c r="D285" s="1"/>
+      <c r="E285" s="1"/>
+      <c r="F285" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G285" s="26"/>
+    </row>
+    <row r="286" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>711</v>
+        <v>689</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>712</v>
+        <v>690</v>
       </c>
       <c r="D286" s="7"/>
-      <c r="E286" s="7" t="s">
-        <v>700</v>
-      </c>
-      <c r="F286" s="5" t="s">
+      <c r="E286" s="7"/>
+      <c r="F286" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G286" s="26"/>
     </row>
-    <row r="287" spans="1:7">
+    <row r="287" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>713</v>
+        <v>691</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>714</v>
+        <v>692</v>
       </c>
       <c r="D287" s="7"/>
       <c r="E287" s="7"/>
       <c r="F287" s="3" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G287" s="26"/>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>715</v>
+        <v>693</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>716</v>
+        <v>694</v>
       </c>
       <c r="D288" s="7"/>
       <c r="E288" s="7"/>
       <c r="F288" s="16" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G288" s="24"/>
     </row>
-    <row r="289" spans="1:7">
+    <row r="289" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>717</v>
+        <v>695</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>718</v>
-      </c>
-      <c r="D289" s="7"/>
-      <c r="E289" s="7"/>
-      <c r="F289" s="19" t="s">
-        <v>20</v>
+        <v>696</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="E289" s="7" t="s">
+        <v>698</v>
+      </c>
+      <c r="F289" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G289" s="26"/>
     </row>
-    <row r="290" spans="1:7">
-      <c r="A290" s="17" t="s">
+    <row r="290" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A290" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="B290" s="17" t="s">
-        <v>719</v>
-      </c>
-      <c r="C290" s="17" t="s">
-        <v>720</v>
-      </c>
-      <c r="D290" s="27"/>
-      <c r="E290" s="27"/>
-      <c r="F290" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G290" s="28"/>
-    </row>
-    <row r="291" spans="1:7" ht="30" customHeight="1">
+      <c r="B290" s="2" t="s">
+        <v>698</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>699</v>
+      </c>
+      <c r="D290" s="7"/>
+      <c r="E290" s="7"/>
+      <c r="F290" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G290" s="24"/>
+    </row>
+    <row r="291" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>721</v>
+        <v>700</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>722</v>
+        <v>701</v>
       </c>
       <c r="D291" s="7"/>
-      <c r="E291" s="7"/>
-      <c r="F291" s="5" t="s">
+      <c r="E291" s="1"/>
+      <c r="F291" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G291" s="26"/>
     </row>
-    <row r="292" spans="1:7">
+    <row r="292" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>723</v>
+        <v>702</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>724</v>
+        <v>703</v>
       </c>
       <c r="D292" s="7"/>
-      <c r="E292" s="1"/>
-      <c r="F292" s="12" t="s">
+      <c r="E292" s="7"/>
+      <c r="F292" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G292" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7">
+        <v>704</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>726</v>
+        <v>705</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="D293" s="7"/>
+        <v>706</v>
+      </c>
+      <c r="D293" s="7" t="s">
+        <v>707</v>
+      </c>
       <c r="E293" s="7"/>
-      <c r="F293" s="5" t="s">
-        <v>10</v>
-      </c>
+      <c r="F293" s="5"/>
       <c r="G293" s="26"/>
     </row>
-    <row r="294" spans="1:7" ht="30" customHeight="1">
+    <row r="294" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>728</v>
+        <v>708</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>729</v>
+        <v>709</v>
       </c>
       <c r="D294" s="7"/>
       <c r="E294" s="7"/>
-      <c r="F294" s="16" t="s">
+      <c r="F294" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G294" s="26" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A295" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B295" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>712</v>
+      </c>
+      <c r="D295" s="7"/>
+      <c r="E295" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="F295" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G294" s="24"/>
-    </row>
-    <row r="295" spans="1:7">
-      <c r="A295" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="B295" s="2" t="s">
-        <v>731</v>
-      </c>
-      <c r="C295" s="2" t="s">
-        <v>732</v>
-      </c>
-      <c r="D295" s="7"/>
-      <c r="E295" s="7"/>
-      <c r="F295" s="5" t="s">
+      <c r="G295" s="26"/>
+    </row>
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>678</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>713</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>714</v>
+      </c>
+      <c r="D296" s="7"/>
+      <c r="E296" s="7"/>
+      <c r="F296" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G295" s="26"/>
-    </row>
-    <row r="296" spans="1:7">
-      <c r="A296" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="B296" s="2" t="s">
-        <v>733</v>
-      </c>
-      <c r="C296" s="2" t="s">
-        <v>734</v>
-      </c>
-      <c r="D296" s="7"/>
-      <c r="E296" s="7" t="s">
-        <v>735</v>
-      </c>
-      <c r="F296" s="5" t="s">
-        <v>37</v>
-      </c>
       <c r="G296" s="26"/>
     </row>
-    <row r="297" spans="1:7" ht="30">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>736</v>
+        <v>715</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>737</v>
+        <v>716</v>
       </c>
       <c r="D297" s="7"/>
       <c r="E297" s="7"/>
-      <c r="F297" s="3" t="s">
+      <c r="F297" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G297" s="26"/>
-    </row>
-    <row r="298" spans="1:7">
+      <c r="G297" s="24"/>
+    </row>
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>738</v>
+        <v>717</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>739</v>
+        <v>718</v>
       </c>
       <c r="D298" s="7"/>
       <c r="E298" s="7"/>
-      <c r="F298" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G298" s="26" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7">
+      <c r="F298" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G298" s="26"/>
+    </row>
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="B299" s="17" t="s">
-        <v>741</v>
+        <v>719</v>
       </c>
       <c r="C299" s="17" t="s">
-        <v>742</v>
+        <v>720</v>
       </c>
       <c r="D299" s="27"/>
       <c r="E299" s="27"/>
-      <c r="F299" s="20" t="s">
+      <c r="F299" s="19" t="s">
         <v>20</v>
       </c>
       <c r="G299" s="28"/>
     </row>
-    <row r="300" spans="1:7" ht="30" customHeight="1">
+    <row r="300" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>743</v>
+        <v>721</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>744</v>
+        <v>722</v>
       </c>
       <c r="D300" s="7"/>
       <c r="E300" s="7"/>
-      <c r="F300" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G300" s="24"/>
-    </row>
-    <row r="301" spans="1:7">
+      <c r="F300" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G300" s="26"/>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>745</v>
+        <v>723</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>746</v>
+        <v>724</v>
       </c>
       <c r="D301" s="7"/>
-      <c r="E301" s="7"/>
-      <c r="F301" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G301" s="24"/>
-    </row>
-    <row r="302" spans="1:7" ht="30">
+      <c r="E301" s="1"/>
+      <c r="F301" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G301" s="26" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>747</v>
+        <v>726</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>748</v>
+        <v>727</v>
       </c>
       <c r="D302" s="7"/>
       <c r="E302" s="7"/>
-      <c r="F302" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G302" s="24"/>
-    </row>
-    <row r="303" spans="1:7" ht="30">
+      <c r="F302" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G302" s="26"/>
+    </row>
+    <row r="303" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>749</v>
+        <v>729</v>
       </c>
       <c r="D303" s="7"/>
       <c r="E303" s="7"/>
-      <c r="F303" s="6" t="s">
-        <v>29</v>
+      <c r="F303" s="16" t="s">
+        <v>10</v>
       </c>
       <c r="G303" s="24"/>
     </row>
-    <row r="304" spans="1:7" ht="30">
-      <c r="A304" s="17" t="s">
-        <v>750</v>
-      </c>
-      <c r="B304" s="17" t="s">
-        <v>751</v>
-      </c>
-      <c r="C304" s="17" t="s">
-        <v>752</v>
-      </c>
-      <c r="D304" s="27"/>
-      <c r="E304" s="27"/>
-      <c r="F304" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="G304" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="305" spans="1:7">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A304" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B304" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="C304" s="2" t="s">
+        <v>732</v>
+      </c>
+      <c r="D304" s="7"/>
+      <c r="E304" s="7"/>
+      <c r="F304" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G304" s="26"/>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>754</v>
+        <v>733</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>755</v>
+        <v>734</v>
       </c>
       <c r="D305" s="7"/>
-      <c r="E305" s="7"/>
-      <c r="F305" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G305" s="26" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7">
+      <c r="E305" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="F305" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G305" s="26"/>
+    </row>
+    <row r="306" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>757</v>
+        <v>736</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>758</v>
+        <v>737</v>
       </c>
       <c r="D306" s="7"/>
       <c r="E306" s="7"/>
-      <c r="F306" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G306" s="26" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="307" spans="1:7" ht="60" customHeight="1">
+      <c r="F306" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G306" s="26"/>
+    </row>
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>750</v>
+        <v>730</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>760</v>
+        <v>738</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>761</v>
+        <v>739</v>
       </c>
       <c r="D307" s="7"/>
       <c r="E307" s="7"/>
-      <c r="F307" s="4" t="s">
-        <v>25</v>
+      <c r="F307" s="12" t="s">
+        <v>14</v>
       </c>
       <c r="G307" s="26" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7">
-      <c r="A308" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="B308" s="2" t="s">
-        <v>763</v>
-      </c>
-      <c r="C308" s="2" t="s">
-        <v>764</v>
-      </c>
-      <c r="D308" s="7"/>
-      <c r="E308" s="7"/>
-      <c r="F308" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G308" s="26"/>
-    </row>
-    <row r="309" spans="1:7">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A308" s="17" t="s">
+        <v>730</v>
+      </c>
+      <c r="B308" s="17" t="s">
+        <v>741</v>
+      </c>
+      <c r="C308" s="17" t="s">
+        <v>742</v>
+      </c>
+      <c r="D308" s="27"/>
+      <c r="E308" s="27"/>
+      <c r="F308" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G308" s="28"/>
+    </row>
+    <row r="309" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>765</v>
+        <v>730</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>766</v>
+        <v>743</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>767</v>
+        <v>744</v>
       </c>
       <c r="D309" s="7"/>
       <c r="E309" s="7"/>
-      <c r="F309" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G309" s="26"/>
-    </row>
-    <row r="310" spans="1:7">
+      <c r="F309" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="G309" s="24"/>
+    </row>
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>765</v>
+        <v>730</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>1004</v>
+        <v>745</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>1005</v>
+        <v>746</v>
       </c>
       <c r="D310" s="7"/>
       <c r="E310" s="7"/>
-      <c r="F310" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G310" s="26"/>
-    </row>
-    <row r="311" spans="1:7">
+      <c r="F310" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G310" s="24"/>
+    </row>
+    <row r="311" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>765</v>
+        <v>730</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>768</v>
+        <v>747</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>769</v>
+        <v>748</v>
       </c>
       <c r="D311" s="7"/>
       <c r="E311" s="7"/>
-      <c r="F311" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G311" s="26"/>
-    </row>
-    <row r="312" spans="1:7" ht="30" customHeight="1">
+      <c r="F311" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G311" s="24"/>
+    </row>
+    <row r="312" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>765</v>
+        <v>730</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>770</v>
+        <v>735</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>771</v>
+        <v>749</v>
       </c>
       <c r="D312" s="7"/>
       <c r="E312" s="7"/>
-      <c r="F312" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G312" s="26"/>
-    </row>
-    <row r="313" spans="1:7">
-      <c r="A313" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="B313" s="2" t="s">
-        <v>772</v>
-      </c>
-      <c r="C313" s="2" t="s">
-        <v>773</v>
-      </c>
-      <c r="D313" s="7"/>
-      <c r="E313" s="7"/>
-      <c r="F313" s="4" t="s">
+      <c r="F312" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G313" s="26"/>
-    </row>
-    <row r="314" spans="1:7">
+      <c r="G312" s="24"/>
+    </row>
+    <row r="313" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A313" s="17" t="s">
+        <v>750</v>
+      </c>
+      <c r="B313" s="17" t="s">
+        <v>751</v>
+      </c>
+      <c r="C313" s="17" t="s">
+        <v>752</v>
+      </c>
+      <c r="D313" s="27"/>
+      <c r="E313" s="27"/>
+      <c r="F313" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="G313" s="28" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>774</v>
+        <v>754</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>775</v>
+        <v>755</v>
       </c>
       <c r="D314" s="7"/>
       <c r="E314" s="7"/>
-      <c r="F314" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G314" s="26"/>
-    </row>
-    <row r="315" spans="1:7" ht="30" customHeight="1">
+      <c r="F314" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G314" s="26" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>776</v>
+        <v>757</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>777</v>
+        <v>758</v>
       </c>
       <c r="D315" s="7"/>
       <c r="E315" s="7"/>
-      <c r="F315" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G315" s="26"/>
-    </row>
-    <row r="316" spans="1:7" ht="60" customHeight="1">
+      <c r="F315" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G315" s="26" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>778</v>
+        <v>760</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>779</v>
+        <v>761</v>
       </c>
       <c r="D316" s="7"/>
       <c r="E316" s="7"/>
-      <c r="F316" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="G316" s="26"/>
-    </row>
-    <row r="317" spans="1:7">
+      <c r="F316" s="4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G316" s="26" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>780</v>
+        <v>763</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>781</v>
+        <v>764</v>
       </c>
       <c r="D317" s="7"/>
-      <c r="E317" s="1"/>
+      <c r="E317" s="7"/>
       <c r="F317" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G317" s="26"/>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>783</v>
+        <v>767</v>
       </c>
       <c r="D318" s="7"/>
       <c r="E318" s="7"/>
-      <c r="F318" s="3" t="s">
-        <v>20</v>
+      <c r="F318" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G318" s="26"/>
     </row>
-    <row r="319" spans="1:7" ht="60" customHeight="1">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>784</v>
+        <v>1003</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>785</v>
+        <v>1004</v>
       </c>
       <c r="D319" s="7"/>
       <c r="E319" s="7"/>
-      <c r="F319" s="5" t="s">
-        <v>10</v>
+      <c r="F319" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G319" s="26"/>
     </row>
-    <row r="320" spans="1:7" ht="60" customHeight="1">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>786</v>
+        <v>768</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>787</v>
+        <v>769</v>
       </c>
       <c r="D320" s="7"/>
       <c r="E320" s="7"/>
       <c r="F320" s="5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G320" s="26"/>
     </row>
-    <row r="321" spans="1:7">
+    <row r="321" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>788</v>
+        <v>770</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>789</v>
+        <v>771</v>
       </c>
       <c r="D321" s="7"/>
       <c r="E321" s="7"/>
-      <c r="F321" s="5" t="s">
-        <v>10</v>
+      <c r="F321" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G321" s="26"/>
     </row>
-    <row r="322" spans="1:7" ht="30" customHeight="1">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>790</v>
+        <v>772</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>791</v>
+        <v>773</v>
       </c>
       <c r="D322" s="7"/>
       <c r="E322" s="7"/>
-      <c r="F322" s="5" t="s">
-        <v>20</v>
+      <c r="F322" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G322" s="26"/>
     </row>
-    <row r="323" spans="1:7" ht="30" customHeight="1">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>792</v>
+        <v>774</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="D323" s="1"/>
+        <v>775</v>
+      </c>
+      <c r="D323" s="7"/>
       <c r="E323" s="7"/>
       <c r="F323" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G323" s="26"/>
     </row>
-    <row r="324" spans="1:7" ht="60" customHeight="1">
+    <row r="324" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>794</v>
+        <v>776</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>795</v>
+        <v>777</v>
       </c>
       <c r="D324" s="7"/>
       <c r="E324" s="7"/>
-      <c r="F324" s="5" t="s">
+      <c r="F324" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G324" s="26"/>
     </row>
-    <row r="325" spans="1:7">
+    <row r="325" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>796</v>
+        <v>778</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>797</v>
+        <v>779</v>
       </c>
       <c r="D325" s="7"/>
       <c r="E325" s="7"/>
       <c r="F325" s="3" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G325" s="26"/>
     </row>
-    <row r="326" spans="1:7" ht="60" customHeight="1">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="D326" s="7" t="s">
-        <v>800</v>
-      </c>
-      <c r="E326" s="7"/>
-      <c r="F326" s="3" t="s">
-        <v>20</v>
+        <v>781</v>
+      </c>
+      <c r="D326" s="7"/>
+      <c r="E326" s="1"/>
+      <c r="F326" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G326" s="26"/>
     </row>
-    <row r="327" spans="1:7" ht="45" customHeight="1">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>801</v>
+        <v>782</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>802</v>
+        <v>783</v>
       </c>
       <c r="D327" s="7"/>
       <c r="E327" s="7"/>
@@ -9739,257 +9836,255 @@
       </c>
       <c r="G327" s="26"/>
     </row>
-    <row r="328" spans="1:7" ht="60" customHeight="1">
+    <row r="328" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>803</v>
+        <v>784</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>804</v>
+        <v>785</v>
       </c>
       <c r="D328" s="7"/>
       <c r="E328" s="7"/>
-      <c r="F328" s="3" t="s">
-        <v>20</v>
+      <c r="F328" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="G328" s="26"/>
     </row>
-    <row r="329" spans="1:7">
+    <row r="329" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>805</v>
+        <v>786</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>806</v>
+        <v>787</v>
       </c>
       <c r="D329" s="7"/>
       <c r="E329" s="7"/>
-      <c r="F329" s="4" t="s">
+      <c r="F329" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G329" s="26"/>
     </row>
-    <row r="330" spans="1:7" ht="30" customHeight="1">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>807</v>
+        <v>788</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>808</v>
+        <v>789</v>
       </c>
       <c r="D330" s="7"/>
       <c r="E330" s="7"/>
-      <c r="F330" s="4" t="s">
+      <c r="F330" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G330" s="26"/>
     </row>
-    <row r="331" spans="1:7" ht="30" customHeight="1">
+    <row r="331" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>809</v>
+        <v>790</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>810</v>
+        <v>791</v>
       </c>
       <c r="D331" s="7"/>
       <c r="E331" s="7"/>
-      <c r="F331" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G331" s="24"/>
-    </row>
-    <row r="332" spans="1:7">
+      <c r="F331" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G331" s="26"/>
+    </row>
+    <row r="332" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>811</v>
+        <v>792</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>812</v>
-      </c>
-      <c r="D332" s="7"/>
+        <v>793</v>
+      </c>
+      <c r="D332" s="1"/>
       <c r="E332" s="7"/>
       <c r="F332" s="5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G332" s="26"/>
     </row>
-    <row r="333" spans="1:7" ht="60" customHeight="1">
+    <row r="333" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>813</v>
+        <v>794</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>814</v>
+        <v>795</v>
       </c>
       <c r="D333" s="7"/>
       <c r="E333" s="7"/>
       <c r="F333" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G333" s="26"/>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>815</v>
+        <v>796</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>816</v>
+        <v>797</v>
       </c>
       <c r="D334" s="7"/>
       <c r="E334" s="7"/>
-      <c r="F334" s="5" t="s">
-        <v>29</v>
+      <c r="F334" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G334" s="26"/>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>817</v>
+        <v>798</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>818</v>
-      </c>
-      <c r="D335" s="7"/>
+        <v>799</v>
+      </c>
+      <c r="D335" s="7" t="s">
+        <v>800</v>
+      </c>
       <c r="E335" s="7"/>
-      <c r="F335" s="4" t="s">
-        <v>819</v>
-      </c>
-      <c r="G335" s="26" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="336" spans="1:7" ht="45" customHeight="1">
+      <c r="F335" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G335" s="26"/>
+    </row>
+    <row r="336" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>821</v>
+        <v>801</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="D336" s="1"/>
+        <v>802</v>
+      </c>
+      <c r="D336" s="7"/>
       <c r="E336" s="7"/>
-      <c r="F336" s="5" t="s">
+      <c r="F336" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G336" s="26"/>
     </row>
-    <row r="337" spans="1:7">
+    <row r="337" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>823</v>
+        <v>803</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>824</v>
+        <v>804</v>
       </c>
       <c r="D337" s="7"/>
       <c r="E337" s="7"/>
-      <c r="F337" s="4" t="s">
+      <c r="F337" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G337" s="26"/>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>825</v>
+        <v>805</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>826</v>
+        <v>806</v>
       </c>
       <c r="D338" s="7"/>
       <c r="E338" s="7"/>
       <c r="F338" s="4" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G338" s="26"/>
     </row>
-    <row r="339" spans="1:7" ht="45" customHeight="1">
+    <row r="339" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>827</v>
+        <v>807</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>828</v>
+        <v>808</v>
       </c>
       <c r="D339" s="7"/>
       <c r="E339" s="7"/>
-      <c r="F339" s="5" t="s">
-        <v>29</v>
+      <c r="F339" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G339" s="26"/>
     </row>
-    <row r="340" spans="1:7" ht="45" customHeight="1">
+    <row r="340" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>829</v>
+        <v>809</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="D340" s="7" t="s">
-        <v>831</v>
-      </c>
+        <v>810</v>
+      </c>
+      <c r="D340" s="7"/>
       <c r="E340" s="7"/>
-      <c r="F340" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G340" s="26"/>
-    </row>
-    <row r="341" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+      <c r="F340" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G340" s="24"/>
+    </row>
+    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>832</v>
+        <v>811</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>833</v>
+        <v>812</v>
       </c>
       <c r="D341" s="7"/>
       <c r="E341" s="7"/>
-      <c r="F341" s="3" t="s">
-        <v>29</v>
+      <c r="F341" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="G341" s="26"/>
     </row>
-    <row r="342" spans="1:7" ht="45" customHeight="1">
+    <row r="342" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>834</v>
+        <v>813</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>835</v>
+        <v>814</v>
       </c>
       <c r="D342" s="7"/>
       <c r="E342" s="7"/>
@@ -9998,688 +10093,845 @@
       </c>
       <c r="G342" s="26"/>
     </row>
-    <row r="343" spans="1:7" ht="30">
+    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>836</v>
+        <v>815</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>837</v>
+        <v>816</v>
       </c>
       <c r="D343" s="7"/>
       <c r="E343" s="7"/>
-      <c r="F343" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G343" s="24"/>
-    </row>
-    <row r="344" spans="1:7" ht="30" customHeight="1">
+      <c r="F343" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G343" s="26"/>
+    </row>
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>838</v>
+        <v>817</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>839</v>
+        <v>818</v>
       </c>
       <c r="D344" s="7"/>
       <c r="E344" s="7"/>
-      <c r="F344" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G344" s="24"/>
-    </row>
-    <row r="345" spans="1:7" ht="30" customHeight="1">
+      <c r="F344" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="G344" s="26" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="345" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>840</v>
+        <v>821</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>841</v>
-      </c>
-      <c r="D345" s="7"/>
+        <v>822</v>
+      </c>
+      <c r="D345" s="1"/>
       <c r="E345" s="7"/>
-      <c r="F345" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G345" s="24"/>
-    </row>
-    <row r="346" spans="1:7">
+      <c r="F345" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G345" s="26"/>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>842</v>
+        <v>823</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>843</v>
+        <v>824</v>
       </c>
       <c r="D346" s="7"/>
-      <c r="E346" s="1"/>
+      <c r="E346" s="7"/>
       <c r="F346" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G346" s="26"/>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>844</v>
+        <v>825</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>845</v>
+        <v>826</v>
       </c>
       <c r="D347" s="7"/>
       <c r="E347" s="7"/>
-      <c r="F347" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G347" s="26" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="348" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+      <c r="F347" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G347" s="26"/>
+    </row>
+    <row r="348" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>847</v>
+        <v>827</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>848</v>
+        <v>828</v>
       </c>
       <c r="D348" s="7"/>
       <c r="E348" s="7"/>
-      <c r="F348" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G348" s="26" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="349" spans="1:7" ht="45" customHeight="1">
+      <c r="F348" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G348" s="26"/>
+    </row>
+    <row r="349" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>849</v>
+        <v>829</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>850</v>
-      </c>
-      <c r="D349" s="7"/>
+        <v>830</v>
+      </c>
+      <c r="D349" s="7" t="s">
+        <v>831</v>
+      </c>
       <c r="E349" s="7"/>
-      <c r="F349" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G349" s="26" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="350" spans="1:7" ht="30" customHeight="1">
+      <c r="F349" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G349" s="26"/>
+    </row>
+    <row r="350" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A350" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>851</v>
+        <v>832</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>852</v>
+        <v>833</v>
       </c>
       <c r="D350" s="7"/>
-      <c r="E350" s="7" t="s">
-        <v>796</v>
-      </c>
-      <c r="F350" s="6" t="s">
+      <c r="E350" s="7"/>
+      <c r="F350" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="G350" s="24"/>
-    </row>
-    <row r="351" spans="1:7" ht="45" customHeight="1">
+      <c r="G350" s="26"/>
+    </row>
+    <row r="351" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>853</v>
+        <v>834</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>854</v>
+        <v>835</v>
       </c>
       <c r="D351" s="7"/>
       <c r="E351" s="7"/>
       <c r="F351" s="5" t="s">
-        <v>855</v>
+        <v>29</v>
       </c>
       <c r="G351" s="26"/>
     </row>
-    <row r="352" spans="1:7" ht="45" customHeight="1">
+    <row r="352" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>1006</v>
+        <v>836</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>1007</v>
+        <v>837</v>
       </c>
       <c r="D352" s="7"/>
       <c r="E352" s="7"/>
-      <c r="F352" s="5" t="s">
+      <c r="F352" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G352" s="26"/>
-    </row>
-    <row r="353" spans="1:7" ht="30">
+      <c r="G352" s="24"/>
+    </row>
+    <row r="353" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>856</v>
+        <v>838</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>857</v>
+        <v>839</v>
       </c>
       <c r="D353" s="7"/>
       <c r="E353" s="7"/>
-      <c r="F353" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G353" s="26"/>
-    </row>
-    <row r="354" spans="1:7" ht="30" customHeight="1">
+      <c r="F353" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G353" s="24"/>
+    </row>
+    <row r="354" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>858</v>
+        <v>840</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>859</v>
+        <v>841</v>
       </c>
       <c r="D354" s="7"/>
       <c r="E354" s="7"/>
       <c r="F354" s="16" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G354" s="24"/>
     </row>
-    <row r="355" spans="1:7" ht="30" customHeight="1">
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>860</v>
+        <v>842</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>861</v>
+        <v>843</v>
       </c>
       <c r="D355" s="7"/>
-      <c r="E355" s="7"/>
-      <c r="F355" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G355" s="26" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="356" spans="1:7">
+      <c r="E355" s="1"/>
+      <c r="F355" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G355" s="26"/>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>863</v>
+        <v>844</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>864</v>
+        <v>845</v>
       </c>
       <c r="D356" s="7"/>
       <c r="E356" s="7"/>
       <c r="F356" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G356" s="26"/>
-    </row>
-    <row r="357" spans="1:7">
+        <v>14</v>
+      </c>
+      <c r="G356" s="26" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A357" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>865</v>
+        <v>847</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>866</v>
+        <v>848</v>
       </c>
       <c r="D357" s="7"/>
       <c r="E357" s="7"/>
       <c r="F357" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G357" s="26"/>
-    </row>
-    <row r="358" spans="1:7" ht="30" customHeight="1">
+        <v>14</v>
+      </c>
+      <c r="G357" s="26" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>867</v>
+        <v>849</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>868</v>
+        <v>850</v>
       </c>
       <c r="D358" s="7"/>
       <c r="E358" s="7"/>
-      <c r="F358" s="5" t="s">
+      <c r="F358" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G358" s="26" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>870</v>
+        <v>851</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>871</v>
+        <v>852</v>
       </c>
       <c r="D359" s="7"/>
-      <c r="E359" s="7"/>
-      <c r="F359" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G359" s="26"/>
-    </row>
-    <row r="360" spans="1:7">
-      <c r="A360" t="s">
+      <c r="E359" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="F359" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G359" s="24"/>
+    </row>
+    <row r="360" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A360" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B360" t="s">
-        <v>872</v>
-      </c>
-      <c r="C360" t="s">
-        <v>873</v>
+      <c r="B360" s="2" t="s">
+        <v>853</v>
+      </c>
+      <c r="C360" s="2" t="s">
+        <v>854</v>
       </c>
       <c r="D360" s="7"/>
       <c r="E360" s="7"/>
-      <c r="F360" s="12" t="s">
-        <v>29</v>
+      <c r="F360" s="5" t="s">
+        <v>855</v>
       </c>
       <c r="G360" s="26"/>
     </row>
-    <row r="361" spans="1:7">
+    <row r="361" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>874</v>
+        <v>1005</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>875</v>
+        <v>1006</v>
       </c>
       <c r="D361" s="7"/>
-      <c r="E361" s="1"/>
+      <c r="E361" s="7"/>
       <c r="F361" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G361" s="26"/>
     </row>
-    <row r="362" spans="1:7">
+    <row r="362" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>876</v>
+        <v>856</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>877</v>
+        <v>857</v>
       </c>
       <c r="D362" s="7"/>
       <c r="E362" s="7"/>
       <c r="F362" s="5" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G362" s="26"/>
     </row>
-    <row r="363" spans="1:7">
+    <row r="363" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>1008</v>
+        <v>858</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>1009</v>
+        <v>859</v>
       </c>
       <c r="D363" s="7"/>
-      <c r="E363" s="7" t="s">
-        <v>1010</v>
-      </c>
-      <c r="F363" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G363" s="26"/>
-    </row>
-    <row r="364" spans="1:7">
+      <c r="E363" s="7"/>
+      <c r="F363" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G363" s="24"/>
+    </row>
+    <row r="364" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>878</v>
+        <v>860</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>879</v>
+        <v>861</v>
       </c>
       <c r="D364" s="7"/>
       <c r="E364" s="7"/>
-      <c r="F364" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G364" s="26"/>
-    </row>
-    <row r="365" spans="1:7">
+      <c r="F364" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G364" s="26" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>880</v>
+        <v>863</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>881</v>
+        <v>864</v>
       </c>
       <c r="D365" s="7"/>
-      <c r="E365" s="7" t="s">
-        <v>876</v>
-      </c>
-      <c r="F365" s="3" t="s">
+      <c r="E365" s="7"/>
+      <c r="F365" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G365" s="24"/>
-    </row>
-    <row r="366" spans="1:7">
+      <c r="G365" s="26"/>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>882</v>
+        <v>865</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>883</v>
+        <v>866</v>
       </c>
       <c r="D366" s="7"/>
       <c r="E366" s="7"/>
-      <c r="F366" s="16" t="s">
+      <c r="F366" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G366" s="24"/>
-    </row>
-    <row r="367" spans="1:7">
-      <c r="A367" s="17" t="s">
+      <c r="G366" s="26"/>
+    </row>
+    <row r="367" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A367" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B367" s="17" t="s">
-        <v>884</v>
-      </c>
-      <c r="C367" s="17" t="s">
-        <v>885</v>
-      </c>
-      <c r="D367" s="27"/>
-      <c r="E367" s="27"/>
-      <c r="F367" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G367" s="28"/>
-    </row>
-    <row r="368" spans="1:7">
+      <c r="B367" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="C367" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="D367" s="7"/>
+      <c r="E367" s="7"/>
+      <c r="F367" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G367" s="26" t="s">
+        <v>869</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>886</v>
+        <v>870</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="D368" s="1"/>
+        <v>871</v>
+      </c>
+      <c r="D368" s="7"/>
       <c r="E368" s="7"/>
-      <c r="F368" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G368" s="26" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7">
-      <c r="A369" s="2" t="s">
+      <c r="F368" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G368" s="26"/>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A369" t="s">
         <v>765</v>
       </c>
-      <c r="B369" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="C369" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="D369" s="1"/>
+      <c r="B369" t="s">
+        <v>872</v>
+      </c>
+      <c r="C369" t="s">
+        <v>873</v>
+      </c>
+      <c r="D369" s="7"/>
       <c r="E369" s="7"/>
-      <c r="F369" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G369" s="26" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="370" spans="1:7" ht="30">
+      <c r="F369" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G369" s="26"/>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>892</v>
+        <v>874</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="D370" s="1"/>
-      <c r="E370" s="7"/>
+        <v>875</v>
+      </c>
+      <c r="D370" s="7"/>
+      <c r="E370" s="1"/>
       <c r="F370" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G370" s="26"/>
     </row>
-    <row r="371" spans="1:7">
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>1011</v>
+        <v>876</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D371" s="1"/>
+        <v>877</v>
+      </c>
+      <c r="D371" s="7"/>
       <c r="E371" s="7"/>
       <c r="F371" s="5" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G371" s="26"/>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>1013</v>
+        <v>1007</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D372" s="1"/>
+        <v>1008</v>
+      </c>
+      <c r="D372" s="7"/>
       <c r="E372" s="7" t="s">
-        <v>772</v>
+        <v>1009</v>
       </c>
       <c r="F372" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G372" s="26"/>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B373" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>879</v>
+      </c>
+      <c r="D373" s="7"/>
+      <c r="E373" s="7"/>
+      <c r="F373" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G373" s="26"/>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A374" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B374" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C374" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="D374" s="7"/>
+      <c r="E374" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="F374" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G374" s="24"/>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A375" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B375" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="D375" s="7"/>
+      <c r="E375" s="7"/>
+      <c r="F375" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G375" s="24"/>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A376" s="17" t="s">
+        <v>765</v>
+      </c>
+      <c r="B376" s="17" t="s">
+        <v>884</v>
+      </c>
+      <c r="C376" s="17" t="s">
+        <v>885</v>
+      </c>
+      <c r="D376" s="27"/>
+      <c r="E376" s="27"/>
+      <c r="F376" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G376" s="28"/>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A377" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B377" s="2" t="s">
+        <v>886</v>
+      </c>
+      <c r="C377" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="D377" s="1"/>
+      <c r="E377" s="7"/>
+      <c r="F377" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G377" s="26" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A378" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B378" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>890</v>
+      </c>
+      <c r="D378" s="1"/>
+      <c r="E378" s="7"/>
+      <c r="F378" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G378" s="26" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A379" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B379" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="C379" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="D379" s="1"/>
+      <c r="E379" s="7"/>
+      <c r="F379" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G379" s="26"/>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A380" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="D380" s="1"/>
+      <c r="E380" s="7"/>
+      <c r="F380" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G380" s="26"/>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A381" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D381" s="1"/>
+      <c r="E381" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="F381" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G381" s="26"/>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A382" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C382" s="2" t="s">
         <v>1015</v>
       </c>
-      <c r="C373" s="2" t="s">
-        <v>1016</v>
-      </c>
-      <c r="D373" s="1"/>
-      <c r="E373" s="7"/>
-      <c r="F373" s="5" t="s">
+      <c r="D382" s="1"/>
+      <c r="E382" s="7"/>
+      <c r="F382" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G373" s="26"/>
-    </row>
-    <row r="374" spans="1:7">
-      <c r="A374" s="2" t="s">
+      <c r="G382" s="26"/>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A383" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="B374" s="2" t="s">
+      <c r="B383" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="C374" s="2" t="s">
+      <c r="C383" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="D374" s="7" t="s">
+      <c r="D383" s="7" t="s">
         <v>897</v>
       </c>
-      <c r="E374" s="7"/>
-      <c r="F374" s="25" t="s">
+      <c r="E383" s="7"/>
+      <c r="F383" s="25" t="s">
         <v>20</v>
       </c>
-      <c r="G374" s="26"/>
-    </row>
-    <row r="375" spans="1:7">
-      <c r="A375" s="2" t="s">
+      <c r="G383" s="26"/>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A384" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="B375" s="2" t="s">
+      <c r="B384" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="C375" s="2" t="s">
+      <c r="C384" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="D375" s="7" t="s">
+      <c r="D384" s="7" t="s">
         <v>900</v>
       </c>
-      <c r="E375" s="7"/>
-      <c r="F375" s="4" t="s">
+      <c r="E384" s="7"/>
+      <c r="F384" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G375" s="26"/>
-    </row>
-    <row r="376" spans="1:7" ht="30">
-      <c r="A376" s="2" t="s">
+      <c r="G384" s="26"/>
+    </row>
+    <row r="385" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A385" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="B376" s="2" t="s">
+      <c r="B385" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="C376" s="2" t="s">
+      <c r="C385" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="D376" s="1" t="s">
+      <c r="D385" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="E376" s="7"/>
-      <c r="F376" s="4" t="s">
+      <c r="E385" s="7"/>
+      <c r="F385" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G376" s="26"/>
-    </row>
-    <row r="377" spans="1:7" ht="30">
-      <c r="A377" s="17" t="s">
+      <c r="G385" s="26"/>
+    </row>
+    <row r="386" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A386" s="17" t="s">
         <v>894</v>
       </c>
-      <c r="B377" s="17" t="s">
+      <c r="B386" s="17" t="s">
         <v>904</v>
       </c>
-      <c r="C377" s="17" t="s">
+      <c r="C386" s="17" t="s">
         <v>905</v>
       </c>
-      <c r="D377" s="27"/>
-      <c r="E377" s="27"/>
-      <c r="F377" s="18" t="s">
+      <c r="D386" s="27"/>
+      <c r="E386" s="27"/>
+      <c r="F386" s="18" t="s">
         <v>906</v>
       </c>
-      <c r="G377" s="28"/>
-    </row>
-    <row r="378" spans="1:7">
-      <c r="A378" t="s">
+      <c r="G386" s="28"/>
+    </row>
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A387" t="s">
         <v>894</v>
       </c>
-      <c r="B378" t="s">
+      <c r="B387" t="s">
         <v>907</v>
       </c>
-      <c r="C378" t="s">
+      <c r="C387" t="s">
         <v>908</v>
       </c>
-      <c r="D378" s="7"/>
-      <c r="E378" s="7"/>
-      <c r="F378" t="s">
+      <c r="D387" s="7"/>
+      <c r="E387" s="7"/>
+      <c r="F387" t="s">
         <v>29</v>
       </c>
-      <c r="G378" s="26"/>
-    </row>
-    <row r="379" spans="1:7">
-      <c r="A379" t="s">
+      <c r="G387" s="26"/>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A388" t="s">
         <v>894</v>
       </c>
-      <c r="B379" t="s">
+      <c r="B388" t="s">
         <v>909</v>
       </c>
-      <c r="C379" t="s">
+      <c r="C388" t="s">
         <v>910</v>
       </c>
-      <c r="D379" s="7" t="s">
+      <c r="D388" s="7" t="s">
         <v>911</v>
       </c>
-      <c r="E379" s="7"/>
-      <c r="F379" t="s">
+      <c r="E388" s="7"/>
+      <c r="F388" t="s">
         <v>29</v>
       </c>
-      <c r="G379" s="26"/>
-    </row>
-    <row r="380" spans="1:7">
-      <c r="A380" t="s">
+      <c r="G388" s="26"/>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A389" t="s">
         <v>894</v>
       </c>
-      <c r="B380" t="s">
+      <c r="B389" t="s">
         <v>912</v>
       </c>
-      <c r="C380" t="s">
+      <c r="C389" t="s">
         <v>913</v>
       </c>
-      <c r="D380" s="7" t="s">
+      <c r="D389" s="7" t="s">
         <v>914</v>
       </c>
-      <c r="E380" s="7"/>
-      <c r="F380" t="s">
+      <c r="E389" s="7"/>
+      <c r="F389" t="s">
         <v>20</v>
       </c>
-      <c r="G380" s="26"/>
-    </row>
-    <row r="381" spans="1:7">
-      <c r="D381" s="7"/>
-      <c r="E381" s="7"/>
-      <c r="G381" s="26"/>
+      <c r="G389" s="26"/>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D390" s="7"/>
+      <c r="E390" s="7"/>
+      <c r="G390" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -10690,13 +10942,13 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
     <col min="2" max="2" width="52.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -10704,7 +10956,7 @@
         <v>974</v>
       </c>
     </row>
-    <row r="2" spans="1:2">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -10712,7 +10964,7 @@
         <v>975</v>
       </c>
     </row>
-    <row r="3" spans="1:2">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
@@ -10720,7 +10972,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -10728,7 +10980,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>131</v>
       </c>
@@ -10736,7 +10988,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="6" spans="1:2">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>141</v>
       </c>
@@ -10744,7 +10996,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="7" spans="1:2">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>137</v>
       </c>
@@ -10752,7 +11004,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="8" spans="1:2">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>196</v>
       </c>
@@ -10760,7 +11012,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="9" spans="1:2">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>210</v>
       </c>
@@ -10768,7 +11020,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="10" spans="1:2">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>388</v>
       </c>
@@ -10776,7 +11028,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="11" spans="1:2">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>405</v>
       </c>
@@ -10784,7 +11036,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="12" spans="1:2">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>467</v>
       </c>
@@ -10792,7 +11044,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="13" spans="1:2">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>475</v>
       </c>
@@ -10800,7 +11052,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="14" spans="1:2">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>510</v>
       </c>
@@ -10808,7 +11060,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>678</v>
       </c>
@@ -10816,7 +11068,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>730</v>
       </c>
@@ -10824,7 +11076,7 @@
         <v>989</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>750</v>
       </c>
@@ -10832,7 +11084,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>765</v>
       </c>
@@ -10840,7 +11092,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="19" spans="1:2">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>894</v>
       </c>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\AppData\Local\Temp\claude\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-input-rename2\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AF0AF5B-A907-47AC-87E4-A9C0CFB9566C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09319B7B-B9B4-4734-B6A5-3E30C1B6365C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1839" uniqueCount="1053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1849" uniqueCount="1059">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -3168,19 +3168,37 @@
     <t>Your country has data on vehicle occupancy or load factors, or on how car ownership responds to transit and demand-management policies</t>
   </si>
   <si>
-    <t>VOS</t>
-  </si>
-  <si>
-    <t>Vehicle Ownership Saturation</t>
-  </si>
-  <si>
-    <t>BFfHO BAU Fleet from Household Ownership, VOS Vehicle Ownership Saturation, VOIR Vehicle Ownership Income Response, MBFGR Minimum BAU Fleet Growth Rate</t>
-  </si>
-  <si>
     <t>SYVbT, NoH, BGDP</t>
   </si>
   <si>
-    <t>Your country has a vehicle-stock projection to fit the car-ownership curve to (otherwise use the published Dargay-Gately defaults in the workbook), or vehicle types whose fleet should keep growing on a trend while loading recovers to normal</t>
+    <t>VpHC</t>
+  </si>
+  <si>
+    <t>Vehicles per Household Curve</t>
+  </si>
+  <si>
+    <t>VpHCS Vehicles per Household Curve Saturation, VpHCIR Vehicles per Household Curve Income Response</t>
+  </si>
+  <si>
+    <t>Your country has a vehicle-stock projection to fit the car-ownership curve to; otherwise use the published Dargay-Gately values in the workbook, converted to per household and to your GDP units</t>
+  </si>
+  <si>
+    <t>BFfHO</t>
+  </si>
+  <si>
+    <t>BAU Fleet from Household Ownership</t>
+  </si>
+  <si>
+    <t>A vehicle type other than passenger cars should follow households x ownership rather than travel at normal use</t>
+  </si>
+  <si>
+    <t>MBFGR</t>
+  </si>
+  <si>
+    <t>Minimum BAU Fleet Growth Rate</t>
+  </si>
+  <si>
+    <t>A vehicle type that fills toward its normal loading (buses, passenger rail, aircraft) should keep growing on an observed fleet trend meanwhile</t>
   </si>
 </sst>
 </file>
@@ -3994,7 +4012,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G392"/>
+  <dimension ref="A1:G394"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
@@ -9902,32 +9920,34 @@
         <v>765</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>788</v>
+        <v>1053</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>789</v>
+        <v>1054</v>
       </c>
       <c r="D330" s="7"/>
       <c r="E330" s="7"/>
       <c r="F330" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G330" s="26"/>
-    </row>
-    <row r="331" spans="1:7" ht="30" customHeight="1">
+        <v>29</v>
+      </c>
+      <c r="G330" s="26" t="s">
+        <v>1055</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7">
       <c r="A331" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D331" s="7"/>
       <c r="E331" s="7"/>
       <c r="F331" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G331" s="26"/>
     </row>
@@ -9936,97 +9956,97 @@
         <v>765</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="D332" s="1"/>
+        <v>791</v>
+      </c>
+      <c r="D332" s="7"/>
       <c r="E332" s="7"/>
       <c r="F332" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G332" s="26"/>
     </row>
-    <row r="333" spans="1:7" ht="60" customHeight="1">
+    <row r="333" spans="1:7" ht="30" customHeight="1">
       <c r="A333" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="D333" s="7"/>
+        <v>793</v>
+      </c>
+      <c r="D333" s="1"/>
       <c r="E333" s="7"/>
       <c r="F333" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G333" s="26"/>
     </row>
-    <row r="334" spans="1:7">
+    <row r="334" spans="1:7" ht="60" customHeight="1">
       <c r="A334" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D334" s="7"/>
       <c r="E334" s="7"/>
-      <c r="F334" s="3" t="s">
+      <c r="F334" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G334" s="26"/>
     </row>
-    <row r="335" spans="1:7" ht="60" customHeight="1">
+    <row r="335" spans="1:7">
       <c r="A335" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="D335" s="7" t="s">
-        <v>800</v>
-      </c>
+        <v>797</v>
+      </c>
+      <c r="D335" s="7"/>
       <c r="E335" s="7"/>
       <c r="F335" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G335" s="26"/>
     </row>
-    <row r="336" spans="1:7" ht="45" customHeight="1">
+    <row r="336" spans="1:7" ht="60" customHeight="1">
       <c r="A336" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="D336" s="7"/>
+        <v>799</v>
+      </c>
+      <c r="D336" s="7" t="s">
+        <v>800</v>
+      </c>
       <c r="E336" s="7"/>
       <c r="F336" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G336" s="26"/>
     </row>
-    <row r="337" spans="1:7" ht="60" customHeight="1">
+    <row r="337" spans="1:7" ht="45" customHeight="1">
       <c r="A337" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D337" s="7"/>
       <c r="E337" s="7"/>
@@ -10035,32 +10055,32 @@
       </c>
       <c r="G337" s="26"/>
     </row>
-    <row r="338" spans="1:7">
+    <row r="338" spans="1:7" ht="60" customHeight="1">
       <c r="A338" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D338" s="7"/>
       <c r="E338" s="7"/>
-      <c r="F338" s="4" t="s">
-        <v>10</v>
+      <c r="F338" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G338" s="26"/>
     </row>
-    <row r="339" spans="1:7" ht="30" customHeight="1">
+    <row r="339" spans="1:7">
       <c r="A339" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D339" s="7"/>
       <c r="E339" s="7"/>
@@ -10074,61 +10094,61 @@
         <v>765</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D340" s="7"/>
       <c r="E340" s="7"/>
-      <c r="F340" s="6" t="s">
+      <c r="F340" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G340" s="24"/>
-    </row>
-    <row r="341" spans="1:7">
+      <c r="G340" s="26"/>
+    </row>
+    <row r="341" spans="1:7" ht="30" customHeight="1">
       <c r="A341" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D341" s="7"/>
       <c r="E341" s="7"/>
-      <c r="F341" s="5" t="s">
+      <c r="F341" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G341" s="26"/>
-    </row>
-    <row r="342" spans="1:7" ht="60" customHeight="1">
+      <c r="G341" s="24"/>
+    </row>
+    <row r="342" spans="1:7">
       <c r="A342" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D342" s="7"/>
       <c r="E342" s="7"/>
       <c r="F342" s="5" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G342" s="26"/>
     </row>
-    <row r="343" spans="1:7">
+    <row r="343" spans="1:7" ht="60" customHeight="1">
       <c r="A343" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D343" s="7"/>
       <c r="E343" s="7"/>
@@ -10142,50 +10162,50 @@
         <v>765</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D344" s="7"/>
       <c r="E344" s="7"/>
-      <c r="F344" s="4" t="s">
-        <v>819</v>
-      </c>
-      <c r="G344" s="26" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="345" spans="1:7" ht="45" customHeight="1">
+      <c r="F344" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G344" s="26"/>
+    </row>
+    <row r="345" spans="1:7">
       <c r="A345" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="D345" s="1"/>
+        <v>818</v>
+      </c>
+      <c r="D345" s="7"/>
       <c r="E345" s="7"/>
-      <c r="F345" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G345" s="26"/>
-    </row>
-    <row r="346" spans="1:7">
+      <c r="F345" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="G345" s="26" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" ht="45" customHeight="1">
       <c r="A346" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="D346" s="7"/>
+        <v>822</v>
+      </c>
+      <c r="D346" s="1"/>
       <c r="E346" s="7"/>
-      <c r="F346" s="4" t="s">
+      <c r="F346" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G346" s="26"/>
@@ -10195,53 +10215,53 @@
         <v>765</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>1044</v>
+        <v>823</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="D347" s="7" t="s">
-        <v>1046</v>
-      </c>
+        <v>824</v>
+      </c>
+      <c r="D347" s="7"/>
       <c r="E347" s="7"/>
-      <c r="F347" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G347" s="26" t="s">
-        <v>1047</v>
-      </c>
+      <c r="F347" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G347" s="26"/>
     </row>
     <row r="348" spans="1:7">
       <c r="A348" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>825</v>
+        <v>1044</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="D348" s="7"/>
+        <v>1045</v>
+      </c>
+      <c r="D348" s="7" t="s">
+        <v>1046</v>
+      </c>
       <c r="E348" s="7"/>
-      <c r="F348" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G348" s="26"/>
-    </row>
-    <row r="349" spans="1:7" ht="45" customHeight="1">
+      <c r="F348" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G348" s="26" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7">
       <c r="A349" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D349" s="7"/>
       <c r="E349" s="7"/>
-      <c r="F349" s="5" t="s">
-        <v>29</v>
+      <c r="F349" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G349" s="26"/>
     </row>
@@ -10250,85 +10270,85 @@
         <v>765</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="D350" s="7" t="s">
-        <v>831</v>
-      </c>
+        <v>828</v>
+      </c>
+      <c r="D350" s="7"/>
       <c r="E350" s="7"/>
-      <c r="F350" s="3" t="s">
-        <v>20</v>
+      <c r="F350" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G350" s="26"/>
     </row>
-    <row r="351" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="351" spans="1:7" ht="45" customHeight="1">
       <c r="A351" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="D351" s="7"/>
+        <v>830</v>
+      </c>
+      <c r="D351" s="7" t="s">
+        <v>831</v>
+      </c>
       <c r="E351" s="7"/>
       <c r="F351" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G351" s="26"/>
     </row>
-    <row r="352" spans="1:7" ht="45" customHeight="1">
+    <row r="352" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
       <c r="A352" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D352" s="7"/>
       <c r="E352" s="7"/>
-      <c r="F352" s="5" t="s">
+      <c r="F352" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G352" s="26"/>
     </row>
-    <row r="353" spans="1:7" ht="30">
+    <row r="353" spans="1:7" ht="45" customHeight="1">
       <c r="A353" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D353" s="7"/>
       <c r="E353" s="7"/>
-      <c r="F353" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G353" s="24"/>
-    </row>
-    <row r="354" spans="1:7" ht="30" customHeight="1">
+      <c r="F353" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G353" s="26"/>
+    </row>
+    <row r="354" spans="1:7" ht="30">
       <c r="A354" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D354" s="7"/>
       <c r="E354" s="7"/>
       <c r="F354" s="16" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G354" s="24"/>
     </row>
@@ -10337,10 +10357,10 @@
         <v>765</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="D355" s="7"/>
       <c r="E355" s="7"/>
@@ -10349,70 +10369,68 @@
       </c>
       <c r="G355" s="24"/>
     </row>
-    <row r="356" spans="1:7">
+    <row r="356" spans="1:7" ht="30" customHeight="1">
       <c r="A356" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D356" s="7"/>
-      <c r="E356" s="1"/>
-      <c r="F356" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G356" s="26"/>
+      <c r="E356" s="7"/>
+      <c r="F356" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G356" s="24"/>
     </row>
     <row r="357" spans="1:7">
       <c r="A357" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D357" s="7"/>
-      <c r="E357" s="7"/>
-      <c r="F357" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G357" s="26" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="358" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+      <c r="E357" s="1"/>
+      <c r="F357" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G357" s="26"/>
+    </row>
+    <row r="358" spans="1:7">
       <c r="A358" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D358" s="7"/>
       <c r="E358" s="7"/>
-      <c r="F358" s="4" t="s">
+      <c r="F358" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G358" s="26" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="45" customHeight="1">
+    <row r="359" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
       <c r="A359" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D359" s="7"/>
       <c r="E359" s="7"/>
@@ -10423,230 +10441,234 @@
         <v>846</v>
       </c>
     </row>
-    <row r="360" spans="1:7" ht="30" customHeight="1">
+    <row r="360" spans="1:7" ht="45" customHeight="1">
       <c r="A360" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D360" s="7"/>
-      <c r="E360" s="7" t="s">
-        <v>796</v>
-      </c>
-      <c r="F360" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G360" s="24"/>
-    </row>
-    <row r="361" spans="1:7" ht="45" customHeight="1">
+      <c r="E360" s="7"/>
+      <c r="F360" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G360" s="26" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7">
       <c r="A361" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>853</v>
+        <v>1056</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>854</v>
+        <v>1057</v>
       </c>
       <c r="D361" s="7"/>
       <c r="E361" s="7"/>
       <c r="F361" s="5" t="s">
-        <v>855</v>
-      </c>
-      <c r="G361" s="26"/>
-    </row>
-    <row r="362" spans="1:7" ht="45" customHeight="1">
+        <v>29</v>
+      </c>
+      <c r="G361" s="26" t="s">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" ht="30" customHeight="1">
       <c r="A362" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>1005</v>
+        <v>851</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1006</v>
+        <v>852</v>
       </c>
       <c r="D362" s="7"/>
-      <c r="E362" s="7"/>
-      <c r="F362" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G362" s="26"/>
-    </row>
-    <row r="363" spans="1:7" ht="30">
+      <c r="E362" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="F362" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G362" s="24"/>
+    </row>
+    <row r="363" spans="1:7" ht="45" customHeight="1">
       <c r="A363" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D363" s="7"/>
       <c r="E363" s="7"/>
       <c r="F363" s="5" t="s">
-        <v>29</v>
+        <v>855</v>
       </c>
       <c r="G363" s="26"/>
     </row>
-    <row r="364" spans="1:7" ht="30" customHeight="1">
+    <row r="364" spans="1:7" ht="45" customHeight="1">
       <c r="A364" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>858</v>
+        <v>1005</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>859</v>
+        <v>1006</v>
       </c>
       <c r="D364" s="7"/>
       <c r="E364" s="7"/>
-      <c r="F364" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G364" s="24"/>
-    </row>
-    <row r="365" spans="1:7" ht="30" customHeight="1">
+      <c r="F364" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G364" s="26"/>
+    </row>
+    <row r="365" spans="1:7" ht="30">
       <c r="A365" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>860</v>
+        <v>856</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="D365" s="7"/>
       <c r="E365" s="7"/>
-      <c r="F365" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G365" s="26" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="366" spans="1:7">
+      <c r="F365" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G365" s="26"/>
+    </row>
+    <row r="366" spans="1:7" ht="30" customHeight="1">
       <c r="A366" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>863</v>
+        <v>858</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>864</v>
+        <v>859</v>
       </c>
       <c r="D366" s="7"/>
       <c r="E366" s="7"/>
-      <c r="F366" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G366" s="26"/>
-    </row>
-    <row r="367" spans="1:7">
+      <c r="F366" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G366" s="24"/>
+    </row>
+    <row r="367" spans="1:7" ht="30" customHeight="1">
       <c r="A367" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>866</v>
+        <v>861</v>
       </c>
       <c r="D367" s="7"/>
       <c r="E367" s="7"/>
-      <c r="F367" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G367" s="26"/>
-    </row>
-    <row r="368" spans="1:7" ht="30" customHeight="1">
+      <c r="F367" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G367" s="26" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7">
       <c r="A368" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>867</v>
+        <v>863</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>868</v>
+        <v>864</v>
       </c>
       <c r="D368" s="7"/>
       <c r="E368" s="7"/>
       <c r="F368" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G368" s="26" t="s">
-        <v>869</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G368" s="26"/>
     </row>
     <row r="369" spans="1:7">
       <c r="A369" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>870</v>
+        <v>865</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>871</v>
+        <v>866</v>
       </c>
       <c r="D369" s="7"/>
       <c r="E369" s="7"/>
-      <c r="F369" s="12" t="s">
+      <c r="F369" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G369" s="26"/>
     </row>
-    <row r="370" spans="1:7">
-      <c r="A370" t="s">
+    <row r="370" spans="1:7" ht="30" customHeight="1">
+      <c r="A370" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B370" t="s">
-        <v>872</v>
-      </c>
-      <c r="C370" t="s">
-        <v>873</v>
+      <c r="B370" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="C370" s="2" t="s">
+        <v>868</v>
       </c>
       <c r="D370" s="7"/>
       <c r="E370" s="7"/>
-      <c r="F370" s="12" t="s">
-        <v>29</v>
-      </c>
-      <c r="G370" s="26"/>
+      <c r="F370" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G370" s="26" t="s">
+        <v>869</v>
+      </c>
     </row>
     <row r="371" spans="1:7">
       <c r="A371" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>874</v>
+        <v>870</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="D371" s="7"/>
-      <c r="E371" s="1"/>
-      <c r="F371" s="5" t="s">
+      <c r="E371" s="7"/>
+      <c r="F371" s="12" t="s">
         <v>20</v>
       </c>
       <c r="G371" s="26"/>
     </row>
     <row r="372" spans="1:7">
-      <c r="A372" s="2" t="s">
+      <c r="A372" t="s">
         <v>765</v>
       </c>
-      <c r="B372" s="2" t="s">
-        <v>876</v>
-      </c>
-      <c r="C372" s="2" t="s">
-        <v>877</v>
+      <c r="B372" t="s">
+        <v>872</v>
+      </c>
+      <c r="C372" t="s">
+        <v>873</v>
       </c>
       <c r="D372" s="7"/>
       <c r="E372" s="7"/>
-      <c r="F372" s="5" t="s">
-        <v>37</v>
+      <c r="F372" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="G372" s="26"/>
     </row>
@@ -10655,15 +10677,13 @@
         <v>765</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>1007</v>
+        <v>874</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>1008</v>
+        <v>875</v>
       </c>
       <c r="D373" s="7"/>
-      <c r="E373" s="7" t="s">
-        <v>1009</v>
-      </c>
+      <c r="E373" s="1"/>
       <c r="F373" s="5" t="s">
         <v>20</v>
       </c>
@@ -10674,15 +10694,15 @@
         <v>765</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D374" s="7"/>
       <c r="E374" s="7"/>
-      <c r="F374" s="4" t="s">
-        <v>96</v>
+      <c r="F374" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G374" s="26"/>
     </row>
@@ -10691,163 +10711,163 @@
         <v>765</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>880</v>
+        <v>1007</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>881</v>
+        <v>1008</v>
       </c>
       <c r="D375" s="7"/>
       <c r="E375" s="7" t="s">
-        <v>876</v>
-      </c>
-      <c r="F375" s="3" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F375" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G375" s="24"/>
+      <c r="G375" s="26"/>
     </row>
     <row r="376" spans="1:7">
       <c r="A376" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>882</v>
+        <v>878</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="D376" s="7"/>
       <c r="E376" s="7"/>
-      <c r="F376" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G376" s="24"/>
+      <c r="F376" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G376" s="26"/>
     </row>
     <row r="377" spans="1:7">
       <c r="A377" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>1048</v>
+        <v>880</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>1049</v>
-      </c>
-      <c r="D377" s="7" t="s">
-        <v>1050</v>
-      </c>
+        <v>881</v>
+      </c>
+      <c r="D377" s="7"/>
       <c r="E377" s="7" t="s">
-        <v>1051</v>
-      </c>
-      <c r="F377" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="F377" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G377" s="26" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="378" spans="1:7" ht="15.75" thickBot="1">
-      <c r="A378" s="17" t="s">
+      <c r="G377" s="24"/>
+    </row>
+    <row r="378" spans="1:7">
+      <c r="A378" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B378" s="17" t="s">
-        <v>884</v>
-      </c>
-      <c r="C378" s="17" t="s">
-        <v>885</v>
-      </c>
-      <c r="D378" s="27"/>
-      <c r="E378" s="27"/>
-      <c r="F378" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G378" s="28"/>
+      <c r="B378" s="2" t="s">
+        <v>882</v>
+      </c>
+      <c r="C378" s="2" t="s">
+        <v>883</v>
+      </c>
+      <c r="D378" s="7"/>
+      <c r="E378" s="7"/>
+      <c r="F378" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G378" s="24"/>
     </row>
     <row r="379" spans="1:7">
       <c r="A379" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>886</v>
+        <v>1049</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="D379" s="1"/>
-      <c r="E379" s="7"/>
+        <v>1050</v>
+      </c>
+      <c r="D379" s="7" t="s">
+        <v>1051</v>
+      </c>
+      <c r="E379" s="7" t="s">
+        <v>1048</v>
+      </c>
       <c r="F379" s="5" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G379" s="26" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="380" spans="1:7">
-      <c r="A380" s="2" t="s">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" ht="15.75" thickBot="1">
+      <c r="A380" s="17" t="s">
         <v>765</v>
       </c>
-      <c r="B380" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="C380" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="D380" s="1"/>
-      <c r="E380" s="7"/>
-      <c r="F380" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G380" s="26" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7" ht="30">
+      <c r="B380" s="17" t="s">
+        <v>884</v>
+      </c>
+      <c r="C380" s="17" t="s">
+        <v>885</v>
+      </c>
+      <c r="D380" s="27"/>
+      <c r="E380" s="27"/>
+      <c r="F380" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G380" s="28"/>
+    </row>
+    <row r="381" spans="1:7">
       <c r="A381" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="D381" s="1"/>
       <c r="E381" s="7"/>
       <c r="F381" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G381" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="G381" s="26" t="s">
+        <v>888</v>
+      </c>
     </row>
     <row r="382" spans="1:7">
       <c r="A382" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1010</v>
+        <v>889</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>1011</v>
+        <v>890</v>
       </c>
       <c r="D382" s="1"/>
       <c r="E382" s="7"/>
       <c r="F382" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G382" s="26"/>
-    </row>
-    <row r="383" spans="1:7">
+        <v>14</v>
+      </c>
+      <c r="G382" s="26" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" ht="30">
       <c r="A383" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>1012</v>
+        <v>892</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>1013</v>
+        <v>893</v>
       </c>
       <c r="D383" s="1"/>
-      <c r="E383" s="7" t="s">
-        <v>772</v>
-      </c>
+      <c r="E383" s="7"/>
       <c r="F383" s="5" t="s">
         <v>29</v>
       </c>
@@ -10858,10 +10878,10 @@
         <v>765</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="D384" s="1"/>
       <c r="E384" s="7"/>
@@ -10872,137 +10892,173 @@
     </row>
     <row r="385" spans="1:7">
       <c r="A385" s="2" t="s">
-        <v>894</v>
+        <v>765</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>895</v>
+        <v>1012</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="D385" s="7" t="s">
-        <v>897</v>
-      </c>
-      <c r="E385" s="7"/>
-      <c r="F385" s="25" t="s">
-        <v>20</v>
+        <v>1013</v>
+      </c>
+      <c r="D385" s="1"/>
+      <c r="E385" s="7" t="s">
+        <v>772</v>
+      </c>
+      <c r="F385" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G385" s="26"/>
     </row>
     <row r="386" spans="1:7">
       <c r="A386" s="2" t="s">
-        <v>894</v>
+        <v>765</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>898</v>
+        <v>1014</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>899</v>
-      </c>
-      <c r="D386" s="7" t="s">
-        <v>900</v>
-      </c>
+        <v>1015</v>
+      </c>
+      <c r="D386" s="1"/>
       <c r="E386" s="7"/>
-      <c r="F386" s="4" t="s">
-        <v>20</v>
+      <c r="F386" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G386" s="26"/>
     </row>
-    <row r="387" spans="1:7" ht="30">
+    <row r="387" spans="1:7">
       <c r="A387" s="2" t="s">
         <v>894</v>
       </c>
       <c r="B387" s="2" t="s">
+        <v>895</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>896</v>
+      </c>
+      <c r="D387" s="7" t="s">
+        <v>897</v>
+      </c>
+      <c r="E387" s="7"/>
+      <c r="F387" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G387" s="26"/>
+    </row>
+    <row r="388" spans="1:7">
+      <c r="A388" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B388" s="2" t="s">
+        <v>898</v>
+      </c>
+      <c r="C388" s="2" t="s">
+        <v>899</v>
+      </c>
+      <c r="D388" s="7" t="s">
+        <v>900</v>
+      </c>
+      <c r="E388" s="7"/>
+      <c r="F388" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G388" s="26"/>
+    </row>
+    <row r="389" spans="1:7" ht="30">
+      <c r="A389" s="2" t="s">
+        <v>894</v>
+      </c>
+      <c r="B389" s="2" t="s">
         <v>901</v>
       </c>
-      <c r="C387" s="2" t="s">
+      <c r="C389" s="2" t="s">
         <v>902</v>
       </c>
-      <c r="D387" s="1" t="s">
+      <c r="D389" s="1" t="s">
         <v>903</v>
       </c>
-      <c r="E387" s="7"/>
-      <c r="F387" s="4" t="s">
+      <c r="E389" s="7"/>
+      <c r="F389" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G387" s="26"/>
-    </row>
-    <row r="388" spans="1:7" ht="30">
-      <c r="A388" s="17" t="s">
+      <c r="G389" s="26"/>
+    </row>
+    <row r="390" spans="1:7" ht="30">
+      <c r="A390" s="17" t="s">
         <v>894</v>
       </c>
-      <c r="B388" s="17" t="s">
+      <c r="B390" s="17" t="s">
         <v>904</v>
       </c>
-      <c r="C388" s="17" t="s">
+      <c r="C390" s="17" t="s">
         <v>905</v>
       </c>
-      <c r="D388" s="27"/>
-      <c r="E388" s="27"/>
-      <c r="F388" s="18" t="s">
+      <c r="D390" s="27"/>
+      <c r="E390" s="27"/>
+      <c r="F390" s="18" t="s">
         <v>906</v>
       </c>
-      <c r="G388" s="28"/>
-    </row>
-    <row r="389" spans="1:7">
-      <c r="A389" t="s">
-        <v>894</v>
-      </c>
-      <c r="B389" t="s">
-        <v>907</v>
-      </c>
-      <c r="C389" t="s">
-        <v>908</v>
-      </c>
-      <c r="D389" s="7"/>
-      <c r="E389" s="7"/>
-      <c r="F389" t="s">
-        <v>29</v>
-      </c>
-      <c r="G389" s="26"/>
-    </row>
-    <row r="390" spans="1:7">
-      <c r="A390" t="s">
-        <v>894</v>
-      </c>
-      <c r="B390" t="s">
-        <v>909</v>
-      </c>
-      <c r="C390" t="s">
-        <v>910</v>
-      </c>
-      <c r="D390" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="E390" s="7"/>
-      <c r="F390" t="s">
-        <v>29</v>
-      </c>
-      <c r="G390" s="26"/>
+      <c r="G390" s="28"/>
     </row>
     <row r="391" spans="1:7">
       <c r="A391" t="s">
         <v>894</v>
       </c>
       <c r="B391" t="s">
-        <v>912</v>
+        <v>907</v>
       </c>
       <c r="C391" t="s">
-        <v>913</v>
-      </c>
-      <c r="D391" s="7" t="s">
-        <v>914</v>
-      </c>
+        <v>908</v>
+      </c>
+      <c r="D391" s="7"/>
       <c r="E391" s="7"/>
       <c r="F391" t="s">
+        <v>29</v>
+      </c>
+      <c r="G391" s="26"/>
+    </row>
+    <row r="392" spans="1:7">
+      <c r="A392" t="s">
+        <v>894</v>
+      </c>
+      <c r="B392" t="s">
+        <v>909</v>
+      </c>
+      <c r="C392" t="s">
+        <v>910</v>
+      </c>
+      <c r="D392" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="E392" s="7"/>
+      <c r="F392" t="s">
+        <v>29</v>
+      </c>
+      <c r="G392" s="26"/>
+    </row>
+    <row r="393" spans="1:7">
+      <c r="A393" t="s">
+        <v>894</v>
+      </c>
+      <c r="B393" t="s">
+        <v>912</v>
+      </c>
+      <c r="C393" t="s">
+        <v>913</v>
+      </c>
+      <c r="D393" s="7" t="s">
+        <v>914</v>
+      </c>
+      <c r="E393" s="7"/>
+      <c r="F393" t="s">
         <v>20</v>
       </c>
-      <c r="G391" s="26"/>
-    </row>
-    <row r="392" spans="1:7">
-      <c r="D392" s="7"/>
-      <c r="E392" s="7"/>
-      <c r="G392" s="26"/>
+      <c r="G393" s="26"/>
+    </row>
+    <row r="394" spans="1:7">
+      <c r="D394" s="7"/>
+      <c r="E394" s="7"/>
+      <c r="G394" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30527"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\.claude\worktrees\cement-onto-robbie\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\.claude\worktrees\retrofit-isic-split\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9437FD38-AFFB-4F98-B00B-B033C273205A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35EDAA96-A1B6-40E5-955B-2C917E4C4944}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1950" windowWidth="21600" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1826" uniqueCount="1044">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1831" uniqueCount="1047">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -3154,6 +3154,15 @@
   </si>
   <si>
     <t>Share of last year's fleet-average CO2 intensity at or below which cement counts as low-carbon for the procurement lever (US: GSA best-20-percent limit over the PCA industry-average declaration, 0.817). Only matters when that lever is used.</t>
+  </si>
+  <si>
+    <t>SoBRCbIC</t>
+  </si>
+  <si>
+    <t>Share of Building Retrofitting Costs by ISIC Code</t>
+  </si>
+  <si>
+    <t>SoBCaICbIC, BRESaC</t>
   </si>
 </sst>
 </file>
@@ -3967,7 +3976,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G390"/>
+  <dimension ref="A1:G391"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
@@ -4628,15 +4637,17 @@
         <v>32</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>94</v>
+        <v>1044</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>95</v>
+        <v>1045</v>
       </c>
       <c r="D37" s="7"/>
-      <c r="E37" s="7"/>
-      <c r="F37" s="14" t="s">
-        <v>96</v>
+      <c r="E37" s="7" t="s">
+        <v>1046</v>
+      </c>
+      <c r="F37" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G37" s="26"/>
     </row>
@@ -4645,15 +4656,15 @@
         <v>32</v>
       </c>
       <c r="B38" s="2" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D38" s="7"/>
       <c r="E38" s="7"/>
-      <c r="F38" s="4" t="s">
-        <v>29</v>
+      <c r="F38" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="G38" s="26"/>
     </row>
@@ -4662,123 +4673,121 @@
         <v>32</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="D39" s="7"/>
+      <c r="E39" s="7"/>
+      <c r="F39" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G39" s="26"/>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A40" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C40" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D39" s="7"/>
-      <c r="E39" s="1" t="s">
+      <c r="D40" s="7"/>
+      <c r="E40" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="F39" s="12" t="s">
+      <c r="F40" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="G39" s="26"/>
-    </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="17" t="s">
+      <c r="G40" s="26"/>
+    </row>
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="B40" s="17" t="s">
+      <c r="B41" s="17" t="s">
         <v>101</v>
       </c>
-      <c r="C40" s="17" t="s">
+      <c r="C41" s="17" t="s">
         <v>102</v>
       </c>
-      <c r="D40" s="27"/>
-      <c r="E40" s="27" t="s">
+      <c r="D41" s="27"/>
+      <c r="E41" s="27" t="s">
         <v>103</v>
       </c>
-      <c r="F40" s="19" t="s">
+      <c r="F41" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G40" s="28"/>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A41" s="2" t="s">
-        <v>104</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D41" s="7"/>
-      <c r="E41" s="7"/>
-      <c r="F41" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G41" s="26"/>
-    </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G41" s="28"/>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B42" s="2" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>108</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>109</v>
-      </c>
+        <v>106</v>
+      </c>
+      <c r="D42" s="7"/>
       <c r="E42" s="7"/>
-      <c r="F42" s="5" t="s">
-        <v>20</v>
+      <c r="F42" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G42" s="26"/>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B43" s="2" t="s">
-        <v>110</v>
+        <v>107</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="D43" s="7"/>
+        <v>108</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>109</v>
+      </c>
       <c r="E43" s="7"/>
-      <c r="F43" s="4" t="s">
-        <v>29</v>
+      <c r="F43" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G43" s="26"/>
     </row>
-    <row r="44" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B44" s="2" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>114</v>
-      </c>
+        <v>111</v>
+      </c>
+      <c r="D44" s="7"/>
       <c r="E44" s="7"/>
-      <c r="F44" s="5" t="s">
-        <v>20</v>
+      <c r="F44" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G44" s="26"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>116</v>
+        <v>113</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>117</v>
+        <v>114</v>
       </c>
       <c r="E45" s="7"/>
       <c r="F45" s="5" t="s">
@@ -4786,17 +4795,19 @@
       </c>
       <c r="G45" s="26"/>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B46" s="2" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C46" s="2" t="s">
-        <v>119</v>
-      </c>
-      <c r="D46" s="7"/>
+        <v>116</v>
+      </c>
+      <c r="D46" s="1" t="s">
+        <v>117</v>
+      </c>
       <c r="E46" s="7"/>
       <c r="F46" s="5" t="s">
         <v>20</v>
@@ -4808,15 +4819,15 @@
         <v>104</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D47" s="7"/>
       <c r="E47" s="7"/>
-      <c r="F47" s="3" t="s">
-        <v>10</v>
+      <c r="F47" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G47" s="26"/>
     </row>
@@ -4825,15 +4836,15 @@
         <v>104</v>
       </c>
       <c r="B48" s="2" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D48" s="7"/>
       <c r="E48" s="7"/>
-      <c r="F48" s="4" t="s">
-        <v>29</v>
+      <c r="F48" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G48" s="26"/>
     </row>
@@ -4842,99 +4853,97 @@
         <v>104</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="D49" s="7"/>
       <c r="E49" s="7"/>
-      <c r="F49" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G49" s="24" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F49" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G49" s="26"/>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>104</v>
       </c>
       <c r="B50" s="2" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="D50" s="7"/>
       <c r="E50" s="7"/>
-      <c r="F50" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G50" s="26"/>
-    </row>
-    <row r="51" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="17" t="s">
+      <c r="F50" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G50" s="24" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A51" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="B51" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="C51" s="17" t="s">
-        <v>130</v>
+      <c r="B51" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="D51" s="7"/>
       <c r="E51" s="7"/>
-      <c r="F51" s="20" t="s">
+      <c r="F51" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G51" s="26"/>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="B52" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>133</v>
+    <row r="52" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="17" t="s">
+        <v>104</v>
+      </c>
+      <c r="B52" s="17" t="s">
+        <v>129</v>
+      </c>
+      <c r="C52" s="17" t="s">
+        <v>130</v>
       </c>
       <c r="D52" s="7"/>
       <c r="E52" s="7"/>
-      <c r="F52" s="4" t="s">
+      <c r="F52" s="20" t="s">
         <v>29</v>
       </c>
       <c r="G52" s="26"/>
     </row>
-    <row r="53" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="17" t="s">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A53" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="B53" s="17" t="s">
-        <v>134</v>
-      </c>
-      <c r="C53" s="17" t="s">
-        <v>135</v>
-      </c>
-      <c r="D53" s="27"/>
-      <c r="E53" s="27"/>
-      <c r="F53" s="22" t="s">
-        <v>25</v>
-      </c>
-      <c r="G53" s="28" t="s">
-        <v>136</v>
-      </c>
+      <c r="B53" s="2" t="s">
+        <v>132</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="D53" s="7"/>
+      <c r="E53" s="7"/>
+      <c r="F53" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G53" s="26"/>
     </row>
     <row r="54" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
-        <v>137</v>
+        <v>131</v>
       </c>
       <c r="B54" s="17" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="D54" s="27"/>
       <c r="E54" s="27"/>
@@ -4942,37 +4951,37 @@
         <v>25</v>
       </c>
       <c r="G54" s="28" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="17" t="s">
+        <v>137</v>
+      </c>
+      <c r="B55" s="17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C55" s="17" t="s">
+        <v>139</v>
+      </c>
+      <c r="D55" s="27"/>
+      <c r="E55" s="27"/>
+      <c r="F55" s="22" t="s">
+        <v>25</v>
+      </c>
+      <c r="G55" s="28" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="B55" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C55" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D55" s="7"/>
-      <c r="E55" s="7"/>
-      <c r="F55" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G55" s="24" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="D56" s="7"/>
       <c r="E56" s="7"/>
@@ -4980,18 +4989,18 @@
         <v>144</v>
       </c>
       <c r="G56" s="24" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B57" s="2" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="D57" s="7"/>
       <c r="E57" s="7"/>
@@ -4999,7 +5008,7 @@
         <v>144</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="58" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -5007,10 +5016,10 @@
         <v>141</v>
       </c>
       <c r="B58" s="2" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="D58" s="7"/>
       <c r="E58" s="7"/>
@@ -5018,18 +5027,18 @@
         <v>144</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B59" s="2" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="D59" s="7"/>
       <c r="E59" s="7"/>
@@ -5037,18 +5046,18 @@
         <v>144</v>
       </c>
       <c r="G59" s="24" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B60" s="2" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="D60" s="7"/>
       <c r="E60" s="7"/>
@@ -5056,7 +5065,7 @@
         <v>144</v>
       </c>
       <c r="G60" s="24" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="61" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -5064,10 +5073,10 @@
         <v>141</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
@@ -5075,7 +5084,7 @@
         <v>144</v>
       </c>
       <c r="G61" s="24" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="62" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
@@ -5083,10 +5092,10 @@
         <v>141</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
@@ -5094,18 +5103,18 @@
         <v>144</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
@@ -5113,18 +5122,18 @@
         <v>144</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
@@ -5132,7 +5141,7 @@
         <v>144</v>
       </c>
       <c r="G64" s="24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -5140,10 +5149,10 @@
         <v>141</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
@@ -5151,18 +5160,18 @@
         <v>144</v>
       </c>
       <c r="G65" s="24" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
@@ -5170,147 +5179,149 @@
         <v>144</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
-      <c r="F67" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G67" s="26"/>
-    </row>
-    <row r="68" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F67" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G67" s="24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
-      <c r="F68" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G68" s="24" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F68" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G68" s="26"/>
+    </row>
+    <row r="69" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D69" s="1" t="s">
-        <v>186</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="D69" s="7"/>
       <c r="E69" s="7"/>
       <c r="F69" s="6" t="s">
         <v>144</v>
       </c>
       <c r="G69" s="24" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D70" s="7"/>
-      <c r="E70" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F70" s="16" t="s">
-        <v>14</v>
+        <v>185</v>
+      </c>
+      <c r="D70" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E70" s="7"/>
+      <c r="F70" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B71" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D71" s="7"/>
+      <c r="E71" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F71" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G71" s="24" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A72" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B72" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C71" s="2" t="s">
+      <c r="C72" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D71" s="7"/>
-      <c r="E71" s="7"/>
-      <c r="F71" s="3" t="s">
+      <c r="D72" s="7"/>
+      <c r="E72" s="7"/>
+      <c r="F72" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G71" s="26"/>
-    </row>
-    <row r="72" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A72" s="17" t="s">
+      <c r="G72" s="26"/>
+    </row>
+    <row r="73" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="B72" s="17" t="s">
+      <c r="B73" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C72" s="17" t="s">
+      <c r="C73" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="D72" s="27"/>
-      <c r="E72" s="27"/>
-      <c r="F72" s="19" t="s">
+      <c r="D73" s="27"/>
+      <c r="E73" s="27"/>
+      <c r="F73" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G72" s="28"/>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A73" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B73" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C73" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D73" s="7"/>
-      <c r="E73" s="7"/>
-      <c r="F73" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G73" s="26"/>
+      <c r="G73" s="28"/>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>196</v>
       </c>
       <c r="B74" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D74" s="7"/>
       <c r="E74" s="7"/>
@@ -5324,15 +5335,15 @@
         <v>196</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
-      <c r="F75" s="5" t="s">
-        <v>20</v>
+      <c r="F75" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G75" s="26"/>
     </row>
@@ -5341,15 +5352,15 @@
         <v>196</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
-      <c r="F76" s="4" t="s">
-        <v>29</v>
+      <c r="F76" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G76" s="26"/>
     </row>
@@ -5358,10 +5369,10 @@
         <v>196</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
@@ -5370,51 +5381,51 @@
       </c>
       <c r="G77" s="26"/>
     </row>
-    <row r="78" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A78" s="17" t="s">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A78" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B78" s="17" t="s">
+      <c r="B78" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D78" s="7"/>
+      <c r="E78" s="7"/>
+      <c r="F78" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G78" s="26"/>
+    </row>
+    <row r="79" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B79" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C78" s="17" t="s">
+      <c r="C79" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="D78" s="27"/>
-      <c r="E78" s="27"/>
-      <c r="F78" s="21" t="s">
+      <c r="D79" s="27"/>
+      <c r="E79" s="27"/>
+      <c r="F79" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G78" s="28" t="s">
+      <c r="G79" s="28" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A79" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B79" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C79" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G79" s="26"/>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B80" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D80" s="7"/>
       <c r="E80" s="7"/>
@@ -5423,94 +5434,92 @@
       </c>
       <c r="G80" s="26"/>
     </row>
-    <row r="81" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D81" s="1" t="s">
-        <v>217</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="D81" s="7"/>
       <c r="E81" s="7"/>
-      <c r="F81" s="5" t="s">
-        <v>20</v>
+      <c r="F81" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G81" s="26"/>
     </row>
-    <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D82" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E82" s="7"/>
-      <c r="F82" s="4" t="s">
-        <v>29</v>
+      <c r="F82" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G82" s="26"/>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D83" s="7"/>
+        <v>219</v>
+      </c>
+      <c r="D83" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="E83" s="7"/>
-      <c r="F83" s="3" t="s">
-        <v>10</v>
+      <c r="F83" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G83" s="26"/>
     </row>
-    <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D84" s="7"/>
       <c r="E84" s="7"/>
-      <c r="F84" s="5" t="s">
-        <v>20</v>
+      <c r="F84" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G84" s="26"/>
     </row>
-    <row r="85" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>227</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="D85" s="7"/>
       <c r="E85" s="7"/>
-      <c r="F85" s="4" t="s">
-        <v>29</v>
+      <c r="F85" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G85" s="26"/>
     </row>
@@ -5519,84 +5528,84 @@
         <v>210</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D86" s="7"/>
+        <v>226</v>
+      </c>
+      <c r="D86" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="E86" s="7"/>
-      <c r="F86" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G86" s="24" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F86" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G86" s="26"/>
+    </row>
+    <row r="87" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D87" s="1" t="s">
-        <v>233</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="D87" s="7"/>
       <c r="E87" s="7"/>
-      <c r="F87" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G87" s="26"/>
+      <c r="F87" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G87" s="24" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D88" s="7"/>
+        <v>232</v>
+      </c>
+      <c r="D88" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="E88" s="7"/>
-      <c r="F88" s="3" t="s">
-        <v>10</v>
+      <c r="F88" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="G88" s="26"/>
     </row>
-    <row r="89" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D89" s="7"/>
       <c r="E89" s="7"/>
-      <c r="F89" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G89" s="24" t="s">
-        <v>238</v>
-      </c>
+      <c r="F89" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G89" s="26"/>
     </row>
     <row r="90" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
@@ -5604,76 +5613,74 @@
         <v>14</v>
       </c>
       <c r="G90" s="24" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
-      <c r="F91" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G91" s="26"/>
+      <c r="F91" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G91" s="24" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
-      <c r="F92" s="5" t="s">
-        <v>20</v>
+      <c r="F92" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G92" s="26"/>
     </row>
-    <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
-      <c r="F93" s="3" t="s">
-        <v>10</v>
+      <c r="F93" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G93" s="26"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E94" s="1" t="s">
-        <v>251</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="D94" s="7"/>
+      <c r="E94" s="7"/>
       <c r="F94" s="3" t="s">
         <v>10</v>
       </c>
@@ -5684,27 +5691,31 @@
         <v>210</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D95" s="7"/>
-      <c r="E95" s="7"/>
+        <v>249</v>
+      </c>
+      <c r="D95" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E95" s="1" t="s">
+        <v>251</v>
+      </c>
       <c r="F95" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G95" s="26"/>
     </row>
-    <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D96" s="7"/>
       <c r="E96" s="7"/>
@@ -5713,15 +5724,15 @@
       </c>
       <c r="G96" s="26"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
@@ -5735,140 +5746,140 @@
         <v>210</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
-      <c r="F98" s="5" t="s">
-        <v>20</v>
+      <c r="F98" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G98" s="26"/>
     </row>
-    <row r="99" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D99" s="1" t="s">
-        <v>262</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="D99" s="7"/>
       <c r="E99" s="7"/>
       <c r="F99" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G99" s="26"/>
     </row>
-    <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D100" s="7"/>
+        <v>261</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>262</v>
+      </c>
       <c r="E100" s="7"/>
       <c r="F100" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G100" s="26"/>
     </row>
-    <row r="101" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D101" s="7"/>
       <c r="E101" s="7"/>
-      <c r="F101" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="G101" s="24" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F101" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G101" s="26"/>
+    </row>
+    <row r="102" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
-      <c r="F102" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G102" s="26"/>
-    </row>
-    <row r="103" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F102" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G102" s="24" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D103" s="1" t="s">
-        <v>273</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="D103" s="7"/>
       <c r="E103" s="7"/>
       <c r="F103" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G103" s="26"/>
     </row>
-    <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D104" s="7"/>
+        <v>272</v>
+      </c>
+      <c r="D104" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="E104" s="7"/>
       <c r="F104" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G104" s="26"/>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D105" s="7"/>
       <c r="E105" s="7"/>
-      <c r="F105" s="4" t="s">
-        <v>29</v>
+      <c r="F105" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G105" s="26"/>
     </row>
@@ -5877,10 +5888,10 @@
         <v>210</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D106" s="7"/>
       <c r="E106" s="7"/>
@@ -5889,22 +5900,20 @@
       </c>
       <c r="G106" s="26"/>
     </row>
-    <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D107" s="1" t="s">
-        <v>282</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="D107" s="7"/>
       <c r="E107" s="7"/>
-      <c r="F107" s="3" t="s">
-        <v>10</v>
+      <c r="F107" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G107" s="26"/>
     </row>
@@ -5913,17 +5922,17 @@
         <v>210</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E108" s="7"/>
-      <c r="F108" s="4" t="s">
-        <v>29</v>
+      <c r="F108" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G108" s="26"/>
     </row>
@@ -5932,36 +5941,36 @@
         <v>210</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E109" s="7"/>
-      <c r="F109" s="3" t="s">
-        <v>10</v>
+      <c r="F109" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G109" s="26"/>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E110" s="7"/>
-      <c r="F110" s="4" t="s">
-        <v>29</v>
+      <c r="F110" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G110" s="26"/>
     </row>
@@ -5970,15 +5979,17 @@
         <v>210</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D111" s="7"/>
+        <v>290</v>
+      </c>
+      <c r="D111" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="E111" s="7"/>
-      <c r="F111" s="5" t="s">
-        <v>20</v>
+      <c r="F111" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G111" s="26"/>
     </row>
@@ -5987,15 +5998,15 @@
         <v>210</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D112" s="7"/>
       <c r="E112" s="7"/>
-      <c r="F112" s="3" t="s">
-        <v>10</v>
+      <c r="F112" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G112" s="26"/>
     </row>
@@ -6004,118 +6015,118 @@
         <v>210</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
-      <c r="F113" s="5" t="s">
-        <v>20</v>
+      <c r="F113" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G113" s="26"/>
     </row>
-    <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D114" s="1" t="s">
-        <v>300</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="D114" s="7"/>
       <c r="E114" s="7"/>
-      <c r="F114" s="3" t="s">
-        <v>10</v>
+      <c r="F114" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G114" s="26"/>
     </row>
-    <row r="115" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D115" s="7"/>
+        <v>299</v>
+      </c>
+      <c r="D115" s="1" t="s">
+        <v>300</v>
+      </c>
       <c r="E115" s="7"/>
-      <c r="F115" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="G115" s="24" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F115" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G115" s="26"/>
+    </row>
+    <row r="116" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D116" s="7"/>
       <c r="E116" s="7"/>
-      <c r="F116" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G116" s="26"/>
+      <c r="F116" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G116" s="24" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
       <c r="F117" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G117" s="26" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G117" s="26"/>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
-      <c r="F118" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G118" s="26"/>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F118" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G118" s="26" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
@@ -6124,15 +6135,15 @@
       </c>
       <c r="G119" s="26"/>
     </row>
-    <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D120" s="7"/>
       <c r="E120" s="7"/>
@@ -6141,20 +6152,20 @@
       </c>
       <c r="G120" s="26"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
-      <c r="F121" s="3" t="s">
-        <v>10</v>
+      <c r="F121" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G121" s="26"/>
     </row>
@@ -6163,10 +6174,10 @@
         <v>210</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
@@ -6180,15 +6191,15 @@
         <v>210</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
-      <c r="F123" s="4" t="s">
-        <v>29</v>
+      <c r="F123" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G123" s="26"/>
     </row>
@@ -6197,10 +6208,10 @@
         <v>210</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
@@ -6214,15 +6225,15 @@
         <v>210</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
-      <c r="F125" s="3" t="s">
-        <v>10</v>
+      <c r="F125" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G125" s="26"/>
     </row>
@@ -6231,15 +6242,15 @@
         <v>210</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
-      <c r="F126" s="4" t="s">
-        <v>29</v>
+      <c r="F126" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G126" s="26"/>
     </row>
@@ -6248,46 +6259,44 @@
         <v>210</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
-      <c r="F127" s="5" t="s">
-        <v>20</v>
+      <c r="F127" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G127" s="26"/>
     </row>
-    <row r="128" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
-      <c r="F128" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="G128" s="24" t="s">
-        <v>331</v>
-      </c>
+      <c r="F128" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G128" s="26"/>
     </row>
     <row r="129" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
@@ -6295,73 +6304,75 @@
         <v>267</v>
       </c>
       <c r="G129" s="24" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D130" s="1" t="s">
-        <v>337</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="D130" s="7"/>
       <c r="E130" s="7"/>
-      <c r="F130" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G130" s="26"/>
-    </row>
-    <row r="131" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F130" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G130" s="24" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E131" s="7"/>
-      <c r="F131" s="14" t="s">
-        <v>96</v>
+      <c r="F131" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G131" s="26"/>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D132" s="7"/>
+        <v>339</v>
+      </c>
+      <c r="D132" s="1" t="s">
+        <v>340</v>
+      </c>
       <c r="E132" s="7"/>
-      <c r="F132" s="4" t="s">
-        <v>29</v>
+      <c r="F132" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="G132" s="26"/>
     </row>
-    <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D133" s="7"/>
       <c r="E133" s="7"/>
@@ -6375,57 +6386,53 @@
         <v>210</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>251</v>
+        <v>343</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D134" s="1" t="s">
-        <v>346</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="D134" s="7"/>
       <c r="E134" s="7"/>
-      <c r="F134" s="5" t="s">
-        <v>347</v>
+      <c r="F134" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G134" s="26"/>
     </row>
-    <row r="135" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>348</v>
+        <v>251</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E135" s="7"/>
       <c r="F135" s="5" t="s">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="G135" s="26"/>
     </row>
-    <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E136" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="F136" s="3" t="s">
-        <v>10</v>
+        <v>350</v>
+      </c>
+      <c r="E136" s="7"/>
+      <c r="F136" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G136" s="26"/>
     </row>
@@ -6434,51 +6441,55 @@
         <v>210</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D137" s="7"/>
-      <c r="E137" s="7"/>
-      <c r="F137" s="14" t="s">
-        <v>96</v>
+        <v>352</v>
+      </c>
+      <c r="D137" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E137" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F137" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G137" s="26"/>
     </row>
-    <row r="138" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D138" s="1" t="s">
-        <v>359</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="D138" s="7"/>
       <c r="E138" s="7"/>
-      <c r="F138" s="4" t="s">
-        <v>29</v>
+      <c r="F138" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="G138" s="26"/>
     </row>
-    <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D139" s="7"/>
+        <v>358</v>
+      </c>
+      <c r="D139" s="1" t="s">
+        <v>359</v>
+      </c>
       <c r="E139" s="7"/>
-      <c r="F139" s="14" t="s">
-        <v>96</v>
+      <c r="F139" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G139" s="26"/>
     </row>
@@ -6487,15 +6498,15 @@
         <v>210</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D140" s="7"/>
       <c r="E140" s="7"/>
-      <c r="F140" s="4" t="s">
-        <v>29</v>
+      <c r="F140" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="G140" s="26"/>
     </row>
@@ -6504,10 +6515,10 @@
         <v>210</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
@@ -6521,10 +6532,10 @@
         <v>210</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
@@ -6533,20 +6544,20 @@
       </c>
       <c r="G142" s="26"/>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D143" s="7"/>
       <c r="E143" s="7"/>
-      <c r="F143" s="3" t="s">
-        <v>10</v>
+      <c r="F143" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G143" s="26"/>
     </row>
@@ -6555,34 +6566,32 @@
         <v>210</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D144" s="7"/>
-      <c r="E144" s="1" t="s">
-        <v>319</v>
-      </c>
+      <c r="E144" s="7"/>
       <c r="F144" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G144" s="26"/>
     </row>
-    <row r="145" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E145" s="7"/>
+        <v>371</v>
+      </c>
+      <c r="D145" s="7"/>
+      <c r="E145" s="1" t="s">
+        <v>319</v>
+      </c>
       <c r="F145" s="3" t="s">
         <v>10</v>
       </c>
@@ -6593,63 +6602,65 @@
         <v>210</v>
       </c>
       <c r="B146" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C146" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D146" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E146" s="7"/>
+      <c r="F146" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G146" s="26"/>
+    </row>
+    <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A147" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B147" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C146" s="2" t="s">
+      <c r="C147" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="D146" s="7"/>
-      <c r="E146" s="7"/>
-      <c r="F146" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G146" s="26"/>
-    </row>
-    <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A147" t="s">
-        <v>210</v>
-      </c>
-      <c r="B147" t="s">
-        <v>377</v>
-      </c>
-      <c r="C147" t="s">
-        <v>378</v>
       </c>
       <c r="D147" s="7"/>
       <c r="E147" s="7"/>
-      <c r="F147" t="s">
-        <v>14</v>
-      </c>
-      <c r="G147" s="26" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A148" s="2" t="s">
+      <c r="F147" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G147" s="26"/>
+    </row>
+    <row r="148" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
         <v>210</v>
       </c>
-      <c r="B148" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C148" s="2" t="s">
-        <v>381</v>
+      <c r="B148" t="s">
+        <v>377</v>
+      </c>
+      <c r="C148" t="s">
+        <v>378</v>
       </c>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
-      <c r="F148" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G148" s="26"/>
-    </row>
-    <row r="149" spans="1:7" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F148" t="s">
+        <v>14</v>
+      </c>
+      <c r="G148" s="26" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B149" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C149" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
@@ -6658,58 +6669,56 @@
       </c>
       <c r="G149" s="26"/>
     </row>
-    <row r="150" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A150" s="17" t="s">
+    <row r="150" spans="1:7" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A150" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B150" s="17" t="s">
+      <c r="B150" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C150" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D150" s="7"/>
+      <c r="E150" s="7"/>
+      <c r="F150" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G150" s="26"/>
+    </row>
+    <row r="151" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A151" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B151" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="C150" s="17" t="s">
+      <c r="C151" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="D150" s="27" t="s">
+      <c r="D151" s="27" t="s">
         <v>386</v>
       </c>
-      <c r="E150" s="27"/>
-      <c r="F150" s="21" t="s">
+      <c r="E151" s="27"/>
+      <c r="F151" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G150" s="28" t="s">
+      <c r="G151" s="28" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="151" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A151" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B151" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C151" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D151" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E151" s="7"/>
-      <c r="F151" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G151" s="26"/>
     </row>
     <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>388</v>
       </c>
       <c r="B152" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C152" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E152" s="7"/>
       <c r="F152" s="4" t="s">
@@ -6722,61 +6731,63 @@
         <v>388</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D153" s="7"/>
+        <v>393</v>
+      </c>
+      <c r="D153" s="1" t="s">
+        <v>394</v>
+      </c>
       <c r="E153" s="7"/>
       <c r="F153" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G153" s="26"/>
     </row>
-    <row r="154" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>388</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D154" s="7"/>
       <c r="E154" s="7"/>
-      <c r="F154" s="5" t="s">
-        <v>20</v>
+      <c r="F154" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G154" s="26"/>
     </row>
-    <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>388</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
-      <c r="F155" s="4" t="s">
-        <v>29</v>
+      <c r="F155" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G155" s="26"/>
     </row>
-    <row r="156" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>388</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
@@ -6785,54 +6796,54 @@
       </c>
       <c r="G156" s="26"/>
     </row>
-    <row r="157" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A157" s="17" t="s">
+    <row r="157" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B157" s="17" t="s">
+      <c r="B157" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C157" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D157" s="7"/>
+      <c r="E157" s="7"/>
+      <c r="F157" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G157" s="26"/>
+    </row>
+    <row r="158" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A158" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="B158" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="C157" s="17" t="s">
+      <c r="C158" s="17" t="s">
         <v>404</v>
       </c>
-      <c r="D157" s="27"/>
-      <c r="E157" s="27"/>
-      <c r="F157" s="20" t="s">
+      <c r="D158" s="27"/>
+      <c r="E158" s="27"/>
+      <c r="F158" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G157" s="28"/>
-    </row>
-    <row r="158" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A158" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="B158" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C158" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G158" s="26"/>
+      <c r="G158" s="28"/>
     </row>
     <row r="159" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B159" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D159" s="7"/>
       <c r="E159" s="7"/>
-      <c r="F159" s="5" t="s">
-        <v>20</v>
+      <c r="F159" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G159" s="26"/>
     </row>
@@ -6841,10 +6852,10 @@
         <v>405</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
@@ -6858,10 +6869,10 @@
         <v>405</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
@@ -6870,22 +6881,20 @@
       </c>
       <c r="G161" s="26"/>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D162" s="1" t="s">
-        <v>416</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="D162" s="7"/>
       <c r="E162" s="7"/>
-      <c r="F162" s="3" t="s">
-        <v>10</v>
+      <c r="F162" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G162" s="26"/>
     </row>
@@ -6894,80 +6903,82 @@
         <v>405</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D163" s="7"/>
+        <v>415</v>
+      </c>
+      <c r="D163" s="1" t="s">
+        <v>416</v>
+      </c>
       <c r="E163" s="7"/>
       <c r="F163" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G163" s="26"/>
     </row>
-    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D164" s="7"/>
       <c r="E164" s="7"/>
-      <c r="F164" s="4" t="s">
-        <v>29</v>
+      <c r="F164" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G164" s="26"/>
     </row>
-    <row r="165" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D165" s="1" t="s">
-        <v>423</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="D165" s="7"/>
       <c r="E165" s="7"/>
-      <c r="F165" s="3" t="s">
-        <v>10</v>
+      <c r="F165" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G165" s="26"/>
     </row>
-    <row r="166" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D166" s="7"/>
+        <v>422</v>
+      </c>
+      <c r="D166" s="1" t="s">
+        <v>423</v>
+      </c>
       <c r="E166" s="7"/>
-      <c r="F166" s="5" t="s">
-        <v>20</v>
+      <c r="F166" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G166" s="26"/>
     </row>
-    <row r="167" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D167" s="7"/>
       <c r="E167" s="7"/>
@@ -6976,15 +6987,15 @@
       </c>
       <c r="G167" s="26"/>
     </row>
-    <row r="168" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
@@ -6993,20 +7004,18 @@
       </c>
       <c r="G168" s="26"/>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D169" s="7"/>
-      <c r="E169" s="1" t="s">
-        <v>432</v>
-      </c>
+      <c r="E169" s="7"/>
       <c r="F169" s="5" t="s">
         <v>20</v>
       </c>
@@ -7017,13 +7026,15 @@
         <v>405</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D170" s="7"/>
-      <c r="E170" s="7"/>
+      <c r="E170" s="1" t="s">
+        <v>432</v>
+      </c>
       <c r="F170" s="5" t="s">
         <v>20</v>
       </c>
@@ -7034,99 +7045,97 @@
         <v>405</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D171" s="7"/>
       <c r="E171" s="7"/>
-      <c r="F171" s="3" t="s">
-        <v>10</v>
+      <c r="F171" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G171" s="26"/>
     </row>
-    <row r="172" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
-      <c r="F172" s="4" t="s">
-        <v>29</v>
+      <c r="F172" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G172" s="26"/>
     </row>
-    <row r="173" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
-      <c r="F173" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G173" s="24" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F173" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G173" s="26"/>
+    </row>
+    <row r="174" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
-      <c r="F174" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G174" s="26"/>
+      <c r="F174" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G174" s="24" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="175" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
-      <c r="F175" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G175" s="24" t="s">
-        <v>446</v>
-      </c>
+      <c r="F175" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G175" s="26"/>
     </row>
     <row r="176" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
@@ -7134,18 +7143,18 @@
         <v>14</v>
       </c>
       <c r="G176" s="24" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D177" s="7"/>
       <c r="E177" s="7"/>
@@ -7153,171 +7162,173 @@
         <v>14</v>
       </c>
       <c r="G177" s="24" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D178" s="1" t="s">
-        <v>455</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="D178" s="7"/>
       <c r="E178" s="7"/>
-      <c r="F178" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G178" s="26"/>
-    </row>
-    <row r="179" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F178" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G178" s="24" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E179" s="7"/>
-      <c r="F179" s="4" t="s">
-        <v>29</v>
+      <c r="F179" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G179" s="26"/>
     </row>
-    <row r="180" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D180" s="7"/>
+        <v>457</v>
+      </c>
+      <c r="D180" s="1" t="s">
+        <v>458</v>
+      </c>
       <c r="E180" s="7"/>
-      <c r="F180" s="3" t="s">
-        <v>10</v>
+      <c r="F180" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G180" s="26"/>
     </row>
-    <row r="181" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D181" s="7"/>
       <c r="E181" s="7"/>
-      <c r="F181" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G181" s="24" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A182" s="17" t="s">
+      <c r="F181" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G181" s="26"/>
+    </row>
+    <row r="182" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A182" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B182" s="17" t="s">
-        <v>464</v>
-      </c>
-      <c r="C182" s="17" t="s">
-        <v>465</v>
+      <c r="B182" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C182" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
-      <c r="F182" s="22" t="s">
+      <c r="F182" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G182" s="24" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="B183" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="C183" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="D183" s="7"/>
+      <c r="E183" s="7"/>
+      <c r="F183" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="G182" s="28" t="s">
+      <c r="G183" s="28" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="183" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A183" s="2" t="s">
+    <row r="184" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A184" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B183" s="2" t="s">
+      <c r="B184" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="C183" s="2" t="s">
+      <c r="C184" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="D183" s="1" t="s">
+      <c r="D184" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="E183" s="7"/>
-      <c r="F183" s="3" t="s">
+      <c r="E184" s="7"/>
+      <c r="F184" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G183" s="26"/>
-    </row>
-    <row r="184" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="17" t="s">
+      <c r="G184" s="26"/>
+    </row>
+    <row r="185" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A185" s="17" t="s">
         <v>471</v>
       </c>
-      <c r="B184" s="17" t="s">
+      <c r="B185" s="17" t="s">
         <v>472</v>
       </c>
-      <c r="C184" s="17" t="s">
+      <c r="C185" s="17" t="s">
         <v>473</v>
       </c>
-      <c r="D184" s="27" t="s">
+      <c r="D185" s="27" t="s">
         <v>474</v>
       </c>
-      <c r="E184" s="7"/>
-      <c r="F184" s="19" t="s">
+      <c r="E185" s="7"/>
+      <c r="F185" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G184" s="26"/>
-    </row>
-    <row r="185" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A185" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="B185" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="C185" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D185" s="7"/>
-      <c r="E185" s="7"/>
-      <c r="F185" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="G185" s="26"/>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B186" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C186" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D186" s="7"/>
       <c r="E186" s="7"/>
-      <c r="F186" s="3" t="s">
-        <v>10</v>
+      <c r="F186" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G186" s="26"/>
     </row>
@@ -7326,15 +7337,15 @@
         <v>475</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D187" s="7"/>
       <c r="E187" s="7"/>
-      <c r="F187" s="4" t="s">
-        <v>29</v>
+      <c r="F187" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G187" s="26"/>
     </row>
@@ -7343,10 +7354,10 @@
         <v>475</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
@@ -7355,138 +7366,138 @@
       </c>
       <c r="G188" s="26"/>
     </row>
-    <row r="189" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D189" s="7"/>
       <c r="E189" s="7"/>
-      <c r="F189" s="5" t="s">
-        <v>20</v>
+      <c r="F189" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G189" s="26"/>
     </row>
-    <row r="190" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D190" s="1" t="s">
-        <v>488</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="D190" s="7"/>
       <c r="E190" s="7"/>
-      <c r="F190" s="4" t="s">
-        <v>29</v>
+      <c r="F190" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G190" s="26"/>
     </row>
-    <row r="191" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D191" s="7"/>
+        <v>487</v>
+      </c>
+      <c r="D191" s="1" t="s">
+        <v>488</v>
+      </c>
       <c r="E191" s="7"/>
-      <c r="F191" s="5" t="s">
-        <v>20</v>
+      <c r="F191" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G191" s="26"/>
     </row>
-    <row r="192" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D192" s="7"/>
       <c r="E192" s="7"/>
-      <c r="F192" s="4" t="s">
-        <v>29</v>
+      <c r="F192" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G192" s="26"/>
     </row>
-    <row r="193" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D193" s="7"/>
       <c r="E193" s="7"/>
-      <c r="F193" s="14" t="s">
-        <v>96</v>
+      <c r="F193" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G193" s="26"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D194" s="7"/>
       <c r="E194" s="7"/>
-      <c r="F194" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G194" s="24" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="195" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F194" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G194" s="26"/>
+    </row>
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D195" s="7"/>
       <c r="E195" s="7"/>
-      <c r="F195" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G195" s="26"/>
+      <c r="F195" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G195" s="24" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="196" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D196" s="7"/>
       <c r="E196" s="7"/>
@@ -7500,10 +7511,10 @@
         <v>475</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D197" s="7"/>
       <c r="E197" s="7"/>
@@ -7517,215 +7528,213 @@
         <v>475</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D198" s="7"/>
       <c r="E198" s="7"/>
-      <c r="F198" s="4" t="s">
-        <v>29</v>
+      <c r="F198" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G198" s="26"/>
     </row>
-    <row r="199" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D199" s="7"/>
       <c r="E199" s="7"/>
-      <c r="F199" s="12" t="s">
-        <v>37</v>
+      <c r="F199" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G199" s="26"/>
     </row>
-    <row r="200" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A200" s="17" t="s">
+    <row r="200" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A200" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B200" s="17" t="s">
-        <v>508</v>
-      </c>
-      <c r="C200" s="17" t="s">
-        <v>509</v>
+      <c r="B200" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C200" s="2" t="s">
+        <v>507</v>
       </c>
       <c r="D200" s="7"/>
       <c r="E200" s="7"/>
-      <c r="F200" s="20" t="s">
-        <v>29</v>
+      <c r="F200" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="G200" s="26"/>
     </row>
-    <row r="201" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A201" t="s">
-        <v>510</v>
-      </c>
-      <c r="B201" t="s">
-        <v>1017</v>
-      </c>
-      <c r="C201" t="s">
-        <v>1018</v>
+    <row r="201" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A201" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="B201" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="C201" s="17" t="s">
+        <v>509</v>
       </c>
       <c r="D201" s="7"/>
       <c r="E201" s="7"/>
-      <c r="F201" t="s">
-        <v>20</v>
-      </c>
-      <c r="G201" s="26" t="s">
-        <v>1019</v>
-      </c>
+      <c r="F201" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G201" s="26"/>
     </row>
     <row r="202" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>510</v>
       </c>
       <c r="B202" t="s">
-        <v>511</v>
+        <v>1017</v>
       </c>
       <c r="C202" t="s">
-        <v>512</v>
+        <v>1018</v>
       </c>
       <c r="D202" s="7"/>
       <c r="E202" s="7"/>
       <c r="F202" t="s">
+        <v>20</v>
+      </c>
+      <c r="G202" s="26" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="203" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>510</v>
+      </c>
+      <c r="B203" t="s">
+        <v>511</v>
+      </c>
+      <c r="C203" t="s">
+        <v>512</v>
+      </c>
+      <c r="D203" s="7"/>
+      <c r="E203" s="7"/>
+      <c r="F203" t="s">
         <v>10</v>
       </c>
-      <c r="G202" s="26"/>
-    </row>
-    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A203" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B203" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C203" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="D203" s="1"/>
-      <c r="E203" s="7"/>
-      <c r="F203" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G203" s="26"/>
     </row>
-    <row r="204" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B204" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C204" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="D204" s="7"/>
+        <v>514</v>
+      </c>
+      <c r="D204" s="1"/>
       <c r="E204" s="7"/>
-      <c r="F204" s="16" t="s">
+      <c r="F204" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G204" s="26" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G204" s="26"/>
+    </row>
+    <row r="205" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D205" s="7" t="s">
-        <v>520</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="D205" s="7"/>
       <c r="E205" s="7"/>
       <c r="F205" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G205" s="26" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="206" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A206" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B206" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C206" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D206" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="E206" s="7"/>
+      <c r="F206" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G205" s="24"/>
-    </row>
-    <row r="206" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A206" t="s">
-        <v>510</v>
-      </c>
-      <c r="B206" t="s">
-        <v>1000</v>
-      </c>
-      <c r="C206" t="s">
-        <v>1001</v>
-      </c>
-      <c r="D206" s="7"/>
-      <c r="E206" s="7"/>
-      <c r="F206" t="s">
-        <v>20</v>
-      </c>
-      <c r="G206" s="26" t="s">
-        <v>1002</v>
-      </c>
+      <c r="G206" s="24"/>
     </row>
     <row r="207" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>510</v>
       </c>
       <c r="B207" t="s">
-        <v>521</v>
+        <v>1000</v>
       </c>
       <c r="C207" t="s">
-        <v>522</v>
+        <v>1001</v>
       </c>
       <c r="D207" s="7"/>
       <c r="E207" s="7"/>
       <c r="F207" t="s">
-        <v>10</v>
-      </c>
-      <c r="G207" s="26"/>
-    </row>
-    <row r="208" spans="1:7" ht="45" x14ac:dyDescent="0.25">
-      <c r="A208" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G207" s="26" t="s">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="208" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A208" t="s">
         <v>510</v>
       </c>
-      <c r="B208" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C208" s="2" t="s">
-        <v>524</v>
+      <c r="B208" t="s">
+        <v>521</v>
+      </c>
+      <c r="C208" t="s">
+        <v>522</v>
       </c>
       <c r="D208" s="7"/>
       <c r="E208" s="7"/>
-      <c r="F208" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G208" s="24" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F208" t="s">
+        <v>10</v>
+      </c>
+      <c r="G208" s="26"/>
+    </row>
+    <row r="209" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B209" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C209" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D209" s="7"/>
       <c r="E209" s="7"/>
-      <c r="F209" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G209" s="26" t="s">
-        <v>528</v>
+      <c r="F209" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G209" s="24" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="210" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7733,31 +7742,33 @@
         <v>510</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D210" s="7"/>
       <c r="E210" s="7"/>
       <c r="F210" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G210" s="26"/>
+      <c r="G210" s="26" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="211" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="D211" s="1"/>
+        <v>530</v>
+      </c>
+      <c r="D211" s="7"/>
       <c r="E211" s="7"/>
-      <c r="F211" s="12" t="s">
+      <c r="F211" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G211" s="26"/>
@@ -7767,17 +7778,15 @@
         <v>510</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="D212" s="7" t="s">
-        <v>535</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="D212" s="1"/>
       <c r="E212" s="7"/>
-      <c r="F212" s="3" t="s">
-        <v>37</v>
+      <c r="F212" s="12" t="s">
+        <v>10</v>
       </c>
       <c r="G212" s="26"/>
     </row>
@@ -7786,15 +7795,17 @@
         <v>510</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="D213" s="1"/>
+        <v>534</v>
+      </c>
+      <c r="D213" s="7" t="s">
+        <v>535</v>
+      </c>
       <c r="E213" s="7"/>
-      <c r="F213" s="14" t="s">
-        <v>10</v>
+      <c r="F213" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="G213" s="26"/>
     </row>
@@ -7803,17 +7814,15 @@
         <v>510</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D214" s="1" t="s">
-        <v>540</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="D214" s="1"/>
       <c r="E214" s="7"/>
-      <c r="F214" s="4" t="s">
-        <v>541</v>
+      <c r="F214" s="14" t="s">
+        <v>10</v>
       </c>
       <c r="G214" s="26"/>
     </row>
@@ -7822,34 +7831,36 @@
         <v>510</v>
       </c>
       <c r="B215" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C215" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D215" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E215" s="7"/>
+      <c r="F215" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="G215" s="26"/>
+    </row>
+    <row r="216" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B216" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C215" s="2" t="s">
+      <c r="C216" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D215" s="7" t="s">
+      <c r="D216" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="E215" s="7"/>
-      <c r="F215" s="5" t="s">
+      <c r="E216" s="7"/>
+      <c r="F216" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="G215" s="26"/>
-    </row>
-    <row r="216" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A216" t="s">
-        <v>510</v>
-      </c>
-      <c r="B216" t="s">
-        <v>545</v>
-      </c>
-      <c r="C216" t="s">
-        <v>546</v>
-      </c>
-      <c r="D216" s="7"/>
-      <c r="E216" s="7"/>
-      <c r="F216" t="s">
-        <v>20</v>
       </c>
       <c r="G216" s="26"/>
     </row>
@@ -7858,48 +7869,46 @@
         <v>510</v>
       </c>
       <c r="B217" t="s">
-        <v>1020</v>
+        <v>545</v>
       </c>
       <c r="C217" t="s">
-        <v>1021</v>
+        <v>546</v>
       </c>
       <c r="D217" s="7"/>
       <c r="E217" s="7"/>
       <c r="F217" t="s">
         <v>20</v>
       </c>
-      <c r="G217" s="26" t="s">
-        <v>1022</v>
-      </c>
+      <c r="G217" s="26"/>
     </row>
     <row r="218" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>510</v>
       </c>
       <c r="B218" t="s">
-        <v>547</v>
+        <v>1020</v>
       </c>
       <c r="C218" t="s">
-        <v>548</v>
+        <v>1021</v>
       </c>
       <c r="D218" s="7"/>
       <c r="E218" s="7"/>
       <c r="F218" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G218" s="26" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="219" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>510</v>
       </c>
       <c r="B219" t="s">
-        <v>1023</v>
+        <v>547</v>
       </c>
       <c r="C219" t="s">
-        <v>1024</v>
+        <v>548</v>
       </c>
       <c r="D219" s="7"/>
       <c r="E219" s="7"/>
@@ -7907,7 +7916,7 @@
         <v>29</v>
       </c>
       <c r="G219" s="26" t="s">
-        <v>1025</v>
+        <v>549</v>
       </c>
     </row>
     <row r="220" spans="1:7" x14ac:dyDescent="0.25">
@@ -7915,10 +7924,10 @@
         <v>510</v>
       </c>
       <c r="B220" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C220" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="D220" s="7"/>
       <c r="E220" s="7"/>
@@ -7926,7 +7935,7 @@
         <v>29</v>
       </c>
       <c r="G220" s="26" t="s">
-        <v>1028</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.25">
@@ -7934,54 +7943,54 @@
         <v>510</v>
       </c>
       <c r="B221" t="s">
-        <v>550</v>
+        <v>1026</v>
       </c>
       <c r="C221" t="s">
-        <v>551</v>
+        <v>1027</v>
       </c>
       <c r="D221" s="7"/>
       <c r="E221" s="7"/>
       <c r="F221" t="s">
-        <v>20</v>
-      </c>
-      <c r="G221" s="26"/>
-    </row>
-    <row r="222" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="G221" s="26" t="s">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>510</v>
       </c>
       <c r="B222" t="s">
-        <v>1029</v>
+        <v>550</v>
       </c>
       <c r="C222" t="s">
-        <v>1030</v>
+        <v>551</v>
       </c>
       <c r="D222" s="7"/>
       <c r="E222" s="7"/>
       <c r="F222" t="s">
         <v>20</v>
       </c>
-      <c r="G222" s="26" t="s">
-        <v>1031</v>
-      </c>
+      <c r="G222" s="26"/>
     </row>
     <row r="223" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>510</v>
       </c>
       <c r="B223" t="s">
-        <v>998</v>
+        <v>1029</v>
       </c>
       <c r="C223" t="s">
-        <v>999</v>
+        <v>1030</v>
       </c>
       <c r="D223" s="7"/>
       <c r="E223" s="7"/>
       <c r="F223" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G223" s="26" t="s">
-        <v>1016</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="224" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -7989,10 +7998,10 @@
         <v>510</v>
       </c>
       <c r="B224" t="s">
-        <v>552</v>
+        <v>998</v>
       </c>
       <c r="C224" t="s">
-        <v>553</v>
+        <v>999</v>
       </c>
       <c r="D224" s="7"/>
       <c r="E224" s="7"/>
@@ -8000,90 +8009,90 @@
         <v>29</v>
       </c>
       <c r="G224" s="26" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="225" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>510</v>
       </c>
       <c r="B225" t="s">
-        <v>555</v>
+        <v>552</v>
       </c>
       <c r="C225" t="s">
-        <v>556</v>
+        <v>553</v>
       </c>
       <c r="D225" s="7"/>
       <c r="E225" s="7"/>
       <c r="F225" t="s">
         <v>29</v>
       </c>
-      <c r="G225" s="26"/>
-    </row>
-    <row r="226" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G225" s="26" t="s">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>510</v>
       </c>
       <c r="B226" t="s">
-        <v>993</v>
+        <v>555</v>
       </c>
       <c r="C226" t="s">
-        <v>994</v>
-      </c>
-      <c r="D226" s="7" t="s">
-        <v>995</v>
-      </c>
+        <v>556</v>
+      </c>
+      <c r="D226" s="7"/>
       <c r="E226" s="7"/>
       <c r="F226" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G226" s="26"/>
     </row>
-    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>510</v>
       </c>
       <c r="B227" t="s">
-        <v>557</v>
+        <v>993</v>
       </c>
       <c r="C227" t="s">
-        <v>558</v>
-      </c>
-      <c r="D227" s="7"/>
+        <v>994</v>
+      </c>
+      <c r="D227" s="7" t="s">
+        <v>995</v>
+      </c>
       <c r="E227" s="7"/>
       <c r="F227" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G227" s="26"/>
     </row>
-    <row r="228" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>510</v>
       </c>
       <c r="B228" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
       <c r="C228" t="s">
-        <v>560</v>
+        <v>558</v>
       </c>
       <c r="D228" s="7"/>
       <c r="E228" s="7"/>
       <c r="F228" t="s">
-        <v>10</v>
-      </c>
-      <c r="G228" s="26" t="s">
-        <v>561</v>
-      </c>
-    </row>
-    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="G228" s="26"/>
+    </row>
+    <row r="229" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>510</v>
       </c>
       <c r="B229" t="s">
-        <v>562</v>
+        <v>559</v>
       </c>
       <c r="C229" t="s">
-        <v>563</v>
+        <v>560</v>
       </c>
       <c r="D229" s="7"/>
       <c r="E229" s="7"/>
@@ -8091,83 +8100,83 @@
         <v>10</v>
       </c>
       <c r="G229" s="26" t="s">
-        <v>564</v>
-      </c>
-    </row>
-    <row r="230" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>510</v>
       </c>
       <c r="B230" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="C230" t="s">
-        <v>566</v>
-      </c>
-      <c r="D230" s="7" t="s">
-        <v>567</v>
-      </c>
+        <v>563</v>
+      </c>
+      <c r="D230" s="7"/>
       <c r="E230" s="7"/>
       <c r="F230" t="s">
+        <v>10</v>
+      </c>
+      <c r="G230" s="26" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="231" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A231" t="s">
+        <v>510</v>
+      </c>
+      <c r="B231" t="s">
+        <v>565</v>
+      </c>
+      <c r="C231" t="s">
+        <v>566</v>
+      </c>
+      <c r="D231" s="7" t="s">
+        <v>567</v>
+      </c>
+      <c r="E231" s="7"/>
+      <c r="F231" t="s">
         <v>20</v>
       </c>
-      <c r="G230" s="26" t="s">
+      <c r="G231" s="26" t="s">
         <v>568</v>
       </c>
-    </row>
-    <row r="231" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B231" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C231" s="2" t="s">
-        <v>570</v>
-      </c>
-      <c r="D231" s="7"/>
-      <c r="E231" s="7"/>
-      <c r="F231" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G231" s="26"/>
     </row>
     <row r="232" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>1032</v>
+        <v>569</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>1033</v>
+        <v>570</v>
       </c>
       <c r="D232" s="7"/>
       <c r="E232" s="7"/>
-      <c r="F232" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G232" s="26" t="s">
-        <v>1034</v>
-      </c>
+      <c r="F232" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G232" s="26"/>
     </row>
     <row r="233" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="D233" s="7"/>
       <c r="E233" s="7"/>
       <c r="F233" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G233" s="26" t="s">
-        <v>1037</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8175,25 +8184,29 @@
         <v>510</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>571</v>
+        <v>1035</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>572</v>
+        <v>1036</v>
       </c>
       <c r="D234" s="7"/>
       <c r="E234" s="7"/>
-      <c r="F234" s="4"/>
-      <c r="G234" s="26"/>
+      <c r="F234" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G234" s="26" t="s">
+        <v>1037</v>
+      </c>
     </row>
     <row r="235" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>996</v>
+        <v>571</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>997</v>
+        <v>572</v>
       </c>
       <c r="D235" s="7"/>
       <c r="E235" s="7"/>
@@ -8205,37 +8218,33 @@
         <v>510</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>573</v>
+        <v>996</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>574</v>
+        <v>997</v>
       </c>
       <c r="D236" s="7"/>
       <c r="E236" s="7"/>
-      <c r="F236" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G236" s="24" t="s">
-        <v>575</v>
-      </c>
+      <c r="F236" s="4"/>
+      <c r="G236" s="26"/>
     </row>
     <row r="237" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D237" s="7"/>
       <c r="E237" s="7"/>
-      <c r="F237" s="5" t="s">
+      <c r="F237" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G237" s="26" t="s">
-        <v>578</v>
+      <c r="G237" s="24" t="s">
+        <v>575</v>
       </c>
     </row>
     <row r="238" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8243,32 +8252,34 @@
         <v>510</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D238" s="7"/>
       <c r="E238" s="7"/>
-      <c r="F238" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G238" s="26"/>
+      <c r="F238" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G238" s="26" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="239" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D239" s="7"/>
       <c r="E239" s="7"/>
       <c r="F239" s="14" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G239" s="26"/>
     </row>
@@ -8277,15 +8288,15 @@
         <v>510</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D240" s="7"/>
       <c r="E240" s="7"/>
-      <c r="F240" s="4" t="s">
-        <v>20</v>
+      <c r="F240" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="G240" s="26"/>
     </row>
@@ -8294,51 +8305,51 @@
         <v>510</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="D241" s="1"/>
+        <v>584</v>
+      </c>
+      <c r="D241" s="7"/>
       <c r="E241" s="7"/>
       <c r="F241" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G241" s="24" t="s">
-        <v>587</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G241" s="26"/>
     </row>
     <row r="242" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="D242" s="7"/>
+        <v>586</v>
+      </c>
+      <c r="D242" s="1"/>
       <c r="E242" s="7"/>
-      <c r="F242" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G242" s="26"/>
+      <c r="F242" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G242" s="24" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="243" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D243" s="7"/>
       <c r="E243" s="7"/>
-      <c r="F243" s="4" t="s">
-        <v>96</v>
+      <c r="F243" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G243" s="26"/>
     </row>
@@ -8347,15 +8358,15 @@
         <v>510</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D244" s="7"/>
       <c r="E244" s="7"/>
       <c r="F244" s="4" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="G244" s="26"/>
     </row>
@@ -8364,173 +8375,171 @@
         <v>510</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D245" s="7"/>
       <c r="E245" s="7"/>
-      <c r="F245" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G245" s="24"/>
+      <c r="F245" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G245" s="26"/>
     </row>
     <row r="246" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D246" s="7" t="s">
-        <v>598</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="D246" s="7"/>
       <c r="E246" s="7"/>
-      <c r="F246" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G246" s="26" t="s">
-        <v>599</v>
-      </c>
+      <c r="F246" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G246" s="24"/>
     </row>
     <row r="247" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D247" s="1"/>
+        <v>597</v>
+      </c>
+      <c r="D247" s="7" t="s">
+        <v>598</v>
+      </c>
       <c r="E247" s="7"/>
       <c r="F247" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G247" s="26" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="D248" s="1"/>
+      <c r="E248" s="7"/>
+      <c r="F248" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G247" s="26"/>
-    </row>
-    <row r="248" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A248" t="s">
+      <c r="G248" s="26"/>
+    </row>
+    <row r="249" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
         <v>510</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B249" t="s">
         <v>602</v>
       </c>
-      <c r="C248" t="s">
+      <c r="C249" t="s">
         <v>603</v>
-      </c>
-      <c r="D248" s="7"/>
-      <c r="E248" s="7"/>
-      <c r="F248" t="s">
-        <v>29</v>
-      </c>
-      <c r="G248" s="26"/>
-    </row>
-    <row r="249" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A249" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>605</v>
       </c>
       <c r="D249" s="7"/>
       <c r="E249" s="7"/>
-      <c r="F249" s="4" t="s">
+      <c r="F249" t="s">
         <v>29</v>
       </c>
       <c r="G249" s="26"/>
     </row>
-    <row r="250" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D250" s="7"/>
       <c r="E250" s="7"/>
-      <c r="F250" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="G250" s="24" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A251" t="s">
+      <c r="F250" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G250" s="26"/>
+    </row>
+    <row r="251" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B251" t="s">
-        <v>609</v>
-      </c>
-      <c r="C251" t="s">
-        <v>610</v>
+      <c r="B251" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>607</v>
       </c>
       <c r="D251" s="7"/>
       <c r="E251" s="7"/>
-      <c r="F251" t="s">
+      <c r="F251" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="G251" s="24" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>510</v>
+      </c>
+      <c r="B252" t="s">
+        <v>609</v>
+      </c>
+      <c r="C252" t="s">
+        <v>610</v>
+      </c>
+      <c r="D252" s="7"/>
+      <c r="E252" s="7"/>
+      <c r="F252" t="s">
         <v>29</v>
       </c>
-      <c r="G251" s="26"/>
-    </row>
-    <row r="252" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A252" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="E252" s="7"/>
-      <c r="F252" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G252" s="24"/>
+      <c r="G252" s="26"/>
     </row>
     <row r="253" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>1038</v>
+        <v>611</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D253" s="1"/>
+        <v>612</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>613</v>
+      </c>
       <c r="E253" s="7"/>
-      <c r="F253" s="14" t="s">
+      <c r="F253" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G253" s="26" t="s">
-        <v>1040</v>
-      </c>
+      <c r="G253" s="24"/>
     </row>
     <row r="254" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>1041</v>
+        <v>1038</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>1042</v>
+        <v>1039</v>
       </c>
       <c r="D254" s="1"/>
       <c r="E254" s="7"/>
@@ -8538,26 +8547,26 @@
         <v>29</v>
       </c>
       <c r="G254" s="26" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7" x14ac:dyDescent="0.25">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>614</v>
+        <v>1041</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>615</v>
+        <v>1042</v>
       </c>
       <c r="D255" s="1"/>
       <c r="E255" s="7"/>
       <c r="F255" s="14" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G255" s="26" t="s">
-        <v>616</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="256" spans="1:7" x14ac:dyDescent="0.25">
@@ -8565,56 +8574,54 @@
         <v>510</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D256" s="7"/>
+        <v>615</v>
+      </c>
+      <c r="D256" s="1"/>
       <c r="E256" s="7"/>
-      <c r="F256" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G256" s="26"/>
-    </row>
-    <row r="257" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="F256" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G256" s="26" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D257" s="7"/>
       <c r="E257" s="7"/>
       <c r="F257" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G257" s="26" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+      <c r="G257" s="26"/>
+    </row>
+    <row r="258" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="D258" s="7" t="s">
-        <v>624</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="D258" s="7"/>
       <c r="E258" s="7"/>
-      <c r="F258" s="5" t="s">
+      <c r="F258" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G258" s="26" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
     </row>
     <row r="259" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
@@ -8622,68 +8629,72 @@
         <v>510</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="D259" s="7" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="E259" s="7"/>
       <c r="F259" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G259" s="26" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D260" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="E260" s="7"/>
+      <c r="F260" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="G259" s="26"/>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A260" t="s">
+      <c r="G260" s="26"/>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
         <v>510</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B261" t="s">
         <v>629</v>
       </c>
-      <c r="C260" t="s">
+      <c r="C261" t="s">
         <v>630</v>
-      </c>
-      <c r="D260" s="7"/>
-      <c r="E260" s="7"/>
-      <c r="F260" t="s">
-        <v>29</v>
-      </c>
-      <c r="G260" s="26"/>
-    </row>
-    <row r="261" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A261" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="D261" s="7"/>
       <c r="E261" s="7"/>
-      <c r="F261" s="4" t="s">
+      <c r="F261" t="s">
         <v>29</v>
       </c>
       <c r="G261" s="26"/>
     </row>
-    <row r="262" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="262" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D262" s="7"/>
       <c r="E262" s="7"/>
       <c r="F262" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G262" s="26"/>
     </row>
@@ -8692,67 +8703,67 @@
         <v>510</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D263" s="7"/>
       <c r="E263" s="7"/>
-      <c r="F263" s="5" t="s">
+      <c r="F263" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G263" s="26"/>
     </row>
-    <row r="264" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="264" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D264" s="7"/>
       <c r="E264" s="7"/>
       <c r="F264" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G264" s="26" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G264" s="26"/>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D265" s="7"/>
       <c r="E265" s="7"/>
-      <c r="F265" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G265" s="26"/>
-    </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A266" t="s">
+      <c r="F265" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G265" s="26" t="s">
+        <v>639</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A266" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B266" t="s">
-        <v>642</v>
-      </c>
-      <c r="C266" t="s">
-        <v>643</v>
+      <c r="B266" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="C266" s="2" t="s">
+        <v>641</v>
       </c>
       <c r="D266" s="7"/>
       <c r="E266" s="7"/>
-      <c r="F266" t="s">
+      <c r="F266" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G266" s="26"/>
@@ -8762,27 +8773,27 @@
         <v>510</v>
       </c>
       <c r="B267" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C267" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D267" s="7"/>
       <c r="E267" s="7"/>
       <c r="F267" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G267" s="26"/>
     </row>
-    <row r="268" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="268" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>510</v>
       </c>
       <c r="B268" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C268" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D268" s="7"/>
       <c r="E268" s="7"/>
@@ -8791,20 +8802,20 @@
       </c>
       <c r="G268" s="26"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="269" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>510</v>
       </c>
       <c r="B269" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="C269" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="D269" s="7"/>
       <c r="E269" s="7"/>
       <c r="F269" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G269" s="26"/>
     </row>
@@ -8813,49 +8824,49 @@
         <v>510</v>
       </c>
       <c r="B270" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C270" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D270" s="7"/>
       <c r="E270" s="7"/>
       <c r="F270" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G270" s="26"/>
     </row>
-    <row r="271" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>510</v>
       </c>
       <c r="B271" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C271" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D271" s="7"/>
       <c r="E271" s="7"/>
       <c r="F271" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G271" s="26"/>
     </row>
-    <row r="272" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>510</v>
       </c>
       <c r="B272" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="C272" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="D272" s="7"/>
       <c r="E272" s="7"/>
       <c r="F272" t="s">
-        <v>10</v>
+        <v>37</v>
       </c>
       <c r="G272" s="26"/>
     </row>
@@ -8864,29 +8875,27 @@
         <v>510</v>
       </c>
       <c r="B273" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C273" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="D273" s="7"/>
       <c r="E273" s="7"/>
       <c r="F273" t="s">
-        <v>14</v>
-      </c>
-      <c r="G273" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
+        <v>10</v>
+      </c>
+      <c r="G273" s="26"/>
+    </row>
+    <row r="274" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>510</v>
       </c>
       <c r="B274" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C274" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D274" s="7"/>
       <c r="E274" s="7"/>
@@ -8898,79 +8907,79 @@
       </c>
     </row>
     <row r="275" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A275" s="2" t="s">
+      <c r="A275" t="s">
         <v>510</v>
       </c>
-      <c r="B275" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C275" s="2" t="s">
-        <v>662</v>
+      <c r="B275" t="s">
+        <v>659</v>
+      </c>
+      <c r="C275" t="s">
+        <v>660</v>
       </c>
       <c r="D275" s="7"/>
       <c r="E275" s="7"/>
-      <c r="F275" s="3" t="s">
+      <c r="F275" t="s">
         <v>14</v>
       </c>
       <c r="G275" s="26" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D276" s="7"/>
       <c r="E276" s="7"/>
-      <c r="F276" s="5" t="s">
+      <c r="F276" s="3" t="s">
         <v>14</v>
       </c>
       <c r="G276" s="26" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A277" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B277" s="2" t="s">
+        <v>664</v>
+      </c>
+      <c r="C277" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="D277" s="7"/>
+      <c r="E277" s="7"/>
+      <c r="F277" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G277" s="26" t="s">
         <v>666</v>
       </c>
     </row>
-    <row r="277" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A277" s="17" t="s">
+    <row r="278" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A278" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="B277" s="17" t="s">
+      <c r="B278" s="17" t="s">
         <v>667</v>
       </c>
-      <c r="C277" s="17" t="s">
+      <c r="C278" s="17" t="s">
         <v>668</v>
       </c>
-      <c r="D277" s="27"/>
-      <c r="E277" s="27"/>
-      <c r="F277" s="18" t="s">
+      <c r="D278" s="27"/>
+      <c r="E278" s="27"/>
+      <c r="F278" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="G277" s="28" t="s">
+      <c r="G278" s="28" t="s">
         <v>669</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A278" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B278" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="C278" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="D278" s="7"/>
-      <c r="E278" s="7"/>
-      <c r="F278" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G278" s="26" t="s">
-        <v>658</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.25">
@@ -8978,12 +8987,12 @@
         <v>510</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>673</v>
-      </c>
-      <c r="D279" s="1"/>
+        <v>671</v>
+      </c>
+      <c r="D279" s="7"/>
       <c r="E279" s="7"/>
       <c r="F279" s="3" t="s">
         <v>14</v>
@@ -8992,70 +9001,70 @@
         <v>658</v>
       </c>
     </row>
-    <row r="280" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="280" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D280" s="1"/>
       <c r="E280" s="7"/>
       <c r="F280" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G280" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="G280" s="26" t="s">
+        <v>658</v>
+      </c>
     </row>
     <row r="281" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="D281" s="7"/>
+        <v>675</v>
+      </c>
+      <c r="D281" s="1"/>
       <c r="E281" s="7"/>
       <c r="F281" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G281" s="26"/>
     </row>
-    <row r="282" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
-        <v>678</v>
+        <v>510</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D282" s="7"/>
       <c r="E282" s="7"/>
       <c r="F282" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G282" s="26"/>
     </row>
-    <row r="283" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="283" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A283" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="D283" s="7" t="s">
-        <v>683</v>
-      </c>
+        <v>680</v>
+      </c>
+      <c r="D283" s="7"/>
       <c r="E283" s="7"/>
       <c r="F283" s="3" t="s">
         <v>10</v>
@@ -9067,13 +9076,13 @@
         <v>678</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E284" s="7"/>
       <c r="F284" s="3" t="s">
@@ -9086,13 +9095,15 @@
         <v>678</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>688</v>
-      </c>
-      <c r="D285" s="1"/>
-      <c r="E285" s="1"/>
+        <v>685</v>
+      </c>
+      <c r="D285" s="7" t="s">
+        <v>686</v>
+      </c>
+      <c r="E285" s="7"/>
       <c r="F285" s="3" t="s">
         <v>10</v>
       </c>
@@ -9103,27 +9114,27 @@
         <v>678</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>690</v>
-      </c>
-      <c r="D286" s="7"/>
-      <c r="E286" s="7"/>
+        <v>688</v>
+      </c>
+      <c r="D286" s="1"/>
+      <c r="E286" s="1"/>
       <c r="F286" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G286" s="26"/>
     </row>
-    <row r="287" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="D287" s="7"/>
       <c r="E287" s="7"/>
@@ -9132,166 +9143,166 @@
       </c>
       <c r="G287" s="26"/>
     </row>
-    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="288" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A288" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D288" s="7"/>
       <c r="E288" s="7"/>
-      <c r="F288" s="16" t="s">
+      <c r="F288" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G288" s="24"/>
-    </row>
-    <row r="289" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="G288" s="26"/>
+    </row>
+    <row r="289" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="E289" s="7" t="s">
-        <v>698</v>
-      </c>
-      <c r="F289" s="3" t="s">
+        <v>694</v>
+      </c>
+      <c r="D289" s="7"/>
+      <c r="E289" s="7"/>
+      <c r="F289" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G289" s="26"/>
-    </row>
-    <row r="290" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G289" s="24"/>
+    </row>
+    <row r="290" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B290" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="C290" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="D290" s="1" t="s">
+        <v>697</v>
+      </c>
+      <c r="E290" s="7" t="s">
         <v>698</v>
       </c>
-      <c r="C290" s="2" t="s">
-        <v>699</v>
-      </c>
-      <c r="D290" s="7"/>
-      <c r="E290" s="7"/>
-      <c r="F290" s="6" t="s">
+      <c r="F290" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G290" s="24"/>
+      <c r="G290" s="26"/>
     </row>
     <row r="291" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D291" s="7"/>
-      <c r="E291" s="1"/>
-      <c r="F291" s="3" t="s">
+      <c r="E291" s="7"/>
+      <c r="F291" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G291" s="26"/>
+      <c r="G291" s="24"/>
     </row>
     <row r="292" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="D292" s="7"/>
-      <c r="E292" s="7"/>
-      <c r="F292" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G292" s="26" t="s">
-        <v>704</v>
-      </c>
+      <c r="E292" s="1"/>
+      <c r="F292" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G292" s="26"/>
     </row>
     <row r="293" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="D293" s="7" t="s">
-        <v>707</v>
-      </c>
+        <v>703</v>
+      </c>
+      <c r="D293" s="7"/>
       <c r="E293" s="7"/>
-      <c r="F293" s="5"/>
-      <c r="G293" s="26"/>
+      <c r="F293" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G293" s="26" t="s">
+        <v>704</v>
+      </c>
     </row>
     <row r="294" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="D294" s="7"/>
+        <v>706</v>
+      </c>
+      <c r="D294" s="7" t="s">
+        <v>707</v>
+      </c>
       <c r="E294" s="7"/>
-      <c r="F294" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G294" s="26" t="s">
-        <v>710</v>
-      </c>
+      <c r="F294" s="5"/>
+      <c r="G294" s="26"/>
     </row>
     <row r="295" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D295" s="7"/>
-      <c r="E295" s="7" t="s">
-        <v>700</v>
-      </c>
+      <c r="E295" s="7"/>
       <c r="F295" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G295" s="26"/>
-    </row>
-    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
+        <v>25</v>
+      </c>
+      <c r="G295" s="26" t="s">
+        <v>710</v>
+      </c>
+    </row>
+    <row r="296" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
-      <c r="F296" s="3" t="s">
-        <v>20</v>
+      <c r="E296" s="7" t="s">
+        <v>700</v>
+      </c>
+      <c r="F296" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="G296" s="26"/>
     </row>
@@ -9300,259 +9311,259 @@
         <v>678</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D297" s="7"/>
       <c r="E297" s="7"/>
-      <c r="F297" s="16" t="s">
+      <c r="F297" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G297" s="24"/>
+      <c r="G297" s="26"/>
     </row>
     <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D298" s="7"/>
       <c r="E298" s="7"/>
-      <c r="F298" s="19" t="s">
+      <c r="F298" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G298" s="26"/>
+      <c r="G298" s="24"/>
     </row>
     <row r="299" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A299" s="17" t="s">
+      <c r="A299" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="B299" s="17" t="s">
-        <v>719</v>
-      </c>
-      <c r="C299" s="17" t="s">
-        <v>720</v>
-      </c>
-      <c r="D299" s="27"/>
-      <c r="E299" s="27"/>
+      <c r="B299" s="2" t="s">
+        <v>717</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>718</v>
+      </c>
+      <c r="D299" s="7"/>
+      <c r="E299" s="7"/>
       <c r="F299" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="G299" s="28"/>
-    </row>
-    <row r="300" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A300" s="2" t="s">
+      <c r="G299" s="26"/>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A300" s="17" t="s">
         <v>678</v>
       </c>
-      <c r="B300" s="2" t="s">
-        <v>721</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>722</v>
-      </c>
-      <c r="D300" s="7"/>
-      <c r="E300" s="7"/>
-      <c r="F300" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G300" s="26"/>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="B300" s="17" t="s">
+        <v>719</v>
+      </c>
+      <c r="C300" s="17" t="s">
+        <v>720</v>
+      </c>
+      <c r="D300" s="27"/>
+      <c r="E300" s="27"/>
+      <c r="F300" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G300" s="28"/>
+    </row>
+    <row r="301" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="D301" s="7"/>
-      <c r="E301" s="1"/>
-      <c r="F301" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G301" s="26" t="s">
-        <v>725</v>
-      </c>
+      <c r="E301" s="7"/>
+      <c r="F301" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G301" s="26"/>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D302" s="7"/>
-      <c r="E302" s="7"/>
-      <c r="F302" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G302" s="26"/>
-    </row>
-    <row r="303" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E302" s="1"/>
+      <c r="F302" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G302" s="26" t="s">
+        <v>725</v>
+      </c>
+    </row>
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
         <v>678</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D303" s="7"/>
       <c r="E303" s="7"/>
-      <c r="F303" s="16" t="s">
+      <c r="F303" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G303" s="24"/>
-    </row>
-    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G303" s="26"/>
+    </row>
+    <row r="304" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>730</v>
+        <v>678</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D304" s="7"/>
       <c r="E304" s="7"/>
-      <c r="F304" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G304" s="26"/>
+      <c r="F304" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G304" s="24"/>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
         <v>730</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D305" s="7"/>
-      <c r="E305" s="7" t="s">
-        <v>735</v>
-      </c>
+      <c r="E305" s="7"/>
       <c r="F305" s="5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G305" s="26"/>
     </row>
-    <row r="306" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
         <v>730</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D306" s="7"/>
-      <c r="E306" s="7"/>
-      <c r="F306" s="3" t="s">
-        <v>20</v>
+      <c r="E306" s="7" t="s">
+        <v>735</v>
+      </c>
+      <c r="F306" s="5" t="s">
+        <v>37</v>
       </c>
       <c r="G306" s="26"/>
     </row>
-    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="307" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
         <v>730</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="D307" s="7"/>
       <c r="E307" s="7"/>
-      <c r="F307" s="12" t="s">
+      <c r="F307" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G307" s="26"/>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A308" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B308" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="C308" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="D308" s="7"/>
+      <c r="E308" s="7"/>
+      <c r="F308" s="12" t="s">
         <v>14</v>
       </c>
-      <c r="G307" s="26" t="s">
+      <c r="G308" s="26" t="s">
         <v>740</v>
       </c>
     </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A308" s="17" t="s">
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A309" s="17" t="s">
         <v>730</v>
       </c>
-      <c r="B308" s="17" t="s">
+      <c r="B309" s="17" t="s">
         <v>741</v>
       </c>
-      <c r="C308" s="17" t="s">
+      <c r="C309" s="17" t="s">
         <v>742</v>
       </c>
-      <c r="D308" s="27"/>
-      <c r="E308" s="27"/>
-      <c r="F308" s="20" t="s">
+      <c r="D309" s="27"/>
+      <c r="E309" s="27"/>
+      <c r="F309" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="G308" s="28"/>
-    </row>
-    <row r="309" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A309" s="2" t="s">
-        <v>730</v>
-      </c>
-      <c r="B309" s="2" t="s">
-        <v>743</v>
-      </c>
-      <c r="C309" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="D309" s="7"/>
-      <c r="E309" s="7"/>
-      <c r="F309" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G309" s="24"/>
-    </row>
-    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G309" s="28"/>
+    </row>
+    <row r="310" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
         <v>730</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D310" s="7"/>
       <c r="E310" s="7"/>
       <c r="F310" s="6" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G310" s="24"/>
     </row>
-    <row r="311" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
         <v>730</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="D311" s="7"/>
       <c r="E311" s="7"/>
       <c r="F311" s="6" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G311" s="24"/>
     </row>
@@ -9561,54 +9572,52 @@
         <v>730</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D312" s="7"/>
       <c r="E312" s="7"/>
       <c r="F312" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G312" s="24"/>
+    </row>
+    <row r="313" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A313" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="B313" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="C313" s="2" t="s">
+        <v>749</v>
+      </c>
+      <c r="D313" s="7"/>
+      <c r="E313" s="7"/>
+      <c r="F313" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G312" s="24"/>
-    </row>
-    <row r="313" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A313" s="17" t="s">
+      <c r="G313" s="24"/>
+    </row>
+    <row r="314" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A314" s="17" t="s">
         <v>750</v>
       </c>
-      <c r="B313" s="17" t="s">
+      <c r="B314" s="17" t="s">
         <v>751</v>
       </c>
-      <c r="C313" s="17" t="s">
+      <c r="C314" s="17" t="s">
         <v>752</v>
       </c>
-      <c r="D313" s="27"/>
-      <c r="E313" s="27"/>
-      <c r="F313" s="22" t="s">
+      <c r="D314" s="27"/>
+      <c r="E314" s="27"/>
+      <c r="F314" s="22" t="s">
         <v>267</v>
       </c>
-      <c r="G313" s="28" t="s">
+      <c r="G314" s="28" t="s">
         <v>753</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A314" s="2" t="s">
-        <v>750</v>
-      </c>
-      <c r="B314" s="2" t="s">
-        <v>754</v>
-      </c>
-      <c r="C314" s="2" t="s">
-        <v>755</v>
-      </c>
-      <c r="D314" s="7"/>
-      <c r="E314" s="7"/>
-      <c r="F314" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G314" s="26" t="s">
-        <v>756</v>
       </c>
     </row>
     <row r="315" spans="1:7" x14ac:dyDescent="0.25">
@@ -9616,70 +9625,72 @@
         <v>750</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D315" s="7"/>
       <c r="E315" s="7"/>
-      <c r="F315" s="14" t="s">
+      <c r="F315" s="4" t="s">
         <v>25</v>
       </c>
       <c r="G315" s="26" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
         <v>750</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D316" s="7"/>
       <c r="E316" s="7"/>
-      <c r="F316" s="4" t="s">
+      <c r="F316" s="14" t="s">
         <v>25</v>
       </c>
       <c r="G316" s="26" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
         <v>750</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D317" s="7"/>
       <c r="E317" s="7"/>
-      <c r="F317" s="5" t="s">
+      <c r="F317" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G317" s="26"/>
+      <c r="G317" s="26" t="s">
+        <v>762</v>
+      </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>765</v>
+        <v>750</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D318" s="7"/>
       <c r="E318" s="7"/>
-      <c r="F318" s="4" t="s">
-        <v>29</v>
+      <c r="F318" s="5" t="s">
+        <v>25</v>
       </c>
       <c r="G318" s="26"/>
     </row>
@@ -9688,10 +9699,10 @@
         <v>765</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>1003</v>
+        <v>766</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>1004</v>
+        <v>767</v>
       </c>
       <c r="D319" s="7"/>
       <c r="E319" s="7"/>
@@ -9705,49 +9716,49 @@
         <v>765</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>768</v>
+        <v>1003</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>769</v>
+        <v>1004</v>
       </c>
       <c r="D320" s="7"/>
       <c r="E320" s="7"/>
-      <c r="F320" s="5" t="s">
+      <c r="F320" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G320" s="26"/>
     </row>
-    <row r="321" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="D321" s="7"/>
       <c r="E321" s="7"/>
-      <c r="F321" s="4" t="s">
-        <v>20</v>
+      <c r="F321" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G321" s="26"/>
     </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="322" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="D322" s="7"/>
       <c r="E322" s="7"/>
       <c r="F322" s="4" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G322" s="26"/>
     </row>
@@ -9756,65 +9767,65 @@
         <v>765</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="D323" s="7"/>
       <c r="E323" s="7"/>
-      <c r="F323" s="5" t="s">
-        <v>20</v>
+      <c r="F323" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G323" s="26"/>
     </row>
-    <row r="324" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
       <c r="D324" s="7"/>
       <c r="E324" s="7"/>
-      <c r="F324" s="3" t="s">
+      <c r="F324" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G324" s="26"/>
     </row>
-    <row r="325" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="325" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>778</v>
+        <v>776</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="D325" s="7"/>
       <c r="E325" s="7"/>
       <c r="F325" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G325" s="26"/>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="326" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="D326" s="7"/>
-      <c r="E326" s="1"/>
-      <c r="F326" s="5" t="s">
+      <c r="E326" s="7"/>
+      <c r="F326" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G326" s="26"/>
@@ -9824,32 +9835,32 @@
         <v>765</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="D327" s="7"/>
-      <c r="E327" s="7"/>
-      <c r="F327" s="3" t="s">
-        <v>20</v>
+      <c r="E327" s="1"/>
+      <c r="F327" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G327" s="26"/>
     </row>
-    <row r="328" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="328" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="D328" s="7"/>
       <c r="E328" s="7"/>
-      <c r="F328" s="5" t="s">
-        <v>10</v>
+      <c r="F328" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G328" s="26"/>
     </row>
@@ -9858,10 +9869,10 @@
         <v>765</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>787</v>
+        <v>785</v>
       </c>
       <c r="D329" s="7"/>
       <c r="E329" s="7"/>
@@ -9870,15 +9881,15 @@
       </c>
       <c r="G329" s="26"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="330" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>789</v>
+        <v>787</v>
       </c>
       <c r="D330" s="7"/>
       <c r="E330" s="7"/>
@@ -9887,20 +9898,20 @@
       </c>
       <c r="G330" s="26"/>
     </row>
-    <row r="331" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="D331" s="7"/>
       <c r="E331" s="7"/>
       <c r="F331" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G331" s="26"/>
     </row>
@@ -9909,97 +9920,97 @@
         <v>765</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>793</v>
-      </c>
-      <c r="D332" s="1"/>
+        <v>791</v>
+      </c>
+      <c r="D332" s="7"/>
       <c r="E332" s="7"/>
       <c r="F332" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G332" s="26"/>
     </row>
-    <row r="333" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="333" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>795</v>
-      </c>
-      <c r="D333" s="7"/>
+        <v>793</v>
+      </c>
+      <c r="D333" s="1"/>
       <c r="E333" s="7"/>
       <c r="F333" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G333" s="26"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="334" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D334" s="7"/>
       <c r="E334" s="7"/>
-      <c r="F334" s="3" t="s">
+      <c r="F334" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G334" s="26"/>
     </row>
-    <row r="335" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>799</v>
-      </c>
-      <c r="D335" s="7" t="s">
-        <v>800</v>
-      </c>
+        <v>797</v>
+      </c>
+      <c r="D335" s="7"/>
       <c r="E335" s="7"/>
       <c r="F335" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G335" s="26"/>
     </row>
-    <row r="336" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="336" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>802</v>
-      </c>
-      <c r="D336" s="7"/>
+        <v>799</v>
+      </c>
+      <c r="D336" s="7" t="s">
+        <v>800</v>
+      </c>
       <c r="E336" s="7"/>
       <c r="F336" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G336" s="26"/>
     </row>
-    <row r="337" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="337" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="D337" s="7"/>
       <c r="E337" s="7"/>
@@ -10008,32 +10019,32 @@
       </c>
       <c r="G337" s="26"/>
     </row>
-    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="338" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>806</v>
+        <v>804</v>
       </c>
       <c r="D338" s="7"/>
       <c r="E338" s="7"/>
-      <c r="F338" s="4" t="s">
-        <v>10</v>
+      <c r="F338" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G338" s="26"/>
     </row>
-    <row r="339" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>807</v>
+        <v>805</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="D339" s="7"/>
       <c r="E339" s="7"/>
@@ -10047,61 +10058,61 @@
         <v>765</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>809</v>
+        <v>807</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
       <c r="D340" s="7"/>
       <c r="E340" s="7"/>
-      <c r="F340" s="6" t="s">
+      <c r="F340" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="G340" s="24"/>
-    </row>
-    <row r="341" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="G340" s="26"/>
+    </row>
+    <row r="341" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>811</v>
+        <v>809</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="D341" s="7"/>
       <c r="E341" s="7"/>
-      <c r="F341" s="5" t="s">
+      <c r="F341" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="G341" s="26"/>
-    </row>
-    <row r="342" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="G341" s="24"/>
+    </row>
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="D342" s="7"/>
       <c r="E342" s="7"/>
       <c r="F342" s="5" t="s">
-        <v>29</v>
+        <v>10</v>
       </c>
       <c r="G342" s="26"/>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="343" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>816</v>
+        <v>814</v>
       </c>
       <c r="D343" s="7"/>
       <c r="E343" s="7"/>
@@ -10115,50 +10126,50 @@
         <v>765</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>818</v>
+        <v>816</v>
       </c>
       <c r="D344" s="7"/>
       <c r="E344" s="7"/>
-      <c r="F344" s="4" t="s">
-        <v>819</v>
-      </c>
-      <c r="G344" s="26" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="345" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F344" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G344" s="26"/>
+    </row>
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>821</v>
+        <v>817</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>822</v>
-      </c>
-      <c r="D345" s="1"/>
+        <v>818</v>
+      </c>
+      <c r="D345" s="7"/>
       <c r="E345" s="7"/>
-      <c r="F345" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G345" s="26"/>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F345" s="4" t="s">
+        <v>819</v>
+      </c>
+      <c r="G345" s="26" t="s">
+        <v>820</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>824</v>
-      </c>
-      <c r="D346" s="7"/>
+        <v>822</v>
+      </c>
+      <c r="D346" s="1"/>
       <c r="E346" s="7"/>
-      <c r="F346" s="4" t="s">
+      <c r="F346" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G346" s="26"/>
@@ -10168,10 +10179,10 @@
         <v>765</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="D347" s="7"/>
       <c r="E347" s="7"/>
@@ -10180,20 +10191,20 @@
       </c>
       <c r="G347" s="26"/>
     </row>
-    <row r="348" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D348" s="7"/>
       <c r="E348" s="7"/>
-      <c r="F348" s="5" t="s">
-        <v>29</v>
+      <c r="F348" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G348" s="26"/>
     </row>
@@ -10202,85 +10213,85 @@
         <v>765</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>830</v>
-      </c>
-      <c r="D349" s="7" t="s">
-        <v>831</v>
-      </c>
+        <v>828</v>
+      </c>
+      <c r="D349" s="7"/>
       <c r="E349" s="7"/>
-      <c r="F349" s="3" t="s">
-        <v>20</v>
+      <c r="F349" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G349" s="26"/>
     </row>
-    <row r="350" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>833</v>
-      </c>
-      <c r="D350" s="7"/>
+        <v>830</v>
+      </c>
+      <c r="D350" s="7" t="s">
+        <v>831</v>
+      </c>
       <c r="E350" s="7"/>
       <c r="F350" s="3" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G350" s="26"/>
     </row>
-    <row r="351" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="351" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A351" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D351" s="7"/>
       <c r="E351" s="7"/>
-      <c r="F351" s="5" t="s">
+      <c r="F351" s="3" t="s">
         <v>29</v>
       </c>
       <c r="G351" s="26"/>
     </row>
-    <row r="352" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="352" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D352" s="7"/>
       <c r="E352" s="7"/>
-      <c r="F352" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G352" s="24"/>
-    </row>
-    <row r="353" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F352" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G352" s="26"/>
+    </row>
+    <row r="353" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D353" s="7"/>
       <c r="E353" s="7"/>
       <c r="F353" s="16" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G353" s="24"/>
     </row>
@@ -10289,10 +10300,10 @@
         <v>765</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="D354" s="7"/>
       <c r="E354" s="7"/>
@@ -10301,70 +10312,68 @@
       </c>
       <c r="G354" s="24"/>
     </row>
-    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="355" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>842</v>
+        <v>840</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>843</v>
+        <v>841</v>
       </c>
       <c r="D355" s="7"/>
-      <c r="E355" s="1"/>
-      <c r="F355" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G355" s="26"/>
+      <c r="E355" s="7"/>
+      <c r="F355" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G355" s="24"/>
     </row>
     <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>844</v>
+        <v>842</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="D356" s="7"/>
-      <c r="E356" s="7"/>
-      <c r="F356" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G356" s="26" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="357" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="E356" s="1"/>
+      <c r="F356" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G356" s="26"/>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D357" s="7"/>
       <c r="E357" s="7"/>
-      <c r="F357" s="4" t="s">
+      <c r="F357" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G357" s="26" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="358" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="358" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A358" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>849</v>
+        <v>847</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="D358" s="7"/>
       <c r="E358" s="7"/>
@@ -10375,213 +10384,215 @@
         <v>846</v>
       </c>
     </row>
-    <row r="359" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="359" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="D359" s="7"/>
-      <c r="E359" s="7" t="s">
-        <v>796</v>
-      </c>
-      <c r="F359" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G359" s="24"/>
-    </row>
-    <row r="360" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="E359" s="7"/>
+      <c r="F359" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G359" s="26" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="D360" s="7"/>
-      <c r="E360" s="7"/>
-      <c r="F360" s="5" t="s">
-        <v>855</v>
-      </c>
-      <c r="G360" s="26"/>
+      <c r="E360" s="7" t="s">
+        <v>796</v>
+      </c>
+      <c r="F360" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G360" s="24"/>
     </row>
     <row r="361" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>1005</v>
+        <v>853</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>1006</v>
+        <v>854</v>
       </c>
       <c r="D361" s="7"/>
       <c r="E361" s="7"/>
       <c r="F361" s="5" t="s">
-        <v>20</v>
+        <v>855</v>
       </c>
       <c r="G361" s="26"/>
     </row>
-    <row r="362" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="362" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>856</v>
+        <v>1005</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>857</v>
+        <v>1006</v>
       </c>
       <c r="D362" s="7"/>
       <c r="E362" s="7"/>
       <c r="F362" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G362" s="26"/>
     </row>
-    <row r="363" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="363" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="D363" s="7"/>
       <c r="E363" s="7"/>
-      <c r="F363" s="16" t="s">
+      <c r="F363" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G363" s="24"/>
+      <c r="G363" s="26"/>
     </row>
     <row r="364" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="D364" s="7"/>
       <c r="E364" s="7"/>
-      <c r="F364" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G364" s="26" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F364" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G364" s="24"/>
+    </row>
+    <row r="365" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="D365" s="7"/>
       <c r="E365" s="7"/>
-      <c r="F365" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G365" s="26"/>
+      <c r="F365" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G365" s="26" t="s">
+        <v>862</v>
+      </c>
     </row>
     <row r="366" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="D366" s="7"/>
       <c r="E366" s="7"/>
-      <c r="F366" s="4" t="s">
+      <c r="F366" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G366" s="26"/>
     </row>
-    <row r="367" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="367" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="D367" s="7"/>
       <c r="E367" s="7"/>
-      <c r="F367" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G367" s="26" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="F367" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G367" s="26"/>
+    </row>
+    <row r="368" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="D368" s="7"/>
       <c r="E368" s="7"/>
-      <c r="F368" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G368" s="26"/>
+      <c r="F368" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G368" s="26" t="s">
+        <v>869</v>
+      </c>
     </row>
     <row r="369" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A369" t="s">
+      <c r="A369" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B369" t="s">
-        <v>872</v>
-      </c>
-      <c r="C369" t="s">
-        <v>873</v>
+      <c r="B369" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="C369" s="2" t="s">
+        <v>871</v>
       </c>
       <c r="D369" s="7"/>
       <c r="E369" s="7"/>
       <c r="F369" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G369" s="26"/>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A370" t="s">
+        <v>765</v>
+      </c>
+      <c r="B370" t="s">
+        <v>872</v>
+      </c>
+      <c r="C370" t="s">
+        <v>873</v>
+      </c>
+      <c r="D370" s="7"/>
+      <c r="E370" s="7"/>
+      <c r="F370" s="12" t="s">
         <v>29</v>
-      </c>
-      <c r="G369" s="26"/>
-    </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A370" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="B370" s="2" t="s">
-        <v>874</v>
-      </c>
-      <c r="C370" s="2" t="s">
-        <v>875</v>
-      </c>
-      <c r="D370" s="7"/>
-      <c r="E370" s="1"/>
-      <c r="F370" s="5" t="s">
-        <v>20</v>
       </c>
       <c r="G370" s="26"/>
     </row>
@@ -10590,15 +10601,15 @@
         <v>765</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="D371" s="7"/>
-      <c r="E371" s="7"/>
+      <c r="E371" s="1"/>
       <c r="F371" s="5" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G371" s="26"/>
     </row>
@@ -10607,17 +10618,15 @@
         <v>765</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>1007</v>
+        <v>876</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>1008</v>
+        <v>877</v>
       </c>
       <c r="D372" s="7"/>
-      <c r="E372" s="7" t="s">
-        <v>1009</v>
-      </c>
+      <c r="E372" s="7"/>
       <c r="F372" s="5" t="s">
-        <v>20</v>
+        <v>37</v>
       </c>
       <c r="G372" s="26"/>
     </row>
@@ -10626,15 +10635,17 @@
         <v>765</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>878</v>
+        <v>1007</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>879</v>
+        <v>1008</v>
       </c>
       <c r="D373" s="7"/>
-      <c r="E373" s="7"/>
-      <c r="F373" s="4" t="s">
-        <v>96</v>
+      <c r="E373" s="7" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F373" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G373" s="26"/>
     </row>
@@ -10643,118 +10654,118 @@
         <v>765</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
       <c r="D374" s="7"/>
-      <c r="E374" s="7" t="s">
-        <v>876</v>
-      </c>
-      <c r="F374" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G374" s="24"/>
+      <c r="E374" s="7"/>
+      <c r="F374" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G374" s="26"/>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B375" s="2" t="s">
+        <v>880</v>
+      </c>
+      <c r="C375" s="2" t="s">
+        <v>881</v>
+      </c>
+      <c r="D375" s="7"/>
+      <c r="E375" s="7" t="s">
+        <v>876</v>
+      </c>
+      <c r="F375" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G375" s="24"/>
+    </row>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A376" s="2" t="s">
+        <v>765</v>
+      </c>
+      <c r="B376" s="2" t="s">
         <v>882</v>
       </c>
-      <c r="C375" s="2" t="s">
+      <c r="C376" s="2" t="s">
         <v>883</v>
       </c>
-      <c r="D375" s="7"/>
-      <c r="E375" s="7"/>
-      <c r="F375" s="16" t="s">
+      <c r="D376" s="7"/>
+      <c r="E376" s="7"/>
+      <c r="F376" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G375" s="24"/>
-    </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A376" s="17" t="s">
+      <c r="G376" s="24"/>
+    </row>
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A377" s="17" t="s">
         <v>765</v>
       </c>
-      <c r="B376" s="17" t="s">
+      <c r="B377" s="17" t="s">
         <v>884</v>
       </c>
-      <c r="C376" s="17" t="s">
+      <c r="C377" s="17" t="s">
         <v>885</v>
       </c>
-      <c r="D376" s="27"/>
-      <c r="E376" s="27"/>
-      <c r="F376" s="20" t="s">
+      <c r="D377" s="27"/>
+      <c r="E377" s="27"/>
+      <c r="F377" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G376" s="28"/>
-    </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A377" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="B377" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="C377" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="D377" s="1"/>
-      <c r="E377" s="7"/>
-      <c r="F377" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G377" s="26" t="s">
-        <v>888</v>
-      </c>
+      <c r="G377" s="28"/>
     </row>
     <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="D378" s="1"/>
       <c r="E378" s="7"/>
       <c r="F378" s="5" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="G378" s="26" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="379" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D379" s="1"/>
       <c r="E379" s="7"/>
       <c r="F379" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G379" s="26"/>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+        <v>14</v>
+      </c>
+      <c r="G379" s="26" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A380" s="2" t="s">
         <v>765</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>1010</v>
+        <v>892</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>1011</v>
+        <v>893</v>
       </c>
       <c r="D380" s="1"/>
       <c r="E380" s="7"/>
@@ -10768,15 +10779,13 @@
         <v>765</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D381" s="1"/>
-      <c r="E381" s="7" t="s">
-        <v>772</v>
-      </c>
+      <c r="E381" s="7"/>
       <c r="F381" s="5" t="s">
         <v>29</v>
       </c>
@@ -10787,13 +10796,15 @@
         <v>765</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
       <c r="D382" s="1"/>
-      <c r="E382" s="7"/>
+      <c r="E382" s="7" t="s">
+        <v>772</v>
+      </c>
       <c r="F382" s="5" t="s">
         <v>29</v>
       </c>
@@ -10801,20 +10812,18 @@
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>894</v>
+        <v>765</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>895</v>
+        <v>1014</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="D383" s="7" t="s">
-        <v>897</v>
-      </c>
+        <v>1015</v>
+      </c>
+      <c r="D383" s="1"/>
       <c r="E383" s="7"/>
-      <c r="F383" s="25" t="s">
-        <v>20</v>
+      <c r="F383" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G383" s="26"/>
     </row>
@@ -10823,32 +10832,32 @@
         <v>894</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D384" s="7" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="E384" s="7"/>
-      <c r="F384" s="4" t="s">
+      <c r="F384" s="25" t="s">
         <v>20</v>
       </c>
       <c r="G384" s="26"/>
     </row>
-    <row r="385" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
         <v>894</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>902</v>
-      </c>
-      <c r="D385" s="1" t="s">
-        <v>903</v>
+        <v>899</v>
+      </c>
+      <c r="D385" s="7" t="s">
+        <v>900</v>
       </c>
       <c r="E385" s="7"/>
       <c r="F385" s="4" t="s">
@@ -10857,52 +10866,52 @@
       <c r="G385" s="26"/>
     </row>
     <row r="386" spans="1:7" ht="30" x14ac:dyDescent="0.25">
-      <c r="A386" s="17" t="s">
+      <c r="A386" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="B386" s="17" t="s">
+      <c r="B386" s="2" t="s">
+        <v>901</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>902</v>
+      </c>
+      <c r="D386" s="1" t="s">
+        <v>903</v>
+      </c>
+      <c r="E386" s="7"/>
+      <c r="F386" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G386" s="26"/>
+    </row>
+    <row r="387" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A387" s="17" t="s">
+        <v>894</v>
+      </c>
+      <c r="B387" s="17" t="s">
         <v>904</v>
       </c>
-      <c r="C386" s="17" t="s">
+      <c r="C387" s="17" t="s">
         <v>905</v>
       </c>
-      <c r="D386" s="27"/>
-      <c r="E386" s="27"/>
-      <c r="F386" s="18" t="s">
+      <c r="D387" s="27"/>
+      <c r="E387" s="27"/>
+      <c r="F387" s="18" t="s">
         <v>906</v>
       </c>
-      <c r="G386" s="28"/>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A387" t="s">
-        <v>894</v>
-      </c>
-      <c r="B387" t="s">
-        <v>907</v>
-      </c>
-      <c r="C387" t="s">
-        <v>908</v>
-      </c>
-      <c r="D387" s="7"/>
-      <c r="E387" s="7"/>
-      <c r="F387" t="s">
-        <v>29</v>
-      </c>
-      <c r="G387" s="26"/>
+      <c r="G387" s="28"/>
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" t="s">
         <v>894</v>
       </c>
       <c r="B388" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="C388" t="s">
-        <v>910</v>
-      </c>
-      <c r="D388" s="7" t="s">
-        <v>911</v>
-      </c>
+        <v>908</v>
+      </c>
+      <c r="D388" s="7"/>
       <c r="E388" s="7"/>
       <c r="F388" t="s">
         <v>29</v>
@@ -10914,24 +10923,43 @@
         <v>894</v>
       </c>
       <c r="B389" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C389" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D389" s="7" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="E389" s="7"/>
       <c r="F389" t="s">
+        <v>29</v>
+      </c>
+      <c r="G389" s="26"/>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A390" t="s">
+        <v>894</v>
+      </c>
+      <c r="B390" t="s">
+        <v>912</v>
+      </c>
+      <c r="C390" t="s">
+        <v>913</v>
+      </c>
+      <c r="D390" s="7" t="s">
+        <v>914</v>
+      </c>
+      <c r="E390" s="7"/>
+      <c r="F390" t="s">
         <v>20</v>
       </c>
-      <c r="G389" s="26"/>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="D390" s="7"/>
-      <c r="E390" s="7"/>
       <c r="G390" s="26"/>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="D391" s="7"/>
+      <c r="E391" s="7"/>
+      <c r="G391" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\RobbieOrvis\Models\EPS Structure Research\eps-us-input-rename2\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\.claude\worktrees\cement-substitute-material-cost\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09319B7B-B9B4-4734-B6A5-3E30C1B6365C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C1AF3ED-7CEA-44EC-A711-1446F282FB76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="57840" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -1935,15 +1935,6 @@
     <t>Repayment Period for Financed Industry Sector Capital Costs</t>
   </si>
   <si>
-    <t>SCMEI</t>
-  </si>
-  <si>
-    <t>SCM Production Energy per Ton of Substitution</t>
-  </si>
-  <si>
-    <t>Marginal-SCM mix (calcined clay share) is region-specific.</t>
-  </si>
-  <si>
     <t>SoCaOMSbRIC</t>
   </si>
   <si>
@@ -3135,9 +3126,6 @@
     <t>Cement Calcined Clay Capital Inputs</t>
   </si>
   <si>
-    <t>Calcined clay plant capital per tonne of annual capacity and the calcined clay share of clinker substitution. Only matters when a policy raises clinker substitution.</t>
-  </si>
-  <si>
     <t>LCCT</t>
   </si>
   <si>
@@ -3199,13 +3187,25 @@
   </si>
   <si>
     <t>A vehicle type that fills toward its normal loading (buses, passenger rail, aircraft) should keep growing on an observed fleet trend meanwhile</t>
+  </si>
+  <si>
+    <t>CSMI</t>
+  </si>
+  <si>
+    <t>Cement Substitute Material Inputs</t>
+  </si>
+  <si>
+    <t>The mix of materials that replaces clinker under policy (calcined clay, limestone, fly ash, slag, natural pozzolan) and from it, by year: the heat to make the mix, the calcined clay share, and the net material cost per ton of clinker replaced. Replaces SCMEI. Only matters when a policy raises clinker substitution.</t>
+  </si>
+  <si>
+    <t>Calcined clay plant capital per tonne of annual capacity (the calcined clay share now comes from CSMI). Only matters when a policy raises clinker substitution.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3682,326 +3682,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="3" spans="1:1">
-      <c r="A3" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="4" spans="1:1">
-      <c r="A4" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="5" spans="1:1">
-      <c r="A5" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="6" spans="1:1">
-      <c r="A6" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="8" spans="1:1">
-      <c r="A8" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="9" spans="1:1">
-      <c r="A9" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="10" spans="1:1">
-      <c r="A10" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>922</v>
       </c>
     </row>
-    <row r="11" spans="1:1">
-      <c r="A11" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>923</v>
       </c>
     </row>
-    <row r="12" spans="1:1">
-      <c r="A12" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>924</v>
       </c>
     </row>
-    <row r="13" spans="1:1">
-      <c r="A13" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>925</v>
       </c>
     </row>
-    <row r="15" spans="1:1">
-      <c r="A15" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1">
-      <c r="A16" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
-      <c r="A17" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B19" t="s">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
         <v>929</v>
       </c>
     </row>
-    <row r="20" spans="1:3">
-      <c r="B20" t="s">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
         <v>930</v>
       </c>
     </row>
-    <row r="21" spans="1:3">
-      <c r="B21" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>931</v>
       </c>
     </row>
-    <row r="22" spans="1:3">
-      <c r="B22" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="B23" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="B24" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
         <v>37</v>
       </c>
       <c r="C26" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C27" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="C28" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B30" t="s">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="31" spans="1:3">
-      <c r="B31" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>939</v>
       </c>
     </row>
-    <row r="32" spans="1:3">
-      <c r="B32" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
         <v>940</v>
       </c>
     </row>
-    <row r="33" spans="1:3">
-      <c r="B33" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="34" spans="1:3">
-      <c r="B34" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
         <v>942</v>
       </c>
     </row>
-    <row r="35" spans="1:3">
-      <c r="B35" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3">
-      <c r="B36" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3">
-      <c r="B37" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B39" t="s">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="40" spans="1:3">
-      <c r="B40" t="s">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
         <v>947</v>
       </c>
     </row>
-    <row r="41" spans="1:3">
-      <c r="B41" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
         <v>948</v>
       </c>
     </row>
-    <row r="42" spans="1:3">
-      <c r="B42" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
         <v>949</v>
       </c>
     </row>
-    <row r="43" spans="1:3">
-      <c r="B43" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
         <v>950</v>
       </c>
     </row>
-    <row r="44" spans="1:3">
-      <c r="B44" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3">
-      <c r="B45" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3">
-      <c r="B46" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
-    <row r="49" spans="1:2">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
         <v>954</v>
       </c>
     </row>
-    <row r="50" spans="1:2">
-      <c r="B50" t="s">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
         <v>955</v>
       </c>
     </row>
-    <row r="51" spans="1:2">
-      <c r="B51" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
         <v>956</v>
       </c>
     </row>
-    <row r="52" spans="1:2">
-      <c r="B52" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
         <v>957</v>
       </c>
     </row>
-    <row r="53" spans="1:2">
-      <c r="B53" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="B54" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="B55" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B57" t="s">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="58" spans="1:2">
-      <c r="B58" t="s">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="59" spans="1:2">
-      <c r="B59" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="60" spans="1:2">
-      <c r="B60" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="62" spans="1:2">
-      <c r="A62" s="7" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="63" spans="1:2">
-      <c r="A63" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>966</v>
       </c>
     </row>
-    <row r="64" spans="1:2">
-      <c r="A64" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>967</v>
       </c>
     </row>
-    <row r="65" spans="1:1">
-      <c r="A65" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>968</v>
       </c>
     </row>
-    <row r="66" spans="1:1">
-      <c r="A66" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>969</v>
       </c>
     </row>
-    <row r="67" spans="1:1">
-      <c r="A67" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>970</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1">
-      <c r="A68" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1">
-      <c r="A69" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1">
-      <c r="A70" t="s">
-        <v>973</v>
       </c>
     </row>
   </sheetData>
@@ -4013,7 +4013,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G394"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
     <col min="2" max="2" width="19.42578125" style="2" customWidth="1"/>
@@ -4026,7 +4026,7 @@
     <col min="10" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -4049,7 +4049,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1">
+    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -4087,7 +4087,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -4106,7 +4106,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -4123,7 +4123,7 @@
       </c>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -4159,7 +4159,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -4176,7 +4176,7 @@
       </c>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>7</v>
       </c>
@@ -4193,7 +4193,7 @@
       </c>
       <c r="G9" s="28"/>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G10" s="26"/>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -4244,7 +4244,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
@@ -4261,7 +4261,7 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -4280,7 +4280,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -4297,7 +4297,7 @@
       </c>
       <c r="G15" s="26"/>
     </row>
-    <row r="16" spans="1:7" ht="45" customHeight="1">
+    <row r="16" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -4316,7 +4316,7 @@
       </c>
       <c r="G16" s="26"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -4335,7 +4335,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="G18" s="26"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>32</v>
       </c>
@@ -4371,7 +4371,7 @@
       </c>
       <c r="G19" s="26"/>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
@@ -4388,7 +4388,7 @@
       </c>
       <c r="G20" s="26"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
@@ -4405,7 +4405,7 @@
       </c>
       <c r="G21" s="26"/>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
@@ -4422,7 +4422,7 @@
       </c>
       <c r="G22" s="26"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>32</v>
       </c>
@@ -4439,7 +4439,7 @@
       </c>
       <c r="G23" s="26"/>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -4456,7 +4456,7 @@
       </c>
       <c r="G24" s="26"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>32</v>
       </c>
@@ -4473,7 +4473,7 @@
       </c>
       <c r="G25" s="26"/>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>32</v>
       </c>
@@ -4490,7 +4490,7 @@
       </c>
       <c r="G26" s="26"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -4509,7 +4509,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
@@ -4526,7 +4526,7 @@
       </c>
       <c r="G28" s="26"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
@@ -4545,7 +4545,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="G30" s="26"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>32</v>
       </c>
@@ -4579,7 +4579,7 @@
       </c>
       <c r="G31" s="26"/>
     </row>
-    <row r="32" spans="1:7" ht="45" customHeight="1">
+    <row r="32" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -4598,7 +4598,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
@@ -4617,7 +4617,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -4634,7 +4634,7 @@
       </c>
       <c r="G34" s="24"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>32</v>
       </c>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="G35" s="26"/>
     </row>
-    <row r="36" spans="1:7">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -4668,7 +4668,7 @@
       </c>
       <c r="G36" s="26"/>
     </row>
-    <row r="37" spans="1:7">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>32</v>
       </c>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="G37" s="26"/>
     </row>
-    <row r="38" spans="1:7">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>32</v>
       </c>
@@ -4702,7 +4702,7 @@
       </c>
       <c r="G38" s="26"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>32</v>
       </c>
@@ -4721,7 +4721,7 @@
       </c>
       <c r="G39" s="26"/>
     </row>
-    <row r="40" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="40" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
         <v>32</v>
       </c>
@@ -4740,7 +4740,7 @@
       </c>
       <c r="G40" s="28"/>
     </row>
-    <row r="41" spans="1:7">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>104</v>
       </c>
@@ -4757,7 +4757,7 @@
       </c>
       <c r="G41" s="26"/>
     </row>
-    <row r="42" spans="1:7" ht="30" customHeight="1">
+    <row r="42" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>104</v>
       </c>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="G42" s="26"/>
     </row>
-    <row r="43" spans="1:7">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>104</v>
       </c>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="G43" s="26"/>
     </row>
-    <row r="44" spans="1:7" ht="120" customHeight="1">
+    <row r="44" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>104</v>
       </c>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="G44" s="26"/>
     </row>
-    <row r="45" spans="1:7" ht="30" customHeight="1">
+    <row r="45" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>104</v>
       </c>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="G45" s="26"/>
     </row>
-    <row r="46" spans="1:7">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>104</v>
       </c>
@@ -4848,7 +4848,7 @@
       </c>
       <c r="G46" s="26"/>
     </row>
-    <row r="47" spans="1:7">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>104</v>
       </c>
@@ -4865,7 +4865,7 @@
       </c>
       <c r="G47" s="26"/>
     </row>
-    <row r="48" spans="1:7">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>104</v>
       </c>
@@ -4882,7 +4882,7 @@
       </c>
       <c r="G48" s="26"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>104</v>
       </c>
@@ -4901,7 +4901,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="1:7" ht="30" customHeight="1">
+    <row r="50" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>104</v>
       </c>
@@ -4918,7 +4918,7 @@
       </c>
       <c r="G50" s="26"/>
     </row>
-    <row r="51" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
+    <row r="51" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="17" t="s">
         <v>104</v>
       </c>
@@ -4935,7 +4935,7 @@
       </c>
       <c r="G51" s="26"/>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>131</v>
       </c>
@@ -4952,7 +4952,7 @@
       </c>
       <c r="G52" s="26"/>
     </row>
-    <row r="53" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="53" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="17" t="s">
         <v>131</v>
       </c>
@@ -4971,7 +4971,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="54" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="54" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
         <v>137</v>
       </c>
@@ -4990,7 +4990,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="60" customHeight="1">
+    <row r="55" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>141</v>
       </c>
@@ -5009,7 +5009,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>141</v>
       </c>
@@ -5028,7 +5028,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="57" spans="1:7" ht="60" customHeight="1">
+    <row r="57" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>141</v>
       </c>
@@ -5047,7 +5047,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="60" customHeight="1">
+    <row r="58" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>141</v>
       </c>
@@ -5066,7 +5066,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="45" customHeight="1">
+    <row r="59" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>141</v>
       </c>
@@ -5085,7 +5085,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="60" customHeight="1">
+    <row r="60" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>141</v>
       </c>
@@ -5104,7 +5104,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="60" customHeight="1">
+    <row r="61" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>141</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="62" spans="1:7" ht="60" customHeight="1">
+    <row r="62" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>141</v>
       </c>
@@ -5142,7 +5142,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="45" customHeight="1">
+    <row r="63" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>141</v>
       </c>
@@ -5161,7 +5161,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="30" customHeight="1">
+    <row r="64" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>141</v>
       </c>
@@ -5180,7 +5180,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="30" customHeight="1">
+    <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>141</v>
       </c>
@@ -5199,7 +5199,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="60" customHeight="1">
+    <row r="66" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>141</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="30" customHeight="1">
+    <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>141</v>
       </c>
@@ -5235,7 +5235,7 @@
       </c>
       <c r="G67" s="26"/>
     </row>
-    <row r="68" spans="1:7" ht="45" customHeight="1">
+    <row r="68" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>141</v>
       </c>
@@ -5254,7 +5254,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="90" customHeight="1">
+    <row r="69" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>141</v>
       </c>
@@ -5275,7 +5275,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="70" spans="1:7" ht="45" customHeight="1">
+    <row r="70" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>141</v>
       </c>
@@ -5296,7 +5296,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>141</v>
       </c>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="G71" s="26"/>
     </row>
-    <row r="72" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="72" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
         <v>141</v>
       </c>
@@ -5330,7 +5330,7 @@
       </c>
       <c r="G72" s="28"/>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>196</v>
       </c>
@@ -5347,7 +5347,7 @@
       </c>
       <c r="G73" s="26"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>196</v>
       </c>
@@ -5364,7 +5364,7 @@
       </c>
       <c r="G74" s="26"/>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>196</v>
       </c>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="G75" s="26"/>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>196</v>
       </c>
@@ -5398,7 +5398,7 @@
       </c>
       <c r="G76" s="26"/>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>196</v>
       </c>
@@ -5415,7 +5415,7 @@
       </c>
       <c r="G77" s="26"/>
     </row>
-    <row r="78" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="78" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A78" s="17" t="s">
         <v>196</v>
       </c>
@@ -5434,7 +5434,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>210</v>
       </c>
@@ -5451,7 +5451,7 @@
       </c>
       <c r="G79" s="26"/>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>210</v>
       </c>
@@ -5468,7 +5468,7 @@
       </c>
       <c r="G80" s="26"/>
     </row>
-    <row r="81" spans="1:7" ht="45" customHeight="1">
+    <row r="81" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>210</v>
       </c>
@@ -5487,7 +5487,7 @@
       </c>
       <c r="G81" s="26"/>
     </row>
-    <row r="82" spans="1:7" ht="30" customHeight="1">
+    <row r="82" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>210</v>
       </c>
@@ -5506,7 +5506,7 @@
       </c>
       <c r="G82" s="26"/>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>210</v>
       </c>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="G83" s="26"/>
     </row>
-    <row r="84" spans="1:7" ht="30" customHeight="1">
+    <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>210</v>
       </c>
@@ -5540,7 +5540,7 @@
       </c>
       <c r="G84" s="26"/>
     </row>
-    <row r="85" spans="1:7" ht="45" customHeight="1">
+    <row r="85" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>210</v>
       </c>
@@ -5559,7 +5559,7 @@
       </c>
       <c r="G85" s="26"/>
     </row>
-    <row r="86" spans="1:7" ht="45" customHeight="1">
+    <row r="86" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>210</v>
       </c>
@@ -5578,7 +5578,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
@@ -5597,7 +5597,7 @@
       </c>
       <c r="G87" s="26"/>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>210</v>
       </c>
@@ -5614,7 +5614,7 @@
       </c>
       <c r="G88" s="26"/>
     </row>
-    <row r="89" spans="1:7" ht="75" customHeight="1">
+    <row r="89" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>210</v>
       </c>
@@ -5633,7 +5633,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="90" spans="1:7" ht="75" customHeight="1">
+    <row r="90" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>210</v>
       </c>
@@ -5652,7 +5652,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>210</v>
       </c>
@@ -5669,7 +5669,7 @@
       </c>
       <c r="G91" s="26"/>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>210</v>
       </c>
@@ -5686,7 +5686,7 @@
       </c>
       <c r="G92" s="26"/>
     </row>
-    <row r="93" spans="1:7" ht="30" customHeight="1">
+    <row r="93" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>210</v>
       </c>
@@ -5703,7 +5703,7 @@
       </c>
       <c r="G93" s="26"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>210</v>
       </c>
@@ -5724,7 +5724,7 @@
       </c>
       <c r="G94" s="26"/>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>210</v>
       </c>
@@ -5741,7 +5741,7 @@
       </c>
       <c r="G95" s="26"/>
     </row>
-    <row r="96" spans="1:7" ht="30" customHeight="1">
+    <row r="96" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>210</v>
       </c>
@@ -5758,7 +5758,7 @@
       </c>
       <c r="G96" s="26"/>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>210</v>
       </c>
@@ -5775,7 +5775,7 @@
       </c>
       <c r="G97" s="26"/>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>210</v>
       </c>
@@ -5792,7 +5792,7 @@
       </c>
       <c r="G98" s="26"/>
     </row>
-    <row r="99" spans="1:7" ht="75" customHeight="1">
+    <row r="99" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>210</v>
       </c>
@@ -5811,7 +5811,7 @@
       </c>
       <c r="G99" s="26"/>
     </row>
-    <row r="100" spans="1:7" ht="30" customHeight="1">
+    <row r="100" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>210</v>
       </c>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="G100" s="26"/>
     </row>
-    <row r="101" spans="1:7" ht="75" customHeight="1">
+    <row r="101" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>210</v>
       </c>
@@ -5847,7 +5847,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>210</v>
       </c>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="G102" s="26"/>
     </row>
-    <row r="103" spans="1:7" ht="90" customHeight="1">
+    <row r="103" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>210</v>
       </c>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="G103" s="26"/>
     </row>
-    <row r="104" spans="1:7" ht="30" customHeight="1">
+    <row r="104" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>210</v>
       </c>
@@ -5900,7 +5900,7 @@
       </c>
       <c r="G104" s="26"/>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>210</v>
       </c>
@@ -5917,7 +5917,7 @@
       </c>
       <c r="G105" s="26"/>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>210</v>
       </c>
@@ -5934,7 +5934,7 @@
       </c>
       <c r="G106" s="26"/>
     </row>
-    <row r="107" spans="1:7" ht="30" customHeight="1">
+    <row r="107" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>210</v>
       </c>
@@ -5953,7 +5953,7 @@
       </c>
       <c r="G107" s="26"/>
     </row>
-    <row r="108" spans="1:7" ht="30" customHeight="1">
+    <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>210</v>
       </c>
@@ -5972,7 +5972,7 @@
       </c>
       <c r="G108" s="26"/>
     </row>
-    <row r="109" spans="1:7" ht="30" customHeight="1">
+    <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>210</v>
       </c>
@@ -5991,7 +5991,7 @@
       </c>
       <c r="G109" s="26"/>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>210</v>
       </c>
@@ -6010,7 +6010,7 @@
       </c>
       <c r="G110" s="26"/>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>210</v>
       </c>
@@ -6027,7 +6027,7 @@
       </c>
       <c r="G111" s="26"/>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>210</v>
       </c>
@@ -6044,7 +6044,7 @@
       </c>
       <c r="G112" s="26"/>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>210</v>
       </c>
@@ -6061,7 +6061,7 @@
       </c>
       <c r="G113" s="26"/>
     </row>
-    <row r="114" spans="1:7" ht="30" customHeight="1">
+    <row r="114" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>210</v>
       </c>
@@ -6080,7 +6080,7 @@
       </c>
       <c r="G114" s="26"/>
     </row>
-    <row r="115" spans="1:7" ht="60" customHeight="1">
+    <row r="115" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>210</v>
       </c>
@@ -6099,7 +6099,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>210</v>
       </c>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="G116" s="26"/>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>210</v>
       </c>
@@ -6135,7 +6135,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="118" spans="1:7" ht="30" customHeight="1">
+    <row r="118" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>210</v>
       </c>
@@ -6152,7 +6152,7 @@
       </c>
       <c r="G118" s="26"/>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>210</v>
       </c>
@@ -6169,7 +6169,7 @@
       </c>
       <c r="G119" s="26"/>
     </row>
-    <row r="120" spans="1:7" ht="30" customHeight="1">
+    <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>210</v>
       </c>
@@ -6186,7 +6186,7 @@
       </c>
       <c r="G120" s="26"/>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>210</v>
       </c>
@@ -6203,7 +6203,7 @@
       </c>
       <c r="G121" s="26"/>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>210</v>
       </c>
@@ -6220,7 +6220,7 @@
       </c>
       <c r="G122" s="26"/>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>210</v>
       </c>
@@ -6237,7 +6237,7 @@
       </c>
       <c r="G123" s="26"/>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>210</v>
       </c>
@@ -6254,7 +6254,7 @@
       </c>
       <c r="G124" s="26"/>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>210</v>
       </c>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="G125" s="26"/>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>210</v>
       </c>
@@ -6288,7 +6288,7 @@
       </c>
       <c r="G126" s="26"/>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>210</v>
       </c>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="G127" s="26"/>
     </row>
-    <row r="128" spans="1:7" ht="60" customHeight="1">
+    <row r="128" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>210</v>
       </c>
@@ -6324,7 +6324,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="129" spans="1:7" ht="60" customHeight="1">
+    <row r="129" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>210</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="130" spans="1:7" ht="30" customHeight="1">
+    <row r="130" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>210</v>
       </c>
@@ -6362,7 +6362,7 @@
       </c>
       <c r="G130" s="26"/>
     </row>
-    <row r="131" spans="1:7" ht="45" customHeight="1">
+    <row r="131" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>210</v>
       </c>
@@ -6381,7 +6381,7 @@
       </c>
       <c r="G131" s="26"/>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>210</v>
       </c>
@@ -6398,7 +6398,7 @@
       </c>
       <c r="G132" s="26"/>
     </row>
-    <row r="133" spans="1:7" ht="30" customHeight="1">
+    <row r="133" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>210</v>
       </c>
@@ -6415,7 +6415,7 @@
       </c>
       <c r="G133" s="26"/>
     </row>
-    <row r="134" spans="1:7" ht="30" customHeight="1">
+    <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>210</v>
       </c>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="G134" s="26"/>
     </row>
-    <row r="135" spans="1:7" ht="45" customHeight="1">
+    <row r="135" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>210</v>
       </c>
@@ -6453,7 +6453,7 @@
       </c>
       <c r="G135" s="26"/>
     </row>
-    <row r="136" spans="1:7" ht="30" customHeight="1">
+    <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>210</v>
       </c>
@@ -6474,7 +6474,7 @@
       </c>
       <c r="G136" s="26"/>
     </row>
-    <row r="137" spans="1:7" ht="30" customHeight="1">
+    <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>210</v>
       </c>
@@ -6491,7 +6491,7 @@
       </c>
       <c r="G137" s="26"/>
     </row>
-    <row r="138" spans="1:7" ht="45" customHeight="1">
+    <row r="138" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>210</v>
       </c>
@@ -6510,7 +6510,7 @@
       </c>
       <c r="G138" s="26"/>
     </row>
-    <row r="139" spans="1:7" ht="30" customHeight="1">
+    <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>210</v>
       </c>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="G139" s="26"/>
     </row>
-    <row r="140" spans="1:7" ht="30" customHeight="1">
+    <row r="140" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>210</v>
       </c>
@@ -6544,7 +6544,7 @@
       </c>
       <c r="G140" s="26"/>
     </row>
-    <row r="141" spans="1:7" ht="30" customHeight="1">
+    <row r="141" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>210</v>
       </c>
@@ -6561,7 +6561,7 @@
       </c>
       <c r="G141" s="26"/>
     </row>
-    <row r="142" spans="1:7" ht="30" customHeight="1">
+    <row r="142" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>210</v>
       </c>
@@ -6578,7 +6578,7 @@
       </c>
       <c r="G142" s="26"/>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>210</v>
       </c>
@@ -6595,7 +6595,7 @@
       </c>
       <c r="G143" s="26"/>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>210</v>
       </c>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="G144" s="26"/>
     </row>
-    <row r="145" spans="1:7" ht="30" customHeight="1">
+    <row r="145" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>210</v>
       </c>
@@ -6633,7 +6633,7 @@
       </c>
       <c r="G145" s="26"/>
     </row>
-    <row r="146" spans="1:7" ht="30" customHeight="1">
+    <row r="146" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>210</v>
       </c>
@@ -6650,7 +6650,7 @@
       </c>
       <c r="G146" s="26"/>
     </row>
-    <row r="147" spans="1:7" ht="30" customHeight="1">
+    <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>210</v>
       </c>
@@ -6669,7 +6669,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="148" spans="1:7" ht="30">
+    <row r="148" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>210</v>
       </c>
@@ -6686,7 +6686,7 @@
       </c>
       <c r="G148" s="26"/>
     </row>
-    <row r="149" spans="1:7" ht="60.75" customHeight="1" thickBot="1">
+    <row r="149" spans="1:7" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>210</v>
       </c>
@@ -6703,7 +6703,7 @@
       </c>
       <c r="G149" s="26"/>
     </row>
-    <row r="150" spans="1:7" ht="30" customHeight="1">
+    <row r="150" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="17" t="s">
         <v>210</v>
       </c>
@@ -6724,7 +6724,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="151" spans="1:7" ht="30" customHeight="1">
+    <row r="151" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>388</v>
       </c>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="G151" s="26"/>
     </row>
-    <row r="152" spans="1:7" ht="30" customHeight="1">
+    <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>388</v>
       </c>
@@ -6762,7 +6762,7 @@
       </c>
       <c r="G152" s="26"/>
     </row>
-    <row r="153" spans="1:7" ht="30" customHeight="1">
+    <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>388</v>
       </c>
@@ -6779,7 +6779,7 @@
       </c>
       <c r="G153" s="26"/>
     </row>
-    <row r="154" spans="1:7" ht="30">
+    <row r="154" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>388</v>
       </c>
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G154" s="26"/>
     </row>
-    <row r="155" spans="1:7" ht="30" customHeight="1">
+    <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>388</v>
       </c>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="G155" s="26"/>
     </row>
-    <row r="156" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="156" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
         <v>388</v>
       </c>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="G156" s="26"/>
     </row>
-    <row r="157" spans="1:7" ht="30">
+    <row r="157" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A157" s="17" t="s">
         <v>388</v>
       </c>
@@ -6847,7 +6847,7 @@
       </c>
       <c r="G157" s="28"/>
     </row>
-    <row r="158" spans="1:7" ht="30" customHeight="1">
+    <row r="158" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>405</v>
       </c>
@@ -6864,7 +6864,7 @@
       </c>
       <c r="G158" s="26"/>
     </row>
-    <row r="159" spans="1:7" ht="30" customHeight="1">
+    <row r="159" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>405</v>
       </c>
@@ -6881,7 +6881,7 @@
       </c>
       <c r="G159" s="26"/>
     </row>
-    <row r="160" spans="1:7" ht="30" customHeight="1">
+    <row r="160" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>405</v>
       </c>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="G160" s="26"/>
     </row>
-    <row r="161" spans="1:7" ht="30" customHeight="1">
+    <row r="161" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>405</v>
       </c>
@@ -6915,7 +6915,7 @@
       </c>
       <c r="G161" s="26"/>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>405</v>
       </c>
@@ -6934,7 +6934,7 @@
       </c>
       <c r="G162" s="26"/>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>405</v>
       </c>
@@ -6951,7 +6951,7 @@
       </c>
       <c r="G163" s="26"/>
     </row>
-    <row r="164" spans="1:7" ht="45" customHeight="1">
+    <row r="164" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>405</v>
       </c>
@@ -6968,7 +6968,7 @@
       </c>
       <c r="G164" s="26"/>
     </row>
-    <row r="165" spans="1:7" ht="45">
+    <row r="165" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>405</v>
       </c>
@@ -6987,7 +6987,7 @@
       </c>
       <c r="G165" s="26"/>
     </row>
-    <row r="166" spans="1:7" ht="30" customHeight="1">
+    <row r="166" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>405</v>
       </c>
@@ -7004,7 +7004,7 @@
       </c>
       <c r="G166" s="26"/>
     </row>
-    <row r="167" spans="1:7" ht="30">
+    <row r="167" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>405</v>
       </c>
@@ -7021,7 +7021,7 @@
       </c>
       <c r="G167" s="26"/>
     </row>
-    <row r="168" spans="1:7" ht="30" customHeight="1">
+    <row r="168" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>405</v>
       </c>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="G168" s="26"/>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>405</v>
       </c>
@@ -7057,7 +7057,7 @@
       </c>
       <c r="G169" s="26"/>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>405</v>
       </c>
@@ -7074,7 +7074,7 @@
       </c>
       <c r="G170" s="26"/>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>405</v>
       </c>
@@ -7091,7 +7091,7 @@
       </c>
       <c r="G171" s="26"/>
     </row>
-    <row r="172" spans="1:7" ht="30" customHeight="1">
+    <row r="172" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>405</v>
       </c>
@@ -7108,7 +7108,7 @@
       </c>
       <c r="G172" s="26"/>
     </row>
-    <row r="173" spans="1:7" ht="30">
+    <row r="173" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>405</v>
       </c>
@@ -7127,7 +7127,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="174" spans="1:7" ht="30" customHeight="1">
+    <row r="174" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>405</v>
       </c>
@@ -7144,7 +7144,7 @@
       </c>
       <c r="G174" s="26"/>
     </row>
-    <row r="175" spans="1:7" ht="30" customHeight="1">
+    <row r="175" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>405</v>
       </c>
@@ -7163,7 +7163,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="30" customHeight="1">
+    <row r="176" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>405</v>
       </c>
@@ -7182,7 +7182,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="177" spans="1:7" ht="45" customHeight="1">
+    <row r="177" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>405</v>
       </c>
@@ -7201,7 +7201,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="60" customHeight="1">
+    <row r="178" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>405</v>
       </c>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="G178" s="26"/>
     </row>
-    <row r="179" spans="1:7" ht="45" customHeight="1">
+    <row r="179" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>405</v>
       </c>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="G179" s="26"/>
     </row>
-    <row r="180" spans="1:7" ht="30" customHeight="1">
+    <row r="180" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>405</v>
       </c>
@@ -7256,7 +7256,7 @@
       </c>
       <c r="G180" s="26"/>
     </row>
-    <row r="181" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1">
+    <row r="181" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
         <v>405</v>
       </c>
@@ -7275,7 +7275,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="182" spans="1:7" ht="30" customHeight="1">
+    <row r="182" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="17" t="s">
         <v>405</v>
       </c>
@@ -7294,7 +7294,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="183" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
+    <row r="183" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>467</v>
       </c>
@@ -7313,7 +7313,7 @@
       </c>
       <c r="G183" s="26"/>
     </row>
-    <row r="184" spans="1:7" ht="30" customHeight="1">
+    <row r="184" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="17" t="s">
         <v>471</v>
       </c>
@@ -7332,7 +7332,7 @@
       </c>
       <c r="G184" s="26"/>
     </row>
-    <row r="185" spans="1:7" ht="30" customHeight="1">
+    <row r="185" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>475</v>
       </c>
@@ -7349,7 +7349,7 @@
       </c>
       <c r="G185" s="26"/>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>475</v>
       </c>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="G186" s="26"/>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>475</v>
       </c>
@@ -7383,7 +7383,7 @@
       </c>
       <c r="G187" s="26"/>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>475</v>
       </c>
@@ -7400,7 +7400,7 @@
       </c>
       <c r="G188" s="26"/>
     </row>
-    <row r="189" spans="1:7" ht="30" customHeight="1">
+    <row r="189" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>475</v>
       </c>
@@ -7417,7 +7417,7 @@
       </c>
       <c r="G189" s="26"/>
     </row>
-    <row r="190" spans="1:7" ht="30">
+    <row r="190" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>475</v>
       </c>
@@ -7436,7 +7436,7 @@
       </c>
       <c r="G190" s="26"/>
     </row>
-    <row r="191" spans="1:7" ht="30" customHeight="1">
+    <row r="191" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>475</v>
       </c>
@@ -7453,7 +7453,7 @@
       </c>
       <c r="G191" s="26"/>
     </row>
-    <row r="192" spans="1:7" ht="30">
+    <row r="192" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>475</v>
       </c>
@@ -7470,7 +7470,7 @@
       </c>
       <c r="G192" s="26"/>
     </row>
-    <row r="193" spans="1:7" ht="30" customHeight="1">
+    <row r="193" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>475</v>
       </c>
@@ -7487,7 +7487,7 @@
       </c>
       <c r="G193" s="26"/>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>475</v>
       </c>
@@ -7506,7 +7506,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="195" spans="1:7" ht="30" customHeight="1">
+    <row r="195" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>475</v>
       </c>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="G195" s="26"/>
     </row>
-    <row r="196" spans="1:7" ht="30" customHeight="1">
+    <row r="196" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>475</v>
       </c>
@@ -7540,7 +7540,7 @@
       </c>
       <c r="G196" s="26"/>
     </row>
-    <row r="197" spans="1:7" ht="30" customHeight="1">
+    <row r="197" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>475</v>
       </c>
@@ -7557,7 +7557,7 @@
       </c>
       <c r="G197" s="26"/>
     </row>
-    <row r="198" spans="1:7" ht="30" customHeight="1">
+    <row r="198" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>475</v>
       </c>
@@ -7574,7 +7574,7 @@
       </c>
       <c r="G198" s="26"/>
     </row>
-    <row r="199" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1">
+    <row r="199" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A199" s="2" t="s">
         <v>475</v>
       </c>
@@ -7591,7 +7591,7 @@
       </c>
       <c r="G199" s="26"/>
     </row>
-    <row r="200" spans="1:7" ht="30.75" thickBot="1">
+    <row r="200" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A200" s="17" t="s">
         <v>475</v>
       </c>
@@ -7608,15 +7608,15 @@
       </c>
       <c r="G200" s="26"/>
     </row>
-    <row r="201" spans="1:7" ht="30" customHeight="1">
+    <row r="201" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>510</v>
       </c>
       <c r="B201" t="s">
-        <v>1017</v>
+        <v>1014</v>
       </c>
       <c r="C201" t="s">
-        <v>1018</v>
+        <v>1015</v>
       </c>
       <c r="D201" s="7"/>
       <c r="E201" s="7"/>
@@ -7624,10 +7624,10 @@
         <v>20</v>
       </c>
       <c r="G201" s="26" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="202" spans="1:7" ht="30" customHeight="1">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="202" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>510</v>
       </c>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="G202" s="26"/>
     </row>
-    <row r="203" spans="1:7">
+    <row r="203" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>510</v>
       </c>
@@ -7661,7 +7661,7 @@
       </c>
       <c r="G203" s="26"/>
     </row>
-    <row r="204" spans="1:7" ht="45" customHeight="1">
+    <row r="204" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>510</v>
       </c>
@@ -7680,7 +7680,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="205" spans="1:7">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>510</v>
       </c>
@@ -7699,15 +7699,15 @@
       </c>
       <c r="G205" s="24"/>
     </row>
-    <row r="206" spans="1:7" ht="30" customHeight="1">
+    <row r="206" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>510</v>
       </c>
       <c r="B206" t="s">
-        <v>1000</v>
+        <v>997</v>
       </c>
       <c r="C206" t="s">
-        <v>1001</v>
+        <v>998</v>
       </c>
       <c r="D206" s="7"/>
       <c r="E206" s="7"/>
@@ -7715,10 +7715,10 @@
         <v>20</v>
       </c>
       <c r="G206" s="26" t="s">
-        <v>1002</v>
-      </c>
-    </row>
-    <row r="207" spans="1:7" ht="30" customHeight="1">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>510</v>
       </c>
@@ -7735,7 +7735,7 @@
       </c>
       <c r="G207" s="26"/>
     </row>
-    <row r="208" spans="1:7" ht="45">
+    <row r="208" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>510</v>
       </c>
@@ -7754,7 +7754,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="209" spans="1:7" ht="30" customHeight="1">
+    <row r="209" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>510</v>
       </c>
@@ -7773,7 +7773,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="210" spans="1:7" ht="30" customHeight="1">
+    <row r="210" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>510</v>
       </c>
@@ -7790,7 +7790,7 @@
       </c>
       <c r="G210" s="26"/>
     </row>
-    <row r="211" spans="1:7" ht="30" customHeight="1">
+    <row r="211" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>510</v>
       </c>
@@ -7807,7 +7807,7 @@
       </c>
       <c r="G211" s="26"/>
     </row>
-    <row r="212" spans="1:7" ht="30" customHeight="1">
+    <row r="212" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>510</v>
       </c>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="G212" s="26"/>
     </row>
-    <row r="213" spans="1:7" ht="30" customHeight="1">
+    <row r="213" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>510</v>
       </c>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="G213" s="26"/>
     </row>
-    <row r="214" spans="1:7" ht="30" customHeight="1">
+    <row r="214" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>510</v>
       </c>
@@ -7862,7 +7862,7 @@
       </c>
       <c r="G214" s="26"/>
     </row>
-    <row r="215" spans="1:7" ht="30" customHeight="1">
+    <row r="215" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>510</v>
       </c>
@@ -7881,7 +7881,7 @@
       </c>
       <c r="G215" s="26"/>
     </row>
-    <row r="216" spans="1:7" ht="30" customHeight="1">
+    <row r="216" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>510</v>
       </c>
@@ -7898,15 +7898,15 @@
       </c>
       <c r="G216" s="26"/>
     </row>
-    <row r="217" spans="1:7" ht="30" customHeight="1">
+    <row r="217" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>510</v>
       </c>
       <c r="B217" t="s">
-        <v>1020</v>
+        <v>1017</v>
       </c>
       <c r="C217" t="s">
-        <v>1021</v>
+        <v>1018</v>
       </c>
       <c r="D217" s="7"/>
       <c r="E217" s="7"/>
@@ -7914,10 +7914,10 @@
         <v>20</v>
       </c>
       <c r="G217" s="26" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="218" spans="1:7" ht="30" customHeight="1">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="218" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>510</v>
       </c>
@@ -7936,15 +7936,15 @@
         <v>549</v>
       </c>
     </row>
-    <row r="219" spans="1:7">
+    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>510</v>
       </c>
       <c r="B219" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="C219" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="D219" s="7"/>
       <c r="E219" s="7"/>
@@ -7952,18 +7952,18 @@
         <v>29</v>
       </c>
       <c r="G219" s="26" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>510</v>
       </c>
       <c r="B220" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C220" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="D220" s="7"/>
       <c r="E220" s="7"/>
@@ -7971,10 +7971,10 @@
         <v>29</v>
       </c>
       <c r="G220" s="26" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="221" spans="1:7">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>510</v>
       </c>
@@ -7991,15 +7991,15 @@
       </c>
       <c r="G221" s="26"/>
     </row>
-    <row r="222" spans="1:7" ht="30" customHeight="1">
+    <row r="222" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>510</v>
       </c>
       <c r="B222" t="s">
-        <v>1029</v>
+        <v>1026</v>
       </c>
       <c r="C222" t="s">
-        <v>1030</v>
+        <v>1027</v>
       </c>
       <c r="D222" s="7"/>
       <c r="E222" s="7"/>
@@ -8007,18 +8007,18 @@
         <v>20</v>
       </c>
       <c r="G222" s="26" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="223" spans="1:7" ht="30" customHeight="1">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="223" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>510</v>
       </c>
       <c r="B223" t="s">
-        <v>998</v>
+        <v>995</v>
       </c>
       <c r="C223" t="s">
-        <v>999</v>
+        <v>996</v>
       </c>
       <c r="D223" s="7"/>
       <c r="E223" s="7"/>
@@ -8026,10 +8026,10 @@
         <v>29</v>
       </c>
       <c r="G223" s="26" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" ht="30" customHeight="1">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>510</v>
       </c>
@@ -8048,7 +8048,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="225" spans="1:7">
+    <row r="225" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>510</v>
       </c>
@@ -8065,18 +8065,18 @@
       </c>
       <c r="G225" s="26"/>
     </row>
-    <row r="226" spans="1:7" ht="45" customHeight="1">
+    <row r="226" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>510</v>
       </c>
       <c r="B226" t="s">
-        <v>993</v>
+        <v>990</v>
       </c>
       <c r="C226" t="s">
-        <v>994</v>
+        <v>991</v>
       </c>
       <c r="D226" s="7" t="s">
-        <v>995</v>
+        <v>992</v>
       </c>
       <c r="E226" s="7"/>
       <c r="F226" t="s">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="G226" s="26"/>
     </row>
-    <row r="227" spans="1:7">
+    <row r="227" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>510</v>
       </c>
@@ -8101,7 +8101,7 @@
       </c>
       <c r="G227" s="26"/>
     </row>
-    <row r="228" spans="1:7" ht="45" customHeight="1">
+    <row r="228" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>510</v>
       </c>
@@ -8120,7 +8120,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="229" spans="1:7">
+    <row r="229" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>510</v>
       </c>
@@ -8139,7 +8139,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="230" spans="1:7" ht="45" customHeight="1">
+    <row r="230" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>510</v>
       </c>
@@ -8160,7 +8160,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="231" spans="1:7" ht="30" customHeight="1">
+    <row r="231" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="2" t="s">
         <v>510</v>
       </c>
@@ -8177,15 +8177,15 @@
       </c>
       <c r="G231" s="26"/>
     </row>
-    <row r="232" spans="1:7" ht="30" customHeight="1">
+    <row r="232" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B232" s="2" t="s">
-        <v>1032</v>
+        <v>1029</v>
       </c>
       <c r="C232" s="2" t="s">
-        <v>1033</v>
+        <v>1030</v>
       </c>
       <c r="D232" s="7"/>
       <c r="E232" s="7"/>
@@ -8193,18 +8193,18 @@
         <v>20</v>
       </c>
       <c r="G232" s="26" t="s">
-        <v>1034</v>
-      </c>
-    </row>
-    <row r="233" spans="1:7" ht="30" customHeight="1">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B233" s="2" t="s">
-        <v>1035</v>
+        <v>1032</v>
       </c>
       <c r="C233" s="2" t="s">
-        <v>1036</v>
+        <v>1033</v>
       </c>
       <c r="D233" s="7"/>
       <c r="E233" s="7"/>
@@ -8212,370 +8212,370 @@
         <v>29</v>
       </c>
       <c r="G233" s="26" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="234" spans="1:7" ht="30" customHeight="1">
+        <v>1058</v>
+      </c>
+    </row>
+    <row r="234" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>571</v>
+        <v>1055</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>572</v>
+        <v>1056</v>
       </c>
       <c r="D234" s="7"/>
       <c r="E234" s="7"/>
-      <c r="F234" s="4"/>
-      <c r="G234" s="26"/>
-    </row>
-    <row r="235" spans="1:7" ht="30" customHeight="1">
+      <c r="F234" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G234" s="26" t="s">
+        <v>1057</v>
+      </c>
+    </row>
+    <row r="235" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>996</v>
+        <v>571</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>997</v>
+        <v>572</v>
       </c>
       <c r="D235" s="7"/>
       <c r="E235" s="7"/>
       <c r="F235" s="4"/>
       <c r="G235" s="26"/>
     </row>
-    <row r="236" spans="1:7" ht="30" customHeight="1">
+    <row r="236" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>573</v>
+        <v>993</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>574</v>
+        <v>994</v>
       </c>
       <c r="D236" s="7"/>
       <c r="E236" s="7"/>
-      <c r="F236" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G236" s="24" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" ht="30" customHeight="1">
+      <c r="F236" s="4"/>
+      <c r="G236" s="26"/>
+    </row>
+    <row r="237" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>576</v>
+        <v>573</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>577</v>
+        <v>574</v>
       </c>
       <c r="D237" s="7"/>
       <c r="E237" s="7"/>
-      <c r="F237" s="5" t="s">
+      <c r="F237" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G237" s="26" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="30" customHeight="1">
+      <c r="G237" s="24" t="s">
+        <v>575</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>579</v>
+        <v>576</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>580</v>
+        <v>577</v>
       </c>
       <c r="D238" s="7"/>
       <c r="E238" s="7"/>
-      <c r="F238" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G238" s="26"/>
-    </row>
-    <row r="239" spans="1:7" ht="30" customHeight="1">
+      <c r="F238" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G238" s="26" t="s">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="239" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
       <c r="D239" s="7"/>
       <c r="E239" s="7"/>
       <c r="F239" s="14" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G239" s="26"/>
     </row>
-    <row r="240" spans="1:7" ht="30" customHeight="1">
+    <row r="240" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>583</v>
+        <v>581</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>584</v>
+        <v>582</v>
       </c>
       <c r="D240" s="7"/>
       <c r="E240" s="7"/>
-      <c r="F240" s="4" t="s">
-        <v>20</v>
+      <c r="F240" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="G240" s="26"/>
     </row>
-    <row r="241" spans="1:7" ht="30" customHeight="1">
+    <row r="241" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>585</v>
+        <v>583</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="D241" s="1"/>
+        <v>584</v>
+      </c>
+      <c r="D241" s="7"/>
       <c r="E241" s="7"/>
       <c r="F241" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G241" s="24" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="242" spans="1:7" ht="30" customHeight="1">
+        <v>20</v>
+      </c>
+      <c r="G241" s="26"/>
+    </row>
+    <row r="242" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="D242" s="7"/>
+        <v>586</v>
+      </c>
+      <c r="D242" s="1"/>
       <c r="E242" s="7"/>
-      <c r="F242" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G242" s="26"/>
-    </row>
-    <row r="243" spans="1:7" ht="30" customHeight="1">
+      <c r="F242" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G242" s="24" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="243" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D243" s="7"/>
       <c r="E243" s="7"/>
-      <c r="F243" s="4" t="s">
-        <v>96</v>
+      <c r="F243" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G243" s="26"/>
     </row>
-    <row r="244" spans="1:7" ht="30" customHeight="1">
+    <row r="244" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="D244" s="7"/>
       <c r="E244" s="7"/>
       <c r="F244" s="4" t="s">
-        <v>29</v>
+        <v>96</v>
       </c>
       <c r="G244" s="26"/>
     </row>
-    <row r="245" spans="1:7" ht="30" customHeight="1">
+    <row r="245" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="D245" s="7"/>
       <c r="E245" s="7"/>
-      <c r="F245" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G245" s="24"/>
-    </row>
-    <row r="246" spans="1:7" ht="30" customHeight="1">
+      <c r="F245" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G245" s="26"/>
+    </row>
+    <row r="246" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D246" s="7" t="s">
-        <v>598</v>
-      </c>
+        <v>595</v>
+      </c>
+      <c r="D246" s="7"/>
       <c r="E246" s="7"/>
-      <c r="F246" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G246" s="26" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="247" spans="1:7" ht="30" customHeight="1">
+      <c r="F246" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G246" s="24"/>
+    </row>
+    <row r="247" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>600</v>
+        <v>596</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D247" s="1"/>
+        <v>597</v>
+      </c>
+      <c r="D247" s="7" t="s">
+        <v>598</v>
+      </c>
       <c r="E247" s="7"/>
       <c r="F247" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G247" s="26" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A248" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B248" s="2" t="s">
+        <v>600</v>
+      </c>
+      <c r="C248" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="D248" s="1"/>
+      <c r="E248" s="7"/>
+      <c r="F248" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G247" s="26"/>
-    </row>
-    <row r="248" spans="1:7" ht="30" customHeight="1">
-      <c r="A248" t="s">
+      <c r="G248" s="26"/>
+    </row>
+    <row r="249" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A249" t="s">
         <v>510</v>
       </c>
-      <c r="B248" t="s">
+      <c r="B249" t="s">
         <v>602</v>
       </c>
-      <c r="C248" t="s">
+      <c r="C249" t="s">
         <v>603</v>
-      </c>
-      <c r="D248" s="7"/>
-      <c r="E248" s="7"/>
-      <c r="F248" t="s">
-        <v>29</v>
-      </c>
-      <c r="G248" s="26"/>
-    </row>
-    <row r="249" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
-      <c r="A249" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B249" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="C249" s="2" t="s">
-        <v>605</v>
       </c>
       <c r="D249" s="7"/>
       <c r="E249" s="7"/>
-      <c r="F249" s="4" t="s">
+      <c r="F249" t="s">
         <v>29</v>
       </c>
       <c r="G249" s="26"/>
     </row>
-    <row r="250" spans="1:7" ht="45">
+    <row r="250" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A250" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
       <c r="D250" s="7"/>
       <c r="E250" s="7"/>
-      <c r="F250" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="G250" s="24" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="251" spans="1:7" ht="30" customHeight="1">
-      <c r="A251" t="s">
+      <c r="F250" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G250" s="26"/>
+    </row>
+    <row r="251" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A251" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B251" t="s">
-        <v>609</v>
-      </c>
-      <c r="C251" t="s">
-        <v>610</v>
+      <c r="B251" s="2" t="s">
+        <v>606</v>
+      </c>
+      <c r="C251" s="2" t="s">
+        <v>607</v>
       </c>
       <c r="D251" s="7"/>
       <c r="E251" s="7"/>
-      <c r="F251" t="s">
+      <c r="F251" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="G251" s="24" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A252" t="s">
+        <v>510</v>
+      </c>
+      <c r="B252" t="s">
+        <v>609</v>
+      </c>
+      <c r="C252" t="s">
+        <v>610</v>
+      </c>
+      <c r="D252" s="7"/>
+      <c r="E252" s="7"/>
+      <c r="F252" t="s">
         <v>29</v>
       </c>
-      <c r="G251" s="26"/>
-    </row>
-    <row r="252" spans="1:7" ht="30">
-      <c r="A252" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B252" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C252" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D252" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="E252" s="7"/>
-      <c r="F252" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G252" s="24"/>
-    </row>
-    <row r="253" spans="1:7" ht="30">
+      <c r="G252" s="26"/>
+    </row>
+    <row r="253" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A253" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B253" s="2" t="s">
-        <v>1038</v>
+        <v>611</v>
       </c>
       <c r="C253" s="2" t="s">
-        <v>1039</v>
-      </c>
-      <c r="D253" s="1"/>
+        <v>612</v>
+      </c>
+      <c r="D253" s="1" t="s">
+        <v>613</v>
+      </c>
       <c r="E253" s="7"/>
-      <c r="F253" s="14" t="s">
+      <c r="F253" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G253" s="26" t="s">
-        <v>1040</v>
-      </c>
-    </row>
-    <row r="254" spans="1:7" ht="30">
+      <c r="G253" s="24"/>
+    </row>
+    <row r="254" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>1041</v>
+        <v>1034</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>1042</v>
+        <v>1035</v>
       </c>
       <c r="D254" s="1"/>
       <c r="E254" s="7"/>
@@ -8583,200 +8583,200 @@
         <v>29</v>
       </c>
       <c r="G254" s="26" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="255" spans="1:7">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>614</v>
+        <v>1037</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>615</v>
+        <v>1038</v>
       </c>
       <c r="D255" s="1"/>
       <c r="E255" s="7"/>
       <c r="F255" s="14" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G255" s="26" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A256" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B256" s="2" t="s">
-        <v>617</v>
+        <v>614</v>
       </c>
       <c r="C256" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D256" s="7"/>
+        <v>615</v>
+      </c>
+      <c r="D256" s="1"/>
       <c r="E256" s="7"/>
-      <c r="F256" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G256" s="26"/>
-    </row>
-    <row r="257" spans="1:7" ht="30">
+      <c r="F256" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G256" s="26" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A257" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D257" s="7"/>
       <c r="E257" s="7"/>
       <c r="F257" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G257" s="26" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" ht="30" customHeight="1">
+        <v>29</v>
+      </c>
+      <c r="G257" s="26"/>
+    </row>
+    <row r="258" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="D258" s="7" t="s">
-        <v>624</v>
-      </c>
+        <v>620</v>
+      </c>
+      <c r="D258" s="7"/>
       <c r="E258" s="7"/>
-      <c r="F258" s="5" t="s">
+      <c r="F258" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G258" s="26" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" ht="30" customHeight="1">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>626</v>
+        <v>622</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>627</v>
+        <v>623</v>
       </c>
       <c r="D259" s="7" t="s">
-        <v>628</v>
+        <v>624</v>
       </c>
       <c r="E259" s="7"/>
       <c r="F259" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G259" s="26" t="s">
+        <v>625</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A260" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B260" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="C260" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="D260" s="7" t="s">
+        <v>628</v>
+      </c>
+      <c r="E260" s="7"/>
+      <c r="F260" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="G259" s="26"/>
-    </row>
-    <row r="260" spans="1:7">
-      <c r="A260" t="s">
+      <c r="G260" s="26"/>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A261" t="s">
         <v>510</v>
       </c>
-      <c r="B260" t="s">
+      <c r="B261" t="s">
         <v>629</v>
       </c>
-      <c r="C260" t="s">
+      <c r="C261" t="s">
         <v>630</v>
-      </c>
-      <c r="D260" s="7"/>
-      <c r="E260" s="7"/>
-      <c r="F260" t="s">
-        <v>29</v>
-      </c>
-      <c r="G260" s="26"/>
-    </row>
-    <row r="261" spans="1:7" ht="30">
-      <c r="A261" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B261" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="C261" s="2" t="s">
-        <v>632</v>
       </c>
       <c r="D261" s="7"/>
       <c r="E261" s="7"/>
-      <c r="F261" s="4" t="s">
+      <c r="F261" t="s">
         <v>29</v>
       </c>
       <c r="G261" s="26"/>
     </row>
-    <row r="262" spans="1:7" ht="30" customHeight="1">
+    <row r="262" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D262" s="7"/>
       <c r="E262" s="7"/>
       <c r="F262" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G262" s="26"/>
     </row>
-    <row r="263" spans="1:7" ht="30" customHeight="1">
+    <row r="263" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="D263" s="7"/>
       <c r="E263" s="7"/>
-      <c r="F263" s="5" t="s">
+      <c r="F263" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G263" s="26"/>
     </row>
-    <row r="264" spans="1:7">
+    <row r="264" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="D264" s="7"/>
       <c r="E264" s="7"/>
       <c r="F264" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G264" s="26" t="s">
-        <v>639</v>
-      </c>
-    </row>
-    <row r="265" spans="1:7" ht="30">
+      <c r="G264" s="26"/>
+    </row>
+    <row r="265" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A265" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B265" s="2" t="s">
-        <v>640</v>
+        <v>637</v>
       </c>
       <c r="C265" s="2" t="s">
-        <v>641</v>
+        <v>638</v>
       </c>
       <c r="D265" s="7"/>
       <c r="E265" s="7"/>
@@ -8785,15 +8785,15 @@
       </c>
       <c r="G265" s="26"/>
     </row>
-    <row r="266" spans="1:7">
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A266" t="s">
         <v>510</v>
       </c>
       <c r="B266" t="s">
-        <v>642</v>
+        <v>639</v>
       </c>
       <c r="C266" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D266" s="7"/>
       <c r="E266" s="7"/>
@@ -8802,15 +8802,15 @@
       </c>
       <c r="G266" s="26"/>
     </row>
-    <row r="267" spans="1:7">
+    <row r="267" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A267" t="s">
         <v>510</v>
       </c>
       <c r="B267" t="s">
-        <v>644</v>
+        <v>641</v>
       </c>
       <c r="C267" t="s">
-        <v>645</v>
+        <v>642</v>
       </c>
       <c r="D267" s="7"/>
       <c r="E267" s="7"/>
@@ -8819,15 +8819,15 @@
       </c>
       <c r="G267" s="26"/>
     </row>
-    <row r="268" spans="1:7" ht="30" customHeight="1">
+    <row r="268" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" t="s">
         <v>510</v>
       </c>
       <c r="B268" t="s">
-        <v>646</v>
+        <v>643</v>
       </c>
       <c r="C268" t="s">
-        <v>647</v>
+        <v>644</v>
       </c>
       <c r="D268" s="7"/>
       <c r="E268" s="7"/>
@@ -8836,15 +8836,15 @@
       </c>
       <c r="G268" s="26"/>
     </row>
-    <row r="269" spans="1:7">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A269" t="s">
         <v>510</v>
       </c>
       <c r="B269" t="s">
-        <v>648</v>
+        <v>645</v>
       </c>
       <c r="C269" t="s">
-        <v>649</v>
+        <v>646</v>
       </c>
       <c r="D269" s="7"/>
       <c r="E269" s="7"/>
@@ -8853,15 +8853,15 @@
       </c>
       <c r="G269" s="26"/>
     </row>
-    <row r="270" spans="1:7">
+    <row r="270" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A270" t="s">
         <v>510</v>
       </c>
       <c r="B270" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="C270" t="s">
-        <v>651</v>
+        <v>648</v>
       </c>
       <c r="D270" s="7"/>
       <c r="E270" s="7"/>
@@ -8870,15 +8870,15 @@
       </c>
       <c r="G270" s="26"/>
     </row>
-    <row r="271" spans="1:7" ht="30" customHeight="1">
+    <row r="271" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>510</v>
       </c>
       <c r="B271" t="s">
-        <v>652</v>
+        <v>649</v>
       </c>
       <c r="C271" t="s">
-        <v>653</v>
+        <v>650</v>
       </c>
       <c r="D271" s="7"/>
       <c r="E271" s="7"/>
@@ -8887,15 +8887,15 @@
       </c>
       <c r="G271" s="26"/>
     </row>
-    <row r="272" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="272" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>510</v>
       </c>
       <c r="B272" t="s">
-        <v>654</v>
+        <v>651</v>
       </c>
       <c r="C272" t="s">
-        <v>655</v>
+        <v>652</v>
       </c>
       <c r="D272" s="7"/>
       <c r="E272" s="7"/>
@@ -8904,15 +8904,15 @@
       </c>
       <c r="G272" s="26"/>
     </row>
-    <row r="273" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="273" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>510</v>
       </c>
       <c r="B273" t="s">
-        <v>656</v>
+        <v>653</v>
       </c>
       <c r="C273" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D273" s="7"/>
       <c r="E273" s="7"/>
@@ -8920,18 +8920,18 @@
         <v>14</v>
       </c>
       <c r="G273" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="274" spans="1:7">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>510</v>
       </c>
       <c r="B274" t="s">
-        <v>659</v>
+        <v>656</v>
       </c>
       <c r="C274" t="s">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="D274" s="7"/>
       <c r="E274" s="7"/>
@@ -8939,18 +8939,18 @@
         <v>14</v>
       </c>
       <c r="G274" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B275" s="2" t="s">
-        <v>661</v>
+        <v>658</v>
       </c>
       <c r="C275" s="2" t="s">
-        <v>662</v>
+        <v>659</v>
       </c>
       <c r="D275" s="7"/>
       <c r="E275" s="7"/>
@@ -8958,18 +8958,18 @@
         <v>14</v>
       </c>
       <c r="G275" s="26" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" ht="30" customHeight="1">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B276" s="2" t="s">
-        <v>664</v>
+        <v>661</v>
       </c>
       <c r="C276" s="2" t="s">
-        <v>665</v>
+        <v>662</v>
       </c>
       <c r="D276" s="7"/>
       <c r="E276" s="7"/>
@@ -8977,18 +8977,18 @@
         <v>14</v>
       </c>
       <c r="G276" s="26" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="30" customHeight="1">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="17" t="s">
         <v>510</v>
       </c>
       <c r="B277" s="17" t="s">
-        <v>667</v>
+        <v>664</v>
       </c>
       <c r="C277" s="17" t="s">
-        <v>668</v>
+        <v>665</v>
       </c>
       <c r="D277" s="27"/>
       <c r="E277" s="27"/>
@@ -8996,18 +8996,18 @@
         <v>14</v>
       </c>
       <c r="G277" s="28" t="s">
-        <v>669</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A278" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B278" s="2" t="s">
-        <v>670</v>
+        <v>667</v>
       </c>
       <c r="C278" s="2" t="s">
-        <v>671</v>
+        <v>668</v>
       </c>
       <c r="D278" s="7"/>
       <c r="E278" s="7"/>
@@ -9015,18 +9015,18 @@
         <v>14</v>
       </c>
       <c r="G278" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A279" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="D279" s="1"/>
       <c r="E279" s="7"/>
@@ -9034,18 +9034,18 @@
         <v>14</v>
       </c>
       <c r="G279" s="26" t="s">
-        <v>658</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" ht="30" customHeight="1">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>675</v>
+        <v>672</v>
       </c>
       <c r="D280" s="1"/>
       <c r="E280" s="7"/>
@@ -9054,15 +9054,15 @@
       </c>
       <c r="G280" s="26"/>
     </row>
-    <row r="281" spans="1:7" ht="30" customHeight="1">
+    <row r="281" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B281" s="2" t="s">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="C281" s="2" t="s">
-        <v>677</v>
+        <v>674</v>
       </c>
       <c r="D281" s="7"/>
       <c r="E281" s="7"/>
@@ -9071,15 +9071,15 @@
       </c>
       <c r="G281" s="26"/>
     </row>
-    <row r="282" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="282" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A282" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>679</v>
+        <v>676</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>680</v>
+        <v>677</v>
       </c>
       <c r="D282" s="7"/>
       <c r="E282" s="7"/>
@@ -9088,18 +9088,18 @@
       </c>
       <c r="G282" s="26"/>
     </row>
-    <row r="283" spans="1:7" ht="30" customHeight="1">
+    <row r="283" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B283" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="B283" s="2" t="s">
-        <v>681</v>
-      </c>
       <c r="C283" s="2" t="s">
-        <v>682</v>
+        <v>679</v>
       </c>
       <c r="D283" s="7" t="s">
-        <v>683</v>
+        <v>680</v>
       </c>
       <c r="E283" s="7"/>
       <c r="F283" s="3" t="s">
@@ -9107,18 +9107,18 @@
       </c>
       <c r="G283" s="26"/>
     </row>
-    <row r="284" spans="1:7" ht="30" customHeight="1">
+    <row r="284" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>685</v>
+        <v>682</v>
       </c>
       <c r="D284" s="7" t="s">
-        <v>686</v>
+        <v>683</v>
       </c>
       <c r="E284" s="7"/>
       <c r="F284" s="3" t="s">
@@ -9126,15 +9126,15 @@
       </c>
       <c r="G284" s="26"/>
     </row>
-    <row r="285" spans="1:7" ht="30" customHeight="1">
+    <row r="285" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>687</v>
+        <v>684</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>688</v>
+        <v>685</v>
       </c>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
@@ -9143,15 +9143,15 @@
       </c>
       <c r="G285" s="26"/>
     </row>
-    <row r="286" spans="1:7" ht="30" customHeight="1">
+    <row r="286" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>689</v>
+        <v>686</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="D286" s="7"/>
       <c r="E286" s="7"/>
@@ -9160,15 +9160,15 @@
       </c>
       <c r="G286" s="26"/>
     </row>
-    <row r="287" spans="1:7" ht="15.75" customHeight="1" thickBot="1">
+    <row r="287" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A287" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>692</v>
+        <v>689</v>
       </c>
       <c r="D287" s="7"/>
       <c r="E287" s="7"/>
@@ -9177,15 +9177,15 @@
       </c>
       <c r="G287" s="26"/>
     </row>
-    <row r="288" spans="1:7">
+    <row r="288" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>694</v>
+        <v>691</v>
       </c>
       <c r="D288" s="7"/>
       <c r="E288" s="7"/>
@@ -9194,36 +9194,36 @@
       </c>
       <c r="G288" s="24"/>
     </row>
-    <row r="289" spans="1:7" ht="30">
+    <row r="289" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A289" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B289" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C289" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="D289" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="E289" s="7" t="s">
         <v>695</v>
-      </c>
-      <c r="C289" s="2" t="s">
-        <v>696</v>
-      </c>
-      <c r="D289" s="1" t="s">
-        <v>697</v>
-      </c>
-      <c r="E289" s="7" t="s">
-        <v>698</v>
       </c>
       <c r="F289" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G289" s="26"/>
     </row>
-    <row r="290" spans="1:7" ht="30" customHeight="1">
+    <row r="290" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D290" s="7"/>
       <c r="E290" s="7"/>
@@ -9232,15 +9232,15 @@
       </c>
       <c r="G290" s="24"/>
     </row>
-    <row r="291" spans="1:7" ht="30" customHeight="1">
+    <row r="291" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="D291" s="7"/>
       <c r="E291" s="1"/>
@@ -9249,15 +9249,15 @@
       </c>
       <c r="G291" s="26"/>
     </row>
-    <row r="292" spans="1:7" ht="30" customHeight="1">
+    <row r="292" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D292" s="7"/>
       <c r="E292" s="7"/>
@@ -9265,35 +9265,35 @@
         <v>14</v>
       </c>
       <c r="G292" s="26" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="293" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A293" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B293" s="2" t="s">
+        <v>702</v>
+      </c>
+      <c r="C293" s="2" t="s">
+        <v>703</v>
+      </c>
+      <c r="D293" s="7" t="s">
         <v>704</v>
-      </c>
-    </row>
-    <row r="293" spans="1:7" ht="30" customHeight="1">
-      <c r="A293" s="2" t="s">
-        <v>678</v>
-      </c>
-      <c r="B293" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="C293" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="D293" s="7" t="s">
-        <v>707</v>
       </c>
       <c r="E293" s="7"/>
       <c r="F293" s="5"/>
       <c r="G293" s="26"/>
     </row>
-    <row r="294" spans="1:7" ht="30" customHeight="1">
+    <row r="294" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="D294" s="7"/>
       <c r="E294" s="7"/>
@@ -9301,37 +9301,37 @@
         <v>25</v>
       </c>
       <c r="G294" s="26" t="s">
-        <v>710</v>
-      </c>
-    </row>
-    <row r="295" spans="1:7" ht="30" customHeight="1">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="295" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>711</v>
+        <v>708</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>712</v>
+        <v>709</v>
       </c>
       <c r="D295" s="7"/>
       <c r="E295" s="7" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="F295" s="5" t="s">
         <v>10</v>
       </c>
       <c r="G295" s="26"/>
     </row>
-    <row r="296" spans="1:7">
+    <row r="296" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A296" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>714</v>
+        <v>711</v>
       </c>
       <c r="D296" s="7"/>
       <c r="E296" s="7"/>
@@ -9340,15 +9340,15 @@
       </c>
       <c r="G296" s="26"/>
     </row>
-    <row r="297" spans="1:7">
+    <row r="297" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A297" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D297" s="7"/>
       <c r="E297" s="7"/>
@@ -9357,15 +9357,15 @@
       </c>
       <c r="G297" s="24"/>
     </row>
-    <row r="298" spans="1:7">
+    <row r="298" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A298" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="D298" s="7"/>
       <c r="E298" s="7"/>
@@ -9374,15 +9374,15 @@
       </c>
       <c r="G298" s="26"/>
     </row>
-    <row r="299" spans="1:7">
+    <row r="299" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A299" s="17" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B299" s="17" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
       <c r="C299" s="17" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D299" s="27"/>
       <c r="E299" s="27"/>
@@ -9391,15 +9391,15 @@
       </c>
       <c r="G299" s="28"/>
     </row>
-    <row r="300" spans="1:7" ht="30" customHeight="1">
+    <row r="300" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B300" s="2" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="C300" s="2" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="D300" s="7"/>
       <c r="E300" s="7"/>
@@ -9408,15 +9408,15 @@
       </c>
       <c r="G300" s="26"/>
     </row>
-    <row r="301" spans="1:7">
+    <row r="301" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A301" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D301" s="7"/>
       <c r="E301" s="1"/>
@@ -9424,18 +9424,18 @@
         <v>14</v>
       </c>
       <c r="G301" s="26" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="302" spans="1:7">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
       <c r="D302" s="7"/>
       <c r="E302" s="7"/>
@@ -9444,15 +9444,15 @@
       </c>
       <c r="G302" s="26"/>
     </row>
-    <row r="303" spans="1:7" ht="30" customHeight="1">
+    <row r="303" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="2" t="s">
-        <v>678</v>
+        <v>675</v>
       </c>
       <c r="B303" s="2" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="C303" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="D303" s="7"/>
       <c r="E303" s="7"/>
@@ -9461,15 +9461,15 @@
       </c>
       <c r="G303" s="24"/>
     </row>
-    <row r="304" spans="1:7">
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D304" s="7"/>
       <c r="E304" s="7"/>
@@ -9478,34 +9478,34 @@
       </c>
       <c r="G304" s="26"/>
     </row>
-    <row r="305" spans="1:7">
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B305" s="2" t="s">
         <v>730</v>
       </c>
-      <c r="B305" s="2" t="s">
-        <v>733</v>
-      </c>
       <c r="C305" s="2" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="D305" s="7"/>
       <c r="E305" s="7" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="F305" s="5" t="s">
         <v>37</v>
       </c>
       <c r="G305" s="26"/>
     </row>
-    <row r="306" spans="1:7" ht="30">
+    <row r="306" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A306" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="D306" s="7"/>
       <c r="E306" s="7"/>
@@ -9514,15 +9514,15 @@
       </c>
       <c r="G306" s="26"/>
     </row>
-    <row r="307" spans="1:7">
+    <row r="307" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
       <c r="D307" s="7"/>
       <c r="E307" s="7"/>
@@ -9530,18 +9530,18 @@
         <v>14</v>
       </c>
       <c r="G307" s="26" t="s">
-        <v>740</v>
-      </c>
-    </row>
-    <row r="308" spans="1:7">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="17" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B308" s="17" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="C308" s="17" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="D308" s="27"/>
       <c r="E308" s="27"/>
@@ -9550,15 +9550,15 @@
       </c>
       <c r="G308" s="28"/>
     </row>
-    <row r="309" spans="1:7" ht="30" customHeight="1">
+    <row r="309" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D309" s="7"/>
       <c r="E309" s="7"/>
@@ -9567,15 +9567,15 @@
       </c>
       <c r="G309" s="24"/>
     </row>
-    <row r="310" spans="1:7">
+    <row r="310" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="D310" s="7"/>
       <c r="E310" s="7"/>
@@ -9584,15 +9584,15 @@
       </c>
       <c r="G310" s="24"/>
     </row>
-    <row r="311" spans="1:7" ht="30">
+    <row r="311" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="D311" s="7"/>
       <c r="E311" s="7"/>
@@ -9601,15 +9601,15 @@
       </c>
       <c r="G311" s="24"/>
     </row>
-    <row r="312" spans="1:7" ht="30">
+    <row r="312" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A312" s="2" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="B312" s="2" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
       <c r="C312" s="2" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="D312" s="7"/>
       <c r="E312" s="7"/>
@@ -9618,15 +9618,15 @@
       </c>
       <c r="G312" s="24"/>
     </row>
-    <row r="313" spans="1:7" ht="30">
+    <row r="313" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A313" s="17" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B313" s="17" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="C313" s="17" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="D313" s="27"/>
       <c r="E313" s="27"/>
@@ -9634,18 +9634,18 @@
         <v>267</v>
       </c>
       <c r="G313" s="28" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="314" spans="1:7">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="D314" s="7"/>
       <c r="E314" s="7"/>
@@ -9653,18 +9653,18 @@
         <v>25</v>
       </c>
       <c r="G314" s="26" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="315" spans="1:7">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A315" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="D315" s="7"/>
       <c r="E315" s="7"/>
@@ -9672,18 +9672,18 @@
         <v>25</v>
       </c>
       <c r="G315" s="26" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7" ht="60" customHeight="1">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="316" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="D316" s="7"/>
       <c r="E316" s="7"/>
@@ -9691,18 +9691,18 @@
         <v>25</v>
       </c>
       <c r="G316" s="26" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="317" spans="1:7">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A317" s="2" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
       <c r="B317" s="2" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="C317" s="2" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="D317" s="7"/>
       <c r="E317" s="7"/>
@@ -9711,15 +9711,15 @@
       </c>
       <c r="G317" s="26"/>
     </row>
-    <row r="318" spans="1:7">
+    <row r="318" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="D318" s="7"/>
       <c r="E318" s="7"/>
@@ -9728,15 +9728,15 @@
       </c>
       <c r="G318" s="26"/>
     </row>
-    <row r="319" spans="1:7">
+    <row r="319" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>1003</v>
+        <v>1000</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>1004</v>
+        <v>1001</v>
       </c>
       <c r="D319" s="7"/>
       <c r="E319" s="7"/>
@@ -9745,15 +9745,15 @@
       </c>
       <c r="G319" s="26"/>
     </row>
-    <row r="320" spans="1:7">
+    <row r="320" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A320" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B320" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B320" s="2" t="s">
-        <v>768</v>
-      </c>
       <c r="C320" s="2" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="D320" s="7"/>
       <c r="E320" s="7"/>
@@ -9762,15 +9762,15 @@
       </c>
       <c r="G320" s="26"/>
     </row>
-    <row r="321" spans="1:7" ht="30" customHeight="1">
+    <row r="321" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="D321" s="7"/>
       <c r="E321" s="7"/>
@@ -9779,15 +9779,15 @@
       </c>
       <c r="G321" s="26"/>
     </row>
-    <row r="322" spans="1:7">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D322" s="7"/>
       <c r="E322" s="7"/>
@@ -9796,15 +9796,15 @@
       </c>
       <c r="G322" s="26"/>
     </row>
-    <row r="323" spans="1:7">
+    <row r="323" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="D323" s="7"/>
       <c r="E323" s="7"/>
@@ -9813,15 +9813,15 @@
       </c>
       <c r="G323" s="26"/>
     </row>
-    <row r="324" spans="1:7" ht="30" customHeight="1">
+    <row r="324" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D324" s="7"/>
       <c r="E324" s="7"/>
@@ -9830,15 +9830,15 @@
       </c>
       <c r="G324" s="26"/>
     </row>
-    <row r="325" spans="1:7" ht="60" customHeight="1">
+    <row r="325" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="D325" s="7"/>
       <c r="E325" s="7"/>
@@ -9847,15 +9847,15 @@
       </c>
       <c r="G325" s="26"/>
     </row>
-    <row r="326" spans="1:7">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D326" s="7"/>
       <c r="E326" s="1"/>
@@ -9864,15 +9864,15 @@
       </c>
       <c r="G326" s="26"/>
     </row>
-    <row r="327" spans="1:7">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="D327" s="7"/>
       <c r="E327" s="7"/>
@@ -9881,15 +9881,15 @@
       </c>
       <c r="G327" s="26"/>
     </row>
-    <row r="328" spans="1:7" ht="60" customHeight="1">
+    <row r="328" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D328" s="7"/>
       <c r="E328" s="7"/>
@@ -9898,15 +9898,15 @@
       </c>
       <c r="G328" s="26"/>
     </row>
-    <row r="329" spans="1:7" ht="60" customHeight="1">
+    <row r="329" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="D329" s="7"/>
       <c r="E329" s="7"/>
@@ -9915,15 +9915,15 @@
       </c>
       <c r="G329" s="26"/>
     </row>
-    <row r="330" spans="1:7">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
       <c r="D330" s="7"/>
       <c r="E330" s="7"/>
@@ -9931,18 +9931,18 @@
         <v>29</v>
       </c>
       <c r="G330" s="26" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="331" spans="1:7">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="331" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D331" s="7"/>
       <c r="E331" s="7"/>
@@ -9951,15 +9951,15 @@
       </c>
       <c r="G331" s="26"/>
     </row>
-    <row r="332" spans="1:7" ht="30" customHeight="1">
+    <row r="332" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="D332" s="7"/>
       <c r="E332" s="7"/>
@@ -9968,15 +9968,15 @@
       </c>
       <c r="G332" s="26"/>
     </row>
-    <row r="333" spans="1:7" ht="30" customHeight="1">
+    <row r="333" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D333" s="1"/>
       <c r="E333" s="7"/>
@@ -9985,15 +9985,15 @@
       </c>
       <c r="G333" s="26"/>
     </row>
-    <row r="334" spans="1:7" ht="60" customHeight="1">
+    <row r="334" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="D334" s="7"/>
       <c r="E334" s="7"/>
@@ -10002,15 +10002,15 @@
       </c>
       <c r="G334" s="26"/>
     </row>
-    <row r="335" spans="1:7">
+    <row r="335" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D335" s="7"/>
       <c r="E335" s="7"/>
@@ -10019,18 +10019,18 @@
       </c>
       <c r="G335" s="26"/>
     </row>
-    <row r="336" spans="1:7" ht="60" customHeight="1">
+    <row r="336" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="D336" s="7" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
       <c r="E336" s="7"/>
       <c r="F336" s="3" t="s">
@@ -10038,15 +10038,15 @@
       </c>
       <c r="G336" s="26"/>
     </row>
-    <row r="337" spans="1:7" ht="45" customHeight="1">
+    <row r="337" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="D337" s="7"/>
       <c r="E337" s="7"/>
@@ -10055,15 +10055,15 @@
       </c>
       <c r="G337" s="26"/>
     </row>
-    <row r="338" spans="1:7" ht="60" customHeight="1">
+    <row r="338" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
       <c r="D338" s="7"/>
       <c r="E338" s="7"/>
@@ -10072,15 +10072,15 @@
       </c>
       <c r="G338" s="26"/>
     </row>
-    <row r="339" spans="1:7">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="D339" s="7"/>
       <c r="E339" s="7"/>
@@ -10089,15 +10089,15 @@
       </c>
       <c r="G339" s="26"/>
     </row>
-    <row r="340" spans="1:7" ht="30" customHeight="1">
+    <row r="340" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
       <c r="D340" s="7"/>
       <c r="E340" s="7"/>
@@ -10106,15 +10106,15 @@
       </c>
       <c r="G340" s="26"/>
     </row>
-    <row r="341" spans="1:7" ht="30" customHeight="1">
+    <row r="341" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="D341" s="7"/>
       <c r="E341" s="7"/>
@@ -10123,15 +10123,15 @@
       </c>
       <c r="G341" s="24"/>
     </row>
-    <row r="342" spans="1:7">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
       <c r="D342" s="7"/>
       <c r="E342" s="7"/>
@@ -10140,15 +10140,15 @@
       </c>
       <c r="G342" s="26"/>
     </row>
-    <row r="343" spans="1:7" ht="60" customHeight="1">
+    <row r="343" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="D343" s="7"/>
       <c r="E343" s="7"/>
@@ -10157,15 +10157,15 @@
       </c>
       <c r="G343" s="26"/>
     </row>
-    <row r="344" spans="1:7">
+    <row r="344" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
       <c r="D344" s="7"/>
       <c r="E344" s="7"/>
@@ -10174,34 +10174,34 @@
       </c>
       <c r="G344" s="26"/>
     </row>
-    <row r="345" spans="1:7">
+    <row r="345" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="D345" s="7"/>
       <c r="E345" s="7"/>
       <c r="F345" s="4" t="s">
+        <v>816</v>
+      </c>
+      <c r="G345" s="26" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="346" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A346" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B346" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="C346" s="2" t="s">
         <v>819</v>
-      </c>
-      <c r="G345" s="26" t="s">
-        <v>820</v>
-      </c>
-    </row>
-    <row r="346" spans="1:7" ht="45" customHeight="1">
-      <c r="A346" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="B346" s="2" t="s">
-        <v>821</v>
-      </c>
-      <c r="C346" s="2" t="s">
-        <v>822</v>
       </c>
       <c r="D346" s="1"/>
       <c r="E346" s="7"/>
@@ -10210,15 +10210,15 @@
       </c>
       <c r="G346" s="26"/>
     </row>
-    <row r="347" spans="1:7">
+    <row r="347" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
       <c r="D347" s="7"/>
       <c r="E347" s="7"/>
@@ -10227,36 +10227,36 @@
       </c>
       <c r="G347" s="26"/>
     </row>
-    <row r="348" spans="1:7">
+    <row r="348" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="D348" s="7" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="E348" s="7"/>
       <c r="F348" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G348" s="26" t="s">
-        <v>1047</v>
-      </c>
-    </row>
-    <row r="349" spans="1:7">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="D349" s="7"/>
       <c r="E349" s="7"/>
@@ -10265,15 +10265,15 @@
       </c>
       <c r="G349" s="26"/>
     </row>
-    <row r="350" spans="1:7" ht="45" customHeight="1">
+    <row r="350" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
       <c r="D350" s="7"/>
       <c r="E350" s="7"/>
@@ -10282,18 +10282,18 @@
       </c>
       <c r="G350" s="26"/>
     </row>
-    <row r="351" spans="1:7" ht="45" customHeight="1">
+    <row r="351" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="D351" s="7" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="E351" s="7"/>
       <c r="F351" s="3" t="s">
@@ -10301,15 +10301,15 @@
       </c>
       <c r="G351" s="26"/>
     </row>
-    <row r="352" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+    <row r="352" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A352" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="D352" s="7"/>
       <c r="E352" s="7"/>
@@ -10318,15 +10318,15 @@
       </c>
       <c r="G352" s="26"/>
     </row>
-    <row r="353" spans="1:7" ht="45" customHeight="1">
+    <row r="353" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="D353" s="7"/>
       <c r="E353" s="7"/>
@@ -10335,15 +10335,15 @@
       </c>
       <c r="G353" s="26"/>
     </row>
-    <row r="354" spans="1:7" ht="30">
+    <row r="354" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D354" s="7"/>
       <c r="E354" s="7"/>
@@ -10352,15 +10352,15 @@
       </c>
       <c r="G354" s="24"/>
     </row>
-    <row r="355" spans="1:7" ht="30" customHeight="1">
+    <row r="355" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="D355" s="7"/>
       <c r="E355" s="7"/>
@@ -10369,15 +10369,15 @@
       </c>
       <c r="G355" s="24"/>
     </row>
-    <row r="356" spans="1:7" ht="30" customHeight="1">
+    <row r="356" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="D356" s="7"/>
       <c r="E356" s="7"/>
@@ -10386,15 +10386,15 @@
       </c>
       <c r="G356" s="24"/>
     </row>
-    <row r="357" spans="1:7">
+    <row r="357" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="D357" s="7"/>
       <c r="E357" s="1"/>
@@ -10403,15 +10403,15 @@
       </c>
       <c r="G357" s="26"/>
     </row>
-    <row r="358" spans="1:7">
+    <row r="358" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="D358" s="7"/>
       <c r="E358" s="7"/>
@@ -10419,18 +10419,18 @@
         <v>14</v>
       </c>
       <c r="G358" s="26" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="359" spans="1:7" ht="30.75" customHeight="1" thickBot="1">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
       <c r="D359" s="7"/>
       <c r="E359" s="7"/>
@@ -10438,18 +10438,18 @@
         <v>14</v>
       </c>
       <c r="G359" s="26" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A360" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B360" s="2" t="s">
         <v>846</v>
       </c>
-    </row>
-    <row r="360" spans="1:7" ht="45" customHeight="1">
-      <c r="A360" s="2" t="s">
-        <v>765</v>
-      </c>
-      <c r="B360" s="2" t="s">
-        <v>849</v>
-      </c>
       <c r="C360" s="2" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="D360" s="7"/>
       <c r="E360" s="7"/>
@@ -10457,18 +10457,18 @@
         <v>14</v>
       </c>
       <c r="G360" s="26" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="361" spans="1:7">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
       <c r="D361" s="7"/>
       <c r="E361" s="7"/>
@@ -10476,54 +10476,54 @@
         <v>29</v>
       </c>
       <c r="G361" s="26" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="362" spans="1:7" ht="30" customHeight="1">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="D362" s="7"/>
       <c r="E362" s="7" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
       <c r="F362" s="6" t="s">
         <v>29</v>
       </c>
       <c r="G362" s="24"/>
     </row>
-    <row r="363" spans="1:7" ht="45" customHeight="1">
+    <row r="363" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="D363" s="7"/>
       <c r="E363" s="7"/>
       <c r="F363" s="5" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="G363" s="26"/>
     </row>
-    <row r="364" spans="1:7" ht="45" customHeight="1">
+    <row r="364" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>1005</v>
+        <v>1002</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>1006</v>
+        <v>1003</v>
       </c>
       <c r="D364" s="7"/>
       <c r="E364" s="7"/>
@@ -10532,15 +10532,15 @@
       </c>
       <c r="G364" s="26"/>
     </row>
-    <row r="365" spans="1:7" ht="30">
+    <row r="365" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D365" s="7"/>
       <c r="E365" s="7"/>
@@ -10549,15 +10549,15 @@
       </c>
       <c r="G365" s="26"/>
     </row>
-    <row r="366" spans="1:7" ht="30" customHeight="1">
+    <row r="366" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="D366" s="7"/>
       <c r="E366" s="7"/>
@@ -10566,15 +10566,15 @@
       </c>
       <c r="G366" s="24"/>
     </row>
-    <row r="367" spans="1:7" ht="30" customHeight="1">
+    <row r="367" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D367" s="7"/>
       <c r="E367" s="7"/>
@@ -10582,18 +10582,18 @@
         <v>25</v>
       </c>
       <c r="G367" s="26" t="s">
-        <v>862</v>
-      </c>
-    </row>
-    <row r="368" spans="1:7">
+        <v>859</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
       <c r="D368" s="7"/>
       <c r="E368" s="7"/>
@@ -10602,15 +10602,15 @@
       </c>
       <c r="G368" s="26"/>
     </row>
-    <row r="369" spans="1:7">
+    <row r="369" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="D369" s="7"/>
       <c r="E369" s="7"/>
@@ -10619,15 +10619,15 @@
       </c>
       <c r="G369" s="26"/>
     </row>
-    <row r="370" spans="1:7" ht="30" customHeight="1">
+    <row r="370" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
       <c r="D370" s="7"/>
       <c r="E370" s="7"/>
@@ -10635,18 +10635,18 @@
         <v>14</v>
       </c>
       <c r="G370" s="26" t="s">
-        <v>869</v>
-      </c>
-    </row>
-    <row r="371" spans="1:7">
+        <v>866</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>870</v>
+        <v>867</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>871</v>
+        <v>868</v>
       </c>
       <c r="D371" s="7"/>
       <c r="E371" s="7"/>
@@ -10655,15 +10655,15 @@
       </c>
       <c r="G371" s="26"/>
     </row>
-    <row r="372" spans="1:7">
+    <row r="372" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A372" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B372" t="s">
-        <v>872</v>
+        <v>869</v>
       </c>
       <c r="C372" t="s">
-        <v>873</v>
+        <v>870</v>
       </c>
       <c r="D372" s="7"/>
       <c r="E372" s="7"/>
@@ -10672,15 +10672,15 @@
       </c>
       <c r="G372" s="26"/>
     </row>
-    <row r="373" spans="1:7">
+    <row r="373" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>874</v>
+        <v>871</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>875</v>
+        <v>872</v>
       </c>
       <c r="D373" s="7"/>
       <c r="E373" s="1"/>
@@ -10689,15 +10689,15 @@
       </c>
       <c r="G373" s="26"/>
     </row>
-    <row r="374" spans="1:7">
+    <row r="374" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>877</v>
+        <v>874</v>
       </c>
       <c r="D374" s="7"/>
       <c r="E374" s="7"/>
@@ -10706,34 +10706,34 @@
       </c>
       <c r="G374" s="26"/>
     </row>
-    <row r="375" spans="1:7">
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>1007</v>
+        <v>1004</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>1008</v>
+        <v>1005</v>
       </c>
       <c r="D375" s="7"/>
       <c r="E375" s="7" t="s">
-        <v>1009</v>
+        <v>1006</v>
       </c>
       <c r="F375" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G375" s="26"/>
     </row>
-    <row r="376" spans="1:7">
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A376" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B376" s="2" t="s">
-        <v>878</v>
+        <v>875</v>
       </c>
       <c r="C376" s="2" t="s">
-        <v>879</v>
+        <v>876</v>
       </c>
       <c r="D376" s="7"/>
       <c r="E376" s="7"/>
@@ -10742,34 +10742,34 @@
       </c>
       <c r="G376" s="26"/>
     </row>
-    <row r="377" spans="1:7">
+    <row r="377" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>880</v>
+        <v>877</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>881</v>
+        <v>878</v>
       </c>
       <c r="D377" s="7"/>
       <c r="E377" s="7" t="s">
-        <v>876</v>
+        <v>873</v>
       </c>
       <c r="F377" s="3" t="s">
         <v>20</v>
       </c>
       <c r="G377" s="24"/>
     </row>
-    <row r="378" spans="1:7">
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>882</v>
+        <v>879</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>883</v>
+        <v>880</v>
       </c>
       <c r="D378" s="7"/>
       <c r="E378" s="7"/>
@@ -10778,38 +10778,38 @@
       </c>
       <c r="G378" s="24"/>
     </row>
-    <row r="379" spans="1:7">
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A379" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
       <c r="D379" s="7" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
       <c r="E379" s="7" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="F379" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G379" s="26" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="380" spans="1:7" ht="15.75" thickBot="1">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="380" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A380" s="17" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B380" s="17" t="s">
-        <v>884</v>
+        <v>881</v>
       </c>
       <c r="C380" s="17" t="s">
-        <v>885</v>
+        <v>882</v>
       </c>
       <c r="D380" s="27"/>
       <c r="E380" s="27"/>
@@ -10818,15 +10818,15 @@
       </c>
       <c r="G380" s="28"/>
     </row>
-    <row r="381" spans="1:7">
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A381" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B381" s="2" t="s">
-        <v>886</v>
+        <v>883</v>
       </c>
       <c r="C381" s="2" t="s">
-        <v>887</v>
+        <v>884</v>
       </c>
       <c r="D381" s="1"/>
       <c r="E381" s="7"/>
@@ -10834,18 +10834,18 @@
         <v>10</v>
       </c>
       <c r="G381" s="26" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="382" spans="1:7">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A382" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>889</v>
+        <v>886</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>890</v>
+        <v>887</v>
       </c>
       <c r="D382" s="1"/>
       <c r="E382" s="7"/>
@@ -10853,18 +10853,18 @@
         <v>14</v>
       </c>
       <c r="G382" s="26" t="s">
-        <v>891</v>
-      </c>
-    </row>
-    <row r="383" spans="1:7" ht="30">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="383" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A383" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>893</v>
+        <v>890</v>
       </c>
       <c r="D383" s="1"/>
       <c r="E383" s="7"/>
@@ -10873,15 +10873,15 @@
       </c>
       <c r="G383" s="26"/>
     </row>
-    <row r="384" spans="1:7">
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A384" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B384" s="2" t="s">
-        <v>1010</v>
+        <v>1007</v>
       </c>
       <c r="C384" s="2" t="s">
-        <v>1011</v>
+        <v>1008</v>
       </c>
       <c r="D384" s="1"/>
       <c r="E384" s="7"/>
@@ -10890,34 +10890,34 @@
       </c>
       <c r="G384" s="26"/>
     </row>
-    <row r="385" spans="1:7">
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A385" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>1012</v>
+        <v>1009</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>1013</v>
+        <v>1010</v>
       </c>
       <c r="D385" s="1"/>
       <c r="E385" s="7" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
       <c r="F385" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G385" s="26"/>
     </row>
-    <row r="386" spans="1:7">
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A386" s="2" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>1014</v>
+        <v>1011</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>1015</v>
+        <v>1012</v>
       </c>
       <c r="D386" s="1"/>
       <c r="E386" s="7"/>
@@ -10926,18 +10926,18 @@
       </c>
       <c r="G386" s="26"/>
     </row>
-    <row r="387" spans="1:7">
+    <row r="387" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A387" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="B387" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="C387" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="D387" s="7" t="s">
         <v>894</v>
-      </c>
-      <c r="B387" s="2" t="s">
-        <v>895</v>
-      </c>
-      <c r="C387" s="2" t="s">
-        <v>896</v>
-      </c>
-      <c r="D387" s="7" t="s">
-        <v>897</v>
       </c>
       <c r="E387" s="7"/>
       <c r="F387" s="25" t="s">
@@ -10945,18 +10945,18 @@
       </c>
       <c r="G387" s="26"/>
     </row>
-    <row r="388" spans="1:7">
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A388" s="2" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>898</v>
+        <v>895</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>899</v>
+        <v>896</v>
       </c>
       <c r="D388" s="7" t="s">
-        <v>900</v>
+        <v>897</v>
       </c>
       <c r="E388" s="7"/>
       <c r="F388" s="4" t="s">
@@ -10964,18 +10964,18 @@
       </c>
       <c r="G388" s="26"/>
     </row>
-    <row r="389" spans="1:7" ht="30">
+    <row r="389" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>901</v>
+        <v>898</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>902</v>
+        <v>899</v>
       </c>
       <c r="D389" s="1" t="s">
-        <v>903</v>
+        <v>900</v>
       </c>
       <c r="E389" s="7"/>
       <c r="F389" s="4" t="s">
@@ -10983,32 +10983,32 @@
       </c>
       <c r="G389" s="26"/>
     </row>
-    <row r="390" spans="1:7" ht="30">
+    <row r="390" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A390" s="17" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B390" s="17" t="s">
-        <v>904</v>
+        <v>901</v>
       </c>
       <c r="C390" s="17" t="s">
-        <v>905</v>
+        <v>902</v>
       </c>
       <c r="D390" s="27"/>
       <c r="E390" s="27"/>
       <c r="F390" s="18" t="s">
-        <v>906</v>
+        <v>903</v>
       </c>
       <c r="G390" s="28"/>
     </row>
-    <row r="391" spans="1:7">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B391" t="s">
-        <v>907</v>
+        <v>904</v>
       </c>
       <c r="C391" t="s">
-        <v>908</v>
+        <v>905</v>
       </c>
       <c r="D391" s="7"/>
       <c r="E391" s="7"/>
@@ -11017,18 +11017,18 @@
       </c>
       <c r="G391" s="26"/>
     </row>
-    <row r="392" spans="1:7">
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A392" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B392" t="s">
-        <v>909</v>
+        <v>906</v>
       </c>
       <c r="C392" t="s">
-        <v>910</v>
+        <v>907</v>
       </c>
       <c r="D392" s="7" t="s">
-        <v>911</v>
+        <v>908</v>
       </c>
       <c r="E392" s="7"/>
       <c r="F392" t="s">
@@ -11036,18 +11036,18 @@
       </c>
       <c r="G392" s="26"/>
     </row>
-    <row r="393" spans="1:7">
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A393" t="s">
-        <v>894</v>
+        <v>891</v>
       </c>
       <c r="B393" t="s">
-        <v>912</v>
+        <v>909</v>
       </c>
       <c r="C393" t="s">
-        <v>913</v>
+        <v>910</v>
       </c>
       <c r="D393" s="7" t="s">
-        <v>914</v>
+        <v>911</v>
       </c>
       <c r="E393" s="7"/>
       <c r="F393" t="s">
@@ -11055,7 +11055,7 @@
       </c>
       <c r="G393" s="26"/>
     </row>
-    <row r="394" spans="1:7">
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
       <c r="D394" s="7"/>
       <c r="E394" s="7"/>
       <c r="G394" s="26"/>
@@ -11069,162 +11069,162 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.5703125" customWidth="1"/>
     <col min="2" max="2" width="52.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>141</v>
       </c>
       <c r="B6" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>196</v>
       </c>
       <c r="B8" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>210</v>
       </c>
       <c r="B9" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>388</v>
       </c>
       <c r="B10" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>405</v>
       </c>
       <c r="B11" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>467</v>
       </c>
       <c r="B12" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>475</v>
       </c>
       <c r="B13" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>510</v>
       </c>
       <c r="B14" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>675</v>
+      </c>
+      <c r="B15" t="s">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>727</v>
+      </c>
+      <c r="B16" t="s">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>747</v>
+      </c>
+      <c r="B17" t="s">
         <v>987</v>
       </c>
     </row>
-    <row r="15" spans="1:2">
-      <c r="A15" t="s">
-        <v>678</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>762</v>
+      </c>
+      <c r="B18" t="s">
         <v>988</v>
       </c>
     </row>
-    <row r="16" spans="1:2">
-      <c r="A16" t="s">
-        <v>730</v>
-      </c>
-      <c r="B16" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>891</v>
+      </c>
+      <c r="B19" t="s">
         <v>989</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" t="s">
-        <v>750</v>
-      </c>
-      <c r="B17" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" t="s">
-        <v>765</v>
-      </c>
-      <c r="B18" t="s">
-        <v>991</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" t="s">
-        <v>894</v>
-      </c>
-      <c r="B19" t="s">
-        <v>992</v>
       </c>
     </row>
   </sheetData>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\.claude\worktrees\retrofit-isic-split\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\.claude\worktrees\cement-carbonation\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1840F174-9800-4D9B-AAB9-151C7523B976}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3B9215-A8A4-47AE-B11A-5F9A9C0DE123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1854" uniqueCount="1062">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="1069">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -3208,6 +3208,27 @@
   </si>
   <si>
     <t>SoBCaICbIC, BRESaC</t>
+  </si>
+  <si>
+    <t>BICCUiT</t>
+  </si>
+  <si>
+    <t>Boolean Include Cement Carbonation Uptake in Totals</t>
+  </si>
+  <si>
+    <t>CCUP</t>
+  </si>
+  <si>
+    <t>Cement Carbonation Uptake Parameters</t>
+  </si>
+  <si>
+    <t>Carbonatable CO2 per Ton of Clinker by Pathway, Share of Cement by Use, In Service Uptake Share by Use, In Service Uptake Time by Use, End of Life Uptake Share by Use</t>
+  </si>
+  <si>
+    <t>HCCbV</t>
+  </si>
+  <si>
+    <t>Historical Clinker Consumed by Vintage</t>
   </si>
 </sst>
 </file>
@@ -4021,7 +4042,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G395"/>
+  <dimension ref="A1:G398"/>
   <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
@@ -5113,34 +5134,32 @@
         <v>157</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>158</v>
+        <v>1062</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>159</v>
+        <v>1063</v>
       </c>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
       <c r="F61" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="G61" s="24" t="s">
-        <v>160</v>
-      </c>
+      <c r="G61" s="24"/>
     </row>
     <row r="62" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="D62" s="7"/>
       <c r="E62" s="7"/>
@@ -5148,7 +5167,7 @@
         <v>144</v>
       </c>
       <c r="G62" s="24" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
     </row>
     <row r="63" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
@@ -5156,10 +5175,10 @@
         <v>141</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="D63" s="7"/>
       <c r="E63" s="7"/>
@@ -5167,18 +5186,18 @@
         <v>144</v>
       </c>
       <c r="G63" s="24" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="D64" s="7"/>
       <c r="E64" s="7"/>
@@ -5186,18 +5205,18 @@
         <v>144</v>
       </c>
       <c r="G64" s="24" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B65" s="2" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D65" s="7"/>
       <c r="E65" s="7"/>
@@ -5205,7 +5224,7 @@
         <v>144</v>
       </c>
       <c r="G65" s="24" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -5213,10 +5232,10 @@
         <v>141</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="D66" s="7"/>
       <c r="E66" s="7"/>
@@ -5224,18 +5243,18 @@
         <v>144</v>
       </c>
       <c r="G66" s="24" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B67" s="2" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D67" s="7"/>
       <c r="E67" s="7"/>
@@ -5243,147 +5262,149 @@
         <v>144</v>
       </c>
       <c r="G67" s="24" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B68" s="2" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="D68" s="7"/>
       <c r="E68" s="7"/>
-      <c r="F68" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G68" s="26"/>
-    </row>
-    <row r="69" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F68" s="6" t="s">
+        <v>144</v>
+      </c>
+      <c r="G68" s="24" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D69" s="7"/>
       <c r="E69" s="7"/>
-      <c r="F69" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G69" s="24" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F69" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G69" s="26"/>
+    </row>
+    <row r="70" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>185</v>
-      </c>
-      <c r="D70" s="1" t="s">
-        <v>186</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="D70" s="7"/>
       <c r="E70" s="7"/>
       <c r="F70" s="6" t="s">
         <v>144</v>
       </c>
       <c r="G70" s="24" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D71" s="7"/>
-      <c r="E71" s="1" t="s">
-        <v>190</v>
-      </c>
-      <c r="F71" s="16" t="s">
-        <v>14</v>
+        <v>185</v>
+      </c>
+      <c r="D71" s="1" t="s">
+        <v>186</v>
+      </c>
+      <c r="E71" s="7"/>
+      <c r="F71" s="6" t="s">
+        <v>144</v>
       </c>
       <c r="G71" s="24" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.35">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B72" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D72" s="7"/>
+      <c r="E72" s="1" t="s">
+        <v>190</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G72" s="24" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B73" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="C73" s="2" t="s">
         <v>193</v>
       </c>
-      <c r="D72" s="7"/>
-      <c r="E72" s="7"/>
-      <c r="F72" s="3" t="s">
+      <c r="D73" s="7"/>
+      <c r="E73" s="7"/>
+      <c r="F73" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G72" s="26"/>
-    </row>
-    <row r="73" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A73" s="17" t="s">
+      <c r="G73" s="26"/>
+    </row>
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A74" s="17" t="s">
         <v>141</v>
       </c>
-      <c r="B73" s="17" t="s">
+      <c r="B74" s="17" t="s">
         <v>194</v>
       </c>
-      <c r="C73" s="17" t="s">
+      <c r="C74" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="D73" s="27"/>
-      <c r="E73" s="27"/>
-      <c r="F73" s="19" t="s">
+      <c r="D74" s="27"/>
+      <c r="E74" s="27"/>
+      <c r="F74" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G73" s="28"/>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A74" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="B74" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="C74" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G74" s="26"/>
+      <c r="G74" s="28"/>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>196</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D75" s="7"/>
       <c r="E75" s="7"/>
@@ -5397,15 +5418,15 @@
         <v>196</v>
       </c>
       <c r="B76" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="D76" s="7"/>
       <c r="E76" s="7"/>
-      <c r="F76" s="5" t="s">
-        <v>20</v>
+      <c r="F76" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G76" s="26"/>
     </row>
@@ -5414,15 +5435,15 @@
         <v>196</v>
       </c>
       <c r="B77" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D77" s="7"/>
       <c r="E77" s="7"/>
-      <c r="F77" s="4" t="s">
-        <v>29</v>
+      <c r="F77" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G77" s="26"/>
     </row>
@@ -5431,10 +5452,10 @@
         <v>196</v>
       </c>
       <c r="B78" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D78" s="7"/>
       <c r="E78" s="7"/>
@@ -5443,51 +5464,51 @@
       </c>
       <c r="G78" s="26"/>
     </row>
-    <row r="79" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A79" s="17" t="s">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="B79" s="17" t="s">
+      <c r="B79" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G79" s="26"/>
+    </row>
+    <row r="80" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A80" s="17" t="s">
+        <v>196</v>
+      </c>
+      <c r="B80" s="17" t="s">
         <v>207</v>
       </c>
-      <c r="C79" s="17" t="s">
+      <c r="C80" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="D79" s="27"/>
-      <c r="E79" s="27"/>
-      <c r="F79" s="21" t="s">
+      <c r="D80" s="27"/>
+      <c r="E80" s="27"/>
+      <c r="F80" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G79" s="28" t="s">
+      <c r="G80" s="28" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A80" s="2" t="s">
-        <v>210</v>
-      </c>
-      <c r="B80" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G80" s="26"/>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D81" s="7"/>
       <c r="E81" s="7"/>
@@ -5496,94 +5517,92 @@
       </c>
       <c r="G81" s="26"/>
     </row>
-    <row r="82" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B82" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="D82" s="1" t="s">
-        <v>217</v>
-      </c>
+        <v>214</v>
+      </c>
+      <c r="D82" s="7"/>
       <c r="E82" s="7"/>
-      <c r="F82" s="5" t="s">
-        <v>20</v>
+      <c r="F82" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G82" s="26"/>
     </row>
-    <row r="83" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B83" s="2" t="s">
-        <v>218</v>
+        <v>215</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="D83" s="1" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="E83" s="7"/>
-      <c r="F83" s="4" t="s">
-        <v>29</v>
+      <c r="F83" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G83" s="26"/>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B84" s="2" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>222</v>
-      </c>
-      <c r="D84" s="7"/>
+        <v>219</v>
+      </c>
+      <c r="D84" s="1" t="s">
+        <v>220</v>
+      </c>
       <c r="E84" s="7"/>
-      <c r="F84" s="3" t="s">
-        <v>10</v>
+      <c r="F84" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G84" s="26"/>
     </row>
-    <row r="85" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B85" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="D85" s="7"/>
       <c r="E85" s="7"/>
-      <c r="F85" s="5" t="s">
-        <v>20</v>
+      <c r="F85" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G85" s="26"/>
     </row>
-    <row r="86" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B86" s="2" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>226</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>227</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="D86" s="7"/>
       <c r="E86" s="7"/>
-      <c r="F86" s="4" t="s">
-        <v>29</v>
+      <c r="F86" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G86" s="26"/>
     </row>
@@ -5592,84 +5611,84 @@
         <v>210</v>
       </c>
       <c r="B87" s="2" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>229</v>
-      </c>
-      <c r="D87" s="7"/>
+        <v>226</v>
+      </c>
+      <c r="D87" s="1" t="s">
+        <v>227</v>
+      </c>
       <c r="E87" s="7"/>
-      <c r="F87" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G87" s="24" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F87" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G87" s="26"/>
+    </row>
+    <row r="88" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B88" s="2" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>233</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="D88" s="7"/>
       <c r="E88" s="7"/>
-      <c r="F88" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="G88" s="26"/>
+      <c r="F88" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G88" s="24" t="s">
+        <v>230</v>
+      </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B89" s="2" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="D89" s="7"/>
+        <v>232</v>
+      </c>
+      <c r="D89" s="1" t="s">
+        <v>233</v>
+      </c>
       <c r="E89" s="7"/>
-      <c r="F89" s="3" t="s">
-        <v>10</v>
+      <c r="F89" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="G89" s="26"/>
     </row>
-    <row r="90" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B90" s="2" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D90" s="7"/>
       <c r="E90" s="7"/>
-      <c r="F90" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G90" s="24" t="s">
-        <v>238</v>
-      </c>
+      <c r="F90" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G90" s="26"/>
     </row>
     <row r="91" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B91" s="2" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D91" s="7"/>
       <c r="E91" s="7"/>
@@ -5677,76 +5696,74 @@
         <v>14</v>
       </c>
       <c r="G91" s="24" t="s">
-        <v>241</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.35">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B92" s="2" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D92" s="7"/>
       <c r="E92" s="7"/>
-      <c r="F92" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G92" s="26"/>
+      <c r="F92" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G92" s="24" t="s">
+        <v>241</v>
+      </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B93" s="2" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="C93" s="2" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="D93" s="7"/>
       <c r="E93" s="7"/>
-      <c r="F93" s="5" t="s">
-        <v>20</v>
+      <c r="F93" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G93" s="26"/>
     </row>
-    <row r="94" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B94" s="2" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C94" s="2" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="D94" s="7"/>
       <c r="E94" s="7"/>
-      <c r="F94" s="3" t="s">
-        <v>10</v>
+      <c r="F94" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G94" s="26"/>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B95" s="2" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="C95" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="D95" s="1" t="s">
-        <v>250</v>
-      </c>
-      <c r="E95" s="1" t="s">
-        <v>251</v>
-      </c>
+        <v>247</v>
+      </c>
+      <c r="D95" s="7"/>
+      <c r="E95" s="7"/>
       <c r="F95" s="3" t="s">
         <v>10</v>
       </c>
@@ -5757,27 +5774,31 @@
         <v>210</v>
       </c>
       <c r="B96" s="2" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C96" s="2" t="s">
-        <v>253</v>
-      </c>
-      <c r="D96" s="7"/>
-      <c r="E96" s="7"/>
+        <v>249</v>
+      </c>
+      <c r="D96" s="1" t="s">
+        <v>250</v>
+      </c>
+      <c r="E96" s="1" t="s">
+        <v>251</v>
+      </c>
       <c r="F96" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G96" s="26"/>
     </row>
-    <row r="97" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B97" s="2" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="C97" s="2" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="D97" s="7"/>
       <c r="E97" s="7"/>
@@ -5786,15 +5807,15 @@
       </c>
       <c r="G97" s="26"/>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B98" s="2" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="C98" s="2" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="D98" s="7"/>
       <c r="E98" s="7"/>
@@ -5808,140 +5829,140 @@
         <v>210</v>
       </c>
       <c r="B99" s="2" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="C99" s="2" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="D99" s="7"/>
       <c r="E99" s="7"/>
-      <c r="F99" s="5" t="s">
-        <v>20</v>
+      <c r="F99" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G99" s="26"/>
     </row>
-    <row r="100" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B100" s="2" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C100" s="2" t="s">
-        <v>261</v>
-      </c>
-      <c r="D100" s="1" t="s">
-        <v>262</v>
-      </c>
+        <v>259</v>
+      </c>
+      <c r="D100" s="7"/>
       <c r="E100" s="7"/>
       <c r="F100" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G100" s="26"/>
     </row>
-    <row r="101" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B101" s="2" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="C101" s="2" t="s">
-        <v>264</v>
-      </c>
-      <c r="D101" s="7"/>
+        <v>261</v>
+      </c>
+      <c r="D101" s="1" t="s">
+        <v>262</v>
+      </c>
       <c r="E101" s="7"/>
       <c r="F101" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G101" s="26"/>
     </row>
-    <row r="102" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B102" s="2" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="C102" s="2" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D102" s="7"/>
       <c r="E102" s="7"/>
-      <c r="F102" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="G102" s="24" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F102" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G102" s="26"/>
+    </row>
+    <row r="103" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B103" s="2" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="C103" s="2" t="s">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="D103" s="7"/>
       <c r="E103" s="7"/>
-      <c r="F103" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G103" s="26"/>
-    </row>
-    <row r="104" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F103" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G103" s="24" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B104" s="2" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C104" s="2" t="s">
-        <v>272</v>
-      </c>
-      <c r="D104" s="1" t="s">
-        <v>273</v>
-      </c>
+        <v>270</v>
+      </c>
+      <c r="D104" s="7"/>
       <c r="E104" s="7"/>
       <c r="F104" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G104" s="26"/>
     </row>
-    <row r="105" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B105" s="2" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="C105" s="2" t="s">
-        <v>275</v>
-      </c>
-      <c r="D105" s="7"/>
+        <v>272</v>
+      </c>
+      <c r="D105" s="1" t="s">
+        <v>273</v>
+      </c>
       <c r="E105" s="7"/>
       <c r="F105" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G105" s="26"/>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B106" s="2" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="C106" s="2" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="D106" s="7"/>
       <c r="E106" s="7"/>
-      <c r="F106" s="4" t="s">
-        <v>29</v>
+      <c r="F106" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G106" s="26"/>
     </row>
@@ -5950,10 +5971,10 @@
         <v>210</v>
       </c>
       <c r="B107" s="2" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="C107" s="2" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="D107" s="7"/>
       <c r="E107" s="7"/>
@@ -5962,22 +5983,20 @@
       </c>
       <c r="G107" s="26"/>
     </row>
-    <row r="108" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B108" s="2" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C108" s="2" t="s">
-        <v>281</v>
-      </c>
-      <c r="D108" s="1" t="s">
-        <v>282</v>
-      </c>
+        <v>279</v>
+      </c>
+      <c r="D108" s="7"/>
       <c r="E108" s="7"/>
-      <c r="F108" s="3" t="s">
-        <v>10</v>
+      <c r="F108" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G108" s="26"/>
     </row>
@@ -5986,17 +6005,17 @@
         <v>210</v>
       </c>
       <c r="B109" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="C109" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="E109" s="7"/>
-      <c r="F109" s="4" t="s">
-        <v>29</v>
+      <c r="F109" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G109" s="26"/>
     </row>
@@ -6005,36 +6024,36 @@
         <v>210</v>
       </c>
       <c r="B110" s="2" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="E110" s="7"/>
-      <c r="F110" s="3" t="s">
-        <v>10</v>
+      <c r="F110" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G110" s="26"/>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B111" s="2" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="C111" s="2" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="E111" s="7"/>
-      <c r="F111" s="4" t="s">
-        <v>29</v>
+      <c r="F111" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G111" s="26"/>
     </row>
@@ -6043,15 +6062,17 @@
         <v>210</v>
       </c>
       <c r="B112" s="2" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="C112" s="2" t="s">
-        <v>293</v>
-      </c>
-      <c r="D112" s="7"/>
+        <v>290</v>
+      </c>
+      <c r="D112" s="1" t="s">
+        <v>291</v>
+      </c>
       <c r="E112" s="7"/>
-      <c r="F112" s="5" t="s">
-        <v>20</v>
+      <c r="F112" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G112" s="26"/>
     </row>
@@ -6060,15 +6081,15 @@
         <v>210</v>
       </c>
       <c r="B113" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="C113" s="2" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="D113" s="7"/>
       <c r="E113" s="7"/>
-      <c r="F113" s="3" t="s">
-        <v>10</v>
+      <c r="F113" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G113" s="26"/>
     </row>
@@ -6077,118 +6098,118 @@
         <v>210</v>
       </c>
       <c r="B114" s="2" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="C114" s="2" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="D114" s="7"/>
       <c r="E114" s="7"/>
-      <c r="F114" s="5" t="s">
-        <v>20</v>
+      <c r="F114" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G114" s="26"/>
     </row>
-    <row r="115" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B115" s="2" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="C115" s="2" t="s">
-        <v>299</v>
-      </c>
-      <c r="D115" s="1" t="s">
-        <v>300</v>
-      </c>
+        <v>297</v>
+      </c>
+      <c r="D115" s="7"/>
       <c r="E115" s="7"/>
-      <c r="F115" s="3" t="s">
-        <v>10</v>
+      <c r="F115" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G115" s="26"/>
     </row>
-    <row r="116" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B116" s="2" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C116" s="2" t="s">
-        <v>302</v>
-      </c>
-      <c r="D116" s="7"/>
+        <v>299</v>
+      </c>
+      <c r="D116" s="1" t="s">
+        <v>300</v>
+      </c>
       <c r="E116" s="7"/>
-      <c r="F116" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="G116" s="24" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F116" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G116" s="26"/>
+    </row>
+    <row r="117" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B117" s="2" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
       <c r="C117" s="2" t="s">
-        <v>305</v>
+        <v>302</v>
       </c>
       <c r="D117" s="7"/>
       <c r="E117" s="7"/>
-      <c r="F117" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G117" s="26"/>
+      <c r="F117" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G117" s="24" t="s">
+        <v>303</v>
+      </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B118" s="2" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="C118" s="2" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="D118" s="7"/>
       <c r="E118" s="7"/>
       <c r="F118" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G118" s="26" t="s">
-        <v>308</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G118" s="26"/>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B119" s="2" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="C119" s="2" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="D119" s="7"/>
       <c r="E119" s="7"/>
-      <c r="F119" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G119" s="26"/>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F119" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G119" s="26" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B120" s="2" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="C120" s="2" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D120" s="7"/>
       <c r="E120" s="7"/>
@@ -6197,15 +6218,15 @@
       </c>
       <c r="G120" s="26"/>
     </row>
-    <row r="121" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B121" s="2" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C121" s="2" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="D121" s="7"/>
       <c r="E121" s="7"/>
@@ -6214,20 +6235,20 @@
       </c>
       <c r="G121" s="26"/>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B122" s="2" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C122" s="2" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="D122" s="7"/>
       <c r="E122" s="7"/>
-      <c r="F122" s="3" t="s">
-        <v>10</v>
+      <c r="F122" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G122" s="26"/>
     </row>
@@ -6236,10 +6257,10 @@
         <v>210</v>
       </c>
       <c r="B123" s="2" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="C123" s="2" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="D123" s="7"/>
       <c r="E123" s="7"/>
@@ -6253,15 +6274,15 @@
         <v>210</v>
       </c>
       <c r="B124" s="2" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="C124" s="2" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="D124" s="7"/>
       <c r="E124" s="7"/>
-      <c r="F124" s="4" t="s">
-        <v>29</v>
+      <c r="F124" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G124" s="26"/>
     </row>
@@ -6270,10 +6291,10 @@
         <v>210</v>
       </c>
       <c r="B125" s="2" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="C125" s="2" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="D125" s="7"/>
       <c r="E125" s="7"/>
@@ -6287,15 +6308,15 @@
         <v>210</v>
       </c>
       <c r="B126" s="2" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="C126" s="2" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="D126" s="7"/>
       <c r="E126" s="7"/>
-      <c r="F126" s="3" t="s">
-        <v>10</v>
+      <c r="F126" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G126" s="26"/>
     </row>
@@ -6304,15 +6325,15 @@
         <v>210</v>
       </c>
       <c r="B127" s="2" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="C127" s="2" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="D127" s="7"/>
       <c r="E127" s="7"/>
-      <c r="F127" s="4" t="s">
-        <v>29</v>
+      <c r="F127" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G127" s="26"/>
     </row>
@@ -6321,46 +6342,44 @@
         <v>210</v>
       </c>
       <c r="B128" s="2" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="C128" s="2" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="D128" s="7"/>
       <c r="E128" s="7"/>
-      <c r="F128" s="5" t="s">
-        <v>20</v>
+      <c r="F128" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G128" s="26"/>
     </row>
-    <row r="129" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B129" s="2" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="C129" s="2" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="D129" s="7"/>
       <c r="E129" s="7"/>
-      <c r="F129" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="G129" s="24" t="s">
-        <v>331</v>
-      </c>
+      <c r="F129" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G129" s="26"/>
     </row>
     <row r="130" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B130" s="2" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="C130" s="2" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="D130" s="7"/>
       <c r="E130" s="7"/>
@@ -6368,73 +6387,75 @@
         <v>267</v>
       </c>
       <c r="G130" s="24" t="s">
-        <v>334</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B131" s="2" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="C131" s="2" t="s">
-        <v>336</v>
-      </c>
-      <c r="D131" s="1" t="s">
-        <v>337</v>
-      </c>
+        <v>333</v>
+      </c>
+      <c r="D131" s="7"/>
       <c r="E131" s="7"/>
-      <c r="F131" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G131" s="26"/>
-    </row>
-    <row r="132" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F131" s="6" t="s">
+        <v>267</v>
+      </c>
+      <c r="G131" s="24" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B132" s="2" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="C132" s="2" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
       <c r="E132" s="7"/>
-      <c r="F132" s="14" t="s">
-        <v>96</v>
+      <c r="F132" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G132" s="26"/>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B133" s="2" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="C133" s="2" t="s">
-        <v>342</v>
-      </c>
-      <c r="D133" s="7"/>
+        <v>339</v>
+      </c>
+      <c r="D133" s="1" t="s">
+        <v>340</v>
+      </c>
       <c r="E133" s="7"/>
-      <c r="F133" s="4" t="s">
-        <v>29</v>
+      <c r="F133" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="G133" s="26"/>
     </row>
-    <row r="134" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B134" s="2" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="C134" s="2" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="D134" s="7"/>
       <c r="E134" s="7"/>
@@ -6448,57 +6469,53 @@
         <v>210</v>
       </c>
       <c r="B135" s="2" t="s">
-        <v>251</v>
+        <v>343</v>
       </c>
       <c r="C135" s="2" t="s">
-        <v>345</v>
-      </c>
-      <c r="D135" s="1" t="s">
-        <v>346</v>
-      </c>
+        <v>344</v>
+      </c>
+      <c r="D135" s="7"/>
       <c r="E135" s="7"/>
-      <c r="F135" s="5" t="s">
-        <v>347</v>
+      <c r="F135" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G135" s="26"/>
     </row>
-    <row r="136" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B136" s="2" t="s">
-        <v>348</v>
+        <v>251</v>
       </c>
       <c r="C136" s="2" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E136" s="7"/>
       <c r="F136" s="5" t="s">
-        <v>20</v>
+        <v>347</v>
       </c>
       <c r="G136" s="26"/>
     </row>
-    <row r="137" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B137" s="2" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>353</v>
-      </c>
-      <c r="E137" s="1" t="s">
-        <v>354</v>
-      </c>
-      <c r="F137" s="3" t="s">
-        <v>10</v>
+        <v>350</v>
+      </c>
+      <c r="E137" s="7"/>
+      <c r="F137" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G137" s="26"/>
     </row>
@@ -6507,51 +6524,55 @@
         <v>210</v>
       </c>
       <c r="B138" s="2" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
       <c r="C138" s="2" t="s">
-        <v>356</v>
-      </c>
-      <c r="D138" s="7"/>
-      <c r="E138" s="7"/>
-      <c r="F138" s="14" t="s">
-        <v>96</v>
+        <v>352</v>
+      </c>
+      <c r="D138" s="1" t="s">
+        <v>353</v>
+      </c>
+      <c r="E138" s="1" t="s">
+        <v>354</v>
+      </c>
+      <c r="F138" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G138" s="26"/>
     </row>
-    <row r="139" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B139" s="2" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>358</v>
-      </c>
-      <c r="D139" s="1" t="s">
-        <v>359</v>
-      </c>
+        <v>356</v>
+      </c>
+      <c r="D139" s="7"/>
       <c r="E139" s="7"/>
-      <c r="F139" s="4" t="s">
-        <v>29</v>
+      <c r="F139" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="G139" s="26"/>
     </row>
-    <row r="140" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B140" s="2" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C140" s="2" t="s">
-        <v>361</v>
-      </c>
-      <c r="D140" s="7"/>
+        <v>358</v>
+      </c>
+      <c r="D140" s="1" t="s">
+        <v>359</v>
+      </c>
       <c r="E140" s="7"/>
-      <c r="F140" s="14" t="s">
-        <v>96</v>
+      <c r="F140" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G140" s="26"/>
     </row>
@@ -6560,15 +6581,15 @@
         <v>210</v>
       </c>
       <c r="B141" s="2" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="C141" s="2" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="D141" s="7"/>
       <c r="E141" s="7"/>
-      <c r="F141" s="4" t="s">
-        <v>29</v>
+      <c r="F141" s="14" t="s">
+        <v>96</v>
       </c>
       <c r="G141" s="26"/>
     </row>
@@ -6577,10 +6598,10 @@
         <v>210</v>
       </c>
       <c r="B142" s="2" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C142" s="2" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D142" s="7"/>
       <c r="E142" s="7"/>
@@ -6594,10 +6615,10 @@
         <v>210</v>
       </c>
       <c r="B143" s="2" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C143" s="2" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D143" s="7"/>
       <c r="E143" s="7"/>
@@ -6606,20 +6627,20 @@
       </c>
       <c r="G143" s="26"/>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B144" s="2" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="C144" s="2" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="D144" s="7"/>
       <c r="E144" s="7"/>
-      <c r="F144" s="3" t="s">
-        <v>10</v>
+      <c r="F144" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G144" s="26"/>
     </row>
@@ -6628,34 +6649,32 @@
         <v>210</v>
       </c>
       <c r="B145" s="2" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="C145" s="2" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D145" s="7"/>
-      <c r="E145" s="1" t="s">
-        <v>319</v>
-      </c>
+      <c r="E145" s="7"/>
       <c r="F145" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G145" s="26"/>
     </row>
-    <row r="146" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B146" s="2" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="C146" s="2" t="s">
-        <v>373</v>
-      </c>
-      <c r="D146" s="1" t="s">
-        <v>374</v>
-      </c>
-      <c r="E146" s="7"/>
+        <v>371</v>
+      </c>
+      <c r="D146" s="7"/>
+      <c r="E146" s="1" t="s">
+        <v>319</v>
+      </c>
       <c r="F146" s="3" t="s">
         <v>10</v>
       </c>
@@ -6666,63 +6685,65 @@
         <v>210</v>
       </c>
       <c r="B147" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="C147" s="2" t="s">
+        <v>373</v>
+      </c>
+      <c r="D147" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="E147" s="7"/>
+      <c r="F147" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G147" s="26"/>
+    </row>
+    <row r="148" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A148" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="B148" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="C147" s="2" t="s">
+      <c r="C148" s="2" t="s">
         <v>376</v>
-      </c>
-      <c r="D147" s="7"/>
-      <c r="E147" s="7"/>
-      <c r="F147" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G147" s="26"/>
-    </row>
-    <row r="148" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A148" t="s">
-        <v>210</v>
-      </c>
-      <c r="B148" t="s">
-        <v>377</v>
-      </c>
-      <c r="C148" t="s">
-        <v>378</v>
       </c>
       <c r="D148" s="7"/>
       <c r="E148" s="7"/>
-      <c r="F148" t="s">
-        <v>14</v>
-      </c>
-      <c r="G148" s="26" t="s">
-        <v>379</v>
-      </c>
-    </row>
-    <row r="149" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A149" s="2" t="s">
+      <c r="F148" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G148" s="26"/>
+    </row>
+    <row r="149" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A149" t="s">
         <v>210</v>
       </c>
-      <c r="B149" s="2" t="s">
-        <v>380</v>
-      </c>
-      <c r="C149" s="2" t="s">
-        <v>381</v>
+      <c r="B149" t="s">
+        <v>377</v>
+      </c>
+      <c r="C149" t="s">
+        <v>378</v>
       </c>
       <c r="D149" s="7"/>
       <c r="E149" s="7"/>
-      <c r="F149" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G149" s="26"/>
-    </row>
-    <row r="150" spans="1:7" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F149" t="s">
+        <v>14</v>
+      </c>
+      <c r="G149" s="26" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>210</v>
       </c>
       <c r="B150" s="2" t="s">
-        <v>382</v>
+        <v>380</v>
       </c>
       <c r="C150" s="2" t="s">
-        <v>383</v>
+        <v>381</v>
       </c>
       <c r="D150" s="7"/>
       <c r="E150" s="7"/>
@@ -6731,58 +6752,56 @@
       </c>
       <c r="G150" s="26"/>
     </row>
-    <row r="151" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A151" s="17" t="s">
+    <row r="151" spans="1:7" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A151" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="B151" s="17" t="s">
+      <c r="B151" s="2" t="s">
+        <v>382</v>
+      </c>
+      <c r="C151" s="2" t="s">
+        <v>383</v>
+      </c>
+      <c r="D151" s="7"/>
+      <c r="E151" s="7"/>
+      <c r="F151" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G151" s="26"/>
+    </row>
+    <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A152" s="17" t="s">
+        <v>210</v>
+      </c>
+      <c r="B152" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="C151" s="17" t="s">
+      <c r="C152" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="D151" s="27" t="s">
+      <c r="D152" s="27" t="s">
         <v>386</v>
       </c>
-      <c r="E151" s="27"/>
-      <c r="F151" s="21" t="s">
+      <c r="E152" s="27"/>
+      <c r="F152" s="21" t="s">
         <v>14</v>
       </c>
-      <c r="G151" s="28" t="s">
+      <c r="G152" s="28" t="s">
         <v>387</v>
       </c>
-    </row>
-    <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A152" s="2" t="s">
-        <v>388</v>
-      </c>
-      <c r="B152" s="2" t="s">
-        <v>389</v>
-      </c>
-      <c r="C152" s="2" t="s">
-        <v>390</v>
-      </c>
-      <c r="D152" s="1" t="s">
-        <v>391</v>
-      </c>
-      <c r="E152" s="7"/>
-      <c r="F152" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G152" s="26"/>
     </row>
     <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>388</v>
       </c>
       <c r="B153" s="2" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="E153" s="7"/>
       <c r="F153" s="4" t="s">
@@ -6795,61 +6814,63 @@
         <v>388</v>
       </c>
       <c r="B154" s="2" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
       <c r="C154" s="2" t="s">
-        <v>396</v>
-      </c>
-      <c r="D154" s="7"/>
+        <v>393</v>
+      </c>
+      <c r="D154" s="1" t="s">
+        <v>394</v>
+      </c>
       <c r="E154" s="7"/>
       <c r="F154" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G154" s="26"/>
     </row>
-    <row r="155" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>388</v>
       </c>
       <c r="B155" s="2" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
       <c r="C155" s="2" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
       <c r="D155" s="7"/>
       <c r="E155" s="7"/>
-      <c r="F155" s="5" t="s">
-        <v>20</v>
+      <c r="F155" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G155" s="26"/>
     </row>
-    <row r="156" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>388</v>
       </c>
       <c r="B156" s="2" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
       <c r="C156" s="2" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
       <c r="D156" s="7"/>
       <c r="E156" s="7"/>
-      <c r="F156" s="4" t="s">
-        <v>29</v>
+      <c r="F156" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G156" s="26"/>
     </row>
-    <row r="157" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>388</v>
       </c>
       <c r="B157" s="2" t="s">
-        <v>401</v>
+        <v>399</v>
       </c>
       <c r="C157" s="2" t="s">
-        <v>402</v>
+        <v>400</v>
       </c>
       <c r="D157" s="7"/>
       <c r="E157" s="7"/>
@@ -6858,54 +6879,54 @@
       </c>
       <c r="G157" s="26"/>
     </row>
-    <row r="158" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A158" s="17" t="s">
+    <row r="158" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A158" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="B158" s="17" t="s">
+      <c r="B158" s="2" t="s">
+        <v>401</v>
+      </c>
+      <c r="C158" s="2" t="s">
+        <v>402</v>
+      </c>
+      <c r="D158" s="7"/>
+      <c r="E158" s="7"/>
+      <c r="F158" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G158" s="26"/>
+    </row>
+    <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A159" s="17" t="s">
+        <v>388</v>
+      </c>
+      <c r="B159" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="C158" s="17" t="s">
+      <c r="C159" s="17" t="s">
         <v>404</v>
       </c>
-      <c r="D158" s="27"/>
-      <c r="E158" s="27"/>
-      <c r="F158" s="20" t="s">
+      <c r="D159" s="27"/>
+      <c r="E159" s="27"/>
+      <c r="F159" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G158" s="28"/>
-    </row>
-    <row r="159" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A159" s="2" t="s">
-        <v>405</v>
-      </c>
-      <c r="B159" s="2" t="s">
-        <v>406</v>
-      </c>
-      <c r="C159" s="2" t="s">
-        <v>407</v>
-      </c>
-      <c r="D159" s="7"/>
-      <c r="E159" s="7"/>
-      <c r="F159" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G159" s="26"/>
+      <c r="G159" s="28"/>
     </row>
     <row r="160" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B160" s="2" t="s">
-        <v>408</v>
+        <v>406</v>
       </c>
       <c r="C160" s="2" t="s">
-        <v>409</v>
+        <v>407</v>
       </c>
       <c r="D160" s="7"/>
       <c r="E160" s="7"/>
-      <c r="F160" s="5" t="s">
-        <v>20</v>
+      <c r="F160" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G160" s="26"/>
     </row>
@@ -6914,10 +6935,10 @@
         <v>405</v>
       </c>
       <c r="B161" s="2" t="s">
-        <v>410</v>
+        <v>408</v>
       </c>
       <c r="C161" s="2" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
       <c r="D161" s="7"/>
       <c r="E161" s="7"/>
@@ -6931,10 +6952,10 @@
         <v>405</v>
       </c>
       <c r="B162" s="2" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
       <c r="C162" s="2" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
       <c r="D162" s="7"/>
       <c r="E162" s="7"/>
@@ -6943,22 +6964,20 @@
       </c>
       <c r="G162" s="26"/>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B163" s="2" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
       <c r="C163" s="2" t="s">
-        <v>415</v>
-      </c>
-      <c r="D163" s="1" t="s">
-        <v>416</v>
-      </c>
+        <v>413</v>
+      </c>
+      <c r="D163" s="7"/>
       <c r="E163" s="7"/>
-      <c r="F163" s="3" t="s">
-        <v>10</v>
+      <c r="F163" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G163" s="26"/>
     </row>
@@ -6967,80 +6986,82 @@
         <v>405</v>
       </c>
       <c r="B164" s="2" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="C164" s="2" t="s">
-        <v>418</v>
-      </c>
-      <c r="D164" s="7"/>
+        <v>415</v>
+      </c>
+      <c r="D164" s="1" t="s">
+        <v>416</v>
+      </c>
       <c r="E164" s="7"/>
       <c r="F164" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G164" s="26"/>
     </row>
-    <row r="165" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B165" s="2" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
       <c r="C165" s="2" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
       <c r="D165" s="7"/>
       <c r="E165" s="7"/>
-      <c r="F165" s="4" t="s">
-        <v>29</v>
+      <c r="F165" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G165" s="26"/>
     </row>
-    <row r="166" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B166" s="2" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
       <c r="C166" s="2" t="s">
-        <v>422</v>
-      </c>
-      <c r="D166" s="1" t="s">
-        <v>423</v>
-      </c>
+        <v>420</v>
+      </c>
+      <c r="D166" s="7"/>
       <c r="E166" s="7"/>
-      <c r="F166" s="3" t="s">
-        <v>10</v>
+      <c r="F166" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G166" s="26"/>
     </row>
-    <row r="167" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B167" s="2" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
       <c r="C167" s="2" t="s">
-        <v>425</v>
-      </c>
-      <c r="D167" s="7"/>
+        <v>422</v>
+      </c>
+      <c r="D167" s="1" t="s">
+        <v>423</v>
+      </c>
       <c r="E167" s="7"/>
-      <c r="F167" s="5" t="s">
-        <v>20</v>
+      <c r="F167" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G167" s="26"/>
     </row>
-    <row r="168" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B168" s="2" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="C168" s="2" t="s">
-        <v>427</v>
+        <v>425</v>
       </c>
       <c r="D168" s="7"/>
       <c r="E168" s="7"/>
@@ -7049,15 +7070,15 @@
       </c>
       <c r="G168" s="26"/>
     </row>
-    <row r="169" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B169" s="2" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="C169" s="2" t="s">
-        <v>429</v>
+        <v>427</v>
       </c>
       <c r="D169" s="7"/>
       <c r="E169" s="7"/>
@@ -7066,20 +7087,18 @@
       </c>
       <c r="G169" s="26"/>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B170" s="2" t="s">
-        <v>430</v>
+        <v>428</v>
       </c>
       <c r="C170" s="2" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="D170" s="7"/>
-      <c r="E170" s="1" t="s">
-        <v>432</v>
-      </c>
+      <c r="E170" s="7"/>
       <c r="F170" s="5" t="s">
         <v>20</v>
       </c>
@@ -7090,13 +7109,15 @@
         <v>405</v>
       </c>
       <c r="B171" s="2" t="s">
-        <v>433</v>
+        <v>430</v>
       </c>
       <c r="C171" s="2" t="s">
-        <v>434</v>
+        <v>431</v>
       </c>
       <c r="D171" s="7"/>
-      <c r="E171" s="7"/>
+      <c r="E171" s="1" t="s">
+        <v>432</v>
+      </c>
       <c r="F171" s="5" t="s">
         <v>20</v>
       </c>
@@ -7107,99 +7128,97 @@
         <v>405</v>
       </c>
       <c r="B172" s="2" t="s">
-        <v>435</v>
+        <v>433</v>
       </c>
       <c r="C172" s="2" t="s">
-        <v>436</v>
+        <v>434</v>
       </c>
       <c r="D172" s="7"/>
       <c r="E172" s="7"/>
-      <c r="F172" s="3" t="s">
-        <v>10</v>
+      <c r="F172" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G172" s="26"/>
     </row>
-    <row r="173" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B173" s="2" t="s">
-        <v>437</v>
+        <v>435</v>
       </c>
       <c r="C173" s="2" t="s">
-        <v>438</v>
+        <v>436</v>
       </c>
       <c r="D173" s="7"/>
       <c r="E173" s="7"/>
-      <c r="F173" s="4" t="s">
-        <v>29</v>
+      <c r="F173" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G173" s="26"/>
     </row>
-    <row r="174" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B174" s="2" t="s">
-        <v>439</v>
+        <v>437</v>
       </c>
       <c r="C174" s="2" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="D174" s="7"/>
       <c r="E174" s="7"/>
-      <c r="F174" s="6" t="s">
-        <v>25</v>
-      </c>
-      <c r="G174" s="24" t="s">
-        <v>441</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F174" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G174" s="26"/>
+    </row>
+    <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B175" s="2" t="s">
-        <v>442</v>
+        <v>439</v>
       </c>
       <c r="C175" s="2" t="s">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="D175" s="7"/>
       <c r="E175" s="7"/>
-      <c r="F175" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G175" s="26"/>
+      <c r="F175" s="6" t="s">
+        <v>25</v>
+      </c>
+      <c r="G175" s="24" t="s">
+        <v>441</v>
+      </c>
     </row>
     <row r="176" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B176" s="2" t="s">
-        <v>444</v>
+        <v>442</v>
       </c>
       <c r="C176" s="2" t="s">
-        <v>445</v>
+        <v>443</v>
       </c>
       <c r="D176" s="7"/>
       <c r="E176" s="7"/>
-      <c r="F176" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G176" s="24" t="s">
-        <v>446</v>
-      </c>
+      <c r="F176" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G176" s="26"/>
     </row>
     <row r="177" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B177" s="2" t="s">
-        <v>447</v>
+        <v>444</v>
       </c>
       <c r="C177" s="2" t="s">
-        <v>448</v>
+        <v>445</v>
       </c>
       <c r="D177" s="7"/>
       <c r="E177" s="7"/>
@@ -7207,18 +7226,18 @@
         <v>14</v>
       </c>
       <c r="G177" s="24" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B178" s="2" t="s">
-        <v>450</v>
+        <v>447</v>
       </c>
       <c r="C178" s="2" t="s">
-        <v>451</v>
+        <v>448</v>
       </c>
       <c r="D178" s="7"/>
       <c r="E178" s="7"/>
@@ -7226,171 +7245,173 @@
         <v>14</v>
       </c>
       <c r="G178" s="24" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B179" s="2" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="C179" s="2" t="s">
-        <v>454</v>
-      </c>
-      <c r="D179" s="1" t="s">
-        <v>455</v>
-      </c>
+        <v>451</v>
+      </c>
+      <c r="D179" s="7"/>
       <c r="E179" s="7"/>
-      <c r="F179" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G179" s="26"/>
-    </row>
-    <row r="180" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F179" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G179" s="24" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B180" s="2" t="s">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="C180" s="2" t="s">
-        <v>457</v>
+        <v>454</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>458</v>
+        <v>455</v>
       </c>
       <c r="E180" s="7"/>
-      <c r="F180" s="4" t="s">
-        <v>29</v>
+      <c r="F180" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G180" s="26"/>
     </row>
-    <row r="181" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B181" s="2" t="s">
-        <v>459</v>
+        <v>456</v>
       </c>
       <c r="C181" s="2" t="s">
-        <v>460</v>
-      </c>
-      <c r="D181" s="7"/>
+        <v>457</v>
+      </c>
+      <c r="D181" s="1" t="s">
+        <v>458</v>
+      </c>
       <c r="E181" s="7"/>
-      <c r="F181" s="3" t="s">
-        <v>10</v>
+      <c r="F181" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G181" s="26"/>
     </row>
-    <row r="182" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>405</v>
       </c>
       <c r="B182" s="2" t="s">
-        <v>461</v>
+        <v>459</v>
       </c>
       <c r="C182" s="2" t="s">
-        <v>462</v>
+        <v>460</v>
       </c>
       <c r="D182" s="7"/>
       <c r="E182" s="7"/>
-      <c r="F182" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G182" s="24" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A183" s="17" t="s">
+      <c r="F182" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G182" s="26"/>
+    </row>
+    <row r="183" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A183" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="B183" s="17" t="s">
-        <v>464</v>
-      </c>
-      <c r="C183" s="17" t="s">
-        <v>465</v>
+      <c r="B183" s="2" t="s">
+        <v>461</v>
+      </c>
+      <c r="C183" s="2" t="s">
+        <v>462</v>
       </c>
       <c r="D183" s="7"/>
       <c r="E183" s="7"/>
-      <c r="F183" s="22" t="s">
+      <c r="F183" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G183" s="24" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A184" s="17" t="s">
+        <v>405</v>
+      </c>
+      <c r="B184" s="17" t="s">
+        <v>464</v>
+      </c>
+      <c r="C184" s="17" t="s">
+        <v>465</v>
+      </c>
+      <c r="D184" s="7"/>
+      <c r="E184" s="7"/>
+      <c r="F184" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="G183" s="28" t="s">
+      <c r="G184" s="28" t="s">
         <v>466</v>
       </c>
     </row>
-    <row r="184" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A184" s="2" t="s">
+    <row r="185" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A185" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="B184" s="2" t="s">
+      <c r="B185" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="C184" s="2" t="s">
+      <c r="C185" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="D184" s="1" t="s">
+      <c r="D185" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="E184" s="7"/>
-      <c r="F184" s="3" t="s">
+      <c r="E185" s="7"/>
+      <c r="F185" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G184" s="26"/>
-    </row>
-    <row r="185" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A185" s="17" t="s">
+      <c r="G185" s="26"/>
+    </row>
+    <row r="186" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A186" s="17" t="s">
         <v>471</v>
       </c>
-      <c r="B185" s="17" t="s">
+      <c r="B186" s="17" t="s">
         <v>472</v>
       </c>
-      <c r="C185" s="17" t="s">
+      <c r="C186" s="17" t="s">
         <v>473</v>
       </c>
-      <c r="D185" s="27" t="s">
+      <c r="D186" s="27" t="s">
         <v>474</v>
       </c>
-      <c r="E185" s="7"/>
-      <c r="F185" s="19" t="s">
+      <c r="E186" s="7"/>
+      <c r="F186" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="G185" s="26"/>
-    </row>
-    <row r="186" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A186" s="2" t="s">
-        <v>475</v>
-      </c>
-      <c r="B186" s="2" t="s">
-        <v>476</v>
-      </c>
-      <c r="C186" s="2" t="s">
-        <v>477</v>
-      </c>
-      <c r="D186" s="7"/>
-      <c r="E186" s="7"/>
-      <c r="F186" s="5" t="s">
-        <v>20</v>
-      </c>
       <c r="G186" s="26"/>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B187" s="2" t="s">
-        <v>478</v>
+        <v>476</v>
       </c>
       <c r="C187" s="2" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
       <c r="D187" s="7"/>
       <c r="E187" s="7"/>
-      <c r="F187" s="3" t="s">
-        <v>10</v>
+      <c r="F187" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G187" s="26"/>
     </row>
@@ -7399,15 +7420,15 @@
         <v>475</v>
       </c>
       <c r="B188" s="2" t="s">
-        <v>480</v>
+        <v>478</v>
       </c>
       <c r="C188" s="2" t="s">
-        <v>481</v>
+        <v>479</v>
       </c>
       <c r="D188" s="7"/>
       <c r="E188" s="7"/>
-      <c r="F188" s="4" t="s">
-        <v>29</v>
+      <c r="F188" s="3" t="s">
+        <v>10</v>
       </c>
       <c r="G188" s="26"/>
     </row>
@@ -7416,10 +7437,10 @@
         <v>475</v>
       </c>
       <c r="B189" s="2" t="s">
-        <v>482</v>
+        <v>480</v>
       </c>
       <c r="C189" s="2" t="s">
-        <v>483</v>
+        <v>481</v>
       </c>
       <c r="D189" s="7"/>
       <c r="E189" s="7"/>
@@ -7428,138 +7449,138 @@
       </c>
       <c r="G189" s="26"/>
     </row>
-    <row r="190" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B190" s="2" t="s">
-        <v>484</v>
+        <v>482</v>
       </c>
       <c r="C190" s="2" t="s">
-        <v>485</v>
+        <v>483</v>
       </c>
       <c r="D190" s="7"/>
       <c r="E190" s="7"/>
-      <c r="F190" s="5" t="s">
-        <v>20</v>
+      <c r="F190" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G190" s="26"/>
     </row>
-    <row r="191" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B191" s="2" t="s">
-        <v>486</v>
+        <v>484</v>
       </c>
       <c r="C191" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="D191" s="1" t="s">
-        <v>488</v>
-      </c>
+        <v>485</v>
+      </c>
+      <c r="D191" s="7"/>
       <c r="E191" s="7"/>
-      <c r="F191" s="4" t="s">
-        <v>29</v>
+      <c r="F191" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G191" s="26"/>
     </row>
-    <row r="192" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B192" s="2" t="s">
-        <v>489</v>
+        <v>486</v>
       </c>
       <c r="C192" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="D192" s="7"/>
+        <v>487</v>
+      </c>
+      <c r="D192" s="1" t="s">
+        <v>488</v>
+      </c>
       <c r="E192" s="7"/>
-      <c r="F192" s="5" t="s">
-        <v>20</v>
+      <c r="F192" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G192" s="26"/>
     </row>
-    <row r="193" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B193" s="2" t="s">
-        <v>491</v>
+        <v>489</v>
       </c>
       <c r="C193" s="2" t="s">
-        <v>492</v>
+        <v>490</v>
       </c>
       <c r="D193" s="7"/>
       <c r="E193" s="7"/>
-      <c r="F193" s="4" t="s">
-        <v>29</v>
+      <c r="F193" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G193" s="26"/>
     </row>
-    <row r="194" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B194" s="2" t="s">
-        <v>493</v>
+        <v>491</v>
       </c>
       <c r="C194" s="2" t="s">
-        <v>494</v>
+        <v>492</v>
       </c>
       <c r="D194" s="7"/>
       <c r="E194" s="7"/>
-      <c r="F194" s="14" t="s">
-        <v>96</v>
+      <c r="F194" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G194" s="26"/>
     </row>
-    <row r="195" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B195" s="2" t="s">
-        <v>495</v>
+        <v>493</v>
       </c>
       <c r="C195" s="2" t="s">
-        <v>496</v>
+        <v>494</v>
       </c>
       <c r="D195" s="7"/>
       <c r="E195" s="7"/>
-      <c r="F195" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G195" s="24" t="s">
-        <v>497</v>
-      </c>
-    </row>
-    <row r="196" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F195" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="G195" s="26"/>
+    </row>
+    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B196" s="2" t="s">
-        <v>498</v>
+        <v>495</v>
       </c>
       <c r="C196" s="2" t="s">
-        <v>499</v>
+        <v>496</v>
       </c>
       <c r="D196" s="7"/>
       <c r="E196" s="7"/>
-      <c r="F196" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G196" s="26"/>
+      <c r="F196" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G196" s="24" t="s">
+        <v>497</v>
+      </c>
     </row>
     <row r="197" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B197" s="2" t="s">
-        <v>500</v>
+        <v>498</v>
       </c>
       <c r="C197" s="2" t="s">
-        <v>501</v>
+        <v>499</v>
       </c>
       <c r="D197" s="7"/>
       <c r="E197" s="7"/>
@@ -7573,10 +7594,10 @@
         <v>475</v>
       </c>
       <c r="B198" s="2" t="s">
-        <v>502</v>
+        <v>500</v>
       </c>
       <c r="C198" s="2" t="s">
-        <v>503</v>
+        <v>501</v>
       </c>
       <c r="D198" s="7"/>
       <c r="E198" s="7"/>
@@ -7590,215 +7611,213 @@
         <v>475</v>
       </c>
       <c r="B199" s="2" t="s">
-        <v>504</v>
+        <v>502</v>
       </c>
       <c r="C199" s="2" t="s">
-        <v>505</v>
+        <v>503</v>
       </c>
       <c r="D199" s="7"/>
       <c r="E199" s="7"/>
-      <c r="F199" s="4" t="s">
-        <v>29</v>
+      <c r="F199" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G199" s="26"/>
     </row>
-    <row r="200" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>475</v>
       </c>
       <c r="B200" s="2" t="s">
-        <v>506</v>
+        <v>504</v>
       </c>
       <c r="C200" s="2" t="s">
-        <v>507</v>
+        <v>505</v>
       </c>
       <c r="D200" s="7"/>
       <c r="E200" s="7"/>
-      <c r="F200" s="12" t="s">
-        <v>37</v>
+      <c r="F200" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G200" s="26"/>
     </row>
-    <row r="201" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A201" s="17" t="s">
+    <row r="201" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A201" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="B201" s="17" t="s">
-        <v>508</v>
-      </c>
-      <c r="C201" s="17" t="s">
-        <v>509</v>
+      <c r="B201" s="2" t="s">
+        <v>506</v>
+      </c>
+      <c r="C201" s="2" t="s">
+        <v>507</v>
       </c>
       <c r="D201" s="7"/>
       <c r="E201" s="7"/>
-      <c r="F201" s="20" t="s">
-        <v>29</v>
+      <c r="F201" s="12" t="s">
+        <v>37</v>
       </c>
       <c r="G201" s="26"/>
     </row>
-    <row r="202" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A202" t="s">
-        <v>510</v>
-      </c>
-      <c r="B202" t="s">
-        <v>1014</v>
-      </c>
-      <c r="C202" t="s">
-        <v>1015</v>
+    <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A202" s="17" t="s">
+        <v>475</v>
+      </c>
+      <c r="B202" s="17" t="s">
+        <v>508</v>
+      </c>
+      <c r="C202" s="17" t="s">
+        <v>509</v>
       </c>
       <c r="D202" s="7"/>
       <c r="E202" s="7"/>
-      <c r="F202" t="s">
-        <v>20</v>
-      </c>
-      <c r="G202" s="26" t="s">
-        <v>1016</v>
-      </c>
+      <c r="F202" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G202" s="26"/>
     </row>
     <row r="203" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A203" t="s">
         <v>510</v>
       </c>
       <c r="B203" t="s">
-        <v>511</v>
+        <v>1014</v>
       </c>
       <c r="C203" t="s">
-        <v>512</v>
+        <v>1015</v>
       </c>
       <c r="D203" s="7"/>
       <c r="E203" s="7"/>
       <c r="F203" t="s">
+        <v>20</v>
+      </c>
+      <c r="G203" s="26" t="s">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A204" t="s">
+        <v>510</v>
+      </c>
+      <c r="B204" t="s">
+        <v>511</v>
+      </c>
+      <c r="C204" t="s">
+        <v>512</v>
+      </c>
+      <c r="D204" s="7"/>
+      <c r="E204" s="7"/>
+      <c r="F204" t="s">
         <v>10</v>
       </c>
-      <c r="G203" s="26"/>
-    </row>
-    <row r="204" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A204" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B204" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="C204" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="D204" s="1"/>
-      <c r="E204" s="7"/>
-      <c r="F204" s="5" t="s">
-        <v>14</v>
-      </c>
       <c r="G204" s="26"/>
     </row>
-    <row r="205" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B205" s="2" t="s">
-        <v>515</v>
+        <v>513</v>
       </c>
       <c r="C205" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="D205" s="7"/>
+        <v>514</v>
+      </c>
+      <c r="D205" s="1"/>
       <c r="E205" s="7"/>
-      <c r="F205" s="16" t="s">
+      <c r="F205" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="G205" s="26" t="s">
-        <v>517</v>
-      </c>
-    </row>
-    <row r="206" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G205" s="26"/>
+    </row>
+    <row r="206" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B206" s="2" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="C206" s="2" t="s">
-        <v>519</v>
-      </c>
-      <c r="D206" s="7" t="s">
-        <v>520</v>
-      </c>
+        <v>516</v>
+      </c>
+      <c r="D206" s="7"/>
       <c r="E206" s="7"/>
       <c r="F206" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G206" s="26" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A207" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B207" s="2" t="s">
+        <v>518</v>
+      </c>
+      <c r="C207" s="2" t="s">
+        <v>519</v>
+      </c>
+      <c r="D207" s="7" t="s">
+        <v>520</v>
+      </c>
+      <c r="E207" s="7"/>
+      <c r="F207" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G206" s="24"/>
-    </row>
-    <row r="207" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A207" t="s">
-        <v>510</v>
-      </c>
-      <c r="B207" t="s">
-        <v>997</v>
-      </c>
-      <c r="C207" t="s">
-        <v>998</v>
-      </c>
-      <c r="D207" s="7"/>
-      <c r="E207" s="7"/>
-      <c r="F207" t="s">
-        <v>20</v>
-      </c>
-      <c r="G207" s="26" t="s">
-        <v>999</v>
-      </c>
+      <c r="G207" s="24"/>
     </row>
     <row r="208" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A208" t="s">
         <v>510</v>
       </c>
       <c r="B208" t="s">
-        <v>521</v>
+        <v>997</v>
       </c>
       <c r="C208" t="s">
-        <v>522</v>
+        <v>998</v>
       </c>
       <c r="D208" s="7"/>
       <c r="E208" s="7"/>
       <c r="F208" t="s">
-        <v>10</v>
-      </c>
-      <c r="G208" s="26"/>
-    </row>
-    <row r="209" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A209" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="G208" s="26" t="s">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A209" t="s">
         <v>510</v>
       </c>
-      <c r="B209" s="2" t="s">
-        <v>523</v>
-      </c>
-      <c r="C209" s="2" t="s">
-        <v>524</v>
+      <c r="B209" t="s">
+        <v>521</v>
+      </c>
+      <c r="C209" t="s">
+        <v>522</v>
       </c>
       <c r="D209" s="7"/>
       <c r="E209" s="7"/>
-      <c r="F209" s="16" t="s">
-        <v>14</v>
-      </c>
-      <c r="G209" s="24" t="s">
-        <v>525</v>
-      </c>
-    </row>
-    <row r="210" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F209" t="s">
+        <v>10</v>
+      </c>
+      <c r="G209" s="26"/>
+    </row>
+    <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B210" s="2" t="s">
-        <v>526</v>
+        <v>523</v>
       </c>
       <c r="C210" s="2" t="s">
-        <v>527</v>
+        <v>524</v>
       </c>
       <c r="D210" s="7"/>
       <c r="E210" s="7"/>
-      <c r="F210" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G210" s="26" t="s">
-        <v>528</v>
+      <c r="F210" s="16" t="s">
+        <v>14</v>
+      </c>
+      <c r="G210" s="24" t="s">
+        <v>525</v>
       </c>
     </row>
     <row r="211" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -7806,31 +7825,33 @@
         <v>510</v>
       </c>
       <c r="B211" s="2" t="s">
-        <v>529</v>
+        <v>526</v>
       </c>
       <c r="C211" s="2" t="s">
-        <v>530</v>
+        <v>527</v>
       </c>
       <c r="D211" s="7"/>
       <c r="E211" s="7"/>
       <c r="F211" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G211" s="26"/>
+      <c r="G211" s="26" t="s">
+        <v>528</v>
+      </c>
     </row>
     <row r="212" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B212" s="2" t="s">
-        <v>531</v>
+        <v>529</v>
       </c>
       <c r="C212" s="2" t="s">
-        <v>532</v>
-      </c>
-      <c r="D212" s="1"/>
+        <v>530</v>
+      </c>
+      <c r="D212" s="7"/>
       <c r="E212" s="7"/>
-      <c r="F212" s="12" t="s">
+      <c r="F212" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G212" s="26"/>
@@ -7840,17 +7861,15 @@
         <v>510</v>
       </c>
       <c r="B213" s="2" t="s">
-        <v>533</v>
+        <v>531</v>
       </c>
       <c r="C213" s="2" t="s">
-        <v>534</v>
-      </c>
-      <c r="D213" s="7" t="s">
-        <v>535</v>
-      </c>
+        <v>532</v>
+      </c>
+      <c r="D213" s="1"/>
       <c r="E213" s="7"/>
-      <c r="F213" s="3" t="s">
-        <v>37</v>
+      <c r="F213" s="12" t="s">
+        <v>10</v>
       </c>
       <c r="G213" s="26"/>
     </row>
@@ -7859,15 +7878,17 @@
         <v>510</v>
       </c>
       <c r="B214" s="2" t="s">
-        <v>536</v>
+        <v>533</v>
       </c>
       <c r="C214" s="2" t="s">
-        <v>537</v>
-      </c>
-      <c r="D214" s="1"/>
+        <v>534</v>
+      </c>
+      <c r="D214" s="7" t="s">
+        <v>535</v>
+      </c>
       <c r="E214" s="7"/>
-      <c r="F214" s="14" t="s">
-        <v>10</v>
+      <c r="F214" s="3" t="s">
+        <v>37</v>
       </c>
       <c r="G214" s="26"/>
     </row>
@@ -7876,17 +7897,15 @@
         <v>510</v>
       </c>
       <c r="B215" s="2" t="s">
-        <v>538</v>
+        <v>536</v>
       </c>
       <c r="C215" s="2" t="s">
-        <v>539</v>
-      </c>
-      <c r="D215" s="1" t="s">
-        <v>540</v>
-      </c>
+        <v>537</v>
+      </c>
+      <c r="D215" s="1"/>
       <c r="E215" s="7"/>
-      <c r="F215" s="4" t="s">
-        <v>541</v>
+      <c r="F215" s="14" t="s">
+        <v>10</v>
       </c>
       <c r="G215" s="26"/>
     </row>
@@ -7895,34 +7914,36 @@
         <v>510</v>
       </c>
       <c r="B216" s="2" t="s">
+        <v>538</v>
+      </c>
+      <c r="C216" s="2" t="s">
+        <v>539</v>
+      </c>
+      <c r="D216" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="E216" s="7"/>
+      <c r="F216" s="4" t="s">
+        <v>541</v>
+      </c>
+      <c r="G216" s="26"/>
+    </row>
+    <row r="217" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A217" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B217" s="2" t="s">
         <v>542</v>
       </c>
-      <c r="C216" s="2" t="s">
+      <c r="C217" s="2" t="s">
         <v>543</v>
       </c>
-      <c r="D216" s="7" t="s">
+      <c r="D217" s="7" t="s">
         <v>544</v>
       </c>
-      <c r="E216" s="7"/>
-      <c r="F216" s="5" t="s">
+      <c r="E217" s="7"/>
+      <c r="F217" s="5" t="s">
         <v>29</v>
-      </c>
-      <c r="G216" s="26"/>
-    </row>
-    <row r="217" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A217" t="s">
-        <v>510</v>
-      </c>
-      <c r="B217" t="s">
-        <v>545</v>
-      </c>
-      <c r="C217" t="s">
-        <v>546</v>
-      </c>
-      <c r="D217" s="7"/>
-      <c r="E217" s="7"/>
-      <c r="F217" t="s">
-        <v>20</v>
       </c>
       <c r="G217" s="26"/>
     </row>
@@ -7931,48 +7952,46 @@
         <v>510</v>
       </c>
       <c r="B218" t="s">
-        <v>1017</v>
+        <v>545</v>
       </c>
       <c r="C218" t="s">
-        <v>1018</v>
+        <v>546</v>
       </c>
       <c r="D218" s="7"/>
       <c r="E218" s="7"/>
       <c r="F218" t="s">
         <v>20</v>
       </c>
-      <c r="G218" s="26" t="s">
-        <v>1019</v>
-      </c>
+      <c r="G218" s="26"/>
     </row>
     <row r="219" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A219" t="s">
         <v>510</v>
       </c>
       <c r="B219" t="s">
-        <v>547</v>
+        <v>1017</v>
       </c>
       <c r="C219" t="s">
-        <v>548</v>
+        <v>1018</v>
       </c>
       <c r="D219" s="7"/>
       <c r="E219" s="7"/>
       <c r="F219" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G219" s="26" t="s">
-        <v>549</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A220" t="s">
         <v>510</v>
       </c>
       <c r="B220" t="s">
-        <v>1020</v>
+        <v>547</v>
       </c>
       <c r="C220" t="s">
-        <v>1021</v>
+        <v>548</v>
       </c>
       <c r="D220" s="7"/>
       <c r="E220" s="7"/>
@@ -7980,7 +7999,7 @@
         <v>29</v>
       </c>
       <c r="G220" s="26" t="s">
-        <v>1022</v>
+        <v>549</v>
       </c>
     </row>
     <row r="221" spans="1:7" x14ac:dyDescent="0.35">
@@ -7988,10 +8007,10 @@
         <v>510</v>
       </c>
       <c r="B221" t="s">
-        <v>1023</v>
+        <v>1020</v>
       </c>
       <c r="C221" t="s">
-        <v>1024</v>
+        <v>1021</v>
       </c>
       <c r="D221" s="7"/>
       <c r="E221" s="7"/>
@@ -7999,7 +8018,7 @@
         <v>29</v>
       </c>
       <c r="G221" s="26" t="s">
-        <v>1025</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="222" spans="1:7" x14ac:dyDescent="0.35">
@@ -8007,120 +8026,122 @@
         <v>510</v>
       </c>
       <c r="B222" t="s">
-        <v>550</v>
+        <v>1064</v>
       </c>
       <c r="C222" t="s">
-        <v>551</v>
-      </c>
-      <c r="D222" s="7"/>
+        <v>1065</v>
+      </c>
+      <c r="D222" s="7" t="s">
+        <v>1066</v>
+      </c>
       <c r="E222" s="7"/>
       <c r="F222" t="s">
         <v>20</v>
       </c>
       <c r="G222" s="26"/>
     </row>
-    <row r="223" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A223" t="s">
         <v>510</v>
       </c>
       <c r="B223" t="s">
-        <v>1026</v>
+        <v>1023</v>
       </c>
       <c r="C223" t="s">
-        <v>1027</v>
+        <v>1024</v>
       </c>
       <c r="D223" s="7"/>
       <c r="E223" s="7"/>
       <c r="F223" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G223" s="26" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1025</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A224" t="s">
         <v>510</v>
       </c>
       <c r="B224" t="s">
-        <v>995</v>
+        <v>550</v>
       </c>
       <c r="C224" t="s">
-        <v>996</v>
+        <v>551</v>
       </c>
       <c r="D224" s="7"/>
       <c r="E224" s="7"/>
       <c r="F224" t="s">
-        <v>29</v>
-      </c>
-      <c r="G224" s="26" t="s">
-        <v>1013</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G224" s="26"/>
     </row>
     <row r="225" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A225" t="s">
         <v>510</v>
       </c>
       <c r="B225" t="s">
-        <v>552</v>
+        <v>1026</v>
       </c>
       <c r="C225" t="s">
-        <v>553</v>
+        <v>1027</v>
       </c>
       <c r="D225" s="7"/>
       <c r="E225" s="7"/>
       <c r="F225" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G225" s="26" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1028</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A226" t="s">
         <v>510</v>
       </c>
       <c r="B226" t="s">
-        <v>555</v>
+        <v>995</v>
       </c>
       <c r="C226" t="s">
-        <v>556</v>
+        <v>996</v>
       </c>
       <c r="D226" s="7"/>
       <c r="E226" s="7"/>
       <c r="F226" t="s">
         <v>29</v>
       </c>
-      <c r="G226" s="26"/>
-    </row>
-    <row r="227" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G226" s="26" t="s">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A227" t="s">
         <v>510</v>
       </c>
       <c r="B227" t="s">
-        <v>990</v>
+        <v>552</v>
       </c>
       <c r="C227" t="s">
-        <v>991</v>
-      </c>
-      <c r="D227" s="7" t="s">
-        <v>992</v>
-      </c>
+        <v>553</v>
+      </c>
+      <c r="D227" s="7"/>
       <c r="E227" s="7"/>
       <c r="F227" t="s">
-        <v>20</v>
-      </c>
-      <c r="G227" s="26"/>
+        <v>29</v>
+      </c>
+      <c r="G227" s="26" t="s">
+        <v>554</v>
+      </c>
     </row>
     <row r="228" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A228" t="s">
         <v>510</v>
       </c>
       <c r="B228" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="C228" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
       <c r="D228" s="7"/>
       <c r="E228" s="7"/>
@@ -8134,94 +8155,94 @@
         <v>510</v>
       </c>
       <c r="B229" t="s">
-        <v>559</v>
+        <v>990</v>
       </c>
       <c r="C229" t="s">
-        <v>560</v>
-      </c>
-      <c r="D229" s="7"/>
+        <v>991</v>
+      </c>
+      <c r="D229" s="7" t="s">
+        <v>992</v>
+      </c>
       <c r="E229" s="7"/>
       <c r="F229" t="s">
-        <v>10</v>
-      </c>
-      <c r="G229" s="26" t="s">
-        <v>561</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G229" s="26"/>
     </row>
     <row r="230" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A230" t="s">
         <v>510</v>
       </c>
       <c r="B230" t="s">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="C230" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="D230" s="7"/>
       <c r="E230" s="7"/>
       <c r="F230" t="s">
-        <v>10</v>
-      </c>
-      <c r="G230" s="26" t="s">
-        <v>564</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="G230" s="26"/>
     </row>
     <row r="231" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A231" t="s">
         <v>510</v>
       </c>
       <c r="B231" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="C231" t="s">
-        <v>566</v>
-      </c>
-      <c r="D231" s="7" t="s">
-        <v>567</v>
-      </c>
+        <v>560</v>
+      </c>
+      <c r="D231" s="7"/>
       <c r="E231" s="7"/>
       <c r="F231" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G231" s="26" t="s">
-        <v>568</v>
-      </c>
-    </row>
-    <row r="232" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A232" s="2" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A232" t="s">
         <v>510</v>
       </c>
-      <c r="B232" s="2" t="s">
-        <v>569</v>
-      </c>
-      <c r="C232" s="2" t="s">
-        <v>570</v>
+      <c r="B232" t="s">
+        <v>562</v>
+      </c>
+      <c r="C232" t="s">
+        <v>563</v>
       </c>
       <c r="D232" s="7"/>
       <c r="E232" s="7"/>
-      <c r="F232" s="5" t="s">
-        <v>96</v>
-      </c>
-      <c r="G232" s="26"/>
-    </row>
-    <row r="233" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A233" s="2" t="s">
+      <c r="F232" t="s">
+        <v>10</v>
+      </c>
+      <c r="G232" s="26" t="s">
+        <v>564</v>
+      </c>
+    </row>
+    <row r="233" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A233" t="s">
         <v>510</v>
       </c>
-      <c r="B233" s="2" t="s">
-        <v>1029</v>
-      </c>
-      <c r="C233" s="2" t="s">
-        <v>1030</v>
-      </c>
-      <c r="D233" s="7"/>
+      <c r="B233" t="s">
+        <v>565</v>
+      </c>
+      <c r="C233" t="s">
+        <v>566</v>
+      </c>
+      <c r="D233" s="7" t="s">
+        <v>567</v>
+      </c>
       <c r="E233" s="7"/>
-      <c r="F233" s="4" t="s">
+      <c r="F233" t="s">
         <v>20</v>
       </c>
       <c r="G233" s="26" t="s">
-        <v>1031</v>
+        <v>568</v>
       </c>
     </row>
     <row r="234" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -8229,29 +8250,27 @@
         <v>510</v>
       </c>
       <c r="B234" s="2" t="s">
-        <v>1032</v>
+        <v>569</v>
       </c>
       <c r="C234" s="2" t="s">
-        <v>1033</v>
+        <v>570</v>
       </c>
       <c r="D234" s="7"/>
       <c r="E234" s="7"/>
-      <c r="F234" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G234" s="26" t="s">
-        <v>1058</v>
-      </c>
+      <c r="F234" s="5" t="s">
+        <v>96</v>
+      </c>
+      <c r="G234" s="26"/>
     </row>
     <row r="235" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A235" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>1055</v>
+        <v>1029</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>1056</v>
+        <v>1030</v>
       </c>
       <c r="D235" s="7"/>
       <c r="E235" s="7"/>
@@ -8259,7 +8278,7 @@
         <v>20</v>
       </c>
       <c r="G235" s="26" t="s">
-        <v>1057</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="236" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -8267,116 +8286,120 @@
         <v>510</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>571</v>
+        <v>1032</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>572</v>
+        <v>1033</v>
       </c>
       <c r="D236" s="7"/>
       <c r="E236" s="7"/>
-      <c r="F236" s="4"/>
-      <c r="G236" s="26"/>
+      <c r="F236" s="4" t="s">
+        <v>29</v>
+      </c>
+      <c r="G236" s="26" t="s">
+        <v>1058</v>
+      </c>
     </row>
     <row r="237" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A237" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>993</v>
+        <v>1055</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>994</v>
+        <v>1056</v>
       </c>
       <c r="D237" s="7"/>
       <c r="E237" s="7"/>
-      <c r="F237" s="4"/>
-      <c r="G237" s="26"/>
+      <c r="F237" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G237" s="26" t="s">
+        <v>1057</v>
+      </c>
     </row>
     <row r="238" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A238" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B238" s="2" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="C238" s="2" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
       <c r="D238" s="7"/>
       <c r="E238" s="7"/>
-      <c r="F238" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G238" s="24" t="s">
-        <v>575</v>
-      </c>
+      <c r="F238" s="4"/>
+      <c r="G238" s="26"/>
     </row>
     <row r="239" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A239" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>576</v>
+        <v>993</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>577</v>
+        <v>994</v>
       </c>
       <c r="D239" s="7"/>
       <c r="E239" s="7"/>
-      <c r="F239" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G239" s="26" t="s">
-        <v>578</v>
-      </c>
+      <c r="F239" s="4"/>
+      <c r="G239" s="26"/>
     </row>
     <row r="240" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A240" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B240" s="2" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="C240" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="D240" s="7"/>
       <c r="E240" s="7"/>
-      <c r="F240" s="14" t="s">
-        <v>20</v>
-      </c>
-      <c r="G240" s="26"/>
+      <c r="F240" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G240" s="24" t="s">
+        <v>575</v>
+      </c>
     </row>
     <row r="241" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A241" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B241" s="2" t="s">
-        <v>581</v>
+        <v>576</v>
       </c>
       <c r="C241" s="2" t="s">
-        <v>582</v>
+        <v>577</v>
       </c>
       <c r="D241" s="7"/>
       <c r="E241" s="7"/>
-      <c r="F241" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G241" s="26"/>
+      <c r="F241" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G241" s="26" t="s">
+        <v>578</v>
+      </c>
     </row>
     <row r="242" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A242" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D242" s="7"/>
       <c r="E242" s="7"/>
-      <c r="F242" s="4" t="s">
+      <c r="F242" s="14" t="s">
         <v>20</v>
       </c>
       <c r="G242" s="26"/>
@@ -8386,33 +8409,31 @@
         <v>510</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="D243" s="1"/>
+        <v>582</v>
+      </c>
+      <c r="D243" s="7"/>
       <c r="E243" s="7"/>
-      <c r="F243" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G243" s="24" t="s">
-        <v>587</v>
-      </c>
+      <c r="F243" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G243" s="26"/>
     </row>
     <row r="244" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A244" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>588</v>
+        <v>583</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>589</v>
+        <v>584</v>
       </c>
       <c r="D244" s="7"/>
       <c r="E244" s="7"/>
-      <c r="F244" s="5" t="s">
+      <c r="F244" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G244" s="26"/>
@@ -8422,152 +8443,152 @@
         <v>510</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>590</v>
+        <v>585</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="D245" s="7"/>
+        <v>586</v>
+      </c>
+      <c r="D245" s="1"/>
       <c r="E245" s="7"/>
       <c r="F245" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G245" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="G245" s="24" t="s">
+        <v>587</v>
+      </c>
     </row>
     <row r="246" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A246" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>592</v>
+        <v>1067</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="D246" s="7"/>
+        <v>1068</v>
+      </c>
+      <c r="D246" s="1"/>
       <c r="E246" s="7"/>
       <c r="F246" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G246" s="26"/>
+        <v>20</v>
+      </c>
+      <c r="G246" s="24"/>
     </row>
     <row r="247" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A247" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D247" s="7"/>
       <c r="E247" s="7"/>
-      <c r="F247" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G247" s="24"/>
+      <c r="F247" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G247" s="26"/>
     </row>
     <row r="248" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A248" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D248" s="7" t="s">
-        <v>598</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="D248" s="7"/>
       <c r="E248" s="7"/>
       <c r="F248" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G248" s="26" t="s">
-        <v>599</v>
-      </c>
+        <v>96</v>
+      </c>
+      <c r="G248" s="26"/>
     </row>
     <row r="249" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A249" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D249" s="1"/>
+        <v>593</v>
+      </c>
+      <c r="D249" s="7"/>
       <c r="E249" s="7"/>
       <c r="F249" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G249" s="26"/>
     </row>
     <row r="250" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A250" t="s">
+      <c r="A250" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B250" t="s">
-        <v>602</v>
-      </c>
-      <c r="C250" t="s">
-        <v>603</v>
+      <c r="B250" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C250" s="2" t="s">
+        <v>595</v>
       </c>
       <c r="D250" s="7"/>
       <c r="E250" s="7"/>
-      <c r="F250" t="s">
-        <v>29</v>
-      </c>
-      <c r="G250" s="26"/>
-    </row>
-    <row r="251" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F250" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G250" s="24"/>
+    </row>
+    <row r="251" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A251" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D251" s="7"/>
+        <v>597</v>
+      </c>
+      <c r="D251" s="7" t="s">
+        <v>598</v>
+      </c>
       <c r="E251" s="7"/>
       <c r="F251" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G251" s="26"/>
-    </row>
-    <row r="252" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="G251" s="26" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="252" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A252" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="D252" s="7"/>
+        <v>601</v>
+      </c>
+      <c r="D252" s="1"/>
       <c r="E252" s="7"/>
-      <c r="F252" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="G252" s="24" t="s">
-        <v>608</v>
-      </c>
+      <c r="F252" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G252" s="26"/>
     </row>
     <row r="253" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A253" t="s">
         <v>510</v>
       </c>
       <c r="B253" t="s">
-        <v>609</v>
+        <v>602</v>
       </c>
       <c r="C253" t="s">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="D253" s="7"/>
       <c r="E253" s="7"/>
@@ -8576,235 +8597,237 @@
       </c>
       <c r="G253" s="26"/>
     </row>
-    <row r="254" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A254" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>611</v>
+        <v>604</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D254" s="1" t="s">
-        <v>613</v>
-      </c>
+        <v>605</v>
+      </c>
+      <c r="D254" s="7"/>
       <c r="E254" s="7"/>
-      <c r="F254" s="16" t="s">
+      <c r="F254" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G254" s="24"/>
-    </row>
-    <row r="255" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G254" s="26"/>
+    </row>
+    <row r="255" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
       <c r="A255" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>1034</v>
+        <v>606</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D255" s="1"/>
+        <v>607</v>
+      </c>
+      <c r="D255" s="7"/>
       <c r="E255" s="7"/>
-      <c r="F255" s="14" t="s">
+      <c r="F255" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="G255" s="24" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="256" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A256" t="s">
+        <v>510</v>
+      </c>
+      <c r="B256" t="s">
+        <v>609</v>
+      </c>
+      <c r="C256" t="s">
+        <v>610</v>
+      </c>
+      <c r="D256" s="7"/>
+      <c r="E256" s="7"/>
+      <c r="F256" t="s">
         <v>29</v>
       </c>
-      <c r="G255" s="26" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A256" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B256" s="2" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C256" s="2" t="s">
-        <v>1038</v>
-      </c>
-      <c r="D256" s="1"/>
-      <c r="E256" s="7"/>
-      <c r="F256" s="14" t="s">
-        <v>29</v>
-      </c>
-      <c r="G256" s="26" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="257" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G256" s="26"/>
+    </row>
+    <row r="257" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A257" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B257" s="2" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="C257" s="2" t="s">
-        <v>615</v>
-      </c>
-      <c r="D257" s="1"/>
+        <v>612</v>
+      </c>
+      <c r="D257" s="1" t="s">
+        <v>613</v>
+      </c>
       <c r="E257" s="7"/>
-      <c r="F257" s="14" t="s">
-        <v>10</v>
-      </c>
-      <c r="G257" s="26" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="258" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F257" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G257" s="24"/>
+    </row>
+    <row r="258" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A258" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>617</v>
+        <v>1034</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D258" s="7"/>
+        <v>1035</v>
+      </c>
+      <c r="D258" s="1"/>
       <c r="E258" s="7"/>
-      <c r="F258" s="4" t="s">
+      <c r="F258" s="14" t="s">
         <v>29</v>
       </c>
-      <c r="G258" s="26"/>
-    </row>
-    <row r="259" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G258" s="26" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="259" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A259" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>619</v>
+        <v>1037</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>620</v>
-      </c>
-      <c r="D259" s="7"/>
+        <v>1038</v>
+      </c>
+      <c r="D259" s="1"/>
       <c r="E259" s="7"/>
-      <c r="F259" s="4" t="s">
-        <v>14</v>
+      <c r="F259" s="14" t="s">
+        <v>29</v>
       </c>
       <c r="G259" s="26" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A260" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>622</v>
+        <v>614</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="D260" s="7" t="s">
-        <v>624</v>
-      </c>
+        <v>615</v>
+      </c>
+      <c r="D260" s="1"/>
       <c r="E260" s="7"/>
-      <c r="F260" s="5" t="s">
-        <v>14</v>
+      <c r="F260" s="14" t="s">
+        <v>10</v>
       </c>
       <c r="G260" s="26" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A261" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>627</v>
-      </c>
-      <c r="D261" s="7" t="s">
-        <v>628</v>
-      </c>
+        <v>618</v>
+      </c>
+      <c r="D261" s="7"/>
       <c r="E261" s="7"/>
-      <c r="F261" s="5" t="s">
-        <v>541</v>
+      <c r="F261" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G261" s="26"/>
     </row>
     <row r="262" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A262" t="s">
+      <c r="A262" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B262" t="s">
-        <v>629</v>
-      </c>
-      <c r="C262" t="s">
-        <v>630</v>
+      <c r="B262" s="2" t="s">
+        <v>619</v>
+      </c>
+      <c r="C262" s="2" t="s">
+        <v>620</v>
       </c>
       <c r="D262" s="7"/>
       <c r="E262" s="7"/>
-      <c r="F262" t="s">
-        <v>29</v>
-      </c>
-      <c r="G262" s="26"/>
-    </row>
-    <row r="263" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="F262" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G262" s="26" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A263" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>632</v>
-      </c>
-      <c r="D263" s="7"/>
+        <v>623</v>
+      </c>
+      <c r="D263" s="7" t="s">
+        <v>624</v>
+      </c>
       <c r="E263" s="7"/>
-      <c r="F263" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G263" s="26"/>
+      <c r="F263" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G263" s="26" t="s">
+        <v>625</v>
+      </c>
     </row>
     <row r="264" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A264" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>633</v>
+        <v>626</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>634</v>
-      </c>
-      <c r="D264" s="7"/>
+        <v>627</v>
+      </c>
+      <c r="D264" s="7" t="s">
+        <v>628</v>
+      </c>
       <c r="E264" s="7"/>
-      <c r="F264" s="4" t="s">
-        <v>20</v>
+      <c r="F264" s="5" t="s">
+        <v>541</v>
       </c>
       <c r="G264" s="26"/>
     </row>
-    <row r="265" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A265" s="2" t="s">
+    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A265" t="s">
         <v>510</v>
       </c>
-      <c r="B265" s="2" t="s">
-        <v>635</v>
-      </c>
-      <c r="C265" s="2" t="s">
-        <v>636</v>
+      <c r="B265" t="s">
+        <v>629</v>
+      </c>
+      <c r="C265" t="s">
+        <v>630</v>
       </c>
       <c r="D265" s="7"/>
       <c r="E265" s="7"/>
-      <c r="F265" s="5" t="s">
-        <v>20</v>
+      <c r="F265" t="s">
+        <v>29</v>
       </c>
       <c r="G265" s="26"/>
     </row>
-    <row r="266" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A266" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B266" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C266" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="D266" s="7"/>
       <c r="E266" s="7"/>
@@ -8813,54 +8836,54 @@
       </c>
       <c r="G266" s="26"/>
     </row>
-    <row r="267" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A267" t="s">
+    <row r="267" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A267" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B267" t="s">
-        <v>639</v>
-      </c>
-      <c r="C267" t="s">
-        <v>640</v>
+      <c r="B267" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C267" s="2" t="s">
+        <v>634</v>
       </c>
       <c r="D267" s="7"/>
       <c r="E267" s="7"/>
-      <c r="F267" t="s">
-        <v>29</v>
+      <c r="F267" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G267" s="26"/>
     </row>
-    <row r="268" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A268" t="s">
+    <row r="268" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A268" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B268" t="s">
-        <v>641</v>
-      </c>
-      <c r="C268" t="s">
-        <v>642</v>
+      <c r="B268" s="2" t="s">
+        <v>635</v>
+      </c>
+      <c r="C268" s="2" t="s">
+        <v>636</v>
       </c>
       <c r="D268" s="7"/>
       <c r="E268" s="7"/>
-      <c r="F268" t="s">
+      <c r="F268" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G268" s="26"/>
     </row>
-    <row r="269" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A269" t="s">
+    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A269" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B269" t="s">
-        <v>643</v>
-      </c>
-      <c r="C269" t="s">
-        <v>644</v>
+      <c r="B269" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="C269" s="2" t="s">
+        <v>638</v>
       </c>
       <c r="D269" s="7"/>
       <c r="E269" s="7"/>
-      <c r="F269" t="s">
-        <v>20</v>
+      <c r="F269" s="4" t="s">
+        <v>29</v>
       </c>
       <c r="G269" s="26"/>
     </row>
@@ -8869,10 +8892,10 @@
         <v>510</v>
       </c>
       <c r="B270" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="C270" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
       <c r="D270" s="7"/>
       <c r="E270" s="7"/>
@@ -8886,15 +8909,15 @@
         <v>510</v>
       </c>
       <c r="B271" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="C271" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="D271" s="7"/>
       <c r="E271" s="7"/>
       <c r="F271" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G271" s="26"/>
     </row>
@@ -8903,128 +8926,122 @@
         <v>510</v>
       </c>
       <c r="B272" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="C272" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="D272" s="7"/>
       <c r="E272" s="7"/>
       <c r="F272" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="G272" s="26"/>
     </row>
-    <row r="273" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A273" t="s">
         <v>510</v>
       </c>
       <c r="B273" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="C273" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="D273" s="7"/>
       <c r="E273" s="7"/>
       <c r="F273" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G273" s="26"/>
     </row>
-    <row r="274" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A274" t="s">
         <v>510</v>
       </c>
       <c r="B274" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
       <c r="C274" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D274" s="7"/>
       <c r="E274" s="7"/>
       <c r="F274" t="s">
-        <v>14</v>
-      </c>
-      <c r="G274" s="26" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="275" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="G274" s="26"/>
+    </row>
+    <row r="275" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A275" t="s">
         <v>510</v>
       </c>
       <c r="B275" t="s">
-        <v>656</v>
+        <v>649</v>
       </c>
       <c r="C275" t="s">
-        <v>657</v>
+        <v>650</v>
       </c>
       <c r="D275" s="7"/>
       <c r="E275" s="7"/>
       <c r="F275" t="s">
-        <v>14</v>
-      </c>
-      <c r="G275" s="26" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="276" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A276" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G275" s="26"/>
+    </row>
+    <row r="276" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A276" t="s">
         <v>510</v>
       </c>
-      <c r="B276" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="C276" s="2" t="s">
-        <v>659</v>
+      <c r="B276" t="s">
+        <v>651</v>
+      </c>
+      <c r="C276" t="s">
+        <v>652</v>
       </c>
       <c r="D276" s="7"/>
       <c r="E276" s="7"/>
-      <c r="F276" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G276" s="26" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="277" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A277" s="2" t="s">
+      <c r="F276" t="s">
+        <v>10</v>
+      </c>
+      <c r="G276" s="26"/>
+    </row>
+    <row r="277" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A277" t="s">
         <v>510</v>
       </c>
-      <c r="B277" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C277" s="2" t="s">
-        <v>662</v>
+      <c r="B277" t="s">
+        <v>653</v>
+      </c>
+      <c r="C277" t="s">
+        <v>654</v>
       </c>
       <c r="D277" s="7"/>
       <c r="E277" s="7"/>
-      <c r="F277" s="5" t="s">
+      <c r="F277" t="s">
         <v>14</v>
       </c>
       <c r="G277" s="26" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A278" s="17" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A278" t="s">
         <v>510</v>
       </c>
-      <c r="B278" s="17" t="s">
-        <v>664</v>
-      </c>
-      <c r="C278" s="17" t="s">
-        <v>665</v>
-      </c>
-      <c r="D278" s="27"/>
-      <c r="E278" s="27"/>
-      <c r="F278" s="18" t="s">
+      <c r="B278" t="s">
+        <v>656</v>
+      </c>
+      <c r="C278" t="s">
+        <v>657</v>
+      </c>
+      <c r="D278" s="7"/>
+      <c r="E278" s="7"/>
+      <c r="F278" t="s">
         <v>14</v>
       </c>
-      <c r="G278" s="28" t="s">
-        <v>666</v>
+      <c r="G278" s="26" t="s">
+        <v>655</v>
       </c>
     </row>
     <row r="279" spans="1:7" x14ac:dyDescent="0.35">
@@ -9032,10 +9049,10 @@
         <v>510</v>
       </c>
       <c r="B279" s="2" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="C279" s="2" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="D279" s="7"/>
       <c r="E279" s="7"/>
@@ -9043,129 +9060,131 @@
         <v>14</v>
       </c>
       <c r="G279" s="26" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" x14ac:dyDescent="0.35">
+        <v>660</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A280" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B280" s="2" t="s">
-        <v>669</v>
+        <v>661</v>
       </c>
       <c r="C280" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="D280" s="1"/>
+        <v>662</v>
+      </c>
+      <c r="D280" s="7"/>
       <c r="E280" s="7"/>
-      <c r="F280" s="3" t="s">
+      <c r="F280" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G280" s="26" t="s">
-        <v>655</v>
+        <v>663</v>
       </c>
     </row>
     <row r="281" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A281" s="2" t="s">
+      <c r="A281" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="B281" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="C281" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="D281" s="1"/>
-      <c r="E281" s="7"/>
-      <c r="F281" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G281" s="26"/>
-    </row>
-    <row r="282" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B281" s="17" t="s">
+        <v>664</v>
+      </c>
+      <c r="C281" s="17" t="s">
+        <v>665</v>
+      </c>
+      <c r="D281" s="27"/>
+      <c r="E281" s="27"/>
+      <c r="F281" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G281" s="28" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A282" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>673</v>
+        <v>667</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>674</v>
+        <v>668</v>
       </c>
       <c r="D282" s="7"/>
       <c r="E282" s="7"/>
       <c r="F282" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G282" s="26"/>
-    </row>
-    <row r="283" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+      <c r="G282" s="26" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A283" s="2" t="s">
-        <v>675</v>
+        <v>510</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>676</v>
+        <v>669</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="D283" s="7"/>
+        <v>670</v>
+      </c>
+      <c r="D283" s="1"/>
       <c r="E283" s="7"/>
       <c r="F283" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G283" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="G283" s="26" t="s">
+        <v>655</v>
+      </c>
     </row>
     <row r="284" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A284" s="2" t="s">
-        <v>675</v>
+        <v>510</v>
       </c>
       <c r="B284" s="2" t="s">
-        <v>678</v>
+        <v>671</v>
       </c>
       <c r="C284" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="D284" s="7" t="s">
-        <v>680</v>
-      </c>
+        <v>672</v>
+      </c>
+      <c r="D284" s="1"/>
       <c r="E284" s="7"/>
       <c r="F284" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G284" s="26"/>
     </row>
     <row r="285" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A285" s="2" t="s">
-        <v>675</v>
+        <v>510</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>681</v>
+        <v>673</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="D285" s="7" t="s">
-        <v>683</v>
-      </c>
+        <v>674</v>
+      </c>
+      <c r="D285" s="7"/>
       <c r="E285" s="7"/>
       <c r="F285" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G285" s="26"/>
     </row>
-    <row r="286" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A286" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>684</v>
+        <v>676</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="D286" s="1"/>
-      <c r="E286" s="1"/>
+        <v>677</v>
+      </c>
+      <c r="D286" s="7"/>
+      <c r="E286" s="7"/>
       <c r="F286" s="3" t="s">
         <v>10</v>
       </c>
@@ -9176,550 +9195,548 @@
         <v>675</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D287" s="7"/>
+        <v>679</v>
+      </c>
+      <c r="D287" s="7" t="s">
+        <v>680</v>
+      </c>
       <c r="E287" s="7"/>
       <c r="F287" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G287" s="26"/>
     </row>
-    <row r="288" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="288" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A288" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>688</v>
+        <v>681</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="D288" s="7"/>
+        <v>682</v>
+      </c>
+      <c r="D288" s="7" t="s">
+        <v>683</v>
+      </c>
       <c r="E288" s="7"/>
       <c r="F288" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G288" s="26"/>
     </row>
-    <row r="289" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A289" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="D289" s="7"/>
-      <c r="E289" s="7"/>
-      <c r="F289" s="16" t="s">
+        <v>685</v>
+      </c>
+      <c r="D289" s="1"/>
+      <c r="E289" s="1"/>
+      <c r="F289" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G289" s="24"/>
-    </row>
-    <row r="290" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G289" s="26"/>
+    </row>
+    <row r="290" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A290" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B290" s="2" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="C290" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="D290" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="E290" s="7" t="s">
-        <v>695</v>
-      </c>
+        <v>687</v>
+      </c>
+      <c r="D290" s="7"/>
+      <c r="E290" s="7"/>
       <c r="F290" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G290" s="26"/>
     </row>
-    <row r="291" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A291" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>695</v>
+        <v>688</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>696</v>
+        <v>689</v>
       </c>
       <c r="D291" s="7"/>
       <c r="E291" s="7"/>
-      <c r="F291" s="6" t="s">
+      <c r="F291" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G291" s="24"/>
-    </row>
-    <row r="292" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G291" s="26"/>
+    </row>
+    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A292" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>697</v>
+        <v>690</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>698</v>
+        <v>691</v>
       </c>
       <c r="D292" s="7"/>
-      <c r="E292" s="1"/>
-      <c r="F292" s="3" t="s">
+      <c r="E292" s="7"/>
+      <c r="F292" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="G292" s="26"/>
-    </row>
-    <row r="293" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G292" s="24"/>
+    </row>
+    <row r="293" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A293" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>700</v>
-      </c>
-      <c r="D293" s="7"/>
-      <c r="E293" s="7"/>
-      <c r="F293" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G293" s="26" t="s">
-        <v>701</v>
-      </c>
+        <v>693</v>
+      </c>
+      <c r="D293" s="1" t="s">
+        <v>694</v>
+      </c>
+      <c r="E293" s="7" t="s">
+        <v>695</v>
+      </c>
+      <c r="F293" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G293" s="26"/>
     </row>
     <row r="294" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A294" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>702</v>
+        <v>695</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="D294" s="7" t="s">
-        <v>704</v>
-      </c>
+        <v>696</v>
+      </c>
+      <c r="D294" s="7"/>
       <c r="E294" s="7"/>
-      <c r="F294" s="5"/>
-      <c r="G294" s="26"/>
+      <c r="F294" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G294" s="24"/>
     </row>
     <row r="295" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A295" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B295" s="2" t="s">
-        <v>705</v>
+        <v>697</v>
       </c>
       <c r="C295" s="2" t="s">
-        <v>706</v>
+        <v>698</v>
       </c>
       <c r="D295" s="7"/>
-      <c r="E295" s="7"/>
-      <c r="F295" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G295" s="26" t="s">
-        <v>707</v>
-      </c>
+      <c r="E295" s="1"/>
+      <c r="F295" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G295" s="26"/>
     </row>
     <row r="296" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A296" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B296" s="2" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="C296" s="2" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="D296" s="7"/>
-      <c r="E296" s="7" t="s">
-        <v>697</v>
-      </c>
+      <c r="E296" s="7"/>
       <c r="F296" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G296" s="26"/>
-    </row>
-    <row r="297" spans="1:7" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="G296" s="26" t="s">
+        <v>701</v>
+      </c>
+    </row>
+    <row r="297" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A297" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B297" s="2" t="s">
-        <v>710</v>
+        <v>702</v>
       </c>
       <c r="C297" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="D297" s="7"/>
+        <v>703</v>
+      </c>
+      <c r="D297" s="7" t="s">
+        <v>704</v>
+      </c>
       <c r="E297" s="7"/>
-      <c r="F297" s="3" t="s">
-        <v>20</v>
-      </c>
+      <c r="F297" s="5"/>
       <c r="G297" s="26"/>
     </row>
-    <row r="298" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A298" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B298" s="2" t="s">
-        <v>712</v>
+        <v>705</v>
       </c>
       <c r="C298" s="2" t="s">
-        <v>713</v>
+        <v>706</v>
       </c>
       <c r="D298" s="7"/>
       <c r="E298" s="7"/>
-      <c r="F298" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G298" s="24"/>
-    </row>
-    <row r="299" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F298" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G298" s="26" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="299" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A299" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B299" s="2" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="C299" s="2" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="D299" s="7"/>
-      <c r="E299" s="7"/>
-      <c r="F299" s="19" t="s">
+      <c r="E299" s="7" t="s">
+        <v>697</v>
+      </c>
+      <c r="F299" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G299" s="26"/>
+    </row>
+    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A300" s="2" t="s">
+        <v>675</v>
+      </c>
+      <c r="B300" s="2" t="s">
+        <v>710</v>
+      </c>
+      <c r="C300" s="2" t="s">
+        <v>711</v>
+      </c>
+      <c r="D300" s="7"/>
+      <c r="E300" s="7"/>
+      <c r="F300" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G299" s="26"/>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A300" s="17" t="s">
-        <v>675</v>
-      </c>
-      <c r="B300" s="17" t="s">
-        <v>716</v>
-      </c>
-      <c r="C300" s="17" t="s">
-        <v>717</v>
-      </c>
-      <c r="D300" s="27"/>
-      <c r="E300" s="27"/>
-      <c r="F300" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G300" s="28"/>
-    </row>
-    <row r="301" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G300" s="26"/>
+    </row>
+    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A301" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B301" s="2" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="C301" s="2" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="D301" s="7"/>
       <c r="E301" s="7"/>
-      <c r="F301" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G301" s="26"/>
+      <c r="F301" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G301" s="24"/>
     </row>
     <row r="302" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A302" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D302" s="7"/>
-      <c r="E302" s="1"/>
-      <c r="F302" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G302" s="26" t="s">
-        <v>722</v>
-      </c>
+      <c r="E302" s="7"/>
+      <c r="F302" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G302" s="26"/>
     </row>
     <row r="303" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A303" s="2" t="s">
+      <c r="A303" s="17" t="s">
         <v>675</v>
       </c>
-      <c r="B303" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="C303" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="D303" s="7"/>
-      <c r="E303" s="7"/>
-      <c r="F303" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G303" s="26"/>
+      <c r="B303" s="17" t="s">
+        <v>716</v>
+      </c>
+      <c r="C303" s="17" t="s">
+        <v>717</v>
+      </c>
+      <c r="D303" s="27"/>
+      <c r="E303" s="27"/>
+      <c r="F303" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G303" s="28"/>
     </row>
     <row r="304" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A304" s="2" t="s">
         <v>675</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>725</v>
+        <v>718</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>726</v>
+        <v>719</v>
       </c>
       <c r="D304" s="7"/>
       <c r="E304" s="7"/>
-      <c r="F304" s="16" t="s">
+      <c r="F304" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G304" s="24"/>
+      <c r="G304" s="26"/>
     </row>
     <row r="305" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A305" s="2" t="s">
-        <v>727</v>
+        <v>675</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>728</v>
+        <v>720</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>729</v>
+        <v>721</v>
       </c>
       <c r="D305" s="7"/>
-      <c r="E305" s="7"/>
-      <c r="F305" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G305" s="26"/>
+      <c r="E305" s="1"/>
+      <c r="F305" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G305" s="26" t="s">
+        <v>722</v>
+      </c>
     </row>
     <row r="306" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A306" s="2" t="s">
-        <v>727</v>
+        <v>675</v>
       </c>
       <c r="B306" s="2" t="s">
-        <v>730</v>
+        <v>723</v>
       </c>
       <c r="C306" s="2" t="s">
-        <v>731</v>
+        <v>724</v>
       </c>
       <c r="D306" s="7"/>
-      <c r="E306" s="7" t="s">
-        <v>732</v>
-      </c>
+      <c r="E306" s="7"/>
       <c r="F306" s="5" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G306" s="26"/>
     </row>
-    <row r="307" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A307" s="2" t="s">
-        <v>727</v>
+        <v>675</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>733</v>
+        <v>725</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>734</v>
+        <v>726</v>
       </c>
       <c r="D307" s="7"/>
       <c r="E307" s="7"/>
-      <c r="F307" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G307" s="26"/>
+      <c r="F307" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G307" s="24"/>
     </row>
     <row r="308" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A308" s="2" t="s">
         <v>727</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>735</v>
+        <v>728</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>736</v>
+        <v>729</v>
       </c>
       <c r="D308" s="7"/>
       <c r="E308" s="7"/>
-      <c r="F308" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G308" s="26" t="s">
-        <v>737</v>
-      </c>
+      <c r="F308" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G308" s="26"/>
     </row>
     <row r="309" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A309" s="17" t="s">
+      <c r="A309" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="B309" s="17" t="s">
-        <v>738</v>
-      </c>
-      <c r="C309" s="17" t="s">
-        <v>739</v>
-      </c>
-      <c r="D309" s="27"/>
-      <c r="E309" s="27"/>
-      <c r="F309" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G309" s="28"/>
-    </row>
-    <row r="310" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B309" s="2" t="s">
+        <v>730</v>
+      </c>
+      <c r="C309" s="2" t="s">
+        <v>731</v>
+      </c>
+      <c r="D309" s="7"/>
+      <c r="E309" s="7" t="s">
+        <v>732</v>
+      </c>
+      <c r="F309" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G309" s="26"/>
+    </row>
+    <row r="310" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A310" s="2" t="s">
         <v>727</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>740</v>
+        <v>733</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>741</v>
+        <v>734</v>
       </c>
       <c r="D310" s="7"/>
       <c r="E310" s="7"/>
-      <c r="F310" s="6" t="s">
+      <c r="F310" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G310" s="24"/>
+      <c r="G310" s="26"/>
     </row>
     <row r="311" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A311" s="2" t="s">
         <v>727</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>742</v>
+        <v>735</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>743</v>
+        <v>736</v>
       </c>
       <c r="D311" s="7"/>
       <c r="E311" s="7"/>
-      <c r="F311" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G311" s="24"/>
-    </row>
-    <row r="312" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A312" s="2" t="s">
+      <c r="F311" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G311" s="26" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A312" s="17" t="s">
         <v>727</v>
       </c>
-      <c r="B312" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="C312" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="D312" s="7"/>
-      <c r="E312" s="7"/>
-      <c r="F312" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G312" s="24"/>
-    </row>
-    <row r="313" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="B312" s="17" t="s">
+        <v>738</v>
+      </c>
+      <c r="C312" s="17" t="s">
+        <v>739</v>
+      </c>
+      <c r="D312" s="27"/>
+      <c r="E312" s="27"/>
+      <c r="F312" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G312" s="28"/>
+    </row>
+    <row r="313" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A313" s="2" t="s">
         <v>727</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>732</v>
+        <v>740</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>746</v>
+        <v>741</v>
       </c>
       <c r="D313" s="7"/>
       <c r="E313" s="7"/>
       <c r="F313" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G313" s="24"/>
     </row>
-    <row r="314" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A314" s="17" t="s">
-        <v>747</v>
-      </c>
-      <c r="B314" s="17" t="s">
-        <v>748</v>
-      </c>
-      <c r="C314" s="17" t="s">
-        <v>749</v>
-      </c>
-      <c r="D314" s="27"/>
-      <c r="E314" s="27"/>
-      <c r="F314" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="G314" s="28" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="315" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A314" s="2" t="s">
+        <v>727</v>
+      </c>
+      <c r="B314" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="C314" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="D314" s="7"/>
+      <c r="E314" s="7"/>
+      <c r="F314" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G314" s="24"/>
+    </row>
+    <row r="315" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A315" s="2" t="s">
-        <v>747</v>
+        <v>727</v>
       </c>
       <c r="B315" s="2" t="s">
-        <v>751</v>
+        <v>744</v>
       </c>
       <c r="C315" s="2" t="s">
-        <v>752</v>
+        <v>745</v>
       </c>
       <c r="D315" s="7"/>
       <c r="E315" s="7"/>
-      <c r="F315" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G315" s="26" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="316" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F315" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G315" s="24"/>
+    </row>
+    <row r="316" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A316" s="2" t="s">
-        <v>747</v>
+        <v>727</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>754</v>
+        <v>732</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="D316" s="7"/>
       <c r="E316" s="7"/>
-      <c r="F316" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G316" s="26" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="317" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A317" s="2" t="s">
+      <c r="F316" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G316" s="24"/>
+    </row>
+    <row r="317" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A317" s="17" t="s">
         <v>747</v>
       </c>
-      <c r="B317" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="C317" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="D317" s="7"/>
-      <c r="E317" s="7"/>
-      <c r="F317" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G317" s="26" t="s">
-        <v>759</v>
+      <c r="B317" s="17" t="s">
+        <v>748</v>
+      </c>
+      <c r="C317" s="17" t="s">
+        <v>749</v>
+      </c>
+      <c r="D317" s="27"/>
+      <c r="E317" s="27"/>
+      <c r="F317" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="G317" s="28" t="s">
+        <v>750</v>
       </c>
     </row>
     <row r="318" spans="1:7" x14ac:dyDescent="0.35">
@@ -9727,83 +9744,89 @@
         <v>747</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="D318" s="7"/>
       <c r="E318" s="7"/>
-      <c r="F318" s="5" t="s">
+      <c r="F318" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G318" s="26"/>
+      <c r="G318" s="26" t="s">
+        <v>753</v>
+      </c>
     </row>
     <row r="319" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A319" s="2" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="D319" s="7"/>
       <c r="E319" s="7"/>
-      <c r="F319" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G319" s="26"/>
-    </row>
-    <row r="320" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F319" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G319" s="26" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="320" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A320" s="2" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="B320" s="2" t="s">
-        <v>1000</v>
+        <v>757</v>
       </c>
       <c r="C320" s="2" t="s">
-        <v>1001</v>
+        <v>758</v>
       </c>
       <c r="D320" s="7"/>
       <c r="E320" s="7"/>
       <c r="F320" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G320" s="26"/>
+        <v>25</v>
+      </c>
+      <c r="G320" s="26" t="s">
+        <v>759</v>
+      </c>
     </row>
     <row r="321" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A321" s="2" t="s">
-        <v>762</v>
+        <v>747</v>
       </c>
       <c r="B321" s="2" t="s">
-        <v>765</v>
+        <v>760</v>
       </c>
       <c r="C321" s="2" t="s">
-        <v>766</v>
+        <v>761</v>
       </c>
       <c r="D321" s="7"/>
       <c r="E321" s="7"/>
       <c r="F321" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G321" s="26"/>
     </row>
-    <row r="322" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A322" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>767</v>
+        <v>763</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="D322" s="7"/>
       <c r="E322" s="7"/>
       <c r="F322" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G322" s="26"/>
     </row>
@@ -9812,10 +9835,10 @@
         <v>762</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>769</v>
+        <v>1000</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>770</v>
+        <v>1001</v>
       </c>
       <c r="D323" s="7"/>
       <c r="E323" s="7"/>
@@ -9829,15 +9852,15 @@
         <v>762</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="D324" s="7"/>
       <c r="E324" s="7"/>
       <c r="F324" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G324" s="26"/>
     </row>
@@ -9846,31 +9869,31 @@
         <v>762</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="D325" s="7"/>
       <c r="E325" s="7"/>
-      <c r="F325" s="3" t="s">
+      <c r="F325" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G325" s="26"/>
     </row>
-    <row r="326" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A326" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="D326" s="7"/>
       <c r="E326" s="7"/>
-      <c r="F326" s="3" t="s">
+      <c r="F326" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G326" s="26"/>
@@ -9880,27 +9903,27 @@
         <v>762</v>
       </c>
       <c r="B327" s="2" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="C327" s="2" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="D327" s="7"/>
-      <c r="E327" s="1"/>
+      <c r="E327" s="7"/>
       <c r="F327" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G327" s="26"/>
     </row>
-    <row r="328" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A328" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="D328" s="7"/>
       <c r="E328" s="7"/>
@@ -9914,32 +9937,32 @@
         <v>762</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="D329" s="7"/>
       <c r="E329" s="7"/>
-      <c r="F329" s="5" t="s">
-        <v>10</v>
+      <c r="F329" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="G329" s="26"/>
     </row>
-    <row r="330" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A330" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="D330" s="7"/>
-      <c r="E330" s="7"/>
+      <c r="E330" s="1"/>
       <c r="F330" s="5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G330" s="26"/>
     </row>
@@ -9948,29 +9971,27 @@
         <v>762</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>1049</v>
+        <v>779</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>1050</v>
+        <v>780</v>
       </c>
       <c r="D331" s="7"/>
       <c r="E331" s="7"/>
-      <c r="F331" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G331" s="26" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="332" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F331" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G331" s="26"/>
+    </row>
+    <row r="332" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A332" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>785</v>
+        <v>781</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>786</v>
+        <v>782</v>
       </c>
       <c r="D332" s="7"/>
       <c r="E332" s="7"/>
@@ -9979,119 +10000,119 @@
       </c>
       <c r="G332" s="26"/>
     </row>
-    <row r="333" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A333" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>787</v>
+        <v>783</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>788</v>
+        <v>784</v>
       </c>
       <c r="D333" s="7"/>
       <c r="E333" s="7"/>
       <c r="F333" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G333" s="26"/>
     </row>
-    <row r="334" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A334" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>789</v>
+        <v>1049</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="D334" s="1"/>
+        <v>1050</v>
+      </c>
+      <c r="D334" s="7"/>
       <c r="E334" s="7"/>
       <c r="F334" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G334" s="26"/>
-    </row>
-    <row r="335" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="G334" s="26" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A335" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="D335" s="7"/>
       <c r="E335" s="7"/>
       <c r="F335" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G335" s="26"/>
     </row>
-    <row r="336" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A336" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="D336" s="7"/>
       <c r="E336" s="7"/>
-      <c r="F336" s="3" t="s">
+      <c r="F336" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G336" s="26"/>
     </row>
-    <row r="337" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A337" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="D337" s="7" t="s">
-        <v>797</v>
-      </c>
+        <v>790</v>
+      </c>
+      <c r="D337" s="1"/>
       <c r="E337" s="7"/>
-      <c r="F337" s="3" t="s">
+      <c r="F337" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G337" s="26"/>
     </row>
-    <row r="338" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A338" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>798</v>
+        <v>791</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>799</v>
+        <v>792</v>
       </c>
       <c r="D338" s="7"/>
       <c r="E338" s="7"/>
-      <c r="F338" s="3" t="s">
+      <c r="F338" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G338" s="26"/>
     </row>
-    <row r="339" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A339" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>800</v>
+        <v>793</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>801</v>
+        <v>794</v>
       </c>
       <c r="D339" s="7"/>
       <c r="E339" s="7"/>
@@ -10100,141 +10121,141 @@
       </c>
       <c r="G339" s="26"/>
     </row>
-    <row r="340" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A340" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>802</v>
+        <v>795</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="D340" s="7"/>
+        <v>796</v>
+      </c>
+      <c r="D340" s="7" t="s">
+        <v>797</v>
+      </c>
       <c r="E340" s="7"/>
-      <c r="F340" s="4" t="s">
-        <v>10</v>
+      <c r="F340" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G340" s="26"/>
     </row>
-    <row r="341" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A341" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
       <c r="D341" s="7"/>
       <c r="E341" s="7"/>
-      <c r="F341" s="4" t="s">
-        <v>10</v>
+      <c r="F341" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G341" s="26"/>
     </row>
-    <row r="342" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A342" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="D342" s="7"/>
       <c r="E342" s="7"/>
-      <c r="F342" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G342" s="24"/>
+      <c r="F342" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G342" s="26"/>
     </row>
     <row r="343" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A343" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
       <c r="D343" s="7"/>
       <c r="E343" s="7"/>
-      <c r="F343" s="5" t="s">
+      <c r="F343" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G343" s="26"/>
     </row>
-    <row r="344" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A344" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="D344" s="7"/>
       <c r="E344" s="7"/>
-      <c r="F344" s="5" t="s">
-        <v>29</v>
+      <c r="F344" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G344" s="26"/>
     </row>
-    <row r="345" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A345" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
       <c r="D345" s="7"/>
       <c r="E345" s="7"/>
-      <c r="F345" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G345" s="26"/>
+      <c r="F345" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G345" s="24"/>
     </row>
     <row r="346" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A346" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="D346" s="7"/>
       <c r="E346" s="7"/>
-      <c r="F346" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="G346" s="26" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="347" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F346" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G346" s="26"/>
+    </row>
+    <row r="347" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A347" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>818</v>
+        <v>810</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="D347" s="1"/>
+        <v>811</v>
+      </c>
+      <c r="D347" s="7"/>
       <c r="E347" s="7"/>
       <c r="F347" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G347" s="26"/>
     </row>
@@ -10243,15 +10264,15 @@
         <v>762</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>820</v>
+        <v>812</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>821</v>
+        <v>813</v>
       </c>
       <c r="D348" s="7"/>
       <c r="E348" s="7"/>
-      <c r="F348" s="4" t="s">
-        <v>20</v>
+      <c r="F348" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G348" s="26"/>
     </row>
@@ -10260,89 +10281,89 @@
         <v>762</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>1040</v>
+        <v>814</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D349" s="7" t="s">
-        <v>1042</v>
-      </c>
+        <v>815</v>
+      </c>
+      <c r="D349" s="7"/>
       <c r="E349" s="7"/>
-      <c r="F349" s="5" t="s">
-        <v>29</v>
+      <c r="F349" s="4" t="s">
+        <v>816</v>
       </c>
       <c r="G349" s="26" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="350" spans="1:7" x14ac:dyDescent="0.35">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="350" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A350" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>822</v>
+        <v>818</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="D350" s="7"/>
+        <v>819</v>
+      </c>
+      <c r="D350" s="1"/>
       <c r="E350" s="7"/>
-      <c r="F350" s="4" t="s">
+      <c r="F350" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G350" s="26"/>
     </row>
-    <row r="351" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A351" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>824</v>
+        <v>820</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>825</v>
+        <v>821</v>
       </c>
       <c r="D351" s="7"/>
       <c r="E351" s="7"/>
-      <c r="F351" s="5" t="s">
-        <v>29</v>
+      <c r="F351" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G351" s="26"/>
     </row>
-    <row r="352" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A352" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>826</v>
+        <v>1040</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>827</v>
+        <v>1041</v>
       </c>
       <c r="D352" s="7" t="s">
-        <v>828</v>
+        <v>1042</v>
       </c>
       <c r="E352" s="7"/>
-      <c r="F352" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G352" s="26"/>
-    </row>
-    <row r="353" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F352" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G352" s="26" t="s">
+        <v>1043</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A353" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>829</v>
+        <v>822</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>830</v>
+        <v>823</v>
       </c>
       <c r="D353" s="7"/>
       <c r="E353" s="7"/>
-      <c r="F353" s="3" t="s">
-        <v>29</v>
+      <c r="F353" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G353" s="26"/>
     </row>
@@ -10351,10 +10372,10 @@
         <v>762</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>831</v>
+        <v>824</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>832</v>
+        <v>825</v>
       </c>
       <c r="D354" s="7"/>
       <c r="E354" s="7"/>
@@ -10363,307 +10384,307 @@
       </c>
       <c r="G354" s="26"/>
     </row>
-    <row r="355" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A355" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B355" s="2" t="s">
-        <v>833</v>
+        <v>826</v>
       </c>
       <c r="C355" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="D355" s="7"/>
+        <v>827</v>
+      </c>
+      <c r="D355" s="7" t="s">
+        <v>828</v>
+      </c>
       <c r="E355" s="7"/>
-      <c r="F355" s="16" t="s">
+      <c r="F355" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G355" s="24"/>
-    </row>
-    <row r="356" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G355" s="26"/>
+    </row>
+    <row r="356" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A356" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="D356" s="7"/>
       <c r="E356" s="7"/>
-      <c r="F356" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G356" s="24"/>
-    </row>
-    <row r="357" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F356" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G356" s="26"/>
+    </row>
+    <row r="357" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A357" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="D357" s="7"/>
       <c r="E357" s="7"/>
-      <c r="F357" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G357" s="24"/>
-    </row>
-    <row r="358" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F357" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G357" s="26"/>
+    </row>
+    <row r="358" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A358" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="D358" s="7"/>
-      <c r="E358" s="1"/>
-      <c r="F358" s="4" t="s">
+      <c r="E358" s="7"/>
+      <c r="F358" s="16" t="s">
         <v>20</v>
       </c>
-      <c r="G358" s="26"/>
-    </row>
-    <row r="359" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G358" s="24"/>
+    </row>
+    <row r="359" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A359" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="D359" s="7"/>
       <c r="E359" s="7"/>
-      <c r="F359" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G359" s="26" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="360" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F359" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G359" s="24"/>
+    </row>
+    <row r="360" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A360" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>844</v>
+        <v>837</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>845</v>
+        <v>838</v>
       </c>
       <c r="D360" s="7"/>
       <c r="E360" s="7"/>
-      <c r="F360" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G360" s="26" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="361" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F360" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G360" s="24"/>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A361" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>846</v>
+        <v>839</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>847</v>
+        <v>840</v>
       </c>
       <c r="D361" s="7"/>
-      <c r="E361" s="7"/>
+      <c r="E361" s="1"/>
       <c r="F361" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G361" s="26" t="s">
-        <v>843</v>
-      </c>
+        <v>20</v>
+      </c>
+      <c r="G361" s="26"/>
     </row>
     <row r="362" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A362" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>1052</v>
+        <v>841</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>1053</v>
+        <v>842</v>
       </c>
       <c r="D362" s="7"/>
       <c r="E362" s="7"/>
       <c r="F362" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G362" s="26" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="363" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A363" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>848</v>
+        <v>844</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>849</v>
+        <v>845</v>
       </c>
       <c r="D363" s="7"/>
-      <c r="E363" s="7" t="s">
-        <v>793</v>
-      </c>
-      <c r="F363" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G363" s="24"/>
+      <c r="E363" s="7"/>
+      <c r="F363" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G363" s="26" t="s">
+        <v>843</v>
+      </c>
     </row>
     <row r="364" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A364" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="D364" s="7"/>
       <c r="E364" s="7"/>
-      <c r="F364" s="5" t="s">
-        <v>852</v>
-      </c>
-      <c r="G364" s="26"/>
-    </row>
-    <row r="365" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F364" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G364" s="26" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A365" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>1002</v>
+        <v>1052</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>1003</v>
+        <v>1053</v>
       </c>
       <c r="D365" s="7"/>
       <c r="E365" s="7"/>
       <c r="F365" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G365" s="26"/>
-    </row>
-    <row r="366" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="G365" s="26" t="s">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A366" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>853</v>
+        <v>848</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="D366" s="7"/>
-      <c r="E366" s="7"/>
-      <c r="F366" s="5" t="s">
+      <c r="E366" s="7" t="s">
+        <v>793</v>
+      </c>
+      <c r="F366" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G366" s="26"/>
-    </row>
-    <row r="367" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G366" s="24"/>
+    </row>
+    <row r="367" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A367" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>855</v>
+        <v>850</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>856</v>
+        <v>851</v>
       </c>
       <c r="D367" s="7"/>
       <c r="E367" s="7"/>
-      <c r="F367" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G367" s="24"/>
-    </row>
-    <row r="368" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F367" s="5" t="s">
+        <v>852</v>
+      </c>
+      <c r="G367" s="26"/>
+    </row>
+    <row r="368" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A368" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>857</v>
+        <v>1002</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>858</v>
+        <v>1003</v>
       </c>
       <c r="D368" s="7"/>
       <c r="E368" s="7"/>
-      <c r="F368" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G368" s="26" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="369" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F368" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G368" s="26"/>
+    </row>
+    <row r="369" spans="1:7" ht="29" x14ac:dyDescent="0.35">
       <c r="A369" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>860</v>
+        <v>853</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>861</v>
+        <v>854</v>
       </c>
       <c r="D369" s="7"/>
       <c r="E369" s="7"/>
       <c r="F369" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G369" s="26"/>
     </row>
-    <row r="370" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A370" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>862</v>
+        <v>855</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>863</v>
+        <v>856</v>
       </c>
       <c r="D370" s="7"/>
       <c r="E370" s="7"/>
-      <c r="F370" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G370" s="26"/>
+      <c r="F370" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G370" s="24"/>
     </row>
     <row r="371" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A371" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>864</v>
+        <v>857</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>865</v>
+        <v>858</v>
       </c>
       <c r="D371" s="7"/>
       <c r="E371" s="7"/>
-      <c r="F371" s="5" t="s">
-        <v>14</v>
+      <c r="F371" s="14" t="s">
+        <v>25</v>
       </c>
       <c r="G371" s="26" t="s">
-        <v>866</v>
+        <v>859</v>
       </c>
     </row>
     <row r="372" spans="1:7" x14ac:dyDescent="0.35">
@@ -10671,85 +10692,85 @@
         <v>762</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>867</v>
+        <v>860</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>868</v>
+        <v>861</v>
       </c>
       <c r="D372" s="7"/>
       <c r="E372" s="7"/>
-      <c r="F372" s="12" t="s">
+      <c r="F372" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G372" s="26"/>
     </row>
     <row r="373" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A373" t="s">
+      <c r="A373" s="2" t="s">
         <v>762</v>
       </c>
-      <c r="B373" t="s">
-        <v>869</v>
-      </c>
-      <c r="C373" t="s">
-        <v>870</v>
+      <c r="B373" s="2" t="s">
+        <v>862</v>
+      </c>
+      <c r="C373" s="2" t="s">
+        <v>863</v>
       </c>
       <c r="D373" s="7"/>
       <c r="E373" s="7"/>
-      <c r="F373" s="12" t="s">
-        <v>29</v>
+      <c r="F373" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G373" s="26"/>
     </row>
-    <row r="374" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A374" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>871</v>
+        <v>864</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>872</v>
+        <v>865</v>
       </c>
       <c r="D374" s="7"/>
-      <c r="E374" s="1"/>
+      <c r="E374" s="7"/>
       <c r="F374" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G374" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="G374" s="26" t="s">
+        <v>866</v>
+      </c>
     </row>
     <row r="375" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A375" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="D375" s="7"/>
       <c r="E375" s="7"/>
-      <c r="F375" s="5" t="s">
-        <v>37</v>
+      <c r="F375" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="G375" s="26"/>
     </row>
     <row r="376" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A376" s="2" t="s">
+      <c r="A376" t="s">
         <v>762</v>
       </c>
-      <c r="B376" s="2" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C376" s="2" t="s">
-        <v>1005</v>
+      <c r="B376" t="s">
+        <v>869</v>
+      </c>
+      <c r="C376" t="s">
+        <v>870</v>
       </c>
       <c r="D376" s="7"/>
-      <c r="E376" s="7" t="s">
-        <v>1006</v>
-      </c>
-      <c r="F376" s="5" t="s">
-        <v>20</v>
+      <c r="E376" s="7"/>
+      <c r="F376" s="12" t="s">
+        <v>29</v>
       </c>
       <c r="G376" s="26"/>
     </row>
@@ -10758,15 +10779,15 @@
         <v>762</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>875</v>
+        <v>871</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="D377" s="7"/>
-      <c r="E377" s="7"/>
-      <c r="F377" s="4" t="s">
-        <v>96</v>
+      <c r="E377" s="1"/>
+      <c r="F377" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G377" s="26"/>
     </row>
@@ -10775,177 +10796,177 @@
         <v>762</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>877</v>
+        <v>873</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>878</v>
+        <v>874</v>
       </c>
       <c r="D378" s="7"/>
-      <c r="E378" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="F378" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G378" s="24"/>
+      <c r="E378" s="7"/>
+      <c r="F378" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G378" s="26"/>
     </row>
     <row r="379" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A379" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B379" s="2" t="s">
-        <v>879</v>
+        <v>1004</v>
       </c>
       <c r="C379" s="2" t="s">
-        <v>880</v>
+        <v>1005</v>
       </c>
       <c r="D379" s="7"/>
-      <c r="E379" s="7"/>
-      <c r="F379" s="16" t="s">
+      <c r="E379" s="7" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F379" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="G379" s="24"/>
+      <c r="G379" s="26"/>
     </row>
     <row r="380" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A380" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B380" s="2" t="s">
-        <v>1045</v>
+        <v>875</v>
       </c>
       <c r="C380" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D380" s="7" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E380" s="7" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F380" s="5" t="s">
+        <v>876</v>
+      </c>
+      <c r="D380" s="7"/>
+      <c r="E380" s="7"/>
+      <c r="F380" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G380" s="26"/>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A381" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>877</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>878</v>
+      </c>
+      <c r="D381" s="7"/>
+      <c r="E381" s="7" t="s">
+        <v>873</v>
+      </c>
+      <c r="F381" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="G380" s="26" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="381" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A381" s="17" t="s">
-        <v>762</v>
-      </c>
-      <c r="B381" s="17" t="s">
-        <v>881</v>
-      </c>
-      <c r="C381" s="17" t="s">
-        <v>882</v>
-      </c>
-      <c r="D381" s="27"/>
-      <c r="E381" s="27"/>
-      <c r="F381" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G381" s="28"/>
+      <c r="G381" s="24"/>
     </row>
     <row r="382" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A382" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B382" s="2" t="s">
-        <v>883</v>
+        <v>879</v>
       </c>
       <c r="C382" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="D382" s="1"/>
+        <v>880</v>
+      </c>
+      <c r="D382" s="7"/>
       <c r="E382" s="7"/>
-      <c r="F382" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G382" s="26" t="s">
-        <v>885</v>
-      </c>
+      <c r="F382" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G382" s="24"/>
     </row>
     <row r="383" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A383" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B383" s="2" t="s">
-        <v>886</v>
+        <v>1045</v>
       </c>
       <c r="C383" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="D383" s="1"/>
-      <c r="E383" s="7"/>
+        <v>1046</v>
+      </c>
+      <c r="D383" s="7" t="s">
+        <v>1047</v>
+      </c>
+      <c r="E383" s="7" t="s">
+        <v>1044</v>
+      </c>
       <c r="F383" s="5" t="s">
-        <v>14</v>
+        <v>20</v>
       </c>
       <c r="G383" s="26" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="384" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A384" s="2" t="s">
+        <v>1048</v>
+      </c>
+    </row>
+    <row r="384" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A384" s="17" t="s">
         <v>762</v>
       </c>
-      <c r="B384" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="C384" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="D384" s="1"/>
-      <c r="E384" s="7"/>
-      <c r="F384" s="5" t="s">
+      <c r="B384" s="17" t="s">
+        <v>881</v>
+      </c>
+      <c r="C384" s="17" t="s">
+        <v>882</v>
+      </c>
+      <c r="D384" s="27"/>
+      <c r="E384" s="27"/>
+      <c r="F384" s="20" t="s">
         <v>29</v>
       </c>
-      <c r="G384" s="26"/>
+      <c r="G384" s="28"/>
     </row>
     <row r="385" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A385" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B385" s="2" t="s">
-        <v>1007</v>
+        <v>883</v>
       </c>
       <c r="C385" s="2" t="s">
-        <v>1008</v>
+        <v>884</v>
       </c>
       <c r="D385" s="1"/>
       <c r="E385" s="7"/>
       <c r="F385" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G385" s="26"/>
+        <v>10</v>
+      </c>
+      <c r="G385" s="26" t="s">
+        <v>885</v>
+      </c>
     </row>
     <row r="386" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A386" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B386" s="2" t="s">
-        <v>1009</v>
+        <v>886</v>
       </c>
       <c r="C386" s="2" t="s">
-        <v>1010</v>
+        <v>887</v>
       </c>
       <c r="D386" s="1"/>
-      <c r="E386" s="7" t="s">
-        <v>769</v>
-      </c>
+      <c r="E386" s="7"/>
       <c r="F386" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G386" s="26"/>
+        <v>14</v>
+      </c>
+      <c r="G386" s="26" t="s">
+        <v>888</v>
+      </c>
     </row>
     <row r="387" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A387" s="2" t="s">
         <v>762</v>
       </c>
       <c r="B387" s="2" t="s">
-        <v>1011</v>
+        <v>889</v>
       </c>
       <c r="C387" s="2" t="s">
-        <v>1012</v>
+        <v>890</v>
       </c>
       <c r="D387" s="1"/>
       <c r="E387" s="7"/>
@@ -10956,137 +10977,190 @@
     </row>
     <row r="388" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A388" s="2" t="s">
-        <v>891</v>
+        <v>762</v>
       </c>
       <c r="B388" s="2" t="s">
-        <v>892</v>
+        <v>1007</v>
       </c>
       <c r="C388" s="2" t="s">
-        <v>893</v>
-      </c>
-      <c r="D388" s="7" t="s">
-        <v>894</v>
-      </c>
+        <v>1008</v>
+      </c>
+      <c r="D388" s="1"/>
       <c r="E388" s="7"/>
-      <c r="F388" s="25" t="s">
-        <v>20</v>
+      <c r="F388" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G388" s="26"/>
     </row>
     <row r="389" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A389" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B389" s="2" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C389" s="2" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D389" s="1"/>
+      <c r="E389" s="7" t="s">
+        <v>769</v>
+      </c>
+      <c r="F389" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G389" s="26"/>
+    </row>
+    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A390" s="2" t="s">
+        <v>762</v>
+      </c>
+      <c r="B390" s="2" t="s">
+        <v>1011</v>
+      </c>
+      <c r="C390" s="2" t="s">
+        <v>1012</v>
+      </c>
+      <c r="D390" s="1"/>
+      <c r="E390" s="7"/>
+      <c r="F390" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G390" s="26"/>
+    </row>
+    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A391" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="B389" s="2" t="s">
+      <c r="B391" s="2" t="s">
+        <v>892</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>893</v>
+      </c>
+      <c r="D391" s="7" t="s">
+        <v>894</v>
+      </c>
+      <c r="E391" s="7"/>
+      <c r="F391" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G391" s="26"/>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A392" s="2" t="s">
+        <v>891</v>
+      </c>
+      <c r="B392" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="C389" s="2" t="s">
+      <c r="C392" s="2" t="s">
         <v>896</v>
       </c>
-      <c r="D389" s="7" t="s">
+      <c r="D392" s="7" t="s">
         <v>897</v>
       </c>
-      <c r="E389" s="7"/>
-      <c r="F389" s="4" t="s">
+      <c r="E392" s="7"/>
+      <c r="F392" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G389" s="26"/>
-    </row>
-    <row r="390" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A390" s="2" t="s">
+      <c r="G392" s="26"/>
+    </row>
+    <row r="393" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A393" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="B390" s="2" t="s">
+      <c r="B393" s="2" t="s">
         <v>898</v>
       </c>
-      <c r="C390" s="2" t="s">
+      <c r="C393" s="2" t="s">
         <v>899</v>
       </c>
-      <c r="D390" s="1" t="s">
+      <c r="D393" s="1" t="s">
         <v>900</v>
       </c>
-      <c r="E390" s="7"/>
-      <c r="F390" s="4" t="s">
+      <c r="E393" s="7"/>
+      <c r="F393" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G390" s="26"/>
-    </row>
-    <row r="391" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A391" s="17" t="s">
+      <c r="G393" s="26"/>
+    </row>
+    <row r="394" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="A394" s="17" t="s">
         <v>891</v>
       </c>
-      <c r="B391" s="17" t="s">
+      <c r="B394" s="17" t="s">
         <v>901</v>
       </c>
-      <c r="C391" s="17" t="s">
+      <c r="C394" s="17" t="s">
         <v>902</v>
       </c>
-      <c r="D391" s="27"/>
-      <c r="E391" s="27"/>
-      <c r="F391" s="18" t="s">
+      <c r="D394" s="27"/>
+      <c r="E394" s="27"/>
+      <c r="F394" s="18" t="s">
         <v>903</v>
       </c>
-      <c r="G391" s="28"/>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A392" t="s">
+      <c r="G394" s="28"/>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A395" t="s">
         <v>891</v>
       </c>
-      <c r="B392" t="s">
+      <c r="B395" t="s">
         <v>904</v>
       </c>
-      <c r="C392" t="s">
+      <c r="C395" t="s">
         <v>905</v>
       </c>
-      <c r="D392" s="7"/>
-      <c r="E392" s="7"/>
-      <c r="F392" t="s">
-        <v>29</v>
-      </c>
-      <c r="G392" s="26"/>
-    </row>
-    <row r="393" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A393" t="s">
-        <v>891</v>
-      </c>
-      <c r="B393" t="s">
-        <v>906</v>
-      </c>
-      <c r="C393" t="s">
-        <v>907</v>
-      </c>
-      <c r="D393" s="7" t="s">
-        <v>908</v>
-      </c>
-      <c r="E393" s="7"/>
-      <c r="F393" t="s">
-        <v>29</v>
-      </c>
-      <c r="G393" s="26"/>
-    </row>
-    <row r="394" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A394" t="s">
-        <v>891</v>
-      </c>
-      <c r="B394" t="s">
-        <v>909</v>
-      </c>
-      <c r="C394" t="s">
-        <v>910</v>
-      </c>
-      <c r="D394" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="E394" s="7"/>
-      <c r="F394" t="s">
-        <v>20</v>
-      </c>
-      <c r="G394" s="26"/>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D395" s="7"/>
       <c r="E395" s="7"/>
+      <c r="F395" t="s">
+        <v>29</v>
+      </c>
       <c r="G395" s="26"/>
+    </row>
+    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A396" t="s">
+        <v>891</v>
+      </c>
+      <c r="B396" t="s">
+        <v>906</v>
+      </c>
+      <c r="C396" t="s">
+        <v>907</v>
+      </c>
+      <c r="D396" s="7" t="s">
+        <v>908</v>
+      </c>
+      <c r="E396" s="7"/>
+      <c r="F396" t="s">
+        <v>29</v>
+      </c>
+      <c r="G396" s="26"/>
+    </row>
+    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A397" t="s">
+        <v>891</v>
+      </c>
+      <c r="B397" t="s">
+        <v>909</v>
+      </c>
+      <c r="C397" t="s">
+        <v>910</v>
+      </c>
+      <c r="D397" s="7" t="s">
+        <v>911</v>
+      </c>
+      <c r="E397" s="7"/>
+      <c r="F397" t="s">
+        <v>20</v>
+      </c>
+      <c r="G397" s="26"/>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="D398" s="7"/>
+      <c r="E398" s="7"/>
+      <c r="G398" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/InputData/acronym-key.xlsx
+++ b/InputData/acronym-key.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\.claude\worktrees\cement-carbonation\InputData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DanOBrien\Models\EPS\US\eps-us\.claude\worktrees\chemicals-module\InputData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B3B9215-A8A4-47AE-B11A-5F9A9C0DE123}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{86DAC0DB-1978-45C3-AA32-B34C73E2B959}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="390" yWindow="390" windowWidth="21600" windowHeight="12585" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1867" uniqueCount="1069">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1884" uniqueCount="1076">
   <si>
     <t>Top Level Folder</t>
   </si>
@@ -1830,18 +1830,6 @@
     <t>Import Export Substitution Elasticities</t>
   </si>
   <si>
-    <t>IFSR</t>
-  </si>
-  <si>
-    <t>Industrial Fuel Shifting Ratio</t>
-  </si>
-  <si>
-    <t>IFSRF</t>
-  </si>
-  <si>
-    <t>Industrial Feedstock Switching Recipient Fuel</t>
-  </si>
-  <si>
     <t>IFStE</t>
   </si>
   <si>
@@ -3229,6 +3217,39 @@
   </si>
   <si>
     <t>Historical Clinker Consumed by Vintage</t>
+  </si>
+  <si>
+    <t>ECCpTSCA</t>
+  </si>
+  <si>
+    <t>Electrified Heat Capital Cost per Ton per Year of Stack CO2 Abated</t>
+  </si>
+  <si>
+    <t>in InputData/indst/_chemicals/ (chemicals process CO2 levers)</t>
+  </si>
+  <si>
+    <t>EEpTSCA</t>
+  </si>
+  <si>
+    <t>Electricity per Ton of Stack CO2 Abated</t>
+  </si>
+  <si>
+    <t>HIR</t>
+  </si>
+  <si>
+    <t>Hydrogen Injection Ratio</t>
+  </si>
+  <si>
+    <t>SoCPCbP</t>
+  </si>
+  <si>
+    <t>Share of Chemicals Process CO2 by Pool</t>
+  </si>
+  <si>
+    <t>SoSVbFF</t>
+  </si>
+  <si>
+    <t>Share of Syngas Vent CO2 by Feedstock Fuel</t>
   </si>
 </sst>
 </file>
@@ -3712,326 +3733,326 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C70"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="10.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
         <v>912</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
         <v>913</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
         <v>915</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
         <v>916</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A8" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
         <v>917</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
         <v>918</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A10" t="s">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
         <v>919</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A11" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
         <v>920</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A12" t="s">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
         <v>921</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A13" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>923</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
         <v>10</v>
       </c>
       <c r="B19" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B20" t="s">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B21" t="s">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B22" t="s">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B23" t="s">
         <v>926</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B20" t="s">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B24" t="s">
         <v>927</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B21" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B22" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B23" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B24" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="B26" s="13" t="s">
         <v>37</v>
       </c>
       <c r="C26" t="s">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C27" t="s">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="C28" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A30" s="10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B30" t="s">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
         <v>932</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C27" t="s">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B32" t="s">
         <v>933</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="C28" t="s">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
         <v>934</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="A30" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="B30" t="s">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B34" t="s">
         <v>935</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B31" t="s">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
         <v>936</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B32" t="s">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
         <v>937</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B33" t="s">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
         <v>938</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B34" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B35" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B36" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B37" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39" s="9" t="s">
         <v>29</v>
       </c>
       <c r="B39" t="s">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B40" t="s">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B41" t="s">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B42" t="s">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B43" t="s">
         <v>943</v>
       </c>
     </row>
-    <row r="40" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B40" t="s">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B44" t="s">
         <v>944</v>
       </c>
     </row>
-    <row r="41" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B41" t="s">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B45" t="s">
         <v>945</v>
       </c>
     </row>
-    <row r="42" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B42" t="s">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="B46" t="s">
         <v>946</v>
       </c>
     </row>
-    <row r="43" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B43" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B44" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B45" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" x14ac:dyDescent="0.35">
-      <c r="B46" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48" s="15" t="s">
         <v>96</v>
       </c>
       <c r="B48" s="15"/>
       <c r="C48" s="15"/>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="B49" t="s">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B50" t="s">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B51" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B52" t="s">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B53" t="s">
         <v>951</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B50" t="s">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B54" t="s">
         <v>952</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B51" t="s">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B55" t="s">
         <v>953</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B52" t="s">
-        <v>954</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B53" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B54" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B55" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
         <v>25</v>
       </c>
       <c r="B57" t="s">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B58" t="s">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B59" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="B60" t="s">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A62" s="7" t="s">
         <v>958</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B58" t="s">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
         <v>959</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B59" t="s">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
         <v>960</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="B60" t="s">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
         <v>961</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A62" s="7" t="s">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
         <v>962</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A63" t="s">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
         <v>963</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A64" t="s">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
         <v>964</v>
       </c>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
         <v>965</v>
       </c>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A66" t="s">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
         <v>966</v>
-      </c>
-    </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A67" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A68" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A69" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A70" t="s">
-        <v>970</v>
       </c>
     </row>
   </sheetData>
@@ -4042,21 +4063,21 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:G398"/>
-  <sheetFormatPr defaultColWidth="8.81640625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:G401"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.54296875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="19.453125" style="2" customWidth="1"/>
-    <col min="3" max="3" width="51.26953125" style="2" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" style="2" customWidth="1"/>
+    <col min="2" max="2" width="19.42578125" style="2" customWidth="1"/>
+    <col min="3" max="3" width="51.28515625" style="2" customWidth="1"/>
     <col min="4" max="4" width="67" style="2" customWidth="1"/>
-    <col min="5" max="5" width="18.81640625" style="2" customWidth="1"/>
-    <col min="6" max="6" width="37.54296875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="18.85546875" style="2" customWidth="1"/>
+    <col min="6" max="6" width="37.5703125" style="2" customWidth="1"/>
     <col min="7" max="7" width="54" style="2" customWidth="1"/>
-    <col min="8" max="9" width="8.81640625" style="2" customWidth="1"/>
-    <col min="10" max="16384" width="8.81640625" style="2"/>
+    <col min="8" max="9" width="8.85546875" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="8.85546875" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="23" t="s">
         <v>0</v>
       </c>
@@ -4079,7 +4100,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>7</v>
       </c>
@@ -4098,7 +4119,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>7</v>
       </c>
@@ -4117,7 +4138,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>7</v>
       </c>
@@ -4136,7 +4157,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>7</v>
       </c>
@@ -4153,7 +4174,7 @@
       </c>
       <c r="G5" s="26"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>7</v>
       </c>
@@ -4170,7 +4191,7 @@
       </c>
       <c r="G6" s="26"/>
     </row>
-    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
@@ -4189,7 +4210,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
@@ -4206,7 +4227,7 @@
       </c>
       <c r="G8" s="26"/>
     </row>
-    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="17" t="s">
         <v>7</v>
       </c>
@@ -4223,7 +4244,7 @@
       </c>
       <c r="G9" s="28"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -4240,7 +4261,7 @@
       </c>
       <c r="G10" s="26"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>32</v>
       </c>
@@ -4257,7 +4278,7 @@
       </c>
       <c r="G11" s="26"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>32</v>
       </c>
@@ -4274,7 +4295,7 @@
       </c>
       <c r="G12" s="26"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>32</v>
       </c>
@@ -4291,7 +4312,7 @@
       </c>
       <c r="G13" s="26"/>
     </row>
-    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>32</v>
       </c>
@@ -4310,7 +4331,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>32</v>
       </c>
@@ -4327,7 +4348,7 @@
       </c>
       <c r="G15" s="26"/>
     </row>
-    <row r="16" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>32</v>
       </c>
@@ -4346,7 +4367,7 @@
       </c>
       <c r="G16" s="26"/>
     </row>
-    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>32</v>
       </c>
@@ -4365,7 +4386,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>32</v>
       </c>
@@ -4382,7 +4403,7 @@
       </c>
       <c r="G18" s="26"/>
     </row>
-    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>32</v>
       </c>
@@ -4401,7 +4422,7 @@
       </c>
       <c r="G19" s="26"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>32</v>
       </c>
@@ -4418,7 +4439,7 @@
       </c>
       <c r="G20" s="26"/>
     </row>
-    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
@@ -4435,7 +4456,7 @@
       </c>
       <c r="G21" s="26"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>32</v>
       </c>
@@ -4452,7 +4473,7 @@
       </c>
       <c r="G22" s="26"/>
     </row>
-    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>32</v>
       </c>
@@ -4469,7 +4490,7 @@
       </c>
       <c r="G23" s="26"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>32</v>
       </c>
@@ -4486,7 +4507,7 @@
       </c>
       <c r="G24" s="26"/>
     </row>
-    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>32</v>
       </c>
@@ -4503,7 +4524,7 @@
       </c>
       <c r="G25" s="26"/>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>32</v>
       </c>
@@ -4520,7 +4541,7 @@
       </c>
       <c r="G26" s="26"/>
     </row>
-    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>32</v>
       </c>
@@ -4539,7 +4560,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>32</v>
       </c>
@@ -4556,7 +4577,7 @@
       </c>
       <c r="G28" s="26"/>
     </row>
-    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>32</v>
       </c>
@@ -4575,7 +4596,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>32</v>
       </c>
@@ -4592,7 +4613,7 @@
       </c>
       <c r="G30" s="26"/>
     </row>
-    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>32</v>
       </c>
@@ -4609,7 +4630,7 @@
       </c>
       <c r="G31" s="26"/>
     </row>
-    <row r="32" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>32</v>
       </c>
@@ -4628,7 +4649,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>32</v>
       </c>
@@ -4647,7 +4668,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>32</v>
       </c>
@@ -4664,7 +4685,7 @@
       </c>
       <c r="G34" s="24"/>
     </row>
-    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>32</v>
       </c>
@@ -4681,7 +4702,7 @@
       </c>
       <c r="G35" s="26"/>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>32</v>
       </c>
@@ -4698,26 +4719,26 @@
       </c>
       <c r="G36" s="26"/>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>32</v>
       </c>
       <c r="B37" s="2" t="s">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>1060</v>
+        <v>1056</v>
       </c>
       <c r="D37" s="7"/>
       <c r="E37" s="7" t="s">
-        <v>1061</v>
+        <v>1057</v>
       </c>
       <c r="F37" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G37" s="26"/>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>32</v>
       </c>
@@ -4734,7 +4755,7 @@
       </c>
       <c r="G38" s="26"/>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>32</v>
       </c>
@@ -4751,7 +4772,7 @@
       </c>
       <c r="G39" s="26"/>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>32</v>
       </c>
@@ -4770,7 +4791,7 @@
       </c>
       <c r="G40" s="26"/>
     </row>
-    <row r="41" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="17" t="s">
         <v>32</v>
       </c>
@@ -4789,7 +4810,7 @@
       </c>
       <c r="G41" s="28"/>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>104</v>
       </c>
@@ -4806,7 +4827,7 @@
       </c>
       <c r="G42" s="26"/>
     </row>
-    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>104</v>
       </c>
@@ -4825,7 +4846,7 @@
       </c>
       <c r="G43" s="26"/>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>104</v>
       </c>
@@ -4842,7 +4863,7 @@
       </c>
       <c r="G44" s="26"/>
     </row>
-    <row r="45" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" ht="120" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>104</v>
       </c>
@@ -4861,7 +4882,7 @@
       </c>
       <c r="G45" s="26"/>
     </row>
-    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>104</v>
       </c>
@@ -4880,7 +4901,7 @@
       </c>
       <c r="G46" s="26"/>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>104</v>
       </c>
@@ -4897,7 +4918,7 @@
       </c>
       <c r="G47" s="26"/>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>104</v>
       </c>
@@ -4914,7 +4935,7 @@
       </c>
       <c r="G48" s="26"/>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>104</v>
       </c>
@@ -4931,7 +4952,7 @@
       </c>
       <c r="G49" s="26"/>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>104</v>
       </c>
@@ -4950,7 +4971,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>104</v>
       </c>
@@ -4967,7 +4988,7 @@
       </c>
       <c r="G51" s="26"/>
     </row>
-    <row r="52" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="17" t="s">
         <v>104</v>
       </c>
@@ -4984,7 +5005,7 @@
       </c>
       <c r="G52" s="26"/>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>131</v>
       </c>
@@ -5001,7 +5022,7 @@
       </c>
       <c r="G53" s="26"/>
     </row>
-    <row r="54" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="17" t="s">
         <v>131</v>
       </c>
@@ -5020,7 +5041,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="55" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="17" t="s">
         <v>137</v>
       </c>
@@ -5039,7 +5060,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="56" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>141</v>
       </c>
@@ -5058,7 +5079,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>141</v>
       </c>
@@ -5077,7 +5098,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="58" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>141</v>
       </c>
@@ -5096,7 +5117,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="59" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>141</v>
       </c>
@@ -5115,7 +5136,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="60" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>141</v>
       </c>
@@ -5134,15 +5155,15 @@
         <v>157</v>
       </c>
     </row>
-    <row r="61" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>141</v>
       </c>
       <c r="B61" s="2" t="s">
-        <v>1062</v>
+        <v>1058</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>1063</v>
+        <v>1059</v>
       </c>
       <c r="D61" s="7"/>
       <c r="E61" s="7"/>
@@ -5151,7 +5172,7 @@
       </c>
       <c r="G61" s="24"/>
     </row>
-    <row r="62" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>141</v>
       </c>
@@ -5170,7 +5191,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="63" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>141</v>
       </c>
@@ -5189,7 +5210,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="64" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>141</v>
       </c>
@@ -5208,7 +5229,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>141</v>
       </c>
@@ -5227,7 +5248,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>141</v>
       </c>
@@ -5246,7 +5267,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>141</v>
       </c>
@@ -5265,7 +5286,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>141</v>
       </c>
@@ -5284,7 +5305,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>141</v>
       </c>
@@ -5301,7 +5322,7 @@
       </c>
       <c r="G69" s="26"/>
     </row>
-    <row r="70" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>141</v>
       </c>
@@ -5320,7 +5341,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="71" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>141</v>
       </c>
@@ -5341,7 +5362,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="72" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>141</v>
       </c>
@@ -5362,7 +5383,7 @@
         <v>191</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>141</v>
       </c>
@@ -5379,7 +5400,7 @@
       </c>
       <c r="G73" s="26"/>
     </row>
-    <row r="74" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A74" s="17" t="s">
         <v>141</v>
       </c>
@@ -5396,7 +5417,7 @@
       </c>
       <c r="G74" s="28"/>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>196</v>
       </c>
@@ -5413,7 +5434,7 @@
       </c>
       <c r="G75" s="26"/>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>196</v>
       </c>
@@ -5430,7 +5451,7 @@
       </c>
       <c r="G76" s="26"/>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>196</v>
       </c>
@@ -5447,7 +5468,7 @@
       </c>
       <c r="G77" s="26"/>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>196</v>
       </c>
@@ -5464,7 +5485,7 @@
       </c>
       <c r="G78" s="26"/>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>196</v>
       </c>
@@ -5481,7 +5502,7 @@
       </c>
       <c r="G79" s="26"/>
     </row>
-    <row r="80" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A80" s="17" t="s">
         <v>196</v>
       </c>
@@ -5500,7 +5521,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>210</v>
       </c>
@@ -5517,7 +5538,7 @@
       </c>
       <c r="G81" s="26"/>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>210</v>
       </c>
@@ -5534,7 +5555,7 @@
       </c>
       <c r="G82" s="26"/>
     </row>
-    <row r="83" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>210</v>
       </c>
@@ -5553,7 +5574,7 @@
       </c>
       <c r="G83" s="26"/>
     </row>
-    <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>210</v>
       </c>
@@ -5572,7 +5593,7 @@
       </c>
       <c r="G84" s="26"/>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>210</v>
       </c>
@@ -5589,7 +5610,7 @@
       </c>
       <c r="G85" s="26"/>
     </row>
-    <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>210</v>
       </c>
@@ -5606,7 +5627,7 @@
       </c>
       <c r="G86" s="26"/>
     </row>
-    <row r="87" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>210</v>
       </c>
@@ -5625,7 +5646,7 @@
       </c>
       <c r="G87" s="26"/>
     </row>
-    <row r="88" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>210</v>
       </c>
@@ -5644,7 +5665,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>210</v>
       </c>
@@ -5663,7 +5684,7 @@
       </c>
       <c r="G89" s="26"/>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>210</v>
       </c>
@@ -5680,7 +5701,7 @@
       </c>
       <c r="G90" s="26"/>
     </row>
-    <row r="91" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>210</v>
       </c>
@@ -5699,7 +5720,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="92" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>210</v>
       </c>
@@ -5718,7 +5739,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>210</v>
       </c>
@@ -5735,7 +5756,7 @@
       </c>
       <c r="G93" s="26"/>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>210</v>
       </c>
@@ -5752,7 +5773,7 @@
       </c>
       <c r="G94" s="26"/>
     </row>
-    <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>210</v>
       </c>
@@ -5769,7 +5790,7 @@
       </c>
       <c r="G95" s="26"/>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>210</v>
       </c>
@@ -5790,7 +5811,7 @@
       </c>
       <c r="G96" s="26"/>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>210</v>
       </c>
@@ -5807,7 +5828,7 @@
       </c>
       <c r="G97" s="26"/>
     </row>
-    <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>210</v>
       </c>
@@ -5824,7 +5845,7 @@
       </c>
       <c r="G98" s="26"/>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>210</v>
       </c>
@@ -5841,7 +5862,7 @@
       </c>
       <c r="G99" s="26"/>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>210</v>
       </c>
@@ -5858,7 +5879,7 @@
       </c>
       <c r="G100" s="26"/>
     </row>
-    <row r="101" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>210</v>
       </c>
@@ -5877,7 +5898,7 @@
       </c>
       <c r="G101" s="26"/>
     </row>
-    <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>210</v>
       </c>
@@ -5894,7 +5915,7 @@
       </c>
       <c r="G102" s="26"/>
     </row>
-    <row r="103" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:7" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>210</v>
       </c>
@@ -5913,7 +5934,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>210</v>
       </c>
@@ -5930,7 +5951,7 @@
       </c>
       <c r="G104" s="26"/>
     </row>
-    <row r="105" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:7" ht="90" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>210</v>
       </c>
@@ -5949,7 +5970,7 @@
       </c>
       <c r="G105" s="26"/>
     </row>
-    <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>210</v>
       </c>
@@ -5966,7 +5987,7 @@
       </c>
       <c r="G106" s="26"/>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>210</v>
       </c>
@@ -5983,7 +6004,7 @@
       </c>
       <c r="G107" s="26"/>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>210</v>
       </c>
@@ -6000,7 +6021,7 @@
       </c>
       <c r="G108" s="26"/>
     </row>
-    <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>210</v>
       </c>
@@ -6019,7 +6040,7 @@
       </c>
       <c r="G109" s="26"/>
     </row>
-    <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>210</v>
       </c>
@@ -6038,7 +6059,7 @@
       </c>
       <c r="G110" s="26"/>
     </row>
-    <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>210</v>
       </c>
@@ -6057,7 +6078,7 @@
       </c>
       <c r="G111" s="26"/>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>210</v>
       </c>
@@ -6076,7 +6097,7 @@
       </c>
       <c r="G112" s="26"/>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>210</v>
       </c>
@@ -6093,7 +6114,7 @@
       </c>
       <c r="G113" s="26"/>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>210</v>
       </c>
@@ -6110,7 +6131,7 @@
       </c>
       <c r="G114" s="26"/>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>210</v>
       </c>
@@ -6127,7 +6148,7 @@
       </c>
       <c r="G115" s="26"/>
     </row>
-    <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>210</v>
       </c>
@@ -6146,7 +6167,7 @@
       </c>
       <c r="G116" s="26"/>
     </row>
-    <row r="117" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>210</v>
       </c>
@@ -6165,7 +6186,7 @@
         <v>303</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>210</v>
       </c>
@@ -6182,7 +6203,7 @@
       </c>
       <c r="G118" s="26"/>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>210</v>
       </c>
@@ -6201,7 +6222,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>210</v>
       </c>
@@ -6218,7 +6239,7 @@
       </c>
       <c r="G120" s="26"/>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>210</v>
       </c>
@@ -6235,7 +6256,7 @@
       </c>
       <c r="G121" s="26"/>
     </row>
-    <row r="122" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>210</v>
       </c>
@@ -6252,7 +6273,7 @@
       </c>
       <c r="G122" s="26"/>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>210</v>
       </c>
@@ -6269,7 +6290,7 @@
       </c>
       <c r="G123" s="26"/>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>210</v>
       </c>
@@ -6286,7 +6307,7 @@
       </c>
       <c r="G124" s="26"/>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>210</v>
       </c>
@@ -6303,7 +6324,7 @@
       </c>
       <c r="G125" s="26"/>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>210</v>
       </c>
@@ -6320,7 +6341,7 @@
       </c>
       <c r="G126" s="26"/>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>210</v>
       </c>
@@ -6337,7 +6358,7 @@
       </c>
       <c r="G127" s="26"/>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>210</v>
       </c>
@@ -6354,7 +6375,7 @@
       </c>
       <c r="G128" s="26"/>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>210</v>
       </c>
@@ -6371,7 +6392,7 @@
       </c>
       <c r="G129" s="26"/>
     </row>
-    <row r="130" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>210</v>
       </c>
@@ -6390,7 +6411,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="131" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>210</v>
       </c>
@@ -6409,7 +6430,7 @@
         <v>334</v>
       </c>
     </row>
-    <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>210</v>
       </c>
@@ -6428,7 +6449,7 @@
       </c>
       <c r="G132" s="26"/>
     </row>
-    <row r="133" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>210</v>
       </c>
@@ -6447,7 +6468,7 @@
       </c>
       <c r="G133" s="26"/>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>210</v>
       </c>
@@ -6464,7 +6485,7 @@
       </c>
       <c r="G134" s="26"/>
     </row>
-    <row r="135" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>210</v>
       </c>
@@ -6481,7 +6502,7 @@
       </c>
       <c r="G135" s="26"/>
     </row>
-    <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>210</v>
       </c>
@@ -6500,7 +6521,7 @@
       </c>
       <c r="G136" s="26"/>
     </row>
-    <row r="137" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>210</v>
       </c>
@@ -6519,7 +6540,7 @@
       </c>
       <c r="G137" s="26"/>
     </row>
-    <row r="138" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>210</v>
       </c>
@@ -6540,7 +6561,7 @@
       </c>
       <c r="G138" s="26"/>
     </row>
-    <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>210</v>
       </c>
@@ -6557,7 +6578,7 @@
       </c>
       <c r="G139" s="26"/>
     </row>
-    <row r="140" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>210</v>
       </c>
@@ -6576,7 +6597,7 @@
       </c>
       <c r="G140" s="26"/>
     </row>
-    <row r="141" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>210</v>
       </c>
@@ -6593,7 +6614,7 @@
       </c>
       <c r="G141" s="26"/>
     </row>
-    <row r="142" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>210</v>
       </c>
@@ -6610,7 +6631,7 @@
       </c>
       <c r="G142" s="26"/>
     </row>
-    <row r="143" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>210</v>
       </c>
@@ -6627,7 +6648,7 @@
       </c>
       <c r="G143" s="26"/>
     </row>
-    <row r="144" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>210</v>
       </c>
@@ -6644,7 +6665,7 @@
       </c>
       <c r="G144" s="26"/>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>210</v>
       </c>
@@ -6661,7 +6682,7 @@
       </c>
       <c r="G145" s="26"/>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>210</v>
       </c>
@@ -6680,7 +6701,7 @@
       </c>
       <c r="G146" s="26"/>
     </row>
-    <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>210</v>
       </c>
@@ -6699,7 +6720,7 @@
       </c>
       <c r="G147" s="26"/>
     </row>
-    <row r="148" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>210</v>
       </c>
@@ -6716,7 +6737,7 @@
       </c>
       <c r="G148" s="26"/>
     </row>
-    <row r="149" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>210</v>
       </c>
@@ -6735,7 +6756,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="150" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>210</v>
       </c>
@@ -6752,7 +6773,7 @@
       </c>
       <c r="G150" s="26"/>
     </row>
-    <row r="151" spans="1:7" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:7" ht="60.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>210</v>
       </c>
@@ -6769,7 +6790,7 @@
       </c>
       <c r="G151" s="26"/>
     </row>
-    <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="17" t="s">
         <v>210</v>
       </c>
@@ -6790,7 +6811,7 @@
         <v>387</v>
       </c>
     </row>
-    <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>388</v>
       </c>
@@ -6809,7 +6830,7 @@
       </c>
       <c r="G153" s="26"/>
     </row>
-    <row r="154" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>388</v>
       </c>
@@ -6828,7 +6849,7 @@
       </c>
       <c r="G154" s="26"/>
     </row>
-    <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>388</v>
       </c>
@@ -6845,7 +6866,7 @@
       </c>
       <c r="G155" s="26"/>
     </row>
-    <row r="156" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>388</v>
       </c>
@@ -6862,7 +6883,7 @@
       </c>
       <c r="G156" s="26"/>
     </row>
-    <row r="157" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>388</v>
       </c>
@@ -6879,7 +6900,7 @@
       </c>
       <c r="G157" s="26"/>
     </row>
-    <row r="158" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
         <v>388</v>
       </c>
@@ -6896,7 +6917,7 @@
       </c>
       <c r="G158" s="26"/>
     </row>
-    <row r="159" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A159" s="17" t="s">
         <v>388</v>
       </c>
@@ -6913,7 +6934,7 @@
       </c>
       <c r="G159" s="28"/>
     </row>
-    <row r="160" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>405</v>
       </c>
@@ -6930,7 +6951,7 @@
       </c>
       <c r="G160" s="26"/>
     </row>
-    <row r="161" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>405</v>
       </c>
@@ -6947,7 +6968,7 @@
       </c>
       <c r="G161" s="26"/>
     </row>
-    <row r="162" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>405</v>
       </c>
@@ -6964,7 +6985,7 @@
       </c>
       <c r="G162" s="26"/>
     </row>
-    <row r="163" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>405</v>
       </c>
@@ -6981,7 +7002,7 @@
       </c>
       <c r="G163" s="26"/>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>405</v>
       </c>
@@ -7000,7 +7021,7 @@
       </c>
       <c r="G164" s="26"/>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>405</v>
       </c>
@@ -7017,7 +7038,7 @@
       </c>
       <c r="G165" s="26"/>
     </row>
-    <row r="166" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>405</v>
       </c>
@@ -7034,7 +7055,7 @@
       </c>
       <c r="G166" s="26"/>
     </row>
-    <row r="167" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>405</v>
       </c>
@@ -7053,7 +7074,7 @@
       </c>
       <c r="G167" s="26"/>
     </row>
-    <row r="168" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>405</v>
       </c>
@@ -7070,7 +7091,7 @@
       </c>
       <c r="G168" s="26"/>
     </row>
-    <row r="169" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>405</v>
       </c>
@@ -7087,7 +7108,7 @@
       </c>
       <c r="G169" s="26"/>
     </row>
-    <row r="170" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>405</v>
       </c>
@@ -7104,7 +7125,7 @@
       </c>
       <c r="G170" s="26"/>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>405</v>
       </c>
@@ -7123,7 +7144,7 @@
       </c>
       <c r="G171" s="26"/>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>405</v>
       </c>
@@ -7140,7 +7161,7 @@
       </c>
       <c r="G172" s="26"/>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>405</v>
       </c>
@@ -7157,7 +7178,7 @@
       </c>
       <c r="G173" s="26"/>
     </row>
-    <row r="174" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>405</v>
       </c>
@@ -7174,7 +7195,7 @@
       </c>
       <c r="G174" s="26"/>
     </row>
-    <row r="175" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>405</v>
       </c>
@@ -7193,7 +7214,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="176" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>405</v>
       </c>
@@ -7210,7 +7231,7 @@
       </c>
       <c r="G176" s="26"/>
     </row>
-    <row r="177" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>405</v>
       </c>
@@ -7229,7 +7250,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="178" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>405</v>
       </c>
@@ -7248,7 +7269,7 @@
         <v>449</v>
       </c>
     </row>
-    <row r="179" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>405</v>
       </c>
@@ -7267,7 +7288,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="180" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>405</v>
       </c>
@@ -7286,7 +7307,7 @@
       </c>
       <c r="G180" s="26"/>
     </row>
-    <row r="181" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>405</v>
       </c>
@@ -7305,7 +7326,7 @@
       </c>
       <c r="G181" s="26"/>
     </row>
-    <row r="182" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>405</v>
       </c>
@@ -7322,7 +7343,7 @@
       </c>
       <c r="G182" s="26"/>
     </row>
-    <row r="183" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:7" s="17" customFormat="1" ht="45" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
         <v>405</v>
       </c>
@@ -7341,7 +7362,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="184" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="17" t="s">
         <v>405</v>
       </c>
@@ -7360,7 +7381,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="185" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
         <v>467</v>
       </c>
@@ -7379,7 +7400,7 @@
       </c>
       <c r="G185" s="26"/>
     </row>
-    <row r="186" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="17" t="s">
         <v>471</v>
       </c>
@@ -7398,7 +7419,7 @@
       </c>
       <c r="G186" s="26"/>
     </row>
-    <row r="187" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>475</v>
       </c>
@@ -7415,7 +7436,7 @@
       </c>
       <c r="G187" s="26"/>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>475</v>
       </c>
@@ -7432,7 +7453,7 @@
       </c>
       <c r="G188" s="26"/>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>475</v>
       </c>
@@ -7449,7 +7470,7 @@
       </c>
       <c r="G189" s="26"/>
     </row>
-    <row r="190" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>475</v>
       </c>
@@ -7466,7 +7487,7 @@
       </c>
       <c r="G190" s="26"/>
     </row>
-    <row r="191" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>475</v>
       </c>
@@ -7483,7 +7504,7 @@
       </c>
       <c r="G191" s="26"/>
     </row>
-    <row r="192" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>475</v>
       </c>
@@ -7502,7 +7523,7 @@
       </c>
       <c r="G192" s="26"/>
     </row>
-    <row r="193" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>475</v>
       </c>
@@ -7519,7 +7540,7 @@
       </c>
       <c r="G193" s="26"/>
     </row>
-    <row r="194" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>475</v>
       </c>
@@ -7536,7 +7557,7 @@
       </c>
       <c r="G194" s="26"/>
     </row>
-    <row r="195" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>475</v>
       </c>
@@ -7553,7 +7574,7 @@
       </c>
       <c r="G195" s="26"/>
     </row>
-    <row r="196" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>475</v>
       </c>
@@ -7572,7 +7593,7 @@
         <v>497</v>
       </c>
     </row>
-    <row r="197" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>475</v>
       </c>
@@ -7589,7 +7610,7 @@
       </c>
       <c r="G197" s="26"/>
     </row>
-    <row r="198" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>475</v>
       </c>
@@ -7606,7 +7627,7 @@
       </c>
       <c r="G198" s="26"/>
     </row>
-    <row r="199" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>475</v>
       </c>
@@ -7623,7 +7644,7 @@
       </c>
       <c r="G199" s="26"/>
     </row>
-    <row r="200" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>475</v>
       </c>
@@ -7640,7 +7661,7 @@
       </c>
       <c r="G200" s="26"/>
     </row>
-    <row r="201" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:7" s="17" customFormat="1" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A201" s="2" t="s">
         <v>475</v>
       </c>
@@ -7657,7 +7678,7 @@
       </c>
       <c r="G201" s="26"/>
     </row>
-    <row r="202" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:7" ht="30.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A202" s="17" t="s">
         <v>475</v>
       </c>
@@ -7674,15 +7695,15 @@
       </c>
       <c r="G202" s="26"/>
     </row>
-    <row r="203" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>510</v>
       </c>
       <c r="B203" t="s">
-        <v>1014</v>
+        <v>1010</v>
       </c>
       <c r="C203" t="s">
-        <v>1015</v>
+        <v>1011</v>
       </c>
       <c r="D203" s="7"/>
       <c r="E203" s="7"/>
@@ -7690,10 +7711,10 @@
         <v>20</v>
       </c>
       <c r="G203" s="26" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="204" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="204" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>510</v>
       </c>
@@ -7710,7 +7731,7 @@
       </c>
       <c r="G204" s="26"/>
     </row>
-    <row r="205" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>510</v>
       </c>
@@ -7727,7 +7748,7 @@
       </c>
       <c r="G205" s="26"/>
     </row>
-    <row r="206" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>510</v>
       </c>
@@ -7746,7 +7767,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="207" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>510</v>
       </c>
@@ -7765,15 +7786,15 @@
       </c>
       <c r="G207" s="24"/>
     </row>
-    <row r="208" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>510</v>
       </c>
       <c r="B208" t="s">
-        <v>997</v>
+        <v>993</v>
       </c>
       <c r="C208" t="s">
-        <v>998</v>
+        <v>994</v>
       </c>
       <c r="D208" s="7"/>
       <c r="E208" s="7"/>
@@ -7781,10 +7802,10 @@
         <v>20</v>
       </c>
       <c r="G208" s="26" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="209" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="209" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>510</v>
       </c>
@@ -7801,7 +7822,7 @@
       </c>
       <c r="G209" s="26"/>
     </row>
-    <row r="210" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:7" ht="45" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>510</v>
       </c>
@@ -7820,7 +7841,7 @@
         <v>525</v>
       </c>
     </row>
-    <row r="211" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>510</v>
       </c>
@@ -7839,7 +7860,7 @@
         <v>528</v>
       </c>
     </row>
-    <row r="212" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>510</v>
       </c>
@@ -7856,7 +7877,7 @@
       </c>
       <c r="G212" s="26"/>
     </row>
-    <row r="213" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>510</v>
       </c>
@@ -7873,7 +7894,7 @@
       </c>
       <c r="G213" s="26"/>
     </row>
-    <row r="214" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>510</v>
       </c>
@@ -7892,7 +7913,7 @@
       </c>
       <c r="G214" s="26"/>
     </row>
-    <row r="215" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>510</v>
       </c>
@@ -7909,7 +7930,7 @@
       </c>
       <c r="G215" s="26"/>
     </row>
-    <row r="216" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>510</v>
       </c>
@@ -7928,7 +7949,7 @@
       </c>
       <c r="G216" s="26"/>
     </row>
-    <row r="217" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>510</v>
       </c>
@@ -7947,7 +7968,7 @@
       </c>
       <c r="G217" s="26"/>
     </row>
-    <row r="218" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>510</v>
       </c>
@@ -7964,15 +7985,15 @@
       </c>
       <c r="G218" s="26"/>
     </row>
-    <row r="219" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>510</v>
       </c>
       <c r="B219" t="s">
-        <v>1017</v>
+        <v>1013</v>
       </c>
       <c r="C219" t="s">
-        <v>1018</v>
+        <v>1014</v>
       </c>
       <c r="D219" s="7"/>
       <c r="E219" s="7"/>
@@ -7980,10 +8001,10 @@
         <v>20</v>
       </c>
       <c r="G219" s="26" t="s">
-        <v>1019</v>
-      </c>
-    </row>
-    <row r="220" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="220" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" t="s">
         <v>510</v>
       </c>
@@ -8002,15 +8023,15 @@
         <v>549</v>
       </c>
     </row>
-    <row r="221" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A221" t="s">
         <v>510</v>
       </c>
       <c r="B221" t="s">
-        <v>1020</v>
+        <v>1016</v>
       </c>
       <c r="C221" t="s">
-        <v>1021</v>
+        <v>1017</v>
       </c>
       <c r="D221" s="7"/>
       <c r="E221" s="7"/>
@@ -8018,21 +8039,21 @@
         <v>29</v>
       </c>
       <c r="G221" s="26" t="s">
-        <v>1022</v>
-      </c>
-    </row>
-    <row r="222" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="222" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A222" t="s">
         <v>510</v>
       </c>
       <c r="B222" t="s">
-        <v>1064</v>
+        <v>1060</v>
       </c>
       <c r="C222" t="s">
-        <v>1065</v>
+        <v>1061</v>
       </c>
       <c r="D222" s="7" t="s">
-        <v>1066</v>
+        <v>1062</v>
       </c>
       <c r="E222" s="7"/>
       <c r="F222" t="s">
@@ -8040,15 +8061,15 @@
       </c>
       <c r="G222" s="26"/>
     </row>
-    <row r="223" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A223" t="s">
         <v>510</v>
       </c>
       <c r="B223" t="s">
-        <v>1023</v>
+        <v>1019</v>
       </c>
       <c r="C223" t="s">
-        <v>1024</v>
+        <v>1020</v>
       </c>
       <c r="D223" s="7"/>
       <c r="E223" s="7"/>
@@ -8056,10 +8077,10 @@
         <v>29</v>
       </c>
       <c r="G223" s="26" t="s">
-        <v>1025</v>
-      </c>
-    </row>
-    <row r="224" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1021</v>
+      </c>
+    </row>
+    <row r="224" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A224" t="s">
         <v>510</v>
       </c>
@@ -8076,15 +8097,15 @@
       </c>
       <c r="G224" s="26"/>
     </row>
-    <row r="225" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" t="s">
         <v>510</v>
       </c>
       <c r="B225" t="s">
-        <v>1026</v>
+        <v>1022</v>
       </c>
       <c r="C225" t="s">
-        <v>1027</v>
+        <v>1023</v>
       </c>
       <c r="D225" s="7"/>
       <c r="E225" s="7"/>
@@ -8092,18 +8113,18 @@
         <v>20</v>
       </c>
       <c r="G225" s="26" t="s">
-        <v>1028</v>
-      </c>
-    </row>
-    <row r="226" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1024</v>
+      </c>
+    </row>
+    <row r="226" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" t="s">
         <v>510</v>
       </c>
       <c r="B226" t="s">
-        <v>995</v>
+        <v>991</v>
       </c>
       <c r="C226" t="s">
-        <v>996</v>
+        <v>992</v>
       </c>
       <c r="D226" s="7"/>
       <c r="E226" s="7"/>
@@ -8111,10 +8132,10 @@
         <v>29</v>
       </c>
       <c r="G226" s="26" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="227" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="227" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" t="s">
         <v>510</v>
       </c>
@@ -8133,7 +8154,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="228" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A228" t="s">
         <v>510</v>
       </c>
@@ -8150,18 +8171,18 @@
       </c>
       <c r="G228" s="26"/>
     </row>
-    <row r="229" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" t="s">
         <v>510</v>
       </c>
       <c r="B229" t="s">
-        <v>990</v>
+        <v>986</v>
       </c>
       <c r="C229" t="s">
-        <v>991</v>
+        <v>987</v>
       </c>
       <c r="D229" s="7" t="s">
-        <v>992</v>
+        <v>988</v>
       </c>
       <c r="E229" s="7"/>
       <c r="F229" t="s">
@@ -8169,7 +8190,7 @@
       </c>
       <c r="G229" s="26"/>
     </row>
-    <row r="230" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A230" t="s">
         <v>510</v>
       </c>
@@ -8186,7 +8207,7 @@
       </c>
       <c r="G230" s="26"/>
     </row>
-    <row r="231" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" t="s">
         <v>510</v>
       </c>
@@ -8205,7 +8226,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="232" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A232" t="s">
         <v>510</v>
       </c>
@@ -8224,7 +8245,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="233" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" t="s">
         <v>510</v>
       </c>
@@ -8245,7 +8266,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="234" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="2" t="s">
         <v>510</v>
       </c>
@@ -8262,15 +8283,15 @@
       </c>
       <c r="G234" s="26"/>
     </row>
-    <row r="235" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B235" s="2" t="s">
-        <v>1029</v>
+        <v>1025</v>
       </c>
       <c r="C235" s="2" t="s">
-        <v>1030</v>
+        <v>1026</v>
       </c>
       <c r="D235" s="7"/>
       <c r="E235" s="7"/>
@@ -8278,18 +8299,18 @@
         <v>20</v>
       </c>
       <c r="G235" s="26" t="s">
-        <v>1031</v>
-      </c>
-    </row>
-    <row r="236" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1027</v>
+      </c>
+    </row>
+    <row r="236" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B236" s="2" t="s">
-        <v>1032</v>
+        <v>1028</v>
       </c>
       <c r="C236" s="2" t="s">
-        <v>1033</v>
+        <v>1029</v>
       </c>
       <c r="D236" s="7"/>
       <c r="E236" s="7"/>
@@ -8297,18 +8318,18 @@
         <v>29</v>
       </c>
       <c r="G236" s="26" t="s">
-        <v>1058</v>
-      </c>
-    </row>
-    <row r="237" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="237" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B237" s="2" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
       <c r="C237" s="2" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
       <c r="D237" s="7"/>
       <c r="E237" s="7"/>
@@ -8316,10 +8337,10 @@
         <v>20</v>
       </c>
       <c r="G237" s="26" t="s">
-        <v>1057</v>
-      </c>
-    </row>
-    <row r="238" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="238" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="2" t="s">
         <v>510</v>
       </c>
@@ -8334,22 +8355,22 @@
       <c r="F238" s="4"/>
       <c r="G238" s="26"/>
     </row>
-    <row r="239" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B239" s="2" t="s">
-        <v>993</v>
+        <v>989</v>
       </c>
       <c r="C239" s="2" t="s">
-        <v>994</v>
+        <v>990</v>
       </c>
       <c r="D239" s="7"/>
       <c r="E239" s="7"/>
       <c r="F239" s="4"/>
       <c r="G239" s="26"/>
     </row>
-    <row r="240" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="2" t="s">
         <v>510</v>
       </c>
@@ -8368,7 +8389,7 @@
         <v>575</v>
       </c>
     </row>
-    <row r="241" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="2" t="s">
         <v>510</v>
       </c>
@@ -8387,316 +8408,320 @@
         <v>578</v>
       </c>
     </row>
-    <row r="242" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B242" s="2" t="s">
-        <v>579</v>
+        <v>1065</v>
       </c>
       <c r="C242" s="2" t="s">
-        <v>580</v>
-      </c>
-      <c r="D242" s="7"/>
+        <v>1066</v>
+      </c>
+      <c r="D242" s="7" t="s">
+        <v>1067</v>
+      </c>
       <c r="E242" s="7"/>
-      <c r="F242" s="14" t="s">
-        <v>20</v>
+      <c r="F242" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G242" s="26"/>
     </row>
-    <row r="243" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B243" s="2" t="s">
-        <v>581</v>
+        <v>1068</v>
       </c>
       <c r="C243" s="2" t="s">
-        <v>582</v>
-      </c>
-      <c r="D243" s="7"/>
+        <v>1069</v>
+      </c>
+      <c r="D243" s="7" t="s">
+        <v>1067</v>
+      </c>
       <c r="E243" s="7"/>
-      <c r="F243" s="14" t="s">
+      <c r="F243" s="5" t="s">
         <v>29</v>
       </c>
       <c r="G243" s="26"/>
     </row>
-    <row r="244" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B244" s="2" t="s">
-        <v>583</v>
+        <v>579</v>
       </c>
       <c r="C244" s="2" t="s">
-        <v>584</v>
+        <v>580</v>
       </c>
       <c r="D244" s="7"/>
       <c r="E244" s="7"/>
-      <c r="F244" s="4" t="s">
+      <c r="F244" s="14" t="s">
         <v>20</v>
       </c>
       <c r="G244" s="26"/>
     </row>
-    <row r="245" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B245" s="2" t="s">
-        <v>585</v>
+        <v>581</v>
       </c>
       <c r="C245" s="2" t="s">
-        <v>586</v>
-      </c>
-      <c r="D245" s="1"/>
+        <v>582</v>
+      </c>
+      <c r="D245" s="7"/>
       <c r="E245" s="7"/>
-      <c r="F245" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G245" s="24" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="246" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F245" s="14" t="s">
+        <v>29</v>
+      </c>
+      <c r="G245" s="26"/>
+    </row>
+    <row r="246" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B246" s="2" t="s">
-        <v>1067</v>
+        <v>583</v>
       </c>
       <c r="C246" s="2" t="s">
-        <v>1068</v>
-      </c>
-      <c r="D246" s="1"/>
+        <v>584</v>
+      </c>
+      <c r="D246" s="7"/>
       <c r="E246" s="7"/>
       <c r="F246" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="G246" s="24"/>
-    </row>
-    <row r="247" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G246" s="26"/>
+    </row>
+    <row r="247" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B247" s="2" t="s">
-        <v>588</v>
+        <v>585</v>
       </c>
       <c r="C247" s="2" t="s">
-        <v>589</v>
-      </c>
-      <c r="D247" s="7"/>
+        <v>586</v>
+      </c>
+      <c r="D247" s="1"/>
       <c r="E247" s="7"/>
-      <c r="F247" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G247" s="26"/>
-    </row>
-    <row r="248" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F247" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G247" s="24" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="248" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B248" s="2" t="s">
-        <v>590</v>
+        <v>1063</v>
       </c>
       <c r="C248" s="2" t="s">
-        <v>591</v>
-      </c>
-      <c r="D248" s="7"/>
+        <v>1064</v>
+      </c>
+      <c r="D248" s="1"/>
       <c r="E248" s="7"/>
       <c r="F248" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G248" s="26"/>
-    </row>
-    <row r="249" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="G248" s="24"/>
+    </row>
+    <row r="249" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B249" s="2" t="s">
-        <v>592</v>
+        <v>1070</v>
       </c>
       <c r="C249" s="2" t="s">
-        <v>593</v>
-      </c>
-      <c r="D249" s="7"/>
+        <v>1071</v>
+      </c>
+      <c r="D249" s="1" t="s">
+        <v>1067</v>
+      </c>
       <c r="E249" s="7"/>
       <c r="F249" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G249" s="26"/>
-    </row>
-    <row r="250" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="G249" s="24"/>
+    </row>
+    <row r="250" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B250" s="2" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
       <c r="C250" s="2" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D250" s="7"/>
       <c r="E250" s="7"/>
-      <c r="F250" s="6" t="s">
-        <v>96</v>
-      </c>
-      <c r="G250" s="24"/>
-    </row>
-    <row r="251" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F250" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G250" s="26"/>
+    </row>
+    <row r="251" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B251" s="2" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="C251" s="2" t="s">
-        <v>597</v>
-      </c>
-      <c r="D251" s="7" t="s">
-        <v>598</v>
-      </c>
+        <v>591</v>
+      </c>
+      <c r="D251" s="7"/>
       <c r="E251" s="7"/>
       <c r="F251" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G251" s="26" t="s">
-        <v>599</v>
-      </c>
-    </row>
-    <row r="252" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>96</v>
+      </c>
+      <c r="G251" s="26"/>
+    </row>
+    <row r="252" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B252" s="2" t="s">
-        <v>600</v>
+        <v>592</v>
       </c>
       <c r="C252" s="2" t="s">
-        <v>601</v>
-      </c>
-      <c r="D252" s="1"/>
+        <v>593</v>
+      </c>
+      <c r="D252" s="7"/>
       <c r="E252" s="7"/>
       <c r="F252" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G252" s="26"/>
     </row>
-    <row r="253" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A253" t="s">
+    <row r="253" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B253" t="s">
-        <v>602</v>
-      </c>
-      <c r="C253" t="s">
-        <v>603</v>
+      <c r="B253" s="2" t="s">
+        <v>594</v>
+      </c>
+      <c r="C253" s="2" t="s">
+        <v>595</v>
       </c>
       <c r="D253" s="7"/>
       <c r="E253" s="7"/>
-      <c r="F253" t="s">
-        <v>29</v>
-      </c>
-      <c r="G253" s="26"/>
-    </row>
-    <row r="254" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F253" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="G253" s="24"/>
+    </row>
+    <row r="254" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B254" s="2" t="s">
-        <v>604</v>
+        <v>596</v>
       </c>
       <c r="C254" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="D254" s="7"/>
+        <v>597</v>
+      </c>
+      <c r="D254" s="7" t="s">
+        <v>598</v>
+      </c>
       <c r="E254" s="7"/>
       <c r="F254" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="G254" s="26"/>
-    </row>
-    <row r="255" spans="1:7" ht="43.5" x14ac:dyDescent="0.35">
+      <c r="G254" s="26" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="255" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B255" s="2" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="C255" s="2" t="s">
-        <v>607</v>
-      </c>
-      <c r="D255" s="7"/>
+        <v>601</v>
+      </c>
+      <c r="D255" s="1"/>
       <c r="E255" s="7"/>
-      <c r="F255" s="16" t="s">
-        <v>267</v>
-      </c>
-      <c r="G255" s="24" t="s">
-        <v>608</v>
-      </c>
-    </row>
-    <row r="256" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A256" t="s">
+      <c r="F255" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G255" s="26"/>
+    </row>
+    <row r="256" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A256" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B256" t="s">
-        <v>609</v>
-      </c>
-      <c r="C256" t="s">
-        <v>610</v>
+      <c r="B256" s="2" t="s">
+        <v>602</v>
+      </c>
+      <c r="C256" s="2" t="s">
+        <v>603</v>
       </c>
       <c r="D256" s="7"/>
       <c r="E256" s="7"/>
-      <c r="F256" t="s">
+      <c r="F256" s="16" t="s">
+        <v>267</v>
+      </c>
+      <c r="G256" s="24" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="257" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A257" t="s">
+        <v>510</v>
+      </c>
+      <c r="B257" t="s">
+        <v>605</v>
+      </c>
+      <c r="C257" t="s">
+        <v>606</v>
+      </c>
+      <c r="D257" s="7"/>
+      <c r="E257" s="7"/>
+      <c r="F257" t="s">
         <v>29</v>
       </c>
-      <c r="G256" s="26"/>
-    </row>
-    <row r="257" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A257" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B257" s="2" t="s">
-        <v>611</v>
-      </c>
-      <c r="C257" s="2" t="s">
-        <v>612</v>
-      </c>
-      <c r="D257" s="1" t="s">
-        <v>613</v>
-      </c>
-      <c r="E257" s="7"/>
-      <c r="F257" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G257" s="24"/>
-    </row>
-    <row r="258" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G257" s="26"/>
+    </row>
+    <row r="258" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A258" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B258" s="2" t="s">
-        <v>1034</v>
+        <v>607</v>
       </c>
       <c r="C258" s="2" t="s">
-        <v>1035</v>
-      </c>
-      <c r="D258" s="1"/>
+        <v>608</v>
+      </c>
+      <c r="D258" s="1" t="s">
+        <v>609</v>
+      </c>
       <c r="E258" s="7"/>
-      <c r="F258" s="14" t="s">
+      <c r="F258" s="16" t="s">
         <v>29</v>
       </c>
-      <c r="G258" s="26" t="s">
-        <v>1036</v>
-      </c>
-    </row>
-    <row r="259" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G258" s="24"/>
+    </row>
+    <row r="259" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A259" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B259" s="2" t="s">
-        <v>1037</v>
+        <v>1030</v>
       </c>
       <c r="C259" s="2" t="s">
-        <v>1038</v>
+        <v>1031</v>
       </c>
       <c r="D259" s="1"/>
       <c r="E259" s="7"/>
@@ -8704,412 +8729,412 @@
         <v>29</v>
       </c>
       <c r="G259" s="26" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="260" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1032</v>
+      </c>
+    </row>
+    <row r="260" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A260" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B260" s="2" t="s">
-        <v>614</v>
+        <v>1033</v>
       </c>
       <c r="C260" s="2" t="s">
-        <v>615</v>
+        <v>1034</v>
       </c>
       <c r="D260" s="1"/>
       <c r="E260" s="7"/>
       <c r="F260" s="14" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G260" s="26" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="261" spans="1:7" x14ac:dyDescent="0.35">
+        <v>1035</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A261" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B261" s="2" t="s">
-        <v>617</v>
+        <v>610</v>
       </c>
       <c r="C261" s="2" t="s">
-        <v>618</v>
-      </c>
-      <c r="D261" s="7"/>
+        <v>611</v>
+      </c>
+      <c r="D261" s="1"/>
       <c r="E261" s="7"/>
-      <c r="F261" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G261" s="26"/>
-    </row>
-    <row r="262" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F261" s="14" t="s">
+        <v>10</v>
+      </c>
+      <c r="G261" s="26" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A262" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B262" s="2" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="C262" s="2" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="D262" s="7"/>
       <c r="E262" s="7"/>
       <c r="F262" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G262" s="26" t="s">
-        <v>621</v>
-      </c>
-    </row>
-    <row r="263" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="G262" s="26"/>
+    </row>
+    <row r="263" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A263" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B263" s="2" t="s">
-        <v>622</v>
+        <v>615</v>
       </c>
       <c r="C263" s="2" t="s">
-        <v>623</v>
-      </c>
-      <c r="D263" s="7" t="s">
-        <v>624</v>
-      </c>
+        <v>616</v>
+      </c>
+      <c r="D263" s="7"/>
       <c r="E263" s="7"/>
-      <c r="F263" s="5" t="s">
+      <c r="F263" s="4" t="s">
         <v>14</v>
       </c>
       <c r="G263" s="26" t="s">
-        <v>625</v>
-      </c>
-    </row>
-    <row r="264" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B264" s="2" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="C264" s="2" t="s">
-        <v>627</v>
+        <v>619</v>
       </c>
       <c r="D264" s="7" t="s">
-        <v>628</v>
+        <v>620</v>
       </c>
       <c r="E264" s="7"/>
       <c r="F264" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G264" s="26" t="s">
+        <v>621</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A265" s="2" t="s">
+        <v>510</v>
+      </c>
+      <c r="B265" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="C265" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="D265" s="7" t="s">
+        <v>624</v>
+      </c>
+      <c r="E265" s="7"/>
+      <c r="F265" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="G264" s="26"/>
-    </row>
-    <row r="265" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A265" t="s">
+      <c r="G265" s="26"/>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A266" t="s">
         <v>510</v>
       </c>
-      <c r="B265" t="s">
-        <v>629</v>
-      </c>
-      <c r="C265" t="s">
-        <v>630</v>
-      </c>
-      <c r="D265" s="7"/>
-      <c r="E265" s="7"/>
-      <c r="F265" t="s">
-        <v>29</v>
-      </c>
-      <c r="G265" s="26"/>
-    </row>
-    <row r="266" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A266" s="2" t="s">
-        <v>510</v>
-      </c>
-      <c r="B266" s="2" t="s">
-        <v>631</v>
-      </c>
-      <c r="C266" s="2" t="s">
-        <v>632</v>
+      <c r="B266" t="s">
+        <v>625</v>
+      </c>
+      <c r="C266" t="s">
+        <v>626</v>
       </c>
       <c r="D266" s="7"/>
       <c r="E266" s="7"/>
-      <c r="F266" s="4" t="s">
+      <c r="F266" t="s">
         <v>29</v>
       </c>
       <c r="G266" s="26"/>
     </row>
-    <row r="267" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A267" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B267" s="2" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="C267" s="2" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="D267" s="7"/>
       <c r="E267" s="7"/>
       <c r="F267" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G267" s="26"/>
     </row>
-    <row r="268" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B268" s="2" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="C268" s="2" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="D268" s="7"/>
       <c r="E268" s="7"/>
-      <c r="F268" s="5" t="s">
+      <c r="F268" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G268" s="26"/>
     </row>
-    <row r="269" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B269" s="2" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="C269" s="2" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="D269" s="7"/>
       <c r="E269" s="7"/>
-      <c r="F269" s="4" t="s">
-        <v>29</v>
+      <c r="F269" s="5" t="s">
+        <v>20</v>
       </c>
       <c r="G269" s="26"/>
     </row>
-    <row r="270" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A270" t="s">
+    <row r="270" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A270" s="2" t="s">
         <v>510</v>
       </c>
-      <c r="B270" t="s">
-        <v>639</v>
-      </c>
-      <c r="C270" t="s">
-        <v>640</v>
+      <c r="B270" s="2" t="s">
+        <v>633</v>
+      </c>
+      <c r="C270" s="2" t="s">
+        <v>634</v>
       </c>
       <c r="D270" s="7"/>
       <c r="E270" s="7"/>
-      <c r="F270" t="s">
+      <c r="F270" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G270" s="26"/>
     </row>
-    <row r="271" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A271" t="s">
         <v>510</v>
       </c>
       <c r="B271" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="C271" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="D271" s="7"/>
       <c r="E271" s="7"/>
       <c r="F271" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G271" s="26"/>
     </row>
-    <row r="272" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A272" t="s">
         <v>510</v>
       </c>
       <c r="B272" t="s">
-        <v>643</v>
+        <v>1072</v>
       </c>
       <c r="C272" t="s">
-        <v>644</v>
-      </c>
-      <c r="D272" s="7"/>
+        <v>1073</v>
+      </c>
+      <c r="D272" s="7" t="s">
+        <v>1067</v>
+      </c>
       <c r="E272" s="7"/>
       <c r="F272" t="s">
         <v>20</v>
       </c>
       <c r="G272" s="26"/>
     </row>
-    <row r="273" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A273" t="s">
         <v>510</v>
       </c>
       <c r="B273" t="s">
-        <v>645</v>
+        <v>637</v>
       </c>
       <c r="C273" t="s">
-        <v>646</v>
+        <v>638</v>
       </c>
       <c r="D273" s="7"/>
       <c r="E273" s="7"/>
       <c r="F273" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G273" s="26"/>
     </row>
-    <row r="274" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" t="s">
         <v>510</v>
       </c>
       <c r="B274" t="s">
-        <v>647</v>
+        <v>639</v>
       </c>
       <c r="C274" t="s">
-        <v>648</v>
+        <v>640</v>
       </c>
       <c r="D274" s="7"/>
       <c r="E274" s="7"/>
       <c r="F274" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G274" s="26"/>
     </row>
-    <row r="275" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A275" t="s">
         <v>510</v>
       </c>
       <c r="B275" t="s">
-        <v>649</v>
+        <v>641</v>
       </c>
       <c r="C275" t="s">
-        <v>650</v>
+        <v>642</v>
       </c>
       <c r="D275" s="7"/>
       <c r="E275" s="7"/>
       <c r="F275" t="s">
-        <v>37</v>
+        <v>29</v>
       </c>
       <c r="G275" s="26"/>
     </row>
-    <row r="276" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="276" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A276" t="s">
         <v>510</v>
       </c>
       <c r="B276" t="s">
-        <v>651</v>
+        <v>1074</v>
       </c>
       <c r="C276" t="s">
-        <v>652</v>
-      </c>
-      <c r="D276" s="7"/>
+        <v>1075</v>
+      </c>
+      <c r="D276" s="7" t="s">
+        <v>1067</v>
+      </c>
       <c r="E276" s="7"/>
       <c r="F276" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G276" s="26"/>
     </row>
-    <row r="277" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="277" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A277" t="s">
         <v>510</v>
       </c>
       <c r="B277" t="s">
-        <v>653</v>
+        <v>643</v>
       </c>
       <c r="C277" t="s">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="D277" s="7"/>
       <c r="E277" s="7"/>
       <c r="F277" t="s">
-        <v>14</v>
-      </c>
-      <c r="G277" s="26" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="278" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="G277" s="26"/>
+    </row>
+    <row r="278" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" t="s">
         <v>510</v>
       </c>
       <c r="B278" t="s">
-        <v>656</v>
+        <v>645</v>
       </c>
       <c r="C278" t="s">
-        <v>657</v>
+        <v>646</v>
       </c>
       <c r="D278" s="7"/>
       <c r="E278" s="7"/>
       <c r="F278" t="s">
-        <v>14</v>
-      </c>
-      <c r="G278" s="26" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="279" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A279" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="G278" s="26"/>
+    </row>
+    <row r="279" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A279" t="s">
         <v>510</v>
       </c>
-      <c r="B279" s="2" t="s">
-        <v>658</v>
-      </c>
-      <c r="C279" s="2" t="s">
-        <v>659</v>
+      <c r="B279" t="s">
+        <v>647</v>
+      </c>
+      <c r="C279" t="s">
+        <v>648</v>
       </c>
       <c r="D279" s="7"/>
       <c r="E279" s="7"/>
-      <c r="F279" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="G279" s="26" t="s">
-        <v>660</v>
-      </c>
-    </row>
-    <row r="280" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A280" s="2" t="s">
+      <c r="F279" t="s">
+        <v>10</v>
+      </c>
+      <c r="G279" s="26"/>
+    </row>
+    <row r="280" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A280" t="s">
         <v>510</v>
       </c>
-      <c r="B280" s="2" t="s">
-        <v>661</v>
-      </c>
-      <c r="C280" s="2" t="s">
-        <v>662</v>
+      <c r="B280" t="s">
+        <v>649</v>
+      </c>
+      <c r="C280" t="s">
+        <v>650</v>
       </c>
       <c r="D280" s="7"/>
       <c r="E280" s="7"/>
-      <c r="F280" s="5" t="s">
+      <c r="F280" t="s">
         <v>14</v>
       </c>
       <c r="G280" s="26" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="281" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A281" s="17" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A281" t="s">
         <v>510</v>
       </c>
-      <c r="B281" s="17" t="s">
-        <v>664</v>
-      </c>
-      <c r="C281" s="17" t="s">
-        <v>665</v>
-      </c>
-      <c r="D281" s="27"/>
-      <c r="E281" s="27"/>
-      <c r="F281" s="18" t="s">
+      <c r="B281" t="s">
+        <v>652</v>
+      </c>
+      <c r="C281" t="s">
+        <v>653</v>
+      </c>
+      <c r="D281" s="7"/>
+      <c r="E281" s="7"/>
+      <c r="F281" t="s">
         <v>14</v>
       </c>
-      <c r="G281" s="28" t="s">
-        <v>666</v>
-      </c>
-    </row>
-    <row r="282" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G281" s="26" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A282" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B282" s="2" t="s">
-        <v>667</v>
+        <v>654</v>
       </c>
       <c r="C282" s="2" t="s">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="D282" s="7"/>
       <c r="E282" s="7"/>
@@ -9117,779 +9142,785 @@
         <v>14</v>
       </c>
       <c r="G282" s="26" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="283" spans="1:7" x14ac:dyDescent="0.35">
+        <v>656</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B283" s="2" t="s">
-        <v>669</v>
+        <v>657</v>
       </c>
       <c r="C283" s="2" t="s">
-        <v>670</v>
-      </c>
-      <c r="D283" s="1"/>
+        <v>658</v>
+      </c>
+      <c r="D283" s="7"/>
       <c r="E283" s="7"/>
-      <c r="F283" s="3" t="s">
+      <c r="F283" s="5" t="s">
         <v>14</v>
       </c>
       <c r="G283" s="26" t="s">
-        <v>655</v>
-      </c>
-    </row>
-    <row r="284" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A284" s="2" t="s">
+        <v>659</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A284" s="17" t="s">
         <v>510</v>
       </c>
-      <c r="B284" s="2" t="s">
-        <v>671</v>
-      </c>
-      <c r="C284" s="2" t="s">
-        <v>672</v>
-      </c>
-      <c r="D284" s="1"/>
-      <c r="E284" s="7"/>
-      <c r="F284" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G284" s="26"/>
-    </row>
-    <row r="285" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B284" s="17" t="s">
+        <v>660</v>
+      </c>
+      <c r="C284" s="17" t="s">
+        <v>661</v>
+      </c>
+      <c r="D284" s="27"/>
+      <c r="E284" s="27"/>
+      <c r="F284" s="18" t="s">
+        <v>14</v>
+      </c>
+      <c r="G284" s="28" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A285" s="2" t="s">
         <v>510</v>
       </c>
       <c r="B285" s="2" t="s">
-        <v>673</v>
+        <v>663</v>
       </c>
       <c r="C285" s="2" t="s">
-        <v>674</v>
+        <v>664</v>
       </c>
       <c r="D285" s="7"/>
       <c r="E285" s="7"/>
       <c r="F285" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G285" s="26"/>
-    </row>
-    <row r="286" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+        <v>14</v>
+      </c>
+      <c r="G285" s="26" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A286" s="2" t="s">
-        <v>675</v>
+        <v>510</v>
       </c>
       <c r="B286" s="2" t="s">
-        <v>676</v>
+        <v>665</v>
       </c>
       <c r="C286" s="2" t="s">
-        <v>677</v>
-      </c>
-      <c r="D286" s="7"/>
+        <v>666</v>
+      </c>
+      <c r="D286" s="1"/>
       <c r="E286" s="7"/>
       <c r="F286" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G286" s="26"/>
-    </row>
-    <row r="287" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="G286" s="26" t="s">
+        <v>651</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="2" t="s">
-        <v>675</v>
+        <v>510</v>
       </c>
       <c r="B287" s="2" t="s">
-        <v>678</v>
+        <v>667</v>
       </c>
       <c r="C287" s="2" t="s">
-        <v>679</v>
-      </c>
-      <c r="D287" s="7" t="s">
-        <v>680</v>
-      </c>
+        <v>668</v>
+      </c>
+      <c r="D287" s="1"/>
       <c r="E287" s="7"/>
       <c r="F287" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G287" s="26"/>
     </row>
-    <row r="288" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="2" t="s">
-        <v>675</v>
+        <v>510</v>
       </c>
       <c r="B288" s="2" t="s">
-        <v>681</v>
+        <v>669</v>
       </c>
       <c r="C288" s="2" t="s">
-        <v>682</v>
-      </c>
-      <c r="D288" s="7" t="s">
-        <v>683</v>
-      </c>
+        <v>670</v>
+      </c>
+      <c r="D288" s="7"/>
       <c r="E288" s="7"/>
       <c r="F288" s="3" t="s">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G288" s="26"/>
     </row>
-    <row r="289" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A289" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B289" s="2" t="s">
-        <v>684</v>
+        <v>672</v>
       </c>
       <c r="C289" s="2" t="s">
-        <v>685</v>
-      </c>
-      <c r="D289" s="1"/>
-      <c r="E289" s="1"/>
+        <v>673</v>
+      </c>
+      <c r="D289" s="7"/>
+      <c r="E289" s="7"/>
       <c r="F289" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G289" s="26"/>
     </row>
-    <row r="290" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B290" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="C290" s="2" t="s">
         <v>675</v>
       </c>
-      <c r="B290" s="2" t="s">
-        <v>686</v>
-      </c>
-      <c r="C290" s="2" t="s">
-        <v>687</v>
-      </c>
-      <c r="D290" s="7"/>
+      <c r="D290" s="7" t="s">
+        <v>676</v>
+      </c>
       <c r="E290" s="7"/>
       <c r="F290" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G290" s="26"/>
     </row>
-    <row r="291" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="291" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B291" s="2" t="s">
-        <v>688</v>
+        <v>677</v>
       </c>
       <c r="C291" s="2" t="s">
-        <v>689</v>
-      </c>
-      <c r="D291" s="7"/>
+        <v>678</v>
+      </c>
+      <c r="D291" s="7" t="s">
+        <v>679</v>
+      </c>
       <c r="E291" s="7"/>
       <c r="F291" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G291" s="26"/>
     </row>
-    <row r="292" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B292" s="2" t="s">
-        <v>690</v>
+        <v>680</v>
       </c>
       <c r="C292" s="2" t="s">
-        <v>691</v>
-      </c>
-      <c r="D292" s="7"/>
-      <c r="E292" s="7"/>
-      <c r="F292" s="16" t="s">
+        <v>681</v>
+      </c>
+      <c r="D292" s="1"/>
+      <c r="E292" s="1"/>
+      <c r="F292" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G292" s="24"/>
-    </row>
-    <row r="293" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="G292" s="26"/>
+    </row>
+    <row r="293" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B293" s="2" t="s">
-        <v>692</v>
+        <v>682</v>
       </c>
       <c r="C293" s="2" t="s">
-        <v>693</v>
-      </c>
-      <c r="D293" s="1" t="s">
-        <v>694</v>
-      </c>
-      <c r="E293" s="7" t="s">
-        <v>695</v>
-      </c>
+        <v>683</v>
+      </c>
+      <c r="D293" s="7"/>
+      <c r="E293" s="7"/>
       <c r="F293" s="3" t="s">
         <v>10</v>
       </c>
       <c r="G293" s="26"/>
     </row>
-    <row r="294" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:7" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A294" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B294" s="2" t="s">
-        <v>695</v>
+        <v>684</v>
       </c>
       <c r="C294" s="2" t="s">
-        <v>696</v>
+        <v>685</v>
       </c>
       <c r="D294" s="7"/>
       <c r="E294" s="7"/>
-      <c r="F294" s="6" t="s">
+      <c r="F294" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="G294" s="24"/>
-    </row>
-    <row r="295" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G294" s="26"/>
+    </row>
+    <row r="295" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A295" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B295" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="C295" s="2" t="s">
+        <v>687</v>
+      </c>
+      <c r="D295" s="7"/>
+      <c r="E295" s="7"/>
+      <c r="F295" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G295" s="24"/>
+    </row>
+    <row r="296" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A296" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B296" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="C296" s="2" t="s">
+        <v>689</v>
+      </c>
+      <c r="D296" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="E296" s="7" t="s">
+        <v>691</v>
+      </c>
+      <c r="F296" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G296" s="26"/>
+    </row>
+    <row r="297" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A297" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B297" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="C297" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="D297" s="7"/>
+      <c r="E297" s="7"/>
+      <c r="F297" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G297" s="24"/>
+    </row>
+    <row r="298" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A298" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B298" s="2" t="s">
+        <v>693</v>
+      </c>
+      <c r="C298" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="D298" s="7"/>
+      <c r="E298" s="1"/>
+      <c r="F298" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="G298" s="26"/>
+    </row>
+    <row r="299" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A299" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B299" s="2" t="s">
+        <v>695</v>
+      </c>
+      <c r="C299" s="2" t="s">
+        <v>696</v>
+      </c>
+      <c r="D299" s="7"/>
+      <c r="E299" s="7"/>
+      <c r="F299" s="5" t="s">
+        <v>14</v>
+      </c>
+      <c r="G299" s="26" t="s">
         <v>697</v>
       </c>
-      <c r="C295" s="2" t="s">
+    </row>
+    <row r="300" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A300" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B300" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="D295" s="7"/>
-      <c r="E295" s="1"/>
-      <c r="F295" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="G295" s="26"/>
-    </row>
-    <row r="296" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A296" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B296" s="2" t="s">
+      <c r="C300" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="C296" s="2" t="s">
+      <c r="D300" s="7" t="s">
         <v>700</v>
       </c>
-      <c r="D296" s="7"/>
-      <c r="E296" s="7"/>
-      <c r="F296" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G296" s="26" t="s">
+      <c r="E300" s="7"/>
+      <c r="F300" s="5"/>
+      <c r="G300" s="26"/>
+    </row>
+    <row r="301" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A301" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B301" s="2" t="s">
         <v>701</v>
       </c>
-    </row>
-    <row r="297" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A297" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B297" s="2" t="s">
+      <c r="C301" s="2" t="s">
         <v>702</v>
-      </c>
-      <c r="C297" s="2" t="s">
-        <v>703</v>
-      </c>
-      <c r="D297" s="7" t="s">
-        <v>704</v>
-      </c>
-      <c r="E297" s="7"/>
-      <c r="F297" s="5"/>
-      <c r="G297" s="26"/>
-    </row>
-    <row r="298" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A298" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B298" s="2" t="s">
-        <v>705</v>
-      </c>
-      <c r="C298" s="2" t="s">
-        <v>706</v>
-      </c>
-      <c r="D298" s="7"/>
-      <c r="E298" s="7"/>
-      <c r="F298" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="G298" s="26" t="s">
-        <v>707</v>
-      </c>
-    </row>
-    <row r="299" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A299" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B299" s="2" t="s">
-        <v>708</v>
-      </c>
-      <c r="C299" s="2" t="s">
-        <v>709</v>
-      </c>
-      <c r="D299" s="7"/>
-      <c r="E299" s="7" t="s">
-        <v>697</v>
-      </c>
-      <c r="F299" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G299" s="26"/>
-    </row>
-    <row r="300" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A300" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B300" s="2" t="s">
-        <v>710</v>
-      </c>
-      <c r="C300" s="2" t="s">
-        <v>711</v>
-      </c>
-      <c r="D300" s="7"/>
-      <c r="E300" s="7"/>
-      <c r="F300" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G300" s="26"/>
-    </row>
-    <row r="301" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A301" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B301" s="2" t="s">
-        <v>712</v>
-      </c>
-      <c r="C301" s="2" t="s">
-        <v>713</v>
       </c>
       <c r="D301" s="7"/>
       <c r="E301" s="7"/>
-      <c r="F301" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G301" s="24"/>
-    </row>
-    <row r="302" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F301" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="G301" s="26" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="302" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B302" s="2" t="s">
-        <v>714</v>
+        <v>704</v>
       </c>
       <c r="C302" s="2" t="s">
-        <v>715</v>
+        <v>705</v>
       </c>
       <c r="D302" s="7"/>
-      <c r="E302" s="7"/>
-      <c r="F302" s="19" t="s">
-        <v>20</v>
+      <c r="E302" s="7" t="s">
+        <v>693</v>
+      </c>
+      <c r="F302" s="5" t="s">
+        <v>10</v>
       </c>
       <c r="G302" s="26"/>
     </row>
-    <row r="303" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A303" s="17" t="s">
-        <v>675</v>
-      </c>
-      <c r="B303" s="17" t="s">
-        <v>716</v>
-      </c>
-      <c r="C303" s="17" t="s">
-        <v>717</v>
-      </c>
-      <c r="D303" s="27"/>
-      <c r="E303" s="27"/>
-      <c r="F303" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G303" s="28"/>
-    </row>
-    <row r="304" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A303" s="2" t="s">
+        <v>671</v>
+      </c>
+      <c r="B303" s="2" t="s">
+        <v>706</v>
+      </c>
+      <c r="C303" s="2" t="s">
+        <v>707</v>
+      </c>
+      <c r="D303" s="7"/>
+      <c r="E303" s="7"/>
+      <c r="F303" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G303" s="26"/>
+    </row>
+    <row r="304" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A304" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B304" s="2" t="s">
-        <v>718</v>
+        <v>708</v>
       </c>
       <c r="C304" s="2" t="s">
-        <v>719</v>
+        <v>709</v>
       </c>
       <c r="D304" s="7"/>
       <c r="E304" s="7"/>
-      <c r="F304" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G304" s="26"/>
-    </row>
-    <row r="305" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F304" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G304" s="24"/>
+    </row>
+    <row r="305" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A305" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B305" s="2" t="s">
-        <v>720</v>
+        <v>710</v>
       </c>
       <c r="C305" s="2" t="s">
-        <v>721</v>
+        <v>711</v>
       </c>
       <c r="D305" s="7"/>
-      <c r="E305" s="1"/>
-      <c r="F305" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G305" s="26" t="s">
-        <v>722</v>
-      </c>
-    </row>
-    <row r="306" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A306" s="2" t="s">
-        <v>675</v>
-      </c>
-      <c r="B306" s="2" t="s">
-        <v>723</v>
-      </c>
-      <c r="C306" s="2" t="s">
-        <v>724</v>
-      </c>
-      <c r="D306" s="7"/>
-      <c r="E306" s="7"/>
-      <c r="F306" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G306" s="26"/>
-    </row>
-    <row r="307" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E305" s="7"/>
+      <c r="F305" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G305" s="26"/>
+    </row>
+    <row r="306" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A306" s="17" t="s">
+        <v>671</v>
+      </c>
+      <c r="B306" s="17" t="s">
+        <v>712</v>
+      </c>
+      <c r="C306" s="17" t="s">
+        <v>713</v>
+      </c>
+      <c r="D306" s="27"/>
+      <c r="E306" s="27"/>
+      <c r="F306" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G306" s="28"/>
+    </row>
+    <row r="307" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="2" t="s">
-        <v>675</v>
+        <v>671</v>
       </c>
       <c r="B307" s="2" t="s">
-        <v>725</v>
+        <v>714</v>
       </c>
       <c r="C307" s="2" t="s">
-        <v>726</v>
+        <v>715</v>
       </c>
       <c r="D307" s="7"/>
       <c r="E307" s="7"/>
-      <c r="F307" s="16" t="s">
+      <c r="F307" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="G307" s="24"/>
-    </row>
-    <row r="308" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G307" s="26"/>
+    </row>
+    <row r="308" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A308" s="2" t="s">
-        <v>727</v>
+        <v>671</v>
       </c>
       <c r="B308" s="2" t="s">
-        <v>728</v>
+        <v>716</v>
       </c>
       <c r="C308" s="2" t="s">
-        <v>729</v>
+        <v>717</v>
       </c>
       <c r="D308" s="7"/>
-      <c r="E308" s="7"/>
-      <c r="F308" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G308" s="26"/>
-    </row>
-    <row r="309" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E308" s="1"/>
+      <c r="F308" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G308" s="26" t="s">
+        <v>718</v>
+      </c>
+    </row>
+    <row r="309" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A309" s="2" t="s">
-        <v>727</v>
+        <v>671</v>
       </c>
       <c r="B309" s="2" t="s">
-        <v>730</v>
+        <v>719</v>
       </c>
       <c r="C309" s="2" t="s">
-        <v>731</v>
+        <v>720</v>
       </c>
       <c r="D309" s="7"/>
-      <c r="E309" s="7" t="s">
-        <v>732</v>
-      </c>
+      <c r="E309" s="7"/>
       <c r="F309" s="5" t="s">
-        <v>37</v>
+        <v>10</v>
       </c>
       <c r="G309" s="26"/>
     </row>
-    <row r="310" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="2" t="s">
-        <v>727</v>
+        <v>671</v>
       </c>
       <c r="B310" s="2" t="s">
-        <v>733</v>
+        <v>721</v>
       </c>
       <c r="C310" s="2" t="s">
-        <v>734</v>
+        <v>722</v>
       </c>
       <c r="D310" s="7"/>
       <c r="E310" s="7"/>
-      <c r="F310" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G310" s="26"/>
-    </row>
-    <row r="311" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F310" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G310" s="24"/>
+    </row>
+    <row r="311" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A311" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B311" s="2" t="s">
-        <v>735</v>
+        <v>724</v>
       </c>
       <c r="C311" s="2" t="s">
-        <v>736</v>
+        <v>725</v>
       </c>
       <c r="D311" s="7"/>
       <c r="E311" s="7"/>
-      <c r="F311" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="G311" s="26" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="312" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A312" s="17" t="s">
+      <c r="F311" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G311" s="26"/>
+    </row>
+    <row r="312" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A312" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B312" s="2" t="s">
+        <v>726</v>
+      </c>
+      <c r="C312" s="2" t="s">
         <v>727</v>
       </c>
-      <c r="B312" s="17" t="s">
-        <v>738</v>
-      </c>
-      <c r="C312" s="17" t="s">
-        <v>739</v>
-      </c>
-      <c r="D312" s="27"/>
-      <c r="E312" s="27"/>
-      <c r="F312" s="20" t="s">
-        <v>20</v>
-      </c>
-      <c r="G312" s="28"/>
-    </row>
-    <row r="313" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D312" s="7"/>
+      <c r="E312" s="7" t="s">
+        <v>728</v>
+      </c>
+      <c r="F312" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="G312" s="26"/>
+    </row>
+    <row r="313" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A313" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B313" s="2" t="s">
-        <v>740</v>
+        <v>729</v>
       </c>
       <c r="C313" s="2" t="s">
-        <v>741</v>
+        <v>730</v>
       </c>
       <c r="D313" s="7"/>
       <c r="E313" s="7"/>
-      <c r="F313" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="G313" s="24"/>
-    </row>
-    <row r="314" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F313" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G313" s="26"/>
+    </row>
+    <row r="314" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A314" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B314" s="2" t="s">
-        <v>742</v>
+        <v>731</v>
       </c>
       <c r="C314" s="2" t="s">
-        <v>743</v>
+        <v>732</v>
       </c>
       <c r="D314" s="7"/>
       <c r="E314" s="7"/>
-      <c r="F314" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G314" s="24"/>
-    </row>
-    <row r="315" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A315" s="2" t="s">
-        <v>727</v>
-      </c>
-      <c r="B315" s="2" t="s">
-        <v>744</v>
-      </c>
-      <c r="C315" s="2" t="s">
-        <v>745</v>
-      </c>
-      <c r="D315" s="7"/>
-      <c r="E315" s="7"/>
-      <c r="F315" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="G315" s="24"/>
-    </row>
-    <row r="316" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+      <c r="F314" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="G314" s="26" t="s">
+        <v>733</v>
+      </c>
+    </row>
+    <row r="315" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A315" s="17" t="s">
+        <v>723</v>
+      </c>
+      <c r="B315" s="17" t="s">
+        <v>734</v>
+      </c>
+      <c r="C315" s="17" t="s">
+        <v>735</v>
+      </c>
+      <c r="D315" s="27"/>
+      <c r="E315" s="27"/>
+      <c r="F315" s="20" t="s">
+        <v>20</v>
+      </c>
+      <c r="G315" s="28"/>
+    </row>
+    <row r="316" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="2" t="s">
-        <v>727</v>
+        <v>723</v>
       </c>
       <c r="B316" s="2" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="C316" s="2" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="D316" s="7"/>
       <c r="E316" s="7"/>
       <c r="F316" s="6" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G316" s="24"/>
     </row>
-    <row r="317" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A317" s="17" t="s">
-        <v>747</v>
-      </c>
-      <c r="B317" s="17" t="s">
-        <v>748</v>
-      </c>
-      <c r="C317" s="17" t="s">
-        <v>749</v>
-      </c>
-      <c r="D317" s="27"/>
-      <c r="E317" s="27"/>
-      <c r="F317" s="22" t="s">
-        <v>267</v>
-      </c>
-      <c r="G317" s="28" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="318" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A317" s="2" t="s">
+        <v>723</v>
+      </c>
+      <c r="B317" s="2" t="s">
+        <v>738</v>
+      </c>
+      <c r="C317" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="D317" s="7"/>
+      <c r="E317" s="7"/>
+      <c r="F317" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G317" s="24"/>
+    </row>
+    <row r="318" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A318" s="2" t="s">
-        <v>747</v>
+        <v>723</v>
       </c>
       <c r="B318" s="2" t="s">
-        <v>751</v>
+        <v>740</v>
       </c>
       <c r="C318" s="2" t="s">
-        <v>752</v>
+        <v>741</v>
       </c>
       <c r="D318" s="7"/>
       <c r="E318" s="7"/>
-      <c r="F318" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G318" s="26" t="s">
-        <v>753</v>
-      </c>
-    </row>
-    <row r="319" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F318" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="G318" s="24"/>
+    </row>
+    <row r="319" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A319" s="2" t="s">
-        <v>747</v>
+        <v>723</v>
       </c>
       <c r="B319" s="2" t="s">
-        <v>754</v>
+        <v>728</v>
       </c>
       <c r="C319" s="2" t="s">
-        <v>755</v>
+        <v>742</v>
       </c>
       <c r="D319" s="7"/>
       <c r="E319" s="7"/>
-      <c r="F319" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G319" s="26" t="s">
-        <v>756</v>
-      </c>
-    </row>
-    <row r="320" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A320" s="2" t="s">
+      <c r="F319" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="G319" s="24"/>
+    </row>
+    <row r="320" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A320" s="17" t="s">
+        <v>743</v>
+      </c>
+      <c r="B320" s="17" t="s">
+        <v>744</v>
+      </c>
+      <c r="C320" s="17" t="s">
+        <v>745</v>
+      </c>
+      <c r="D320" s="27"/>
+      <c r="E320" s="27"/>
+      <c r="F320" s="22" t="s">
+        <v>267</v>
+      </c>
+      <c r="G320" s="28" t="s">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="321" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A321" s="2" t="s">
+        <v>743</v>
+      </c>
+      <c r="B321" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="B320" s="2" t="s">
-        <v>757</v>
-      </c>
-      <c r="C320" s="2" t="s">
-        <v>758</v>
-      </c>
-      <c r="D320" s="7"/>
-      <c r="E320" s="7"/>
-      <c r="F320" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="G320" s="26" t="s">
-        <v>759</v>
-      </c>
-    </row>
-    <row r="321" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A321" s="2" t="s">
-        <v>747</v>
-      </c>
-      <c r="B321" s="2" t="s">
-        <v>760</v>
-      </c>
       <c r="C321" s="2" t="s">
-        <v>761</v>
+        <v>748</v>
       </c>
       <c r="D321" s="7"/>
       <c r="E321" s="7"/>
-      <c r="F321" s="5" t="s">
+      <c r="F321" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="G321" s="26"/>
-    </row>
-    <row r="322" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G321" s="26" t="s">
+        <v>749</v>
+      </c>
+    </row>
+    <row r="322" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A322" s="2" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="B322" s="2" t="s">
-        <v>763</v>
+        <v>750</v>
       </c>
       <c r="C322" s="2" t="s">
-        <v>764</v>
+        <v>751</v>
       </c>
       <c r="D322" s="7"/>
       <c r="E322" s="7"/>
-      <c r="F322" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G322" s="26"/>
-    </row>
-    <row r="323" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F322" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="G322" s="26" t="s">
+        <v>752</v>
+      </c>
+    </row>
+    <row r="323" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="2" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="B323" s="2" t="s">
-        <v>1000</v>
+        <v>753</v>
       </c>
       <c r="C323" s="2" t="s">
-        <v>1001</v>
+        <v>754</v>
       </c>
       <c r="D323" s="7"/>
       <c r="E323" s="7"/>
       <c r="F323" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="G323" s="26"/>
-    </row>
-    <row r="324" spans="1:7" x14ac:dyDescent="0.35">
+        <v>25</v>
+      </c>
+      <c r="G323" s="26" t="s">
+        <v>755</v>
+      </c>
+    </row>
+    <row r="324" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A324" s="2" t="s">
-        <v>762</v>
+        <v>743</v>
       </c>
       <c r="B324" s="2" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="C324" s="2" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="D324" s="7"/>
       <c r="E324" s="7"/>
       <c r="F324" s="5" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G324" s="26"/>
     </row>
-    <row r="325" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A325" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B325" s="2" t="s">
-        <v>767</v>
+        <v>759</v>
       </c>
       <c r="C325" s="2" t="s">
-        <v>768</v>
+        <v>760</v>
       </c>
       <c r="D325" s="7"/>
       <c r="E325" s="7"/>
       <c r="F325" s="4" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G325" s="26"/>
     </row>
-    <row r="326" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A326" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B326" s="2" t="s">
-        <v>769</v>
+        <v>996</v>
       </c>
       <c r="C326" s="2" t="s">
-        <v>770</v>
+        <v>997</v>
       </c>
       <c r="D326" s="7"/>
       <c r="E326" s="7"/>
@@ -9898,83 +9929,83 @@
       </c>
       <c r="G326" s="26"/>
     </row>
-    <row r="327" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A327" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B327" s="2" t="s">
+        <v>761</v>
+      </c>
+      <c r="C327" s="2" t="s">
         <v>762</v>
-      </c>
-      <c r="B327" s="2" t="s">
-        <v>771</v>
-      </c>
-      <c r="C327" s="2" t="s">
-        <v>772</v>
       </c>
       <c r="D327" s="7"/>
       <c r="E327" s="7"/>
       <c r="F327" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G327" s="26"/>
     </row>
-    <row r="328" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B328" s="2" t="s">
-        <v>773</v>
+        <v>763</v>
       </c>
       <c r="C328" s="2" t="s">
-        <v>774</v>
+        <v>764</v>
       </c>
       <c r="D328" s="7"/>
       <c r="E328" s="7"/>
-      <c r="F328" s="3" t="s">
+      <c r="F328" s="4" t="s">
         <v>20</v>
       </c>
       <c r="G328" s="26"/>
     </row>
-    <row r="329" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A329" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B329" s="2" t="s">
-        <v>775</v>
+        <v>765</v>
       </c>
       <c r="C329" s="2" t="s">
-        <v>776</v>
+        <v>766</v>
       </c>
       <c r="D329" s="7"/>
       <c r="E329" s="7"/>
-      <c r="F329" s="3" t="s">
+      <c r="F329" s="4" t="s">
         <v>29</v>
       </c>
       <c r="G329" s="26"/>
     </row>
-    <row r="330" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A330" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B330" s="2" t="s">
-        <v>777</v>
+        <v>767</v>
       </c>
       <c r="C330" s="2" t="s">
-        <v>778</v>
+        <v>768</v>
       </c>
       <c r="D330" s="7"/>
-      <c r="E330" s="1"/>
+      <c r="E330" s="7"/>
       <c r="F330" s="5" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="G330" s="26"/>
     </row>
-    <row r="331" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B331" s="2" t="s">
-        <v>779</v>
+        <v>769</v>
       </c>
       <c r="C331" s="2" t="s">
-        <v>780</v>
+        <v>770</v>
       </c>
       <c r="D331" s="7"/>
       <c r="E331" s="7"/>
@@ -9983,68 +10014,66 @@
       </c>
       <c r="G331" s="26"/>
     </row>
-    <row r="332" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B332" s="2" t="s">
-        <v>781</v>
+        <v>771</v>
       </c>
       <c r="C332" s="2" t="s">
-        <v>782</v>
+        <v>772</v>
       </c>
       <c r="D332" s="7"/>
       <c r="E332" s="7"/>
-      <c r="F332" s="5" t="s">
-        <v>10</v>
+      <c r="F332" s="3" t="s">
+        <v>29</v>
       </c>
       <c r="G332" s="26"/>
     </row>
-    <row r="333" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A333" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B333" s="2" t="s">
-        <v>783</v>
+        <v>773</v>
       </c>
       <c r="C333" s="2" t="s">
-        <v>784</v>
+        <v>774</v>
       </c>
       <c r="D333" s="7"/>
-      <c r="E333" s="7"/>
+      <c r="E333" s="1"/>
       <c r="F333" s="5" t="s">
-        <v>10</v>
+        <v>29</v>
       </c>
       <c r="G333" s="26"/>
     </row>
-    <row r="334" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A334" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B334" s="2" t="s">
-        <v>1049</v>
+        <v>775</v>
       </c>
       <c r="C334" s="2" t="s">
-        <v>1050</v>
+        <v>776</v>
       </c>
       <c r="D334" s="7"/>
       <c r="E334" s="7"/>
-      <c r="F334" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G334" s="26" t="s">
-        <v>1051</v>
-      </c>
-    </row>
-    <row r="335" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F334" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G334" s="26"/>
+    </row>
+    <row r="335" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B335" s="2" t="s">
-        <v>785</v>
+        <v>777</v>
       </c>
       <c r="C335" s="2" t="s">
-        <v>786</v>
+        <v>778</v>
       </c>
       <c r="D335" s="7"/>
       <c r="E335" s="7"/>
@@ -10053,119 +10082,119 @@
       </c>
       <c r="G335" s="26"/>
     </row>
-    <row r="336" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B336" s="2" t="s">
-        <v>787</v>
+        <v>779</v>
       </c>
       <c r="C336" s="2" t="s">
-        <v>788</v>
+        <v>780</v>
       </c>
       <c r="D336" s="7"/>
       <c r="E336" s="7"/>
       <c r="F336" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G336" s="26"/>
     </row>
-    <row r="337" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A337" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B337" s="2" t="s">
-        <v>789</v>
+        <v>1045</v>
       </c>
       <c r="C337" s="2" t="s">
-        <v>790</v>
-      </c>
-      <c r="D337" s="1"/>
+        <v>1046</v>
+      </c>
+      <c r="D337" s="7"/>
       <c r="E337" s="7"/>
       <c r="F337" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G337" s="26"/>
-    </row>
-    <row r="338" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="G337" s="26" t="s">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="338" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A338" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B338" s="2" t="s">
-        <v>791</v>
+        <v>781</v>
       </c>
       <c r="C338" s="2" t="s">
-        <v>792</v>
+        <v>782</v>
       </c>
       <c r="D338" s="7"/>
       <c r="E338" s="7"/>
       <c r="F338" s="5" t="s">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G338" s="26"/>
     </row>
-    <row r="339" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B339" s="2" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="C339" s="2" t="s">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="D339" s="7"/>
       <c r="E339" s="7"/>
-      <c r="F339" s="3" t="s">
+      <c r="F339" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G339" s="26"/>
     </row>
-    <row r="340" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B340" s="2" t="s">
-        <v>795</v>
+        <v>785</v>
       </c>
       <c r="C340" s="2" t="s">
-        <v>796</v>
-      </c>
-      <c r="D340" s="7" t="s">
-        <v>797</v>
-      </c>
+        <v>786</v>
+      </c>
+      <c r="D340" s="1"/>
       <c r="E340" s="7"/>
-      <c r="F340" s="3" t="s">
+      <c r="F340" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G340" s="26"/>
     </row>
-    <row r="341" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B341" s="2" t="s">
-        <v>798</v>
+        <v>787</v>
       </c>
       <c r="C341" s="2" t="s">
-        <v>799</v>
+        <v>788</v>
       </c>
       <c r="D341" s="7"/>
       <c r="E341" s="7"/>
-      <c r="F341" s="3" t="s">
+      <c r="F341" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G341" s="26"/>
     </row>
-    <row r="342" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A342" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B342" s="2" t="s">
-        <v>800</v>
+        <v>789</v>
       </c>
       <c r="C342" s="2" t="s">
-        <v>801</v>
+        <v>790</v>
       </c>
       <c r="D342" s="7"/>
       <c r="E342" s="7"/>
@@ -10174,261 +10203,261 @@
       </c>
       <c r="G342" s="26"/>
     </row>
-    <row r="343" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B343" s="2" t="s">
-        <v>802</v>
+        <v>791</v>
       </c>
       <c r="C343" s="2" t="s">
-        <v>803</v>
-      </c>
-      <c r="D343" s="7"/>
+        <v>792</v>
+      </c>
+      <c r="D343" s="7" t="s">
+        <v>793</v>
+      </c>
       <c r="E343" s="7"/>
-      <c r="F343" s="4" t="s">
-        <v>10</v>
+      <c r="F343" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G343" s="26"/>
     </row>
-    <row r="344" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B344" s="2" t="s">
-        <v>804</v>
+        <v>794</v>
       </c>
       <c r="C344" s="2" t="s">
-        <v>805</v>
+        <v>795</v>
       </c>
       <c r="D344" s="7"/>
       <c r="E344" s="7"/>
-      <c r="F344" s="4" t="s">
-        <v>10</v>
+      <c r="F344" s="3" t="s">
+        <v>20</v>
       </c>
       <c r="G344" s="26"/>
     </row>
-    <row r="345" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B345" s="2" t="s">
-        <v>806</v>
+        <v>796</v>
       </c>
       <c r="C345" s="2" t="s">
-        <v>807</v>
+        <v>797</v>
       </c>
       <c r="D345" s="7"/>
       <c r="E345" s="7"/>
-      <c r="F345" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="G345" s="24"/>
-    </row>
-    <row r="346" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F345" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G345" s="26"/>
+    </row>
+    <row r="346" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A346" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B346" s="2" t="s">
-        <v>808</v>
+        <v>798</v>
       </c>
       <c r="C346" s="2" t="s">
-        <v>809</v>
+        <v>799</v>
       </c>
       <c r="D346" s="7"/>
       <c r="E346" s="7"/>
-      <c r="F346" s="5" t="s">
+      <c r="F346" s="4" t="s">
         <v>10</v>
       </c>
       <c r="G346" s="26"/>
     </row>
-    <row r="347" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B347" s="2" t="s">
-        <v>810</v>
+        <v>800</v>
       </c>
       <c r="C347" s="2" t="s">
-        <v>811</v>
+        <v>801</v>
       </c>
       <c r="D347" s="7"/>
       <c r="E347" s="7"/>
-      <c r="F347" s="5" t="s">
-        <v>29</v>
+      <c r="F347" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="G347" s="26"/>
     </row>
-    <row r="348" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B348" s="2" t="s">
-        <v>812</v>
+        <v>802</v>
       </c>
       <c r="C348" s="2" t="s">
-        <v>813</v>
+        <v>803</v>
       </c>
       <c r="D348" s="7"/>
       <c r="E348" s="7"/>
-      <c r="F348" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G348" s="26"/>
-    </row>
-    <row r="349" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F348" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="G348" s="24"/>
+    </row>
+    <row r="349" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A349" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B349" s="2" t="s">
-        <v>814</v>
+        <v>804</v>
       </c>
       <c r="C349" s="2" t="s">
-        <v>815</v>
+        <v>805</v>
       </c>
       <c r="D349" s="7"/>
       <c r="E349" s="7"/>
-      <c r="F349" s="4" t="s">
-        <v>816</v>
-      </c>
-      <c r="G349" s="26" t="s">
-        <v>817</v>
-      </c>
-    </row>
-    <row r="350" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F349" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="G349" s="26"/>
+    </row>
+    <row r="350" spans="1:7" ht="60" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B350" s="2" t="s">
-        <v>818</v>
+        <v>806</v>
       </c>
       <c r="C350" s="2" t="s">
-        <v>819</v>
-      </c>
-      <c r="D350" s="1"/>
+        <v>807</v>
+      </c>
+      <c r="D350" s="7"/>
       <c r="E350" s="7"/>
       <c r="F350" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G350" s="26"/>
     </row>
-    <row r="351" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A351" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B351" s="2" t="s">
-        <v>820</v>
+        <v>808</v>
       </c>
       <c r="C351" s="2" t="s">
-        <v>821</v>
+        <v>809</v>
       </c>
       <c r="D351" s="7"/>
       <c r="E351" s="7"/>
-      <c r="F351" s="4" t="s">
-        <v>20</v>
+      <c r="F351" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="G351" s="26"/>
     </row>
-    <row r="352" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A352" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B352" s="2" t="s">
-        <v>1040</v>
+        <v>810</v>
       </c>
       <c r="C352" s="2" t="s">
-        <v>1041</v>
-      </c>
-      <c r="D352" s="7" t="s">
-        <v>1042</v>
-      </c>
+        <v>811</v>
+      </c>
+      <c r="D352" s="7"/>
       <c r="E352" s="7"/>
-      <c r="F352" s="5" t="s">
-        <v>29</v>
+      <c r="F352" s="4" t="s">
+        <v>812</v>
       </c>
       <c r="G352" s="26" t="s">
-        <v>1043</v>
-      </c>
-    </row>
-    <row r="353" spans="1:7" x14ac:dyDescent="0.35">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B353" s="2" t="s">
-        <v>822</v>
+        <v>814</v>
       </c>
       <c r="C353" s="2" t="s">
-        <v>823</v>
-      </c>
-      <c r="D353" s="7"/>
+        <v>815</v>
+      </c>
+      <c r="D353" s="1"/>
       <c r="E353" s="7"/>
-      <c r="F353" s="4" t="s">
+      <c r="F353" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G353" s="26"/>
     </row>
-    <row r="354" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A354" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B354" s="2" t="s">
-        <v>824</v>
+        <v>816</v>
       </c>
       <c r="C354" s="2" t="s">
-        <v>825</v>
+        <v>817</v>
       </c>
       <c r="D354" s="7"/>
       <c r="E354" s="7"/>
-      <c r="F354" s="5" t="s">
+      <c r="F354" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G354" s="26"/>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A355" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B355" s="2" t="s">
+        <v>1036</v>
+      </c>
+      <c r="C355" s="2" t="s">
+        <v>1037</v>
+      </c>
+      <c r="D355" s="7" t="s">
+        <v>1038</v>
+      </c>
+      <c r="E355" s="7"/>
+      <c r="F355" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="G354" s="26"/>
-    </row>
-    <row r="355" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A355" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B355" s="2" t="s">
-        <v>826</v>
-      </c>
-      <c r="C355" s="2" t="s">
-        <v>827</v>
-      </c>
-      <c r="D355" s="7" t="s">
-        <v>828</v>
-      </c>
-      <c r="E355" s="7"/>
-      <c r="F355" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G355" s="26"/>
-    </row>
-    <row r="356" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G355" s="26" t="s">
+        <v>1039</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A356" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B356" s="2" t="s">
-        <v>829</v>
+        <v>818</v>
       </c>
       <c r="C356" s="2" t="s">
-        <v>830</v>
+        <v>819</v>
       </c>
       <c r="D356" s="7"/>
       <c r="E356" s="7"/>
-      <c r="F356" s="3" t="s">
-        <v>29</v>
+      <c r="F356" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G356" s="26"/>
     </row>
-    <row r="357" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B357" s="2" t="s">
-        <v>831</v>
+        <v>820</v>
       </c>
       <c r="C357" s="2" t="s">
-        <v>832</v>
+        <v>821</v>
       </c>
       <c r="D357" s="7"/>
       <c r="E357" s="7"/>
@@ -10437,589 +10466,589 @@
       </c>
       <c r="G357" s="26"/>
     </row>
-    <row r="358" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B358" s="2" t="s">
-        <v>833</v>
+        <v>822</v>
       </c>
       <c r="C358" s="2" t="s">
-        <v>834</v>
-      </c>
-      <c r="D358" s="7"/>
+        <v>823</v>
+      </c>
+      <c r="D358" s="7" t="s">
+        <v>824</v>
+      </c>
       <c r="E358" s="7"/>
-      <c r="F358" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G358" s="24"/>
-    </row>
-    <row r="359" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F358" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G358" s="26"/>
+    </row>
+    <row r="359" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A359" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B359" s="2" t="s">
-        <v>835</v>
+        <v>825</v>
       </c>
       <c r="C359" s="2" t="s">
-        <v>836</v>
+        <v>826</v>
       </c>
       <c r="D359" s="7"/>
       <c r="E359" s="7"/>
-      <c r="F359" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G359" s="24"/>
-    </row>
-    <row r="360" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F359" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G359" s="26"/>
+    </row>
+    <row r="360" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B360" s="2" t="s">
-        <v>837</v>
+        <v>827</v>
       </c>
       <c r="C360" s="2" t="s">
-        <v>838</v>
+        <v>828</v>
       </c>
       <c r="D360" s="7"/>
       <c r="E360" s="7"/>
-      <c r="F360" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="G360" s="24"/>
-    </row>
-    <row r="361" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F360" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G360" s="26"/>
+    </row>
+    <row r="361" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A361" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B361" s="2" t="s">
-        <v>839</v>
+        <v>829</v>
       </c>
       <c r="C361" s="2" t="s">
-        <v>840</v>
+        <v>830</v>
       </c>
       <c r="D361" s="7"/>
-      <c r="E361" s="1"/>
-      <c r="F361" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G361" s="26"/>
-    </row>
-    <row r="362" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E361" s="7"/>
+      <c r="F361" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G361" s="24"/>
+    </row>
+    <row r="362" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B362" s="2" t="s">
-        <v>841</v>
+        <v>831</v>
       </c>
       <c r="C362" s="2" t="s">
-        <v>842</v>
+        <v>832</v>
       </c>
       <c r="D362" s="7"/>
       <c r="E362" s="7"/>
-      <c r="F362" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G362" s="26" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="363" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="F362" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G362" s="24"/>
+    </row>
+    <row r="363" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B363" s="2" t="s">
-        <v>844</v>
+        <v>833</v>
       </c>
       <c r="C363" s="2" t="s">
-        <v>845</v>
+        <v>834</v>
       </c>
       <c r="D363" s="7"/>
       <c r="E363" s="7"/>
-      <c r="F363" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G363" s="26" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="364" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F363" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="G363" s="24"/>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A364" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B364" s="2" t="s">
-        <v>846</v>
+        <v>835</v>
       </c>
       <c r="C364" s="2" t="s">
-        <v>847</v>
+        <v>836</v>
       </c>
       <c r="D364" s="7"/>
-      <c r="E364" s="7"/>
+      <c r="E364" s="1"/>
       <c r="F364" s="4" t="s">
-        <v>14</v>
-      </c>
-      <c r="G364" s="26" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="365" spans="1:7" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+      <c r="G364" s="26"/>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A365" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B365" s="2" t="s">
-        <v>1052</v>
+        <v>837</v>
       </c>
       <c r="C365" s="2" t="s">
-        <v>1053</v>
+        <v>838</v>
       </c>
       <c r="D365" s="7"/>
       <c r="E365" s="7"/>
       <c r="F365" s="5" t="s">
-        <v>29</v>
+        <v>14</v>
       </c>
       <c r="G365" s="26" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="366" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" ht="30.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A366" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B366" s="2" t="s">
-        <v>848</v>
+        <v>840</v>
       </c>
       <c r="C366" s="2" t="s">
-        <v>849</v>
+        <v>841</v>
       </c>
       <c r="D366" s="7"/>
-      <c r="E366" s="7" t="s">
-        <v>793</v>
-      </c>
-      <c r="F366" s="6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G366" s="24"/>
-    </row>
-    <row r="367" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="E366" s="7"/>
+      <c r="F366" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G366" s="26" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B367" s="2" t="s">
-        <v>850</v>
+        <v>842</v>
       </c>
       <c r="C367" s="2" t="s">
-        <v>851</v>
+        <v>843</v>
       </c>
       <c r="D367" s="7"/>
       <c r="E367" s="7"/>
-      <c r="F367" s="5" t="s">
-        <v>852</v>
-      </c>
-      <c r="G367" s="26"/>
-    </row>
-    <row r="368" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F367" s="4" t="s">
+        <v>14</v>
+      </c>
+      <c r="G367" s="26" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A368" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B368" s="2" t="s">
-        <v>1002</v>
+        <v>1048</v>
       </c>
       <c r="C368" s="2" t="s">
-        <v>1003</v>
+        <v>1049</v>
       </c>
       <c r="D368" s="7"/>
       <c r="E368" s="7"/>
       <c r="F368" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G368" s="26"/>
-    </row>
-    <row r="369" spans="1:7" ht="29" x14ac:dyDescent="0.35">
+        <v>29</v>
+      </c>
+      <c r="G368" s="26" t="s">
+        <v>1050</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B369" s="2" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="C369" s="2" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="D369" s="7"/>
-      <c r="E369" s="7"/>
-      <c r="F369" s="5" t="s">
+      <c r="E369" s="7" t="s">
+        <v>789</v>
+      </c>
+      <c r="F369" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="G369" s="26"/>
-    </row>
-    <row r="370" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="G369" s="24"/>
+    </row>
+    <row r="370" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B370" s="2" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="C370" s="2" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="D370" s="7"/>
       <c r="E370" s="7"/>
-      <c r="F370" s="16" t="s">
-        <v>29</v>
-      </c>
-      <c r="G370" s="24"/>
-    </row>
-    <row r="371" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F370" s="5" t="s">
+        <v>848</v>
+      </c>
+      <c r="G370" s="26"/>
+    </row>
+    <row r="371" spans="1:7" ht="45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B371" s="2" t="s">
-        <v>857</v>
+        <v>998</v>
       </c>
       <c r="C371" s="2" t="s">
-        <v>858</v>
+        <v>999</v>
       </c>
       <c r="D371" s="7"/>
       <c r="E371" s="7"/>
-      <c r="F371" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="G371" s="26" t="s">
-        <v>859</v>
-      </c>
-    </row>
-    <row r="372" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="F371" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G371" s="26"/>
+    </row>
+    <row r="372" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A372" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B372" s="2" t="s">
-        <v>860</v>
+        <v>849</v>
       </c>
       <c r="C372" s="2" t="s">
-        <v>861</v>
+        <v>850</v>
       </c>
       <c r="D372" s="7"/>
       <c r="E372" s="7"/>
       <c r="F372" s="5" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="G372" s="26"/>
     </row>
-    <row r="373" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B373" s="2" t="s">
-        <v>862</v>
+        <v>851</v>
       </c>
       <c r="C373" s="2" t="s">
-        <v>863</v>
+        <v>852</v>
       </c>
       <c r="D373" s="7"/>
       <c r="E373" s="7"/>
-      <c r="F373" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G373" s="26"/>
-    </row>
-    <row r="374" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="F373" s="16" t="s">
+        <v>29</v>
+      </c>
+      <c r="G373" s="24"/>
+    </row>
+    <row r="374" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B374" s="2" t="s">
-        <v>864</v>
+        <v>853</v>
       </c>
       <c r="C374" s="2" t="s">
-        <v>865</v>
+        <v>854</v>
       </c>
       <c r="D374" s="7"/>
       <c r="E374" s="7"/>
-      <c r="F374" s="5" t="s">
-        <v>14</v>
+      <c r="F374" s="14" t="s">
+        <v>25</v>
       </c>
       <c r="G374" s="26" t="s">
-        <v>866</v>
-      </c>
-    </row>
-    <row r="375" spans="1:7" x14ac:dyDescent="0.35">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="375" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A375" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B375" s="2" t="s">
-        <v>867</v>
+        <v>856</v>
       </c>
       <c r="C375" s="2" t="s">
-        <v>868</v>
+        <v>857</v>
       </c>
       <c r="D375" s="7"/>
       <c r="E375" s="7"/>
-      <c r="F375" s="12" t="s">
+      <c r="F375" s="5" t="s">
         <v>20</v>
       </c>
       <c r="G375" s="26"/>
     </row>
-    <row r="376" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A376" t="s">
-        <v>762</v>
-      </c>
-      <c r="B376" t="s">
-        <v>869</v>
-      </c>
-      <c r="C376" t="s">
-        <v>870</v>
+    <row r="376" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A376" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B376" s="2" t="s">
+        <v>858</v>
+      </c>
+      <c r="C376" s="2" t="s">
+        <v>859</v>
       </c>
       <c r="D376" s="7"/>
       <c r="E376" s="7"/>
-      <c r="F376" s="12" t="s">
-        <v>29</v>
+      <c r="F376" s="4" t="s">
+        <v>20</v>
       </c>
       <c r="G376" s="26"/>
     </row>
-    <row r="377" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:7" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B377" s="2" t="s">
-        <v>871</v>
+        <v>860</v>
       </c>
       <c r="C377" s="2" t="s">
-        <v>872</v>
+        <v>861</v>
       </c>
       <c r="D377" s="7"/>
-      <c r="E377" s="1"/>
+      <c r="E377" s="7"/>
       <c r="F377" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G377" s="26"/>
-    </row>
-    <row r="378" spans="1:7" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="G377" s="26" t="s">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="378" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A378" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B378" s="2" t="s">
-        <v>873</v>
+        <v>863</v>
       </c>
       <c r="C378" s="2" t="s">
-        <v>874</v>
+        <v>864</v>
       </c>
       <c r="D378" s="7"/>
       <c r="E378" s="7"/>
-      <c r="F378" s="5" t="s">
+      <c r="F378" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="G378" s="26"/>
+    </row>
+    <row r="379" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A379" t="s">
+        <v>758</v>
+      </c>
+      <c r="B379" t="s">
+        <v>865</v>
+      </c>
+      <c r="C379" t="s">
+        <v>866</v>
+      </c>
+      <c r="D379" s="7"/>
+      <c r="E379" s="7"/>
+      <c r="F379" s="12" t="s">
+        <v>29</v>
+      </c>
+      <c r="G379" s="26"/>
+    </row>
+    <row r="380" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A380" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B380" s="2" t="s">
+        <v>867</v>
+      </c>
+      <c r="C380" s="2" t="s">
+        <v>868</v>
+      </c>
+      <c r="D380" s="7"/>
+      <c r="E380" s="1"/>
+      <c r="F380" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G380" s="26"/>
+    </row>
+    <row r="381" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A381" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B381" s="2" t="s">
+        <v>869</v>
+      </c>
+      <c r="C381" s="2" t="s">
+        <v>870</v>
+      </c>
+      <c r="D381" s="7"/>
+      <c r="E381" s="7"/>
+      <c r="F381" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="G378" s="26"/>
-    </row>
-    <row r="379" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A379" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B379" s="2" t="s">
-        <v>1004</v>
-      </c>
-      <c r="C379" s="2" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D379" s="7"/>
-      <c r="E379" s="7" t="s">
-        <v>1006</v>
-      </c>
-      <c r="F379" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G379" s="26"/>
-    </row>
-    <row r="380" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A380" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B380" s="2" t="s">
+      <c r="G381" s="26"/>
+    </row>
+    <row r="382" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A382" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B382" s="2" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C382" s="2" t="s">
+        <v>1001</v>
+      </c>
+      <c r="D382" s="7"/>
+      <c r="E382" s="7" t="s">
+        <v>1002</v>
+      </c>
+      <c r="F382" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G382" s="26"/>
+    </row>
+    <row r="383" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A383" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B383" s="2" t="s">
+        <v>871</v>
+      </c>
+      <c r="C383" s="2" t="s">
+        <v>872</v>
+      </c>
+      <c r="D383" s="7"/>
+      <c r="E383" s="7"/>
+      <c r="F383" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="G383" s="26"/>
+    </row>
+    <row r="384" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A384" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B384" s="2" t="s">
+        <v>873</v>
+      </c>
+      <c r="C384" s="2" t="s">
+        <v>874</v>
+      </c>
+      <c r="D384" s="7"/>
+      <c r="E384" s="7" t="s">
+        <v>869</v>
+      </c>
+      <c r="F384" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="G384" s="24"/>
+    </row>
+    <row r="385" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A385" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B385" s="2" t="s">
         <v>875</v>
       </c>
-      <c r="C380" s="2" t="s">
+      <c r="C385" s="2" t="s">
         <v>876</v>
       </c>
-      <c r="D380" s="7"/>
-      <c r="E380" s="7"/>
-      <c r="F380" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="G380" s="26"/>
-    </row>
-    <row r="381" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A381" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B381" s="2" t="s">
+      <c r="D385" s="7"/>
+      <c r="E385" s="7"/>
+      <c r="F385" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G385" s="24"/>
+    </row>
+    <row r="386" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A386" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B386" s="2" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C386" s="2" t="s">
+        <v>1042</v>
+      </c>
+      <c r="D386" s="7" t="s">
+        <v>1043</v>
+      </c>
+      <c r="E386" s="7" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F386" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="G386" s="26" t="s">
+        <v>1044</v>
+      </c>
+    </row>
+    <row r="387" spans="1:7" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A387" s="17" t="s">
+        <v>758</v>
+      </c>
+      <c r="B387" s="17" t="s">
         <v>877</v>
       </c>
-      <c r="C381" s="2" t="s">
+      <c r="C387" s="17" t="s">
         <v>878</v>
       </c>
-      <c r="D381" s="7"/>
-      <c r="E381" s="7" t="s">
-        <v>873</v>
-      </c>
-      <c r="F381" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="G381" s="24"/>
-    </row>
-    <row r="382" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A382" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B382" s="2" t="s">
+      <c r="D387" s="27"/>
+      <c r="E387" s="27"/>
+      <c r="F387" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="G387" s="28"/>
+    </row>
+    <row r="388" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A388" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B388" s="2" t="s">
         <v>879</v>
       </c>
-      <c r="C382" s="2" t="s">
+      <c r="C388" s="2" t="s">
         <v>880</v>
-      </c>
-      <c r="D382" s="7"/>
-      <c r="E382" s="7"/>
-      <c r="F382" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G382" s="24"/>
-    </row>
-    <row r="383" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A383" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B383" s="2" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C383" s="2" t="s">
-        <v>1046</v>
-      </c>
-      <c r="D383" s="7" t="s">
-        <v>1047</v>
-      </c>
-      <c r="E383" s="7" t="s">
-        <v>1044</v>
-      </c>
-      <c r="F383" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="G383" s="26" t="s">
-        <v>1048</v>
-      </c>
-    </row>
-    <row r="384" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A384" s="17" t="s">
-        <v>762</v>
-      </c>
-      <c r="B384" s="17" t="s">
-        <v>881</v>
-      </c>
-      <c r="C384" s="17" t="s">
-        <v>882</v>
-      </c>
-      <c r="D384" s="27"/>
-      <c r="E384" s="27"/>
-      <c r="F384" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="G384" s="28"/>
-    </row>
-    <row r="385" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A385" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B385" s="2" t="s">
-        <v>883</v>
-      </c>
-      <c r="C385" s="2" t="s">
-        <v>884</v>
-      </c>
-      <c r="D385" s="1"/>
-      <c r="E385" s="7"/>
-      <c r="F385" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="G385" s="26" t="s">
-        <v>885</v>
-      </c>
-    </row>
-    <row r="386" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A386" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B386" s="2" t="s">
-        <v>886</v>
-      </c>
-      <c r="C386" s="2" t="s">
-        <v>887</v>
-      </c>
-      <c r="D386" s="1"/>
-      <c r="E386" s="7"/>
-      <c r="F386" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="G386" s="26" t="s">
-        <v>888</v>
-      </c>
-    </row>
-    <row r="387" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A387" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B387" s="2" t="s">
-        <v>889</v>
-      </c>
-      <c r="C387" s="2" t="s">
-        <v>890</v>
-      </c>
-      <c r="D387" s="1"/>
-      <c r="E387" s="7"/>
-      <c r="F387" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G387" s="26"/>
-    </row>
-    <row r="388" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A388" s="2" t="s">
-        <v>762</v>
-      </c>
-      <c r="B388" s="2" t="s">
-        <v>1007</v>
-      </c>
-      <c r="C388" s="2" t="s">
-        <v>1008</v>
       </c>
       <c r="D388" s="1"/>
       <c r="E388" s="7"/>
       <c r="F388" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G388" s="26"/>
-    </row>
-    <row r="389" spans="1:7" x14ac:dyDescent="0.35">
+        <v>10</v>
+      </c>
+      <c r="G388" s="26" t="s">
+        <v>881</v>
+      </c>
+    </row>
+    <row r="389" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A389" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B389" s="2" t="s">
-        <v>1009</v>
+        <v>882</v>
       </c>
       <c r="C389" s="2" t="s">
-        <v>1010</v>
+        <v>883</v>
       </c>
       <c r="D389" s="1"/>
-      <c r="E389" s="7" t="s">
-        <v>769</v>
-      </c>
+      <c r="E389" s="7"/>
       <c r="F389" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="G389" s="26"/>
-    </row>
-    <row r="390" spans="1:7" x14ac:dyDescent="0.35">
+        <v>14</v>
+      </c>
+      <c r="G389" s="26" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="390" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A390" s="2" t="s">
-        <v>762</v>
+        <v>758</v>
       </c>
       <c r="B390" s="2" t="s">
-        <v>1011</v>
+        <v>885</v>
       </c>
       <c r="C390" s="2" t="s">
-        <v>1012</v>
+        <v>886</v>
       </c>
       <c r="D390" s="1"/>
       <c r="E390" s="7"/>
@@ -11028,139 +11057,192 @@
       </c>
       <c r="G390" s="26"/>
     </row>
-    <row r="391" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A391" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B391" s="2" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C391" s="2" t="s">
+        <v>1004</v>
+      </c>
+      <c r="D391" s="1"/>
+      <c r="E391" s="7"/>
+      <c r="F391" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G391" s="26"/>
+    </row>
+    <row r="392" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A392" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B392" s="2" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C392" s="2" t="s">
+        <v>1006</v>
+      </c>
+      <c r="D392" s="1"/>
+      <c r="E392" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="F392" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G392" s="26"/>
+    </row>
+    <row r="393" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A393" s="2" t="s">
+        <v>758</v>
+      </c>
+      <c r="B393" s="2" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C393" s="2" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D393" s="1"/>
+      <c r="E393" s="7"/>
+      <c r="F393" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="G393" s="26"/>
+    </row>
+    <row r="394" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A394" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B394" s="2" t="s">
+        <v>888</v>
+      </c>
+      <c r="C394" s="2" t="s">
+        <v>889</v>
+      </c>
+      <c r="D394" s="7" t="s">
+        <v>890</v>
+      </c>
+      <c r="E394" s="7"/>
+      <c r="F394" s="25" t="s">
+        <v>20</v>
+      </c>
+      <c r="G394" s="26"/>
+    </row>
+    <row r="395" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A395" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B395" s="2" t="s">
         <v>891</v>
       </c>
-      <c r="B391" s="2" t="s">
+      <c r="C395" s="2" t="s">
         <v>892</v>
       </c>
-      <c r="C391" s="2" t="s">
+      <c r="D395" s="7" t="s">
         <v>893</v>
       </c>
-      <c r="D391" s="7" t="s">
+      <c r="E395" s="7"/>
+      <c r="F395" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G395" s="26"/>
+    </row>
+    <row r="396" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A396" s="2" t="s">
+        <v>887</v>
+      </c>
+      <c r="B396" s="2" t="s">
         <v>894</v>
       </c>
-      <c r="E391" s="7"/>
-      <c r="F391" s="25" t="s">
-        <v>20</v>
-      </c>
-      <c r="G391" s="26"/>
-    </row>
-    <row r="392" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A392" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="B392" s="2" t="s">
+      <c r="C396" s="2" t="s">
         <v>895</v>
       </c>
-      <c r="C392" s="2" t="s">
+      <c r="D396" s="1" t="s">
         <v>896</v>
       </c>
-      <c r="D392" s="7" t="s">
+      <c r="E396" s="7"/>
+      <c r="F396" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="G396" s="26"/>
+    </row>
+    <row r="397" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+      <c r="A397" s="17" t="s">
+        <v>887</v>
+      </c>
+      <c r="B397" s="17" t="s">
         <v>897</v>
       </c>
-      <c r="E392" s="7"/>
-      <c r="F392" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G392" s="26"/>
-    </row>
-    <row r="393" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A393" s="2" t="s">
-        <v>891</v>
-      </c>
-      <c r="B393" s="2" t="s">
+      <c r="C397" s="17" t="s">
         <v>898</v>
       </c>
-      <c r="C393" s="2" t="s">
+      <c r="D397" s="27"/>
+      <c r="E397" s="27"/>
+      <c r="F397" s="18" t="s">
         <v>899</v>
       </c>
-      <c r="D393" s="1" t="s">
+      <c r="G397" s="28"/>
+    </row>
+    <row r="398" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A398" t="s">
+        <v>887</v>
+      </c>
+      <c r="B398" t="s">
         <v>900</v>
       </c>
-      <c r="E393" s="7"/>
-      <c r="F393" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="G393" s="26"/>
-    </row>
-    <row r="394" spans="1:7" ht="29" x14ac:dyDescent="0.35">
-      <c r="A394" s="17" t="s">
-        <v>891</v>
-      </c>
-      <c r="B394" s="17" t="s">
+      <c r="C398" t="s">
         <v>901</v>
       </c>
-      <c r="C394" s="17" t="s">
-        <v>902</v>
-      </c>
-      <c r="D394" s="27"/>
-      <c r="E394" s="27"/>
-      <c r="F394" s="18" t="s">
-        <v>903</v>
-      </c>
-      <c r="G394" s="28"/>
-    </row>
-    <row r="395" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A395" t="s">
-        <v>891</v>
-      </c>
-      <c r="B395" t="s">
-        <v>904</v>
-      </c>
-      <c r="C395" t="s">
-        <v>905</v>
-      </c>
-      <c r="D395" s="7"/>
-      <c r="E395" s="7"/>
-      <c r="F395" t="s">
-        <v>29</v>
-      </c>
-      <c r="G395" s="26"/>
-    </row>
-    <row r="396" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A396" t="s">
-        <v>891</v>
-      </c>
-      <c r="B396" t="s">
-        <v>906</v>
-      </c>
-      <c r="C396" t="s">
-        <v>907</v>
-      </c>
-      <c r="D396" s="7" t="s">
-        <v>908</v>
-      </c>
-      <c r="E396" s="7"/>
-      <c r="F396" t="s">
-        <v>29</v>
-      </c>
-      <c r="G396" s="26"/>
-    </row>
-    <row r="397" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A397" t="s">
-        <v>891</v>
-      </c>
-      <c r="B397" t="s">
-        <v>909</v>
-      </c>
-      <c r="C397" t="s">
-        <v>910</v>
-      </c>
-      <c r="D397" s="7" t="s">
-        <v>911</v>
-      </c>
-      <c r="E397" s="7"/>
-      <c r="F397" t="s">
-        <v>20</v>
-      </c>
-      <c r="G397" s="26"/>
-    </row>
-    <row r="398" spans="1:7" x14ac:dyDescent="0.35">
       <c r="D398" s="7"/>
       <c r="E398" s="7"/>
+      <c r="F398" t="s">
+        <v>29</v>
+      </c>
       <c r="G398" s="26"/>
+    </row>
+    <row r="399" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A399" t="s">
+        <v>887</v>
+      </c>
+      <c r="B399" t="s">
+        <v>902</v>
+      </c>
+      <c r="C399" t="s">
+        <v>903</v>
+      </c>
+      <c r="D399" s="7" t="s">
+        <v>904</v>
+      </c>
+      <c r="E399" s="7"/>
+      <c r="F399" t="s">
+        <v>29</v>
+      </c>
+      <c r="G399" s="26"/>
+    </row>
+    <row r="400" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A400" t="s">
+        <v>887</v>
+      </c>
+      <c r="B400" t="s">
+        <v>905</v>
+      </c>
+      <c r="C400" t="s">
+        <v>906</v>
+      </c>
+      <c r="D400" s="7" t="s">
+        <v>907</v>
+      </c>
+      <c r="E400" s="7"/>
+      <c r="F400" t="s">
+        <v>20</v>
+      </c>
+      <c r="G400" s="26"/>
+    </row>
+    <row r="401" spans="4:7" x14ac:dyDescent="0.25">
+      <c r="D401" s="7"/>
+      <c r="E401" s="7"/>
+      <c r="G401" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -11171,162 +11253,162 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B19"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18.54296875" customWidth="1"/>
-    <col min="2" max="2" width="52.26953125" customWidth="1"/>
+    <col min="1" max="1" width="18.5703125" customWidth="1"/>
+    <col min="2" max="2" width="52.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>971</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
       <c r="B2" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>104</v>
       </c>
       <c r="B4" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+        <v>970</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>131</v>
       </c>
       <c r="B5" t="s">
-        <v>975</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>141</v>
       </c>
       <c r="B6" t="s">
-        <v>976</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>977</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>196</v>
       </c>
       <c r="B8" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+        <v>974</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>210</v>
       </c>
       <c r="B9" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+        <v>975</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>388</v>
       </c>
       <c r="B10" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>405</v>
       </c>
       <c r="B11" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>467</v>
       </c>
       <c r="B12" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>475</v>
       </c>
       <c r="B13" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>510</v>
       </c>
       <c r="B14" t="s">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>671</v>
+      </c>
+      <c r="B15" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>723</v>
+      </c>
+      <c r="B16" t="s">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>743</v>
+      </c>
+      <c r="B17" t="s">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>758</v>
+      </c>
+      <c r="B18" t="s">
         <v>984</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A15" t="s">
-        <v>675</v>
-      </c>
-      <c r="B15" t="s">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>887</v>
+      </c>
+      <c r="B19" t="s">
         <v>985</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>727</v>
-      </c>
-      <c r="B16" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A17" t="s">
-        <v>747</v>
-      </c>
-      <c r="B17" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A18" t="s">
-        <v>762</v>
-      </c>
-      <c r="B18" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
-      <c r="A19" t="s">
-        <v>891</v>
-      </c>
-      <c r="B19" t="s">
-        <v>989</v>
       </c>
     </row>
   </sheetData>
